--- a/data/job_matches.xlsx
+++ b/data/job_matches.xlsx
@@ -499,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M139"/>
+  <dimension ref="A1:M167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -757,9 +757,9 @@
           <t>Not stated in JD</t>
         </is>
       </c>
-      <c r="K4" s="7" t="inlineStr">
-        <is>
-          <t>New this run (2026-08-27 06:43 UTC)</t>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>From previous run</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -905,26 +905,26 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Applied AI Engineer (m/w/d)</t>
+          <t>AI/ML &amp; Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>SIXT</t>
+          <t>Jobgether</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Munich, Bavaria, Germany</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F7" s="4" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
@@ -933,12 +933,12 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>The candidate is a strong technical fit, possessing core specialization in agentic workflows, LangChain, Python, and scalable AI solutions which directly match SIXT's requirements for an Applied AI Engineer. Seniority aligns well with the hands-on engineering focus, though the job posting specifies fluent German which is a minor mismatch since the candidate's resume does not state German fluency.</t>
+          <t>The role requires extensive hands-on experience in GenAI, LLMs, RAG pipelines, NLP, and evaluation frameworks, which matches the candidate's core specialization and project background exceptionally well. Seniority requirements (8+ years of experience) also align closely with the candidate's 10 years of professional experience.</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>Yes - German required (see JD for exact level)</t>
+          <t>Not stated in JD</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="M7" s="6" t="inlineStr">
         <is>
-          <t>https://de.linkedin.com/jobs/view/applied-ai-engineer-m-w-d-at-sixt-4459317899?position=18&amp;pageNum=0&amp;refId=T%2F0KkBXL%2Fl%2B5Iv5tUGTY7Q%3D%3D&amp;trackingId=9xsjycSgyTNXBayiA7uUag%3D%3D</t>
+          <t>https://nl.linkedin.com/jobs/view/ai-ml-forward-deployed-engineer-at-jobgether-4458608966?position=30&amp;pageNum=0&amp;refId=oiBIn1Czflg0JjZjH5z0Lg%3D%3D&amp;trackingId=ICN2A0jAiRfL0Sl%2BL8jtWQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -968,26 +968,26 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Consultant (m/w/d) Data Science</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>R+V Versicherung</t>
+          <t>Sundayy</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Wiesbaden, Hesse, Germany</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
@@ -996,12 +996,12 @@
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>The role directly aligns with the candidate's core specialization in Generative AI, agentic systems, and Azure Cloud, matching his hands-on experience in Python and AI architectures. The seniority level (mehrjährige Berufserfahrung) is a strong fit for his 10+ years of experience.</t>
+          <t>The role requires building GenAI applications like assistant tools, knowledge bases, and conversational AI within an Azure environment, aligning perfectly with the candidate's core expertise in LangChain, RAG, and Azure OpenAI. Seniority also lines up well for an experienced AI engineer profile.</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>Yes - German required (see JD for exact level)</t>
+          <t>Not stated in JD</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="M8" s="6" t="inlineStr">
         <is>
-          <t>https://de.linkedin.com/jobs/view/consultant-m-w-d-data-science-at-r%2Bv-versicherung-4446657931?position=6&amp;pageNum=0&amp;refId=T%2F0KkBXL%2Fl%2B5Iv5tUGTY7Q%3D%3D&amp;trackingId=ge9b6YnCaLfUPNBvtlXfRw%3D%3D</t>
+          <t>https://nl.linkedin.com/jobs/view/ai-engineer-at-sundayy-4459683837?position=13&amp;pageNum=0&amp;refId=oiBIn1Czflg0JjZjH5z0Lg%3D%3D&amp;trackingId=CxWxp5aF0MawwmZwPbDSyQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -1031,17 +1031,17 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Applied AI Engineer (m/w/d)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Sundayy</t>
+          <t>SIXT</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Munich, Bavaria, Germany</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1059,12 +1059,12 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>The role heavily emphasizes GenAI, conversational AI, smart knowledge bases, and Microsoft Azure which directly match the candidate's core specialization in LLMs, RAG, and Azure OpenAI, with an appropriate senior-level alignment.</t>
+          <t>The candidate is a strong technical fit, possessing core specialization in agentic workflows, LangChain, Python, and scalable AI solutions which directly match SIXT's requirements for an Applied AI Engineer. Seniority aligns well with the hands-on engineering focus, though the job posting specifies fluent German which is a minor mismatch since the candidate's resume does not state German fluency.</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>Not stated in JD</t>
+          <t>Yes - German required (see JD for exact level)</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="M9" s="6" t="inlineStr">
         <is>
-          <t>https://nl.linkedin.com/jobs/view/ai-engineer-at-sundayy-4459186195?position=19&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=n67II6bPgk6xPxGFIQd19w%3D%3D</t>
+          <t>https://de.linkedin.com/jobs/view/applied-ai-engineer-m-w-d-at-sixt-4459317899?position=18&amp;pageNum=0&amp;refId=T%2F0KkBXL%2Fl%2B5Iv5tUGTY7Q%3D%3D&amp;trackingId=9xsjycSgyTNXBayiA7uUag%3D%3D</t>
         </is>
       </c>
     </row>
@@ -1094,17 +1094,17 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Data Scientist - Transaction Banking Data Domain</t>
+          <t>Consultant (m/w/d) Data Science</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>ABN AMRO Bank N.V.</t>
+          <t>R+V Versicherung</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Amsterdam, North Holland, Netherlands</t>
+          <t>Wiesbaden, Hesse, Germany</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>The role specifically focuses on Generative AI, LLMs, RAG, and AI Agents within a modern tech stack, aligning exceptionally well with the candidate's core specialization. Seniority is a solid match with the 6-8 years requirement against the candidate's 10+ years of experience.</t>
+          <t>The role directly aligns with the candidate's core specialization in Generative AI, agentic systems, and Azure Cloud, matching his hands-on experience in Python and AI architectures. The seniority level (mehrjährige Berufserfahrung) is a strong fit for his 10+ years of experience.</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>Not stated in JD</t>
+          <t>Yes - German required (see JD for exact level)</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="M10" s="6" t="inlineStr">
         <is>
-          <t>https://nl.linkedin.com/jobs/view/data-scientist-transaction-banking-data-domain-at-abn-amro-bank-n-v-4459153776?position=5&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=zQMYy8gDwNsARC45qT5ebg%3D%3D</t>
+          <t>https://de.linkedin.com/jobs/view/consultant-m-w-d-data-science-at-r%2Bv-versicherung-4446657931?position=6&amp;pageNum=0&amp;refId=T%2F0KkBXL%2Fl%2B5Iv5tUGTY7Q%3D%3D&amp;trackingId=ge9b6YnCaLfUPNBvtlXfRw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -1157,17 +1157,17 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>AI Engineer Consultant</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>Sundayy</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Aarhus, Central Denmark Region, Denmark</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>The candidate has a nearly identical technical stack matching the core requirements, including Generative AI, RAG, multi-agent systems, Azure, and Databricks. The only slight mismatch is the requirement for Danish language proficiency, though technically and experientially the profile is an exceptionally strong fit.</t>
+          <t>The role heavily emphasizes GenAI, conversational AI, smart knowledge bases, and Microsoft Azure which directly match the candidate's core specialization in LLMs, RAG, and Azure OpenAI, with an appropriate senior-level alignment.</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
@@ -1210,7 +1210,7 @@
       </c>
       <c r="M11" s="6" t="inlineStr">
         <is>
-          <t>https://dk.linkedin.com/jobs/view/ai-engineer-consultant-at-ibm-4446638850?position=3&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=bu43imu3DIyhHkKBFyKzMQ%3D%3D</t>
+          <t>https://nl.linkedin.com/jobs/view/ai-engineer-at-sundayy-4459186195?position=19&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=n67II6bPgk6xPxGFIQd19w%3D%3D</t>
         </is>
       </c>
     </row>
@@ -1220,17 +1220,17 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Data Scientist - Transaction Banking Data Domain</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>ai71</t>
+          <t>ABN AMRO Bank N.V.</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Abu Dhabi, Abu Dhabi Emirate, United Arab Emirates</t>
+          <t>Amsterdam, North Holland, Netherlands</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>The role matches the candidate's strong GenAI, LLMs, LangChain, and LangGraph specialization and 8+ years experience requirement. Minor deductions exist for specific fine-tuning (LoRA) or competitive programming preferences not heavily emphasized on the resume.</t>
+          <t>The role specifically focuses on Generative AI, LLMs, RAG, and AI Agents within a modern tech stack, aligning exceptionally well with the candidate's core specialization. Seniority is a solid match with the 6-8 years requirement against the candidate's 10+ years of experience.</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>Possible - relocation support mentioned, visa not explicit</t>
-        </is>
-      </c>
-      <c r="K12" s="7" t="inlineStr">
-        <is>
-          <t>New this run (2026-08-27 06:43 UTC)</t>
+          <t>Not stated in JD</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>From previous run</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="M12" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/senior-machine-learning-engineer-at-ai71-4459173576?position=7&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=ppLipnN13SHhYrjunrTYmA%3D%3D</t>
+          <t>https://nl.linkedin.com/jobs/view/data-scientist-transaction-banking-data-domain-at-abn-amro-bank-n-v-4459153776?position=5&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=zQMYy8gDwNsARC45qT5ebg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -1283,17 +1283,17 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Interim Data Scientist (m/w/d)</t>
+          <t>AI Engineer Consultant</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Michael Page</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>Cologne, North Rhine-Westphalia, Germany</t>
+          <t>Aarhus, Central Denmark Region, Denmark</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1302,7 +1302,7 @@
         </is>
       </c>
       <c r="F13" s="4" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
@@ -1311,12 +1311,12 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>The role aligns very well with the candidate's core specialization in LLMs, prompt engineering, and document extraction workflows using Python and Databricks. However, the score is slightly docked due to the interim/contract nature and the explicit requirement for fluent German language skills.</t>
+          <t>The candidate has a nearly identical technical stack matching the core requirements, including Generative AI, RAG, multi-agent systems, Azure, and Databricks. The only slight mismatch is the requirement for Danish language proficiency, though technically and experientially the profile is an exceptionally strong fit.</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>Yes - fluent/C1+ German explicitly required</t>
+          <t>Not stated in JD</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="M13" s="6" t="inlineStr">
         <is>
-          <t>https://de.linkedin.com/jobs/view/interim-data-scientist-m-w-d-at-michael-page-4459606063?position=10&amp;pageNum=0&amp;refId=T%2F0KkBXL%2Fl%2B5Iv5tUGTY7Q%3D%3D&amp;trackingId=wpbzTBfGmj4VgpsbFsCPlw%3D%3D</t>
+          <t>https://dk.linkedin.com/jobs/view/ai-engineer-consultant-at-ibm-4446638850?position=3&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=bu43imu3DIyhHkKBFyKzMQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -1346,17 +1346,17 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Forward Deployed AI Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Intellishore</t>
+          <t>ai71</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>Copenhagen, Capital Region of Denmark, Denmark</t>
+          <t>Abu Dhabi, Abu Dhabi Emirate, United Arab Emirates</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="F14" s="4" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
@@ -1374,17 +1374,17 @@
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>The role strongly aligns with the candidate's core specialization in applied generative AI, RAG, agentic workflows, and Azure cloud deployment, combined with strong client-facing stakeholder experience. However, it leans towards a consulting/forward-deployed model requiring full-stack backend/frontend engineering (Python/JavaScript) and system architecture beyond his strictly data-science-heavy background, resulting in a minor technical and functional fit gap.</t>
+          <t>The role matches the candidate's strong GenAI, LLMs, LangChain, and LangGraph specialization and 8+ years experience requirement. Minor deductions exist for specific fine-tuning (LoRA) or competitive programming preferences not heavily emphasized on the resume.</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>Yes - German required (see JD for exact level)</t>
+          <t>Not stated in JD</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>Not stated in JD</t>
+          <t>Possible - relocation support mentioned, visa not explicit</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1399,7 +1399,7 @@
       </c>
       <c r="M14" s="6" t="inlineStr">
         <is>
-          <t>https://dk.linkedin.com/jobs/view/forward-deployed-ai-engineer-at-intellishore-4459152169?position=9&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=%2F8E1AX%2BqrUaYyGRvSSoXlA%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/senior-machine-learning-engineer-at-ai71-4459173576?position=7&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=ppLipnN13SHhYrjunrTYmA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -1409,40 +1409,40 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Specialist</t>
+          <t>Artificial Intelligence Engineer</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>THRYVE</t>
+          <t>MPower Plus</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Zaandam, North Holland, Netherlands</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="F15" s="8" t="n">
-        <v>68</v>
-      </c>
-      <c r="G15" s="9" t="inlineStr">
-        <is>
-          <t>Below threshold</t>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>85</v>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>APPLY</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>The role focuses on NLP, LLMs, and Python development for custom AI and chatbot solutions, which aligns well with the candidate's core specialization in Generative AI and agentic workflows. However, the requirement for fluency in German and a slight mismatch in software engineering/DevOps balance pull the score down moderately.</t>
+          <t>The role aligns exceptionally well with the candidate's core specialization in production-level GenAI, RAG, agentic AI, LangChain, and Azure. The only minor mismatch is that the candidate has around 8+ years of data science/AI experience, whereas the role specifies 2-5 years, making him slightly overqualified.</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>Yes - German required (see JD for exact level)</t>
+          <t>Not stated in JD</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="M15" s="6" t="inlineStr">
         <is>
-          <t>https://de.linkedin.com/jobs/view/artificial-intelligence-specialist-at-thryve-4459322570?position=24&amp;pageNum=0&amp;refId=T%2F0KkBXL%2Fl%2B5Iv5tUGTY7Q%3D%3D&amp;trackingId=2lkuiNNfm1ldDWyfUviSiQ%3D%3D</t>
+          <t>https://nl.linkedin.com/jobs/view/artificial-intelligence-engineer-at-mpower-plus-4459696412?position=23&amp;pageNum=0&amp;refId=oiBIn1Czflg0JjZjH5z0Lg%3D%3D&amp;trackingId=aETrfscAqnZIhdOqHWjNzQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -1472,35 +1472,35 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Data &amp; AI Consultant</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Netlight</t>
+          <t>Vivid Resourcing</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Hamburg, Germany</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="F16" s="8" t="n">
-        <v>68</v>
-      </c>
-      <c r="G16" s="9" t="inlineStr">
-        <is>
-          <t>Below threshold</t>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>85</v>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>APPLY</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>The candidate has strong technical skills in Python, cloud platforms, and modern AI/ML systems that align well with Netlight's consulting focus on data and AI solutions. However, the role requires only 2-3 years of experience, whereas the candidate brings 10+ years of seniority, creating a potential experience mismatch.</t>
+          <t>The role is an exceptionally strong match, requiring core skills in LLMs, Generative AI, production deployment, and Python, which align directly with the candidate's specialization and recent projects. The seniority requirement of 5+ years fits well with the candidate's 10 years of total experience.</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="M16" s="6" t="inlineStr">
         <is>
-          <t>https://de.linkedin.com/jobs/view/data-ai-consultant-at-netlight-4457267225?position=15&amp;pageNum=0&amp;refId=T%2F0KkBXL%2Fl%2B5Iv5tUGTY7Q%3D%3D&amp;trackingId=4N9yZsL4vr3kG7uXSjmfcw%3D%3D</t>
+          <t>https://nl.linkedin.com/jobs/view/senior-ai-engineer-at-vivid-resourcing-4459659771?position=18&amp;pageNum=0&amp;refId=oiBIn1Czflg0JjZjH5z0Lg%3D%3D&amp;trackingId=7AxnixAktWvMxhhSHmEC%2Bw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -1535,17 +1535,17 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Creative AI Technologist</t>
+          <t>Interim Data Scientist (m/w/d)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>ACT.agency</t>
+          <t>Michael Page</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Amsterdam, North Holland, Netherlands</t>
+          <t>Cologne, North Rhine-Westphalia, Germany</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1553,27 +1553,27 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F17" s="8" t="n">
-        <v>68</v>
-      </c>
-      <c r="G17" s="9" t="inlineStr">
-        <is>
-          <t>Below threshold</t>
+      <c r="F17" s="4" t="n">
+        <v>75</v>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>APPLY</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>The candidate has a strong GenAI specialization with extensive hands-on experience in building RAG pipelines, multi-agent systems, and Python development, matching the core technical requirements. However, the role requires specific front-end/full-stack tech stack exposure (React, Next.js, TypeScript), deep familiarity with creative tooling, and an advertising/content agency background which falls outside the candidate's core enterprise data science profile.</t>
+          <t>The role aligns very well with the candidate's core specialization in LLMs, prompt engineering, and document extraction workflows using Python and Databricks. However, the score is slightly docked due to the interim/contract nature and the explicit requirement for fluent German language skills.</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>Not stated in JD</t>
+          <t>Yes - fluent/C1+ German explicitly required</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>Possible - relocation support mentioned, visa not explicit</t>
+          <t>Not stated in JD</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1588,7 +1588,7 @@
       </c>
       <c r="M17" s="6" t="inlineStr">
         <is>
-          <t>https://nl.linkedin.com/jobs/view/creative-ai-technologist-at-act-agency-4457224486?position=30&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=yEglHgtaLJcIUGsBXtZ8rg%3D%3D</t>
+          <t>https://de.linkedin.com/jobs/view/interim-data-scientist-m-w-d-at-michael-page-4459606063?position=10&amp;pageNum=0&amp;refId=T%2F0KkBXL%2Fl%2B5Iv5tUGTY7Q%3D%3D&amp;trackingId=wpbzTBfGmj4VgpsbFsCPlw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -1598,17 +1598,17 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Principal AI Consultant (m/f/d)</t>
+          <t>Forward Deployed AI Engineer</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>ClearPeaks</t>
+          <t>Intellishore</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Abu Dhabi, Abu Dhabi Emirate, United Arab Emirates</t>
+          <t>Copenhagen, Capital Region of Denmark, Denmark</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1616,32 +1616,32 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F18" s="8" t="n">
-        <v>68</v>
-      </c>
-      <c r="G18" s="9" t="inlineStr">
-        <is>
-          <t>Below threshold</t>
+      <c r="F18" s="4" t="n">
+        <v>75</v>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>APPLY</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>The candidate has strong technical alignment with the role's requirements in GenAI, RAG, agentic applications, and Python (10 years total experience, matching the 7+ years required). However, the role is a Principal-level consultancy position requiring extensive client-facing leadership and team management, whereas the candidate's current title is Lead Data Scientist, making it a slight seniority stretch.</t>
+          <t>The role strongly aligns with the candidate's core specialization in applied generative AI, RAG, agentic workflows, and Azure cloud deployment, combined with strong client-facing stakeholder experience. However, it leans towards a consulting/forward-deployed model requiring full-stack backend/frontend engineering (Python/JavaScript) and system architecture beyond his strictly data-science-heavy background, resulting in a minor technical and functional fit gap.</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>Not stated in JD</t>
+          <t>Yes - German required (see JD for exact level)</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>Yes - explicitly stated in JD</t>
-        </is>
-      </c>
-      <c r="K18" s="7" t="inlineStr">
-        <is>
-          <t>New this run (2026-08-27 06:43 UTC)</t>
+          <t>Not stated in JD</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>From previous run</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="M18" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/principal-ai-consultant-m-f-d-at-clearpeaks-4414212566?position=10&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=9VTjBjH6AiNyYuNhMg0BOA%3D%3D</t>
+          <t>https://dk.linkedin.com/jobs/view/forward-deployed-ai-engineer-at-intellishore-4459152169?position=9&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=%2F8E1AX%2BqrUaYyGRvSSoXlA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -1661,17 +1661,17 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>GenAI Engineer - Assetization Team</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>HireAlpha</t>
+          <t>Nationale-Nederlanden</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>Abu Dhabi Emirate, United Arab Emirates</t>
+          <t>The Hague, South Holland, Netherlands</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1679,17 +1679,17 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="F19" s="8" t="n">
-        <v>68</v>
-      </c>
-      <c r="G19" s="9" t="inlineStr">
-        <is>
-          <t>Below threshold</t>
+      <c r="F19" s="4" t="n">
+        <v>75</v>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>APPLY</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>The role requires 5 years of experience in data science and machine learning, which aligns well with the candidate's 10+ years of background. However, the job is a general classical machine learning and MLOps position with only brief, optional mentions of generative AI or LLMs, whereas the candidate is heavily specialized in GenAI, LangChain, and multi-agent RAG systems.</t>
+          <t>The candidate has strong direct experience with the core GenAI tech stack requested, including LangChain, LangGraph, and Azure cloud deployment of AI solutions. However, the seniority match is slightly misaligned as the role asks for 2-5 years of experience while the candidate has 10+ years (Lead level).</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
@@ -1702,9 +1702,9 @@
           <t>Not stated in JD</t>
         </is>
       </c>
-      <c r="K19" s="7" t="inlineStr">
-        <is>
-          <t>New this run (2026-08-27 06:43 UTC)</t>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>From previous run</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="M19" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/data-scientist-at-hirealpha-4458350452?position=1&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=abjLBGKW0FxFG3xv5sDJBQ%3D%3D</t>
+          <t>https://nl.linkedin.com/jobs/view/genai-engineer-assetization-team-at-nationale-nederlanden-4432242825?position=25&amp;pageNum=0&amp;refId=oiBIn1Czflg0JjZjH5z0Lg%3D%3D&amp;trackingId=L85%2FZt%2BbuLdXBbTQ0gv5IA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -1724,40 +1724,40 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Machine Learning Researcher</t>
+          <t>Senior Engineer - AI / MACHINE LEARNING</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>THRYVE</t>
+          <t>Conjugate Consulting</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Dubai, United Arab Emirates</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="F20" s="8" t="n">
-        <v>65</v>
-      </c>
-      <c r="G20" s="9" t="inlineStr">
-        <is>
-          <t>Below threshold</t>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>75</v>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>APPLY</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>The role focuses on applied AI, prototyping, and intelligent assistants which aligns reasonably with the candidate's strong GenAI and agentic workflow background. However, it leans heavily towards a traditional ML researcher/engineer profile requiring PyTorch/TensorFlow and a Master's or PhD, making it a moderate rather than ideal fit.</t>
+          <t>The candidate has a strong match in Generative AI, LLMs, NLP, and agentic systems, aligning well with the technical focus of the senior engineering role. However, the role is a broad talent network/consulting listing with leadership expectations in Dubai, and the candidate's primary experience is as a Lead Data Scientist rather than a senior core engineering/infrastructure leader.</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>Yes - German required (see JD for exact level)</t>
+          <t>Not stated in JD</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1765,9 +1765,9 @@
           <t>Not stated in JD</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>From previous run</t>
+      <c r="K20" s="7" t="inlineStr">
+        <is>
+          <t>New this run (2026-08-27 15:40 UTC)</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="M20" s="6" t="inlineStr">
         <is>
-          <t>https://de.linkedin.com/jobs/view/machine-learning-researcher-at-thryve-4459314646?position=28&amp;pageNum=0&amp;refId=T%2F0KkBXL%2Fl%2B5Iv5tUGTY7Q%3D%3D&amp;trackingId=mCVd91CgmWUGtWYqsfkNEg%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/senior-engineer-ai-machine-learning-at-conjugate-consulting-4459669877?position=3&amp;pageNum=0&amp;refId=50H6yCrEXIuhgr6eqEojNg%3D%3D&amp;trackingId=HOTLlJuvnEYPYYvZpFnskA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -1787,17 +1787,17 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>KI Engineer (d/w/m)</t>
+          <t>Artificial Intelligence Specialist</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Plan International Deutschland e.V.</t>
+          <t>THRYVE</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>Hamburg, Hamburg, Germany</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1806,7 +1806,7 @@
         </is>
       </c>
       <c r="F21" s="8" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="G21" s="9" t="inlineStr">
         <is>
@@ -1815,12 +1815,12 @@
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>The role involves direct hands-on responsibilities for building and operating GenAI workflows, LLM platforms, and RAG architectures, which aligns well with the candidate's core specialization. However, the seniority is slightly below the candidate's 10+ years of experience (requiring around 5 years), and the posting explicitly requires C1-level German fluency, which the candidate does not possess.</t>
+          <t>The role focuses on NLP, LLMs, and Python development for custom AI and chatbot solutions, which aligns well with the candidate's core specialization in Generative AI and agentic workflows. However, the requirement for fluency in German and a slight mismatch in software engineering/DevOps balance pull the score down moderately.</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>Yes - fluent/C1+ German explicitly required</t>
+          <t>Yes - German required (see JD for exact level)</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="M21" s="6" t="inlineStr">
         <is>
-          <t>https://de.linkedin.com/jobs/view/ki-engineer-d-w-m-at-plan-international-deutschland-e-v-4457949243?position=25&amp;pageNum=0&amp;refId=T%2F0KkBXL%2Fl%2B5Iv5tUGTY7Q%3D%3D&amp;trackingId=NLVaEk9SoB7Ww3toHl7GGw%3D%3D</t>
+          <t>https://de.linkedin.com/jobs/view/artificial-intelligence-specialist-at-thryve-4459322570?position=24&amp;pageNum=0&amp;refId=T%2F0KkBXL%2Fl%2B5Iv5tUGTY7Q%3D%3D&amp;trackingId=2lkuiNNfm1ldDWyfUviSiQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -1850,26 +1850,26 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Forward Deployed AI Integrator , Field Engineering</t>
+          <t>Data &amp; AI Consultant</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Amazon Web Services (AWS)</t>
+          <t>Netlight</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>Dubai, Dubai, United Arab Emirates</t>
+          <t>Hamburg, Germany</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F22" s="8" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>The role requires hands-on GenAI integration, workflow automation, and agentic tooling, aligning well with the candidate's strong background in LangChain, LangGraph, and RAG. However, it leans more toward field engineering, technical program management, and operational enablement rather than core model development or data science leadership, and the candidate's 10+ years of experience is slightly overqualified for a 3+ years requirement.</t>
+          <t>The candidate has strong technical skills in Python, cloud platforms, and modern AI/ML systems that align well with Netlight's consulting focus on data and AI solutions. However, the role requires only 2-3 years of experience, whereas the candidate brings 10+ years of seniority, creating a potential experience mismatch.</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
@@ -1903,7 +1903,7 @@
       </c>
       <c r="M22" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/forward-deployed-ai-integrator-field-engineering-at-amazon-web-services-aws-4459657890?position=17&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=atAxpZN9jwvhmhmDyzC8IQ%3D%3D</t>
+          <t>https://de.linkedin.com/jobs/view/data-ai-consultant-at-netlight-4457267225?position=15&amp;pageNum=0&amp;refId=T%2F0KkBXL%2Fl%2B5Iv5tUGTY7Q%3D%3D&amp;trackingId=4N9yZsL4vr3kG7uXSjmfcw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -1913,17 +1913,17 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Creative AI Technologist</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Acrisure Netherlands</t>
+          <t>ACT.agency</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>Alkmaar, North Holland, Netherlands</t>
+          <t>Amsterdam, North Holland, Netherlands</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1932,7 +1932,7 @@
         </is>
       </c>
       <c r="F23" s="8" t="n">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="G23" s="9" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>The role involves building LLM solutions, AI agents, and RAG architectures alongside data engineering tasks, aligning well with the candidate's core GenAI and Python specialization. However, the position is primarily titled Data Engineer with a required 3-5 years of experience, representing a slight seniority and role-definition mismatch for a Lead Data Scientist with 10+ years of experience.</t>
+          <t>The candidate has a strong GenAI specialization with extensive hands-on experience in building RAG pipelines, multi-agent systems, and Python development, matching the core technical requirements. However, the role requires specific front-end/full-stack tech stack exposure (React, Next.js, TypeScript), deep familiarity with creative tooling, and an advertising/content agency background which falls outside the candidate's core enterprise data science profile.</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>Not stated in JD</t>
+          <t>Possible - relocation support mentioned, visa not explicit</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="M23" s="6" t="inlineStr">
         <is>
-          <t>https://nl.linkedin.com/jobs/view/data-engineer-at-acrisure-netherlands-4435689555?position=20&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=LJAUvNH2xtcog%2BwAhWKWEA%3D%3D</t>
+          <t>https://nl.linkedin.com/jobs/view/creative-ai-technologist-at-act-agency-4457224486?position=30&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=yEglHgtaLJcIUGsBXtZ8rg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -1976,17 +1976,17 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Senior AI Engineer – AI Centre of Excellence</t>
+          <t>Principal AI Consultant (m/f/d)</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Saxo Bank</t>
+          <t>ClearPeaks</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>Copenhagen, Capital Region of Denmark, Denmark</t>
+          <t>Abu Dhabi, Abu Dhabi Emirate, United Arab Emirates</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1995,7 +1995,7 @@
         </is>
       </c>
       <c r="F24" s="8" t="n">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="G24" s="9" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>The candidate has strong direct experience with production LLM/agent work, RAG, and Azure OpenAI within financial services, perfectly matching the domain and core GenAI requirements. However, the role heavily emphasizes C#/.NET enterprise development and Microsoft Copilot Studio/Power Platform integrations, which are outside the candidate's primary Python-centric stack, creating a notable tech-stack mismatch.</t>
+          <t>The candidate has strong technical alignment with the role's requirements in GenAI, RAG, agentic applications, and Python (10 years total experience, matching the 7+ years required). However, the role is a Principal-level consultancy position requiring extensive client-facing leadership and team management, whereas the candidate's current title is Lead Data Scientist, making it a slight seniority stretch.</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>Not stated in JD</t>
+          <t>Yes - explicitly stated in JD</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -2029,7 +2029,7 @@
       </c>
       <c r="M24" s="6" t="inlineStr">
         <is>
-          <t>https://dk.linkedin.com/jobs/view/senior-ai-engineer-%E2%80%93-ai-centre-of-excellence-at-saxo-bank-4423203071?position=19&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=oK4IPYd2VWkgx4cBmked5A%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/principal-ai-consultant-m-f-d-at-clearpeaks-4414212566?position=10&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=9VTjBjH6AiNyYuNhMg0BOA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -2039,26 +2039,26 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Consultant Business &amp; AI Insights (m/w/d) in Stuttgart</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>HireAlpha</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>Stuttgart, Baden-Württemberg, Germany</t>
+          <t>Abu Dhabi Emirate, United Arab Emirates</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F25" s="8" t="n">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="G25" s="9" t="inlineStr">
         <is>
@@ -2067,12 +2067,12 @@
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>The role is a junior-to-mid level consulting position ("Consultant") focusing broadly on BI, data analytics, and general AI, which is a significant seniority mismatch for a Lead Data Scientist with 10+ years of experience. While it mentions GenAI and RAG frameworks as nice-to-haves, the day-to-day work is heavily weighted toward general analytics consulting rather than advanced agentic AI specialization.</t>
+          <t>The role requires 5 years of experience in data science and machine learning, which aligns well with the candidate's 10+ years of background. However, the job is a general classical machine learning and MLOps position with only brief, optional mentions of generative AI or LLMs, whereas the candidate is heavily specialized in GenAI, LangChain, and multi-agent RAG systems.</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>Yes - fluent/C1+ German explicitly required</t>
+          <t>Not stated in JD</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -2092,7 +2092,7 @@
       </c>
       <c r="M25" s="6" t="inlineStr">
         <is>
-          <t>https://de.linkedin.com/jobs/view/consultant-business-ai-insights-m-w-d-in-stuttgart-at-deloitte-4440569165?position=20&amp;pageNum=0&amp;refId=T%2F0KkBXL%2Fl%2B5Iv5tUGTY7Q%3D%3D&amp;trackingId=WIf1oxbjDsUKKiZvxr62ig%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/data-scientist-at-hirealpha-4458350452?position=1&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=abjLBGKW0FxFG3xv5sDJBQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -2102,26 +2102,26 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Senior Manager - Martech</t>
+          <t>Agentic AI engineer</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Astra Tech</t>
+          <t>Xccelerated | Part of Xebia</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>Dubai, Dubai, United Arab Emirates</t>
+          <t>Utrecht Area</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F26" s="8" t="n">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="G26" s="9" t="inlineStr">
         <is>
@@ -2130,7 +2130,7 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>The role is a Senior Manager of Martech focusing on marketing tech stacks, CDPs, and CRM operations rather than a dedicated GenAI, LLM, or agentic AI engineering role, making the domain fit a weaker match. However, the candidate's 10+ years of experience aligns well with the 7-10+ years seniority requirement, and the position touches on predictive modeling and internal AI tooling.</t>
+          <t>The candidate has strong direct alignment with the core Generative AI, LLM, and agentic framework requirements (using LangChain and LangGraph for multi-agent workflows) and enterprise production experience. However, the role heavily emphasizes heavy software engineering, platform engineering, and infrastructure automation/DevOps (Terraform/Bicep), which represents a partial technical mismatch with the candidate's data science and analytics heavy background.</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="M26" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/senior-manager-martech-at-astra-tech-4457903179?position=12&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=9UstVcnD5je41ZfhWPt1AQ%3D%3D</t>
+          <t>https://nl.linkedin.com/jobs/view/agentic-ai-engineer-at-xccelerated-part-of-xebia-4459668536?position=27&amp;pageNum=0&amp;refId=oiBIn1Czflg0JjZjH5z0Lg%3D%3D&amp;trackingId=DM2xqwYLrSMl03X4FAANaw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -2165,17 +2165,17 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Principal AI Engineer</t>
+          <t>AI engineer and innovator</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>A.P. Moller - Maersk</t>
+          <t>FULL FORCE DIGITAL</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>Copenhagen Metropolitan Area</t>
+          <t>Naarden, North Holland, Netherlands</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -2184,7 +2184,7 @@
         </is>
       </c>
       <c r="F27" s="8" t="n">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="G27" s="9" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>The role strongly features agentic AI and multi-agent systems which align well with the candidate's core specialization, but it is a Principal-level technical leadership position requiring deep expertise in Operations Research, mathematical programming, and optimization solvers that exceed the candidate's profile.</t>
+          <t>The role requires building AI infrastructures, agents, and workflows which aligns exceptionally well with the candidate's core specialization in LangGraph, multi-agent orchestration, and LLM applications. However, the score is slightly adjusted down due to preferred tools mentioned (Crew AI, Make.com, Microsoft Foundry) that diverge from his specific Azure OpenAI/LangChain stack, and a geographic mismatch requirement (Netherlands vs candidate in India).</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
@@ -2218,7 +2218,7 @@
       </c>
       <c r="M27" s="6" t="inlineStr">
         <is>
-          <t>https://dk.linkedin.com/jobs/view/principal-ai-engineer-at-a-p-moller-maersk-4445976056?position=8&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=cXORh69SWuwKg77z4%2FjXOA%3D%3D</t>
+          <t>https://nl.linkedin.com/jobs/view/ai-engineer-and-innovator-at-full-force-digital-4459197906?position=12&amp;pageNum=0&amp;refId=oiBIn1Czflg0JjZjH5z0Lg%3D%3D&amp;trackingId=yu3IoKXV%2F%2FaEFXp8JQdeUA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -2228,26 +2228,26 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Principle AI Engineer</t>
+          <t>AI Technical Lead</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Analog</t>
+          <t>Fundamentl</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>Abu Dhabi, Abu Dhabi Emirate, United Arab Emirates</t>
+          <t>Dubai, United Arab Emirates</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F28" s="8" t="n">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="G28" s="9" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>The role requires a Principal AI Engineer to lead responsible AI standards, model evaluation, and governance in high-stakes domains like defense, which aligns well with the candidate's technical breadth and domain background in finance. However, the seniority is a mismatch as the candidate is at a Lead level rather than Principal, and the location requirement (Abu Dhabi) does not align with the candidate's target region.</t>
+          <t>The role perfectly matches the candidate's core specialization in Generative AI, agentic systems, LangGraph, and RAG architectures. However, there is a minor seniority mismatch as the position explicitly requires 15+ years of experience while the candidate has 10 years.</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="K28" s="7" t="inlineStr">
         <is>
-          <t>New this run (2026-08-27 06:43 UTC)</t>
+          <t>New this run (2026-08-27 15:40 UTC)</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="M28" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/principle-ai-engineer-at-analog-4457965112?position=22&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=9BE6FaPZTeRRBQuVWNoE5A%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/ai-technical-lead-at-fundamentl-4459848200?position=13&amp;pageNum=0&amp;refId=50H6yCrEXIuhgr6eqEojNg%3D%3D&amp;trackingId=2DlipS%2Bi2EfsUVi9eE28fg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -2291,26 +2291,26 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Research Engineer/Technician in the Division of Science (Computer Science) - Dr. Nizar Habash</t>
+          <t>AI Technical Lead / AI Solution Architect</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>New York University Abu Dhabi</t>
+          <t>Pink Camel Recruitment</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>Abu Dhabi, Abu Dhabi Emirate, United Arab Emirates</t>
+          <t>Dubai, United Arab Emirates</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F29" s="8" t="n">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="G29" s="9" t="inlineStr">
         <is>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>The role focuses heavily on academic and applied Natural Language Processing, computational linguistics, and research tool development at an academic lab (CAMeL Lab), which overlaps with the candidate's NLP background. However, it is an academic research engineering position rather than a commercial GenAI/LLM/agentic architecture role, and expects academic publication experience which is not the candidate's primary focus.</t>
+          <t>The candidate has strong technical alignment with the role's requirements in Generative AI, LLMs, LangChain, LangGraph, and Azure cloud technologies, combined with relevant financial domain experience. However, there is a seniority and experience mismatch as the role requests 14+ years of overall IT experience while the candidate has around 10 years, making it a moderately strong but slightly senior-heavy fit.</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
@@ -2329,12 +2329,12 @@
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>Possible - relocation support mentioned, visa not explicit</t>
+          <t>Not stated in JD</t>
         </is>
       </c>
       <c r="K29" s="7" t="inlineStr">
         <is>
-          <t>New this run (2026-08-27 06:43 UTC)</t>
+          <t>New this run (2026-08-27 15:40 UTC)</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
@@ -2344,7 +2344,7 @@
       </c>
       <c r="M29" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/research-engineer-technician-in-the-division-of-science-computer-science-dr-nizar-habash-at-new-york-university-abu-dhabi-4432261664?position=15&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=Eg%2BhyoQTsgcu3W8ar6ARQw%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/ai-technical-lead-ai-solution-architect-at-pink-camel-recruitment-4458607973?position=9&amp;pageNum=0&amp;refId=50H6yCrEXIuhgr6eqEojNg%3D%3D&amp;trackingId=rXMKDRzY3rMebJ%2FkXWMHcA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -2354,17 +2354,17 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>AI Solution Lead</t>
+          <t>Machine Learning Researcher</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Royal Wagenborg</t>
+          <t>THRYVE</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>Delfzijl, Groningen, Netherlands</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -2373,7 +2373,7 @@
         </is>
       </c>
       <c r="F30" s="8" t="n">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="G30" s="9" t="inlineStr">
         <is>
@@ -2382,12 +2382,12 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>The role explicitly highlights a use case for an AI search engine over documentation, aligning with the candidate's core RAG and Azure AI Search expertise. However, the position focuses heavily on classical ML, time-series analysis, IoT, and industrial/OT environments, which are only peripheral to the candidate's deep Generative AI and agentic specialization.</t>
+          <t>The role focuses on applied AI, prototyping, and intelligent assistants which aligns reasonably with the candidate's strong GenAI and agentic workflow background. However, it leans heavily towards a traditional ML researcher/engineer profile requiring PyTorch/TensorFlow and a Master's or PhD, making it a moderate rather than ideal fit.</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>Not stated in JD</t>
+          <t>Yes - German required (see JD for exact level)</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
@@ -2407,7 +2407,7 @@
       </c>
       <c r="M30" s="6" t="inlineStr">
         <is>
-          <t>https://nl.linkedin.com/jobs/view/ai-solution-lead-at-royal-wagenborg-4457954118?position=14&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=vxrN54FA7uiALBltM74joA%3D%3D</t>
+          <t>https://de.linkedin.com/jobs/view/machine-learning-researcher-at-thryve-4459314646?position=28&amp;pageNum=0&amp;refId=T%2F0KkBXL%2Fl%2B5Iv5tUGTY7Q%3D%3D&amp;trackingId=mCVd91CgmWUGtWYqsfkNEg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -2417,26 +2417,26 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Python Software Engineer -  AI team</t>
+          <t>KI Engineer (d/w/m)</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Channable</t>
+          <t>Plan International Deutschland e.V.</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>Utrecht, Utrecht, Netherlands</t>
+          <t>Hamburg, Hamburg, Germany</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F31" s="8" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="G31" s="9" t="inlineStr">
         <is>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>This role is primarily a Python Software Engineer position focusing on data processing, backend web frameworks, and e-commerce infrastructure rather than advanced GenAI, LLMs, or agentic architectures. While the candidate has over 10 years of experience and strong GenAI expertise, the heavy emphasis on traditional software engineering infrastructure and lower seniority requirements makes this a weaker fit.</t>
+          <t>The role involves direct hands-on responsibilities for building and operating GenAI workflows, LLM platforms, and RAG architectures, which aligns well with the candidate's core specialization. However, the seniority is slightly below the candidate's 10+ years of experience (requiring around 5 years), and the posting explicitly requires C1-level German fluency, which the candidate does not possess.</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>Not stated in JD</t>
+          <t>Yes - fluent/C1+ German explicitly required</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="M31" s="6" t="inlineStr">
         <is>
-          <t>https://nl.linkedin.com/jobs/view/python-software-engineer-ai-team-at-channable-4454702624?position=17&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=C0S4tD8hFUIyS0haOgnRyg%3D%3D</t>
+          <t>https://de.linkedin.com/jobs/view/ki-engineer-d-w-m-at-plan-international-deutschland-e-v-4457949243?position=25&amp;pageNum=0&amp;refId=T%2F0KkBXL%2Fl%2B5Iv5tUGTY7Q%3D%3D&amp;trackingId=NLVaEk9SoB7Ww3toHl7GGw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -2480,26 +2480,26 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Data engineer til Hvidvasksekretariatet - Danmarks finansielle efterretningsenhed</t>
+          <t>Forward Deployed AI Integrator , Field Engineering</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>Politi</t>
+          <t>Amazon Web Services (AWS)</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>Copenhagen, Capital Region of Denmark, Denmark</t>
+          <t>Dubai, Dubai, United Arab Emirates</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F32" s="8" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="G32" s="9" t="inlineStr">
         <is>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>The role is primarily a Data Engineering position focused on ETL, databases, and financial crime analysis platforms, which only touches LLMs as a minor passing mention rather than centering on core GenAI/agentic specialization. However, the candidate's strong Python, SQL, and banking domain background provide some relevant foundational overlap.</t>
+          <t>The role requires hands-on GenAI integration, workflow automation, and agentic tooling, aligning well with the candidate's strong background in LangChain, LangGraph, and RAG. However, it leans more toward field engineering, technical program management, and operational enablement rather than core model development or data science leadership, and the candidate's 10+ years of experience is slightly overqualified for a 3+ years requirement.</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="M32" s="6" t="inlineStr">
         <is>
-          <t>https://dk.linkedin.com/jobs/view/data-engineer-til-hvidvasksekretariatet-danmarks-finansielle-efterretningsenhed-at-politi-4457966663?position=10&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=YZMqDSG0b%2BEmx5Ptpd%2FXGw%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/forward-deployed-ai-integrator-field-engineering-at-amazon-web-services-aws-4459657890?position=17&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=atAxpZN9jwvhmhmDyzC8IQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -2543,17 +2543,17 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Regulatory Compliance Manager</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>Bybit</t>
+          <t>Acrisure Netherlands</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>Abu Dhabi Emirate, United Arab Emirates</t>
+          <t>Alkmaar, North Holland, Netherlands</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -2562,7 +2562,7 @@
         </is>
       </c>
       <c r="F33" s="8" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="G33" s="9" t="inlineStr">
         <is>
@@ -2571,7 +2571,7 @@
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>The role involves building AI-enabled compliance and RAG/LLM workflows, which moderately aligns with the candidate's core GenAI and vector search expertise. However, it requires a primary background in regulatory compliance and financial services law rather than data science, making it a weaker domain and seniority fit.</t>
+          <t>The role involves building LLM solutions, AI agents, and RAG architectures alongside data engineering tasks, aligning well with the candidate's core GenAI and Python specialization. However, the position is primarily titled Data Engineer with a required 3-5 years of experience, representing a slight seniority and role-definition mismatch for a Lead Data Scientist with 10+ years of experience.</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
@@ -2584,9 +2584,9 @@
           <t>Not stated in JD</t>
         </is>
       </c>
-      <c r="K33" s="7" t="inlineStr">
-        <is>
-          <t>New this run (2026-08-27 06:43 UTC)</t>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>From previous run</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="M33" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/regulatory-compliance-manager-at-bybit-4449794088?position=25&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=jQJTq4KHiygix7eADF6Ovw%3D%3D</t>
+          <t>https://nl.linkedin.com/jobs/view/data-engineer-at-acrisure-netherlands-4435689555?position=20&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=LJAUvNH2xtcog%2BwAhWKWEA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -2606,26 +2606,26 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Data Scientist - AI/ML (Remote)</t>
+          <t>Senior AI Engineer – AI Centre of Excellence</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>Quik Hire Staffing</t>
+          <t>Saxo Bank</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>Copenhagen, Capital Region of Denmark, Denmark</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F34" s="8" t="n">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="G34" s="9" t="inlineStr">
         <is>
@@ -2634,7 +2634,7 @@
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>The role is a general classical machine learning and MLOps position focused on traditional classification, regression, and clustering tasks using scikit-learn or PyTorch, rather than leveraging the candidate's core specialization in GenAI, LLMs, LangChain, and agentic workflows. While the candidate's Python and Azure cloud background align well, the technical scope is a weaker fit.</t>
+          <t>The candidate has strong direct experience with production LLM/agent work, RAG, and Azure OpenAI within financial services, perfectly matching the domain and core GenAI requirements. However, the role heavily emphasizes C#/.NET enterprise development and Microsoft Copilot Studio/Power Platform integrations, which are outside the candidate's primary Python-centric stack, creating a notable tech-stack mismatch.</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
@@ -2647,9 +2647,9 @@
           <t>Not stated in JD</t>
         </is>
       </c>
-      <c r="K34" s="7" t="inlineStr">
-        <is>
-          <t>New this run (2026-08-27 06:43 UTC)</t>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>From previous run</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="M34" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/data-scientist-ai-ml-remote-at-quik-hire-staffing-4459642594?position=9&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=5JzrtHYdDMeIkrN4Gn8eng%3D%3D</t>
+          <t>https://dk.linkedin.com/jobs/view/senior-ai-engineer-%E2%80%93-ai-centre-of-excellence-at-saxo-bank-4423203071?position=19&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=oK4IPYd2VWkgx4cBmked5A%3D%3D</t>
         </is>
       </c>
     </row>
@@ -2669,17 +2669,17 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Machine Learning (AI) Engineer (Hybrid)</t>
+          <t>Lead AI Engineer (PhD)</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>Quik Hire Staffing</t>
+          <t>Talent Seed</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Dubai, Dubai, United Arab Emirates</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -2688,7 +2688,7 @@
         </is>
       </c>
       <c r="F35" s="8" t="n">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="G35" s="9" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>The role focuses heavily on traditional deep learning frameworks (TensorFlow, PyTorch), MLOps, and model training rather than the candidate's core specialization in Generative AI, LLMs, and agentic workflows. However, it is still a technical AI/ML engineering position that aligns reasonably well in terms of experience level.</t>
+          <t>The candidate matches the 8+ years of experience, fintech domain background, and hands-on GenAI/ML engineering skill set. However, the role strictly requires a PhD or strong academic research background, which the candidate lacks (holding a B.Tech and MBA instead), creating a notable profile mismatch.</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
@@ -2710,9 +2710,9 @@
           <t>Not stated in JD</t>
         </is>
       </c>
-      <c r="K35" s="2" t="inlineStr">
-        <is>
-          <t>From previous run</t>
+      <c r="K35" s="7" t="inlineStr">
+        <is>
+          <t>New this run (2026-08-27 15:40 UTC)</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
@@ -2722,7 +2722,7 @@
       </c>
       <c r="M35" s="6" t="inlineStr">
         <is>
-          <t>https://de.linkedin.com/jobs/view/machine-learning-ai-engineer-hybrid-at-quik-hire-staffing-4459653741?position=27&amp;pageNum=0&amp;refId=T%2F0KkBXL%2Fl%2B5Iv5tUGTY7Q%3D%3D&amp;trackingId=xAvCgryMmzYLEKjSJh9cEw%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/lead-ai-engineer-phd-at-talent-seed-4457749740?position=2&amp;pageNum=0&amp;refId=50H6yCrEXIuhgr6eqEojNg%3D%3D&amp;trackingId=EZ22EvZ4LnqSKMhMS5nk8Q%3D%3D</t>
         </is>
       </c>
     </row>
@@ -2732,17 +2732,17 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Senior Applied Scientist (All genders)</t>
+          <t>Consultant Business &amp; AI Insights (m/w/d) in Stuttgart</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>Zalando</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>Berlin, Berlin, Germany</t>
+          <t>Stuttgart, Baden-Württemberg, Germany</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -2751,7 +2751,7 @@
         </is>
       </c>
       <c r="F36" s="8" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="G36" s="9" t="inlineStr">
         <is>
@@ -2760,17 +2760,17 @@
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>This is a classical ML and causal inference role focused on marketing mix modeling, experimentation, and econometrics rather than the candidate's core specialization in Generative AI, LLMs, and agentic systems. However, the seniority level (Senior Applied Scientist with 5+ years experience) aligns reasonably well with the candidate's 10+ years of experience.</t>
+          <t>The role is a junior-to-mid level consulting position ("Consultant") focusing broadly on BI, data analytics, and general AI, which is a significant seniority mismatch for a Lead Data Scientist with 10+ years of experience. While it mentions GenAI and RAG frameworks as nice-to-haves, the day-to-day work is heavily weighted toward general analytics consulting rather than advanced agentic AI specialization.</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>Not stated in JD</t>
+          <t>Yes - fluent/C1+ German explicitly required</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>Possible - relocation support mentioned, visa not explicit</t>
+          <t>Not stated in JD</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -2785,7 +2785,7 @@
       </c>
       <c r="M36" s="6" t="inlineStr">
         <is>
-          <t>https://de.linkedin.com/jobs/view/senior-applied-scientist-all-genders-at-zalando-4457268030?position=29&amp;pageNum=0&amp;refId=T%2F0KkBXL%2Fl%2B5Iv5tUGTY7Q%3D%3D&amp;trackingId=uPBCURAa%2BhpqUjOtZt20sg%3D%3D</t>
+          <t>https://de.linkedin.com/jobs/view/consultant-business-ai-insights-m-w-d-in-stuttgart-at-deloitte-4440569165?position=20&amp;pageNum=0&amp;refId=T%2F0KkBXL%2Fl%2B5Iv5tUGTY7Q%3D%3D&amp;trackingId=WIf1oxbjDsUKKiZvxr62ig%3D%3D</t>
         </is>
       </c>
     </row>
@@ -2795,17 +2795,17 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Consultant Business &amp; AI Insights (m/w/d) in München</t>
+          <t>Senior Manager - Martech</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Astra Tech</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>Munich, Bavaria, Germany</t>
+          <t>Dubai, Dubai, United Arab Emirates</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -2814,7 +2814,7 @@
         </is>
       </c>
       <c r="F37" s="8" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="G37" s="9" t="inlineStr">
         <is>
@@ -2823,12 +2823,12 @@
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>The candidate has strong GenAI and MLOps specialization, but this Deloitte role is at the junior/consultant level requiring early-career experience, making it a severe seniority mismatch for a Lead Data Scientist with 10+ years of experience. Furthermore, the role focuses heavily on general BI, analytics engineering, and basic consulting rather than advanced agentic AI development.</t>
+          <t>The role is a Senior Manager of Martech focusing on marketing tech stacks, CDPs, and CRM operations rather than a dedicated GenAI, LLM, or agentic AI engineering role, making the domain fit a weaker match. However, the candidate's 10+ years of experience aligns well with the 7-10+ years seniority requirement, and the position touches on predictive modeling and internal AI tooling.</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>Yes - fluent/C1+ German explicitly required</t>
+          <t>Not stated in JD</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
@@ -2848,7 +2848,7 @@
       </c>
       <c r="M37" s="6" t="inlineStr">
         <is>
-          <t>https://de.linkedin.com/jobs/view/consultant-business-ai-insights-m-w-d-in-m%C3%BCnchen-at-deloitte-4440568216?position=21&amp;pageNum=0&amp;refId=T%2F0KkBXL%2Fl%2B5Iv5tUGTY7Q%3D%3D&amp;trackingId=%2BjmC%2BHZAc9MdN%2BCr7d%2BCiw%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/senior-manager-martech-at-astra-tech-4457903179?position=12&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=9UstVcnD5je41ZfhWPt1AQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -2858,26 +2858,26 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Senior Manager - Artificial Intelligence</t>
+          <t>Principal AI Engineer</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>Hays</t>
+          <t>A.P. Moller - Maersk</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>Dubai, United Arab Emirates</t>
+          <t>Copenhagen Metropolitan Area</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F38" s="8" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="G38" s="9" t="inlineStr">
         <is>
@@ -2886,7 +2886,7 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>The role focuses heavily on AI governance, assurance, model evaluation, and risk management rather than hands-on GenAI application development or agentic workflows, which are the candidate's core strengths. Additionally, the Senior Manager title leans toward a managerial and compliance track compared to the candidate's hands-on Lead Data Scientist background.</t>
+          <t>The role strongly features agentic AI and multi-agent systems which align well with the candidate's core specialization, but it is a Principal-level technical leadership position requiring deep expertise in Operations Research, mathematical programming, and optimization solvers that exceed the candidate's profile.</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="M38" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/senior-manager-artificial-intelligence-at-hays-4457227403?position=27&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=m8EGYWiqeCT0F9aowu0X7g%3D%3D</t>
+          <t>https://dk.linkedin.com/jobs/view/principal-ai-engineer-at-a-p-moller-maersk-4445976056?position=8&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=cXORh69SWuwKg77z4%2FjXOA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -2921,17 +2921,17 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>AI GTM Consulting - Banking</t>
+          <t>Principle AI Engineer</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>NTT DATA, Inc.</t>
+          <t>Analog</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>Dubai, Dubai, United Arab Emirates</t>
+          <t>Abu Dhabi, Abu Dhabi Emirate, United Arab Emirates</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -2940,7 +2940,7 @@
         </is>
       </c>
       <c r="F39" s="8" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="G39" s="9" t="inlineStr">
         <is>
@@ -2949,7 +2949,7 @@
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t>The candidate has strong technical GenAI and LLM expertise, but this role is primarily a client-facing AI GTM consulting and pre-sales position focused on the Middle East banking sector rather than hands-on technical model development. Additionally, the candidate lacks the required regional Gulf consulting experience and heavy banking industry operating model background.</t>
+          <t>The role requires a Principal AI Engineer to lead responsible AI standards, model evaluation, and governance in high-stakes domains like defense, which aligns well with the candidate's technical breadth and domain background in finance. However, the seniority is a mismatch as the candidate is at a Lead level rather than Principal, and the location requirement (Abu Dhabi) does not align with the candidate's target region.</t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="M39" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/ai-gtm-consulting-banking-at-ntt-data-inc-4446632891?position=28&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=KvV4cGbrQRe2y%2FdaiwjIeA%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/principle-ai-engineer-at-analog-4457965112?position=22&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=9BE6FaPZTeRRBQuVWNoE5A%3D%3D</t>
         </is>
       </c>
     </row>
@@ -2984,17 +2984,17 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Senior Consultant - Financial Crime Prevention</t>
+          <t>Research Engineer/Technician in the Division of Science (Computer Science) - Dr. Nizar Habash</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>Zanders</t>
+          <t>New York University Abu Dhabi</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>Utrecht, Utrecht, Netherlands</t>
+          <t>Abu Dhabi, Abu Dhabi Emirate, United Arab Emirates</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -3003,7 +3003,7 @@
         </is>
       </c>
       <c r="F40" s="8" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="G40" s="9" t="inlineStr">
         <is>
@@ -3012,7 +3012,7 @@
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>The role is primarily a traditional quantitative financial crime and risk consulting position where GenAI and LLMs are only mentioned as a minor plus, making it a weak match for the candidate's core GenAI and agentic AI specialization despite matching his overall years of experience.</t>
+          <t>The role focuses heavily on academic and applied Natural Language Processing, computational linguistics, and research tool development at an academic lab (CAMeL Lab), which overlaps with the candidate's NLP background. However, it is an academic research engineering position rather than a commercial GenAI/LLM/agentic architecture role, and expects academic publication experience which is not the candidate's primary focus.</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
@@ -3022,7 +3022,7 @@
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>Not stated in JD</t>
+          <t>Possible - relocation support mentioned, visa not explicit</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -3037,7 +3037,7 @@
       </c>
       <c r="M40" s="6" t="inlineStr">
         <is>
-          <t>https://nl.linkedin.com/jobs/view/senior-consultant-financial-crime-prevention-at-zanders-4457921059?position=27&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=Xn8L7cLgbmU3MmPJfLc4Jg%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/research-engineer-technician-in-the-division-of-science-computer-science-dr-nizar-habash-at-new-york-university-abu-dhabi-4432261664?position=15&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=Eg%2BhyoQTsgcu3W8ar6ARQw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -3047,26 +3047,26 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Senior Consultant - Financial Crime Prevention</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>Zanders</t>
+          <t>Rubicon Cloud Advisor</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>Amsterdam, North Holland, Netherlands</t>
+          <t>The Randstad, Netherlands</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F41" s="8" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="G41" s="9" t="inlineStr">
         <is>
@@ -3075,7 +3075,7 @@
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t>The role is primarily focused on quantitative risk advisory and financial crime prevention consulting with classical modeling and model validation, where NLP and LLM pipeline experience is only a minor plus rather than the core focus. Seniority-wise, the Senior Consultant position requires 2+ years of track record, which aligns with the candidate's experience, but the domain mismatch results in a lower score.</t>
+          <t>The role involves Databricks, Python, and some GenAI/RAG components which align with the candidate's core stack, but it requires fluency in Dutch which the candidate does not have. Additionally, the seniority (3-4 years experience) is slightly below the candidate's 10-year profile, making this a weaker linguistic and seniority match.</t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
@@ -3100,7 +3100,7 @@
       </c>
       <c r="M41" s="6" t="inlineStr">
         <is>
-          <t>https://nl.linkedin.com/jobs/view/senior-consultant-financial-crime-prevention-at-zanders-4457902287?position=25&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=JPzSeOLZttSxrJAgb7RtbQ%3D%3D</t>
+          <t>https://nl.linkedin.com/jobs/view/data-scientist-at-rubicon-cloud-advisor-4449382178?position=2&amp;pageNum=0&amp;refId=oiBIn1Czflg0JjZjH5z0Lg%3D%3D&amp;trackingId=rpvzZo3yE9tXsukpo3UKWQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -3110,17 +3110,17 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Lead Data Scientist</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>AS Watson Benelux</t>
+          <t>GFR Fund</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>Renswoude, Utrecht, Netherlands</t>
+          <t>Amsterdam, North Holland, Netherlands</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="F42" s="8" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="G42" s="9" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>This Lead Data Scientist role focuses heavily on classical machine learning, forecasting, optimization, and traditional data science applications for retail (such as sales forecasting and promotional personalization), with no mention of Generative AI, LLMs, or agentic workflows. However, the candidate's 10+ years of experience and leadership background align well with the seniority requirements of the role.</t>
+          <t>The role mentions exposure to modern AI methodologies like RAG and LLM-augmented models, which matches the candidate's core specialization, but it is primarily a classical ML and audience modeling data science role focused on high-volume data and entity resolution. Furthermore, there is a significant seniority mismatch as the candidate has 10 years of experience and a Lead title, whereas the posting is for a Junior Data Scientist with 2+ years of experience.</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="M42" s="6" t="inlineStr">
         <is>
-          <t>https://nl.linkedin.com/jobs/view/lead-data-scientist-at-as-watson-benelux-4377637626?position=11&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=D%2Bd%2FEPbAvDXvjR5ZJgWEIQ%3D%3D</t>
+          <t>https://nl.linkedin.com/jobs/view/data-scientist-at-gfr-fund-4459322290?position=1&amp;pageNum=0&amp;refId=oiBIn1Czflg0JjZjH5z0Lg%3D%3D&amp;trackingId=tzZbdlNky9Fn%2BVWE2R%2FOFg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -3173,17 +3173,17 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Applied Data Scientist - Intelligent Document Processing</t>
+          <t>AI Solution Lead</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>ABN AMRO Bank N.V.</t>
+          <t>Royal Wagenborg</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>Amersfoort, Utrecht, Netherlands</t>
+          <t>Delfzijl, Groningen, Netherlands</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="F43" s="8" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="G43" s="9" t="inlineStr">
         <is>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t>The role focuses on Intelligent Document Processing (IDP) and document classification using existing components rather than cutting-edge GenAI/LLM orchestration or agentic systems. Additionally, the position asks for 3-6 years of experience (whereas the candidate has 10+) and explicitly requires Dutch language proficiency, making it a weaker fit.</t>
+          <t>The role explicitly highlights a use case for an AI search engine over documentation, aligning with the candidate's core RAG and Azure AI Search expertise. However, the position focuses heavily on classical ML, time-series analysis, IoT, and industrial/OT environments, which are only peripheral to the candidate's deep Generative AI and agentic specialization.</t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="M43" s="6" t="inlineStr">
         <is>
-          <t>https://nl.linkedin.com/jobs/view/applied-data-scientist-intelligent-document-processing-at-abn-amro-bank-n-v-4440507839?position=4&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=yeF1JJiNzo5kSVTx1eGVfw%3D%3D</t>
+          <t>https://nl.linkedin.com/jobs/view/ai-solution-lead-at-royal-wagenborg-4457954118?position=14&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=vxrN54FA7uiALBltM74joA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -3236,26 +3236,26 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Python Software Engineer -  AI team</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>CIMSOLUTIONS</t>
+          <t>Channable</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>North Brabant, Netherlands</t>
+          <t>Utrecht, Utrecht, Netherlands</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F44" s="8" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G44" s="9" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>This role focuses on traditional data science, predictive analysis, and business intelligence without any mention of Generative AI, LLMs, or agentic frameworks. Additionally, the job explicitly requires excellent communication skills in both Dutch and English, which creates a mismatch as the candidate lacks Dutch fluency.</t>
+          <t>This role is primarily a Python Software Engineer position focusing on data processing, backend web frameworks, and e-commerce infrastructure rather than advanced GenAI, LLMs, or agentic architectures. While the candidate has over 10 years of experience and strong GenAI expertise, the heavy emphasis on traditional software engineering infrastructure and lower seniority requirements makes this a weaker fit.</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
@@ -3289,7 +3289,7 @@
       </c>
       <c r="M44" s="6" t="inlineStr">
         <is>
-          <t>https://nl.linkedin.com/jobs/view/data-scientist-at-cimsolutions-4457901406?position=2&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=b3VmH8PYtChkdpJv0VgUxA%3D%3D</t>
+          <t>https://nl.linkedin.com/jobs/view/python-software-engineer-ai-team-at-channable-4454702624?position=17&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=C0S4tD8hFUIyS0haOgnRyg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -3299,17 +3299,17 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>Data Scientist Kruidvat</t>
+          <t>Data engineer til Hvidvasksekretariatet - Danmarks finansielle efterretningsenhed</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>AS Watson Benelux</t>
+          <t>Politi</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>Renswoude, Utrecht, Netherlands</t>
+          <t>Copenhagen, Capital Region of Denmark, Denmark</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -3318,7 +3318,7 @@
         </is>
       </c>
       <c r="F45" s="8" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G45" s="9" t="inlineStr">
         <is>
@@ -3327,7 +3327,7 @@
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>This role focuses on classical data science applications like time-series forecasting, supply chain optimization, and predictive modeling for retail, lacking any mention of Generative AI, LLMs, or agentic systems which are the candidate's core specialization. Although the tech stack includes Databricks and Azure, the domain mismatch makes it a weak fit.</t>
+          <t>The role is primarily a Data Engineering position focused on ETL, databases, and financial crime analysis platforms, which only touches LLMs as a minor passing mention rather than centering on core GenAI/agentic specialization. However, the candidate's strong Python, SQL, and banking domain background provide some relevant foundational overlap.</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
@@ -3352,7 +3352,7 @@
       </c>
       <c r="M45" s="6" t="inlineStr">
         <is>
-          <t>https://nl.linkedin.com/jobs/view/data-scientist-kruidvat-at-as-watson-benelux-4439964615?position=3&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=tWylwGWz364M%2B%2FotR1FLZg%3D%3D</t>
+          <t>https://dk.linkedin.com/jobs/view/data-engineer-til-hvidvasksekretariatet-danmarks-finansielle-efterretningsenhed-at-politi-4457966663?position=10&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=YZMqDSG0b%2BEmx5Ptpd%2FXGw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -3362,17 +3362,17 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Regulatory Compliance Manager</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>CIMSOLUTIONS</t>
+          <t>Bybit</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>South Holland, Netherlands</t>
+          <t>Abu Dhabi Emirate, United Arab Emirates</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="F46" s="8" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G46" s="9" t="inlineStr">
         <is>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>This role focuses on traditional data science, predictive modeling, and business intelligence with standard ML libraries (TensorFlow, scikit-learn), lacking any focus on the candidate's core Generative AI, LLM, and agentic AI specialization. Additionally, the job explicitly requires excellent communication skills in both Dutch and English, which creates a significant language mismatch for the candidate.</t>
+          <t>The role involves building AI-enabled compliance and RAG/LLM workflows, which moderately aligns with the candidate's core GenAI and vector search expertise. However, it requires a primary background in regulatory compliance and financial services law rather than data science, making it a weaker domain and seniority fit.</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
@@ -3415,7 +3415,7 @@
       </c>
       <c r="M46" s="6" t="inlineStr">
         <is>
-          <t>https://nl.linkedin.com/jobs/view/data-scientist-at-cimsolutions-4457917043?position=1&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=1JSHNn3m2jBGxvl6iC8lcw%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/regulatory-compliance-manager-at-bybit-4449794088?position=25&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=jQJTq4KHiygix7eADF6Ovw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -3425,26 +3425,26 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>AI Product Owner</t>
+          <t>Data-analist DevOps team Kapitaalmarkten</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>Novo Nordisk</t>
+          <t>Autoriteit Financiële Markten</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>Ballerup Municipality, Capital Region of Denmark, Denmark</t>
+          <t>Amsterdam, North Holland, Netherlands</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F47" s="8" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G47" s="9" t="inlineStr">
         <is>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="H47" s="3" t="inlineStr">
         <is>
-          <t>This is an AI Product Owner role focused on manufacturing and supply chain systems, which requires product management and stakeholder alignment rather than hands-on GenAI/LLM development. The candidate is a technical Lead Data Scientist specializing in hands-on LangChain/LangGraph and agentic workflows, presenting a significant mismatch in role function and domain expertise.</t>
+          <t>The role requires data analysis and mentions LLMs as a passing preference rather than a core focus, making it a weaker fit compared to dedicated GenAI-specialist positions. Additionally, the seniority expected (minimum 3 years) is slightly below the candidate's 10 years of experience, and the position is located in the Netherlands with Dutch regulatory context.</t>
         </is>
       </c>
       <c r="I47" s="3" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="M47" s="6" t="inlineStr">
         <is>
-          <t>https://dk.linkedin.com/jobs/view/ai-product-owner-at-novo-nordisk-4457258669?position=24&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=s56Z90FxaVSj7XKQs6qQuA%3D%3D</t>
+          <t>https://nl.linkedin.com/jobs/view/data-analist-devops-team-kapitaalmarkten-at-autoriteit-financi%C3%ABle-markten-4446764564?position=20&amp;pageNum=0&amp;refId=oiBIn1Czflg0JjZjH5z0Lg%3D%3D&amp;trackingId=sRIfcLqjQQWvZalqlxOpog%3D%3D</t>
         </is>
       </c>
     </row>
@@ -3488,26 +3488,26 @@
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Forretningskonsulent</t>
+          <t>Data Scientist - AI/ML (Remote)</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>Bankdata</t>
+          <t>Quik Hire Staffing</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>Silkeborg, Central Denmark Region, Denmark</t>
+          <t>United Arab Emirates</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F48" s="8" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G48" s="9" t="inlineStr">
         <is>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>This is a business/risk consultant role focusing on regulatory compliance, credit risk models, and SAS/SQL data analysis rather than a hands-on Generative AI or LLM specialization. While the candidate brings strong banking domain experience and Python skills, the core responsibilities do not align with his advanced GenAI and agentic AI expertise.</t>
+          <t>The role is a general classical machine learning and MLOps position focused on traditional classification, regression, and clustering tasks using scikit-learn or PyTorch, rather than leveraging the candidate's core specialization in GenAI, LLMs, LangChain, and agentic workflows. While the candidate's Python and Azure cloud background align well, the technical scope is a weaker fit.</t>
         </is>
       </c>
       <c r="I48" s="3" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="M48" s="6" t="inlineStr">
         <is>
-          <t>https://dk.linkedin.com/jobs/view/forretningskonsulent-at-bankdata-4448894922?position=22&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=o%2BWOTBX123ODc%2FiV7%2B9GIw%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/data-scientist-ai-ml-remote-at-quik-hire-staffing-4459642594?position=9&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=5JzrtHYdDMeIkrN4Gn8eng%3D%3D</t>
         </is>
       </c>
     </row>
@@ -3551,22 +3551,22 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>Developer</t>
+          <t>Machine Learning (AI) Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>MAP</t>
+          <t>Quik Hire Staffing</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>Copenhagen, Capital Region of Denmark, Denmark</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F49" s="8" t="n">
@@ -3579,7 +3579,7 @@
       </c>
       <c r="H49" s="3" t="inlineStr">
         <is>
-          <t>The role is primarily a backend/full-stack software engineering position requiring .NET/C# and Vue/TypeScript, which does not align with the candidate's core Data Science and GenAI specialization. While there are passing mentions of Python and agentic AI as nice-to-haves, the job is fundamentally a software development role rather than an advanced GenAI/LLM specialist position.</t>
+          <t>The role focuses heavily on traditional deep learning frameworks (TensorFlow, PyTorch), MLOps, and model training rather than the candidate's core specialization in Generative AI, LLMs, and agentic workflows. However, it is still a technical AI/ML engineering position that aligns reasonably well in terms of experience level.</t>
         </is>
       </c>
       <c r="I49" s="3" t="inlineStr">
@@ -3604,7 +3604,7 @@
       </c>
       <c r="M49" s="6" t="inlineStr">
         <is>
-          <t>https://dk.linkedin.com/jobs/view/developer-at-map-4459176960?position=23&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=YgE2RztI4uaVgk5SXXlkQw%3D%3D</t>
+          <t>https://de.linkedin.com/jobs/view/machine-learning-ai-engineer-hybrid-at-quik-hire-staffing-4459653741?position=27&amp;pageNum=0&amp;refId=T%2F0KkBXL%2Fl%2B5Iv5tUGTY7Q%3D%3D&amp;trackingId=xAvCgryMmzYLEKjSJh9cEw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -3614,17 +3614,17 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>AI Innovation Specialist - Renewable Energy Solutions</t>
+          <t>Senior Applied Scientist (All genders)</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>Vestas</t>
+          <t>Zalando</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>Aarhus Municipality, Central Denmark Region, Denmark</t>
+          <t>Berlin, Berlin, Germany</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t>The candidate has strong technical skills in Python and machine learning, but this role focuses heavily on industrial AI, computer vision, sensor data, and predictive maintenance in the renewable energy sector rather than the candidate's core specialization in LLMs, RAG, and agentic workflows. Furthermore, the seniority alignment is slightly mismatched as the role asks for 4+ years while the candidate is a senior/lead with 10 years of experience.</t>
+          <t>This is a classical ML and causal inference role focused on marketing mix modeling, experimentation, and econometrics rather than the candidate's core specialization in Generative AI, LLMs, and agentic systems. However, the seniority level (Senior Applied Scientist with 5+ years experience) aligns reasonably well with the candidate's 10+ years of experience.</t>
         </is>
       </c>
       <c r="I50" s="3" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>Not stated in JD</t>
+          <t>Possible - relocation support mentioned, visa not explicit</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -3667,7 +3667,7 @@
       </c>
       <c r="M50" s="6" t="inlineStr">
         <is>
-          <t>https://dk.linkedin.com/jobs/view/ai-innovation-specialist-renewable-energy-solutions-at-vestas-4459358646?position=4&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=x6uemge6vMfQH6CFPei6kw%3D%3D</t>
+          <t>https://de.linkedin.com/jobs/view/senior-applied-scientist-all-genders-at-zalando-4457268030?position=29&amp;pageNum=0&amp;refId=T%2F0KkBXL%2Fl%2B5Iv5tUGTY7Q%3D%3D&amp;trackingId=uPBCURAa%2BhpqUjOtZt20sg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -3677,22 +3677,22 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>Data Scientist (Remote)</t>
+          <t>Consultant Business &amp; AI Insights (m/w/d) in München</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>Hire Feed</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>Munich, Bavaria, Germany</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F51" s="8" t="n">
@@ -3705,12 +3705,12 @@
       </c>
       <c r="H51" s="3" t="inlineStr">
         <is>
-          <t>This role is a generic classical machine learning position focused on predictive modeling, Python, and scikit-learn, with no mention of Generative AI, LLMs, RAG, or agentic systems that form the core of the candidate's expertise. While the candidate has the necessary background to perform the work, it underutilizes his specialized GenAI skillset and matches the scoring guidance for a weaker classical ML/statistics fit.</t>
+          <t>The candidate has strong GenAI and MLOps specialization, but this Deloitte role is at the junior/consultant level requiring early-career experience, making it a severe seniority mismatch for a Lead Data Scientist with 10+ years of experience. Furthermore, the role focuses heavily on general BI, analytics engineering, and basic consulting rather than advanced agentic AI development.</t>
         </is>
       </c>
       <c r="I51" s="3" t="inlineStr">
         <is>
-          <t>Not stated in JD</t>
+          <t>Yes - fluent/C1+ German explicitly required</t>
         </is>
       </c>
       <c r="J51" s="3" t="inlineStr">
@@ -3718,9 +3718,9 @@
           <t>Not stated in JD</t>
         </is>
       </c>
-      <c r="K51" s="7" t="inlineStr">
-        <is>
-          <t>New this run (2026-08-27 06:43 UTC)</t>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>From previous run</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
@@ -3730,7 +3730,7 @@
       </c>
       <c r="M51" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/data-scientist-remote-at-hire-feed-4459652348?position=8&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=eN2UeQevFS%2FiNl5F%2FHqH8A%3D%3D</t>
+          <t>https://de.linkedin.com/jobs/view/consultant-business-ai-insights-m-w-d-in-m%C3%BCnchen-at-deloitte-4440568216?position=21&amp;pageNum=0&amp;refId=T%2F0KkBXL%2Fl%2B5Iv5tUGTY7Q%3D%3D&amp;trackingId=%2BjmC%2BHZAc9MdN%2BCr7d%2BCiw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -3740,22 +3740,22 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>Machine Learning (AI) Engineer (Hybrid)</t>
+          <t>Senior Manager - Artificial Intelligence</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>Quik Hire Staffing</t>
+          <t>Hays</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>Dubai, United Arab Emirates</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F52" s="8" t="n">
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t>The role is focused heavily on classical Machine Learning, MLOps, deep learning frameworks (TensorFlow, PyTorch), and model training rather than the candidate's core specialization in Generative AI, LLMs, RAG, and agentic systems. Seniority aligns well, but the technical domain mismatch makes this a weaker fit.</t>
+          <t>The role focuses heavily on AI governance, assurance, model evaluation, and risk management rather than hands-on GenAI application development or agentic workflows, which are the candidate's core strengths. Additionally, the Senior Manager title leans toward a managerial and compliance track compared to the candidate's hands-on Lead Data Scientist background.</t>
         </is>
       </c>
       <c r="I52" s="3" t="inlineStr">
@@ -3781,9 +3781,9 @@
           <t>Not stated in JD</t>
         </is>
       </c>
-      <c r="K52" s="7" t="inlineStr">
-        <is>
-          <t>New this run (2026-08-27 06:43 UTC)</t>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>From previous run</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
@@ -3793,7 +3793,7 @@
       </c>
       <c r="M52" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/machine-learning-ai-engineer-hybrid-at-quik-hire-staffing-4459649596?position=5&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=sbTD%2BYZZjPOfeagKS2Yixw%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/senior-manager-artificial-intelligence-at-hays-4457227403?position=27&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=m8EGYWiqeCT0F9aowu0X7g%3D%3D</t>
         </is>
       </c>
     </row>
@@ -3803,17 +3803,17 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>Decision Scientist, Marketing Modelling Intelligence, Marketing DSA</t>
+          <t>AI GTM Consulting - Banking</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>Vinted</t>
+          <t>NTT DATA, Inc.</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>Berlin, Berlin, Germany</t>
+          <t>Dubai, Dubai, United Arab Emirates</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -3822,7 +3822,7 @@
         </is>
       </c>
       <c r="F53" s="8" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G53" s="9" t="inlineStr">
         <is>
@@ -3831,12 +3831,12 @@
       </c>
       <c r="H53" s="3" t="inlineStr">
         <is>
-          <t>This is a classical marketing analytics and econometrics role focused on Bayesian Media Mix Modeling and ROI measurement with no mention of Generative AI, LLMs, or agentic systems. Furthermore, the candidate is a Lead Data Scientist with 10+ years of experience, making the 2-4 year experience requirement a significant seniority mismatch.</t>
+          <t>The candidate has strong technical GenAI and LLM expertise, but this role is primarily a client-facing AI GTM consulting and pre-sales position focused on the Middle East banking sector rather than hands-on technical model development. Additionally, the candidate lacks the required regional Gulf consulting experience and heavy banking industry operating model background.</t>
         </is>
       </c>
       <c r="I53" s="3" t="inlineStr">
         <is>
-          <t>Yes - German required (see JD for exact level)</t>
+          <t>Not stated in JD</t>
         </is>
       </c>
       <c r="J53" s="3" t="inlineStr">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="M53" s="6" t="inlineStr">
         <is>
-          <t>https://de.linkedin.com/jobs/view/decision-scientist-marketing-modelling-intelligence-marketing-dsa-at-vinted-4431734157?position=23&amp;pageNum=0&amp;refId=T%2F0KkBXL%2Fl%2B5Iv5tUGTY7Q%3D%3D&amp;trackingId=ym8Uxiee8AvGv52T5S0EVQ%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/ai-gtm-consulting-banking-at-ntt-data-inc-4446632891?position=28&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=KvV4cGbrQRe2y%2FdaiwjIeA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -3866,17 +3866,17 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>Data Analyst / Data Science Specialist (m/w/d)</t>
+          <t>Senior Consultant - Financial Crime Prevention</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>Molkerei Gropper GmbH &amp; Co. KG</t>
+          <t>Zanders</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>Bissingen, Bavaria, Germany</t>
+          <t>Utrecht, Utrecht, Netherlands</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -3885,7 +3885,7 @@
         </is>
       </c>
       <c r="F54" s="8" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G54" s="9" t="inlineStr">
         <is>
@@ -3894,12 +3894,12 @@
       </c>
       <c r="H54" s="3" t="inlineStr">
         <is>
-          <t>This role is focused primarily on traditional Data Warehousing, BI, ETL, and reporting with SAP systems, where AI is merely a passing mention of interest rather than a core focus. It is a significant mismatch for the candidate's advanced Generative AI, LLM, and agentic specialization.</t>
+          <t>The role is primarily a traditional quantitative financial crime and risk consulting position where GenAI and LLMs are only mentioned as a minor plus, making it a weak match for the candidate's core GenAI and agentic AI specialization despite matching his overall years of experience.</t>
         </is>
       </c>
       <c r="I54" s="3" t="inlineStr">
         <is>
-          <t>Yes - German required (see JD for exact level)</t>
+          <t>Not stated in JD</t>
         </is>
       </c>
       <c r="J54" s="3" t="inlineStr">
@@ -3919,7 +3919,7 @@
       </c>
       <c r="M54" s="6" t="inlineStr">
         <is>
-          <t>https://de.linkedin.com/jobs/view/data-analyst-data-science-specialist-m-w-d-at-molkerei-gropper-gmbh-co-kg-4459396175?position=16&amp;pageNum=0&amp;refId=T%2F0KkBXL%2Fl%2B5Iv5tUGTY7Q%3D%3D&amp;trackingId=hDs2N%2Ft3sDgczR%2Fh%2Biow4g%3D%3D</t>
+          <t>https://nl.linkedin.com/jobs/view/senior-consultant-financial-crime-prevention-at-zanders-4457921059?position=27&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=Xn8L7cLgbmU3MmPJfLc4Jg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -3929,17 +3929,17 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>Specialist Data Science</t>
+          <t>Senior Consultant - Financial Crime Prevention</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>HDI Group</t>
+          <t>Zanders</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>Hannover, Lower Saxony, Germany</t>
+          <t>Amsterdam, North Holland, Netherlands</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -3948,7 +3948,7 @@
         </is>
       </c>
       <c r="F55" s="8" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G55" s="9" t="inlineStr">
         <is>
@@ -3957,7 +3957,7 @@
       </c>
       <c r="H55" s="3" t="inlineStr">
         <is>
-          <t>This role focuses heavily on data engineering, analytics, and R-based pricing tools within the insurance domain, offering only passing alignment with classical data science rather than the candidate's core GenAI, LLMs, and agentic AI specialization.</t>
+          <t>The role is primarily focused on quantitative risk advisory and financial crime prevention consulting with classical modeling and model validation, where NLP and LLM pipeline experience is only a minor plus rather than the core focus. Seniority-wise, the Senior Consultant position requires 2+ years of track record, which aligns with the candidate's experience, but the domain mismatch results in a lower score.</t>
         </is>
       </c>
       <c r="I55" s="3" t="inlineStr">
@@ -3982,7 +3982,7 @@
       </c>
       <c r="M55" s="6" t="inlineStr">
         <is>
-          <t>https://de.linkedin.com/jobs/view/specialist-data-science-at-hdi-group-4449488553?position=9&amp;pageNum=0&amp;refId=T%2F0KkBXL%2Fl%2B5Iv5tUGTY7Q%3D%3D&amp;trackingId=4kEwk2%2BQdqX%2FDjmyxZ2xyA%3D%3D</t>
+          <t>https://nl.linkedin.com/jobs/view/senior-consultant-financial-crime-prevention-at-zanders-4457902287?position=25&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=JPzSeOLZttSxrJAgb7RtbQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -3992,17 +3992,17 @@
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>Data Scientist (m/w/d) für analytisches CRM und datengestützte Potenziale</t>
+          <t>Lead Data Scientist</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>R+V Versicherung</t>
+          <t>AS Watson Benelux</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>Wiesbaden, Hesse, Germany</t>
+          <t>Renswoude, Utrecht, Netherlands</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -4011,7 +4011,7 @@
         </is>
       </c>
       <c r="F56" s="8" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G56" s="9" t="inlineStr">
         <is>
@@ -4020,12 +4020,12 @@
       </c>
       <c r="H56" s="3" t="inlineStr">
         <is>
-          <t>This role focuses on analytical CRM, customer segmentation, and rule-based next-best-offer systems using SQL and traditional data methods, offering only passing mention of AI approaches. It lacks the core Generative AI, LLM, and agentic specialization that defines the candidate's profile.</t>
+          <t>This Lead Data Scientist role focuses heavily on classical machine learning, forecasting, optimization, and traditional data science applications for retail (such as sales forecasting and promotional personalization), with no mention of Generative AI, LLMs, or agentic workflows. However, the candidate's 10+ years of experience and leadership background align well with the seniority requirements of the role.</t>
         </is>
       </c>
       <c r="I56" s="3" t="inlineStr">
         <is>
-          <t>Yes - fluent/C1+ German explicitly required</t>
+          <t>Not stated in JD</t>
         </is>
       </c>
       <c r="J56" s="3" t="inlineStr">
@@ -4045,7 +4045,7 @@
       </c>
       <c r="M56" s="6" t="inlineStr">
         <is>
-          <t>https://de.linkedin.com/jobs/view/data-scientist-m-w-d-f%C3%BCr-analytisches-crm-und-datengest%C3%BCtzte-potenziale-at-r%2Bv-versicherung-4446660524?position=7&amp;pageNum=0&amp;refId=T%2F0KkBXL%2Fl%2B5Iv5tUGTY7Q%3D%3D&amp;trackingId=na3WACzOriMr43dXtkckXw%3D%3D</t>
+          <t>https://nl.linkedin.com/jobs/view/lead-data-scientist-at-as-watson-benelux-4377637626?position=11&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=D%2Bd%2FEPbAvDXvjR5ZJgWEIQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -4055,17 +4055,17 @@
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>Senior Data Scientist (m/f/d)</t>
+          <t>Applied Data Scientist - Intelligent Document Processing</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>AutoScout24</t>
+          <t>ABN AMRO Bank N.V.</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>Munich, Bavaria, Germany</t>
+          <t>Amersfoort, Utrecht, Netherlands</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -4074,7 +4074,7 @@
         </is>
       </c>
       <c r="F57" s="8" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G57" s="9" t="inlineStr">
         <is>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="H57" s="3" t="inlineStr">
         <is>
-          <t>[FALLBACK SCORER - Gemini call failed] Matched 2 core GenAI term(s) via keyword search. Verify manually; this is a degraded-mode score.</t>
+          <t>The role focuses on Intelligent Document Processing (IDP) and document classification using existing components rather than cutting-edge GenAI/LLM orchestration or agentic systems. Additionally, the position asks for 3-6 years of experience (whereas the candidate has 10+) and explicitly requires Dutch language proficiency, making it a weaker fit.</t>
         </is>
       </c>
       <c r="I57" s="3" t="inlineStr">
@@ -4108,7 +4108,7 @@
       </c>
       <c r="M57" s="6" t="inlineStr">
         <is>
-          <t>https://de.linkedin.com/jobs/view/senior-data-scientist-m-f-d-at-autoscout24-4432214339?position=11&amp;pageNum=0&amp;refId=T%2F0KkBXL%2Fl%2B5Iv5tUGTY7Q%3D%3D&amp;trackingId=7SGOVxV%2FwAFkUhW1fBv2EA%3D%3D</t>
+          <t>https://nl.linkedin.com/jobs/view/applied-data-scientist-intelligent-document-processing-at-abn-amro-bank-n-v-4440507839?position=4&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=yeF1JJiNzo5kSVTx1eGVfw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -4118,17 +4118,17 @@
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>Data Analyst / Scientist (m/w/d)</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>Dr. Wolff Group</t>
+          <t>CIMSOLUTIONS</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>Bielefeld, North Rhine-Westphalia, Germany</t>
+          <t>North Brabant, Netherlands</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -4137,7 +4137,7 @@
         </is>
       </c>
       <c r="F58" s="8" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G58" s="9" t="inlineStr">
         <is>
@@ -4146,12 +4146,12 @@
       </c>
       <c r="H58" s="3" t="inlineStr">
         <is>
-          <t>[FALLBACK SCORER - Gemini call failed] Matched 2 core GenAI term(s) via keyword search. Verify manually; this is a degraded-mode score.</t>
+          <t>This role focuses on traditional data science, predictive analysis, and business intelligence without any mention of Generative AI, LLMs, or agentic frameworks. Additionally, the job explicitly requires excellent communication skills in both Dutch and English, which creates a mismatch as the candidate lacks Dutch fluency.</t>
         </is>
       </c>
       <c r="I58" s="3" t="inlineStr">
         <is>
-          <t>Yes - German required (see JD for exact level)</t>
+          <t>Not stated in JD</t>
         </is>
       </c>
       <c r="J58" s="3" t="inlineStr">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="M58" s="6" t="inlineStr">
         <is>
-          <t>https://de.linkedin.com/jobs/view/data-analyst-scientist-m-w-d-at-dr-wolff-group-4459323885?position=2&amp;pageNum=0&amp;refId=T%2F0KkBXL%2Fl%2B5Iv5tUGTY7Q%3D%3D&amp;trackingId=fnXlAvETsQ4TzuiWcW6AWA%3D%3D</t>
+          <t>https://nl.linkedin.com/jobs/view/data-scientist-at-cimsolutions-4457901406?position=2&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=b3VmH8PYtChkdpJv0VgUxA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -4181,17 +4181,17 @@
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>Data Scientist - AI Search &amp; Ranking</t>
+          <t>Data Scientist Kruidvat</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>trivago</t>
+          <t>AS Watson Benelux</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>Düsseldorf, North Rhine-Westphalia, Germany</t>
+          <t>Renswoude, Utrecht, Netherlands</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -4200,7 +4200,7 @@
         </is>
       </c>
       <c r="F59" s="8" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G59" s="9" t="inlineStr">
         <is>
@@ -4209,7 +4209,7 @@
       </c>
       <c r="H59" s="3" t="inlineStr">
         <is>
-          <t>[FALLBACK SCORER - Gemini call failed] Matched 2 core GenAI term(s) via keyword search. Verify manually; this is a degraded-mode score.</t>
+          <t>This role focuses on classical data science applications like time-series forecasting, supply chain optimization, and predictive modeling for retail, lacking any mention of Generative AI, LLMs, or agentic systems which are the candidate's core specialization. Although the tech stack includes Databricks and Azure, the domain mismatch makes it a weak fit.</t>
         </is>
       </c>
       <c r="I59" s="3" t="inlineStr">
@@ -4234,7 +4234,7 @@
       </c>
       <c r="M59" s="6" t="inlineStr">
         <is>
-          <t>https://de.linkedin.com/jobs/view/data-scientist-ai-search-ranking-at-trivago-4451695166?position=3&amp;pageNum=0&amp;refId=T%2F0KkBXL%2Fl%2B5Iv5tUGTY7Q%3D%3D&amp;trackingId=653eapm3ns02Vx9zaTVbNw%3D%3D</t>
+          <t>https://nl.linkedin.com/jobs/view/data-scientist-kruidvat-at-as-watson-benelux-4439964615?position=3&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=tWylwGWz364M%2B%2FotR1FLZg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -4244,17 +4244,17 @@
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>Senior Manager, Digital Forensics &amp; eDiscovery</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>Robert Walters</t>
+          <t>CIMSOLUTIONS</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>Dubai, Dubai, United Arab Emirates</t>
+          <t>South Holland, Netherlands</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -4263,7 +4263,7 @@
         </is>
       </c>
       <c r="F60" s="8" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G60" s="9" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H60" s="3" t="inlineStr">
         <is>
-          <t>The role is focused heavily on digital forensics, eDiscovery, and regulatory investigations, which does not align with the candidate's core specialization in Generative AI, LangGraph, and agentic LLM pipelines. While it mentions emerging AI technologies and LLMs as a secondary component, the candidate's strong GenAI background is largely mismatched with the core forensic and eDiscovery tech stack.</t>
+          <t>This role focuses on traditional data science, predictive modeling, and business intelligence with standard ML libraries (TensorFlow, scikit-learn), lacking any focus on the candidate's core Generative AI, LLM, and agentic AI specialization. Additionally, the job explicitly requires excellent communication skills in both Dutch and English, which creates a significant language mismatch for the candidate.</t>
         </is>
       </c>
       <c r="I60" s="3" t="inlineStr">
@@ -4297,7 +4297,7 @@
       </c>
       <c r="M60" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/senior-manager-digital-forensics-ediscovery-at-robert-walters-4457258106?position=26&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=nugpWYWcIAXvX9xB18JHdw%3D%3D</t>
+          <t>https://nl.linkedin.com/jobs/view/data-scientist-at-cimsolutions-4457917043?position=1&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=1JSHNn3m2jBGxvl6iC8lcw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -4307,17 +4307,17 @@
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>Business Analyst - instashop</t>
+          <t>AI Product Owner</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>talabat</t>
+          <t>Novo Nordisk</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>Dubai, Dubai, United Arab Emirates</t>
+          <t>Ballerup Municipality, Capital Region of Denmark, Denmark</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -4326,7 +4326,7 @@
         </is>
       </c>
       <c r="F61" s="8" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G61" s="9" t="inlineStr">
         <is>
@@ -4335,7 +4335,7 @@
       </c>
       <c r="H61" s="3" t="inlineStr">
         <is>
-          <t>This is a Business Analyst role focused on traditional commercial analytics, SQL, and BI reporting, with only passing mentions of using generative AI tools as productivity boosters. It represents a significant mismatch in domain and seniority compared to the candidate's core specialization as a Lead GenAI/LLM/Agentic AI specialist with 10+ years of experience.</t>
+          <t>This is an AI Product Owner role focused on manufacturing and supply chain systems, which requires product management and stakeholder alignment rather than hands-on GenAI/LLM development. The candidate is a technical Lead Data Scientist specializing in hands-on LangChain/LangGraph and agentic workflows, presenting a significant mismatch in role function and domain expertise.</t>
         </is>
       </c>
       <c r="I61" s="3" t="inlineStr">
@@ -4360,7 +4360,7 @@
       </c>
       <c r="M61" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/business-analyst-instashop-at-talabat-4447352935?position=6&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=gGEviUFke%2FcNigxE2hYK8w%3D%3D</t>
+          <t>https://dk.linkedin.com/jobs/view/ai-product-owner-at-novo-nordisk-4457258669?position=24&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=s56Z90FxaVSj7XKQs6qQuA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -4370,17 +4370,17 @@
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>Senior MLOps/Data Engineer</t>
+          <t>Forretningskonsulent</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>TomTom</t>
+          <t>Bankdata</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>Amsterdam, North Holland, Netherlands</t>
+          <t>Silkeborg, Central Denmark Region, Denmark</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -4389,7 +4389,7 @@
         </is>
       </c>
       <c r="F62" s="8" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G62" s="9" t="inlineStr">
         <is>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H62" s="3" t="inlineStr">
         <is>
-          <t>This is a Senior MLOps/Data Engineer role focusing on PySpark, Databricks, and pipeline orchestration rather than Generative AI or LLMs. While the candidate has Azure and Python experience, the core technical requirements do not align with his GenAI and agentic specialization.</t>
+          <t>This is a business/risk consultant role focusing on regulatory compliance, credit risk models, and SAS/SQL data analysis rather than a hands-on Generative AI or LLM specialization. While the candidate brings strong banking domain experience and Python skills, the core responsibilities do not align with his advanced GenAI and agentic AI expertise.</t>
         </is>
       </c>
       <c r="I62" s="3" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="M62" s="6" t="inlineStr">
         <is>
-          <t>https://nl.linkedin.com/jobs/view/senior-mlops-data-engineer-at-tomtom-4448554856?position=23&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=SHR8gYATTGX6qegw6hmLAw%3D%3D</t>
+          <t>https://dk.linkedin.com/jobs/view/forretningskonsulent-at-bankdata-4448894922?position=22&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=o%2BWOTBX123ODc%2FiV7%2B9GIw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -4433,17 +4433,17 @@
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>Decision Scientist, Marketing Modelling Intelligence, Marketing DSA</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>Vinted</t>
+          <t>MAP</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>Amsterdam, North Holland, Netherlands</t>
+          <t>Copenhagen, Capital Region of Denmark, Denmark</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -4452,7 +4452,7 @@
         </is>
       </c>
       <c r="F63" s="8" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G63" s="9" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
       </c>
       <c r="H63" s="3" t="inlineStr">
         <is>
-          <t>This is a marketing analytics and econometric modeling role focused on Bayesian Media Mix Models, which only touches classical statistics and regression without any GenAI, LLMs, or agentic systems. Furthermore, the seniority expectation (2-4 years) is a major mismatch for a candidate with 10+ years of experience.</t>
+          <t>The role is primarily a backend/full-stack software engineering position requiring .NET/C# and Vue/TypeScript, which does not align with the candidate's core Data Science and GenAI specialization. While there are passing mentions of Python and agentic AI as nice-to-haves, the job is fundamentally a software development role rather than an advanced GenAI/LLM specialist position.</t>
         </is>
       </c>
       <c r="I63" s="3" t="inlineStr">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="M63" s="6" t="inlineStr">
         <is>
-          <t>https://nl.linkedin.com/jobs/view/decision-scientist-marketing-modelling-intelligence-marketing-dsa-at-vinted-4431724987?position=12&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=CGELWLumu99gkHZTfq3gCQ%3D%3D</t>
+          <t>https://dk.linkedin.com/jobs/view/developer-at-map-4459176960?position=23&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=YgE2RztI4uaVgk5SXXlkQw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -4496,17 +4496,17 @@
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>Lead Data Science</t>
+          <t>AI Innovation Specialist - Renewable Energy Solutions</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>Zonneplan</t>
+          <t>Vestas</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>Zwolle, Overijssel, Netherlands</t>
+          <t>Aarhus Municipality, Central Denmark Region, Denmark</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -4515,7 +4515,7 @@
         </is>
       </c>
       <c r="F64" s="8" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G64" s="9" t="inlineStr">
         <is>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H64" s="3" t="inlineStr">
         <is>
-          <t>The role is focused heavily on classical time-series forecasting, energy optimization, and MLOps for trading systems rather than Generative AI, LLMs, or agentic workflows. While the candidate's seniority as a Lead matches well, the lack of core GenAI focus makes this a weak technical fit.</t>
+          <t>The candidate has strong technical skills in Python and machine learning, but this role focuses heavily on industrial AI, computer vision, sensor data, and predictive maintenance in the renewable energy sector rather than the candidate's core specialization in LLMs, RAG, and agentic workflows. Furthermore, the seniority alignment is slightly mismatched as the role asks for 4+ years while the candidate is a senior/lead with 10 years of experience.</t>
         </is>
       </c>
       <c r="I64" s="3" t="inlineStr">
@@ -4549,7 +4549,7 @@
       </c>
       <c r="M64" s="6" t="inlineStr">
         <is>
-          <t>https://nl.linkedin.com/jobs/view/lead-data-science-at-zonneplan-4414158731?position=8&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=1yTKWUbJDbOf0JWJnBF0EQ%3D%3D</t>
+          <t>https://dk.linkedin.com/jobs/view/ai-innovation-specialist-renewable-energy-solutions-at-vestas-4459358646?position=4&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=x6uemge6vMfQH6CFPei6kw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -4559,26 +4559,26 @@
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Scientist (Remote)</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>Confidential</t>
+          <t>Hire Feed</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>Abu Dhabi Emirate, United Arab Emirates</t>
+          <t>United Arab Emirates</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F65" s="8" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G65" s="9" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
       </c>
       <c r="H65" s="3" t="inlineStr">
         <is>
-          <t>This is a Data Engineering role focusing on cloud pipelines, lakehouses, streaming, and data warehousing rather than a GenAI or LLM specialization role. While it mentions building datasets and vector pipelines for AI, the core function is infrastructure and data engineering rather than the candidate's core expertise as a Lead Data Scientist in GenAI and agentic workflows.</t>
+          <t>This role is a generic classical machine learning position focused on predictive modeling, Python, and scikit-learn, with no mention of Generative AI, LLMs, RAG, or agentic systems that form the core of the candidate's expertise. While the candidate has the necessary background to perform the work, it underutilizes his specialized GenAI skillset and matches the scoring guidance for a weaker classical ML/statistics fit.</t>
         </is>
       </c>
       <c r="I65" s="3" t="inlineStr">
@@ -4600,9 +4600,9 @@
           <t>Not stated in JD</t>
         </is>
       </c>
-      <c r="K65" s="7" t="inlineStr">
-        <is>
-          <t>New this run (2026-08-27 06:43 UTC)</t>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>From previous run</t>
         </is>
       </c>
       <c r="L65" s="2" t="inlineStr">
@@ -4612,7 +4612,7 @@
       </c>
       <c r="M65" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/data-engineer-at-confidential-4457913992?position=27&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=0E%2Bet6hk0hz6AFQRQUNpjg%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/data-scientist-remote-at-hire-feed-4459652348?position=8&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=eN2UeQevFS%2FiNl5F%2FHqH8A%3D%3D</t>
         </is>
       </c>
     </row>
@@ -4622,17 +4622,17 @@
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>Head of Data Science</t>
+          <t>Machine Learning (AI) Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>Jex Recruitment | Connecting top talent with leading companies</t>
+          <t>Quik Hire Staffing</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>Abu Dhabi, Abu Dhabi Emirate, United Arab Emirates</t>
+          <t>United Arab Emirates</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -4641,7 +4641,7 @@
         </is>
       </c>
       <c r="F66" s="8" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G66" s="9" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="H66" s="3" t="inlineStr">
         <is>
-          <t>The role requires executive leadership (Head of Data Science) focused on managing teams, strategy, and classical banking use cases rather than hands-on technical GenAI or agentic AI work. This is a significant seniority and role-type mismatch for a Lead Data Scientist specializing in LLMs and RAG.</t>
+          <t>The role is focused heavily on classical Machine Learning, MLOps, deep learning frameworks (TensorFlow, PyTorch), and model training rather than the candidate's core specialization in Generative AI, LLMs, RAG, and agentic systems. Seniority aligns well, but the technical domain mismatch makes this a weaker fit.</t>
         </is>
       </c>
       <c r="I66" s="3" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
-          <t>Possible - relocation support mentioned, visa not explicit</t>
-        </is>
-      </c>
-      <c r="K66" s="7" t="inlineStr">
-        <is>
-          <t>New this run (2026-08-27 06:43 UTC)</t>
+          <t>Not stated in JD</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>From previous run</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
@@ -4675,7 +4675,7 @@
       </c>
       <c r="M66" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/head-of-data-science-at-jex-recruitment-connecting-top-talent-with-leading-companies-4458343957?position=23&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=SiTMdQz8r7KHa1LqknvQjg%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/machine-learning-ai-engineer-hybrid-at-quik-hire-staffing-4459649596?position=5&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=sbTD%2BYZZjPOfeagKS2Yixw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -4685,26 +4685,26 @@
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Consultant Data &amp; AI</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>Mammoet</t>
+          <t>ITDS</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>Schiedam, South Holland, Netherlands</t>
+          <t>Amsterdam, North Holland, Netherlands</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F67" s="8" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="G67" s="9" t="inlineStr">
         <is>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="H67" s="3" t="inlineStr">
         <is>
-          <t>This is a Data Engineer role focused on cloud data platforms, ETL pipelines, and Data Vault modeling, which does not leverage the candidate's core specialization in Generative AI, LLMs, and agentic workflows. Additionally, the required 0-5 years of experience represents a seniority mismatch for a Lead Data Scientist with over 10 years of experience.</t>
+          <t>The role is a generalist data and AI consulting position focusing heavily on data management, business analysis, and governance within the financial sector, rather than a specialized GenAI/LLM engineering role. Additionally, it requires Dutch language proficiency and a consultant/analyst profile that is a mismatch for the candidate's senior GenAI technical expertise.</t>
         </is>
       </c>
       <c r="I67" s="3" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="M67" s="6" t="inlineStr">
         <is>
-          <t>https://nl.linkedin.com/jobs/view/data-engineer-at-mammoet-4459379074?position=24&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=vEO3k7c4HScCtKkTbNh8Xg%3D%3D</t>
+          <t>https://nl.linkedin.com/jobs/view/consultant-data-ai-at-itds-4458351898?position=19&amp;pageNum=0&amp;refId=oiBIn1Czflg0JjZjH5z0Lg%3D%3D&amp;trackingId=1Zr9TFJHo0JFjEQpwgyXZg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -4748,26 +4748,26 @@
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>Medior data-analist</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>Finance Ideas</t>
+          <t>Rubicon Cloud Advisor</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>Utrecht, Utrecht, Netherlands</t>
+          <t>The Randstad, Netherlands</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F68" s="8" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="G68" s="9" t="inlineStr">
         <is>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="H68" s="3" t="inlineStr">
         <is>
-          <t>This is a medior data analyst role focused on financial and strategic healthcare dashboards and predictive modeling using SQL and Excel, with only a passing mention of AI. It does not utilize the candidate's core GenAI, LLM, and agentic specialization, and represents a significant mismatch in both focus and seniority.</t>
+          <t>The role is for an MLOps Engineer focusing on ML infrastructure, pipelines, and deployment using Databricks and MLflow, which touches some of the candidate's supporting tech stack but misses his core Generative AI, LLM, and agentic specialization. Additionally, the job posting requires Dutch language proficiency, though language fit was not factored into the penalty per instructions.</t>
         </is>
       </c>
       <c r="I68" s="3" t="inlineStr">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="M68" s="6" t="inlineStr">
         <is>
-          <t>https://nl.linkedin.com/jobs/view/medior-data-analist-at-finance-ideas-4459185767?position=16&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=Aag%2FWZa%2Bp4QUCt1avtmqXw%3D%3D</t>
+          <t>https://nl.linkedin.com/jobs/view/mlops-engineer-at-rubicon-cloud-advisor-4450093837?position=15&amp;pageNum=0&amp;refId=oiBIn1Czflg0JjZjH5z0Lg%3D%3D&amp;trackingId=bnH0HGZbT4T4t%2FkIxlYWZQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -4811,17 +4811,17 @@
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>Junior Data Scientist – Personalization</t>
+          <t>Decision Scientist, Marketing Modelling Intelligence, Marketing DSA</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>Future Impact</t>
+          <t>Vinted</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>Amsterdam, North Holland, Netherlands</t>
+          <t>Berlin, Berlin, Germany</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -4830,7 +4830,7 @@
         </is>
       </c>
       <c r="F69" s="8" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="G69" s="9" t="inlineStr">
         <is>
@@ -4839,17 +4839,17 @@
       </c>
       <c r="H69" s="3" t="inlineStr">
         <is>
-          <t>This role is a severe seniority and domain mismatch, requiring a junior-level data scientist (1+ years experience) focused on classical machine learning, personalization, and tabular/text mining rather than the candidate's advanced GenAI, LLMs, and agentic orchestration specialization.</t>
+          <t>This is a classical marketing analytics and econometrics role focused on Bayesian Media Mix Modeling and ROI measurement with no mention of Generative AI, LLMs, or agentic systems. Furthermore, the candidate is a Lead Data Scientist with 10+ years of experience, making the 2-4 year experience requirement a significant seniority mismatch.</t>
         </is>
       </c>
       <c r="I69" s="3" t="inlineStr">
         <is>
-          <t>Not stated in JD</t>
+          <t>Yes - German required (see JD for exact level)</t>
         </is>
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
-          <t>Possible - relocation support mentioned, visa not explicit</t>
+          <t>Not stated in JD</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -4864,7 +4864,7 @@
       </c>
       <c r="M69" s="6" t="inlineStr">
         <is>
-          <t>https://nl.linkedin.com/jobs/view/junior-data-scientist-%E2%80%93-personalization-at-future-impact-4459176208?position=6&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=%2F2X0%2FMpduifeqyUanMFmiQ%3D%3D</t>
+          <t>https://de.linkedin.com/jobs/view/decision-scientist-marketing-modelling-intelligence-marketing-dsa-at-vinted-4431734157?position=23&amp;pageNum=0&amp;refId=T%2F0KkBXL%2Fl%2B5Iv5tUGTY7Q%3D%3D&amp;trackingId=ym8Uxiee8AvGv52T5S0EVQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -4874,17 +4874,17 @@
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>Senior Software Developer</t>
+          <t>Data Analyst / Data Science Specialist (m/w/d)</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>Bankdata</t>
+          <t>Molkerei Gropper GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>Silkeborg, Central Denmark Region, Denmark</t>
+          <t>Bissingen, Bavaria, Germany</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -4893,7 +4893,7 @@
         </is>
       </c>
       <c r="F70" s="8" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G70" s="9" t="inlineStr">
         <is>
@@ -4902,12 +4902,12 @@
       </c>
       <c r="H70" s="3" t="inlineStr">
         <is>
-          <t>This is a Senior Software Developer role focused on core data engineering, Java/Spring Boot, Angular, and legacy systems rather than Generative AI or LLMs. Although Databricks, Python, and financial domain experience overlap with the candidate's background, the lack of software engineering specialization in Java/frontend and absence of GenAI/agentic requirements make it a weak technical fit.</t>
+          <t>This role is focused primarily on traditional Data Warehousing, BI, ETL, and reporting with SAP systems, where AI is merely a passing mention of interest rather than a core focus. It is a significant mismatch for the candidate's advanced Generative AI, LLM, and agentic specialization.</t>
         </is>
       </c>
       <c r="I70" s="3" t="inlineStr">
         <is>
-          <t>Not stated in JD</t>
+          <t>Yes - German required (see JD for exact level)</t>
         </is>
       </c>
       <c r="J70" s="3" t="inlineStr">
@@ -4927,7 +4927,7 @@
       </c>
       <c r="M70" s="6" t="inlineStr">
         <is>
-          <t>https://dk.linkedin.com/jobs/view/senior-software-developer-at-bankdata-4449002669?position=27&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=HL%2Flu1131ad6ecWWSqhgeg%3D%3D</t>
+          <t>https://de.linkedin.com/jobs/view/data-analyst-data-science-specialist-m-w-d-at-molkerei-gropper-gmbh-co-kg-4459396175?position=16&amp;pageNum=0&amp;refId=T%2F0KkBXL%2Fl%2B5Iv5tUGTY7Q%3D%3D&amp;trackingId=hDs2N%2Ft3sDgczR%2Fh%2Biow4g%3D%3D</t>
         </is>
       </c>
     </row>
@@ -4937,17 +4937,17 @@
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>Data Scientist (m/w/d)</t>
+          <t>Specialist Data Science</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>Alliance Healthcare Deutschland GmbH</t>
+          <t>HDI Group</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>Frankfurt, Hesse, Germany</t>
+          <t>Hannover, Lower Saxony, Germany</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -4956,7 +4956,7 @@
         </is>
       </c>
       <c r="F71" s="8" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="G71" s="9" t="inlineStr">
         <is>
@@ -4965,12 +4965,12 @@
       </c>
       <c r="H71" s="3" t="inlineStr">
         <is>
-          <t>[FALLBACK SCORER - Gemini call failed] Matched 1 core GenAI term(s) via keyword search. Verify manually; this is a degraded-mode score.</t>
+          <t>This role focuses heavily on data engineering, analytics, and R-based pricing tools within the insurance domain, offering only passing alignment with classical data science rather than the candidate's core GenAI, LLMs, and agentic AI specialization.</t>
         </is>
       </c>
       <c r="I71" s="3" t="inlineStr">
         <is>
-          <t>Yes - fluent/C1+ German explicitly required</t>
+          <t>Not stated in JD</t>
         </is>
       </c>
       <c r="J71" s="3" t="inlineStr">
@@ -4990,7 +4990,7 @@
       </c>
       <c r="M71" s="6" t="inlineStr">
         <is>
-          <t>https://de.linkedin.com/jobs/view/data-scientist-m-w-d-at-alliance-healthcare-deutschland-gmbh-4459307202?position=1&amp;pageNum=0&amp;refId=T%2F0KkBXL%2Fl%2B5Iv5tUGTY7Q%3D%3D&amp;trackingId=a%2BRgoPI8HwvjxaQsctZHFQ%3D%3D</t>
+          <t>https://de.linkedin.com/jobs/view/specialist-data-science-at-hdi-group-4449488553?position=9&amp;pageNum=0&amp;refId=T%2F0KkBXL%2Fl%2B5Iv5tUGTY7Q%3D%3D&amp;trackingId=4kEwk2%2BQdqX%2FDjmyxZ2xyA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -5000,17 +5000,17 @@
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>Data Analytics Manager</t>
+          <t>Data Scientist (m/w/d) für analytisches CRM und datengestützte Potenziale</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>Salt</t>
+          <t>R+V Versicherung</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>Dubai, United Arab Emirates</t>
+          <t>Wiesbaden, Hesse, Germany</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -5019,7 +5019,7 @@
         </is>
       </c>
       <c r="F72" s="8" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="G72" s="9" t="inlineStr">
         <is>
@@ -5028,12 +5028,12 @@
       </c>
       <c r="H72" s="3" t="inlineStr">
         <is>
-          <t>This is a traditional Business Intelligence and Analytics Manager role focused on SQL, BI platforms, and dashboard governance, which is entirely misaligned with the candidate's core specialization in Generative AI, LLMs, and agentic systems. Although the seniority and years of experience generally align, the technical scope is classical data analytics rather than advanced AI.</t>
+          <t>This role focuses on analytical CRM, customer segmentation, and rule-based next-best-offer systems using SQL and traditional data methods, offering only passing mention of AI approaches. It lacks the core Generative AI, LLM, and agentic specialization that defines the candidate's profile.</t>
         </is>
       </c>
       <c r="I72" s="3" t="inlineStr">
         <is>
-          <t>Not stated in JD</t>
+          <t>Yes - fluent/C1+ German explicitly required</t>
         </is>
       </c>
       <c r="J72" s="3" t="inlineStr">
@@ -5053,7 +5053,7 @@
       </c>
       <c r="M72" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/data-analytics-manager-at-salt-4444546523?position=19&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=nocZsmIJ8Yx5LNeo0Qbyfg%3D%3D</t>
+          <t>https://de.linkedin.com/jobs/view/data-scientist-m-w-d-f%C3%BCr-analytisches-crm-und-datengest%C3%BCtzte-potenziale-at-r%2Bv-versicherung-4446660524?position=7&amp;pageNum=0&amp;refId=T%2F0KkBXL%2Fl%2B5Iv5tUGTY7Q%3D%3D&amp;trackingId=na3WACzOriMr43dXtkckXw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -5063,17 +5063,17 @@
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>Junior Data Scientist Hypotheken DataLab (Amersfoort)</t>
+          <t>Senior Data Scientist (m/f/d)</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>Future Impact</t>
+          <t>AutoScout24</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>Amsterdam, North Holland, Netherlands</t>
+          <t>Munich, Bavaria, Germany</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -5082,7 +5082,7 @@
         </is>
       </c>
       <c r="F73" s="8" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="G73" s="9" t="inlineStr">
         <is>
@@ -5091,7 +5091,7 @@
       </c>
       <c r="H73" s="3" t="inlineStr">
         <is>
-          <t>This is a junior data scientist role focused on traditional mortgage analytics and classical machine learning, representing a severe seniority and domain mismatch for a 10+ year GenAI lead specialist. Additionally, the role explicitly requires fluent Dutch language skills which the candidate lacks.</t>
+          <t>[FALLBACK SCORER - Gemini call failed] Matched 2 core GenAI term(s) via keyword search. Verify manually; this is a degraded-mode score.</t>
         </is>
       </c>
       <c r="I73" s="3" t="inlineStr">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="M73" s="6" t="inlineStr">
         <is>
-          <t>https://nl.linkedin.com/jobs/view/junior-data-scientist-hypotheken-datalab-amersfoort-at-future-impact-4459169232?position=10&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=PCmMM9pEfOFRNmRrvy5XFw%3D%3D</t>
+          <t>https://de.linkedin.com/jobs/view/senior-data-scientist-m-f-d-at-autoscout24-4432214339?position=11&amp;pageNum=0&amp;refId=T%2F0KkBXL%2Fl%2B5Iv5tUGTY7Q%3D%3D&amp;trackingId=7SGOVxV%2FwAFkUhW1fBv2EA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -5126,17 +5126,17 @@
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>Manager – Data Engineering, Architecture &amp; Reporting Platform - Dubai / Abu Dhabi</t>
+          <t>Data Analyst / Scientist (m/w/d)</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>Agthia Group PJSC</t>
+          <t>Dr. Wolff Group</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>Dubai, Dubai, United Arab Emirates</t>
+          <t>Bielefeld, North Rhine-Westphalia, Germany</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -5145,7 +5145,7 @@
         </is>
       </c>
       <c r="F74" s="8" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="G74" s="9" t="inlineStr">
         <is>
@@ -5154,12 +5154,12 @@
       </c>
       <c r="H74" s="3" t="inlineStr">
         <is>
-          <t>This is a data engineering and platform architecture role focused on cloud lakehouse setup, ETL pipelines, and semantic layers, completely lacking any Generative AI, LLMs, or agentic workflows which form the candidate's core specialization. Additionally, while the candidate has 10+ years of experience, the heavy infrastructure and data engineering focus makes it a weak technical fit.</t>
+          <t>[FALLBACK SCORER - Gemini call failed] Matched 2 core GenAI term(s) via keyword search. Verify manually; this is a degraded-mode score.</t>
         </is>
       </c>
       <c r="I74" s="3" t="inlineStr">
         <is>
-          <t>Not stated in JD</t>
+          <t>Yes - German required (see JD for exact level)</t>
         </is>
       </c>
       <c r="J74" s="3" t="inlineStr">
@@ -5179,7 +5179,7 @@
       </c>
       <c r="M74" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/manager-%E2%80%93-data-engineering-architecture-reporting-platform-dubai-abu-dhabi-at-agthia-group-pjsc-4457225736?position=30&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=uCZRYkPcw%2FLl2O0EJmhVdQ%3D%3D</t>
+          <t>https://de.linkedin.com/jobs/view/data-analyst-scientist-m-w-d-at-dr-wolff-group-4459323885?position=2&amp;pageNum=0&amp;refId=T%2F0KkBXL%2Fl%2B5Iv5tUGTY7Q%3D%3D&amp;trackingId=fnXlAvETsQ4TzuiWcW6AWA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -5189,17 +5189,17 @@
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>Research Informatics Data Engineer</t>
+          <t>Data Scientist - AI Search &amp; Ranking</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>Lundbeck</t>
+          <t>trivago</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>Copenhagen, Capital Region of Denmark, Denmark</t>
+          <t>Düsseldorf, North Rhine-Westphalia, Germany</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
@@ -5208,7 +5208,7 @@
         </is>
       </c>
       <c r="F75" s="8" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="G75" s="9" t="inlineStr">
         <is>
@@ -5217,7 +5217,7 @@
       </c>
       <c r="H75" s="3" t="inlineStr">
         <is>
-          <t>This is a Research Informatics Data Engineer role focusing on life sciences data management, laboratory informatics, and scientific platform integration rather than Generative AI or advanced LLM application development. While LLMs are briefly mentioned as an optional tool for coding assistance, the candidate's core specialization in multi-agent orchestration, RAG architectures, and production GenAI systems does not align with this software/data engineering workflow role.</t>
+          <t>[FALLBACK SCORER - Gemini call failed] Matched 2 core GenAI term(s) via keyword search. Verify manually; this is a degraded-mode score.</t>
         </is>
       </c>
       <c r="I75" s="3" t="inlineStr">
@@ -5242,7 +5242,7 @@
       </c>
       <c r="M75" s="6" t="inlineStr">
         <is>
-          <t>https://dk.linkedin.com/jobs/view/research-informatics-data-engineer-at-lundbeck-4448898202?position=5&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=5fkJnjfpF2QdhMDLztM5Vw%3D%3D</t>
+          <t>https://de.linkedin.com/jobs/view/data-scientist-ai-search-ranking-at-trivago-4451695166?position=3&amp;pageNum=0&amp;refId=T%2F0KkBXL%2Fl%2B5Iv5tUGTY7Q%3D%3D&amp;trackingId=653eapm3ns02Vx9zaTVbNw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -5252,17 +5252,17 @@
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>Head of Data Analytics</t>
+          <t>Senior Manager, Digital Forensics &amp; eDiscovery</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>Right Calibre Consulting</t>
+          <t>Robert Walters</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>Dubai, United Arab Emirates</t>
+          <t>Dubai, Dubai, United Arab Emirates</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -5271,7 +5271,7 @@
         </is>
       </c>
       <c r="F76" s="8" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="G76" s="9" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="H76" s="3" t="inlineStr">
         <is>
-          <t>This is a Head of Data Analytics role focused on traditional BI, commercial insights, data governance, and leading analytics teams in the media and technology sector. It completely lacks any GenAI, LLM, or agentic AI focus, and the Head/Director-level leadership scope exceeds the candidate's current Lead Data Scientist level.</t>
+          <t>The role is focused heavily on digital forensics, eDiscovery, and regulatory investigations, which does not align with the candidate's core specialization in Generative AI, LangGraph, and agentic LLM pipelines. While it mentions emerging AI technologies and LLMs as a secondary component, the candidate's strong GenAI background is largely mismatched with the core forensic and eDiscovery tech stack.</t>
         </is>
       </c>
       <c r="I76" s="3" t="inlineStr">
@@ -5305,7 +5305,7 @@
       </c>
       <c r="M76" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/head-of-data-analytics-at-right-calibre-consulting-4459174081?position=24&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=dZTHuLROd%2FTUDsdWxlHCPg%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/senior-manager-digital-forensics-ediscovery-at-robert-walters-4457258106?position=26&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=nugpWYWcIAXvX9xB18JHdw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -5315,12 +5315,12 @@
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>Customer Intelligence Manager</t>
+          <t>Business Analyst - instashop</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>Al Tayer Insignia</t>
+          <t>talabat</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
@@ -5334,7 +5334,7 @@
         </is>
       </c>
       <c r="F77" s="8" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="G77" s="9" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="H77" s="3" t="inlineStr">
         <is>
-          <t>This Customer Intelligence Manager role focuses on market research, consumer insights, and retail analytics rather than Generative AI, LLMs, or agentic systems. It represents a fundamental domain mismatch for the candidate's specialized technical profile.</t>
+          <t>This is a Business Analyst role focused on traditional commercial analytics, SQL, and BI reporting, with only passing mentions of using generative AI tools as productivity boosters. It represents a significant mismatch in domain and seniority compared to the candidate's core specialization as a Lead GenAI/LLM/Agentic AI specialist with 10+ years of experience.</t>
         </is>
       </c>
       <c r="I77" s="3" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="M77" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/customer-intelligence-manager-at-al-tayer-insignia-4457235794?position=9&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=PiyoN3pPhVcxMx9vtAIf5g%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/business-analyst-instashop-at-talabat-4447352935?position=6&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=gGEviUFke%2FcNigxE2hYK8w%3D%3D</t>
         </is>
       </c>
     </row>
@@ -5378,17 +5378,17 @@
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>Service Review Insights Lead</t>
+          <t>Senior MLOps/Data Engineer</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>Discovered MENA</t>
+          <t>TomTom</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>Dubai, United Arab Emirates</t>
+          <t>Amsterdam, North Holland, Netherlands</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -5397,7 +5397,7 @@
         </is>
       </c>
       <c r="F78" s="8" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="G78" s="9" t="inlineStr">
         <is>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="H78" s="3" t="inlineStr">
         <is>
-          <t>This role focuses heavily on operational analytics, call center metrics, and executive board presentations with no connection to Generative AI, LLMs, or data science. It is completely outside the candidate's core technical specialization and domain.</t>
+          <t>This is a Senior MLOps/Data Engineer role focusing on PySpark, Databricks, and pipeline orchestration rather than Generative AI or LLMs. While the candidate has Azure and Python experience, the core technical requirements do not align with his GenAI and agentic specialization.</t>
         </is>
       </c>
       <c r="I78" s="3" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="M78" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/service-review-insights-lead-at-discovered-mena-4456958136?position=10&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=oMos4kbDfkh42RiAd%2Bimnw%3D%3D</t>
+          <t>https://nl.linkedin.com/jobs/view/senior-mlops-data-engineer-at-tomtom-4448554856?position=23&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=SHR8gYATTGX6qegw6hmLAw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -5441,17 +5441,17 @@
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>QEHS Digital Analyst - UAE National</t>
+          <t>Decision Scientist, Marketing Modelling Intelligence, Marketing DSA</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>Siemens Energy</t>
+          <t>Vinted</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>Dubai, Dubai, United Arab Emirates</t>
+          <t>Amsterdam, North Holland, Netherlands</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
@@ -5460,7 +5460,7 @@
         </is>
       </c>
       <c r="F79" s="8" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="G79" s="9" t="inlineStr">
         <is>
@@ -5469,7 +5469,7 @@
       </c>
       <c r="H79" s="3" t="inlineStr">
         <is>
-          <t>This role is focused on Quality, Environment, Health, and Safety (QEHS) digital transformation, enterprise systems like SAP and Salesforce, and quality management standards rather than Generative AI or LLM specialization. It represents a significant domain and technical mismatch for a Lead Data Scientist specializing in agentic AI and RAG architectures.</t>
+          <t>This is a marketing analytics and econometric modeling role focused on Bayesian Media Mix Models, which only touches classical statistics and regression without any GenAI, LLMs, or agentic systems. Furthermore, the seniority expectation (2-4 years) is a major mismatch for a candidate with 10+ years of experience.</t>
         </is>
       </c>
       <c r="I79" s="3" t="inlineStr">
@@ -5494,7 +5494,7 @@
       </c>
       <c r="M79" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/qehs-digital-analyst-uae-national-at-siemens-energy-4439835820?position=8&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=jLKXnOBvB%2BaDszNV2BAbbA%3D%3D</t>
+          <t>https://nl.linkedin.com/jobs/view/decision-scientist-marketing-modelling-intelligence-marketing-dsa-at-vinted-4431724987?position=12&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=CGELWLumu99gkHZTfq3gCQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -5504,17 +5504,17 @@
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>Data Analyst - UAE National, ICQA/LND Analytics Team</t>
+          <t>Lead Data Science</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Zonneplan</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>Dubai, Dubai, United Arab Emirates</t>
+          <t>Zwolle, Overijssel, Netherlands</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -5523,7 +5523,7 @@
         </is>
       </c>
       <c r="F80" s="8" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="G80" s="9" t="inlineStr">
         <is>
@@ -5532,7 +5532,7 @@
       </c>
       <c r="H80" s="3" t="inlineStr">
         <is>
-          <t>This Data Analyst role at Amazon focuses on SQL reporting, dashboards, and operational data management, lacking any connection to the candidate's core GenAI, LLMs, and agentic AI specialization. Furthermore, the role is restricted to UAE Nationals and represents a significant mismatch in domain and function.</t>
+          <t>The role is focused heavily on classical time-series forecasting, energy optimization, and MLOps for trading systems rather than Generative AI, LLMs, or agentic workflows. While the candidate's seniority as a Lead matches well, the lack of core GenAI focus makes this a weak technical fit.</t>
         </is>
       </c>
       <c r="I80" s="3" t="inlineStr">
@@ -5557,7 +5557,7 @@
       </c>
       <c r="M80" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/data-analyst-uae-national-icqa-lnd-analytics-team-at-amazon-4459169756?position=7&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=dtuARx3ylMmIho9xSQNgYg%3D%3D</t>
+          <t>https://nl.linkedin.com/jobs/view/lead-data-science-at-zonneplan-4414158731?position=8&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=1yTKWUbJDbOf0JWJnBF0EQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -5567,17 +5567,17 @@
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>Senior Data Analyst - Strategy</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>dubizzle</t>
+          <t>Confidential</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>Dubai, Dubai, United Arab Emirates</t>
+          <t>Abu Dhabi Emirate, United Arab Emirates</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -5586,7 +5586,7 @@
         </is>
       </c>
       <c r="F81" s="8" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="G81" s="9" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="H81" s="3" t="inlineStr">
         <is>
-          <t>This is a Senior Data Analyst - Strategy role focused on business analytics, executive dashboards, and commercial growth rather than AI, lacking any GenAI, LLM, or agentic specialization. Additionally, it represents a domain and functional mismatch for an AI/ML Lead Data Scientist.</t>
+          <t>This is a Data Engineering role focusing on cloud pipelines, lakehouses, streaming, and data warehousing rather than a GenAI or LLM specialization role. While it mentions building datasets and vector pipelines for AI, the core function is infrastructure and data engineering rather than the candidate's core expertise as a Lead Data Scientist in GenAI and agentic workflows.</t>
         </is>
       </c>
       <c r="I81" s="3" t="inlineStr">
@@ -5620,7 +5620,7 @@
       </c>
       <c r="M81" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/senior-data-analyst-strategy-at-dubizzle-4446647656?position=5&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=oDSAohEFPlpSK2IK3vFpNg%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/data-engineer-at-confidential-4457913992?position=27&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=0E%2Bet6hk0hz6AFQRQUNpjg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -5630,26 +5630,26 @@
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Head of Data Science</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>Insify</t>
+          <t>Jex Recruitment | Connecting top talent with leading companies</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>Amsterdam, North Holland, Netherlands</t>
+          <t>Abu Dhabi, Abu Dhabi Emirate, United Arab Emirates</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F82" s="8" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="G82" s="9" t="inlineStr">
         <is>
@@ -5658,17 +5658,17 @@
       </c>
       <c r="H82" s="3" t="inlineStr">
         <is>
-          <t>This is a classical Data Analyst role focused on SQL, A/B testing, and business metrics, which is completely unrelated to the candidate's core specialization in Generative AI, LLMs, and agentic workflows.</t>
+          <t>The role requires executive leadership (Head of Data Science) focused on managing teams, strategy, and classical banking use cases rather than hands-on technical GenAI or agentic AI work. This is a significant seniority and role-type mismatch for a Lead Data Scientist specializing in LLMs and RAG.</t>
         </is>
       </c>
       <c r="I82" s="3" t="inlineStr">
         <is>
-          <t>Yes - German required (see JD for exact level)</t>
+          <t>Not stated in JD</t>
         </is>
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
-          <t>Not stated in JD</t>
+          <t>Possible - relocation support mentioned, visa not explicit</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -5683,7 +5683,7 @@
       </c>
       <c r="M82" s="6" t="inlineStr">
         <is>
-          <t>https://nl.linkedin.com/jobs/view/data-analyst-at-insify-4457952341?position=26&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=kZIox38P2PV0MRG6Tih7Dw%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/head-of-data-science-at-jex-recruitment-connecting-top-talent-with-leading-companies-4458343957?position=23&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=SiTMdQz8r7KHa1LqknvQjg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -5693,12 +5693,12 @@
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>Research Analyst - NL</t>
+          <t>Data Scientist Delivery Domain</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>OPEN Health</t>
+          <t>Coolblue</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr">
@@ -5708,11 +5708,11 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F83" s="8" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="G83" s="9" t="inlineStr">
         <is>
@@ -5721,7 +5721,7 @@
       </c>
       <c r="H83" s="3" t="inlineStr">
         <is>
-          <t>This role focuses on health economics, meta-analysis, and HEOR modeling (cost-effectiveness, budget impact) using R and statistical software, which is completely unrelated to the candidate's GenAI, LLMs, and agentic AI specialization.</t>
+          <t>This is a classical forecasting and operations research role focusing on delivery and installation planning using Python and SQL, with no mention of Generative AI, LLMs, or agentic systems which are the candidate's core specialization. Although the candidate has background in traditional machine learning that overlaps slightly, it represents a weak fit for his current profile.</t>
         </is>
       </c>
       <c r="I83" s="3" t="inlineStr">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="M83" s="6" t="inlineStr">
         <is>
-          <t>https://nl.linkedin.com/jobs/view/research-analyst-nl-at-open-health-4457247414?position=28&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=lxrHLFZXxcKuwp8%2F8mz0KA%3D%3D</t>
+          <t>https://nl.linkedin.com/jobs/view/data-scientist-delivery-domain-at-coolblue-4459662808?position=3&amp;pageNum=0&amp;refId=oiBIn1Czflg0JjZjH5z0Lg%3D%3D&amp;trackingId=V2dKcwpv0YpijBJw41fQVg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -5756,26 +5756,26 @@
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>Data Analyst / Data Scientist</t>
+          <t>Lead Data Scientist, Revenue - Ads, Revenue</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>Trinamics</t>
+          <t>Vinted</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>North Brabant, Netherlands</t>
+          <t>Amsterdam, North Holland, Netherlands</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F84" s="8" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="G84" s="9" t="inlineStr">
         <is>
@@ -5784,7 +5784,7 @@
       </c>
       <c r="H84" s="3" t="inlineStr">
         <is>
-          <t>This is a financial reporting, data analysis, and dashboard-building role focusing on SAP, Spotfire, and Power BI with no connection to Generative AI, LLMs, or agentic systems. It is entirely unrelated to the candidate's core specialization and represents a major mismatch in domain and technical stack.</t>
+          <t>This role focuses heavily on Ad Tech systems, auction mechanics, ads ranking, and real-time optimization, which falls outside the candidate's core specialization in Generative AI, LLMs, and agentic pipelines. While the seniority level (Lead Data Scientist) aligns, the domain mismatch makes it a weak technical fit.</t>
         </is>
       </c>
       <c r="I84" s="3" t="inlineStr">
@@ -5809,7 +5809,7 @@
       </c>
       <c r="M84" s="6" t="inlineStr">
         <is>
-          <t>https://nl.linkedin.com/jobs/view/data-analyst-data-scientist-at-trinamics-4459172477?position=15&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=wKQaRNJqc3u7QhTWjoCU%2FQ%3D%3D</t>
+          <t>https://nl.linkedin.com/jobs/view/lead-data-scientist-revenue-ads-revenue-at-vinted-4431741084?position=8&amp;pageNum=0&amp;refId=oiBIn1Czflg0JjZjH5z0Lg%3D%3D&amp;trackingId=ZcYNzhXf9h2M3%2FWEms9aMw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -5819,26 +5819,26 @@
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>De Rijksoverheid zoekt: Data scientist AI driven weather model</t>
+          <t>AI Product Manager</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>KNMI - Royal Netherlands Meteorological Institute</t>
+          <t>Auxo Talent</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>De Bilt, Utrecht, Netherlands</t>
+          <t>Dubai, United Arab Emirates</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F85" s="8" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="G85" s="9" t="inlineStr">
         <is>
@@ -5847,7 +5847,7 @@
       </c>
       <c r="H85" s="3" t="inlineStr">
         <is>
-          <t>This role focuses on specialized deep learning for meteorological modeling, graph neural networks, and diffusion models applied to weather forecasting, which has virtually no overlap with the candidate's core GenAI, LLMs, and agentic AI specialization.</t>
+          <t>This role is for an AI Product Manager rather than a hands-on technical Data Scientist or Generative AI engineer. While the candidate has deep technical expertise in GenAI and relevant fintech domain knowledge, he lacks the required professional product management background and roadmap-owning experience demanded by the position.</t>
         </is>
       </c>
       <c r="I85" s="3" t="inlineStr">
@@ -5860,9 +5860,9 @@
           <t>Not stated in JD</t>
         </is>
       </c>
-      <c r="K85" s="2" t="inlineStr">
-        <is>
-          <t>From previous run</t>
+      <c r="K85" s="7" t="inlineStr">
+        <is>
+          <t>New this run (2026-08-27 15:40 UTC)</t>
         </is>
       </c>
       <c r="L85" s="2" t="inlineStr">
@@ -5872,7 +5872,7 @@
       </c>
       <c r="M85" s="6" t="inlineStr">
         <is>
-          <t>https://nl.linkedin.com/jobs/view/de-rijksoverheid-zoekt-data-scientist-ai-driven-weather-model-at-knmi-royal-netherlands-meteorological-institute-4459321694?position=7&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=uEDe9phb4vscnrkupOYRog%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/ai-product-manager-at-auxo-talent-4458373508?position=12&amp;pageNum=0&amp;refId=50H6yCrEXIuhgr6eqEojNg%3D%3D&amp;trackingId=y5Nqep1ywbJPUkaTD9Vo3g%3D%3D</t>
         </is>
       </c>
     </row>
@@ -5882,26 +5882,26 @@
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>Decision Scientist, Trust &amp; Safety</t>
+          <t>AI and Data Architect</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>Vinted</t>
+          <t>Fundamentl</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>Amsterdam, North Holland, Netherlands</t>
+          <t>Dubai, United Arab Emirates</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F86" s="8" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="G86" s="9" t="inlineStr">
         <is>
@@ -5910,7 +5910,7 @@
       </c>
       <c r="H86" s="3" t="inlineStr">
         <is>
-          <t>This is a Decision Scientist role focused on product experimentation, SQL/BI dashboards, and Trust &amp; Safety analytics, which is completely unrelated to the candidate's core specialization in Generative AI, LLMs, and agentic workflows.</t>
+          <t>The role aligns well technically with the candidate's specialization in GenAI, Agentic AI, RAG, LangChain, LangGraph, and Azure tools. However, there is a severe seniority mismatch requiring 18+ years of experience for an AI and Data Architect role, whereas the candidate has 10 years of experience, making it a weak fit.</t>
         </is>
       </c>
       <c r="I86" s="3" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
-          <t>Not stated in JD</t>
-        </is>
-      </c>
-      <c r="K86" s="2" t="inlineStr">
-        <is>
-          <t>From previous run</t>
+          <t>Yes - explicitly stated in JD</t>
+        </is>
+      </c>
+      <c r="K86" s="7" t="inlineStr">
+        <is>
+          <t>New this run (2026-08-27 15:40 UTC)</t>
         </is>
       </c>
       <c r="L86" s="2" t="inlineStr">
@@ -5935,7 +5935,7 @@
       </c>
       <c r="M86" s="6" t="inlineStr">
         <is>
-          <t>https://nl.linkedin.com/jobs/view/decision-scientist-trust-safety-at-vinted-4431734156?position=13&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=5DKFgkv450iADwhSNzZiDw%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/ai-and-data-architect-at-fundamentl-4459845026?position=11&amp;pageNum=0&amp;refId=50H6yCrEXIuhgr6eqEojNg%3D%3D&amp;trackingId=Bd15IH4kHpjPXnejnC%2BLzw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -5945,17 +5945,17 @@
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - System Optimization</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>Danfoss</t>
+          <t>Mammoet</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>Copenhagen, Capital Region of Denmark, Denmark</t>
+          <t>Schiedam, South Holland, Netherlands</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
@@ -5964,7 +5964,7 @@
         </is>
       </c>
       <c r="F87" s="8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="G87" s="9" t="inlineStr">
         <is>
@@ -5973,12 +5973,12 @@
       </c>
       <c r="H87" s="3" t="inlineStr">
         <is>
-          <t>This is a Senior Data Scientist role focused on physical modelling, thermo-hydraulic simulation, and Mixed-Integer Linear Programming (MILP) for energy networks, which has zero overlap with the candidate's core specialization in Generative AI, LLMs, and agentic systems.</t>
+          <t>This is a Data Engineer role focused on cloud data platforms, ETL pipelines, and Data Vault modeling, which does not leverage the candidate's core specialization in Generative AI, LLMs, and agentic workflows. Additionally, the required 0-5 years of experience represents a seniority mismatch for a Lead Data Scientist with over 10 years of experience.</t>
         </is>
       </c>
       <c r="I87" s="3" t="inlineStr">
         <is>
-          <t>No - English fluency stated as sufficient</t>
+          <t>Not stated in JD</t>
         </is>
       </c>
       <c r="J87" s="3" t="inlineStr">
@@ -5998,7 +5998,7 @@
       </c>
       <c r="M87" s="6" t="inlineStr">
         <is>
-          <t>https://dk.linkedin.com/jobs/view/senior-data-scientist-system-optimization-at-danfoss-4459328391?position=28&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=pWSiaSPEvTB%2Fj17raCtBPA%3D%3D</t>
+          <t>https://nl.linkedin.com/jobs/view/data-engineer-at-mammoet-4459379074?position=24&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=vEO3k7c4HScCtKkTbNh8Xg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -6008,17 +6008,17 @@
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - System Optimization</t>
+          <t>Medior data-analist</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>Danfoss</t>
+          <t>Finance Ideas</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>Kolding, Region of Southern Denmark, Denmark</t>
+          <t>Utrecht, Utrecht, Netherlands</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -6027,7 +6027,7 @@
         </is>
       </c>
       <c r="F88" s="8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="G88" s="9" t="inlineStr">
         <is>
@@ -6036,12 +6036,12 @@
       </c>
       <c r="H88" s="3" t="inlineStr">
         <is>
-          <t>This is a Senior Data Scientist role focused on physical modelling, thermo-hydraulic simulation of energy networks, and Mixed-Integer Linear Programming (MILP), which is entirely unrelated to the candidate's core specialization in Generative AI, LLMs, and agentic systems.</t>
+          <t>This is a medior data analyst role focused on financial and strategic healthcare dashboards and predictive modeling using SQL and Excel, with only a passing mention of AI. It does not utilize the candidate's core GenAI, LLM, and agentic specialization, and represents a significant mismatch in both focus and seniority.</t>
         </is>
       </c>
       <c r="I88" s="3" t="inlineStr">
         <is>
-          <t>No - English fluency stated as sufficient</t>
+          <t>Not stated in JD</t>
         </is>
       </c>
       <c r="J88" s="3" t="inlineStr">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="M88" s="6" t="inlineStr">
         <is>
-          <t>https://dk.linkedin.com/jobs/view/senior-data-scientist-system-optimization-at-danfoss-4459334294?position=29&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=6IO8CqSe4TjOJrnH%2BoTbig%3D%3D</t>
+          <t>https://nl.linkedin.com/jobs/view/medior-data-analist-at-finance-ideas-4459185767?position=16&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=Aag%2FWZa%2Bp4QUCt1avtmqXw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -6071,17 +6071,17 @@
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>Product Owner</t>
+          <t>Junior Data Scientist – Personalization</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>Ørsted</t>
+          <t>Future Impact</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>Gentofte, Capital Region of Denmark, Denmark</t>
+          <t>Amsterdam, North Holland, Netherlands</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
@@ -6090,7 +6090,7 @@
         </is>
       </c>
       <c r="F89" s="8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="G89" s="9" t="inlineStr">
         <is>
@@ -6099,7 +6099,7 @@
       </c>
       <c r="H89" s="3" t="inlineStr">
         <is>
-          <t>This is a Product Owner role focused on quantitative analytics, portfolio models, and trading infrastructure rather than a hands-on Generative AI or data science engineering position. It is completely outside the candidate's core specialization in LLMs, RAG, and agentic systems, and involves product management responsibilities rather than technical AI development.</t>
+          <t>This role is a severe seniority and domain mismatch, requiring a junior-level data scientist (1+ years experience) focused on classical machine learning, personalization, and tabular/text mining rather than the candidate's advanced GenAI, LLMs, and agentic orchestration specialization.</t>
         </is>
       </c>
       <c r="I89" s="3" t="inlineStr">
@@ -6109,7 +6109,7 @@
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
-          <t>Not stated in JD</t>
+          <t>Possible - relocation support mentioned, visa not explicit</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
@@ -6124,7 +6124,7 @@
       </c>
       <c r="M89" s="6" t="inlineStr">
         <is>
-          <t>https://dk.linkedin.com/jobs/view/product-owner-at-%C3%B8rsted-4457976275?position=30&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=kwPJx%2Freb7nWWcV4YkYqtg%3D%3D</t>
+          <t>https://nl.linkedin.com/jobs/view/junior-data-scientist-%E2%80%93-personalization-at-future-impact-4459176208?position=6&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=%2F2X0%2FMpduifeqyUanMFmiQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -6134,17 +6134,17 @@
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>Product Owner</t>
+          <t>Senior Software Developer</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>Ørsted</t>
+          <t>Bankdata</t>
         </is>
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>Gentofte, Capital Region of Denmark, Denmark</t>
+          <t>Silkeborg, Central Denmark Region, Denmark</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -6153,7 +6153,7 @@
         </is>
       </c>
       <c r="F90" s="8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G90" s="9" t="inlineStr">
         <is>
@@ -6162,7 +6162,7 @@
       </c>
       <c r="H90" s="3" t="inlineStr">
         <is>
-          <t>This is a Product Owner role focused on commodity and energy trading platforms rather than a hands-on technical Generative AI, LLM, or agentic AI role. There is a severe mismatch in job function and seniority focus, as the candidate is a technical Lead Data Scientist specializing in hands-on GenAI systems.</t>
+          <t>This is a Senior Software Developer role focused on core data engineering, Java/Spring Boot, Angular, and legacy systems rather than Generative AI or LLMs. Although Databricks, Python, and financial domain experience overlap with the candidate's background, the lack of software engineering specialization in Java/frontend and absence of GenAI/agentic requirements make it a weak technical fit.</t>
         </is>
       </c>
       <c r="I90" s="3" t="inlineStr">
@@ -6187,7 +6187,7 @@
       </c>
       <c r="M90" s="6" t="inlineStr">
         <is>
-          <t>https://dk.linkedin.com/jobs/view/product-owner-at-%C3%B8rsted-4457969343?position=16&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=Srm0W8oPqBLXtVvd0AdJlg%3D%3D</t>
+          <t>https://dk.linkedin.com/jobs/view/senior-software-developer-at-bankdata-4449002669?position=27&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=HL%2Flu1131ad6ecWWSqhgeg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -6197,17 +6197,17 @@
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>Dataspecialist - Afd. for Uddannelse og Studerende</t>
+          <t>Data Scientist (m/w/d)</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>DTU - Technical University of Denmark</t>
+          <t>Alliance Healthcare Deutschland GmbH</t>
         </is>
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>Kongens Lyngby, Capital Region of Denmark, Denmark</t>
+          <t>Frankfurt, Hesse, Germany</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
@@ -6216,7 +6216,7 @@
         </is>
       </c>
       <c r="F91" s="8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G91" s="9" t="inlineStr">
         <is>
@@ -6225,12 +6225,12 @@
       </c>
       <c r="H91" s="3" t="inlineStr">
         <is>
-          <t>This role at DTU focuses on educational data analysis, stakeholder communication, and business intelligence reporting within a university setting, completely lacking any connection to the candidate's core GenAI, LLMs, or agentic AI specialization.</t>
+          <t>[FALLBACK SCORER - Gemini call failed] Matched 1 core GenAI term(s) via keyword search. Verify manually; this is a degraded-mode score.</t>
         </is>
       </c>
       <c r="I91" s="3" t="inlineStr">
         <is>
-          <t>Not stated in JD</t>
+          <t>Yes - fluent/C1+ German explicitly required</t>
         </is>
       </c>
       <c r="J91" s="3" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="M91" s="6" t="inlineStr">
         <is>
-          <t>https://dk.linkedin.com/jobs/view/dataspecialist-afd-for-uddannelse-og-studerende-at-dtu-technical-university-of-denmark-4458711406?position=12&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=jpgFSNpWhcVL9zGHYU%2Fxbw%3D%3D</t>
+          <t>https://de.linkedin.com/jobs/view/data-scientist-m-w-d-at-alliance-healthcare-deutschland-gmbh-4459307202?position=1&amp;pageNum=0&amp;refId=T%2F0KkBXL%2Fl%2B5Iv5tUGTY7Q%3D%3D&amp;trackingId=a%2BRgoPI8HwvjxaQsctZHFQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -6260,17 +6260,17 @@
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Analytics Manager</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>Abacus Medicine Group</t>
+          <t>Salt</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>Copenhagen, Capital Region of Denmark, Denmark</t>
+          <t>Dubai, United Arab Emirates</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -6279,7 +6279,7 @@
         </is>
       </c>
       <c r="F92" s="8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G92" s="9" t="inlineStr">
         <is>
@@ -6288,7 +6288,7 @@
       </c>
       <c r="H92" s="3" t="inlineStr">
         <is>
-          <t>This is a Data Engineer role focusing on data pipelines, infrastructure, and warehousing, which is entirely unrelated to the candidate's core specialization in Generative AI, LLMs, and agentic workflows. Furthermore, the role is aimed at someone starting their career in data engineering, representing a major seniority mismatch for a Lead Data Scientist with 10 years of experience.</t>
+          <t>This is a traditional Business Intelligence and Analytics Manager role focused on SQL, BI platforms, and dashboard governance, which is entirely misaligned with the candidate's core specialization in Generative AI, LLMs, and agentic systems. Although the seniority and years of experience generally align, the technical scope is classical data analytics rather than advanced AI.</t>
         </is>
       </c>
       <c r="I92" s="3" t="inlineStr">
@@ -6313,7 +6313,7 @@
       </c>
       <c r="M92" s="6" t="inlineStr">
         <is>
-          <t>https://dk.linkedin.com/jobs/view/data-engineer-at-abacus-medicine-group-4448014908?position=7&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=naNFtA2OuhXjDVLQEaIksw%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/data-analytics-manager-at-salt-4444546523?position=19&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=nocZsmIJ8Yx5LNeo0Qbyfg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -6323,17 +6323,17 @@
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>Product Owner &amp; Analytics Engineer</t>
+          <t>Junior Data Scientist Hypotheken DataLab (Amersfoort)</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>Future Impact</t>
         </is>
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>Viby, Region of Southern Denmark, Denmark</t>
+          <t>Amsterdam, North Holland, Netherlands</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
@@ -6342,7 +6342,7 @@
         </is>
       </c>
       <c r="F93" s="8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G93" s="9" t="inlineStr">
         <is>
@@ -6351,7 +6351,7 @@
       </c>
       <c r="H93" s="3" t="inlineStr">
         <is>
-          <t>This role is a Product Owner and Analytics Engineer position focused on data platforms, BI, dbt, and stakeholder management rather than GenAI or LLM development. It is an extremely weak technical fit for a GenAI specialist.</t>
+          <t>This is a junior data scientist role focused on traditional mortgage analytics and classical machine learning, representing a severe seniority and domain mismatch for a 10+ year GenAI lead specialist. Additionally, the role explicitly requires fluent Dutch language skills which the candidate lacks.</t>
         </is>
       </c>
       <c r="I93" s="3" t="inlineStr">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="M93" s="6" t="inlineStr">
         <is>
-          <t>https://dk.linkedin.com/jobs/view/product-owner-analytics-engineer-at-ok-4457992725?position=11&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=D2ySyPo8bFWVMMg%2FjecIMw%3D%3D</t>
+          <t>https://nl.linkedin.com/jobs/view/junior-data-scientist-hypotheken-datalab-amersfoort-at-future-impact-4459169232?position=10&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=PCmMM9pEfOFRNmRrvy5XFw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -6386,17 +6386,17 @@
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>Data Scientist - Energy Forecasting</t>
+          <t>Manager – Data Engineering, Architecture &amp; Reporting Platform - Dubai / Abu Dhabi</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>Danfoss</t>
+          <t>Agthia Group PJSC</t>
         </is>
       </c>
       <c r="D94" s="3" t="inlineStr">
         <is>
-          <t>Kolding, Region of Southern Denmark, Denmark</t>
+          <t>Dubai, Dubai, United Arab Emirates</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -6405,7 +6405,7 @@
         </is>
       </c>
       <c r="F94" s="8" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G94" s="9" t="inlineStr">
         <is>
@@ -6414,12 +6414,12 @@
       </c>
       <c r="H94" s="3" t="inlineStr">
         <is>
-          <t>This energy forecasting and physical systems role has zero overlap with the candidate's core specialization in Generative AI, LLMs, and agentic workflows, representing a completely different domain.</t>
+          <t>This is a data engineering and platform architecture role focused on cloud lakehouse setup, ETL pipelines, and semantic layers, completely lacking any Generative AI, LLMs, or agentic workflows which form the candidate's core specialization. Additionally, while the candidate has 10+ years of experience, the heavy infrastructure and data engineering focus makes it a weak technical fit.</t>
         </is>
       </c>
       <c r="I94" s="3" t="inlineStr">
         <is>
-          <t>No - English fluency stated as sufficient</t>
+          <t>Not stated in JD</t>
         </is>
       </c>
       <c r="J94" s="3" t="inlineStr">
@@ -6439,7 +6439,7 @@
       </c>
       <c r="M94" s="6" t="inlineStr">
         <is>
-          <t>https://dk.linkedin.com/jobs/view/data-scientist-energy-forecasting-at-danfoss-4459332327?position=2&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=%2BhOuUASw5VgnQYgphl%2BfiQ%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/manager-%E2%80%93-data-engineering-architecture-reporting-platform-dubai-abu-dhabi-at-agthia-group-pjsc-4457225736?position=30&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=uCZRYkPcw%2FLl2O0EJmhVdQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -6449,12 +6449,12 @@
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>Data Scientist - Energy Forecasting</t>
+          <t>Research Informatics Data Engineer</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>Danfoss</t>
+          <t>Lundbeck</t>
         </is>
       </c>
       <c r="D95" s="3" t="inlineStr">
@@ -6468,7 +6468,7 @@
         </is>
       </c>
       <c r="F95" s="8" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G95" s="9" t="inlineStr">
         <is>
@@ -6477,12 +6477,12 @@
       </c>
       <c r="H95" s="3" t="inlineStr">
         <is>
-          <t>This is a classical machine learning role focused entirely on energy demand forecasting, time-series modeling, and physical systems for district heating, which has no overlap with the candidate's core specialization in Generative AI, LLMs, and agentic workflows.</t>
+          <t>This is a Research Informatics Data Engineer role focusing on life sciences data management, laboratory informatics, and scientific platform integration rather than Generative AI or advanced LLM application development. While LLMs are briefly mentioned as an optional tool for coding assistance, the candidate's core specialization in multi-agent orchestration, RAG architectures, and production GenAI systems does not align with this software/data engineering workflow role.</t>
         </is>
       </c>
       <c r="I95" s="3" t="inlineStr">
         <is>
-          <t>No - English fluency stated as sufficient</t>
+          <t>Not stated in JD</t>
         </is>
       </c>
       <c r="J95" s="3" t="inlineStr">
@@ -6502,7 +6502,7 @@
       </c>
       <c r="M95" s="6" t="inlineStr">
         <is>
-          <t>https://dk.linkedin.com/jobs/view/data-scientist-energy-forecasting-at-danfoss-4459316434?position=1&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=Jfk6JIiJcse1eCPfqN9rvg%3D%3D</t>
+          <t>https://dk.linkedin.com/jobs/view/research-informatics-data-engineer-at-lundbeck-4448898202?position=5&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=5fkJnjfpF2QdhMDLztM5Vw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -6512,22 +6512,22 @@
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Engineer (EMIRATI)</t>
+          <t>Head of Data Analytics</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>Salt</t>
+          <t>Right Calibre Consulting</t>
         </is>
       </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
-          <t>Abu Dhabi Emirate, United Arab Emirates</t>
+          <t>Dubai, United Arab Emirates</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F96" s="8" t="n">
@@ -6540,7 +6540,7 @@
       </c>
       <c r="H96" s="3" t="inlineStr">
         <is>
-          <t>The role requires an early-career software engineer with 2+ years of experience, representing a significant seniority mismatch for a Lead Data Scientist with 10+ years of experience. Furthermore, the position explicitly specifies that it is for Emirati nationals only.</t>
+          <t>This is a Head of Data Analytics role focused on traditional BI, commercial insights, data governance, and leading analytics teams in the media and technology sector. It completely lacks any GenAI, LLM, or agentic AI focus, and the Head/Director-level leadership scope exceeds the candidate's current Lead Data Scientist level.</t>
         </is>
       </c>
       <c r="I96" s="3" t="inlineStr">
@@ -6553,9 +6553,9 @@
           <t>Not stated in JD</t>
         </is>
       </c>
-      <c r="K96" s="7" t="inlineStr">
-        <is>
-          <t>New this run (2026-08-27 06:43 UTC)</t>
+      <c r="K96" s="2" t="inlineStr">
+        <is>
+          <t>From previous run</t>
         </is>
       </c>
       <c r="L96" s="2" t="inlineStr">
@@ -6565,7 +6565,7 @@
       </c>
       <c r="M96" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/artificial-intelligence-engineer-emirati-at-salt-4457723960?position=26&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=OL7voNOllXDyxcDmkFiWQw%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/head-of-data-analytics-at-right-calibre-consulting-4459174081?position=24&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=dZTHuLROd%2FTUDsdWxlHCPg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -6575,17 +6575,17 @@
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>Junior Research Scientist In the Division of Engineering (Electrical and Computer Engineering) - Dr. Fang Yi</t>
+          <t>Customer Intelligence Manager</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>New York University Abu Dhabi</t>
+          <t>Al Tayer Insignia</t>
         </is>
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t>Abu Dhabi, Abu Dhabi Emirate, United Arab Emirates</t>
+          <t>Dubai, Dubai, United Arab Emirates</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
@@ -6603,7 +6603,7 @@
       </c>
       <c r="H97" s="3" t="inlineStr">
         <is>
-          <t>This is an academic research scientist role focused on robotics, embodied AI, and assistive technologies, which does not align with the candidate's core specialization in enterprise Generative AI, LLMs, and RAG. Additionally, there is a major seniority mismatch as the role targets junior researchers with under five years of experience, whereas the candidate is a Lead Data Scientist with 10+ years of experience.</t>
+          <t>This Customer Intelligence Manager role focuses on market research, consumer insights, and retail analytics rather than Generative AI, LLMs, or agentic systems. It represents a fundamental domain mismatch for the candidate's specialized technical profile.</t>
         </is>
       </c>
       <c r="I97" s="3" t="inlineStr">
@@ -6613,12 +6613,12 @@
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
-          <t>Possible - relocation support mentioned, visa not explicit</t>
-        </is>
-      </c>
-      <c r="K97" s="7" t="inlineStr">
-        <is>
-          <t>New this run (2026-08-27 06:43 UTC)</t>
+          <t>Not stated in JD</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr">
+        <is>
+          <t>From previous run</t>
         </is>
       </c>
       <c r="L97" s="2" t="inlineStr">
@@ -6628,7 +6628,7 @@
       </c>
       <c r="M97" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/junior-research-scientist-in-the-division-of-engineering-electrical-and-computer-engineering-dr-fang-yi-at-new-york-university-abu-dhabi-4448981054?position=17&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=Quv11sfD16F354%2FzN0KXRg%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/customer-intelligence-manager-at-al-tayer-insignia-4457235794?position=9&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=PiyoN3pPhVcxMx9vtAIf5g%3D%3D</t>
         </is>
       </c>
     </row>
@@ -6638,17 +6638,17 @@
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>Business Intelligence Analytics</t>
+          <t>Service Review Insights Lead</t>
         </is>
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>Confidential</t>
+          <t>Discovered MENA</t>
         </is>
       </c>
       <c r="D98" s="3" t="inlineStr">
         <is>
-          <t>Abu Dhabi Emirate, United Arab Emirates</t>
+          <t>Dubai, United Arab Emirates</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
@@ -6666,7 +6666,7 @@
       </c>
       <c r="H98" s="3" t="inlineStr">
         <is>
-          <t>This is a Business Intelligence and reporting role focusing on traditional tools like SQL Server, Tableau, PowerBI, and IT service management, completely lacking any Generative AI, LLM, or agentic specialization. The candidate's advanced GenAI and data science background is a severe mismatch for this operational BI position.</t>
+          <t>This role focuses heavily on operational analytics, call center metrics, and executive board presentations with no connection to Generative AI, LLMs, or data science. It is completely outside the candidate's core technical specialization and domain.</t>
         </is>
       </c>
       <c r="I98" s="3" t="inlineStr">
@@ -6679,9 +6679,9 @@
           <t>Not stated in JD</t>
         </is>
       </c>
-      <c r="K98" s="7" t="inlineStr">
-        <is>
-          <t>New this run (2026-08-27 06:43 UTC)</t>
+      <c r="K98" s="2" t="inlineStr">
+        <is>
+          <t>From previous run</t>
         </is>
       </c>
       <c r="L98" s="2" t="inlineStr">
@@ -6691,7 +6691,7 @@
       </c>
       <c r="M98" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/business-intelligence-analytics-at-pump-dynamics-4457247369?position=16&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=q3L54POb%2Ba8jMFybGRPVBA%3D%3D&amp;trk=public_jobs_jserp-result_search-card</t>
+          <t>https://ae.linkedin.com/jobs/view/service-review-insights-lead-at-discovered-mena-4456958136?position=10&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=oMos4kbDfkh42RiAd%2Bimnw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -6701,17 +6701,17 @@
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>Data Analyst - UAE National, ICQA/LND Analytics Team</t>
+          <t>QEHS Digital Analyst - UAE National</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Siemens Energy</t>
         </is>
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
-          <t>Abu Dhabi, Abu Dhabi Emirate, United Arab Emirates</t>
+          <t>Dubai, Dubai, United Arab Emirates</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -6729,7 +6729,7 @@
       </c>
       <c r="H99" s="3" t="inlineStr">
         <is>
-          <t>This is a Data Analyst role focusing on standard reporting, SQL, QuickSight, and AWS data warehousing infrastructure, which is entirely unrelated to the candidate's core specialization in Generative AI, LLMs, and agentic workflows. Furthermore, there is a severe seniority and domain mismatch as the role targets data analysis rather than advanced AI leadership.</t>
+          <t>This role is focused on Quality, Environment, Health, and Safety (QEHS) digital transformation, enterprise systems like SAP and Salesforce, and quality management standards rather than Generative AI or LLM specialization. It represents a significant domain and technical mismatch for a Lead Data Scientist specializing in agentic AI and RAG architectures.</t>
         </is>
       </c>
       <c r="I99" s="3" t="inlineStr">
@@ -6742,9 +6742,9 @@
           <t>Not stated in JD</t>
         </is>
       </c>
-      <c r="K99" s="7" t="inlineStr">
-        <is>
-          <t>New this run (2026-08-27 06:43 UTC)</t>
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t>From previous run</t>
         </is>
       </c>
       <c r="L99" s="2" t="inlineStr">
@@ -6754,7 +6754,7 @@
       </c>
       <c r="M99" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/data-analyst-uae-national-icqa-lnd-analytics-team-at-amazon-4459175702?position=13&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=2u0HotRhWhUDg980ATy2nw%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/qehs-digital-analyst-uae-national-at-siemens-energy-4439835820?position=8&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=jLKXnOBvB%2BaDszNV2BAbbA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -6764,22 +6764,22 @@
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>Mathematician (Remote)</t>
+          <t>Data Analyst - UAE National, ICQA/LND Analytics Team</t>
         </is>
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>Hired</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="D100" s="3" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>Dubai, Dubai, United Arab Emirates</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F100" s="8" t="n">
@@ -6792,7 +6792,7 @@
       </c>
       <c r="H100" s="3" t="inlineStr">
         <is>
-          <t>This remote contractor role focuses on pure applied mathematics and algorithmic optimization rather than Generative AI, LLMs, or agentic frameworks. While the candidate has a strong data science background, the job is entirely unrelated to his core GenAI and RAG specialization.</t>
+          <t>This Data Analyst role at Amazon focuses on SQL reporting, dashboards, and operational data management, lacking any connection to the candidate's core GenAI, LLMs, and agentic AI specialization. Furthermore, the role is restricted to UAE Nationals and represents a significant mismatch in domain and function.</t>
         </is>
       </c>
       <c r="I100" s="3" t="inlineStr">
@@ -6805,9 +6805,9 @@
           <t>Not stated in JD</t>
         </is>
       </c>
-      <c r="K100" s="7" t="inlineStr">
-        <is>
-          <t>New this run (2026-08-27 06:43 UTC)</t>
+      <c r="K100" s="2" t="inlineStr">
+        <is>
+          <t>From previous run</t>
         </is>
       </c>
       <c r="L100" s="2" t="inlineStr">
@@ -6817,7 +6817,7 @@
       </c>
       <c r="M100" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/mathematician-remote-at-hired-4459651401?position=11&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=L0rt1zlpnHOlSTn4%2BjbBZg%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/data-analyst-uae-national-icqa-lnd-analytics-team-at-amazon-4459169756?position=7&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=dtuARx3ylMmIho9xSQNgYg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -6827,22 +6827,22 @@
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>Statistician (Remote)</t>
+          <t>Senior Data Analyst - Strategy</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>Hired</t>
+          <t>dubizzle</t>
         </is>
       </c>
       <c r="D101" s="3" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>Dubai, Dubai, United Arab Emirates</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F101" s="8" t="n">
@@ -6855,7 +6855,7 @@
       </c>
       <c r="H101" s="3" t="inlineStr">
         <is>
-          <t>This role focuses heavily on classical statistics, experimental design, and A/B testing, requiring a PhD in Statistics, which does not match the candidate's core GenAI and LLM specialization. Furthermore, it is a contract statistician role rather than an advanced AI engineering or agentic systems role.</t>
+          <t>This is a Senior Data Analyst - Strategy role focused on business analytics, executive dashboards, and commercial growth rather than AI, lacking any GenAI, LLM, or agentic specialization. Additionally, it represents a domain and functional mismatch for an AI/ML Lead Data Scientist.</t>
         </is>
       </c>
       <c r="I101" s="3" t="inlineStr">
@@ -6868,9 +6868,9 @@
           <t>Not stated in JD</t>
         </is>
       </c>
-      <c r="K101" s="7" t="inlineStr">
-        <is>
-          <t>New this run (2026-08-27 06:43 UTC)</t>
+      <c r="K101" s="2" t="inlineStr">
+        <is>
+          <t>From previous run</t>
         </is>
       </c>
       <c r="L101" s="2" t="inlineStr">
@@ -6880,7 +6880,7 @@
       </c>
       <c r="M101" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/statistician-remote-at-hired-4459636643?position=12&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=%2FKljESl%2B5ntTSKKRsgpGUg%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/senior-data-analyst-strategy-at-dubizzle-4446647656?position=5&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=oDSAohEFPlpSK2IK3vFpNg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -6890,17 +6890,17 @@
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t>Graphene Photonics Data Analyst (f/m/d)</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="C102" s="3" t="inlineStr">
         <is>
-          <t>Black Semiconductor</t>
+          <t>Insify</t>
         </is>
       </c>
       <c r="D102" s="3" t="inlineStr">
         <is>
-          <t>Aachen, North Rhine-Westphalia, Germany</t>
+          <t>Amsterdam, North Holland, Netherlands</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -6909,7 +6909,7 @@
         </is>
       </c>
       <c r="F102" s="8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G102" s="9" t="inlineStr">
         <is>
@@ -6918,12 +6918,12 @@
       </c>
       <c r="H102" s="3" t="inlineStr">
         <is>
-          <t>This role is entirely focused on semiconductor hardware, graphene photonics, and physical data analysis, with zero relevance to the candidate's core specialization in Generative AI, LLMs, and agentic workflows.</t>
+          <t>This is a classical Data Analyst role focused on SQL, A/B testing, and business metrics, which is completely unrelated to the candidate's core specialization in Generative AI, LLMs, and agentic workflows.</t>
         </is>
       </c>
       <c r="I102" s="3" t="inlineStr">
         <is>
-          <t>Not stated in JD</t>
+          <t>Yes - German required (see JD for exact level)</t>
         </is>
       </c>
       <c r="J102" s="3" t="inlineStr">
@@ -6943,7 +6943,7 @@
       </c>
       <c r="M102" s="6" t="inlineStr">
         <is>
-          <t>https://de.linkedin.com/jobs/view/graphene-photonics-data-analyst-f-m-d-at-black-semiconductor-4459334621?position=26&amp;pageNum=0&amp;refId=T%2F0KkBXL%2Fl%2B5Iv5tUGTY7Q%3D%3D&amp;trackingId=KgQ01De6ChDgIN8UxnUvXg%3D%3D</t>
+          <t>https://nl.linkedin.com/jobs/view/data-analyst-at-insify-4457952341?position=26&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=kZIox38P2PV0MRG6Tih7Dw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -6953,17 +6953,17 @@
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>Financial Planning and Analysis Manager</t>
+          <t>Research Analyst - NL</t>
         </is>
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>Confidential Jobs</t>
+          <t>OPEN Health</t>
         </is>
       </c>
       <c r="D103" s="3" t="inlineStr">
         <is>
-          <t>Dubai, United Arab Emirates</t>
+          <t>Rotterdam, South Holland, Netherlands</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
@@ -6972,7 +6972,7 @@
         </is>
       </c>
       <c r="F103" s="8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G103" s="9" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
       </c>
       <c r="H103" s="3" t="inlineStr">
         <is>
-          <t>This Financial Planning and Analysis Manager role is entirely unrelated to data science, machine learning, or software engineering, focusing instead on corporate finance, budgeting, construction economics, and IFRS 15 accounting. There is a massive domain and seniority mismatch for an AI/GenAI Lead Data Scientist.</t>
+          <t>This role focuses on health economics, meta-analysis, and HEOR modeling (cost-effectiveness, budget impact) using R and statistical software, which is completely unrelated to the candidate's GenAI, LLMs, and agentic AI specialization.</t>
         </is>
       </c>
       <c r="I103" s="3" t="inlineStr">
@@ -7006,7 +7006,7 @@
       </c>
       <c r="M103" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/financial-planning-and-analysis-manager-at-confidential-jobs-4452594332?position=29&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=KEfZVTEknZKckxH1vstrzQ%3D%3D</t>
+          <t>https://nl.linkedin.com/jobs/view/research-analyst-nl-at-open-health-4457247414?position=28&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=lxrHLFZXxcKuwp8%2F8mz0KA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -7016,17 +7016,17 @@
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>Data QA Engineer</t>
+          <t>Data Analyst / Data Scientist</t>
         </is>
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t>ClearGrid</t>
+          <t>Trinamics</t>
         </is>
       </c>
       <c r="D104" s="3" t="inlineStr">
         <is>
-          <t>Dubai, Dubai, United Arab Emirates</t>
+          <t>North Brabant, Netherlands</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="F104" s="8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G104" s="9" t="inlineStr">
         <is>
@@ -7044,7 +7044,7 @@
       </c>
       <c r="H104" s="3" t="inlineStr">
         <is>
-          <t>This role is a Data QA Engineer focused entirely on data quality, dbt testing, and warehouse reconciliation in a fintech/collections environment, lacking any Generative AI, LLM, or agentic specialization. Furthermore, the seniority requirement (2+ years) is well below the candidate's 10+ years as a Lead Data Scientist.</t>
+          <t>This is a financial reporting, data analysis, and dashboard-building role focusing on SAP, Spotfire, and Power BI with no connection to Generative AI, LLMs, or agentic systems. It is entirely unrelated to the candidate's core specialization and represents a major mismatch in domain and technical stack.</t>
         </is>
       </c>
       <c r="I104" s="3" t="inlineStr">
@@ -7069,7 +7069,7 @@
       </c>
       <c r="M104" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/data-qa-engineer-at-cleargrid-4457980735?position=25&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=RbMMQ6DAm%2FMomlqBLUM2IQ%3D%3D</t>
+          <t>https://nl.linkedin.com/jobs/view/data-analyst-data-scientist-at-trinamics-4459172477?position=15&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=wKQaRNJqc3u7QhTWjoCU%2FQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -7079,17 +7079,17 @@
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>OTR Planning Manager, Hub Delivery UAE , Hub Delivery</t>
+          <t>De Rijksoverheid zoekt: Data scientist AI driven weather model</t>
         </is>
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>KNMI - Royal Netherlands Meteorological Institute</t>
         </is>
       </c>
       <c r="D105" s="3" t="inlineStr">
         <is>
-          <t>Dubai, Dubai, United Arab Emirates</t>
+          <t>De Bilt, Utrecht, Netherlands</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
@@ -7098,7 +7098,7 @@
         </is>
       </c>
       <c r="F105" s="8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G105" s="9" t="inlineStr">
         <is>
@@ -7107,7 +7107,7 @@
       </c>
       <c r="H105" s="3" t="inlineStr">
         <is>
-          <t>This operations and logistics management role is entirely unrelated to data science, machine learning, and Generative AI, focusing instead on supply chain planning and fleet management. Therefore, it is a very poor match for the candidate's core specialization.</t>
+          <t>This role focuses on specialized deep learning for meteorological modeling, graph neural networks, and diffusion models applied to weather forecasting, which has virtually no overlap with the candidate's core GenAI, LLMs, and agentic AI specialization.</t>
         </is>
       </c>
       <c r="I105" s="3" t="inlineStr">
@@ -7132,7 +7132,7 @@
       </c>
       <c r="M105" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/otr-planning-manager-hub-delivery-uae-hub-delivery-at-amazon-4459184678?position=21&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=bqoXqft%2BGFtLz05C2kL0FA%3D%3D</t>
+          <t>https://nl.linkedin.com/jobs/view/de-rijksoverheid-zoekt-data-scientist-ai-driven-weather-model-at-knmi-royal-netherlands-meteorological-institute-4459321694?position=7&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=uEDe9phb4vscnrkupOYRog%3D%3D</t>
         </is>
       </c>
     </row>
@@ -7142,17 +7142,17 @@
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t>Senior Compensation Analyst</t>
+          <t>Decision Scientist, Trust &amp; Safety</t>
         </is>
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t>Cartier</t>
+          <t>Vinted</t>
         </is>
       </c>
       <c r="D106" s="3" t="inlineStr">
         <is>
-          <t>Dubai, Dubai, United Arab Emirates</t>
+          <t>Amsterdam, North Holland, Netherlands</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
@@ -7161,7 +7161,7 @@
         </is>
       </c>
       <c r="F106" s="8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G106" s="9" t="inlineStr">
         <is>
@@ -7170,12 +7170,12 @@
       </c>
       <c r="H106" s="3" t="inlineStr">
         <is>
-          <t>This is a non-technical role focused strictly on compensation analysis, financial modeling, and advanced Excel simulation design within HR, which has no overlap with the candidate's core GenAI, LLM, or data science specialization.</t>
+          <t>This is a Decision Scientist role focused on product experimentation, SQL/BI dashboards, and Trust &amp; Safety analytics, which is completely unrelated to the candidate's core specialization in Generative AI, LLMs, and agentic workflows.</t>
         </is>
       </c>
       <c r="I106" s="3" t="inlineStr">
         <is>
-          <t>Not stated in JD</t>
+          <t>No - English fluency stated as sufficient</t>
         </is>
       </c>
       <c r="J106" s="3" t="inlineStr">
@@ -7195,7 +7195,7 @@
       </c>
       <c r="M106" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/senior-compensation-analyst-at-cartier-4448528069?position=20&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=uU%2BxMpwsg7Xv71%2Fjk83xeg%3D%3D</t>
+          <t>https://nl.linkedin.com/jobs/view/decision-scientist-trust-safety-at-vinted-4431734156?position=13&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=5DKFgkv450iADwhSNzZiDw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -7205,17 +7205,17 @@
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>AI &amp; Data - BrightStar program - Part-Time For Students | UAE Nationals Only - Dubai</t>
+          <t>Senior Data Scientist - System Optimization</t>
         </is>
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Danfoss</t>
         </is>
       </c>
       <c r="D107" s="3" t="inlineStr">
         <is>
-          <t>Dubai, Dubai, United Arab Emirates</t>
+          <t>Copenhagen, Capital Region of Denmark, Denmark</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
@@ -7224,7 +7224,7 @@
         </is>
       </c>
       <c r="F107" s="8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G107" s="9" t="inlineStr">
         <is>
@@ -7233,12 +7233,12 @@
       </c>
       <c r="H107" s="3" t="inlineStr">
         <is>
-          <t>This student internship/part-time program is an extreme seniority mismatch for a Lead Data Scientist with 10+ years of experience. Furthermore, the role is strictly restricted to UAE Nationals and unrelated to the candidate's specialized GenAI and agentic AI expertise.</t>
+          <t>This is a Senior Data Scientist role focused on physical modelling, thermo-hydraulic simulation, and Mixed-Integer Linear Programming (MILP) for energy networks, which has zero overlap with the candidate's core specialization in Generative AI, LLMs, and agentic systems.</t>
         </is>
       </c>
       <c r="I107" s="3" t="inlineStr">
         <is>
-          <t>Not stated in JD</t>
+          <t>No - English fluency stated as sufficient</t>
         </is>
       </c>
       <c r="J107" s="3" t="inlineStr">
@@ -7258,7 +7258,7 @@
       </c>
       <c r="M107" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/ai-data-brightstar-program-part-time-for-students-uae-nationals-only-dubai-at-deloitte-4459165278?position=18&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=rkeXlOzDBapH9BYwLoMUoA%3D%3D</t>
+          <t>https://dk.linkedin.com/jobs/view/senior-data-scientist-system-optimization-at-danfoss-4459328391?position=28&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=pWSiaSPEvTB%2Fj17raCtBPA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -7268,17 +7268,17 @@
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t>Junior Market Analyst - UAE National</t>
+          <t>Senior Data Scientist - System Optimization</t>
         </is>
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t>Richemont</t>
+          <t>Danfoss</t>
         </is>
       </c>
       <c r="D108" s="3" t="inlineStr">
         <is>
-          <t>Dubai, Dubai, United Arab Emirates</t>
+          <t>Kolding, Region of Southern Denmark, Denmark</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
@@ -7287,7 +7287,7 @@
         </is>
       </c>
       <c r="F108" s="8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G108" s="9" t="inlineStr">
         <is>
@@ -7296,12 +7296,12 @@
       </c>
       <c r="H108" s="3" t="inlineStr">
         <is>
-          <t>This role is a junior market research and business development position focused on luxury retail intelligence in the MEIAT region, which is completely unrelated to data science, artificial intelligence, or the candidate's GenAI and LLM specialization.</t>
+          <t>This is a Senior Data Scientist role focused on physical modelling, thermo-hydraulic simulation of energy networks, and Mixed-Integer Linear Programming (MILP), which is entirely unrelated to the candidate's core specialization in Generative AI, LLMs, and agentic systems.</t>
         </is>
       </c>
       <c r="I108" s="3" t="inlineStr">
         <is>
-          <t>Not stated in JD</t>
+          <t>No - English fluency stated as sufficient</t>
         </is>
       </c>
       <c r="J108" s="3" t="inlineStr">
@@ -7321,7 +7321,7 @@
       </c>
       <c r="M108" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/junior-market-analyst-uae-national-at-richemont-4448527067?position=22&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=fabWFpBqiTWxCuIFUXVosg%3D%3D</t>
+          <t>https://dk.linkedin.com/jobs/view/senior-data-scientist-system-optimization-at-danfoss-4459334294?position=29&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=6IO8CqSe4TjOJrnH%2BoTbig%3D%3D</t>
         </is>
       </c>
     </row>
@@ -7331,17 +7331,17 @@
       </c>
       <c r="B109" s="3" t="inlineStr">
         <is>
-          <t>Data Analyst - (Advanced Excel expertise)</t>
+          <t>Product Owner</t>
         </is>
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>BigTapp Analytics</t>
+          <t>Ørsted</t>
         </is>
       </c>
       <c r="D109" s="3" t="inlineStr">
         <is>
-          <t>Dubai, Dubai, United Arab Emirates</t>
+          <t>Gentofte, Capital Region of Denmark, Denmark</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
@@ -7350,7 +7350,7 @@
         </is>
       </c>
       <c r="F109" s="8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G109" s="9" t="inlineStr">
         <is>
@@ -7359,7 +7359,7 @@
       </c>
       <c r="H109" s="3" t="inlineStr">
         <is>
-          <t>This is a Data Analyst role focused entirely on Advanced Excel, corporate tax data quality, and data validation, with no connection to the candidate's GenAI, LLM, or agentic AI specialization.</t>
+          <t>This is a Product Owner role focused on quantitative analytics, portfolio models, and trading infrastructure rather than a hands-on Generative AI or data science engineering position. It is completely outside the candidate's core specialization in LLMs, RAG, and agentic systems, and involves product management responsibilities rather than technical AI development.</t>
         </is>
       </c>
       <c r="I109" s="3" t="inlineStr">
@@ -7384,7 +7384,7 @@
       </c>
       <c r="M109" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/data-analyst-advanced-excel-expertise-at-bigtapp-analytics-4459194093?position=16&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=vJ8ubhhJtvsWirwhmdkH%2BA%3D%3D</t>
+          <t>https://dk.linkedin.com/jobs/view/product-owner-at-%C3%B8rsted-4457976275?position=30&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=kwPJx%2Freb7nWWcV4YkYqtg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -7394,17 +7394,17 @@
       </c>
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t>Junior Data Analyst</t>
+          <t>Product Owner</t>
         </is>
       </c>
       <c r="C110" s="3" t="inlineStr">
         <is>
-          <t>Arabian Private Holdings</t>
+          <t>Ørsted</t>
         </is>
       </c>
       <c r="D110" s="3" t="inlineStr">
         <is>
-          <t>Sharjah, Sharjah Emirate, United Arab Emirates</t>
+          <t>Gentofte, Capital Region of Denmark, Denmark</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
@@ -7413,7 +7413,7 @@
         </is>
       </c>
       <c r="F110" s="8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G110" s="9" t="inlineStr">
         <is>
@@ -7422,7 +7422,7 @@
       </c>
       <c r="H110" s="3" t="inlineStr">
         <is>
-          <t>This is a junior data analyst role focused on operational data interpretation, basic SQL/Excel database maintenance, and corporate strategy support, completely unrelated to the candidate's GenAI, LLMs, and agentic AI specialization. Additionally, there is a severe seniority mismatch as the role is strictly junior while the candidate is a Lead Data Scientist with 10+ years of experience.</t>
+          <t>This is a Product Owner role focused on commodity and energy trading platforms rather than a hands-on technical Generative AI, LLM, or agentic AI role. There is a severe mismatch in job function and seniority focus, as the candidate is a technical Lead Data Scientist specializing in hands-on GenAI systems.</t>
         </is>
       </c>
       <c r="I110" s="3" t="inlineStr">
@@ -7447,7 +7447,7 @@
       </c>
       <c r="M110" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/junior-data-analyst-at-arabian-private-holdings-4457918646?position=11&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=n3OKFNsTAywRSCMqHYFmlg%3D%3D</t>
+          <t>https://dk.linkedin.com/jobs/view/product-owner-at-%C3%B8rsted-4457969343?position=16&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=Srm0W8oPqBLXtVvd0AdJlg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -7457,17 +7457,17 @@
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>Data Analyst – Social Support Operations - UAE National</t>
+          <t>Dataspecialist - Afd. for Uddannelse og Studerende</t>
         </is>
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>Ministry of Community Empowerment</t>
+          <t>DTU - Technical University of Denmark</t>
         </is>
       </c>
       <c r="D111" s="3" t="inlineStr">
         <is>
-          <t>Dubai, United Arab Emirates</t>
+          <t>Kongens Lyngby, Capital Region of Denmark, Denmark</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
@@ -7476,7 +7476,7 @@
         </is>
       </c>
       <c r="F111" s="8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G111" s="9" t="inlineStr">
         <is>
@@ -7485,7 +7485,7 @@
       </c>
       <c r="H111" s="3" t="inlineStr">
         <is>
-          <t>This role is a data analyst position focused on BI, Power BI dashboards, SQL, and social support operations, which is completely unrelated to the candidate's core GenAI, LLMs, and agentic AI specialization. Additionally, it specifies a nationality requirement.</t>
+          <t>This role at DTU focuses on educational data analysis, stakeholder communication, and business intelligence reporting within a university setting, completely lacking any connection to the candidate's core GenAI, LLMs, or agentic AI specialization.</t>
         </is>
       </c>
       <c r="I111" s="3" t="inlineStr">
@@ -7510,7 +7510,7 @@
       </c>
       <c r="M111" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/data-analyst-%E2%80%93-social-support-operations-uae-national-at-ministry-of-community-empowerment-4459118725?position=4&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=q%2FHUZ0XJHF5eY2WSwIWmAg%3D%3D</t>
+          <t>https://dk.linkedin.com/jobs/view/dataspecialist-afd-for-uddannelse-og-studerende-at-dtu-technical-university-of-denmark-4458711406?position=12&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=jpgFSNpWhcVL9zGHYU%2Fxbw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -7520,17 +7520,17 @@
       </c>
       <c r="B112" s="3" t="inlineStr">
         <is>
-          <t>Graduate - Data Scientist إماراتيين (خلاصة القيد)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="C112" s="3" t="inlineStr">
         <is>
-          <t>AECOM</t>
+          <t>Abacus Medicine Group</t>
         </is>
       </c>
       <c r="D112" s="3" t="inlineStr">
         <is>
-          <t>Dubai, Dubai, United Arab Emirates</t>
+          <t>Copenhagen, Capital Region of Denmark, Denmark</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
@@ -7539,7 +7539,7 @@
         </is>
       </c>
       <c r="F112" s="8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G112" s="9" t="inlineStr">
         <is>
@@ -7548,7 +7548,7 @@
       </c>
       <c r="H112" s="3" t="inlineStr">
         <is>
-          <t>This is a graduate/entry-level program designed specifically for recent graduates (2024-2026) and UAE Nationals, representing a severe seniority and eligibility mismatch for a Lead Data Scientist with 10+ years of experience. Furthermore, the role focuses on construction digital tools, cost management, and general data analytics rather than the candidate's core GenAI, LLMs, and agentic AI specialization.</t>
+          <t>This is a Data Engineer role focusing on data pipelines, infrastructure, and warehousing, which is entirely unrelated to the candidate's core specialization in Generative AI, LLMs, and agentic workflows. Furthermore, the role is aimed at someone starting their career in data engineering, representing a major seniority mismatch for a Lead Data Scientist with 10 years of experience.</t>
         </is>
       </c>
       <c r="I112" s="3" t="inlineStr">
@@ -7573,7 +7573,7 @@
       </c>
       <c r="M112" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/graduate-data-scientist-%D8%A5%D9%85%D8%A7%D8%B1%D8%A7%D8%AA%D9%8A%D9%8A%D9%86-%D8%AE%D9%84%D8%A7%D8%B5%D8%A9-%D8%A7%D9%84%D9%82%D9%8A%D8%AF-at-aecom-4457915285?position=1&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=deUfOEFHstE7TEtandLeTg%3D%3D</t>
+          <t>https://dk.linkedin.com/jobs/view/data-engineer-at-abacus-medicine-group-4448014908?position=7&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=naNFtA2OuhXjDVLQEaIksw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -7583,17 +7583,17 @@
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>Quantitative Researcher, Quantitative Strategies</t>
+          <t>Product Owner &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>Millennium</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="D113" s="3" t="inlineStr">
         <is>
-          <t>Dubai, Dubai, United Arab Emirates</t>
+          <t>Viby, Region of Southern Denmark, Denmark</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
@@ -7602,7 +7602,7 @@
         </is>
       </c>
       <c r="F113" s="8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G113" s="9" t="inlineStr">
         <is>
@@ -7611,7 +7611,7 @@
       </c>
       <c r="H113" s="3" t="inlineStr">
         <is>
-          <t>This role focuses entirely on quantitative finance, statistical modeling, and systematic equity trading in Asian markets, which has no overlap with the candidate's core specialization in Generative AI, LLMs, and agentic systems. Additionally, the domain requires specific desk quant trading experience that is absent from the candidate's profile.</t>
+          <t>This role is a Product Owner and Analytics Engineer position focused on data platforms, BI, dbt, and stakeholder management rather than GenAI or LLM development. It is an extremely weak technical fit for a GenAI specialist.</t>
         </is>
       </c>
       <c r="I113" s="3" t="inlineStr">
@@ -7636,7 +7636,7 @@
       </c>
       <c r="M113" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/quantitative-researcher-quantitative-strategies-at-millennium-4439427782?position=2&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=uptfSAbwEngBw3yrsrQehg%3D%3D</t>
+          <t>https://dk.linkedin.com/jobs/view/product-owner-analytics-engineer-at-ok-4457992725?position=11&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=D2ySyPo8bFWVMMg%2FjecIMw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -7646,17 +7646,17 @@
       </c>
       <c r="B114" s="3" t="inlineStr">
         <is>
-          <t>Analyst I - Advisory</t>
+          <t>Data Scientist - Energy Forecasting</t>
         </is>
       </c>
       <c r="C114" s="3" t="inlineStr">
         <is>
-          <t>Marsh Risk</t>
+          <t>Danfoss</t>
         </is>
       </c>
       <c r="D114" s="3" t="inlineStr">
         <is>
-          <t>Dubai, Dubai, United Arab Emirates</t>
+          <t>Kolding, Region of Southern Denmark, Denmark</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
@@ -7665,7 +7665,7 @@
         </is>
       </c>
       <c r="F114" s="8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G114" s="9" t="inlineStr">
         <is>
@@ -7674,12 +7674,12 @@
       </c>
       <c r="H114" s="3" t="inlineStr">
         <is>
-          <t>This is a fresh-graduate/entry-level role for recent graduates that focuses heavily on risk engineering and basic internal digitalization using Excel and Microsoft tools, which is far below the candidate's 10+ years of experience as a Lead Data Scientist specializing in advanced GenAI and agentic systems.</t>
+          <t>This energy forecasting and physical systems role has zero overlap with the candidate's core specialization in Generative AI, LLMs, and agentic workflows, representing a completely different domain.</t>
         </is>
       </c>
       <c r="I114" s="3" t="inlineStr">
         <is>
-          <t>Not stated in JD</t>
+          <t>No - English fluency stated as sufficient</t>
         </is>
       </c>
       <c r="J114" s="3" t="inlineStr">
@@ -7699,7 +7699,7 @@
       </c>
       <c r="M114" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/analyst-i-advisory-at-marsh-risk-4459165267?position=3&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=NpomdoqDoXrgLAw8%2BZjEQA%3D%3D</t>
+          <t>https://dk.linkedin.com/jobs/view/data-scientist-energy-forecasting-at-danfoss-4459332327?position=2&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=%2BhOuUASw5VgnQYgphl%2BfiQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -7709,17 +7709,17 @@
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>Demand Planner (f/m/x)</t>
+          <t>Data Scientist - Energy Forecasting</t>
         </is>
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>HelloFresh</t>
+          <t>Danfoss</t>
         </is>
       </c>
       <c r="D115" s="3" t="inlineStr">
         <is>
-          <t>Amsterdam, North Holland, Netherlands</t>
+          <t>Copenhagen, Capital Region of Denmark, Denmark</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
@@ -7728,7 +7728,7 @@
         </is>
       </c>
       <c r="F115" s="8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G115" s="9" t="inlineStr">
         <is>
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H115" s="3" t="inlineStr">
         <is>
-          <t>This is a supply chain demand planning role requiring 2-3 years of experience in business forecasting, which is completely unrelated to the candidate's specialization in Generative AI, LLMs, and agentic systems. Furthermore, there is a severe seniority mismatch as the candidate is a Lead Data Scientist with 10+ years of experience.</t>
+          <t>This is a classical machine learning role focused entirely on energy demand forecasting, time-series modeling, and physical systems for district heating, which has no overlap with the candidate's core specialization in Generative AI, LLMs, and agentic workflows.</t>
         </is>
       </c>
       <c r="I115" s="3" t="inlineStr">
         <is>
-          <t>Not stated in JD</t>
+          <t>No - English fluency stated as sufficient</t>
         </is>
       </c>
       <c r="J115" s="3" t="inlineStr">
@@ -7762,7 +7762,7 @@
       </c>
       <c r="M115" s="6" t="inlineStr">
         <is>
-          <t>https://nl.linkedin.com/jobs/view/demand-planner-f-m-x-at-hellofresh-4459621163?position=29&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=ScTLY%2B93hMGSjD1GtPlxQw%3D%3D</t>
+          <t>https://dk.linkedin.com/jobs/view/data-scientist-energy-forecasting-at-danfoss-4459316434?position=1&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=Jfk6JIiJcse1eCPfqN9rvg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -7772,26 +7772,26 @@
       </c>
       <c r="B116" s="3" t="inlineStr">
         <is>
-          <t>Traineeship Data Analytics</t>
+          <t>Artificial Intelligence Engineer (EMIRATI)</t>
         </is>
       </c>
       <c r="C116" s="3" t="inlineStr">
         <is>
-          <t>Breinstein</t>
+          <t>Salt</t>
         </is>
       </c>
       <c r="D116" s="3" t="inlineStr">
         <is>
-          <t>Groningen, Netherlands</t>
+          <t>Abu Dhabi Emirate, United Arab Emirates</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F116" s="8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G116" s="9" t="inlineStr">
         <is>
@@ -7800,7 +7800,7 @@
       </c>
       <c r="H116" s="3" t="inlineStr">
         <is>
-          <t>This is a junior/graduate-level traineeship requiring Dutch language proficiency, which represents a severe mismatch with the candidate's 10+ years of senior experience and Generative AI/LLM specialization.</t>
+          <t>The role requires an early-career software engineer with 2+ years of experience, representing a significant seniority mismatch for a Lead Data Scientist with 10+ years of experience. Furthermore, the position explicitly specifies that it is for Emirati nationals only.</t>
         </is>
       </c>
       <c r="I116" s="3" t="inlineStr">
@@ -7825,7 +7825,7 @@
       </c>
       <c r="M116" s="6" t="inlineStr">
         <is>
-          <t>https://nl.linkedin.com/jobs/view/traineeship-data-analytics-at-breinstein-4457240429?position=18&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=09Fo%2Bt8pd71ON%2B4bzhNIXw%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/artificial-intelligence-engineer-emirati-at-salt-4457723960?position=26&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=OL7voNOllXDyxcDmkFiWQw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -7835,17 +7835,17 @@
       </c>
       <c r="B117" s="3" t="inlineStr">
         <is>
-          <t>Økonom til finansielle data om pensionssektoren og investeringsfonde i Nationalbanken</t>
+          <t>Junior Research Scientist In the Division of Engineering (Electrical and Computer Engineering) - Dr. Fang Yi</t>
         </is>
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t>Altandetlige.dk</t>
+          <t>New York University Abu Dhabi</t>
         </is>
       </c>
       <c r="D117" s="3" t="inlineStr">
         <is>
-          <t>Copenhagen, Capital Region of Denmark, Denmark</t>
+          <t>Abu Dhabi, Abu Dhabi Emirate, United Arab Emirates</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
@@ -7854,7 +7854,7 @@
         </is>
       </c>
       <c r="F117" s="8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G117" s="9" t="inlineStr">
         <is>
@@ -7863,7 +7863,7 @@
       </c>
       <c r="H117" s="3" t="inlineStr">
         <is>
-          <t>This is a non-technical economics and financial statistics role at Denmark's central bank focusing on pension funds and investment data, which is completely unrelated to the candidate's specialization in Generative AI, LLMs, and agentic systems.</t>
+          <t>This is an academic research scientist role focused on robotics, embodied AI, and assistive technologies, which does not align with the candidate's core specialization in enterprise Generative AI, LLMs, and RAG. Additionally, there is a major seniority mismatch as the role targets junior researchers with under five years of experience, whereas the candidate is a Lead Data Scientist with 10+ years of experience.</t>
         </is>
       </c>
       <c r="I117" s="3" t="inlineStr">
@@ -7873,7 +7873,7 @@
       </c>
       <c r="J117" s="3" t="inlineStr">
         <is>
-          <t>Not stated in JD</t>
+          <t>Possible - relocation support mentioned, visa not explicit</t>
         </is>
       </c>
       <c r="K117" s="2" t="inlineStr">
@@ -7888,7 +7888,7 @@
       </c>
       <c r="M117" s="6" t="inlineStr">
         <is>
-          <t>https://dk.linkedin.com/jobs/view/%C3%B8konom-til-finansielle-data-om-pensionssektoren-og-investeringsfonde-i-nationalbanken-at-altandetlige-dk-4459168468?position=25&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=%2BEekg%2B%2FvA%2BH0hxU4LsvJ5w%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/junior-research-scientist-in-the-division-of-engineering-electrical-and-computer-engineering-dr-fang-yi-at-new-york-university-abu-dhabi-4448981054?position=17&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=Quv11sfD16F354%2FzN0KXRg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -7898,17 +7898,17 @@
       </c>
       <c r="B118" s="3" t="inlineStr">
         <is>
-          <t>Lead Trading Strategist</t>
+          <t>Business Intelligence Analytics</t>
         </is>
       </c>
       <c r="C118" s="3" t="inlineStr">
         <is>
-          <t>Ørsted</t>
+          <t>Confidential</t>
         </is>
       </c>
       <c r="D118" s="3" t="inlineStr">
         <is>
-          <t>Gentofte, Capital Region of Denmark, Denmark</t>
+          <t>Abu Dhabi Emirate, United Arab Emirates</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
@@ -7917,7 +7917,7 @@
         </is>
       </c>
       <c r="F118" s="8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G118" s="9" t="inlineStr">
         <is>
@@ -7926,7 +7926,7 @@
       </c>
       <c r="H118" s="3" t="inlineStr">
         <is>
-          <t>This is a quantitative energy trading and fundamental market analysis role requiring deep domain expertise in European power markets and commodities trading, which is completely unrelated to the candidate's core GenAI, LLM, and data science specialization.</t>
+          <t>This is a Business Intelligence and reporting role focusing on traditional tools like SQL Server, Tableau, PowerBI, and IT service management, completely lacking any Generative AI, LLM, or agentic specialization. The candidate's advanced GenAI and data science background is a severe mismatch for this operational BI position.</t>
         </is>
       </c>
       <c r="I118" s="3" t="inlineStr">
@@ -7951,7 +7951,7 @@
       </c>
       <c r="M118" s="6" t="inlineStr">
         <is>
-          <t>https://dk.linkedin.com/jobs/view/lead-trading-strategist-at-%C3%B8rsted-4439179684?position=21&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=LxVb1rg9c7QiaOEs5%2BY%2FTw%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/business-intelligence-analytics-at-pump-dynamics-4457247369?position=16&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=q3L54POb%2Ba8jMFybGRPVBA%3D%3D&amp;trk=public_jobs_jserp-result_search-card</t>
         </is>
       </c>
     </row>
@@ -7961,17 +7961,17 @@
       </c>
       <c r="B119" s="3" t="inlineStr">
         <is>
-          <t>Analytikere med flair for databehandling til PET's kontraspionageindsats mod Rusland</t>
+          <t>Data Analyst - UAE National, ICQA/LND Analytics Team</t>
         </is>
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>Politiets Efterretningstjeneste (PET)</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="D119" s="3" t="inlineStr">
         <is>
-          <t>Copenhagen, Capital Region of Denmark, Denmark</t>
+          <t>Abu Dhabi, Abu Dhabi Emirate, United Arab Emirates</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
@@ -7980,7 +7980,7 @@
         </is>
       </c>
       <c r="F119" s="8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G119" s="9" t="inlineStr">
         <is>
@@ -7989,7 +7989,7 @@
       </c>
       <c r="H119" s="3" t="inlineStr">
         <is>
-          <t>This is a national security intelligence and counter-espionage analyst role entirely unrelated to data science, artificial intelligence, LLMs, or software engineering. It focuses on intelligence operations and telecommunications data processing rather than the candidate's core Generative AI specialization.</t>
+          <t>This is a Data Analyst role focusing on standard reporting, SQL, QuickSight, and AWS data warehousing infrastructure, which is entirely unrelated to the candidate's core specialization in Generative AI, LLMs, and agentic workflows. Furthermore, there is a severe seniority and domain mismatch as the role targets data analysis rather than advanced AI leadership.</t>
         </is>
       </c>
       <c r="I119" s="3" t="inlineStr">
@@ -8014,7 +8014,7 @@
       </c>
       <c r="M119" s="6" t="inlineStr">
         <is>
-          <t>https://dk.linkedin.com/jobs/view/analytikere-med-flair-for-databehandling-til-pet-s-kontraspionageindsats-mod-rusland-at-politiets-efterretningstjeneste-pet-4457295379?position=17&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=jfzRay2PLGqzZJAC5yISBA%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/data-analyst-uae-national-icqa-lnd-analytics-team-at-amazon-4459175702?position=13&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=2u0HotRhWhUDg980ATy2nw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -8024,26 +8024,26 @@
       </c>
       <c r="B120" s="3" t="inlineStr">
         <is>
-          <t>BI Specialist - turn healthcare data into better care decisions</t>
+          <t>Mathematician (Remote)</t>
         </is>
       </c>
       <c r="C120" s="3" t="inlineStr">
         <is>
-          <t>Systematic</t>
+          <t>Hired</t>
         </is>
       </c>
       <c r="D120" s="3" t="inlineStr">
         <is>
-          <t>Aarhus, Central Denmark Region, Denmark</t>
+          <t>United Arab Emirates</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F120" s="8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G120" s="9" t="inlineStr">
         <is>
@@ -8052,7 +8052,7 @@
       </c>
       <c r="H120" s="3" t="inlineStr">
         <is>
-          <t>This role is for a BI Specialist focusing on healthcare data systems, SQL, T-SQL, DAX, and client communication, which is completely unrelated to the candidate's core specialization in Generative AI, LLMs, and agentic AI systems. Additionally, it requires proficiency in Danish.</t>
+          <t>This remote contractor role focuses on pure applied mathematics and algorithmic optimization rather than Generative AI, LLMs, or agentic frameworks. While the candidate has a strong data science background, the job is entirely unrelated to his core GenAI and RAG specialization.</t>
         </is>
       </c>
       <c r="I120" s="3" t="inlineStr">
@@ -8077,7 +8077,7 @@
       </c>
       <c r="M120" s="6" t="inlineStr">
         <is>
-          <t>https://dk.linkedin.com/jobs/view/bi-specialist-turn-healthcare-data-into-better-care-decisions-at-systematic-4449000390?position=13&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=C4YvYCcgfvLE1Lup1m630A%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/mathematician-remote-at-hired-4459651401?position=11&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=L0rt1zlpnHOlSTn4%2BjbBZg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -8087,26 +8087,26 @@
       </c>
       <c r="B121" s="3" t="inlineStr">
         <is>
-          <t>Demand Planner (f/m/x)</t>
+          <t>Statistician (Remote)</t>
         </is>
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>HelloFresh</t>
+          <t>Hired</t>
         </is>
       </c>
       <c r="D121" s="3" t="inlineStr">
         <is>
-          <t>Copenhagen Municipality, Capital Region of Denmark, Denmark</t>
+          <t>United Arab Emirates</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F121" s="8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G121" s="9" t="inlineStr">
         <is>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="H121" s="3" t="inlineStr">
         <is>
-          <t>This is a non-AI supply chain demand planning role focused on SQL, logistics, and forecasting metrics like MAPE, which is completely unrelated to the candidate's core GenAI, LLM, and agentic AI specialization.</t>
+          <t>This role focuses heavily on classical statistics, experimental design, and A/B testing, requiring a PhD in Statistics, which does not match the candidate's core GenAI and LLM specialization. Furthermore, it is a contract statistician role rather than an advanced AI engineering or agentic systems role.</t>
         </is>
       </c>
       <c r="I121" s="3" t="inlineStr">
@@ -8140,7 +8140,7 @@
       </c>
       <c r="M121" s="6" t="inlineStr">
         <is>
-          <t>https://dk.linkedin.com/jobs/view/demand-planner-f-m-x-at-hellofresh-4459625132?position=6&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=%2FDvrjQmxzWwgXh6GBB3pqA%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/statistician-remote-at-hired-4459636643?position=12&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=%2FKljESl%2B5ntTSKKRsgpGUg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -8150,26 +8150,26 @@
       </c>
       <c r="B122" s="3" t="inlineStr">
         <is>
-          <t>Senior Analyst - Market Intelligence (Trade &amp; Commodities)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="C122" s="3" t="inlineStr">
         <is>
-          <t>Robert Walters</t>
+          <t>TenneT</t>
         </is>
       </c>
       <c r="D122" s="3" t="inlineStr">
         <is>
-          <t>Abu Dhabi, Abu Dhabi Emirate, United Arab Emirates</t>
+          <t>Arnhem, Gelderland, Netherlands</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F122" s="8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G122" s="9" t="inlineStr">
         <is>
@@ -8178,7 +8178,7 @@
       </c>
       <c r="H122" s="3" t="inlineStr">
         <is>
-          <t>This is a non-technical role focusing on market intelligence, trade flows, and supply chain analysis requiring Arabic fluency, which has no overlap with the candidate's core GenAI, LLMs, and agentic AI specialization.</t>
+          <t>This is a Data Engineer role focused on infrastructure, Java/Python backend development, Kubernetes, and streaming platforms like Apache Kafka, which is completely misaligned with the candidate's specialization in Generative AI, LLMs, and agentic workflows. Additionally, the role explicitly requires professional fluency in Dutch, which the candidate lacks.</t>
         </is>
       </c>
       <c r="I122" s="3" t="inlineStr">
@@ -8191,9 +8191,9 @@
           <t>Not stated in JD</t>
         </is>
       </c>
-      <c r="K122" s="7" t="inlineStr">
-        <is>
-          <t>New this run (2026-08-27 06:43 UTC)</t>
+      <c r="K122" s="2" t="inlineStr">
+        <is>
+          <t>From previous run</t>
         </is>
       </c>
       <c r="L122" s="2" t="inlineStr">
@@ -8203,7 +8203,7 @@
       </c>
       <c r="M122" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/senior-analyst-market-intelligence-trade-commodities-at-robert-walters-4457222382?position=30&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=JK2lIzdStMxW3Rb1o%2FxSgQ%3D%3D</t>
+          <t>https://nl.linkedin.com/jobs/view/data-engineer-at-tennet-4459682650?position=28&amp;pageNum=0&amp;refId=oiBIn1Czflg0JjZjH5z0Lg%3D%3D&amp;trackingId=VjGapIUBNcJsDHWWWnnyCQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -8213,26 +8213,26 @@
       </c>
       <c r="B123" s="3" t="inlineStr">
         <is>
-          <t>AI &amp; Data - BrightStar program - Part-Time For Students | UAE Nationals Only - Dubai</t>
+          <t>E-commerce Data Analyst</t>
         </is>
       </c>
       <c r="C123" s="3" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>My Jewellery</t>
         </is>
       </c>
       <c r="D123" s="3" t="inlineStr">
         <is>
-          <t>Abu Dhabi, Abu Dhabi Emirate, United Arab Emirates</t>
+          <t>’s-Hertogenbosch, North Brabant, Netherlands</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F123" s="8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G123" s="9" t="inlineStr">
         <is>
@@ -8241,7 +8241,7 @@
       </c>
       <c r="H123" s="3" t="inlineStr">
         <is>
-          <t>This is a student/internship program ('Part-Time For Students') restricted to UAE Nationals only, representing a severe seniority and eligibility mismatch for a Lead Data Scientist with 10 years of experience.</t>
+          <t>This is an e-commerce data analytics role focused on business intelligence, conversion rate optimization, and dashboards rather than Generative AI, LLMs, or agentic systems. Furthermore, the candidate's 10+ years of senior AI/ML and GenAI experience represent a severe overqualification mismatch for a role requiring around 2 years of e-commerce analytics experience.</t>
         </is>
       </c>
       <c r="I123" s="3" t="inlineStr">
@@ -8254,9 +8254,9 @@
           <t>Not stated in JD</t>
         </is>
       </c>
-      <c r="K123" s="7" t="inlineStr">
-        <is>
-          <t>New this run (2026-08-27 06:43 UTC)</t>
+      <c r="K123" s="2" t="inlineStr">
+        <is>
+          <t>From previous run</t>
         </is>
       </c>
       <c r="L123" s="2" t="inlineStr">
@@ -8266,7 +8266,7 @@
       </c>
       <c r="M123" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/ai-data-brightstar-program-part-time-for-students-uae-nationals-only-dubai-at-deloitte-4459166169?position=29&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=eJo5yKx6Zm7GgBBf0abvaA%3D%3D</t>
+          <t>https://nl.linkedin.com/jobs/view/e-commerce-data-analyst-at-my-jewellery-4458352332?position=24&amp;pageNum=0&amp;refId=oiBIn1Czflg0JjZjH5z0Lg%3D%3D&amp;trackingId=l7ZuY53wCY8i%2FsbUtVRI1w%3D%3D</t>
         </is>
       </c>
     </row>
@@ -8276,26 +8276,26 @@
       </c>
       <c r="B124" s="3" t="inlineStr">
         <is>
-          <t>SAS Analyst</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="C124" s="3" t="inlineStr">
         <is>
-          <t>One75mb HRM Pvt Ltd.</t>
+          <t>Kitopi</t>
         </is>
       </c>
       <c r="D124" s="3" t="inlineStr">
         <is>
-          <t>Abu Dhabi Emirate, United Arab Emirates</t>
+          <t>Dubai, United Arab Emirates</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F124" s="8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G124" s="9" t="inlineStr">
         <is>
@@ -8304,7 +8304,7 @@
       </c>
       <c r="H124" s="3" t="inlineStr">
         <is>
-          <t>This role is a SAS Anti-Money Laundering (AML) Developer position focused on SAS Viya, SAS programming, and compliance systems. It has no connection to Generative AI, LLMs, RAG, or agentic systems, making it an entirely irrelevant fit for a GenAI specialist.</t>
+          <t>This is a role for a Senior Data Engineer focused on building data pipelines, ELT processes, Snowflake, and dbt, which is completely unrelated to the candidate's core specialization as a Lead Data Scientist specializing in GenAI, LLMs, and agentic workflows.</t>
         </is>
       </c>
       <c r="I124" s="3" t="inlineStr">
@@ -8319,7 +8319,7 @@
       </c>
       <c r="K124" s="7" t="inlineStr">
         <is>
-          <t>New this run (2026-08-27 06:43 UTC)</t>
+          <t>New this run (2026-08-27 15:40 UTC)</t>
         </is>
       </c>
       <c r="L124" s="2" t="inlineStr">
@@ -8329,7 +8329,7 @@
       </c>
       <c r="M124" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/sas-analyst-at-one75mb-hrm-pvt-ltd-4459306494?position=19&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=NfyeO5P7KUMAsO5xQjjwEA%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/senior-data-engineer-at-kitopi-4457746184?position=4&amp;pageNum=0&amp;refId=50H6yCrEXIuhgr6eqEojNg%3D%3D&amp;trackingId=brdZZnynoUz1kG72mAhlOg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -8339,26 +8339,26 @@
       </c>
       <c r="B125" s="3" t="inlineStr">
         <is>
-          <t>Finance Information Systems Analyst</t>
+          <t>Total Rewards Analyst | Corporate Services | Dubai</t>
         </is>
       </c>
       <c r="C125" s="3" t="inlineStr">
         <is>
-          <t>United Arab Emirates University, Department of Family Medicine</t>
+          <t>Al-Futtaim</t>
         </is>
       </c>
       <c r="D125" s="3" t="inlineStr">
         <is>
-          <t>Abu Dhabi, Abu Dhabi Emirate, United Arab Emirates</t>
+          <t>Dubai, Dubai, United Arab Emirates</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F125" s="8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G125" s="9" t="inlineStr">
         <is>
@@ -8367,7 +8367,7 @@
       </c>
       <c r="H125" s="3" t="inlineStr">
         <is>
-          <t>This role is for a Finance Information Systems Analyst focusing on Oracle SQL, financial reporting, and system maintenance, which is completely unrelated to the candidate's core expertise in Generative AI, LLMs, and agentic workflows.</t>
+          <t>This is a Total Rewards (compensation and benefits) HR analyst role focused on HRIS systems, pay equity, and market benchmarking, completely unrelated to the candidate's core specialization in Generative AI, LLMs, and agentic workflows.</t>
         </is>
       </c>
       <c r="I125" s="3" t="inlineStr">
@@ -8382,7 +8382,7 @@
       </c>
       <c r="K125" s="7" t="inlineStr">
         <is>
-          <t>New this run (2026-08-27 06:43 UTC)</t>
+          <t>New this run (2026-08-27 15:40 UTC)</t>
         </is>
       </c>
       <c r="L125" s="2" t="inlineStr">
@@ -8392,7 +8392,7 @@
       </c>
       <c r="M125" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/finance-information-systems-analyst-at-united-arab-emirates-university-department-of-family-medicine-4458309884?position=18&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=ZkLRAbbB1OpTP3DQTi%2FB4Q%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/total-rewards-analyst-corporate-services-dubai-at-al-futtaim-4449646903?position=8&amp;pageNum=0&amp;refId=50H6yCrEXIuhgr6eqEojNg%3D%3D&amp;trackingId=ZNz4Qjdr30DeI436luixFQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -8402,17 +8402,17 @@
       </c>
       <c r="B126" s="3" t="inlineStr">
         <is>
-          <t>Analyst I - Advisory</t>
+          <t>Graphene Photonics Data Analyst (f/m/d)</t>
         </is>
       </c>
       <c r="C126" s="3" t="inlineStr">
         <is>
-          <t>Marsh Risk</t>
+          <t>Black Semiconductor</t>
         </is>
       </c>
       <c r="D126" s="3" t="inlineStr">
         <is>
-          <t>Abu Dhabi, Abu Dhabi Emirate, United Arab Emirates</t>
+          <t>Aachen, North Rhine-Westphalia, Germany</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
@@ -8430,7 +8430,7 @@
       </c>
       <c r="H126" s="3" t="inlineStr">
         <is>
-          <t>This is a graduate/entry-level risk engineering and data analyst role located in the UAE restricted to UAE Nationals, representing a severe mismatch in both seniority and specialization for a Lead Data Scientist with 10+ years of experience in GenAI.</t>
+          <t>This role is entirely focused on semiconductor hardware, graphene photonics, and physical data analysis, with zero relevance to the candidate's core specialization in Generative AI, LLMs, and agentic workflows.</t>
         </is>
       </c>
       <c r="I126" s="3" t="inlineStr">
@@ -8443,9 +8443,9 @@
           <t>Not stated in JD</t>
         </is>
       </c>
-      <c r="K126" s="7" t="inlineStr">
-        <is>
-          <t>New this run (2026-08-27 06:43 UTC)</t>
+      <c r="K126" s="2" t="inlineStr">
+        <is>
+          <t>From previous run</t>
         </is>
       </c>
       <c r="L126" s="2" t="inlineStr">
@@ -8455,7 +8455,7 @@
       </c>
       <c r="M126" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/analyst-i-advisory-at-marsh-risk-4459170127?position=6&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=hO0QLO%2FIAeXdRsG2PtQkTA%3D%3D</t>
+          <t>https://de.linkedin.com/jobs/view/graphene-photonics-data-analyst-f-m-d-at-black-semiconductor-4459334621?position=26&amp;pageNum=0&amp;refId=T%2F0KkBXL%2Fl%2B5Iv5tUGTY7Q%3D%3D&amp;trackingId=KgQ01De6ChDgIN8UxnUvXg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -8465,17 +8465,17 @@
       </c>
       <c r="B127" s="3" t="inlineStr">
         <is>
-          <t>Senior Economist / Economic Researcher</t>
+          <t>Financial Planning and Analysis Manager</t>
         </is>
       </c>
       <c r="C127" s="3" t="inlineStr">
         <is>
-          <t>Robert Walters</t>
+          <t>Confidential Jobs</t>
         </is>
       </c>
       <c r="D127" s="3" t="inlineStr">
         <is>
-          <t>Abu Dhabi, Abu Dhabi Emirate, United Arab Emirates</t>
+          <t>Dubai, United Arab Emirates</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
@@ -8493,7 +8493,7 @@
       </c>
       <c r="H127" s="3" t="inlineStr">
         <is>
-          <t>This role is for a Senior Economist focusing on macroeconomic research, policy analysis, and economic forecasting, which is completely unrelated to the candidate's specialization in Generative AI, LLMs, and data science.</t>
+          <t>This Financial Planning and Analysis Manager role is entirely unrelated to data science, machine learning, or software engineering, focusing instead on corporate finance, budgeting, construction economics, and IFRS 15 accounting. There is a massive domain and seniority mismatch for an AI/GenAI Lead Data Scientist.</t>
         </is>
       </c>
       <c r="I127" s="3" t="inlineStr">
@@ -8506,9 +8506,9 @@
           <t>Not stated in JD</t>
         </is>
       </c>
-      <c r="K127" s="7" t="inlineStr">
-        <is>
-          <t>New this run (2026-08-27 06:43 UTC)</t>
+      <c r="K127" s="2" t="inlineStr">
+        <is>
+          <t>From previous run</t>
         </is>
       </c>
       <c r="L127" s="2" t="inlineStr">
@@ -8518,7 +8518,7 @@
       </c>
       <c r="M127" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/senior-economist-economic-researcher-at-robert-walters-4457234594?position=21&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=hNkG3K%2BgFb1grR8QDMiBxA%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/financial-planning-and-analysis-manager-at-confidential-jobs-4452594332?position=29&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=KEfZVTEknZKckxH1vstrzQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -8528,12 +8528,12 @@
       </c>
       <c r="B128" s="3" t="inlineStr">
         <is>
-          <t>National Assistant Planner</t>
+          <t>Data QA Engineer</t>
         </is>
       </c>
       <c r="C128" s="3" t="inlineStr">
         <is>
-          <t>Al-Futtaim</t>
+          <t>ClearGrid</t>
         </is>
       </c>
       <c r="D128" s="3" t="inlineStr">
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="F128" s="8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G128" s="9" t="inlineStr">
         <is>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="H128" s="3" t="inlineStr">
         <is>
-          <t>This is a non-technical retail merchandise planning role focused on financial forecasting, inventory management, and sales planning, which is entirely unrelated to the candidate's GenAI, LLM, and data science specialization.</t>
+          <t>This role is a Data QA Engineer focused entirely on data quality, dbt testing, and warehouse reconciliation in a fintech/collections environment, lacking any Generative AI, LLM, or agentic specialization. Furthermore, the seniority requirement (2+ years) is well below the candidate's 10+ years as a Lead Data Scientist.</t>
         </is>
       </c>
       <c r="I128" s="3" t="inlineStr">
@@ -8581,7 +8581,7 @@
       </c>
       <c r="M128" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/national-assistant-planner-at-al-futtaim-4459335643?position=23&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=udE1OmanEOJo5NqnDVVmsw%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/data-qa-engineer-at-cleargrid-4457980735?position=25&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=RbMMQ6DAm%2FMomlqBLUM2IQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -8591,12 +8591,12 @@
       </c>
       <c r="B129" s="3" t="inlineStr">
         <is>
-          <t>Forward Deployed AI Integrator (UAE National Only), Field Engineering</t>
+          <t>OTR Planning Manager, Hub Delivery UAE , Hub Delivery</t>
         </is>
       </c>
       <c r="C129" s="3" t="inlineStr">
         <is>
-          <t>Amazon Web Services (AWS)</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="D129" s="3" t="inlineStr">
@@ -8606,11 +8606,11 @@
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F129" s="8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G129" s="9" t="inlineStr">
         <is>
@@ -8619,7 +8619,7 @@
       </c>
       <c r="H129" s="3" t="inlineStr">
         <is>
-          <t>Although the role involves AI tooling and Python, it is restricted to UAE Nationals only, making it impossible for the candidate to qualify. Additionally, the position leans heavily toward technical program management rather than hands-on Generative AI and LLM engineering.</t>
+          <t>This operations and logistics management role is entirely unrelated to data science, machine learning, and Generative AI, focusing instead on supply chain planning and fleet management. Therefore, it is a very poor match for the candidate's core specialization.</t>
         </is>
       </c>
       <c r="I129" s="3" t="inlineStr">
@@ -8644,7 +8644,7 @@
       </c>
       <c r="M129" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/forward-deployed-ai-integrator-uae-national-only-field-engineering-at-amazon-web-services-aws-4459616402?position=14&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=suYy8hgZkG37o3lG7FlDHQ%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/otr-planning-manager-hub-delivery-uae-hub-delivery-at-amazon-4459184678?position=21&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=bqoXqft%2BGFtLz05C2kL0FA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -8654,12 +8654,12 @@
       </c>
       <c r="B130" s="3" t="inlineStr">
         <is>
-          <t>GIS Specialist / Developer</t>
+          <t>Senior Compensation Analyst</t>
         </is>
       </c>
       <c r="C130" s="3" t="inlineStr">
         <is>
-          <t>AECOM</t>
+          <t>Cartier</t>
         </is>
       </c>
       <c r="D130" s="3" t="inlineStr">
@@ -8673,7 +8673,7 @@
         </is>
       </c>
       <c r="F130" s="8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G130" s="9" t="inlineStr">
         <is>
@@ -8682,7 +8682,7 @@
       </c>
       <c r="H130" s="3" t="inlineStr">
         <is>
-          <t>This is a GIS Specialist role focused on ArcGIS Enterprise administration, spatial analysis, and Python/ArcPy automation, which is completely unrelated to the candidate's core specialization in Generative AI, LLMs, and agentic systems.</t>
+          <t>This is a non-technical role focused strictly on compensation analysis, financial modeling, and advanced Excel simulation design within HR, which has no overlap with the candidate's core GenAI, LLM, or data science specialization.</t>
         </is>
       </c>
       <c r="I130" s="3" t="inlineStr">
@@ -8707,7 +8707,7 @@
       </c>
       <c r="M130" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/gis-specialist-developer-at-aecom-4456869023?position=15&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=lGxG6%2FYECt2YwYGWf5hEZA%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/senior-compensation-analyst-at-cartier-4448528069?position=20&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=uU%2BxMpwsg7Xv71%2Fjk83xeg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -8717,12 +8717,12 @@
       </c>
       <c r="B131" s="3" t="inlineStr">
         <is>
-          <t>Quant Desk Lead and Portfolio Manager</t>
+          <t>AI &amp; Data - BrightStar program - Part-Time For Students | UAE Nationals Only - Dubai</t>
         </is>
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t>EMCD</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="D131" s="3" t="inlineStr">
@@ -8736,7 +8736,7 @@
         </is>
       </c>
       <c r="F131" s="8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G131" s="9" t="inlineStr">
         <is>
@@ -8745,7 +8745,7 @@
       </c>
       <c r="H131" s="3" t="inlineStr">
         <is>
-          <t>This is a finance and quantitative trading role focused on running a systematic trading desk, portfolio management, and P&amp;L ownership, which is entirely unrelated to the candidate's core specialization in Generative AI, LLMs, and agentic systems.</t>
+          <t>This student internship/part-time program is an extreme seniority mismatch for a Lead Data Scientist with 10+ years of experience. Furthermore, the role is strictly restricted to UAE Nationals and unrelated to the candidate's specialized GenAI and agentic AI expertise.</t>
         </is>
       </c>
       <c r="I131" s="3" t="inlineStr">
@@ -8770,7 +8770,7 @@
       </c>
       <c r="M131" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/quant-desk-lead-and-portfolio-manager-at-emcd-4457949555?position=13&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=drHtrw6uBtEz5S2i%2BjBT5A%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/ai-data-brightstar-program-part-time-for-students-uae-nationals-only-dubai-at-deloitte-4459165278?position=18&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=rkeXlOzDBapH9BYwLoMUoA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -8780,17 +8780,17 @@
       </c>
       <c r="B132" s="3" t="inlineStr">
         <is>
-          <t>Join Norlys Energy Trading</t>
+          <t>Junior Market Analyst - UAE National</t>
         </is>
       </c>
       <c r="C132" s="3" t="inlineStr">
         <is>
-          <t>Norlys Energy Trading A/S</t>
+          <t>Richemont</t>
         </is>
       </c>
       <c r="D132" s="3" t="inlineStr">
         <is>
-          <t>Aalborg, North Denmark Region, Denmark</t>
+          <t>Dubai, Dubai, United Arab Emirates</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
@@ -8799,7 +8799,7 @@
         </is>
       </c>
       <c r="F132" s="8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G132" s="9" t="inlineStr">
         <is>
@@ -8808,7 +8808,7 @@
       </c>
       <c r="H132" s="3" t="inlineStr">
         <is>
-          <t>This is an open, unsolicited job application for a general talent pool in energy trading, rather than a defined Data Science or Generative AI role. It completely lacks technical specifications, making it impossible to evaluate against the candidate's specialized GenAI and LLM expertise.</t>
+          <t>This role is a junior market research and business development position focused on luxury retail intelligence in the MEIAT region, which is completely unrelated to data science, artificial intelligence, or the candidate's GenAI and LLM specialization.</t>
         </is>
       </c>
       <c r="I132" s="3" t="inlineStr">
@@ -8833,7 +8833,7 @@
       </c>
       <c r="M132" s="6" t="inlineStr">
         <is>
-          <t>https://dk.linkedin.com/jobs/view/join-norlys-energy-trading-at-norlys-energy-trading-a-s-4459158084?position=26&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=Z%2BOuDrbPap3omWro18MA2g%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/junior-market-analyst-uae-national-at-richemont-4448527067?position=22&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=fabWFpBqiTWxCuIFUXVosg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -8843,17 +8843,17 @@
       </c>
       <c r="B133" s="3" t="inlineStr">
         <is>
-          <t>PhD scholarship in Modeling and Control of Parkinson’s Disease - DTU Electro</t>
+          <t>Data Analyst - (Advanced Excel expertise)</t>
         </is>
       </c>
       <c r="C133" s="3" t="inlineStr">
         <is>
-          <t>DTU - Technical University of Denmark</t>
+          <t>BigTapp Analytics</t>
         </is>
       </c>
       <c r="D133" s="3" t="inlineStr">
         <is>
-          <t>Kongens Lyngby, Capital Region of Denmark, Denmark</t>
+          <t>Dubai, Dubai, United Arab Emirates</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
@@ -8862,7 +8862,7 @@
         </is>
       </c>
       <c r="F133" s="8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G133" s="9" t="inlineStr">
         <is>
@@ -8871,7 +8871,7 @@
       </c>
       <c r="H133" s="3" t="inlineStr">
         <is>
-          <t>This is a PhD scholarship position in neuroengineering, control systems, and healthcare technology at DTU, which is completely unrelated to the candidate's specialization in Generative AI, LLMs, and agentic systems.</t>
+          <t>This is a Data Analyst role focused entirely on Advanced Excel, corporate tax data quality, and data validation, with no connection to the candidate's GenAI, LLM, or agentic AI specialization.</t>
         </is>
       </c>
       <c r="I133" s="3" t="inlineStr">
@@ -8881,7 +8881,7 @@
       </c>
       <c r="J133" s="3" t="inlineStr">
         <is>
-          <t>Possible - relocation support mentioned, visa not explicit</t>
+          <t>Not stated in JD</t>
         </is>
       </c>
       <c r="K133" s="2" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="M133" s="6" t="inlineStr">
         <is>
-          <t>https://dk.linkedin.com/jobs/view/phd-scholarship-in-modeling-and-control-of-parkinson%E2%80%99s-disease-dtu-electro-at-dtu-technical-university-of-denmark-4459145557?position=20&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=mStwcLkWBAvzmreGSwO4Hw%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/data-analyst-advanced-excel-expertise-at-bigtapp-analytics-4459194093?position=16&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=vJ8ubhhJtvsWirwhmdkH%2BA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -8906,17 +8906,17 @@
       </c>
       <c r="B134" s="3" t="inlineStr">
         <is>
-          <t>Analytikere med flair for databehandling til PET's kontraspionageindsats mod Rusland</t>
+          <t>Junior Data Analyst</t>
         </is>
       </c>
       <c r="C134" s="3" t="inlineStr">
         <is>
-          <t>Politi</t>
+          <t>Arabian Private Holdings</t>
         </is>
       </c>
       <c r="D134" s="3" t="inlineStr">
         <is>
-          <t>Copenhagen, Capital Region of Denmark, Denmark</t>
+          <t>Sharjah, Sharjah Emirate, United Arab Emirates</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
@@ -8925,7 +8925,7 @@
         </is>
       </c>
       <c r="F134" s="8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G134" s="9" t="inlineStr">
         <is>
@@ -8934,7 +8934,7 @@
       </c>
       <c r="H134" s="3" t="inlineStr">
         <is>
-          <t>This is a national security intelligence and counter-espionage analyst role at the Danish Security and Intelligence Service (PET), which is completely unrelated to data science, artificial intelligence, or the candidate's Generative AI and LLM specialization.</t>
+          <t>This is a junior data analyst role focused on operational data interpretation, basic SQL/Excel database maintenance, and corporate strategy support, completely unrelated to the candidate's GenAI, LLMs, and agentic AI specialization. Additionally, there is a severe seniority mismatch as the role is strictly junior while the candidate is a Lead Data Scientist with 10+ years of experience.</t>
         </is>
       </c>
       <c r="I134" s="3" t="inlineStr">
@@ -8959,7 +8959,7 @@
       </c>
       <c r="M134" s="6" t="inlineStr">
         <is>
-          <t>https://dk.linkedin.com/jobs/view/analytikere-med-flair-for-databehandling-til-pet-s-kontraspionageindsats-mod-rusland-at-politi-4457943820?position=18&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=%2FGEw4KOC0oARqkQIDTGJ4Q%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/junior-data-analyst-at-arabian-private-holdings-4457918646?position=11&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=n3OKFNsTAywRSCMqHYFmlg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -8969,17 +8969,17 @@
       </c>
       <c r="B135" s="3" t="inlineStr">
         <is>
-          <t>PostDoc - Uncertainty-Aware Optimization in Inverse Problems for Next-Generation 3D Scanning</t>
+          <t>Data Analyst – Social Support Operations - UAE National</t>
         </is>
       </c>
       <c r="C135" s="3" t="inlineStr">
         <is>
-          <t>3Shape</t>
+          <t>Ministry of Community Empowerment</t>
         </is>
       </c>
       <c r="D135" s="3" t="inlineStr">
         <is>
-          <t>Copenhagen, Capital Region of Denmark, Denmark</t>
+          <t>Dubai, United Arab Emirates</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
@@ -8988,7 +8988,7 @@
         </is>
       </c>
       <c r="F135" s="8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G135" s="9" t="inlineStr">
         <is>
@@ -8997,7 +8997,7 @@
       </c>
       <c r="H135" s="3" t="inlineStr">
         <is>
-          <t>This is a PostDoc position focused on mathematical optimization, numerical linear algebra, and uncertainty quantification for 3D scanning, which requires a PhD. It has no overlap with the candidate's specialization in GenAI, LLMs, and agentic systems.</t>
+          <t>This role is a data analyst position focused on BI, Power BI dashboards, SQL, and social support operations, which is completely unrelated to the candidate's core GenAI, LLMs, and agentic AI specialization. Additionally, it specifies a nationality requirement.</t>
         </is>
       </c>
       <c r="I135" s="3" t="inlineStr">
@@ -9022,7 +9022,7 @@
       </c>
       <c r="M135" s="6" t="inlineStr">
         <is>
-          <t>https://dk.linkedin.com/jobs/view/postdoc-uncertainty-aware-optimization-in-inverse-problems-for-next-generation-3d-scanning-at-3shape-4459171806?position=15&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=bO0aSGZ%2FUAxThXN9yvOERg%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/data-analyst-%E2%80%93-social-support-operations-uae-national-at-ministry-of-community-empowerment-4459118725?position=4&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=q%2FHUZ0XJHF5eY2WSwIWmAg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -9032,17 +9032,17 @@
       </c>
       <c r="B136" s="3" t="inlineStr">
         <is>
-          <t>Scientist, Quantitative Clinical Pharmacology (PK/PD Modeling &amp; Simulation)</t>
+          <t>Graduate - Data Scientist إماراتيين (خلاصة القيد)</t>
         </is>
       </c>
       <c r="C136" s="3" t="inlineStr">
         <is>
-          <t>Hemab Therapeutics</t>
+          <t>AECOM</t>
         </is>
       </c>
       <c r="D136" s="3" t="inlineStr">
         <is>
-          <t>Copenhagen Metropolitan Area</t>
+          <t>Dubai, Dubai, United Arab Emirates</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
@@ -9051,7 +9051,7 @@
         </is>
       </c>
       <c r="F136" s="8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G136" s="9" t="inlineStr">
         <is>
@@ -9060,7 +9060,7 @@
       </c>
       <c r="H136" s="3" t="inlineStr">
         <is>
-          <t>This is a highly specialized biomedical role focusing on Pharmacokinetics/Pharmacodynamics (PK/PD) modeling and clinical pharmacology, requiring a Ph.D. and experience with tools like NONMEM or Monolix. It has zero overlap with the candidate's GenAI, LLM, and data science background.</t>
+          <t>This is a graduate/entry-level program designed specifically for recent graduates (2024-2026) and UAE Nationals, representing a severe seniority and eligibility mismatch for a Lead Data Scientist with 10+ years of experience. Furthermore, the role focuses on construction digital tools, cost management, and general data analytics rather than the candidate's core GenAI, LLMs, and agentic AI specialization.</t>
         </is>
       </c>
       <c r="I136" s="3" t="inlineStr">
@@ -9085,7 +9085,7 @@
       </c>
       <c r="M136" s="6" t="inlineStr">
         <is>
-          <t>https://dk.linkedin.com/jobs/view/scientist-quantitative-clinical-pharmacology-pk-pd-modeling-simulation-at-hemab-therapeutics-4457218306?position=14&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=jhTyKvDAQ70R9PD5s0x2yA%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/graduate-data-scientist-%D8%A5%D9%85%D8%A7%D8%B1%D8%A7%D8%AA%D9%8A%D9%8A%D9%86-%D8%AE%D9%84%D8%A7%D8%B5%D8%A9-%D8%A7%D9%84%D9%82%D9%8A%D8%AF-at-aecom-4457915285?position=1&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=deUfOEFHstE7TEtandLeTg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -9095,17 +9095,17 @@
       </c>
       <c r="B137" s="3" t="inlineStr">
         <is>
-          <t>Senior Payload Data Operator</t>
+          <t>Quantitative Researcher, Quantitative Strategies</t>
         </is>
       </c>
       <c r="C137" s="3" t="inlineStr">
         <is>
-          <t>FADA</t>
+          <t>Millennium</t>
         </is>
       </c>
       <c r="D137" s="3" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>Dubai, Dubai, United Arab Emirates</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
@@ -9114,7 +9114,7 @@
         </is>
       </c>
       <c r="F137" s="8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G137" s="9" t="inlineStr">
         <is>
@@ -9123,7 +9123,7 @@
       </c>
       <c r="H137" s="3" t="inlineStr">
         <is>
-          <t>This is a satellite payload data engineering role focused on aerospace, remote sensing, and image processing (EO/SAR), which is completely unrelated to the candidate's specialization in GenAI, LLMs, and agentic systems.</t>
+          <t>This role focuses entirely on quantitative finance, statistical modeling, and systematic equity trading in Asian markets, which has no overlap with the candidate's core specialization in Generative AI, LLMs, and agentic systems. Additionally, the domain requires specific desk quant trading experience that is absent from the candidate's profile.</t>
         </is>
       </c>
       <c r="I137" s="3" t="inlineStr">
@@ -9136,9 +9136,9 @@
           <t>Not stated in JD</t>
         </is>
       </c>
-      <c r="K137" s="7" t="inlineStr">
-        <is>
-          <t>New this run (2026-08-27 06:43 UTC)</t>
+      <c r="K137" s="2" t="inlineStr">
+        <is>
+          <t>From previous run</t>
         </is>
       </c>
       <c r="L137" s="2" t="inlineStr">
@@ -9148,7 +9148,7 @@
       </c>
       <c r="M137" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/senior-payload-data-operator-at-fada-4448986926?position=20&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=xdfP2za0I45WGIW%2FRJb%2BgA%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/quantitative-researcher-quantitative-strategies-at-millennium-4439427782?position=2&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=uptfSAbwEngBw3yrsrQehg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -9158,26 +9158,26 @@
       </c>
       <c r="B138" s="3" t="inlineStr">
         <is>
-          <t>Arabic Speech And Natural Language Processing Specialist</t>
+          <t>Analyst I - Advisory</t>
         </is>
       </c>
       <c r="C138" s="3" t="inlineStr">
         <is>
-          <t>Birbal AI</t>
+          <t>Marsh Risk</t>
         </is>
       </c>
       <c r="D138" s="3" t="inlineStr">
         <is>
-          <t>Abu Dhabi Emirate, United Arab Emirates</t>
+          <t>Dubai, Dubai, United Arab Emirates</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F138" s="8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G138" s="9" t="inlineStr">
         <is>
@@ -9186,7 +9186,7 @@
       </c>
       <c r="H138" s="3" t="inlineStr">
         <is>
-          <t>The role requires specialized expertise in Arabic speech technology (ASR, TTS, audio DSP) and native command of Gulf Arabic dialects, which does not match the candidate's core background in GenAI, LLMs, and RAG for English-language banking and HR use cases.</t>
+          <t>This is a fresh-graduate/entry-level role for recent graduates that focuses heavily on risk engineering and basic internal digitalization using Excel and Microsoft tools, which is far below the candidate's 10+ years of experience as a Lead Data Scientist specializing in advanced GenAI and agentic systems.</t>
         </is>
       </c>
       <c r="I138" s="3" t="inlineStr">
@@ -9199,9 +9199,9 @@
           <t>Not stated in JD</t>
         </is>
       </c>
-      <c r="K138" s="7" t="inlineStr">
-        <is>
-          <t>New this run (2026-08-27 06:43 UTC)</t>
+      <c r="K138" s="2" t="inlineStr">
+        <is>
+          <t>From previous run</t>
         </is>
       </c>
       <c r="L138" s="2" t="inlineStr">
@@ -9211,7 +9211,7 @@
       </c>
       <c r="M138" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/arabic-speech-and-natural-language-processing-specialist-at-birbal-ai-4457738899?position=14&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=ztG06Ly%2FIZ3fxm%2Fhvl626A%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/analyst-i-advisory-at-marsh-risk-4459165267?position=3&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=NpomdoqDoXrgLAw8%2BZjEQA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -9221,60 +9221,1824 @@
       </c>
       <c r="B139" s="3" t="inlineStr">
         <is>
+          <t>Demand Planner (f/m/x)</t>
+        </is>
+      </c>
+      <c r="C139" s="3" t="inlineStr">
+        <is>
+          <t>HelloFresh</t>
+        </is>
+      </c>
+      <c r="D139" s="3" t="inlineStr">
+        <is>
+          <t>Amsterdam, North Holland, Netherlands</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="F139" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="G139" s="9" t="inlineStr">
+        <is>
+          <t>Below threshold</t>
+        </is>
+      </c>
+      <c r="H139" s="3" t="inlineStr">
+        <is>
+          <t>This is a supply chain demand planning role requiring 2-3 years of experience in business forecasting, which is completely unrelated to the candidate's specialization in Generative AI, LLMs, and agentic systems. Furthermore, there is a severe seniority mismatch as the candidate is a Lead Data Scientist with 10+ years of experience.</t>
+        </is>
+      </c>
+      <c r="I139" s="3" t="inlineStr">
+        <is>
+          <t>Not stated in JD</t>
+        </is>
+      </c>
+      <c r="J139" s="3" t="inlineStr">
+        <is>
+          <t>Not stated in JD</t>
+        </is>
+      </c>
+      <c r="K139" s="2" t="inlineStr">
+        <is>
+          <t>From previous run</t>
+        </is>
+      </c>
+      <c r="L139" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="M139" s="6" t="inlineStr">
+        <is>
+          <t>https://nl.linkedin.com/jobs/view/demand-planner-f-m-x-at-hellofresh-4459621163?position=29&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=ScTLY%2B93hMGSjD1GtPlxQw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="55" customHeight="1">
+      <c r="A140" s="2" t="n">
+        <v>139</v>
+      </c>
+      <c r="B140" s="3" t="inlineStr">
+        <is>
+          <t>Traineeship Data Analytics</t>
+        </is>
+      </c>
+      <c r="C140" s="3" t="inlineStr">
+        <is>
+          <t>Breinstein</t>
+        </is>
+      </c>
+      <c r="D140" s="3" t="inlineStr">
+        <is>
+          <t>Groningen, Netherlands</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="F140" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="G140" s="9" t="inlineStr">
+        <is>
+          <t>Below threshold</t>
+        </is>
+      </c>
+      <c r="H140" s="3" t="inlineStr">
+        <is>
+          <t>This is a junior/graduate-level traineeship requiring Dutch language proficiency, which represents a severe mismatch with the candidate's 10+ years of senior experience and Generative AI/LLM specialization.</t>
+        </is>
+      </c>
+      <c r="I140" s="3" t="inlineStr">
+        <is>
+          <t>Not stated in JD</t>
+        </is>
+      </c>
+      <c r="J140" s="3" t="inlineStr">
+        <is>
+          <t>Not stated in JD</t>
+        </is>
+      </c>
+      <c r="K140" s="2" t="inlineStr">
+        <is>
+          <t>From previous run</t>
+        </is>
+      </c>
+      <c r="L140" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="M140" s="6" t="inlineStr">
+        <is>
+          <t>https://nl.linkedin.com/jobs/view/traineeship-data-analytics-at-breinstein-4457240429?position=18&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=09Fo%2Bt8pd71ON%2B4bzhNIXw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="55" customHeight="1">
+      <c r="A141" s="2" t="n">
+        <v>140</v>
+      </c>
+      <c r="B141" s="3" t="inlineStr">
+        <is>
+          <t>Økonom til finansielle data om pensionssektoren og investeringsfonde i Nationalbanken</t>
+        </is>
+      </c>
+      <c r="C141" s="3" t="inlineStr">
+        <is>
+          <t>Altandetlige.dk</t>
+        </is>
+      </c>
+      <c r="D141" s="3" t="inlineStr">
+        <is>
+          <t>Copenhagen, Capital Region of Denmark, Denmark</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="F141" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="G141" s="9" t="inlineStr">
+        <is>
+          <t>Below threshold</t>
+        </is>
+      </c>
+      <c r="H141" s="3" t="inlineStr">
+        <is>
+          <t>This is a non-technical economics and financial statistics role at Denmark's central bank focusing on pension funds and investment data, which is completely unrelated to the candidate's specialization in Generative AI, LLMs, and agentic systems.</t>
+        </is>
+      </c>
+      <c r="I141" s="3" t="inlineStr">
+        <is>
+          <t>Not stated in JD</t>
+        </is>
+      </c>
+      <c r="J141" s="3" t="inlineStr">
+        <is>
+          <t>Not stated in JD</t>
+        </is>
+      </c>
+      <c r="K141" s="2" t="inlineStr">
+        <is>
+          <t>From previous run</t>
+        </is>
+      </c>
+      <c r="L141" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="M141" s="6" t="inlineStr">
+        <is>
+          <t>https://dk.linkedin.com/jobs/view/%C3%B8konom-til-finansielle-data-om-pensionssektoren-og-investeringsfonde-i-nationalbanken-at-altandetlige-dk-4459168468?position=25&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=%2BEekg%2B%2FvA%2BH0hxU4LsvJ5w%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="55" customHeight="1">
+      <c r="A142" s="2" t="n">
+        <v>141</v>
+      </c>
+      <c r="B142" s="3" t="inlineStr">
+        <is>
+          <t>Lead Trading Strategist</t>
+        </is>
+      </c>
+      <c r="C142" s="3" t="inlineStr">
+        <is>
+          <t>Ørsted</t>
+        </is>
+      </c>
+      <c r="D142" s="3" t="inlineStr">
+        <is>
+          <t>Gentofte, Capital Region of Denmark, Denmark</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="F142" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="G142" s="9" t="inlineStr">
+        <is>
+          <t>Below threshold</t>
+        </is>
+      </c>
+      <c r="H142" s="3" t="inlineStr">
+        <is>
+          <t>This is a quantitative energy trading and fundamental market analysis role requiring deep domain expertise in European power markets and commodities trading, which is completely unrelated to the candidate's core GenAI, LLM, and data science specialization.</t>
+        </is>
+      </c>
+      <c r="I142" s="3" t="inlineStr">
+        <is>
+          <t>Not stated in JD</t>
+        </is>
+      </c>
+      <c r="J142" s="3" t="inlineStr">
+        <is>
+          <t>Not stated in JD</t>
+        </is>
+      </c>
+      <c r="K142" s="2" t="inlineStr">
+        <is>
+          <t>From previous run</t>
+        </is>
+      </c>
+      <c r="L142" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="M142" s="6" t="inlineStr">
+        <is>
+          <t>https://dk.linkedin.com/jobs/view/lead-trading-strategist-at-%C3%B8rsted-4439179684?position=21&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=LxVb1rg9c7QiaOEs5%2BY%2FTw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="55" customHeight="1">
+      <c r="A143" s="2" t="n">
+        <v>142</v>
+      </c>
+      <c r="B143" s="3" t="inlineStr">
+        <is>
+          <t>Analytikere med flair for databehandling til PET's kontraspionageindsats mod Rusland</t>
+        </is>
+      </c>
+      <c r="C143" s="3" t="inlineStr">
+        <is>
+          <t>Politiets Efterretningstjeneste (PET)</t>
+        </is>
+      </c>
+      <c r="D143" s="3" t="inlineStr">
+        <is>
+          <t>Copenhagen, Capital Region of Denmark, Denmark</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="F143" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="G143" s="9" t="inlineStr">
+        <is>
+          <t>Below threshold</t>
+        </is>
+      </c>
+      <c r="H143" s="3" t="inlineStr">
+        <is>
+          <t>This is a national security intelligence and counter-espionage analyst role entirely unrelated to data science, artificial intelligence, LLMs, or software engineering. It focuses on intelligence operations and telecommunications data processing rather than the candidate's core Generative AI specialization.</t>
+        </is>
+      </c>
+      <c r="I143" s="3" t="inlineStr">
+        <is>
+          <t>Not stated in JD</t>
+        </is>
+      </c>
+      <c r="J143" s="3" t="inlineStr">
+        <is>
+          <t>Not stated in JD</t>
+        </is>
+      </c>
+      <c r="K143" s="2" t="inlineStr">
+        <is>
+          <t>From previous run</t>
+        </is>
+      </c>
+      <c r="L143" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="M143" s="6" t="inlineStr">
+        <is>
+          <t>https://dk.linkedin.com/jobs/view/analytikere-med-flair-for-databehandling-til-pet-s-kontraspionageindsats-mod-rusland-at-politiets-efterretningstjeneste-pet-4457295379?position=17&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=jfzRay2PLGqzZJAC5yISBA%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="55" customHeight="1">
+      <c r="A144" s="2" t="n">
+        <v>143</v>
+      </c>
+      <c r="B144" s="3" t="inlineStr">
+        <is>
+          <t>BI Specialist - turn healthcare data into better care decisions</t>
+        </is>
+      </c>
+      <c r="C144" s="3" t="inlineStr">
+        <is>
+          <t>Systematic</t>
+        </is>
+      </c>
+      <c r="D144" s="3" t="inlineStr">
+        <is>
+          <t>Aarhus, Central Denmark Region, Denmark</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="F144" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="G144" s="9" t="inlineStr">
+        <is>
+          <t>Below threshold</t>
+        </is>
+      </c>
+      <c r="H144" s="3" t="inlineStr">
+        <is>
+          <t>This role is for a BI Specialist focusing on healthcare data systems, SQL, T-SQL, DAX, and client communication, which is completely unrelated to the candidate's core specialization in Generative AI, LLMs, and agentic AI systems. Additionally, it requires proficiency in Danish.</t>
+        </is>
+      </c>
+      <c r="I144" s="3" t="inlineStr">
+        <is>
+          <t>Not stated in JD</t>
+        </is>
+      </c>
+      <c r="J144" s="3" t="inlineStr">
+        <is>
+          <t>Not stated in JD</t>
+        </is>
+      </c>
+      <c r="K144" s="2" t="inlineStr">
+        <is>
+          <t>From previous run</t>
+        </is>
+      </c>
+      <c r="L144" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="M144" s="6" t="inlineStr">
+        <is>
+          <t>https://dk.linkedin.com/jobs/view/bi-specialist-turn-healthcare-data-into-better-care-decisions-at-systematic-4449000390?position=13&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=C4YvYCcgfvLE1Lup1m630A%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="55" customHeight="1">
+      <c r="A145" s="2" t="n">
+        <v>144</v>
+      </c>
+      <c r="B145" s="3" t="inlineStr">
+        <is>
+          <t>Demand Planner (f/m/x)</t>
+        </is>
+      </c>
+      <c r="C145" s="3" t="inlineStr">
+        <is>
+          <t>HelloFresh</t>
+        </is>
+      </c>
+      <c r="D145" s="3" t="inlineStr">
+        <is>
+          <t>Copenhagen Municipality, Capital Region of Denmark, Denmark</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="F145" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="G145" s="9" t="inlineStr">
+        <is>
+          <t>Below threshold</t>
+        </is>
+      </c>
+      <c r="H145" s="3" t="inlineStr">
+        <is>
+          <t>This is a non-AI supply chain demand planning role focused on SQL, logistics, and forecasting metrics like MAPE, which is completely unrelated to the candidate's core GenAI, LLM, and agentic AI specialization.</t>
+        </is>
+      </c>
+      <c r="I145" s="3" t="inlineStr">
+        <is>
+          <t>Not stated in JD</t>
+        </is>
+      </c>
+      <c r="J145" s="3" t="inlineStr">
+        <is>
+          <t>Not stated in JD</t>
+        </is>
+      </c>
+      <c r="K145" s="2" t="inlineStr">
+        <is>
+          <t>From previous run</t>
+        </is>
+      </c>
+      <c r="L145" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="M145" s="6" t="inlineStr">
+        <is>
+          <t>https://dk.linkedin.com/jobs/view/demand-planner-f-m-x-at-hellofresh-4459625132?position=6&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=%2FDvrjQmxzWwgXh6GBB3pqA%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="55" customHeight="1">
+      <c r="A146" s="2" t="n">
+        <v>145</v>
+      </c>
+      <c r="B146" s="3" t="inlineStr">
+        <is>
+          <t>Senior Analyst - Market Intelligence (Trade &amp; Commodities)</t>
+        </is>
+      </c>
+      <c r="C146" s="3" t="inlineStr">
+        <is>
+          <t>Robert Walters</t>
+        </is>
+      </c>
+      <c r="D146" s="3" t="inlineStr">
+        <is>
+          <t>Abu Dhabi, Abu Dhabi Emirate, United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="F146" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="G146" s="9" t="inlineStr">
+        <is>
+          <t>Below threshold</t>
+        </is>
+      </c>
+      <c r="H146" s="3" t="inlineStr">
+        <is>
+          <t>This is a non-technical role focusing on market intelligence, trade flows, and supply chain analysis requiring Arabic fluency, which has no overlap with the candidate's core GenAI, LLMs, and agentic AI specialization.</t>
+        </is>
+      </c>
+      <c r="I146" s="3" t="inlineStr">
+        <is>
+          <t>Not stated in JD</t>
+        </is>
+      </c>
+      <c r="J146" s="3" t="inlineStr">
+        <is>
+          <t>Not stated in JD</t>
+        </is>
+      </c>
+      <c r="K146" s="2" t="inlineStr">
+        <is>
+          <t>From previous run</t>
+        </is>
+      </c>
+      <c r="L146" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="M146" s="6" t="inlineStr">
+        <is>
+          <t>https://ae.linkedin.com/jobs/view/senior-analyst-market-intelligence-trade-commodities-at-robert-walters-4457222382?position=30&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=JK2lIzdStMxW3Rb1o%2FxSgQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="55" customHeight="1">
+      <c r="A147" s="2" t="n">
+        <v>146</v>
+      </c>
+      <c r="B147" s="3" t="inlineStr">
+        <is>
+          <t>AI &amp; Data - BrightStar program - Part-Time For Students | UAE Nationals Only - Dubai</t>
+        </is>
+      </c>
+      <c r="C147" s="3" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="D147" s="3" t="inlineStr">
+        <is>
+          <t>Abu Dhabi, Abu Dhabi Emirate, United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="F147" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="G147" s="9" t="inlineStr">
+        <is>
+          <t>Below threshold</t>
+        </is>
+      </c>
+      <c r="H147" s="3" t="inlineStr">
+        <is>
+          <t>This is a student/internship program ('Part-Time For Students') restricted to UAE Nationals only, representing a severe seniority and eligibility mismatch for a Lead Data Scientist with 10 years of experience.</t>
+        </is>
+      </c>
+      <c r="I147" s="3" t="inlineStr">
+        <is>
+          <t>Not stated in JD</t>
+        </is>
+      </c>
+      <c r="J147" s="3" t="inlineStr">
+        <is>
+          <t>Not stated in JD</t>
+        </is>
+      </c>
+      <c r="K147" s="2" t="inlineStr">
+        <is>
+          <t>From previous run</t>
+        </is>
+      </c>
+      <c r="L147" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="M147" s="6" t="inlineStr">
+        <is>
+          <t>https://ae.linkedin.com/jobs/view/ai-data-brightstar-program-part-time-for-students-uae-nationals-only-dubai-at-deloitte-4459166169?position=29&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=eJo5yKx6Zm7GgBBf0abvaA%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="55" customHeight="1">
+      <c r="A148" s="2" t="n">
+        <v>147</v>
+      </c>
+      <c r="B148" s="3" t="inlineStr">
+        <is>
+          <t>SAS Analyst</t>
+        </is>
+      </c>
+      <c r="C148" s="3" t="inlineStr">
+        <is>
+          <t>One75mb HRM Pvt Ltd.</t>
+        </is>
+      </c>
+      <c r="D148" s="3" t="inlineStr">
+        <is>
+          <t>Abu Dhabi Emirate, United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="F148" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="G148" s="9" t="inlineStr">
+        <is>
+          <t>Below threshold</t>
+        </is>
+      </c>
+      <c r="H148" s="3" t="inlineStr">
+        <is>
+          <t>This role is a SAS Anti-Money Laundering (AML) Developer position focused on SAS Viya, SAS programming, and compliance systems. It has no connection to Generative AI, LLMs, RAG, or agentic systems, making it an entirely irrelevant fit for a GenAI specialist.</t>
+        </is>
+      </c>
+      <c r="I148" s="3" t="inlineStr">
+        <is>
+          <t>Not stated in JD</t>
+        </is>
+      </c>
+      <c r="J148" s="3" t="inlineStr">
+        <is>
+          <t>Not stated in JD</t>
+        </is>
+      </c>
+      <c r="K148" s="2" t="inlineStr">
+        <is>
+          <t>From previous run</t>
+        </is>
+      </c>
+      <c r="L148" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="M148" s="6" t="inlineStr">
+        <is>
+          <t>https://ae.linkedin.com/jobs/view/sas-analyst-at-one75mb-hrm-pvt-ltd-4459306494?position=19&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=NfyeO5P7KUMAsO5xQjjwEA%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="55" customHeight="1">
+      <c r="A149" s="2" t="n">
+        <v>148</v>
+      </c>
+      <c r="B149" s="3" t="inlineStr">
+        <is>
+          <t>Finance Information Systems Analyst</t>
+        </is>
+      </c>
+      <c r="C149" s="3" t="inlineStr">
+        <is>
+          <t>United Arab Emirates University, Department of Family Medicine</t>
+        </is>
+      </c>
+      <c r="D149" s="3" t="inlineStr">
+        <is>
+          <t>Abu Dhabi, Abu Dhabi Emirate, United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="F149" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="G149" s="9" t="inlineStr">
+        <is>
+          <t>Below threshold</t>
+        </is>
+      </c>
+      <c r="H149" s="3" t="inlineStr">
+        <is>
+          <t>This role is for a Finance Information Systems Analyst focusing on Oracle SQL, financial reporting, and system maintenance, which is completely unrelated to the candidate's core expertise in Generative AI, LLMs, and agentic workflows.</t>
+        </is>
+      </c>
+      <c r="I149" s="3" t="inlineStr">
+        <is>
+          <t>Not stated in JD</t>
+        </is>
+      </c>
+      <c r="J149" s="3" t="inlineStr">
+        <is>
+          <t>Not stated in JD</t>
+        </is>
+      </c>
+      <c r="K149" s="2" t="inlineStr">
+        <is>
+          <t>From previous run</t>
+        </is>
+      </c>
+      <c r="L149" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="M149" s="6" t="inlineStr">
+        <is>
+          <t>https://ae.linkedin.com/jobs/view/finance-information-systems-analyst-at-united-arab-emirates-university-department-of-family-medicine-4458309884?position=18&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=ZkLRAbbB1OpTP3DQTi%2FB4Q%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="55" customHeight="1">
+      <c r="A150" s="2" t="n">
+        <v>149</v>
+      </c>
+      <c r="B150" s="3" t="inlineStr">
+        <is>
+          <t>Analyst I - Advisory</t>
+        </is>
+      </c>
+      <c r="C150" s="3" t="inlineStr">
+        <is>
+          <t>Marsh Risk</t>
+        </is>
+      </c>
+      <c r="D150" s="3" t="inlineStr">
+        <is>
+          <t>Abu Dhabi, Abu Dhabi Emirate, United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="F150" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="G150" s="9" t="inlineStr">
+        <is>
+          <t>Below threshold</t>
+        </is>
+      </c>
+      <c r="H150" s="3" t="inlineStr">
+        <is>
+          <t>This is a graduate/entry-level risk engineering and data analyst role located in the UAE restricted to UAE Nationals, representing a severe mismatch in both seniority and specialization for a Lead Data Scientist with 10+ years of experience in GenAI.</t>
+        </is>
+      </c>
+      <c r="I150" s="3" t="inlineStr">
+        <is>
+          <t>Not stated in JD</t>
+        </is>
+      </c>
+      <c r="J150" s="3" t="inlineStr">
+        <is>
+          <t>Not stated in JD</t>
+        </is>
+      </c>
+      <c r="K150" s="2" t="inlineStr">
+        <is>
+          <t>From previous run</t>
+        </is>
+      </c>
+      <c r="L150" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="M150" s="6" t="inlineStr">
+        <is>
+          <t>https://ae.linkedin.com/jobs/view/analyst-i-advisory-at-marsh-risk-4459170127?position=6&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=hO0QLO%2FIAeXdRsG2PtQkTA%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="55" customHeight="1">
+      <c r="A151" s="2" t="n">
+        <v>150</v>
+      </c>
+      <c r="B151" s="3" t="inlineStr">
+        <is>
+          <t>Senior Economist / Economic Researcher</t>
+        </is>
+      </c>
+      <c r="C151" s="3" t="inlineStr">
+        <is>
+          <t>Robert Walters</t>
+        </is>
+      </c>
+      <c r="D151" s="3" t="inlineStr">
+        <is>
+          <t>Abu Dhabi, Abu Dhabi Emirate, United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="F151" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="G151" s="9" t="inlineStr">
+        <is>
+          <t>Below threshold</t>
+        </is>
+      </c>
+      <c r="H151" s="3" t="inlineStr">
+        <is>
+          <t>This role is for a Senior Economist focusing on macroeconomic research, policy analysis, and economic forecasting, which is completely unrelated to the candidate's specialization in Generative AI, LLMs, and data science.</t>
+        </is>
+      </c>
+      <c r="I151" s="3" t="inlineStr">
+        <is>
+          <t>Not stated in JD</t>
+        </is>
+      </c>
+      <c r="J151" s="3" t="inlineStr">
+        <is>
+          <t>Not stated in JD</t>
+        </is>
+      </c>
+      <c r="K151" s="2" t="inlineStr">
+        <is>
+          <t>From previous run</t>
+        </is>
+      </c>
+      <c r="L151" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="M151" s="6" t="inlineStr">
+        <is>
+          <t>https://ae.linkedin.com/jobs/view/senior-economist-economic-researcher-at-robert-walters-4457234594?position=21&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=hNkG3K%2BgFb1grR8QDMiBxA%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="55" customHeight="1">
+      <c r="A152" s="2" t="n">
+        <v>151</v>
+      </c>
+      <c r="B152" s="3" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="C152" s="3" t="inlineStr">
+        <is>
+          <t>ChipSoft Nederland</t>
+        </is>
+      </c>
+      <c r="D152" s="3" t="inlineStr">
+        <is>
+          <t>Amsterdam, North Holland, Netherlands</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="F152" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="G152" s="9" t="inlineStr">
+        <is>
+          <t>Below threshold</t>
+        </is>
+      </c>
+      <c r="H152" s="3" t="inlineStr">
+        <is>
+          <t>This is a Data Engineer role focused on ELT, SQL, data warehousing, and clickstream data, which is entirely unrelated to the candidate's core specialization in Generative AI, LLMs, and agentic systems.</t>
+        </is>
+      </c>
+      <c r="I152" s="3" t="inlineStr">
+        <is>
+          <t>Not stated in JD</t>
+        </is>
+      </c>
+      <c r="J152" s="3" t="inlineStr">
+        <is>
+          <t>Not stated in JD</t>
+        </is>
+      </c>
+      <c r="K152" s="2" t="inlineStr">
+        <is>
+          <t>From previous run</t>
+        </is>
+      </c>
+      <c r="L152" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="M152" s="6" t="inlineStr">
+        <is>
+          <t>https://nl.linkedin.com/jobs/view/data-engineer-at-chipsoft-nederland-4448895866?position=29&amp;pageNum=0&amp;refId=oiBIn1Czflg0JjZjH5z0Lg%3D%3D&amp;trackingId=CakhxR8nCpksAoEXyMZPHQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="55" customHeight="1">
+      <c r="A153" s="2" t="n">
+        <v>152</v>
+      </c>
+      <c r="B153" s="3" t="inlineStr">
+        <is>
+          <t>Quantitative Developer - Pricing Data</t>
+        </is>
+      </c>
+      <c r="C153" s="3" t="inlineStr">
+        <is>
+          <t>Optiver</t>
+        </is>
+      </c>
+      <c r="D153" s="3" t="inlineStr">
+        <is>
+          <t>Amsterdam, North Holland, Netherlands</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="F153" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="G153" s="9" t="inlineStr">
+        <is>
+          <t>Below threshold</t>
+        </is>
+      </c>
+      <c r="H153" s="3" t="inlineStr">
+        <is>
+          <t>This Quantitative Developer role focuses entirely on financial pricing data systems, market data pipelines, and low-latency/historical trading infrastructure in C++/Python, which is completely unrelated to the candidate's specialization in Generative AI, LLMs, and agentic workflows.</t>
+        </is>
+      </c>
+      <c r="I153" s="3" t="inlineStr">
+        <is>
+          <t>Not stated in JD</t>
+        </is>
+      </c>
+      <c r="J153" s="3" t="inlineStr">
+        <is>
+          <t>Yes - explicitly stated in JD</t>
+        </is>
+      </c>
+      <c r="K153" s="2" t="inlineStr">
+        <is>
+          <t>From previous run</t>
+        </is>
+      </c>
+      <c r="L153" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="M153" s="6" t="inlineStr">
+        <is>
+          <t>https://nl.linkedin.com/jobs/view/quantitative-developer-pricing-data-at-optiver-4437686371?position=21&amp;pageNum=0&amp;refId=oiBIn1Czflg0JjZjH5z0Lg%3D%3D&amp;trackingId=bm7u%2BG7QRNRgNoiTgqdkzg%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="154" ht="55" customHeight="1">
+      <c r="A154" s="2" t="n">
+        <v>153</v>
+      </c>
+      <c r="B154" s="3" t="inlineStr">
+        <is>
+          <t>Data Analyst — Operational Analysis (Python, Power BI, Modelling) for NATO with security clearance</t>
+        </is>
+      </c>
+      <c r="C154" s="3" t="inlineStr">
+        <is>
+          <t>WLG</t>
+        </is>
+      </c>
+      <c r="D154" s="3" t="inlineStr">
+        <is>
+          <t>The Hague, South Holland, Netherlands</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="F154" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="G154" s="9" t="inlineStr">
+        <is>
+          <t>Below threshold</t>
+        </is>
+      </c>
+      <c r="H154" s="3" t="inlineStr">
+        <is>
+          <t>This is an unrelated junior Data Analyst role focused on operational analysis, dashboards, and spreadsheets rather than Generative AI or advanced data science. Given the candidate's 10+ years of experience as a Lead Data Scientist specializing in LLMs and agentic AI, this position represents a severe mismatch in both domain and seniority.</t>
+        </is>
+      </c>
+      <c r="I154" s="3" t="inlineStr">
+        <is>
+          <t>Not stated in JD</t>
+        </is>
+      </c>
+      <c r="J154" s="3" t="inlineStr">
+        <is>
+          <t>Not stated in JD</t>
+        </is>
+      </c>
+      <c r="K154" s="2" t="inlineStr">
+        <is>
+          <t>From previous run</t>
+        </is>
+      </c>
+      <c r="L154" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="M154" s="6" t="inlineStr">
+        <is>
+          <t>https://nl.linkedin.com/jobs/view/data-analyst-%E2%80%94-operational-analysis-python-power-bi-modelling-for-nato-with-security-clearance-at-wlg-4458620413?position=26&amp;pageNum=0&amp;refId=oiBIn1Czflg0JjZjH5z0Lg%3D%3D&amp;trackingId=NK7DxxVQL3iwGI1saGNrZg%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" ht="55" customHeight="1">
+      <c r="A155" s="2" t="n">
+        <v>154</v>
+      </c>
+      <c r="B155" s="3" t="inlineStr">
+        <is>
+          <t>National Assistant Planner</t>
+        </is>
+      </c>
+      <c r="C155" s="3" t="inlineStr">
+        <is>
+          <t>Al-Futtaim</t>
+        </is>
+      </c>
+      <c r="D155" s="3" t="inlineStr">
+        <is>
+          <t>Dubai, Dubai, United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="F155" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G155" s="9" t="inlineStr">
+        <is>
+          <t>Below threshold</t>
+        </is>
+      </c>
+      <c r="H155" s="3" t="inlineStr">
+        <is>
+          <t>This is a non-technical retail merchandise planning role focused on financial forecasting, inventory management, and sales planning, which is entirely unrelated to the candidate's GenAI, LLM, and data science specialization.</t>
+        </is>
+      </c>
+      <c r="I155" s="3" t="inlineStr">
+        <is>
+          <t>Not stated in JD</t>
+        </is>
+      </c>
+      <c r="J155" s="3" t="inlineStr">
+        <is>
+          <t>Not stated in JD</t>
+        </is>
+      </c>
+      <c r="K155" s="2" t="inlineStr">
+        <is>
+          <t>From previous run</t>
+        </is>
+      </c>
+      <c r="L155" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="M155" s="6" t="inlineStr">
+        <is>
+          <t>https://ae.linkedin.com/jobs/view/national-assistant-planner-at-al-futtaim-4459335643?position=23&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=udE1OmanEOJo5NqnDVVmsw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="55" customHeight="1">
+      <c r="A156" s="2" t="n">
+        <v>155</v>
+      </c>
+      <c r="B156" s="3" t="inlineStr">
+        <is>
+          <t>Forward Deployed AI Integrator (UAE National Only), Field Engineering</t>
+        </is>
+      </c>
+      <c r="C156" s="3" t="inlineStr">
+        <is>
+          <t>Amazon Web Services (AWS)</t>
+        </is>
+      </c>
+      <c r="D156" s="3" t="inlineStr">
+        <is>
+          <t>Dubai, Dubai, United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="F156" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G156" s="9" t="inlineStr">
+        <is>
+          <t>Below threshold</t>
+        </is>
+      </c>
+      <c r="H156" s="3" t="inlineStr">
+        <is>
+          <t>Although the role involves AI tooling and Python, it is restricted to UAE Nationals only, making it impossible for the candidate to qualify. Additionally, the position leans heavily toward technical program management rather than hands-on Generative AI and LLM engineering.</t>
+        </is>
+      </c>
+      <c r="I156" s="3" t="inlineStr">
+        <is>
+          <t>Not stated in JD</t>
+        </is>
+      </c>
+      <c r="J156" s="3" t="inlineStr">
+        <is>
+          <t>Not stated in JD</t>
+        </is>
+      </c>
+      <c r="K156" s="2" t="inlineStr">
+        <is>
+          <t>From previous run</t>
+        </is>
+      </c>
+      <c r="L156" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="M156" s="6" t="inlineStr">
+        <is>
+          <t>https://ae.linkedin.com/jobs/view/forward-deployed-ai-integrator-uae-national-only-field-engineering-at-amazon-web-services-aws-4459616402?position=14&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=suYy8hgZkG37o3lG7FlDHQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="55" customHeight="1">
+      <c r="A157" s="2" t="n">
+        <v>156</v>
+      </c>
+      <c r="B157" s="3" t="inlineStr">
+        <is>
+          <t>GIS Specialist / Developer</t>
+        </is>
+      </c>
+      <c r="C157" s="3" t="inlineStr">
+        <is>
+          <t>AECOM</t>
+        </is>
+      </c>
+      <c r="D157" s="3" t="inlineStr">
+        <is>
+          <t>Dubai, Dubai, United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="F157" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G157" s="9" t="inlineStr">
+        <is>
+          <t>Below threshold</t>
+        </is>
+      </c>
+      <c r="H157" s="3" t="inlineStr">
+        <is>
+          <t>This is a GIS Specialist role focused on ArcGIS Enterprise administration, spatial analysis, and Python/ArcPy automation, which is completely unrelated to the candidate's core specialization in Generative AI, LLMs, and agentic systems.</t>
+        </is>
+      </c>
+      <c r="I157" s="3" t="inlineStr">
+        <is>
+          <t>Not stated in JD</t>
+        </is>
+      </c>
+      <c r="J157" s="3" t="inlineStr">
+        <is>
+          <t>Not stated in JD</t>
+        </is>
+      </c>
+      <c r="K157" s="2" t="inlineStr">
+        <is>
+          <t>From previous run</t>
+        </is>
+      </c>
+      <c r="L157" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="M157" s="6" t="inlineStr">
+        <is>
+          <t>https://ae.linkedin.com/jobs/view/gis-specialist-developer-at-aecom-4456869023?position=15&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=lGxG6%2FYECt2YwYGWf5hEZA%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" ht="55" customHeight="1">
+      <c r="A158" s="2" t="n">
+        <v>157</v>
+      </c>
+      <c r="B158" s="3" t="inlineStr">
+        <is>
+          <t>Quant Desk Lead and Portfolio Manager</t>
+        </is>
+      </c>
+      <c r="C158" s="3" t="inlineStr">
+        <is>
+          <t>EMCD</t>
+        </is>
+      </c>
+      <c r="D158" s="3" t="inlineStr">
+        <is>
+          <t>Dubai, Dubai, United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="F158" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G158" s="9" t="inlineStr">
+        <is>
+          <t>Below threshold</t>
+        </is>
+      </c>
+      <c r="H158" s="3" t="inlineStr">
+        <is>
+          <t>This is a finance and quantitative trading role focused on running a systematic trading desk, portfolio management, and P&amp;L ownership, which is entirely unrelated to the candidate's core specialization in Generative AI, LLMs, and agentic systems.</t>
+        </is>
+      </c>
+      <c r="I158" s="3" t="inlineStr">
+        <is>
+          <t>Not stated in JD</t>
+        </is>
+      </c>
+      <c r="J158" s="3" t="inlineStr">
+        <is>
+          <t>Not stated in JD</t>
+        </is>
+      </c>
+      <c r="K158" s="2" t="inlineStr">
+        <is>
+          <t>From previous run</t>
+        </is>
+      </c>
+      <c r="L158" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="M158" s="6" t="inlineStr">
+        <is>
+          <t>https://ae.linkedin.com/jobs/view/quant-desk-lead-and-portfolio-manager-at-emcd-4457949555?position=13&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=drHtrw6uBtEz5S2i%2BjBT5A%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="159" ht="55" customHeight="1">
+      <c r="A159" s="2" t="n">
+        <v>158</v>
+      </c>
+      <c r="B159" s="3" t="inlineStr">
+        <is>
+          <t>Join Norlys Energy Trading</t>
+        </is>
+      </c>
+      <c r="C159" s="3" t="inlineStr">
+        <is>
+          <t>Norlys Energy Trading A/S</t>
+        </is>
+      </c>
+      <c r="D159" s="3" t="inlineStr">
+        <is>
+          <t>Aalborg, North Denmark Region, Denmark</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="F159" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G159" s="9" t="inlineStr">
+        <is>
+          <t>Below threshold</t>
+        </is>
+      </c>
+      <c r="H159" s="3" t="inlineStr">
+        <is>
+          <t>This is an open, unsolicited job application for a general talent pool in energy trading, rather than a defined Data Science or Generative AI role. It completely lacks technical specifications, making it impossible to evaluate against the candidate's specialized GenAI and LLM expertise.</t>
+        </is>
+      </c>
+      <c r="I159" s="3" t="inlineStr">
+        <is>
+          <t>Not stated in JD</t>
+        </is>
+      </c>
+      <c r="J159" s="3" t="inlineStr">
+        <is>
+          <t>Not stated in JD</t>
+        </is>
+      </c>
+      <c r="K159" s="2" t="inlineStr">
+        <is>
+          <t>From previous run</t>
+        </is>
+      </c>
+      <c r="L159" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="M159" s="6" t="inlineStr">
+        <is>
+          <t>https://dk.linkedin.com/jobs/view/join-norlys-energy-trading-at-norlys-energy-trading-a-s-4459158084?position=26&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=Z%2BOuDrbPap3omWro18MA2g%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="160" ht="55" customHeight="1">
+      <c r="A160" s="2" t="n">
+        <v>159</v>
+      </c>
+      <c r="B160" s="3" t="inlineStr">
+        <is>
+          <t>PhD scholarship in Modeling and Control of Parkinson’s Disease - DTU Electro</t>
+        </is>
+      </c>
+      <c r="C160" s="3" t="inlineStr">
+        <is>
+          <t>DTU - Technical University of Denmark</t>
+        </is>
+      </c>
+      <c r="D160" s="3" t="inlineStr">
+        <is>
+          <t>Kongens Lyngby, Capital Region of Denmark, Denmark</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="F160" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G160" s="9" t="inlineStr">
+        <is>
+          <t>Below threshold</t>
+        </is>
+      </c>
+      <c r="H160" s="3" t="inlineStr">
+        <is>
+          <t>This is a PhD scholarship position in neuroengineering, control systems, and healthcare technology at DTU, which is completely unrelated to the candidate's specialization in Generative AI, LLMs, and agentic systems.</t>
+        </is>
+      </c>
+      <c r="I160" s="3" t="inlineStr">
+        <is>
+          <t>Not stated in JD</t>
+        </is>
+      </c>
+      <c r="J160" s="3" t="inlineStr">
+        <is>
+          <t>Possible - relocation support mentioned, visa not explicit</t>
+        </is>
+      </c>
+      <c r="K160" s="2" t="inlineStr">
+        <is>
+          <t>From previous run</t>
+        </is>
+      </c>
+      <c r="L160" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="M160" s="6" t="inlineStr">
+        <is>
+          <t>https://dk.linkedin.com/jobs/view/phd-scholarship-in-modeling-and-control-of-parkinson%E2%80%99s-disease-dtu-electro-at-dtu-technical-university-of-denmark-4459145557?position=20&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=mStwcLkWBAvzmreGSwO4Hw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="161" ht="55" customHeight="1">
+      <c r="A161" s="2" t="n">
+        <v>160</v>
+      </c>
+      <c r="B161" s="3" t="inlineStr">
+        <is>
+          <t>Analytikere med flair for databehandling til PET's kontraspionageindsats mod Rusland</t>
+        </is>
+      </c>
+      <c r="C161" s="3" t="inlineStr">
+        <is>
+          <t>Politi</t>
+        </is>
+      </c>
+      <c r="D161" s="3" t="inlineStr">
+        <is>
+          <t>Copenhagen, Capital Region of Denmark, Denmark</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="F161" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G161" s="9" t="inlineStr">
+        <is>
+          <t>Below threshold</t>
+        </is>
+      </c>
+      <c r="H161" s="3" t="inlineStr">
+        <is>
+          <t>This is a national security intelligence and counter-espionage analyst role at the Danish Security and Intelligence Service (PET), which is completely unrelated to data science, artificial intelligence, or the candidate's Generative AI and LLM specialization.</t>
+        </is>
+      </c>
+      <c r="I161" s="3" t="inlineStr">
+        <is>
+          <t>Not stated in JD</t>
+        </is>
+      </c>
+      <c r="J161" s="3" t="inlineStr">
+        <is>
+          <t>Not stated in JD</t>
+        </is>
+      </c>
+      <c r="K161" s="2" t="inlineStr">
+        <is>
+          <t>From previous run</t>
+        </is>
+      </c>
+      <c r="L161" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="M161" s="6" t="inlineStr">
+        <is>
+          <t>https://dk.linkedin.com/jobs/view/analytikere-med-flair-for-databehandling-til-pet-s-kontraspionageindsats-mod-rusland-at-politi-4457943820?position=18&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=%2FGEw4KOC0oARqkQIDTGJ4Q%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="162" ht="55" customHeight="1">
+      <c r="A162" s="2" t="n">
+        <v>161</v>
+      </c>
+      <c r="B162" s="3" t="inlineStr">
+        <is>
+          <t>PostDoc - Uncertainty-Aware Optimization in Inverse Problems for Next-Generation 3D Scanning</t>
+        </is>
+      </c>
+      <c r="C162" s="3" t="inlineStr">
+        <is>
+          <t>3Shape</t>
+        </is>
+      </c>
+      <c r="D162" s="3" t="inlineStr">
+        <is>
+          <t>Copenhagen, Capital Region of Denmark, Denmark</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="F162" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G162" s="9" t="inlineStr">
+        <is>
+          <t>Below threshold</t>
+        </is>
+      </c>
+      <c r="H162" s="3" t="inlineStr">
+        <is>
+          <t>This is a PostDoc position focused on mathematical optimization, numerical linear algebra, and uncertainty quantification for 3D scanning, which requires a PhD. It has no overlap with the candidate's specialization in GenAI, LLMs, and agentic systems.</t>
+        </is>
+      </c>
+      <c r="I162" s="3" t="inlineStr">
+        <is>
+          <t>Not stated in JD</t>
+        </is>
+      </c>
+      <c r="J162" s="3" t="inlineStr">
+        <is>
+          <t>Not stated in JD</t>
+        </is>
+      </c>
+      <c r="K162" s="2" t="inlineStr">
+        <is>
+          <t>From previous run</t>
+        </is>
+      </c>
+      <c r="L162" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="M162" s="6" t="inlineStr">
+        <is>
+          <t>https://dk.linkedin.com/jobs/view/postdoc-uncertainty-aware-optimization-in-inverse-problems-for-next-generation-3d-scanning-at-3shape-4459171806?position=15&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=bO0aSGZ%2FUAxThXN9yvOERg%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="163" ht="55" customHeight="1">
+      <c r="A163" s="2" t="n">
+        <v>162</v>
+      </c>
+      <c r="B163" s="3" t="inlineStr">
+        <is>
+          <t>Scientist, Quantitative Clinical Pharmacology (PK/PD Modeling &amp; Simulation)</t>
+        </is>
+      </c>
+      <c r="C163" s="3" t="inlineStr">
+        <is>
+          <t>Hemab Therapeutics</t>
+        </is>
+      </c>
+      <c r="D163" s="3" t="inlineStr">
+        <is>
+          <t>Copenhagen Metropolitan Area</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="F163" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G163" s="9" t="inlineStr">
+        <is>
+          <t>Below threshold</t>
+        </is>
+      </c>
+      <c r="H163" s="3" t="inlineStr">
+        <is>
+          <t>This is a highly specialized biomedical role focusing on Pharmacokinetics/Pharmacodynamics (PK/PD) modeling and clinical pharmacology, requiring a Ph.D. and experience with tools like NONMEM or Monolix. It has zero overlap with the candidate's GenAI, LLM, and data science background.</t>
+        </is>
+      </c>
+      <c r="I163" s="3" t="inlineStr">
+        <is>
+          <t>Not stated in JD</t>
+        </is>
+      </c>
+      <c r="J163" s="3" t="inlineStr">
+        <is>
+          <t>Not stated in JD</t>
+        </is>
+      </c>
+      <c r="K163" s="2" t="inlineStr">
+        <is>
+          <t>From previous run</t>
+        </is>
+      </c>
+      <c r="L163" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="M163" s="6" t="inlineStr">
+        <is>
+          <t>https://dk.linkedin.com/jobs/view/scientist-quantitative-clinical-pharmacology-pk-pd-modeling-simulation-at-hemab-therapeutics-4457218306?position=14&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=jhTyKvDAQ70R9PD5s0x2yA%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="164" ht="55" customHeight="1">
+      <c r="A164" s="2" t="n">
+        <v>163</v>
+      </c>
+      <c r="B164" s="3" t="inlineStr">
+        <is>
+          <t>Senior Payload Data Operator</t>
+        </is>
+      </c>
+      <c r="C164" s="3" t="inlineStr">
+        <is>
+          <t>FADA</t>
+        </is>
+      </c>
+      <c r="D164" s="3" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="F164" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G164" s="9" t="inlineStr">
+        <is>
+          <t>Below threshold</t>
+        </is>
+      </c>
+      <c r="H164" s="3" t="inlineStr">
+        <is>
+          <t>This is a satellite payload data engineering role focused on aerospace, remote sensing, and image processing (EO/SAR), which is completely unrelated to the candidate's specialization in GenAI, LLMs, and agentic systems.</t>
+        </is>
+      </c>
+      <c r="I164" s="3" t="inlineStr">
+        <is>
+          <t>Not stated in JD</t>
+        </is>
+      </c>
+      <c r="J164" s="3" t="inlineStr">
+        <is>
+          <t>Not stated in JD</t>
+        </is>
+      </c>
+      <c r="K164" s="2" t="inlineStr">
+        <is>
+          <t>From previous run</t>
+        </is>
+      </c>
+      <c r="L164" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="M164" s="6" t="inlineStr">
+        <is>
+          <t>https://ae.linkedin.com/jobs/view/senior-payload-data-operator-at-fada-4448986926?position=20&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=xdfP2za0I45WGIW%2FRJb%2BgA%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="165" ht="55" customHeight="1">
+      <c r="A165" s="2" t="n">
+        <v>164</v>
+      </c>
+      <c r="B165" s="3" t="inlineStr">
+        <is>
+          <t>Arabic Speech And Natural Language Processing Specialist</t>
+        </is>
+      </c>
+      <c r="C165" s="3" t="inlineStr">
+        <is>
+          <t>Birbal AI</t>
+        </is>
+      </c>
+      <c r="D165" s="3" t="inlineStr">
+        <is>
+          <t>Abu Dhabi Emirate, United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="F165" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G165" s="9" t="inlineStr">
+        <is>
+          <t>Below threshold</t>
+        </is>
+      </c>
+      <c r="H165" s="3" t="inlineStr">
+        <is>
+          <t>The role requires specialized expertise in Arabic speech technology (ASR, TTS, audio DSP) and native command of Gulf Arabic dialects, which does not match the candidate's core background in GenAI, LLMs, and RAG for English-language banking and HR use cases.</t>
+        </is>
+      </c>
+      <c r="I165" s="3" t="inlineStr">
+        <is>
+          <t>Not stated in JD</t>
+        </is>
+      </c>
+      <c r="J165" s="3" t="inlineStr">
+        <is>
+          <t>Not stated in JD</t>
+        </is>
+      </c>
+      <c r="K165" s="2" t="inlineStr">
+        <is>
+          <t>From previous run</t>
+        </is>
+      </c>
+      <c r="L165" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="M165" s="6" t="inlineStr">
+        <is>
+          <t>https://ae.linkedin.com/jobs/view/arabic-speech-and-natural-language-processing-specialist-at-birbal-ai-4457738899?position=14&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=ztG06Ly%2FIZ3fxm%2Fhvl626A%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="166" ht="55" customHeight="1">
+      <c r="A166" s="2" t="n">
+        <v>165</v>
+      </c>
+      <c r="B166" s="3" t="inlineStr">
+        <is>
           <t>Member of Technical Staff - Medical Research (Remote)</t>
         </is>
       </c>
-      <c r="C139" s="3" t="inlineStr">
+      <c r="C166" s="3" t="inlineStr">
         <is>
           <t>Hire Feed</t>
         </is>
       </c>
-      <c r="D139" s="3" t="inlineStr">
+      <c r="D166" s="3" t="inlineStr">
         <is>
           <t>United Arab Emirates</t>
         </is>
       </c>
-      <c r="E139" s="2" t="inlineStr">
+      <c r="E166" s="2" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="F139" s="8" t="n">
+      <c r="F166" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="G139" s="9" t="inlineStr">
-        <is>
-          <t>Below threshold</t>
-        </is>
-      </c>
-      <c r="H139" s="3" t="inlineStr">
+      <c r="G166" s="9" t="inlineStr">
+        <is>
+          <t>Below threshold</t>
+        </is>
+      </c>
+      <c r="H166" s="3" t="inlineStr">
         <is>
           <t>This role is completely unrelated to the candidate's specialization in Generative AI, LLMs, and agentic workflows, focusing instead on medical imaging, computational biology, and clinical research requiring a PhD.</t>
         </is>
       </c>
-      <c r="I139" s="3" t="inlineStr">
-        <is>
-          <t>Not stated in JD</t>
-        </is>
-      </c>
-      <c r="J139" s="3" t="inlineStr">
-        <is>
-          <t>Not stated in JD</t>
-        </is>
-      </c>
-      <c r="K139" s="7" t="inlineStr">
-        <is>
-          <t>New this run (2026-08-27 06:43 UTC)</t>
-        </is>
-      </c>
-      <c r="L139" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="M139" s="6" t="inlineStr">
+      <c r="I166" s="3" t="inlineStr">
+        <is>
+          <t>Not stated in JD</t>
+        </is>
+      </c>
+      <c r="J166" s="3" t="inlineStr">
+        <is>
+          <t>Not stated in JD</t>
+        </is>
+      </c>
+      <c r="K166" s="2" t="inlineStr">
+        <is>
+          <t>From previous run</t>
+        </is>
+      </c>
+      <c r="L166" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="M166" s="6" t="inlineStr">
         <is>
           <t>https://ae.linkedin.com/jobs/view/member-of-technical-staff-medical-research-remote-at-hire-feed-4459638503?position=3&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=b91zxKPZNgdFnMmW%2FlYbHA%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="167" ht="55" customHeight="1">
+      <c r="A167" s="2" t="n">
+        <v>166</v>
+      </c>
+      <c r="B167" s="3" t="inlineStr">
+        <is>
+          <t>AI Image Specialist</t>
+        </is>
+      </c>
+      <c r="C167" s="3" t="inlineStr">
+        <is>
+          <t>Puffy</t>
+        </is>
+      </c>
+      <c r="D167" s="3" t="inlineStr">
+        <is>
+          <t>Dubai, United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="F167" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G167" s="9" t="inlineStr">
+        <is>
+          <t>Below threshold</t>
+        </is>
+      </c>
+      <c r="H167" s="3" t="inlineStr">
+        <is>
+          <t>This is an AI Image Specialist role focused on generative visual design and creative production (Midjourney, DALL-E, image synthesis), which is completely unrelated to the candidate's core specialization in LLMs, RAG, LangChain, and agentic AI pipelines for data science and enterprise applications.</t>
+        </is>
+      </c>
+      <c r="I167" s="3" t="inlineStr">
+        <is>
+          <t>Not stated in JD</t>
+        </is>
+      </c>
+      <c r="J167" s="3" t="inlineStr">
+        <is>
+          <t>Yes - explicitly stated in JD</t>
+        </is>
+      </c>
+      <c r="K167" s="7" t="inlineStr">
+        <is>
+          <t>New this run (2026-08-27 15:40 UTC)</t>
+        </is>
+      </c>
+      <c r="L167" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="M167" s="6" t="inlineStr">
+        <is>
+          <t>https://ae.linkedin.com/jobs/view/ai-image-specialist-at-puffy-4457756193?position=10&amp;pageNum=0&amp;refId=50H6yCrEXIuhgr6eqEojNg%3D%3D&amp;trackingId=9EIvgvUNu%2BE37717JffiJA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -9418,6 +11182,34 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M137" r:id="rId136"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M138" r:id="rId137"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M167" r:id="rId166"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/job_matches.xlsx
+++ b/data/job_matches.xlsx
@@ -68,14 +68,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-        <bgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00FFC7CE"/>
+        <bgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-        <bgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -125,10 +125,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -499,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M167"/>
+  <dimension ref="A1:M173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1765,9 +1765,9 @@
           <t>Not stated in JD</t>
         </is>
       </c>
-      <c r="K20" s="7" t="inlineStr">
-        <is>
-          <t>New this run (2026-08-27 15:40 UTC)</t>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>From previous run</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -1805,10 +1805,10 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F21" s="8" t="n">
+      <c r="F21" s="7" t="n">
         <v>68</v>
       </c>
-      <c r="G21" s="9" t="inlineStr">
+      <c r="G21" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -1868,10 +1868,10 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F22" s="8" t="n">
+      <c r="F22" s="7" t="n">
         <v>68</v>
       </c>
-      <c r="G22" s="9" t="inlineStr">
+      <c r="G22" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -1931,10 +1931,10 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F23" s="8" t="n">
+      <c r="F23" s="7" t="n">
         <v>68</v>
       </c>
-      <c r="G23" s="9" t="inlineStr">
+      <c r="G23" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -1994,10 +1994,10 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F24" s="8" t="n">
+      <c r="F24" s="7" t="n">
         <v>68</v>
       </c>
-      <c r="G24" s="9" t="inlineStr">
+      <c r="G24" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -2057,10 +2057,10 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="F25" s="8" t="n">
+      <c r="F25" s="7" t="n">
         <v>68</v>
       </c>
-      <c r="G25" s="9" t="inlineStr">
+      <c r="G25" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -2120,10 +2120,10 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="F26" s="8" t="n">
+      <c r="F26" s="7" t="n">
         <v>68</v>
       </c>
-      <c r="G26" s="9" t="inlineStr">
+      <c r="G26" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -2183,10 +2183,10 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="F27" s="8" t="n">
+      <c r="F27" s="7" t="n">
         <v>68</v>
       </c>
-      <c r="G27" s="9" t="inlineStr">
+      <c r="G27" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -2246,10 +2246,10 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="F28" s="8" t="n">
+      <c r="F28" s="7" t="n">
         <v>68</v>
       </c>
-      <c r="G28" s="9" t="inlineStr">
+      <c r="G28" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -2269,9 +2269,9 @@
           <t>Not stated in JD</t>
         </is>
       </c>
-      <c r="K28" s="7" t="inlineStr">
-        <is>
-          <t>New this run (2026-08-27 15:40 UTC)</t>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>From previous run</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
@@ -2309,10 +2309,10 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="F29" s="8" t="n">
+      <c r="F29" s="7" t="n">
         <v>68</v>
       </c>
-      <c r="G29" s="9" t="inlineStr">
+      <c r="G29" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -2332,9 +2332,9 @@
           <t>Not stated in JD</t>
         </is>
       </c>
-      <c r="K29" s="7" t="inlineStr">
-        <is>
-          <t>New this run (2026-08-27 15:40 UTC)</t>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>From previous run</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
@@ -2372,10 +2372,10 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F30" s="8" t="n">
+      <c r="F30" s="7" t="n">
         <v>65</v>
       </c>
-      <c r="G30" s="9" t="inlineStr">
+      <c r="G30" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -2435,10 +2435,10 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F31" s="8" t="n">
+      <c r="F31" s="7" t="n">
         <v>65</v>
       </c>
-      <c r="G31" s="9" t="inlineStr">
+      <c r="G31" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -2498,10 +2498,10 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="F32" s="8" t="n">
+      <c r="F32" s="7" t="n">
         <v>65</v>
       </c>
-      <c r="G32" s="9" t="inlineStr">
+      <c r="G32" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -2543,35 +2543,35 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer, Agents</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>Acrisure Netherlands</t>
+          <t>FELICIS</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>Alkmaar, North Holland, Netherlands</t>
+          <t>New Shwaib, Abu Dhabi Emirate, United Arab Emirates</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="F33" s="8" t="n">
-        <v>60</v>
-      </c>
-      <c r="G33" s="9" t="inlineStr">
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="n">
+        <v>65</v>
+      </c>
+      <c r="G33" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>The role involves building LLM solutions, AI agents, and RAG architectures alongside data engineering tasks, aligning well with the candidate's core GenAI and Python specialization. However, the position is primarily titled Data Engineer with a required 3-5 years of experience, representing a slight seniority and role-definition mismatch for a Lead Data Scientist with 10+ years of experience.</t>
+          <t>The candidate has strong direct experience with the core agentic and LLM stack required, including Python, LangChain, LangGraph, and LangSmith. However, the role leans more toward a hybrid software engineering and infrastructure focus (FastAPI, backend services, orchestration) rather than a pure data science or applied ML role, presenting a slight scope and background misalignment.</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>Not stated in JD</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>From previous run</t>
+          <t>Possible - relocation support mentioned, visa not explicit</t>
+        </is>
+      </c>
+      <c r="K33" s="9" t="inlineStr">
+        <is>
+          <t>New this run (2026-08-28 08:27 UTC)</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="M33" s="6" t="inlineStr">
         <is>
-          <t>https://nl.linkedin.com/jobs/view/data-engineer-at-acrisure-netherlands-4435689555?position=20&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=LJAUvNH2xtcog%2BwAhWKWEA%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/software-engineer-agents-at-felicis-4460310034?position=4&amp;pageNum=0&amp;refId=zJBbvwb5H0wsbJ5fs9ZTVw%3D%3D&amp;trackingId=gFjj6vRINEEOLx6sclcqng%3D%3D</t>
         </is>
       </c>
     </row>
@@ -2606,17 +2606,17 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Senior AI Engineer – AI Centre of Excellence</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>Saxo Bank</t>
+          <t>Acrisure Netherlands</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>Copenhagen, Capital Region of Denmark, Denmark</t>
+          <t>Alkmaar, North Holland, Netherlands</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -2624,17 +2624,17 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F34" s="8" t="n">
+      <c r="F34" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="G34" s="9" t="inlineStr">
+      <c r="G34" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>The candidate has strong direct experience with production LLM/agent work, RAG, and Azure OpenAI within financial services, perfectly matching the domain and core GenAI requirements. However, the role heavily emphasizes C#/.NET enterprise development and Microsoft Copilot Studio/Power Platform integrations, which are outside the candidate's primary Python-centric stack, creating a notable tech-stack mismatch.</t>
+          <t>The role involves building LLM solutions, AI agents, and RAG architectures alongside data engineering tasks, aligning well with the candidate's core GenAI and Python specialization. However, the position is primarily titled Data Engineer with a required 3-5 years of experience, representing a slight seniority and role-definition mismatch for a Lead Data Scientist with 10+ years of experience.</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="M34" s="6" t="inlineStr">
         <is>
-          <t>https://dk.linkedin.com/jobs/view/senior-ai-engineer-%E2%80%93-ai-centre-of-excellence-at-saxo-bank-4423203071?position=19&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=oK4IPYd2VWkgx4cBmked5A%3D%3D</t>
+          <t>https://nl.linkedin.com/jobs/view/data-engineer-at-acrisure-netherlands-4435689555?position=20&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=LJAUvNH2xtcog%2BwAhWKWEA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -2669,35 +2669,35 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Lead AI Engineer (PhD)</t>
+          <t>Senior AI Engineer – AI Centre of Excellence</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>Talent Seed</t>
+          <t>Saxo Bank</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>Dubai, Dubai, United Arab Emirates</t>
+          <t>Copenhagen, Capital Region of Denmark, Denmark</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="F35" s="8" t="n">
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="G35" s="9" t="inlineStr">
+      <c r="G35" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>The candidate matches the 8+ years of experience, fintech domain background, and hands-on GenAI/ML engineering skill set. However, the role strictly requires a PhD or strong academic research background, which the candidate lacks (holding a B.Tech and MBA instead), creating a notable profile mismatch.</t>
+          <t>The candidate has strong direct experience with production LLM/agent work, RAG, and Azure OpenAI within financial services, perfectly matching the domain and core GenAI requirements. However, the role heavily emphasizes C#/.NET enterprise development and Microsoft Copilot Studio/Power Platform integrations, which are outside the candidate's primary Python-centric stack, creating a notable tech-stack mismatch.</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
@@ -2710,9 +2710,9 @@
           <t>Not stated in JD</t>
         </is>
       </c>
-      <c r="K35" s="7" t="inlineStr">
-        <is>
-          <t>New this run (2026-08-27 15:40 UTC)</t>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>From previous run</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
@@ -2722,7 +2722,7 @@
       </c>
       <c r="M35" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/lead-ai-engineer-phd-at-talent-seed-4457749740?position=2&amp;pageNum=0&amp;refId=50H6yCrEXIuhgr6eqEojNg%3D%3D&amp;trackingId=EZ22EvZ4LnqSKMhMS5nk8Q%3D%3D</t>
+          <t>https://dk.linkedin.com/jobs/view/senior-ai-engineer-%E2%80%93-ai-centre-of-excellence-at-saxo-bank-4423203071?position=19&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=oK4IPYd2VWkgx4cBmked5A%3D%3D</t>
         </is>
       </c>
     </row>
@@ -2732,40 +2732,40 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Consultant Business &amp; AI Insights (m/w/d) in Stuttgart</t>
+          <t>Lead AI Engineer (PhD)</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Talent Seed</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>Stuttgart, Baden-Württemberg, Germany</t>
+          <t>Dubai, Dubai, United Arab Emirates</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="F36" s="8" t="n">
-        <v>45</v>
-      </c>
-      <c r="G36" s="9" t="inlineStr">
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="F36" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="G36" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>The role is a junior-to-mid level consulting position ("Consultant") focusing broadly on BI, data analytics, and general AI, which is a significant seniority mismatch for a Lead Data Scientist with 10+ years of experience. While it mentions GenAI and RAG frameworks as nice-to-haves, the day-to-day work is heavily weighted toward general analytics consulting rather than advanced agentic AI specialization.</t>
+          <t>The candidate matches the 8+ years of experience, fintech domain background, and hands-on GenAI/ML engineering skill set. However, the role strictly requires a PhD or strong academic research background, which the candidate lacks (holding a B.Tech and MBA instead), creating a notable profile mismatch.</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>Yes - fluent/C1+ German explicitly required</t>
+          <t>Not stated in JD</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
@@ -2785,7 +2785,7 @@
       </c>
       <c r="M36" s="6" t="inlineStr">
         <is>
-          <t>https://de.linkedin.com/jobs/view/consultant-business-ai-insights-m-w-d-in-stuttgart-at-deloitte-4440569165?position=20&amp;pageNum=0&amp;refId=T%2F0KkBXL%2Fl%2B5Iv5tUGTY7Q%3D%3D&amp;trackingId=WIf1oxbjDsUKKiZvxr62ig%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/lead-ai-engineer-phd-at-talent-seed-4457749740?position=2&amp;pageNum=0&amp;refId=50H6yCrEXIuhgr6eqEojNg%3D%3D&amp;trackingId=EZ22EvZ4LnqSKMhMS5nk8Q%3D%3D</t>
         </is>
       </c>
     </row>
@@ -2795,17 +2795,17 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Senior Manager - Martech</t>
+          <t>Consultant Business &amp; AI Insights (m/w/d) in Stuttgart</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>Astra Tech</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>Dubai, Dubai, United Arab Emirates</t>
+          <t>Stuttgart, Baden-Württemberg, Germany</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -2813,22 +2813,22 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F37" s="8" t="n">
+      <c r="F37" s="7" t="n">
         <v>45</v>
       </c>
-      <c r="G37" s="9" t="inlineStr">
+      <c r="G37" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>The role is a Senior Manager of Martech focusing on marketing tech stacks, CDPs, and CRM operations rather than a dedicated GenAI, LLM, or agentic AI engineering role, making the domain fit a weaker match. However, the candidate's 10+ years of experience aligns well with the 7-10+ years seniority requirement, and the position touches on predictive modeling and internal AI tooling.</t>
+          <t>The role is a junior-to-mid level consulting position ("Consultant") focusing broadly on BI, data analytics, and general AI, which is a significant seniority mismatch for a Lead Data Scientist with 10+ years of experience. While it mentions GenAI and RAG frameworks as nice-to-haves, the day-to-day work is heavily weighted toward general analytics consulting rather than advanced agentic AI specialization.</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>Not stated in JD</t>
+          <t>Yes - fluent/C1+ German explicitly required</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
@@ -2848,7 +2848,7 @@
       </c>
       <c r="M37" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/senior-manager-martech-at-astra-tech-4457903179?position=12&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=9UstVcnD5je41ZfhWPt1AQ%3D%3D</t>
+          <t>https://de.linkedin.com/jobs/view/consultant-business-ai-insights-m-w-d-in-stuttgart-at-deloitte-4440569165?position=20&amp;pageNum=0&amp;refId=T%2F0KkBXL%2Fl%2B5Iv5tUGTY7Q%3D%3D&amp;trackingId=WIf1oxbjDsUKKiZvxr62ig%3D%3D</t>
         </is>
       </c>
     </row>
@@ -2858,35 +2858,35 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Principal AI Engineer</t>
+          <t>Senior Manager - Martech</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>A.P. Moller - Maersk</t>
+          <t>Astra Tech</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>Copenhagen Metropolitan Area</t>
+          <t>Dubai, Dubai, United Arab Emirates</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="F38" s="8" t="n">
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="F38" s="7" t="n">
         <v>45</v>
       </c>
-      <c r="G38" s="9" t="inlineStr">
+      <c r="G38" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>The role strongly features agentic AI and multi-agent systems which align well with the candidate's core specialization, but it is a Principal-level technical leadership position requiring deep expertise in Operations Research, mathematical programming, and optimization solvers that exceed the candidate's profile.</t>
+          <t>The role is a Senior Manager of Martech focusing on marketing tech stacks, CDPs, and CRM operations rather than a dedicated GenAI, LLM, or agentic AI engineering role, making the domain fit a weaker match. However, the candidate's 10+ years of experience aligns well with the 7-10+ years seniority requirement, and the position touches on predictive modeling and internal AI tooling.</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="M38" s="6" t="inlineStr">
         <is>
-          <t>https://dk.linkedin.com/jobs/view/principal-ai-engineer-at-a-p-moller-maersk-4445976056?position=8&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=cXORh69SWuwKg77z4%2FjXOA%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/senior-manager-martech-at-astra-tech-4457903179?position=12&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=9UstVcnD5je41ZfhWPt1AQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -2921,35 +2921,35 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Principle AI Engineer</t>
+          <t>Principal AI Engineer</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>Analog</t>
+          <t>A.P. Moller - Maersk</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>Abu Dhabi, Abu Dhabi Emirate, United Arab Emirates</t>
+          <t>Copenhagen Metropolitan Area</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="F39" s="8" t="n">
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="n">
         <v>45</v>
       </c>
-      <c r="G39" s="9" t="inlineStr">
+      <c r="G39" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t>The role requires a Principal AI Engineer to lead responsible AI standards, model evaluation, and governance in high-stakes domains like defense, which aligns well with the candidate's technical breadth and domain background in finance. However, the seniority is a mismatch as the candidate is at a Lead level rather than Principal, and the location requirement (Abu Dhabi) does not align with the candidate's target region.</t>
+          <t>The role strongly features agentic AI and multi-agent systems which align well with the candidate's core specialization, but it is a Principal-level technical leadership position requiring deep expertise in Operations Research, mathematical programming, and optimization solvers that exceed the candidate's profile.</t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="M39" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/principle-ai-engineer-at-analog-4457965112?position=22&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=9BE6FaPZTeRRBQuVWNoE5A%3D%3D</t>
+          <t>https://dk.linkedin.com/jobs/view/principal-ai-engineer-at-a-p-moller-maersk-4445976056?position=8&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=cXORh69SWuwKg77z4%2FjXOA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -2984,12 +2984,12 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Research Engineer/Technician in the Division of Science (Computer Science) - Dr. Nizar Habash</t>
+          <t>Principle AI Engineer</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>New York University Abu Dhabi</t>
+          <t>Analog</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
@@ -3002,17 +3002,17 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F40" s="8" t="n">
+      <c r="F40" s="7" t="n">
         <v>45</v>
       </c>
-      <c r="G40" s="9" t="inlineStr">
+      <c r="G40" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>The role focuses heavily on academic and applied Natural Language Processing, computational linguistics, and research tool development at an academic lab (CAMeL Lab), which overlaps with the candidate's NLP background. However, it is an academic research engineering position rather than a commercial GenAI/LLM/agentic architecture role, and expects academic publication experience which is not the candidate's primary focus.</t>
+          <t>The role requires a Principal AI Engineer to lead responsible AI standards, model evaluation, and governance in high-stakes domains like defense, which aligns well with the candidate's technical breadth and domain background in finance. However, the seniority is a mismatch as the candidate is at a Lead level rather than Principal, and the location requirement (Abu Dhabi) does not align with the candidate's target region.</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
@@ -3022,7 +3022,7 @@
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>Possible - relocation support mentioned, visa not explicit</t>
+          <t>Not stated in JD</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -3037,7 +3037,7 @@
       </c>
       <c r="M40" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/research-engineer-technician-in-the-division-of-science-computer-science-dr-nizar-habash-at-new-york-university-abu-dhabi-4432261664?position=15&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=Eg%2BhyoQTsgcu3W8ar6ARQw%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/principle-ai-engineer-at-analog-4457965112?position=22&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=9BE6FaPZTeRRBQuVWNoE5A%3D%3D</t>
         </is>
       </c>
     </row>
@@ -3047,35 +3047,35 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Research Engineer/Technician in the Division of Science (Computer Science) - Dr. Nizar Habash</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>Rubicon Cloud Advisor</t>
+          <t>New York University Abu Dhabi</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>The Randstad, Netherlands</t>
+          <t>Abu Dhabi, Abu Dhabi Emirate, United Arab Emirates</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="F41" s="8" t="n">
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="F41" s="7" t="n">
         <v>45</v>
       </c>
-      <c r="G41" s="9" t="inlineStr">
+      <c r="G41" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t>The role involves Databricks, Python, and some GenAI/RAG components which align with the candidate's core stack, but it requires fluency in Dutch which the candidate does not have. Additionally, the seniority (3-4 years experience) is slightly below the candidate's 10-year profile, making this a weaker linguistic and seniority match.</t>
+          <t>The role focuses heavily on academic and applied Natural Language Processing, computational linguistics, and research tool development at an academic lab (CAMeL Lab), which overlaps with the candidate's NLP background. However, it is an academic research engineering position rather than a commercial GenAI/LLM/agentic architecture role, and expects academic publication experience which is not the candidate's primary focus.</t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
@@ -3085,7 +3085,7 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>Not stated in JD</t>
+          <t>Possible - relocation support mentioned, visa not explicit</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -3100,7 +3100,7 @@
       </c>
       <c r="M41" s="6" t="inlineStr">
         <is>
-          <t>https://nl.linkedin.com/jobs/view/data-scientist-at-rubicon-cloud-advisor-4449382178?position=2&amp;pageNum=0&amp;refId=oiBIn1Czflg0JjZjH5z0Lg%3D%3D&amp;trackingId=rpvzZo3yE9tXsukpo3UKWQ%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/research-engineer-technician-in-the-division-of-science-computer-science-dr-nizar-habash-at-new-york-university-abu-dhabi-4432261664?position=15&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=Eg%2BhyoQTsgcu3W8ar6ARQw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -3115,30 +3115,30 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>GFR Fund</t>
+          <t>Rubicon Cloud Advisor</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>Amsterdam, North Holland, Netherlands</t>
+          <t>The Randstad, Netherlands</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="F42" s="8" t="n">
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="F42" s="7" t="n">
         <v>45</v>
       </c>
-      <c r="G42" s="9" t="inlineStr">
+      <c r="G42" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>The role mentions exposure to modern AI methodologies like RAG and LLM-augmented models, which matches the candidate's core specialization, but it is primarily a classical ML and audience modeling data science role focused on high-volume data and entity resolution. Furthermore, there is a significant seniority mismatch as the candidate has 10 years of experience and a Lead title, whereas the posting is for a Junior Data Scientist with 2+ years of experience.</t>
+          <t>The role involves Databricks, Python, and some GenAI/RAG components which align with the candidate's core stack, but it requires fluency in Dutch which the candidate does not have. Additionally, the seniority (3-4 years experience) is slightly below the candidate's 10-year profile, making this a weaker linguistic and seniority match.</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="M42" s="6" t="inlineStr">
         <is>
-          <t>https://nl.linkedin.com/jobs/view/data-scientist-at-gfr-fund-4459322290?position=1&amp;pageNum=0&amp;refId=oiBIn1Czflg0JjZjH5z0Lg%3D%3D&amp;trackingId=tzZbdlNky9Fn%2BVWE2R%2FOFg%3D%3D</t>
+          <t>https://nl.linkedin.com/jobs/view/data-scientist-at-rubicon-cloud-advisor-4449382178?position=2&amp;pageNum=0&amp;refId=oiBIn1Czflg0JjZjH5z0Lg%3D%3D&amp;trackingId=rpvzZo3yE9tXsukpo3UKWQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -3173,17 +3173,17 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>AI Solution Lead</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>Royal Wagenborg</t>
+          <t>GFR Fund</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>Delfzijl, Groningen, Netherlands</t>
+          <t>Amsterdam, North Holland, Netherlands</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -3191,17 +3191,17 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F43" s="8" t="n">
-        <v>42</v>
-      </c>
-      <c r="G43" s="9" t="inlineStr">
+      <c r="F43" s="7" t="n">
+        <v>45</v>
+      </c>
+      <c r="G43" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t>The role explicitly highlights a use case for an AI search engine over documentation, aligning with the candidate's core RAG and Azure AI Search expertise. However, the position focuses heavily on classical ML, time-series analysis, IoT, and industrial/OT environments, which are only peripheral to the candidate's deep Generative AI and agentic specialization.</t>
+          <t>The role mentions exposure to modern AI methodologies like RAG and LLM-augmented models, which matches the candidate's core specialization, but it is primarily a classical ML and audience modeling data science role focused on high-volume data and entity resolution. Furthermore, there is a significant seniority mismatch as the candidate has 10 years of experience and a Lead title, whereas the posting is for a Junior Data Scientist with 2+ years of experience.</t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="M43" s="6" t="inlineStr">
         <is>
-          <t>https://nl.linkedin.com/jobs/view/ai-solution-lead-at-royal-wagenborg-4457954118?position=14&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=vxrN54FA7uiALBltM74joA%3D%3D</t>
+          <t>https://nl.linkedin.com/jobs/view/data-scientist-at-gfr-fund-4459322290?position=1&amp;pageNum=0&amp;refId=oiBIn1Czflg0JjZjH5z0Lg%3D%3D&amp;trackingId=tzZbdlNky9Fn%2BVWE2R%2FOFg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -3236,35 +3236,35 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Python Software Engineer -  AI team</t>
+          <t>AI Solution Lead</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>Channable</t>
+          <t>Royal Wagenborg</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>Utrecht, Utrecht, Netherlands</t>
+          <t>Delfzijl, Groningen, Netherlands</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="F44" s="8" t="n">
-        <v>40</v>
-      </c>
-      <c r="G44" s="9" t="inlineStr">
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="F44" s="7" t="n">
+        <v>42</v>
+      </c>
+      <c r="G44" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>This role is primarily a Python Software Engineer position focusing on data processing, backend web frameworks, and e-commerce infrastructure rather than advanced GenAI, LLMs, or agentic architectures. While the candidate has over 10 years of experience and strong GenAI expertise, the heavy emphasis on traditional software engineering infrastructure and lower seniority requirements makes this a weaker fit.</t>
+          <t>The role explicitly highlights a use case for an AI search engine over documentation, aligning with the candidate's core RAG and Azure AI Search expertise. However, the position focuses heavily on classical ML, time-series analysis, IoT, and industrial/OT environments, which are only peripheral to the candidate's deep Generative AI and agentic specialization.</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
@@ -3289,7 +3289,7 @@
       </c>
       <c r="M44" s="6" t="inlineStr">
         <is>
-          <t>https://nl.linkedin.com/jobs/view/python-software-engineer-ai-team-at-channable-4454702624?position=17&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=C0S4tD8hFUIyS0haOgnRyg%3D%3D</t>
+          <t>https://nl.linkedin.com/jobs/view/ai-solution-lead-at-royal-wagenborg-4457954118?position=14&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=vxrN54FA7uiALBltM74joA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -3299,35 +3299,35 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>Data engineer til Hvidvasksekretariatet - Danmarks finansielle efterretningsenhed</t>
+          <t>Python Software Engineer -  AI team</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>Politi</t>
+          <t>Channable</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>Copenhagen, Capital Region of Denmark, Denmark</t>
+          <t>Utrecht, Utrecht, Netherlands</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="F45" s="8" t="n">
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="F45" s="7" t="n">
         <v>40</v>
       </c>
-      <c r="G45" s="9" t="inlineStr">
+      <c r="G45" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>The role is primarily a Data Engineering position focused on ETL, databases, and financial crime analysis platforms, which only touches LLMs as a minor passing mention rather than centering on core GenAI/agentic specialization. However, the candidate's strong Python, SQL, and banking domain background provide some relevant foundational overlap.</t>
+          <t>This role is primarily a Python Software Engineer position focusing on data processing, backend web frameworks, and e-commerce infrastructure rather than advanced GenAI, LLMs, or agentic architectures. While the candidate has over 10 years of experience and strong GenAI expertise, the heavy emphasis on traditional software engineering infrastructure and lower seniority requirements makes this a weaker fit.</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
@@ -3352,7 +3352,7 @@
       </c>
       <c r="M45" s="6" t="inlineStr">
         <is>
-          <t>https://dk.linkedin.com/jobs/view/data-engineer-til-hvidvasksekretariatet-danmarks-finansielle-efterretningsenhed-at-politi-4457966663?position=10&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=YZMqDSG0b%2BEmx5Ptpd%2FXGw%3D%3D</t>
+          <t>https://nl.linkedin.com/jobs/view/python-software-engineer-ai-team-at-channable-4454702624?position=17&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=C0S4tD8hFUIyS0haOgnRyg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -3362,17 +3362,17 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Regulatory Compliance Manager</t>
+          <t>Data engineer til Hvidvasksekretariatet - Danmarks finansielle efterretningsenhed</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>Bybit</t>
+          <t>Politi</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>Abu Dhabi Emirate, United Arab Emirates</t>
+          <t>Copenhagen, Capital Region of Denmark, Denmark</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -3380,17 +3380,17 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F46" s="8" t="n">
+      <c r="F46" s="7" t="n">
         <v>40</v>
       </c>
-      <c r="G46" s="9" t="inlineStr">
+      <c r="G46" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>The role involves building AI-enabled compliance and RAG/LLM workflows, which moderately aligns with the candidate's core GenAI and vector search expertise. However, it requires a primary background in regulatory compliance and financial services law rather than data science, making it a weaker domain and seniority fit.</t>
+          <t>The role is primarily a Data Engineering position focused on ETL, databases, and financial crime analysis platforms, which only touches LLMs as a minor passing mention rather than centering on core GenAI/agentic specialization. However, the candidate's strong Python, SQL, and banking domain background provide some relevant foundational overlap.</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
@@ -3415,7 +3415,7 @@
       </c>
       <c r="M46" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/regulatory-compliance-manager-at-bybit-4449794088?position=25&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=jQJTq4KHiygix7eADF6Ovw%3D%3D</t>
+          <t>https://dk.linkedin.com/jobs/view/data-engineer-til-hvidvasksekretariatet-danmarks-finansielle-efterretningsenhed-at-politi-4457966663?position=10&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=YZMqDSG0b%2BEmx5Ptpd%2FXGw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -3425,35 +3425,35 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>Data-analist DevOps team Kapitaalmarkten</t>
+          <t>Regulatory Compliance Manager</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>Autoriteit Financiële Markten</t>
+          <t>Bybit</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>Amsterdam, North Holland, Netherlands</t>
+          <t>Abu Dhabi Emirate, United Arab Emirates</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="F47" s="8" t="n">
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="F47" s="7" t="n">
         <v>40</v>
       </c>
-      <c r="G47" s="9" t="inlineStr">
+      <c r="G47" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H47" s="3" t="inlineStr">
         <is>
-          <t>The role requires data analysis and mentions LLMs as a passing preference rather than a core focus, making it a weaker fit compared to dedicated GenAI-specialist positions. Additionally, the seniority expected (minimum 3 years) is slightly below the candidate's 10 years of experience, and the position is located in the Netherlands with Dutch regulatory context.</t>
+          <t>The role involves building AI-enabled compliance and RAG/LLM workflows, which moderately aligns with the candidate's core GenAI and vector search expertise. However, it requires a primary background in regulatory compliance and financial services law rather than data science, making it a weaker domain and seniority fit.</t>
         </is>
       </c>
       <c r="I47" s="3" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="M47" s="6" t="inlineStr">
         <is>
-          <t>https://nl.linkedin.com/jobs/view/data-analist-devops-team-kapitaalmarkten-at-autoriteit-financi%C3%ABle-markten-4446764564?position=20&amp;pageNum=0&amp;refId=oiBIn1Czflg0JjZjH5z0Lg%3D%3D&amp;trackingId=sRIfcLqjQQWvZalqlxOpog%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/regulatory-compliance-manager-at-bybit-4449794088?position=25&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=jQJTq4KHiygix7eADF6Ovw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -3488,17 +3488,17 @@
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Data Scientist - AI/ML (Remote)</t>
+          <t>Data-analist DevOps team Kapitaalmarkten</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>Quik Hire Staffing</t>
+          <t>Autoriteit Financiële Markten</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>Amsterdam, North Holland, Netherlands</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -3506,17 +3506,17 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="F48" s="8" t="n">
-        <v>38</v>
-      </c>
-      <c r="G48" s="9" t="inlineStr">
+      <c r="F48" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="G48" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>The role is a general classical machine learning and MLOps position focused on traditional classification, regression, and clustering tasks using scikit-learn or PyTorch, rather than leveraging the candidate's core specialization in GenAI, LLMs, LangChain, and agentic workflows. While the candidate's Python and Azure cloud background align well, the technical scope is a weaker fit.</t>
+          <t>The role requires data analysis and mentions LLMs as a passing preference rather than a core focus, making it a weaker fit compared to dedicated GenAI-specialist positions. Additionally, the seniority expected (minimum 3 years) is slightly below the candidate's 10 years of experience, and the position is located in the Netherlands with Dutch regulatory context.</t>
         </is>
       </c>
       <c r="I48" s="3" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="M48" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/data-scientist-ai-ml-remote-at-quik-hire-staffing-4459642594?position=9&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=5JzrtHYdDMeIkrN4Gn8eng%3D%3D</t>
+          <t>https://nl.linkedin.com/jobs/view/data-analist-devops-team-kapitaalmarkten-at-autoriteit-financi%C3%ABle-markten-4446764564?position=20&amp;pageNum=0&amp;refId=oiBIn1Czflg0JjZjH5z0Lg%3D%3D&amp;trackingId=sRIfcLqjQQWvZalqlxOpog%3D%3D</t>
         </is>
       </c>
     </row>
@@ -3551,7 +3551,7 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>Machine Learning (AI) Engineer (Hybrid)</t>
+          <t>Data Scientist - AI/ML (Remote)</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
@@ -3561,7 +3561,7 @@
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>United Arab Emirates</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -3569,17 +3569,17 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="F49" s="8" t="n">
-        <v>35</v>
-      </c>
-      <c r="G49" s="9" t="inlineStr">
+      <c r="F49" s="7" t="n">
+        <v>38</v>
+      </c>
+      <c r="G49" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H49" s="3" t="inlineStr">
         <is>
-          <t>The role focuses heavily on traditional deep learning frameworks (TensorFlow, PyTorch), MLOps, and model training rather than the candidate's core specialization in Generative AI, LLMs, and agentic workflows. However, it is still a technical AI/ML engineering position that aligns reasonably well in terms of experience level.</t>
+          <t>The role is a general classical machine learning and MLOps position focused on traditional classification, regression, and clustering tasks using scikit-learn or PyTorch, rather than leveraging the candidate's core specialization in GenAI, LLMs, LangChain, and agentic workflows. While the candidate's Python and Azure cloud background align well, the technical scope is a weaker fit.</t>
         </is>
       </c>
       <c r="I49" s="3" t="inlineStr">
@@ -3604,7 +3604,7 @@
       </c>
       <c r="M49" s="6" t="inlineStr">
         <is>
-          <t>https://de.linkedin.com/jobs/view/machine-learning-ai-engineer-hybrid-at-quik-hire-staffing-4459653741?position=27&amp;pageNum=0&amp;refId=T%2F0KkBXL%2Fl%2B5Iv5tUGTY7Q%3D%3D&amp;trackingId=xAvCgryMmzYLEKjSJh9cEw%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/data-scientist-ai-ml-remote-at-quik-hire-staffing-4459642594?position=9&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=5JzrtHYdDMeIkrN4Gn8eng%3D%3D</t>
         </is>
       </c>
     </row>
@@ -3614,35 +3614,35 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Senior Applied Scientist (All genders)</t>
+          <t>Machine Learning (AI) Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>Zalando</t>
+          <t>Quik Hire Staffing</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>Berlin, Berlin, Germany</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="F50" s="8" t="n">
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="F50" s="7" t="n">
         <v>35</v>
       </c>
-      <c r="G50" s="9" t="inlineStr">
+      <c r="G50" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t>This is a classical ML and causal inference role focused on marketing mix modeling, experimentation, and econometrics rather than the candidate's core specialization in Generative AI, LLMs, and agentic systems. However, the seniority level (Senior Applied Scientist with 5+ years experience) aligns reasonably well with the candidate's 10+ years of experience.</t>
+          <t>The role focuses heavily on traditional deep learning frameworks (TensorFlow, PyTorch), MLOps, and model training rather than the candidate's core specialization in Generative AI, LLMs, and agentic workflows. However, it is still a technical AI/ML engineering position that aligns reasonably well in terms of experience level.</t>
         </is>
       </c>
       <c r="I50" s="3" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>Possible - relocation support mentioned, visa not explicit</t>
+          <t>Not stated in JD</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -3667,7 +3667,7 @@
       </c>
       <c r="M50" s="6" t="inlineStr">
         <is>
-          <t>https://de.linkedin.com/jobs/view/senior-applied-scientist-all-genders-at-zalando-4457268030?position=29&amp;pageNum=0&amp;refId=T%2F0KkBXL%2Fl%2B5Iv5tUGTY7Q%3D%3D&amp;trackingId=uPBCURAa%2BhpqUjOtZt20sg%3D%3D</t>
+          <t>https://de.linkedin.com/jobs/view/machine-learning-ai-engineer-hybrid-at-quik-hire-staffing-4459653741?position=27&amp;pageNum=0&amp;refId=T%2F0KkBXL%2Fl%2B5Iv5tUGTY7Q%3D%3D&amp;trackingId=xAvCgryMmzYLEKjSJh9cEw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -3677,17 +3677,17 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>Consultant Business &amp; AI Insights (m/w/d) in München</t>
+          <t>Senior Applied Scientist (All genders)</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Zalando</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>Munich, Bavaria, Germany</t>
+          <t>Berlin, Berlin, Germany</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -3695,27 +3695,27 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F51" s="8" t="n">
+      <c r="F51" s="7" t="n">
         <v>35</v>
       </c>
-      <c r="G51" s="9" t="inlineStr">
+      <c r="G51" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H51" s="3" t="inlineStr">
         <is>
-          <t>The candidate has strong GenAI and MLOps specialization, but this Deloitte role is at the junior/consultant level requiring early-career experience, making it a severe seniority mismatch for a Lead Data Scientist with 10+ years of experience. Furthermore, the role focuses heavily on general BI, analytics engineering, and basic consulting rather than advanced agentic AI development.</t>
+          <t>This is a classical ML and causal inference role focused on marketing mix modeling, experimentation, and econometrics rather than the candidate's core specialization in Generative AI, LLMs, and agentic systems. However, the seniority level (Senior Applied Scientist with 5+ years experience) aligns reasonably well with the candidate's 10+ years of experience.</t>
         </is>
       </c>
       <c r="I51" s="3" t="inlineStr">
         <is>
-          <t>Yes - fluent/C1+ German explicitly required</t>
+          <t>Not stated in JD</t>
         </is>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t>Not stated in JD</t>
+          <t>Possible - relocation support mentioned, visa not explicit</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -3730,7 +3730,7 @@
       </c>
       <c r="M51" s="6" t="inlineStr">
         <is>
-          <t>https://de.linkedin.com/jobs/view/consultant-business-ai-insights-m-w-d-in-m%C3%BCnchen-at-deloitte-4440568216?position=21&amp;pageNum=0&amp;refId=T%2F0KkBXL%2Fl%2B5Iv5tUGTY7Q%3D%3D&amp;trackingId=%2BjmC%2BHZAc9MdN%2BCr7d%2BCiw%3D%3D</t>
+          <t>https://de.linkedin.com/jobs/view/senior-applied-scientist-all-genders-at-zalando-4457268030?position=29&amp;pageNum=0&amp;refId=T%2F0KkBXL%2Fl%2B5Iv5tUGTY7Q%3D%3D&amp;trackingId=uPBCURAa%2BhpqUjOtZt20sg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -3740,17 +3740,17 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>Senior Manager - Artificial Intelligence</t>
+          <t>Consultant Business &amp; AI Insights (m/w/d) in München</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>Hays</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>Dubai, United Arab Emirates</t>
+          <t>Munich, Bavaria, Germany</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -3758,22 +3758,22 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F52" s="8" t="n">
+      <c r="F52" s="7" t="n">
         <v>35</v>
       </c>
-      <c r="G52" s="9" t="inlineStr">
+      <c r="G52" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t>The role focuses heavily on AI governance, assurance, model evaluation, and risk management rather than hands-on GenAI application development or agentic workflows, which are the candidate's core strengths. Additionally, the Senior Manager title leans toward a managerial and compliance track compared to the candidate's hands-on Lead Data Scientist background.</t>
+          <t>The candidate has strong GenAI and MLOps specialization, but this Deloitte role is at the junior/consultant level requiring early-career experience, making it a severe seniority mismatch for a Lead Data Scientist with 10+ years of experience. Furthermore, the role focuses heavily on general BI, analytics engineering, and basic consulting rather than advanced agentic AI development.</t>
         </is>
       </c>
       <c r="I52" s="3" t="inlineStr">
         <is>
-          <t>Not stated in JD</t>
+          <t>Yes - fluent/C1+ German explicitly required</t>
         </is>
       </c>
       <c r="J52" s="3" t="inlineStr">
@@ -3793,7 +3793,7 @@
       </c>
       <c r="M52" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/senior-manager-artificial-intelligence-at-hays-4457227403?position=27&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=m8EGYWiqeCT0F9aowu0X7g%3D%3D</t>
+          <t>https://de.linkedin.com/jobs/view/consultant-business-ai-insights-m-w-d-in-m%C3%BCnchen-at-deloitte-4440568216?position=21&amp;pageNum=0&amp;refId=T%2F0KkBXL%2Fl%2B5Iv5tUGTY7Q%3D%3D&amp;trackingId=%2BjmC%2BHZAc9MdN%2BCr7d%2BCiw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -3803,17 +3803,17 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>AI GTM Consulting - Banking</t>
+          <t>Senior Manager - Artificial Intelligence</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>NTT DATA, Inc.</t>
+          <t>Hays</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>Dubai, Dubai, United Arab Emirates</t>
+          <t>Dubai, United Arab Emirates</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -3821,17 +3821,17 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F53" s="8" t="n">
+      <c r="F53" s="7" t="n">
         <v>35</v>
       </c>
-      <c r="G53" s="9" t="inlineStr">
+      <c r="G53" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H53" s="3" t="inlineStr">
         <is>
-          <t>The candidate has strong technical GenAI and LLM expertise, but this role is primarily a client-facing AI GTM consulting and pre-sales position focused on the Middle East banking sector rather than hands-on technical model development. Additionally, the candidate lacks the required regional Gulf consulting experience and heavy banking industry operating model background.</t>
+          <t>The role focuses heavily on AI governance, assurance, model evaluation, and risk management rather than hands-on GenAI application development or agentic workflows, which are the candidate's core strengths. Additionally, the Senior Manager title leans toward a managerial and compliance track compared to the candidate's hands-on Lead Data Scientist background.</t>
         </is>
       </c>
       <c r="I53" s="3" t="inlineStr">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="M53" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/ai-gtm-consulting-banking-at-ntt-data-inc-4446632891?position=28&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=KvV4cGbrQRe2y%2FdaiwjIeA%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/senior-manager-artificial-intelligence-at-hays-4457227403?position=27&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=m8EGYWiqeCT0F9aowu0X7g%3D%3D</t>
         </is>
       </c>
     </row>
@@ -3866,17 +3866,17 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>Senior Consultant - Financial Crime Prevention</t>
+          <t>AI GTM Consulting - Banking</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>Zanders</t>
+          <t>NTT DATA, Inc.</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>Utrecht, Utrecht, Netherlands</t>
+          <t>Dubai, Dubai, United Arab Emirates</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -3884,17 +3884,17 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F54" s="8" t="n">
+      <c r="F54" s="7" t="n">
         <v>35</v>
       </c>
-      <c r="G54" s="9" t="inlineStr">
+      <c r="G54" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H54" s="3" t="inlineStr">
         <is>
-          <t>The role is primarily a traditional quantitative financial crime and risk consulting position where GenAI and LLMs are only mentioned as a minor plus, making it a weak match for the candidate's core GenAI and agentic AI specialization despite matching his overall years of experience.</t>
+          <t>The candidate has strong technical GenAI and LLM expertise, but this role is primarily a client-facing AI GTM consulting and pre-sales position focused on the Middle East banking sector rather than hands-on technical model development. Additionally, the candidate lacks the required regional Gulf consulting experience and heavy banking industry operating model background.</t>
         </is>
       </c>
       <c r="I54" s="3" t="inlineStr">
@@ -3919,7 +3919,7 @@
       </c>
       <c r="M54" s="6" t="inlineStr">
         <is>
-          <t>https://nl.linkedin.com/jobs/view/senior-consultant-financial-crime-prevention-at-zanders-4457921059?position=27&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=Xn8L7cLgbmU3MmPJfLc4Jg%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/ai-gtm-consulting-banking-at-ntt-data-inc-4446632891?position=28&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=KvV4cGbrQRe2y%2FdaiwjIeA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -3939,7 +3939,7 @@
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>Amsterdam, North Holland, Netherlands</t>
+          <t>Utrecht, Utrecht, Netherlands</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -3947,17 +3947,17 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F55" s="8" t="n">
+      <c r="F55" s="7" t="n">
         <v>35</v>
       </c>
-      <c r="G55" s="9" t="inlineStr">
+      <c r="G55" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H55" s="3" t="inlineStr">
         <is>
-          <t>The role is primarily focused on quantitative risk advisory and financial crime prevention consulting with classical modeling and model validation, where NLP and LLM pipeline experience is only a minor plus rather than the core focus. Seniority-wise, the Senior Consultant position requires 2+ years of track record, which aligns with the candidate's experience, but the domain mismatch results in a lower score.</t>
+          <t>The role is primarily a traditional quantitative financial crime and risk consulting position where GenAI and LLMs are only mentioned as a minor plus, making it a weak match for the candidate's core GenAI and agentic AI specialization despite matching his overall years of experience.</t>
         </is>
       </c>
       <c r="I55" s="3" t="inlineStr">
@@ -3982,7 +3982,7 @@
       </c>
       <c r="M55" s="6" t="inlineStr">
         <is>
-          <t>https://nl.linkedin.com/jobs/view/senior-consultant-financial-crime-prevention-at-zanders-4457902287?position=25&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=JPzSeOLZttSxrJAgb7RtbQ%3D%3D</t>
+          <t>https://nl.linkedin.com/jobs/view/senior-consultant-financial-crime-prevention-at-zanders-4457921059?position=27&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=Xn8L7cLgbmU3MmPJfLc4Jg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -3992,17 +3992,17 @@
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>Lead Data Scientist</t>
+          <t>Senior Consultant - Financial Crime Prevention</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>AS Watson Benelux</t>
+          <t>Zanders</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>Renswoude, Utrecht, Netherlands</t>
+          <t>Amsterdam, North Holland, Netherlands</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -4010,17 +4010,17 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F56" s="8" t="n">
+      <c r="F56" s="7" t="n">
         <v>35</v>
       </c>
-      <c r="G56" s="9" t="inlineStr">
+      <c r="G56" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H56" s="3" t="inlineStr">
         <is>
-          <t>This Lead Data Scientist role focuses heavily on classical machine learning, forecasting, optimization, and traditional data science applications for retail (such as sales forecasting and promotional personalization), with no mention of Generative AI, LLMs, or agentic workflows. However, the candidate's 10+ years of experience and leadership background align well with the seniority requirements of the role.</t>
+          <t>The role is primarily focused on quantitative risk advisory and financial crime prevention consulting with classical modeling and model validation, where NLP and LLM pipeline experience is only a minor plus rather than the core focus. Seniority-wise, the Senior Consultant position requires 2+ years of track record, which aligns with the candidate's experience, but the domain mismatch results in a lower score.</t>
         </is>
       </c>
       <c r="I56" s="3" t="inlineStr">
@@ -4045,7 +4045,7 @@
       </c>
       <c r="M56" s="6" t="inlineStr">
         <is>
-          <t>https://nl.linkedin.com/jobs/view/lead-data-scientist-at-as-watson-benelux-4377637626?position=11&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=D%2Bd%2FEPbAvDXvjR5ZJgWEIQ%3D%3D</t>
+          <t>https://nl.linkedin.com/jobs/view/senior-consultant-financial-crime-prevention-at-zanders-4457902287?position=25&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=JPzSeOLZttSxrJAgb7RtbQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -4055,17 +4055,17 @@
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>Applied Data Scientist - Intelligent Document Processing</t>
+          <t>Lead Data Scientist</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>ABN AMRO Bank N.V.</t>
+          <t>AS Watson Benelux</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>Amersfoort, Utrecht, Netherlands</t>
+          <t>Renswoude, Utrecht, Netherlands</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -4073,17 +4073,17 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F57" s="8" t="n">
+      <c r="F57" s="7" t="n">
         <v>35</v>
       </c>
-      <c r="G57" s="9" t="inlineStr">
+      <c r="G57" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H57" s="3" t="inlineStr">
         <is>
-          <t>The role focuses on Intelligent Document Processing (IDP) and document classification using existing components rather than cutting-edge GenAI/LLM orchestration or agentic systems. Additionally, the position asks for 3-6 years of experience (whereas the candidate has 10+) and explicitly requires Dutch language proficiency, making it a weaker fit.</t>
+          <t>This Lead Data Scientist role focuses heavily on classical machine learning, forecasting, optimization, and traditional data science applications for retail (such as sales forecasting and promotional personalization), with no mention of Generative AI, LLMs, or agentic workflows. However, the candidate's 10+ years of experience and leadership background align well with the seniority requirements of the role.</t>
         </is>
       </c>
       <c r="I57" s="3" t="inlineStr">
@@ -4108,7 +4108,7 @@
       </c>
       <c r="M57" s="6" t="inlineStr">
         <is>
-          <t>https://nl.linkedin.com/jobs/view/applied-data-scientist-intelligent-document-processing-at-abn-amro-bank-n-v-4440507839?position=4&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=yeF1JJiNzo5kSVTx1eGVfw%3D%3D</t>
+          <t>https://nl.linkedin.com/jobs/view/lead-data-scientist-at-as-watson-benelux-4377637626?position=11&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=D%2Bd%2FEPbAvDXvjR5ZJgWEIQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -4118,17 +4118,17 @@
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Applied Data Scientist - Intelligent Document Processing</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>CIMSOLUTIONS</t>
+          <t>ABN AMRO Bank N.V.</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>North Brabant, Netherlands</t>
+          <t>Amersfoort, Utrecht, Netherlands</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -4136,17 +4136,17 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F58" s="8" t="n">
+      <c r="F58" s="7" t="n">
         <v>35</v>
       </c>
-      <c r="G58" s="9" t="inlineStr">
+      <c r="G58" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H58" s="3" t="inlineStr">
         <is>
-          <t>This role focuses on traditional data science, predictive analysis, and business intelligence without any mention of Generative AI, LLMs, or agentic frameworks. Additionally, the job explicitly requires excellent communication skills in both Dutch and English, which creates a mismatch as the candidate lacks Dutch fluency.</t>
+          <t>The role focuses on Intelligent Document Processing (IDP) and document classification using existing components rather than cutting-edge GenAI/LLM orchestration or agentic systems. Additionally, the position asks for 3-6 years of experience (whereas the candidate has 10+) and explicitly requires Dutch language proficiency, making it a weaker fit.</t>
         </is>
       </c>
       <c r="I58" s="3" t="inlineStr">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="M58" s="6" t="inlineStr">
         <is>
-          <t>https://nl.linkedin.com/jobs/view/data-scientist-at-cimsolutions-4457901406?position=2&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=b3VmH8PYtChkdpJv0VgUxA%3D%3D</t>
+          <t>https://nl.linkedin.com/jobs/view/applied-data-scientist-intelligent-document-processing-at-abn-amro-bank-n-v-4440507839?position=4&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=yeF1JJiNzo5kSVTx1eGVfw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -4181,17 +4181,17 @@
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>Data Scientist Kruidvat</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>AS Watson Benelux</t>
+          <t>CIMSOLUTIONS</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>Renswoude, Utrecht, Netherlands</t>
+          <t>North Brabant, Netherlands</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -4199,17 +4199,17 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F59" s="8" t="n">
+      <c r="F59" s="7" t="n">
         <v>35</v>
       </c>
-      <c r="G59" s="9" t="inlineStr">
+      <c r="G59" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H59" s="3" t="inlineStr">
         <is>
-          <t>This role focuses on classical data science applications like time-series forecasting, supply chain optimization, and predictive modeling for retail, lacking any mention of Generative AI, LLMs, or agentic systems which are the candidate's core specialization. Although the tech stack includes Databricks and Azure, the domain mismatch makes it a weak fit.</t>
+          <t>This role focuses on traditional data science, predictive analysis, and business intelligence without any mention of Generative AI, LLMs, or agentic frameworks. Additionally, the job explicitly requires excellent communication skills in both Dutch and English, which creates a mismatch as the candidate lacks Dutch fluency.</t>
         </is>
       </c>
       <c r="I59" s="3" t="inlineStr">
@@ -4234,7 +4234,7 @@
       </c>
       <c r="M59" s="6" t="inlineStr">
         <is>
-          <t>https://nl.linkedin.com/jobs/view/data-scientist-kruidvat-at-as-watson-benelux-4439964615?position=3&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=tWylwGWz364M%2B%2FotR1FLZg%3D%3D</t>
+          <t>https://nl.linkedin.com/jobs/view/data-scientist-at-cimsolutions-4457901406?position=2&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=b3VmH8PYtChkdpJv0VgUxA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -4244,17 +4244,17 @@
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Data Scientist Kruidvat</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>CIMSOLUTIONS</t>
+          <t>AS Watson Benelux</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>South Holland, Netherlands</t>
+          <t>Renswoude, Utrecht, Netherlands</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -4262,17 +4262,17 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F60" s="8" t="n">
+      <c r="F60" s="7" t="n">
         <v>35</v>
       </c>
-      <c r="G60" s="9" t="inlineStr">
+      <c r="G60" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H60" s="3" t="inlineStr">
         <is>
-          <t>This role focuses on traditional data science, predictive modeling, and business intelligence with standard ML libraries (TensorFlow, scikit-learn), lacking any focus on the candidate's core Generative AI, LLM, and agentic AI specialization. Additionally, the job explicitly requires excellent communication skills in both Dutch and English, which creates a significant language mismatch for the candidate.</t>
+          <t>This role focuses on classical data science applications like time-series forecasting, supply chain optimization, and predictive modeling for retail, lacking any mention of Generative AI, LLMs, or agentic systems which are the candidate's core specialization. Although the tech stack includes Databricks and Azure, the domain mismatch makes it a weak fit.</t>
         </is>
       </c>
       <c r="I60" s="3" t="inlineStr">
@@ -4297,7 +4297,7 @@
       </c>
       <c r="M60" s="6" t="inlineStr">
         <is>
-          <t>https://nl.linkedin.com/jobs/view/data-scientist-at-cimsolutions-4457917043?position=1&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=1JSHNn3m2jBGxvl6iC8lcw%3D%3D</t>
+          <t>https://nl.linkedin.com/jobs/view/data-scientist-kruidvat-at-as-watson-benelux-4439964615?position=3&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=tWylwGWz364M%2B%2FotR1FLZg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -4307,17 +4307,17 @@
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>AI Product Owner</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>Novo Nordisk</t>
+          <t>CIMSOLUTIONS</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>Ballerup Municipality, Capital Region of Denmark, Denmark</t>
+          <t>South Holland, Netherlands</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -4325,17 +4325,17 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F61" s="8" t="n">
+      <c r="F61" s="7" t="n">
         <v>35</v>
       </c>
-      <c r="G61" s="9" t="inlineStr">
+      <c r="G61" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H61" s="3" t="inlineStr">
         <is>
-          <t>This is an AI Product Owner role focused on manufacturing and supply chain systems, which requires product management and stakeholder alignment rather than hands-on GenAI/LLM development. The candidate is a technical Lead Data Scientist specializing in hands-on LangChain/LangGraph and agentic workflows, presenting a significant mismatch in role function and domain expertise.</t>
+          <t>This role focuses on traditional data science, predictive modeling, and business intelligence with standard ML libraries (TensorFlow, scikit-learn), lacking any focus on the candidate's core Generative AI, LLM, and agentic AI specialization. Additionally, the job explicitly requires excellent communication skills in both Dutch and English, which creates a significant language mismatch for the candidate.</t>
         </is>
       </c>
       <c r="I61" s="3" t="inlineStr">
@@ -4360,7 +4360,7 @@
       </c>
       <c r="M61" s="6" t="inlineStr">
         <is>
-          <t>https://dk.linkedin.com/jobs/view/ai-product-owner-at-novo-nordisk-4457258669?position=24&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=s56Z90FxaVSj7XKQs6qQuA%3D%3D</t>
+          <t>https://nl.linkedin.com/jobs/view/data-scientist-at-cimsolutions-4457917043?position=1&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=1JSHNn3m2jBGxvl6iC8lcw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -4370,17 +4370,17 @@
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>Forretningskonsulent</t>
+          <t>AI Product Owner</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>Bankdata</t>
+          <t>Novo Nordisk</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>Silkeborg, Central Denmark Region, Denmark</t>
+          <t>Ballerup Municipality, Capital Region of Denmark, Denmark</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -4388,17 +4388,17 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F62" s="8" t="n">
+      <c r="F62" s="7" t="n">
         <v>35</v>
       </c>
-      <c r="G62" s="9" t="inlineStr">
+      <c r="G62" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H62" s="3" t="inlineStr">
         <is>
-          <t>This is a business/risk consultant role focusing on regulatory compliance, credit risk models, and SAS/SQL data analysis rather than a hands-on Generative AI or LLM specialization. While the candidate brings strong banking domain experience and Python skills, the core responsibilities do not align with his advanced GenAI and agentic AI expertise.</t>
+          <t>This is an AI Product Owner role focused on manufacturing and supply chain systems, which requires product management and stakeholder alignment rather than hands-on GenAI/LLM development. The candidate is a technical Lead Data Scientist specializing in hands-on LangChain/LangGraph and agentic workflows, presenting a significant mismatch in role function and domain expertise.</t>
         </is>
       </c>
       <c r="I62" s="3" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="M62" s="6" t="inlineStr">
         <is>
-          <t>https://dk.linkedin.com/jobs/view/forretningskonsulent-at-bankdata-4448894922?position=22&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=o%2BWOTBX123ODc%2FiV7%2B9GIw%3D%3D</t>
+          <t>https://dk.linkedin.com/jobs/view/ai-product-owner-at-novo-nordisk-4457258669?position=24&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=s56Z90FxaVSj7XKQs6qQuA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -4433,17 +4433,17 @@
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>Developer</t>
+          <t>Forretningskonsulent</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>MAP</t>
+          <t>Bankdata</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>Copenhagen, Capital Region of Denmark, Denmark</t>
+          <t>Silkeborg, Central Denmark Region, Denmark</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -4451,17 +4451,17 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F63" s="8" t="n">
+      <c r="F63" s="7" t="n">
         <v>35</v>
       </c>
-      <c r="G63" s="9" t="inlineStr">
+      <c r="G63" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H63" s="3" t="inlineStr">
         <is>
-          <t>The role is primarily a backend/full-stack software engineering position requiring .NET/C# and Vue/TypeScript, which does not align with the candidate's core Data Science and GenAI specialization. While there are passing mentions of Python and agentic AI as nice-to-haves, the job is fundamentally a software development role rather than an advanced GenAI/LLM specialist position.</t>
+          <t>This is a business/risk consultant role focusing on regulatory compliance, credit risk models, and SAS/SQL data analysis rather than a hands-on Generative AI or LLM specialization. While the candidate brings strong banking domain experience and Python skills, the core responsibilities do not align with his advanced GenAI and agentic AI expertise.</t>
         </is>
       </c>
       <c r="I63" s="3" t="inlineStr">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="M63" s="6" t="inlineStr">
         <is>
-          <t>https://dk.linkedin.com/jobs/view/developer-at-map-4459176960?position=23&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=YgE2RztI4uaVgk5SXXlkQw%3D%3D</t>
+          <t>https://dk.linkedin.com/jobs/view/forretningskonsulent-at-bankdata-4448894922?position=22&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=o%2BWOTBX123ODc%2FiV7%2B9GIw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -4496,17 +4496,17 @@
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>AI Innovation Specialist - Renewable Energy Solutions</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>Vestas</t>
+          <t>MAP</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>Aarhus Municipality, Central Denmark Region, Denmark</t>
+          <t>Copenhagen, Capital Region of Denmark, Denmark</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -4514,17 +4514,17 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F64" s="8" t="n">
+      <c r="F64" s="7" t="n">
         <v>35</v>
       </c>
-      <c r="G64" s="9" t="inlineStr">
+      <c r="G64" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H64" s="3" t="inlineStr">
         <is>
-          <t>The candidate has strong technical skills in Python and machine learning, but this role focuses heavily on industrial AI, computer vision, sensor data, and predictive maintenance in the renewable energy sector rather than the candidate's core specialization in LLMs, RAG, and agentic workflows. Furthermore, the seniority alignment is slightly mismatched as the role asks for 4+ years while the candidate is a senior/lead with 10 years of experience.</t>
+          <t>The role is primarily a backend/full-stack software engineering position requiring .NET/C# and Vue/TypeScript, which does not align with the candidate's core Data Science and GenAI specialization. While there are passing mentions of Python and agentic AI as nice-to-haves, the job is fundamentally a software development role rather than an advanced GenAI/LLM specialist position.</t>
         </is>
       </c>
       <c r="I64" s="3" t="inlineStr">
@@ -4549,7 +4549,7 @@
       </c>
       <c r="M64" s="6" t="inlineStr">
         <is>
-          <t>https://dk.linkedin.com/jobs/view/ai-innovation-specialist-renewable-energy-solutions-at-vestas-4459358646?position=4&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=x6uemge6vMfQH6CFPei6kw%3D%3D</t>
+          <t>https://dk.linkedin.com/jobs/view/developer-at-map-4459176960?position=23&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=YgE2RztI4uaVgk5SXXlkQw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -4559,35 +4559,35 @@
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>Data Scientist (Remote)</t>
+          <t>AI Innovation Specialist - Renewable Energy Solutions</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>Hire Feed</t>
+          <t>Vestas</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>Aarhus Municipality, Central Denmark Region, Denmark</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="F65" s="8" t="n">
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="F65" s="7" t="n">
         <v>35</v>
       </c>
-      <c r="G65" s="9" t="inlineStr">
+      <c r="G65" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H65" s="3" t="inlineStr">
         <is>
-          <t>This role is a generic classical machine learning position focused on predictive modeling, Python, and scikit-learn, with no mention of Generative AI, LLMs, RAG, or agentic systems that form the core of the candidate's expertise. While the candidate has the necessary background to perform the work, it underutilizes his specialized GenAI skillset and matches the scoring guidance for a weaker classical ML/statistics fit.</t>
+          <t>The candidate has strong technical skills in Python and machine learning, but this role focuses heavily on industrial AI, computer vision, sensor data, and predictive maintenance in the renewable energy sector rather than the candidate's core specialization in LLMs, RAG, and agentic workflows. Furthermore, the seniority alignment is slightly mismatched as the role asks for 4+ years while the candidate is a senior/lead with 10 years of experience.</t>
         </is>
       </c>
       <c r="I65" s="3" t="inlineStr">
@@ -4612,7 +4612,7 @@
       </c>
       <c r="M65" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/data-scientist-remote-at-hire-feed-4459652348?position=8&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=eN2UeQevFS%2FiNl5F%2FHqH8A%3D%3D</t>
+          <t>https://dk.linkedin.com/jobs/view/ai-innovation-specialist-renewable-energy-solutions-at-vestas-4459358646?position=4&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=x6uemge6vMfQH6CFPei6kw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -4622,12 +4622,12 @@
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>Machine Learning (AI) Engineer (Hybrid)</t>
+          <t>Data Scientist (Remote)</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>Quik Hire Staffing</t>
+          <t>Hire Feed</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
@@ -4640,17 +4640,17 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="F66" s="8" t="n">
+      <c r="F66" s="7" t="n">
         <v>35</v>
       </c>
-      <c r="G66" s="9" t="inlineStr">
+      <c r="G66" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H66" s="3" t="inlineStr">
         <is>
-          <t>The role is focused heavily on classical Machine Learning, MLOps, deep learning frameworks (TensorFlow, PyTorch), and model training rather than the candidate's core specialization in Generative AI, LLMs, RAG, and agentic systems. Seniority aligns well, but the technical domain mismatch makes this a weaker fit.</t>
+          <t>This role is a generic classical machine learning position focused on predictive modeling, Python, and scikit-learn, with no mention of Generative AI, LLMs, RAG, or agentic systems that form the core of the candidate's expertise. While the candidate has the necessary background to perform the work, it underutilizes his specialized GenAI skillset and matches the scoring guidance for a weaker classical ML/statistics fit.</t>
         </is>
       </c>
       <c r="I66" s="3" t="inlineStr">
@@ -4675,7 +4675,7 @@
       </c>
       <c r="M66" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/machine-learning-ai-engineer-hybrid-at-quik-hire-staffing-4459649596?position=5&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=sbTD%2BYZZjPOfeagKS2Yixw%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/data-scientist-remote-at-hire-feed-4459652348?position=8&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=eN2UeQevFS%2FiNl5F%2FHqH8A%3D%3D</t>
         </is>
       </c>
     </row>
@@ -4685,17 +4685,17 @@
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>Consultant Data &amp; AI</t>
+          <t>Machine Learning (AI) Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>ITDS</t>
+          <t>Quik Hire Staffing</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>Amsterdam, North Holland, Netherlands</t>
+          <t>United Arab Emirates</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -4703,17 +4703,17 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="F67" s="8" t="n">
+      <c r="F67" s="7" t="n">
         <v>35</v>
       </c>
-      <c r="G67" s="9" t="inlineStr">
+      <c r="G67" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H67" s="3" t="inlineStr">
         <is>
-          <t>The role is a generalist data and AI consulting position focusing heavily on data management, business analysis, and governance within the financial sector, rather than a specialized GenAI/LLM engineering role. Additionally, it requires Dutch language proficiency and a consultant/analyst profile that is a mismatch for the candidate's senior GenAI technical expertise.</t>
+          <t>The role is focused heavily on classical Machine Learning, MLOps, deep learning frameworks (TensorFlow, PyTorch), and model training rather than the candidate's core specialization in Generative AI, LLMs, RAG, and agentic systems. Seniority aligns well, but the technical domain mismatch makes this a weaker fit.</t>
         </is>
       </c>
       <c r="I67" s="3" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="M67" s="6" t="inlineStr">
         <is>
-          <t>https://nl.linkedin.com/jobs/view/consultant-data-ai-at-itds-4458351898?position=19&amp;pageNum=0&amp;refId=oiBIn1Czflg0JjZjH5z0Lg%3D%3D&amp;trackingId=1Zr9TFJHo0JFjEQpwgyXZg%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/machine-learning-ai-engineer-hybrid-at-quik-hire-staffing-4459649596?position=5&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=sbTD%2BYZZjPOfeagKS2Yixw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -4748,17 +4748,17 @@
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Consultant Data &amp; AI</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>Rubicon Cloud Advisor</t>
+          <t>ITDS</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>The Randstad, Netherlands</t>
+          <t>Amsterdam, North Holland, Netherlands</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -4766,17 +4766,17 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="F68" s="8" t="n">
+      <c r="F68" s="7" t="n">
         <v>35</v>
       </c>
-      <c r="G68" s="9" t="inlineStr">
+      <c r="G68" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H68" s="3" t="inlineStr">
         <is>
-          <t>The role is for an MLOps Engineer focusing on ML infrastructure, pipelines, and deployment using Databricks and MLflow, which touches some of the candidate's supporting tech stack but misses his core Generative AI, LLM, and agentic specialization. Additionally, the job posting requires Dutch language proficiency, though language fit was not factored into the penalty per instructions.</t>
+          <t>The role is a generalist data and AI consulting position focusing heavily on data management, business analysis, and governance within the financial sector, rather than a specialized GenAI/LLM engineering role. Additionally, it requires Dutch language proficiency and a consultant/analyst profile that is a mismatch for the candidate's senior GenAI technical expertise.</t>
         </is>
       </c>
       <c r="I68" s="3" t="inlineStr">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="M68" s="6" t="inlineStr">
         <is>
-          <t>https://nl.linkedin.com/jobs/view/mlops-engineer-at-rubicon-cloud-advisor-4450093837?position=15&amp;pageNum=0&amp;refId=oiBIn1Czflg0JjZjH5z0Lg%3D%3D&amp;trackingId=bnH0HGZbT4T4t%2FkIxlYWZQ%3D%3D</t>
+          <t>https://nl.linkedin.com/jobs/view/consultant-data-ai-at-itds-4458351898?position=19&amp;pageNum=0&amp;refId=oiBIn1Czflg0JjZjH5z0Lg%3D%3D&amp;trackingId=1Zr9TFJHo0JFjEQpwgyXZg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -4811,40 +4811,40 @@
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>Decision Scientist, Marketing Modelling Intelligence, Marketing DSA</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>Vinted</t>
+          <t>Rubicon Cloud Advisor</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>Berlin, Berlin, Germany</t>
+          <t>The Randstad, Netherlands</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="F69" s="8" t="n">
-        <v>30</v>
-      </c>
-      <c r="G69" s="9" t="inlineStr">
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="F69" s="7" t="n">
+        <v>35</v>
+      </c>
+      <c r="G69" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H69" s="3" t="inlineStr">
         <is>
-          <t>This is a classical marketing analytics and econometrics role focused on Bayesian Media Mix Modeling and ROI measurement with no mention of Generative AI, LLMs, or agentic systems. Furthermore, the candidate is a Lead Data Scientist with 10+ years of experience, making the 2-4 year experience requirement a significant seniority mismatch.</t>
+          <t>The role is for an MLOps Engineer focusing on ML infrastructure, pipelines, and deployment using Databricks and MLflow, which touches some of the candidate's supporting tech stack but misses his core Generative AI, LLM, and agentic specialization. Additionally, the job posting requires Dutch language proficiency, though language fit was not factored into the penalty per instructions.</t>
         </is>
       </c>
       <c r="I69" s="3" t="inlineStr">
         <is>
-          <t>Yes - German required (see JD for exact level)</t>
+          <t>Not stated in JD</t>
         </is>
       </c>
       <c r="J69" s="3" t="inlineStr">
@@ -4864,7 +4864,7 @@
       </c>
       <c r="M69" s="6" t="inlineStr">
         <is>
-          <t>https://de.linkedin.com/jobs/view/decision-scientist-marketing-modelling-intelligence-marketing-dsa-at-vinted-4431734157?position=23&amp;pageNum=0&amp;refId=T%2F0KkBXL%2Fl%2B5Iv5tUGTY7Q%3D%3D&amp;trackingId=ym8Uxiee8AvGv52T5S0EVQ%3D%3D</t>
+          <t>https://nl.linkedin.com/jobs/view/mlops-engineer-at-rubicon-cloud-advisor-4450093837?position=15&amp;pageNum=0&amp;refId=oiBIn1Czflg0JjZjH5z0Lg%3D%3D&amp;trackingId=bnH0HGZbT4T4t%2FkIxlYWZQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -4874,17 +4874,17 @@
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>Data Analyst / Data Science Specialist (m/w/d)</t>
+          <t>Decision Scientist, Marketing Modelling Intelligence, Marketing DSA</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>Molkerei Gropper GmbH &amp; Co. KG</t>
+          <t>Vinted</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>Bissingen, Bavaria, Germany</t>
+          <t>Berlin, Berlin, Germany</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -4892,17 +4892,17 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F70" s="8" t="n">
+      <c r="F70" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="G70" s="9" t="inlineStr">
+      <c r="G70" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H70" s="3" t="inlineStr">
         <is>
-          <t>This role is focused primarily on traditional Data Warehousing, BI, ETL, and reporting with SAP systems, where AI is merely a passing mention of interest rather than a core focus. It is a significant mismatch for the candidate's advanced Generative AI, LLM, and agentic specialization.</t>
+          <t>This is a classical marketing analytics and econometrics role focused on Bayesian Media Mix Modeling and ROI measurement with no mention of Generative AI, LLMs, or agentic systems. Furthermore, the candidate is a Lead Data Scientist with 10+ years of experience, making the 2-4 year experience requirement a significant seniority mismatch.</t>
         </is>
       </c>
       <c r="I70" s="3" t="inlineStr">
@@ -4927,7 +4927,7 @@
       </c>
       <c r="M70" s="6" t="inlineStr">
         <is>
-          <t>https://de.linkedin.com/jobs/view/data-analyst-data-science-specialist-m-w-d-at-molkerei-gropper-gmbh-co-kg-4459396175?position=16&amp;pageNum=0&amp;refId=T%2F0KkBXL%2Fl%2B5Iv5tUGTY7Q%3D%3D&amp;trackingId=hDs2N%2Ft3sDgczR%2Fh%2Biow4g%3D%3D</t>
+          <t>https://de.linkedin.com/jobs/view/decision-scientist-marketing-modelling-intelligence-marketing-dsa-at-vinted-4431734157?position=23&amp;pageNum=0&amp;refId=T%2F0KkBXL%2Fl%2B5Iv5tUGTY7Q%3D%3D&amp;trackingId=ym8Uxiee8AvGv52T5S0EVQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -4937,17 +4937,17 @@
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>Specialist Data Science</t>
+          <t>Data Analyst / Data Science Specialist (m/w/d)</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>HDI Group</t>
+          <t>Molkerei Gropper GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>Hannover, Lower Saxony, Germany</t>
+          <t>Bissingen, Bavaria, Germany</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -4955,22 +4955,22 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F71" s="8" t="n">
+      <c r="F71" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="G71" s="9" t="inlineStr">
+      <c r="G71" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H71" s="3" t="inlineStr">
         <is>
-          <t>This role focuses heavily on data engineering, analytics, and R-based pricing tools within the insurance domain, offering only passing alignment with classical data science rather than the candidate's core GenAI, LLMs, and agentic AI specialization.</t>
+          <t>This role is focused primarily on traditional Data Warehousing, BI, ETL, and reporting with SAP systems, where AI is merely a passing mention of interest rather than a core focus. It is a significant mismatch for the candidate's advanced Generative AI, LLM, and agentic specialization.</t>
         </is>
       </c>
       <c r="I71" s="3" t="inlineStr">
         <is>
-          <t>Not stated in JD</t>
+          <t>Yes - German required (see JD for exact level)</t>
         </is>
       </c>
       <c r="J71" s="3" t="inlineStr">
@@ -4990,7 +4990,7 @@
       </c>
       <c r="M71" s="6" t="inlineStr">
         <is>
-          <t>https://de.linkedin.com/jobs/view/specialist-data-science-at-hdi-group-4449488553?position=9&amp;pageNum=0&amp;refId=T%2F0KkBXL%2Fl%2B5Iv5tUGTY7Q%3D%3D&amp;trackingId=4kEwk2%2BQdqX%2FDjmyxZ2xyA%3D%3D</t>
+          <t>https://de.linkedin.com/jobs/view/data-analyst-data-science-specialist-m-w-d-at-molkerei-gropper-gmbh-co-kg-4459396175?position=16&amp;pageNum=0&amp;refId=T%2F0KkBXL%2Fl%2B5Iv5tUGTY7Q%3D%3D&amp;trackingId=hDs2N%2Ft3sDgczR%2Fh%2Biow4g%3D%3D</t>
         </is>
       </c>
     </row>
@@ -5000,17 +5000,17 @@
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>Data Scientist (m/w/d) für analytisches CRM und datengestützte Potenziale</t>
+          <t>Specialist Data Science</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>R+V Versicherung</t>
+          <t>HDI Group</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>Wiesbaden, Hesse, Germany</t>
+          <t>Hannover, Lower Saxony, Germany</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -5018,22 +5018,22 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F72" s="8" t="n">
+      <c r="F72" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="G72" s="9" t="inlineStr">
+      <c r="G72" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H72" s="3" t="inlineStr">
         <is>
-          <t>This role focuses on analytical CRM, customer segmentation, and rule-based next-best-offer systems using SQL and traditional data methods, offering only passing mention of AI approaches. It lacks the core Generative AI, LLM, and agentic specialization that defines the candidate's profile.</t>
+          <t>This role focuses heavily on data engineering, analytics, and R-based pricing tools within the insurance domain, offering only passing alignment with classical data science rather than the candidate's core GenAI, LLMs, and agentic AI specialization.</t>
         </is>
       </c>
       <c r="I72" s="3" t="inlineStr">
         <is>
-          <t>Yes - fluent/C1+ German explicitly required</t>
+          <t>Not stated in JD</t>
         </is>
       </c>
       <c r="J72" s="3" t="inlineStr">
@@ -5053,7 +5053,7 @@
       </c>
       <c r="M72" s="6" t="inlineStr">
         <is>
-          <t>https://de.linkedin.com/jobs/view/data-scientist-m-w-d-f%C3%BCr-analytisches-crm-und-datengest%C3%BCtzte-potenziale-at-r%2Bv-versicherung-4446660524?position=7&amp;pageNum=0&amp;refId=T%2F0KkBXL%2Fl%2B5Iv5tUGTY7Q%3D%3D&amp;trackingId=na3WACzOriMr43dXtkckXw%3D%3D</t>
+          <t>https://de.linkedin.com/jobs/view/specialist-data-science-at-hdi-group-4449488553?position=9&amp;pageNum=0&amp;refId=T%2F0KkBXL%2Fl%2B5Iv5tUGTY7Q%3D%3D&amp;trackingId=4kEwk2%2BQdqX%2FDjmyxZ2xyA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -5063,17 +5063,17 @@
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>Senior Data Scientist (m/f/d)</t>
+          <t>Data Scientist (m/w/d) für analytisches CRM und datengestützte Potenziale</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>AutoScout24</t>
+          <t>R+V Versicherung</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>Munich, Bavaria, Germany</t>
+          <t>Wiesbaden, Hesse, Germany</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -5081,22 +5081,22 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F73" s="8" t="n">
+      <c r="F73" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="G73" s="9" t="inlineStr">
+      <c r="G73" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H73" s="3" t="inlineStr">
         <is>
-          <t>[FALLBACK SCORER - Gemini call failed] Matched 2 core GenAI term(s) via keyword search. Verify manually; this is a degraded-mode score.</t>
+          <t>This role focuses on analytical CRM, customer segmentation, and rule-based next-best-offer systems using SQL and traditional data methods, offering only passing mention of AI approaches. It lacks the core Generative AI, LLM, and agentic specialization that defines the candidate's profile.</t>
         </is>
       </c>
       <c r="I73" s="3" t="inlineStr">
         <is>
-          <t>Not stated in JD</t>
+          <t>Yes - fluent/C1+ German explicitly required</t>
         </is>
       </c>
       <c r="J73" s="3" t="inlineStr">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="M73" s="6" t="inlineStr">
         <is>
-          <t>https://de.linkedin.com/jobs/view/senior-data-scientist-m-f-d-at-autoscout24-4432214339?position=11&amp;pageNum=0&amp;refId=T%2F0KkBXL%2Fl%2B5Iv5tUGTY7Q%3D%3D&amp;trackingId=7SGOVxV%2FwAFkUhW1fBv2EA%3D%3D</t>
+          <t>https://de.linkedin.com/jobs/view/data-scientist-m-w-d-f%C3%BCr-analytisches-crm-und-datengest%C3%BCtzte-potenziale-at-r%2Bv-versicherung-4446660524?position=7&amp;pageNum=0&amp;refId=T%2F0KkBXL%2Fl%2B5Iv5tUGTY7Q%3D%3D&amp;trackingId=na3WACzOriMr43dXtkckXw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -5126,17 +5126,17 @@
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>Data Analyst / Scientist (m/w/d)</t>
+          <t>Senior Data Scientist (m/f/d)</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>Dr. Wolff Group</t>
+          <t>AutoScout24</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>Bielefeld, North Rhine-Westphalia, Germany</t>
+          <t>Munich, Bavaria, Germany</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -5144,10 +5144,10 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F74" s="8" t="n">
+      <c r="F74" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="G74" s="9" t="inlineStr">
+      <c r="G74" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -5159,7 +5159,7 @@
       </c>
       <c r="I74" s="3" t="inlineStr">
         <is>
-          <t>Yes - German required (see JD for exact level)</t>
+          <t>Not stated in JD</t>
         </is>
       </c>
       <c r="J74" s="3" t="inlineStr">
@@ -5179,7 +5179,7 @@
       </c>
       <c r="M74" s="6" t="inlineStr">
         <is>
-          <t>https://de.linkedin.com/jobs/view/data-analyst-scientist-m-w-d-at-dr-wolff-group-4459323885?position=2&amp;pageNum=0&amp;refId=T%2F0KkBXL%2Fl%2B5Iv5tUGTY7Q%3D%3D&amp;trackingId=fnXlAvETsQ4TzuiWcW6AWA%3D%3D</t>
+          <t>https://de.linkedin.com/jobs/view/senior-data-scientist-m-f-d-at-autoscout24-4432214339?position=11&amp;pageNum=0&amp;refId=T%2F0KkBXL%2Fl%2B5Iv5tUGTY7Q%3D%3D&amp;trackingId=7SGOVxV%2FwAFkUhW1fBv2EA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -5189,17 +5189,17 @@
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>Data Scientist - AI Search &amp; Ranking</t>
+          <t>Data Analyst / Scientist (m/w/d)</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>trivago</t>
+          <t>Dr. Wolff Group</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>Düsseldorf, North Rhine-Westphalia, Germany</t>
+          <t>Bielefeld, North Rhine-Westphalia, Germany</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
@@ -5207,10 +5207,10 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F75" s="8" t="n">
+      <c r="F75" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="G75" s="9" t="inlineStr">
+      <c r="G75" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -5222,7 +5222,7 @@
       </c>
       <c r="I75" s="3" t="inlineStr">
         <is>
-          <t>Not stated in JD</t>
+          <t>Yes - German required (see JD for exact level)</t>
         </is>
       </c>
       <c r="J75" s="3" t="inlineStr">
@@ -5242,7 +5242,7 @@
       </c>
       <c r="M75" s="6" t="inlineStr">
         <is>
-          <t>https://de.linkedin.com/jobs/view/data-scientist-ai-search-ranking-at-trivago-4451695166?position=3&amp;pageNum=0&amp;refId=T%2F0KkBXL%2Fl%2B5Iv5tUGTY7Q%3D%3D&amp;trackingId=653eapm3ns02Vx9zaTVbNw%3D%3D</t>
+          <t>https://de.linkedin.com/jobs/view/data-analyst-scientist-m-w-d-at-dr-wolff-group-4459323885?position=2&amp;pageNum=0&amp;refId=T%2F0KkBXL%2Fl%2B5Iv5tUGTY7Q%3D%3D&amp;trackingId=fnXlAvETsQ4TzuiWcW6AWA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -5252,17 +5252,17 @@
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>Senior Manager, Digital Forensics &amp; eDiscovery</t>
+          <t>Data Scientist - AI Search &amp; Ranking</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>Robert Walters</t>
+          <t>trivago</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>Dubai, Dubai, United Arab Emirates</t>
+          <t>Düsseldorf, North Rhine-Westphalia, Germany</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -5270,17 +5270,17 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F76" s="8" t="n">
+      <c r="F76" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="G76" s="9" t="inlineStr">
+      <c r="G76" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H76" s="3" t="inlineStr">
         <is>
-          <t>The role is focused heavily on digital forensics, eDiscovery, and regulatory investigations, which does not align with the candidate's core specialization in Generative AI, LangGraph, and agentic LLM pipelines. While it mentions emerging AI technologies and LLMs as a secondary component, the candidate's strong GenAI background is largely mismatched with the core forensic and eDiscovery tech stack.</t>
+          <t>[FALLBACK SCORER - Gemini call failed] Matched 2 core GenAI term(s) via keyword search. Verify manually; this is a degraded-mode score.</t>
         </is>
       </c>
       <c r="I76" s="3" t="inlineStr">
@@ -5305,7 +5305,7 @@
       </c>
       <c r="M76" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/senior-manager-digital-forensics-ediscovery-at-robert-walters-4457258106?position=26&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=nugpWYWcIAXvX9xB18JHdw%3D%3D</t>
+          <t>https://de.linkedin.com/jobs/view/data-scientist-ai-search-ranking-at-trivago-4451695166?position=3&amp;pageNum=0&amp;refId=T%2F0KkBXL%2Fl%2B5Iv5tUGTY7Q%3D%3D&amp;trackingId=653eapm3ns02Vx9zaTVbNw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -5315,12 +5315,12 @@
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>Business Analyst - instashop</t>
+          <t>Senior Manager, Digital Forensics &amp; eDiscovery</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>talabat</t>
+          <t>Robert Walters</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
@@ -5333,17 +5333,17 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F77" s="8" t="n">
+      <c r="F77" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="G77" s="9" t="inlineStr">
+      <c r="G77" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H77" s="3" t="inlineStr">
         <is>
-          <t>This is a Business Analyst role focused on traditional commercial analytics, SQL, and BI reporting, with only passing mentions of using generative AI tools as productivity boosters. It represents a significant mismatch in domain and seniority compared to the candidate's core specialization as a Lead GenAI/LLM/Agentic AI specialist with 10+ years of experience.</t>
+          <t>The role is focused heavily on digital forensics, eDiscovery, and regulatory investigations, which does not align with the candidate's core specialization in Generative AI, LangGraph, and agentic LLM pipelines. While it mentions emerging AI technologies and LLMs as a secondary component, the candidate's strong GenAI background is largely mismatched with the core forensic and eDiscovery tech stack.</t>
         </is>
       </c>
       <c r="I77" s="3" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="M77" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/business-analyst-instashop-at-talabat-4447352935?position=6&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=gGEviUFke%2FcNigxE2hYK8w%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/senior-manager-digital-forensics-ediscovery-at-robert-walters-4457258106?position=26&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=nugpWYWcIAXvX9xB18JHdw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -5378,17 +5378,17 @@
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>Senior MLOps/Data Engineer</t>
+          <t>Business Analyst - instashop</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>TomTom</t>
+          <t>talabat</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>Amsterdam, North Holland, Netherlands</t>
+          <t>Dubai, Dubai, United Arab Emirates</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -5396,17 +5396,17 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F78" s="8" t="n">
+      <c r="F78" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="G78" s="9" t="inlineStr">
+      <c r="G78" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H78" s="3" t="inlineStr">
         <is>
-          <t>This is a Senior MLOps/Data Engineer role focusing on PySpark, Databricks, and pipeline orchestration rather than Generative AI or LLMs. While the candidate has Azure and Python experience, the core technical requirements do not align with his GenAI and agentic specialization.</t>
+          <t>This is a Business Analyst role focused on traditional commercial analytics, SQL, and BI reporting, with only passing mentions of using generative AI tools as productivity boosters. It represents a significant mismatch in domain and seniority compared to the candidate's core specialization as a Lead GenAI/LLM/Agentic AI specialist with 10+ years of experience.</t>
         </is>
       </c>
       <c r="I78" s="3" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="M78" s="6" t="inlineStr">
         <is>
-          <t>https://nl.linkedin.com/jobs/view/senior-mlops-data-engineer-at-tomtom-4448554856?position=23&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=SHR8gYATTGX6qegw6hmLAw%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/business-analyst-instashop-at-talabat-4447352935?position=6&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=gGEviUFke%2FcNigxE2hYK8w%3D%3D</t>
         </is>
       </c>
     </row>
@@ -5441,12 +5441,12 @@
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>Decision Scientist, Marketing Modelling Intelligence, Marketing DSA</t>
+          <t>Senior MLOps/Data Engineer</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>Vinted</t>
+          <t>TomTom</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
@@ -5459,17 +5459,17 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F79" s="8" t="n">
+      <c r="F79" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="G79" s="9" t="inlineStr">
+      <c r="G79" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H79" s="3" t="inlineStr">
         <is>
-          <t>This is a marketing analytics and econometric modeling role focused on Bayesian Media Mix Models, which only touches classical statistics and regression without any GenAI, LLMs, or agentic systems. Furthermore, the seniority expectation (2-4 years) is a major mismatch for a candidate with 10+ years of experience.</t>
+          <t>This is a Senior MLOps/Data Engineer role focusing on PySpark, Databricks, and pipeline orchestration rather than Generative AI or LLMs. While the candidate has Azure and Python experience, the core technical requirements do not align with his GenAI and agentic specialization.</t>
         </is>
       </c>
       <c r="I79" s="3" t="inlineStr">
@@ -5494,7 +5494,7 @@
       </c>
       <c r="M79" s="6" t="inlineStr">
         <is>
-          <t>https://nl.linkedin.com/jobs/view/decision-scientist-marketing-modelling-intelligence-marketing-dsa-at-vinted-4431724987?position=12&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=CGELWLumu99gkHZTfq3gCQ%3D%3D</t>
+          <t>https://nl.linkedin.com/jobs/view/senior-mlops-data-engineer-at-tomtom-4448554856?position=23&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=SHR8gYATTGX6qegw6hmLAw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -5504,17 +5504,17 @@
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>Lead Data Science</t>
+          <t>Decision Scientist, Marketing Modelling Intelligence, Marketing DSA</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>Zonneplan</t>
+          <t>Vinted</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>Zwolle, Overijssel, Netherlands</t>
+          <t>Amsterdam, North Holland, Netherlands</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -5522,17 +5522,17 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F80" s="8" t="n">
+      <c r="F80" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="G80" s="9" t="inlineStr">
+      <c r="G80" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H80" s="3" t="inlineStr">
         <is>
-          <t>The role is focused heavily on classical time-series forecasting, energy optimization, and MLOps for trading systems rather than Generative AI, LLMs, or agentic workflows. While the candidate's seniority as a Lead matches well, the lack of core GenAI focus makes this a weak technical fit.</t>
+          <t>This is a marketing analytics and econometric modeling role focused on Bayesian Media Mix Models, which only touches classical statistics and regression without any GenAI, LLMs, or agentic systems. Furthermore, the seniority expectation (2-4 years) is a major mismatch for a candidate with 10+ years of experience.</t>
         </is>
       </c>
       <c r="I80" s="3" t="inlineStr">
@@ -5557,7 +5557,7 @@
       </c>
       <c r="M80" s="6" t="inlineStr">
         <is>
-          <t>https://nl.linkedin.com/jobs/view/lead-data-science-at-zonneplan-4414158731?position=8&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=1yTKWUbJDbOf0JWJnBF0EQ%3D%3D</t>
+          <t>https://nl.linkedin.com/jobs/view/decision-scientist-marketing-modelling-intelligence-marketing-dsa-at-vinted-4431724987?position=12&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=CGELWLumu99gkHZTfq3gCQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -5567,17 +5567,17 @@
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Lead Data Science</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>Confidential</t>
+          <t>Zonneplan</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>Abu Dhabi Emirate, United Arab Emirates</t>
+          <t>Zwolle, Overijssel, Netherlands</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -5585,17 +5585,17 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F81" s="8" t="n">
+      <c r="F81" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="G81" s="9" t="inlineStr">
+      <c r="G81" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H81" s="3" t="inlineStr">
         <is>
-          <t>This is a Data Engineering role focusing on cloud pipelines, lakehouses, streaming, and data warehousing rather than a GenAI or LLM specialization role. While it mentions building datasets and vector pipelines for AI, the core function is infrastructure and data engineering rather than the candidate's core expertise as a Lead Data Scientist in GenAI and agentic workflows.</t>
+          <t>The role is focused heavily on classical time-series forecasting, energy optimization, and MLOps for trading systems rather than Generative AI, LLMs, or agentic workflows. While the candidate's seniority as a Lead matches well, the lack of core GenAI focus makes this a weak technical fit.</t>
         </is>
       </c>
       <c r="I81" s="3" t="inlineStr">
@@ -5620,7 +5620,7 @@
       </c>
       <c r="M81" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/data-engineer-at-confidential-4457913992?position=27&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=0E%2Bet6hk0hz6AFQRQUNpjg%3D%3D</t>
+          <t>https://nl.linkedin.com/jobs/view/lead-data-science-at-zonneplan-4414158731?position=8&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=1yTKWUbJDbOf0JWJnBF0EQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -5630,35 +5630,35 @@
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>Head of Data Science</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>Jex Recruitment | Connecting top talent with leading companies</t>
+          <t>Confidential</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>Abu Dhabi, Abu Dhabi Emirate, United Arab Emirates</t>
+          <t>Abu Dhabi Emirate, United Arab Emirates</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="F82" s="8" t="n">
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="F82" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="G82" s="9" t="inlineStr">
+      <c r="G82" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H82" s="3" t="inlineStr">
         <is>
-          <t>The role requires executive leadership (Head of Data Science) focused on managing teams, strategy, and classical banking use cases rather than hands-on technical GenAI or agentic AI work. This is a significant seniority and role-type mismatch for a Lead Data Scientist specializing in LLMs and RAG.</t>
+          <t>This is a Data Engineering role focusing on cloud pipelines, lakehouses, streaming, and data warehousing rather than a GenAI or LLM specialization role. While it mentions building datasets and vector pipelines for AI, the core function is infrastructure and data engineering rather than the candidate's core expertise as a Lead Data Scientist in GenAI and agentic workflows.</t>
         </is>
       </c>
       <c r="I82" s="3" t="inlineStr">
@@ -5668,7 +5668,7 @@
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
-          <t>Possible - relocation support mentioned, visa not explicit</t>
+          <t>Not stated in JD</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -5683,7 +5683,7 @@
       </c>
       <c r="M82" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/head-of-data-science-at-jex-recruitment-connecting-top-talent-with-leading-companies-4458343957?position=23&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=SiTMdQz8r7KHa1LqknvQjg%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/data-engineer-at-confidential-4457913992?position=27&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=0E%2Bet6hk0hz6AFQRQUNpjg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -5693,17 +5693,17 @@
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>Data Scientist Delivery Domain</t>
+          <t>Head of Data Science</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>Coolblue</t>
+          <t>Jex Recruitment | Connecting top talent with leading companies</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>Rotterdam, South Holland, Netherlands</t>
+          <t>Abu Dhabi, Abu Dhabi Emirate, United Arab Emirates</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
@@ -5711,17 +5711,17 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="F83" s="8" t="n">
+      <c r="F83" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="G83" s="9" t="inlineStr">
+      <c r="G83" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H83" s="3" t="inlineStr">
         <is>
-          <t>This is a classical forecasting and operations research role focusing on delivery and installation planning using Python and SQL, with no mention of Generative AI, LLMs, or agentic systems which are the candidate's core specialization. Although the candidate has background in traditional machine learning that overlaps slightly, it represents a weak fit for his current profile.</t>
+          <t>The role requires executive leadership (Head of Data Science) focused on managing teams, strategy, and classical banking use cases rather than hands-on technical GenAI or agentic AI work. This is a significant seniority and role-type mismatch for a Lead Data Scientist specializing in LLMs and RAG.</t>
         </is>
       </c>
       <c r="I83" s="3" t="inlineStr">
@@ -5731,7 +5731,7 @@
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
-          <t>Not stated in JD</t>
+          <t>Possible - relocation support mentioned, visa not explicit</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="M83" s="6" t="inlineStr">
         <is>
-          <t>https://nl.linkedin.com/jobs/view/data-scientist-delivery-domain-at-coolblue-4459662808?position=3&amp;pageNum=0&amp;refId=oiBIn1Czflg0JjZjH5z0Lg%3D%3D&amp;trackingId=V2dKcwpv0YpijBJw41fQVg%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/head-of-data-science-at-jex-recruitment-connecting-top-talent-with-leading-companies-4458343957?position=23&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=SiTMdQz8r7KHa1LqknvQjg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -5756,17 +5756,17 @@
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>Lead Data Scientist, Revenue - Ads, Revenue</t>
+          <t>Data Scientist Delivery Domain</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>Vinted</t>
+          <t>Coolblue</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>Amsterdam, North Holland, Netherlands</t>
+          <t>Rotterdam, South Holland, Netherlands</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -5774,17 +5774,17 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="F84" s="8" t="n">
+      <c r="F84" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="G84" s="9" t="inlineStr">
+      <c r="G84" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H84" s="3" t="inlineStr">
         <is>
-          <t>This role focuses heavily on Ad Tech systems, auction mechanics, ads ranking, and real-time optimization, which falls outside the candidate's core specialization in Generative AI, LLMs, and agentic pipelines. While the seniority level (Lead Data Scientist) aligns, the domain mismatch makes it a weak technical fit.</t>
+          <t>This is a classical forecasting and operations research role focusing on delivery and installation planning using Python and SQL, with no mention of Generative AI, LLMs, or agentic systems which are the candidate's core specialization. Although the candidate has background in traditional machine learning that overlaps slightly, it represents a weak fit for his current profile.</t>
         </is>
       </c>
       <c r="I84" s="3" t="inlineStr">
@@ -5809,7 +5809,7 @@
       </c>
       <c r="M84" s="6" t="inlineStr">
         <is>
-          <t>https://nl.linkedin.com/jobs/view/lead-data-scientist-revenue-ads-revenue-at-vinted-4431741084?position=8&amp;pageNum=0&amp;refId=oiBIn1Czflg0JjZjH5z0Lg%3D%3D&amp;trackingId=ZcYNzhXf9h2M3%2FWEms9aMw%3D%3D</t>
+          <t>https://nl.linkedin.com/jobs/view/data-scientist-delivery-domain-at-coolblue-4459662808?position=3&amp;pageNum=0&amp;refId=oiBIn1Czflg0JjZjH5z0Lg%3D%3D&amp;trackingId=V2dKcwpv0YpijBJw41fQVg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -5819,17 +5819,17 @@
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>AI Product Manager</t>
+          <t>Lead Data Scientist, Revenue - Ads, Revenue</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>Auxo Talent</t>
+          <t>Vinted</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>Dubai, United Arab Emirates</t>
+          <t>Amsterdam, North Holland, Netherlands</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
@@ -5837,17 +5837,17 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="F85" s="8" t="n">
+      <c r="F85" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="G85" s="9" t="inlineStr">
+      <c r="G85" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H85" s="3" t="inlineStr">
         <is>
-          <t>This role is for an AI Product Manager rather than a hands-on technical Data Scientist or Generative AI engineer. While the candidate has deep technical expertise in GenAI and relevant fintech domain knowledge, he lacks the required professional product management background and roadmap-owning experience demanded by the position.</t>
+          <t>This role focuses heavily on Ad Tech systems, auction mechanics, ads ranking, and real-time optimization, which falls outside the candidate's core specialization in Generative AI, LLMs, and agentic pipelines. While the seniority level (Lead Data Scientist) aligns, the domain mismatch makes it a weak technical fit.</t>
         </is>
       </c>
       <c r="I85" s="3" t="inlineStr">
@@ -5860,9 +5860,9 @@
           <t>Not stated in JD</t>
         </is>
       </c>
-      <c r="K85" s="7" t="inlineStr">
-        <is>
-          <t>New this run (2026-08-27 15:40 UTC)</t>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>From previous run</t>
         </is>
       </c>
       <c r="L85" s="2" t="inlineStr">
@@ -5872,7 +5872,7 @@
       </c>
       <c r="M85" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/ai-product-manager-at-auxo-talent-4458373508?position=12&amp;pageNum=0&amp;refId=50H6yCrEXIuhgr6eqEojNg%3D%3D&amp;trackingId=y5Nqep1ywbJPUkaTD9Vo3g%3D%3D</t>
+          <t>https://nl.linkedin.com/jobs/view/lead-data-scientist-revenue-ads-revenue-at-vinted-4431741084?position=8&amp;pageNum=0&amp;refId=oiBIn1Czflg0JjZjH5z0Lg%3D%3D&amp;trackingId=ZcYNzhXf9h2M3%2FWEms9aMw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -5882,12 +5882,12 @@
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>AI and Data Architect</t>
+          <t>AI Product Manager</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>Fundamentl</t>
+          <t>Auxo Talent</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
@@ -5900,32 +5900,32 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="F86" s="8" t="n">
+      <c r="F86" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="G86" s="9" t="inlineStr">
+      <c r="G86" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H86" s="3" t="inlineStr">
         <is>
-          <t>The role aligns well technically with the candidate's specialization in GenAI, Agentic AI, RAG, LangChain, LangGraph, and Azure tools. However, there is a severe seniority mismatch requiring 18+ years of experience for an AI and Data Architect role, whereas the candidate has 10 years of experience, making it a weak fit.</t>
+          <t>This role is for an AI Product Manager rather than a hands-on technical Data Scientist or Generative AI engineer. While the candidate has deep technical expertise in GenAI and relevant fintech domain knowledge, he lacks the required professional product management background and roadmap-owning experience demanded by the position.</t>
         </is>
       </c>
       <c r="I86" s="3" t="inlineStr">
         <is>
-          <t>No - English fluency stated as sufficient</t>
+          <t>Not stated in JD</t>
         </is>
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
-          <t>Yes - explicitly stated in JD</t>
-        </is>
-      </c>
-      <c r="K86" s="7" t="inlineStr">
-        <is>
-          <t>New this run (2026-08-27 15:40 UTC)</t>
+          <t>Not stated in JD</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>From previous run</t>
         </is>
       </c>
       <c r="L86" s="2" t="inlineStr">
@@ -5935,7 +5935,7 @@
       </c>
       <c r="M86" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/ai-and-data-architect-at-fundamentl-4459845026?position=11&amp;pageNum=0&amp;refId=50H6yCrEXIuhgr6eqEojNg%3D%3D&amp;trackingId=Bd15IH4kHpjPXnejnC%2BLzw%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/ai-product-manager-at-auxo-talent-4458373508?position=12&amp;pageNum=0&amp;refId=50H6yCrEXIuhgr6eqEojNg%3D%3D&amp;trackingId=y5Nqep1ywbJPUkaTD9Vo3g%3D%3D</t>
         </is>
       </c>
     </row>
@@ -5945,45 +5945,45 @@
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI and Data Architect</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>Mammoet</t>
+          <t>Fundamentl</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>Schiedam, South Holland, Netherlands</t>
+          <t>Dubai, United Arab Emirates</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="F87" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="G87" s="9" t="inlineStr">
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="F87" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="G87" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H87" s="3" t="inlineStr">
         <is>
-          <t>This is a Data Engineer role focused on cloud data platforms, ETL pipelines, and Data Vault modeling, which does not leverage the candidate's core specialization in Generative AI, LLMs, and agentic workflows. Additionally, the required 0-5 years of experience represents a seniority mismatch for a Lead Data Scientist with over 10 years of experience.</t>
+          <t>The role aligns well technically with the candidate's specialization in GenAI, Agentic AI, RAG, LangChain, LangGraph, and Azure tools. However, there is a severe seniority mismatch requiring 18+ years of experience for an AI and Data Architect role, whereas the candidate has 10 years of experience, making it a weak fit.</t>
         </is>
       </c>
       <c r="I87" s="3" t="inlineStr">
         <is>
-          <t>Not stated in JD</t>
+          <t>No - English fluency stated as sufficient</t>
         </is>
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
-          <t>Not stated in JD</t>
+          <t>Yes - explicitly stated in JD</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
@@ -5998,7 +5998,7 @@
       </c>
       <c r="M87" s="6" t="inlineStr">
         <is>
-          <t>https://nl.linkedin.com/jobs/view/data-engineer-at-mammoet-4459379074?position=24&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=vEO3k7c4HScCtKkTbNh8Xg%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/ai-and-data-architect-at-fundamentl-4459845026?position=11&amp;pageNum=0&amp;refId=50H6yCrEXIuhgr6eqEojNg%3D%3D&amp;trackingId=Bd15IH4kHpjPXnejnC%2BLzw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -6008,17 +6008,17 @@
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>Medior data-analist</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>Finance Ideas</t>
+          <t>Mammoet</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>Utrecht, Utrecht, Netherlands</t>
+          <t>Schiedam, South Holland, Netherlands</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -6026,17 +6026,17 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F88" s="8" t="n">
+      <c r="F88" s="7" t="n">
         <v>25</v>
       </c>
-      <c r="G88" s="9" t="inlineStr">
+      <c r="G88" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H88" s="3" t="inlineStr">
         <is>
-          <t>This is a medior data analyst role focused on financial and strategic healthcare dashboards and predictive modeling using SQL and Excel, with only a passing mention of AI. It does not utilize the candidate's core GenAI, LLM, and agentic specialization, and represents a significant mismatch in both focus and seniority.</t>
+          <t>This is a Data Engineer role focused on cloud data platforms, ETL pipelines, and Data Vault modeling, which does not leverage the candidate's core specialization in Generative AI, LLMs, and agentic workflows. Additionally, the required 0-5 years of experience represents a seniority mismatch for a Lead Data Scientist with over 10 years of experience.</t>
         </is>
       </c>
       <c r="I88" s="3" t="inlineStr">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="M88" s="6" t="inlineStr">
         <is>
-          <t>https://nl.linkedin.com/jobs/view/medior-data-analist-at-finance-ideas-4459185767?position=16&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=Aag%2FWZa%2Bp4QUCt1avtmqXw%3D%3D</t>
+          <t>https://nl.linkedin.com/jobs/view/data-engineer-at-mammoet-4459379074?position=24&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=vEO3k7c4HScCtKkTbNh8Xg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -6071,17 +6071,17 @@
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>Junior Data Scientist – Personalization</t>
+          <t>Medior data-analist</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>Future Impact</t>
+          <t>Finance Ideas</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>Amsterdam, North Holland, Netherlands</t>
+          <t>Utrecht, Utrecht, Netherlands</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
@@ -6089,17 +6089,17 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F89" s="8" t="n">
+      <c r="F89" s="7" t="n">
         <v>25</v>
       </c>
-      <c r="G89" s="9" t="inlineStr">
+      <c r="G89" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H89" s="3" t="inlineStr">
         <is>
-          <t>This role is a severe seniority and domain mismatch, requiring a junior-level data scientist (1+ years experience) focused on classical machine learning, personalization, and tabular/text mining rather than the candidate's advanced GenAI, LLMs, and agentic orchestration specialization.</t>
+          <t>This is a medior data analyst role focused on financial and strategic healthcare dashboards and predictive modeling using SQL and Excel, with only a passing mention of AI. It does not utilize the candidate's core GenAI, LLM, and agentic specialization, and represents a significant mismatch in both focus and seniority.</t>
         </is>
       </c>
       <c r="I89" s="3" t="inlineStr">
@@ -6109,7 +6109,7 @@
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
-          <t>Possible - relocation support mentioned, visa not explicit</t>
+          <t>Not stated in JD</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
@@ -6124,7 +6124,7 @@
       </c>
       <c r="M89" s="6" t="inlineStr">
         <is>
-          <t>https://nl.linkedin.com/jobs/view/junior-data-scientist-%E2%80%93-personalization-at-future-impact-4459176208?position=6&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=%2F2X0%2FMpduifeqyUanMFmiQ%3D%3D</t>
+          <t>https://nl.linkedin.com/jobs/view/medior-data-analist-at-finance-ideas-4459185767?position=16&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=Aag%2FWZa%2Bp4QUCt1avtmqXw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -6134,17 +6134,17 @@
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>Senior Software Developer</t>
+          <t>Junior Data Scientist – Personalization</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>Bankdata</t>
+          <t>Future Impact</t>
         </is>
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>Silkeborg, Central Denmark Region, Denmark</t>
+          <t>Amsterdam, North Holland, Netherlands</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -6152,17 +6152,17 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F90" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="G90" s="9" t="inlineStr">
+      <c r="F90" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="G90" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H90" s="3" t="inlineStr">
         <is>
-          <t>This is a Senior Software Developer role focused on core data engineering, Java/Spring Boot, Angular, and legacy systems rather than Generative AI or LLMs. Although Databricks, Python, and financial domain experience overlap with the candidate's background, the lack of software engineering specialization in Java/frontend and absence of GenAI/agentic requirements make it a weak technical fit.</t>
+          <t>This role is a severe seniority and domain mismatch, requiring a junior-level data scientist (1+ years experience) focused on classical machine learning, personalization, and tabular/text mining rather than the candidate's advanced GenAI, LLMs, and agentic orchestration specialization.</t>
         </is>
       </c>
       <c r="I90" s="3" t="inlineStr">
@@ -6172,7 +6172,7 @@
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
-          <t>Not stated in JD</t>
+          <t>Possible - relocation support mentioned, visa not explicit</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
@@ -6187,7 +6187,7 @@
       </c>
       <c r="M90" s="6" t="inlineStr">
         <is>
-          <t>https://dk.linkedin.com/jobs/view/senior-software-developer-at-bankdata-4449002669?position=27&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=HL%2Flu1131ad6ecWWSqhgeg%3D%3D</t>
+          <t>https://nl.linkedin.com/jobs/view/junior-data-scientist-%E2%80%93-personalization-at-future-impact-4459176208?position=6&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=%2F2X0%2FMpduifeqyUanMFmiQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -6197,17 +6197,17 @@
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>Data Scientist (m/w/d)</t>
+          <t>Senior Software Developer</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>Alliance Healthcare Deutschland GmbH</t>
+          <t>Bankdata</t>
         </is>
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>Frankfurt, Hesse, Germany</t>
+          <t>Silkeborg, Central Denmark Region, Denmark</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
@@ -6215,22 +6215,22 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F91" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="G91" s="9" t="inlineStr">
+      <c r="F91" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="G91" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H91" s="3" t="inlineStr">
         <is>
-          <t>[FALLBACK SCORER - Gemini call failed] Matched 1 core GenAI term(s) via keyword search. Verify manually; this is a degraded-mode score.</t>
+          <t>This is a Senior Software Developer role focused on core data engineering, Java/Spring Boot, Angular, and legacy systems rather than Generative AI or LLMs. Although Databricks, Python, and financial domain experience overlap with the candidate's background, the lack of software engineering specialization in Java/frontend and absence of GenAI/agentic requirements make it a weak technical fit.</t>
         </is>
       </c>
       <c r="I91" s="3" t="inlineStr">
         <is>
-          <t>Yes - fluent/C1+ German explicitly required</t>
+          <t>Not stated in JD</t>
         </is>
       </c>
       <c r="J91" s="3" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="M91" s="6" t="inlineStr">
         <is>
-          <t>https://de.linkedin.com/jobs/view/data-scientist-m-w-d-at-alliance-healthcare-deutschland-gmbh-4459307202?position=1&amp;pageNum=0&amp;refId=T%2F0KkBXL%2Fl%2B5Iv5tUGTY7Q%3D%3D&amp;trackingId=a%2BRgoPI8HwvjxaQsctZHFQ%3D%3D</t>
+          <t>https://dk.linkedin.com/jobs/view/senior-software-developer-at-bankdata-4449002669?position=27&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=HL%2Flu1131ad6ecWWSqhgeg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -6260,35 +6260,35 @@
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>Data Analytics Manager</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>Salt</t>
+          <t>Wilshire Lane Capital</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>Dubai, United Arab Emirates</t>
+          <t>Dubai, Dubai, United Arab Emirates</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="F92" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="G92" s="9" t="inlineStr">
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="F92" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="G92" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H92" s="3" t="inlineStr">
         <is>
-          <t>This is a traditional Business Intelligence and Analytics Manager role focused on SQL, BI platforms, and dashboard governance, which is entirely misaligned with the candidate's core specialization in Generative AI, LLMs, and agentic systems. Although the seniority and years of experience generally align, the technical scope is classical data analytics rather than advanced AI.</t>
+          <t>This is a Senior Data Engineer role focused on Snowflake, ELT pipelines, dbt, and Airflow rather than GenAI, LLMs, or agentic systems. While the candidate has Python and SQL skills, the core domain is infrastructure engineering rather than the candidate's specialization in Generative AI and data science.</t>
         </is>
       </c>
       <c r="I92" s="3" t="inlineStr">
@@ -6301,9 +6301,9 @@
           <t>Not stated in JD</t>
         </is>
       </c>
-      <c r="K92" s="2" t="inlineStr">
-        <is>
-          <t>From previous run</t>
+      <c r="K92" s="9" t="inlineStr">
+        <is>
+          <t>New this run (2026-08-28 08:27 UTC)</t>
         </is>
       </c>
       <c r="L92" s="2" t="inlineStr">
@@ -6313,7 +6313,7 @@
       </c>
       <c r="M92" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/data-analytics-manager-at-salt-4444546523?position=19&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=nocZsmIJ8Yx5LNeo0Qbyfg%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/senior-data-engineer-at-wilshire-lane-capital-4460178348?position=5&amp;pageNum=0&amp;refId=zJBbvwb5H0wsbJ5fs9ZTVw%3D%3D&amp;trackingId=TNqC9%2FHt9lY4eoN2myLPYg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -6323,17 +6323,17 @@
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>Junior Data Scientist Hypotheken DataLab (Amersfoort)</t>
+          <t>Data Scientist (m/w/d)</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>Future Impact</t>
+          <t>Alliance Healthcare Deutschland GmbH</t>
         </is>
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>Amsterdam, North Holland, Netherlands</t>
+          <t>Frankfurt, Hesse, Germany</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
@@ -6341,22 +6341,22 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F93" s="8" t="n">
+      <c r="F93" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="G93" s="9" t="inlineStr">
+      <c r="G93" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H93" s="3" t="inlineStr">
         <is>
-          <t>This is a junior data scientist role focused on traditional mortgage analytics and classical machine learning, representing a severe seniority and domain mismatch for a 10+ year GenAI lead specialist. Additionally, the role explicitly requires fluent Dutch language skills which the candidate lacks.</t>
+          <t>[FALLBACK SCORER - Gemini call failed] Matched 1 core GenAI term(s) via keyword search. Verify manually; this is a degraded-mode score.</t>
         </is>
       </c>
       <c r="I93" s="3" t="inlineStr">
         <is>
-          <t>Not stated in JD</t>
+          <t>Yes - fluent/C1+ German explicitly required</t>
         </is>
       </c>
       <c r="J93" s="3" t="inlineStr">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="M93" s="6" t="inlineStr">
         <is>
-          <t>https://nl.linkedin.com/jobs/view/junior-data-scientist-hypotheken-datalab-amersfoort-at-future-impact-4459169232?position=10&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=PCmMM9pEfOFRNmRrvy5XFw%3D%3D</t>
+          <t>https://de.linkedin.com/jobs/view/data-scientist-m-w-d-at-alliance-healthcare-deutschland-gmbh-4459307202?position=1&amp;pageNum=0&amp;refId=T%2F0KkBXL%2Fl%2B5Iv5tUGTY7Q%3D%3D&amp;trackingId=a%2BRgoPI8HwvjxaQsctZHFQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -6386,17 +6386,17 @@
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>Manager – Data Engineering, Architecture &amp; Reporting Platform - Dubai / Abu Dhabi</t>
+          <t>Data Analytics Manager</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>Agthia Group PJSC</t>
+          <t>Salt</t>
         </is>
       </c>
       <c r="D94" s="3" t="inlineStr">
         <is>
-          <t>Dubai, Dubai, United Arab Emirates</t>
+          <t>Dubai, United Arab Emirates</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -6404,17 +6404,17 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F94" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="G94" s="9" t="inlineStr">
+      <c r="F94" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="G94" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H94" s="3" t="inlineStr">
         <is>
-          <t>This is a data engineering and platform architecture role focused on cloud lakehouse setup, ETL pipelines, and semantic layers, completely lacking any Generative AI, LLMs, or agentic workflows which form the candidate's core specialization. Additionally, while the candidate has 10+ years of experience, the heavy infrastructure and data engineering focus makes it a weak technical fit.</t>
+          <t>This is a traditional Business Intelligence and Analytics Manager role focused on SQL, BI platforms, and dashboard governance, which is entirely misaligned with the candidate's core specialization in Generative AI, LLMs, and agentic systems. Although the seniority and years of experience generally align, the technical scope is classical data analytics rather than advanced AI.</t>
         </is>
       </c>
       <c r="I94" s="3" t="inlineStr">
@@ -6439,7 +6439,7 @@
       </c>
       <c r="M94" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/manager-%E2%80%93-data-engineering-architecture-reporting-platform-dubai-abu-dhabi-at-agthia-group-pjsc-4457225736?position=30&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=uCZRYkPcw%2FLl2O0EJmhVdQ%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/data-analytics-manager-at-salt-4444546523?position=19&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=nocZsmIJ8Yx5LNeo0Qbyfg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>Research Informatics Data Engineer</t>
+          <t>Junior Data Scientist Hypotheken DataLab (Amersfoort)</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>Lundbeck</t>
+          <t>Future Impact</t>
         </is>
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t>Copenhagen, Capital Region of Denmark, Denmark</t>
+          <t>Amsterdam, North Holland, Netherlands</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
@@ -6467,17 +6467,17 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F95" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="G95" s="9" t="inlineStr">
+      <c r="F95" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="G95" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H95" s="3" t="inlineStr">
         <is>
-          <t>This is a Research Informatics Data Engineer role focusing on life sciences data management, laboratory informatics, and scientific platform integration rather than Generative AI or advanced LLM application development. While LLMs are briefly mentioned as an optional tool for coding assistance, the candidate's core specialization in multi-agent orchestration, RAG architectures, and production GenAI systems does not align with this software/data engineering workflow role.</t>
+          <t>This is a junior data scientist role focused on traditional mortgage analytics and classical machine learning, representing a severe seniority and domain mismatch for a 10+ year GenAI lead specialist. Additionally, the role explicitly requires fluent Dutch language skills which the candidate lacks.</t>
         </is>
       </c>
       <c r="I95" s="3" t="inlineStr">
@@ -6502,7 +6502,7 @@
       </c>
       <c r="M95" s="6" t="inlineStr">
         <is>
-          <t>https://dk.linkedin.com/jobs/view/research-informatics-data-engineer-at-lundbeck-4448898202?position=5&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=5fkJnjfpF2QdhMDLztM5Vw%3D%3D</t>
+          <t>https://nl.linkedin.com/jobs/view/junior-data-scientist-hypotheken-datalab-amersfoort-at-future-impact-4459169232?position=10&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=PCmMM9pEfOFRNmRrvy5XFw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -6512,17 +6512,17 @@
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>Head of Data Analytics</t>
+          <t>Manager – Data Engineering, Architecture &amp; Reporting Platform - Dubai / Abu Dhabi</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>Right Calibre Consulting</t>
+          <t>Agthia Group PJSC</t>
         </is>
       </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
-          <t>Dubai, United Arab Emirates</t>
+          <t>Dubai, Dubai, United Arab Emirates</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -6530,17 +6530,17 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F96" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="G96" s="9" t="inlineStr">
+      <c r="F96" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="G96" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H96" s="3" t="inlineStr">
         <is>
-          <t>This is a Head of Data Analytics role focused on traditional BI, commercial insights, data governance, and leading analytics teams in the media and technology sector. It completely lacks any GenAI, LLM, or agentic AI focus, and the Head/Director-level leadership scope exceeds the candidate's current Lead Data Scientist level.</t>
+          <t>This is a data engineering and platform architecture role focused on cloud lakehouse setup, ETL pipelines, and semantic layers, completely lacking any Generative AI, LLMs, or agentic workflows which form the candidate's core specialization. Additionally, while the candidate has 10+ years of experience, the heavy infrastructure and data engineering focus makes it a weak technical fit.</t>
         </is>
       </c>
       <c r="I96" s="3" t="inlineStr">
@@ -6565,7 +6565,7 @@
       </c>
       <c r="M96" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/head-of-data-analytics-at-right-calibre-consulting-4459174081?position=24&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=dZTHuLROd%2FTUDsdWxlHCPg%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/manager-%E2%80%93-data-engineering-architecture-reporting-platform-dubai-abu-dhabi-at-agthia-group-pjsc-4457225736?position=30&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=uCZRYkPcw%2FLl2O0EJmhVdQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -6575,17 +6575,17 @@
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>Customer Intelligence Manager</t>
+          <t>Research Informatics Data Engineer</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>Al Tayer Insignia</t>
+          <t>Lundbeck</t>
         </is>
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t>Dubai, Dubai, United Arab Emirates</t>
+          <t>Copenhagen, Capital Region of Denmark, Denmark</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
@@ -6593,17 +6593,17 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F97" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="G97" s="9" t="inlineStr">
+      <c r="F97" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="G97" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H97" s="3" t="inlineStr">
         <is>
-          <t>This Customer Intelligence Manager role focuses on market research, consumer insights, and retail analytics rather than Generative AI, LLMs, or agentic systems. It represents a fundamental domain mismatch for the candidate's specialized technical profile.</t>
+          <t>This is a Research Informatics Data Engineer role focusing on life sciences data management, laboratory informatics, and scientific platform integration rather than Generative AI or advanced LLM application development. While LLMs are briefly mentioned as an optional tool for coding assistance, the candidate's core specialization in multi-agent orchestration, RAG architectures, and production GenAI systems does not align with this software/data engineering workflow role.</t>
         </is>
       </c>
       <c r="I97" s="3" t="inlineStr">
@@ -6628,7 +6628,7 @@
       </c>
       <c r="M97" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/customer-intelligence-manager-at-al-tayer-insignia-4457235794?position=9&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=PiyoN3pPhVcxMx9vtAIf5g%3D%3D</t>
+          <t>https://dk.linkedin.com/jobs/view/research-informatics-data-engineer-at-lundbeck-4448898202?position=5&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=5fkJnjfpF2QdhMDLztM5Vw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -6638,12 +6638,12 @@
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>Service Review Insights Lead</t>
+          <t>Head of Data Analytics</t>
         </is>
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>Discovered MENA</t>
+          <t>Right Calibre Consulting</t>
         </is>
       </c>
       <c r="D98" s="3" t="inlineStr">
@@ -6656,17 +6656,17 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F98" s="8" t="n">
+      <c r="F98" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="G98" s="9" t="inlineStr">
+      <c r="G98" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H98" s="3" t="inlineStr">
         <is>
-          <t>This role focuses heavily on operational analytics, call center metrics, and executive board presentations with no connection to Generative AI, LLMs, or data science. It is completely outside the candidate's core technical specialization and domain.</t>
+          <t>This is a Head of Data Analytics role focused on traditional BI, commercial insights, data governance, and leading analytics teams in the media and technology sector. It completely lacks any GenAI, LLM, or agentic AI focus, and the Head/Director-level leadership scope exceeds the candidate's current Lead Data Scientist level.</t>
         </is>
       </c>
       <c r="I98" s="3" t="inlineStr">
@@ -6691,7 +6691,7 @@
       </c>
       <c r="M98" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/service-review-insights-lead-at-discovered-mena-4456958136?position=10&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=oMos4kbDfkh42RiAd%2Bimnw%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/head-of-data-analytics-at-right-calibre-consulting-4459174081?position=24&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=dZTHuLROd%2FTUDsdWxlHCPg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -6701,12 +6701,12 @@
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>QEHS Digital Analyst - UAE National</t>
+          <t>Customer Intelligence Manager</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>Siemens Energy</t>
+          <t>Al Tayer Insignia</t>
         </is>
       </c>
       <c r="D99" s="3" t="inlineStr">
@@ -6719,17 +6719,17 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F99" s="8" t="n">
+      <c r="F99" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="G99" s="9" t="inlineStr">
+      <c r="G99" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H99" s="3" t="inlineStr">
         <is>
-          <t>This role is focused on Quality, Environment, Health, and Safety (QEHS) digital transformation, enterprise systems like SAP and Salesforce, and quality management standards rather than Generative AI or LLM specialization. It represents a significant domain and technical mismatch for a Lead Data Scientist specializing in agentic AI and RAG architectures.</t>
+          <t>This Customer Intelligence Manager role focuses on market research, consumer insights, and retail analytics rather than Generative AI, LLMs, or agentic systems. It represents a fundamental domain mismatch for the candidate's specialized technical profile.</t>
         </is>
       </c>
       <c r="I99" s="3" t="inlineStr">
@@ -6754,7 +6754,7 @@
       </c>
       <c r="M99" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/qehs-digital-analyst-uae-national-at-siemens-energy-4439835820?position=8&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=jLKXnOBvB%2BaDszNV2BAbbA%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/customer-intelligence-manager-at-al-tayer-insignia-4457235794?position=9&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=PiyoN3pPhVcxMx9vtAIf5g%3D%3D</t>
         </is>
       </c>
     </row>
@@ -6764,17 +6764,17 @@
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>Data Analyst - UAE National, ICQA/LND Analytics Team</t>
+          <t>Service Review Insights Lead</t>
         </is>
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Discovered MENA</t>
         </is>
       </c>
       <c r="D100" s="3" t="inlineStr">
         <is>
-          <t>Dubai, Dubai, United Arab Emirates</t>
+          <t>Dubai, United Arab Emirates</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -6782,17 +6782,17 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F100" s="8" t="n">
+      <c r="F100" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="G100" s="9" t="inlineStr">
+      <c r="G100" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H100" s="3" t="inlineStr">
         <is>
-          <t>This Data Analyst role at Amazon focuses on SQL reporting, dashboards, and operational data management, lacking any connection to the candidate's core GenAI, LLMs, and agentic AI specialization. Furthermore, the role is restricted to UAE Nationals and represents a significant mismatch in domain and function.</t>
+          <t>This role focuses heavily on operational analytics, call center metrics, and executive board presentations with no connection to Generative AI, LLMs, or data science. It is completely outside the candidate's core technical specialization and domain.</t>
         </is>
       </c>
       <c r="I100" s="3" t="inlineStr">
@@ -6817,7 +6817,7 @@
       </c>
       <c r="M100" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/data-analyst-uae-national-icqa-lnd-analytics-team-at-amazon-4459169756?position=7&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=dtuARx3ylMmIho9xSQNgYg%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/service-review-insights-lead-at-discovered-mena-4456958136?position=10&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=oMos4kbDfkh42RiAd%2Bimnw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -6827,12 +6827,12 @@
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>Senior Data Analyst - Strategy</t>
+          <t>QEHS Digital Analyst - UAE National</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>dubizzle</t>
+          <t>Siemens Energy</t>
         </is>
       </c>
       <c r="D101" s="3" t="inlineStr">
@@ -6845,17 +6845,17 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F101" s="8" t="n">
+      <c r="F101" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="G101" s="9" t="inlineStr">
+      <c r="G101" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H101" s="3" t="inlineStr">
         <is>
-          <t>This is a Senior Data Analyst - Strategy role focused on business analytics, executive dashboards, and commercial growth rather than AI, lacking any GenAI, LLM, or agentic specialization. Additionally, it represents a domain and functional mismatch for an AI/ML Lead Data Scientist.</t>
+          <t>This role is focused on Quality, Environment, Health, and Safety (QEHS) digital transformation, enterprise systems like SAP and Salesforce, and quality management standards rather than Generative AI or LLM specialization. It represents a significant domain and technical mismatch for a Lead Data Scientist specializing in agentic AI and RAG architectures.</t>
         </is>
       </c>
       <c r="I101" s="3" t="inlineStr">
@@ -6880,7 +6880,7 @@
       </c>
       <c r="M101" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/senior-data-analyst-strategy-at-dubizzle-4446647656?position=5&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=oDSAohEFPlpSK2IK3vFpNg%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/qehs-digital-analyst-uae-national-at-siemens-energy-4439835820?position=8&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=jLKXnOBvB%2BaDszNV2BAbbA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -6890,17 +6890,17 @@
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Data Analyst - UAE National, ICQA/LND Analytics Team</t>
         </is>
       </c>
       <c r="C102" s="3" t="inlineStr">
         <is>
-          <t>Insify</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="D102" s="3" t="inlineStr">
         <is>
-          <t>Amsterdam, North Holland, Netherlands</t>
+          <t>Dubai, Dubai, United Arab Emirates</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -6908,22 +6908,22 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F102" s="8" t="n">
+      <c r="F102" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="G102" s="9" t="inlineStr">
+      <c r="G102" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H102" s="3" t="inlineStr">
         <is>
-          <t>This is a classical Data Analyst role focused on SQL, A/B testing, and business metrics, which is completely unrelated to the candidate's core specialization in Generative AI, LLMs, and agentic workflows.</t>
+          <t>This Data Analyst role at Amazon focuses on SQL reporting, dashboards, and operational data management, lacking any connection to the candidate's core GenAI, LLMs, and agentic AI specialization. Furthermore, the role is restricted to UAE Nationals and represents a significant mismatch in domain and function.</t>
         </is>
       </c>
       <c r="I102" s="3" t="inlineStr">
         <is>
-          <t>Yes - German required (see JD for exact level)</t>
+          <t>Not stated in JD</t>
         </is>
       </c>
       <c r="J102" s="3" t="inlineStr">
@@ -6943,7 +6943,7 @@
       </c>
       <c r="M102" s="6" t="inlineStr">
         <is>
-          <t>https://nl.linkedin.com/jobs/view/data-analyst-at-insify-4457952341?position=26&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=kZIox38P2PV0MRG6Tih7Dw%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/data-analyst-uae-national-icqa-lnd-analytics-team-at-amazon-4459169756?position=7&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=dtuARx3ylMmIho9xSQNgYg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -6953,17 +6953,17 @@
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>Research Analyst - NL</t>
+          <t>Senior Data Analyst - Strategy</t>
         </is>
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>OPEN Health</t>
+          <t>dubizzle</t>
         </is>
       </c>
       <c r="D103" s="3" t="inlineStr">
         <is>
-          <t>Rotterdam, South Holland, Netherlands</t>
+          <t>Dubai, Dubai, United Arab Emirates</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
@@ -6971,17 +6971,17 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F103" s="8" t="n">
+      <c r="F103" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="G103" s="9" t="inlineStr">
+      <c r="G103" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H103" s="3" t="inlineStr">
         <is>
-          <t>This role focuses on health economics, meta-analysis, and HEOR modeling (cost-effectiveness, budget impact) using R and statistical software, which is completely unrelated to the candidate's GenAI, LLMs, and agentic AI specialization.</t>
+          <t>This is a Senior Data Analyst - Strategy role focused on business analytics, executive dashboards, and commercial growth rather than AI, lacking any GenAI, LLM, or agentic specialization. Additionally, it represents a domain and functional mismatch for an AI/ML Lead Data Scientist.</t>
         </is>
       </c>
       <c r="I103" s="3" t="inlineStr">
@@ -7006,7 +7006,7 @@
       </c>
       <c r="M103" s="6" t="inlineStr">
         <is>
-          <t>https://nl.linkedin.com/jobs/view/research-analyst-nl-at-open-health-4457247414?position=28&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=lxrHLFZXxcKuwp8%2F8mz0KA%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/senior-data-analyst-strategy-at-dubizzle-4446647656?position=5&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=oDSAohEFPlpSK2IK3vFpNg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -7016,17 +7016,17 @@
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>Data Analyst / Data Scientist</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t>Trinamics</t>
+          <t>Insify</t>
         </is>
       </c>
       <c r="D104" s="3" t="inlineStr">
         <is>
-          <t>North Brabant, Netherlands</t>
+          <t>Amsterdam, North Holland, Netherlands</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
@@ -7034,22 +7034,22 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F104" s="8" t="n">
+      <c r="F104" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="G104" s="9" t="inlineStr">
+      <c r="G104" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H104" s="3" t="inlineStr">
         <is>
-          <t>This is a financial reporting, data analysis, and dashboard-building role focusing on SAP, Spotfire, and Power BI with no connection to Generative AI, LLMs, or agentic systems. It is entirely unrelated to the candidate's core specialization and represents a major mismatch in domain and technical stack.</t>
+          <t>This is a classical Data Analyst role focused on SQL, A/B testing, and business metrics, which is completely unrelated to the candidate's core specialization in Generative AI, LLMs, and agentic workflows.</t>
         </is>
       </c>
       <c r="I104" s="3" t="inlineStr">
         <is>
-          <t>Not stated in JD</t>
+          <t>Yes - German required (see JD for exact level)</t>
         </is>
       </c>
       <c r="J104" s="3" t="inlineStr">
@@ -7069,7 +7069,7 @@
       </c>
       <c r="M104" s="6" t="inlineStr">
         <is>
-          <t>https://nl.linkedin.com/jobs/view/data-analyst-data-scientist-at-trinamics-4459172477?position=15&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=wKQaRNJqc3u7QhTWjoCU%2FQ%3D%3D</t>
+          <t>https://nl.linkedin.com/jobs/view/data-analyst-at-insify-4457952341?position=26&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=kZIox38P2PV0MRG6Tih7Dw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -7079,17 +7079,17 @@
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>De Rijksoverheid zoekt: Data scientist AI driven weather model</t>
+          <t>Research Analyst - NL</t>
         </is>
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>KNMI - Royal Netherlands Meteorological Institute</t>
+          <t>OPEN Health</t>
         </is>
       </c>
       <c r="D105" s="3" t="inlineStr">
         <is>
-          <t>De Bilt, Utrecht, Netherlands</t>
+          <t>Rotterdam, South Holland, Netherlands</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
@@ -7097,17 +7097,17 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F105" s="8" t="n">
+      <c r="F105" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="G105" s="9" t="inlineStr">
+      <c r="G105" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H105" s="3" t="inlineStr">
         <is>
-          <t>This role focuses on specialized deep learning for meteorological modeling, graph neural networks, and diffusion models applied to weather forecasting, which has virtually no overlap with the candidate's core GenAI, LLMs, and agentic AI specialization.</t>
+          <t>This role focuses on health economics, meta-analysis, and HEOR modeling (cost-effectiveness, budget impact) using R and statistical software, which is completely unrelated to the candidate's GenAI, LLMs, and agentic AI specialization.</t>
         </is>
       </c>
       <c r="I105" s="3" t="inlineStr">
@@ -7132,7 +7132,7 @@
       </c>
       <c r="M105" s="6" t="inlineStr">
         <is>
-          <t>https://nl.linkedin.com/jobs/view/de-rijksoverheid-zoekt-data-scientist-ai-driven-weather-model-at-knmi-royal-netherlands-meteorological-institute-4459321694?position=7&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=uEDe9phb4vscnrkupOYRog%3D%3D</t>
+          <t>https://nl.linkedin.com/jobs/view/research-analyst-nl-at-open-health-4457247414?position=28&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=lxrHLFZXxcKuwp8%2F8mz0KA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -7142,17 +7142,17 @@
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t>Decision Scientist, Trust &amp; Safety</t>
+          <t>Data Analyst / Data Scientist</t>
         </is>
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t>Vinted</t>
+          <t>Trinamics</t>
         </is>
       </c>
       <c r="D106" s="3" t="inlineStr">
         <is>
-          <t>Amsterdam, North Holland, Netherlands</t>
+          <t>North Brabant, Netherlands</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
@@ -7160,22 +7160,22 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F106" s="8" t="n">
+      <c r="F106" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="G106" s="9" t="inlineStr">
+      <c r="G106" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H106" s="3" t="inlineStr">
         <is>
-          <t>This is a Decision Scientist role focused on product experimentation, SQL/BI dashboards, and Trust &amp; Safety analytics, which is completely unrelated to the candidate's core specialization in Generative AI, LLMs, and agentic workflows.</t>
+          <t>This is a financial reporting, data analysis, and dashboard-building role focusing on SAP, Spotfire, and Power BI with no connection to Generative AI, LLMs, or agentic systems. It is entirely unrelated to the candidate's core specialization and represents a major mismatch in domain and technical stack.</t>
         </is>
       </c>
       <c r="I106" s="3" t="inlineStr">
         <is>
-          <t>No - English fluency stated as sufficient</t>
+          <t>Not stated in JD</t>
         </is>
       </c>
       <c r="J106" s="3" t="inlineStr">
@@ -7195,7 +7195,7 @@
       </c>
       <c r="M106" s="6" t="inlineStr">
         <is>
-          <t>https://nl.linkedin.com/jobs/view/decision-scientist-trust-safety-at-vinted-4431734156?position=13&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=5DKFgkv450iADwhSNzZiDw%3D%3D</t>
+          <t>https://nl.linkedin.com/jobs/view/data-analyst-data-scientist-at-trinamics-4459172477?position=15&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=wKQaRNJqc3u7QhTWjoCU%2FQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -7205,17 +7205,17 @@
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - System Optimization</t>
+          <t>De Rijksoverheid zoekt: Data scientist AI driven weather model</t>
         </is>
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>Danfoss</t>
+          <t>KNMI - Royal Netherlands Meteorological Institute</t>
         </is>
       </c>
       <c r="D107" s="3" t="inlineStr">
         <is>
-          <t>Copenhagen, Capital Region of Denmark, Denmark</t>
+          <t>De Bilt, Utrecht, Netherlands</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
@@ -7223,22 +7223,22 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F107" s="8" t="n">
+      <c r="F107" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="G107" s="9" t="inlineStr">
+      <c r="G107" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H107" s="3" t="inlineStr">
         <is>
-          <t>This is a Senior Data Scientist role focused on physical modelling, thermo-hydraulic simulation, and Mixed-Integer Linear Programming (MILP) for energy networks, which has zero overlap with the candidate's core specialization in Generative AI, LLMs, and agentic systems.</t>
+          <t>This role focuses on specialized deep learning for meteorological modeling, graph neural networks, and diffusion models applied to weather forecasting, which has virtually no overlap with the candidate's core GenAI, LLMs, and agentic AI specialization.</t>
         </is>
       </c>
       <c r="I107" s="3" t="inlineStr">
         <is>
-          <t>No - English fluency stated as sufficient</t>
+          <t>Not stated in JD</t>
         </is>
       </c>
       <c r="J107" s="3" t="inlineStr">
@@ -7258,7 +7258,7 @@
       </c>
       <c r="M107" s="6" t="inlineStr">
         <is>
-          <t>https://dk.linkedin.com/jobs/view/senior-data-scientist-system-optimization-at-danfoss-4459328391?position=28&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=pWSiaSPEvTB%2Fj17raCtBPA%3D%3D</t>
+          <t>https://nl.linkedin.com/jobs/view/de-rijksoverheid-zoekt-data-scientist-ai-driven-weather-model-at-knmi-royal-netherlands-meteorological-institute-4459321694?position=7&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=uEDe9phb4vscnrkupOYRog%3D%3D</t>
         </is>
       </c>
     </row>
@@ -7268,17 +7268,17 @@
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - System Optimization</t>
+          <t>Decision Scientist, Trust &amp; Safety</t>
         </is>
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t>Danfoss</t>
+          <t>Vinted</t>
         </is>
       </c>
       <c r="D108" s="3" t="inlineStr">
         <is>
-          <t>Kolding, Region of Southern Denmark, Denmark</t>
+          <t>Amsterdam, North Holland, Netherlands</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
@@ -7286,17 +7286,17 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F108" s="8" t="n">
+      <c r="F108" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="G108" s="9" t="inlineStr">
+      <c r="G108" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H108" s="3" t="inlineStr">
         <is>
-          <t>This is a Senior Data Scientist role focused on physical modelling, thermo-hydraulic simulation of energy networks, and Mixed-Integer Linear Programming (MILP), which is entirely unrelated to the candidate's core specialization in Generative AI, LLMs, and agentic systems.</t>
+          <t>This is a Decision Scientist role focused on product experimentation, SQL/BI dashboards, and Trust &amp; Safety analytics, which is completely unrelated to the candidate's core specialization in Generative AI, LLMs, and agentic workflows.</t>
         </is>
       </c>
       <c r="I108" s="3" t="inlineStr">
@@ -7321,7 +7321,7 @@
       </c>
       <c r="M108" s="6" t="inlineStr">
         <is>
-          <t>https://dk.linkedin.com/jobs/view/senior-data-scientist-system-optimization-at-danfoss-4459334294?position=29&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=6IO8CqSe4TjOJrnH%2BoTbig%3D%3D</t>
+          <t>https://nl.linkedin.com/jobs/view/decision-scientist-trust-safety-at-vinted-4431734156?position=13&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=5DKFgkv450iADwhSNzZiDw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -7331,17 +7331,17 @@
       </c>
       <c r="B109" s="3" t="inlineStr">
         <is>
-          <t>Product Owner</t>
+          <t>Senior Data Scientist - System Optimization</t>
         </is>
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>Ørsted</t>
+          <t>Danfoss</t>
         </is>
       </c>
       <c r="D109" s="3" t="inlineStr">
         <is>
-          <t>Gentofte, Capital Region of Denmark, Denmark</t>
+          <t>Copenhagen, Capital Region of Denmark, Denmark</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
@@ -7349,22 +7349,22 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F109" s="8" t="n">
+      <c r="F109" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="G109" s="9" t="inlineStr">
+      <c r="G109" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H109" s="3" t="inlineStr">
         <is>
-          <t>This is a Product Owner role focused on quantitative analytics, portfolio models, and trading infrastructure rather than a hands-on Generative AI or data science engineering position. It is completely outside the candidate's core specialization in LLMs, RAG, and agentic systems, and involves product management responsibilities rather than technical AI development.</t>
+          <t>This is a Senior Data Scientist role focused on physical modelling, thermo-hydraulic simulation, and Mixed-Integer Linear Programming (MILP) for energy networks, which has zero overlap with the candidate's core specialization in Generative AI, LLMs, and agentic systems.</t>
         </is>
       </c>
       <c r="I109" s="3" t="inlineStr">
         <is>
-          <t>Not stated in JD</t>
+          <t>No - English fluency stated as sufficient</t>
         </is>
       </c>
       <c r="J109" s="3" t="inlineStr">
@@ -7384,7 +7384,7 @@
       </c>
       <c r="M109" s="6" t="inlineStr">
         <is>
-          <t>https://dk.linkedin.com/jobs/view/product-owner-at-%C3%B8rsted-4457976275?position=30&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=kwPJx%2Freb7nWWcV4YkYqtg%3D%3D</t>
+          <t>https://dk.linkedin.com/jobs/view/senior-data-scientist-system-optimization-at-danfoss-4459328391?position=28&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=pWSiaSPEvTB%2Fj17raCtBPA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -7394,17 +7394,17 @@
       </c>
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t>Product Owner</t>
+          <t>Senior Data Scientist - System Optimization</t>
         </is>
       </c>
       <c r="C110" s="3" t="inlineStr">
         <is>
-          <t>Ørsted</t>
+          <t>Danfoss</t>
         </is>
       </c>
       <c r="D110" s="3" t="inlineStr">
         <is>
-          <t>Gentofte, Capital Region of Denmark, Denmark</t>
+          <t>Kolding, Region of Southern Denmark, Denmark</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
@@ -7412,22 +7412,22 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F110" s="8" t="n">
+      <c r="F110" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="G110" s="9" t="inlineStr">
+      <c r="G110" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H110" s="3" t="inlineStr">
         <is>
-          <t>This is a Product Owner role focused on commodity and energy trading platforms rather than a hands-on technical Generative AI, LLM, or agentic AI role. There is a severe mismatch in job function and seniority focus, as the candidate is a technical Lead Data Scientist specializing in hands-on GenAI systems.</t>
+          <t>This is a Senior Data Scientist role focused on physical modelling, thermo-hydraulic simulation of energy networks, and Mixed-Integer Linear Programming (MILP), which is entirely unrelated to the candidate's core specialization in Generative AI, LLMs, and agentic systems.</t>
         </is>
       </c>
       <c r="I110" s="3" t="inlineStr">
         <is>
-          <t>Not stated in JD</t>
+          <t>No - English fluency stated as sufficient</t>
         </is>
       </c>
       <c r="J110" s="3" t="inlineStr">
@@ -7447,7 +7447,7 @@
       </c>
       <c r="M110" s="6" t="inlineStr">
         <is>
-          <t>https://dk.linkedin.com/jobs/view/product-owner-at-%C3%B8rsted-4457969343?position=16&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=Srm0W8oPqBLXtVvd0AdJlg%3D%3D</t>
+          <t>https://dk.linkedin.com/jobs/view/senior-data-scientist-system-optimization-at-danfoss-4459334294?position=29&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=6IO8CqSe4TjOJrnH%2BoTbig%3D%3D</t>
         </is>
       </c>
     </row>
@@ -7457,17 +7457,17 @@
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>Dataspecialist - Afd. for Uddannelse og Studerende</t>
+          <t>Product Owner</t>
         </is>
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>DTU - Technical University of Denmark</t>
+          <t>Ørsted</t>
         </is>
       </c>
       <c r="D111" s="3" t="inlineStr">
         <is>
-          <t>Kongens Lyngby, Capital Region of Denmark, Denmark</t>
+          <t>Gentofte, Capital Region of Denmark, Denmark</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
@@ -7475,17 +7475,17 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F111" s="8" t="n">
+      <c r="F111" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="G111" s="9" t="inlineStr">
+      <c r="G111" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H111" s="3" t="inlineStr">
         <is>
-          <t>This role at DTU focuses on educational data analysis, stakeholder communication, and business intelligence reporting within a university setting, completely lacking any connection to the candidate's core GenAI, LLMs, or agentic AI specialization.</t>
+          <t>This is a Product Owner role focused on quantitative analytics, portfolio models, and trading infrastructure rather than a hands-on Generative AI or data science engineering position. It is completely outside the candidate's core specialization in LLMs, RAG, and agentic systems, and involves product management responsibilities rather than technical AI development.</t>
         </is>
       </c>
       <c r="I111" s="3" t="inlineStr">
@@ -7510,7 +7510,7 @@
       </c>
       <c r="M111" s="6" t="inlineStr">
         <is>
-          <t>https://dk.linkedin.com/jobs/view/dataspecialist-afd-for-uddannelse-og-studerende-at-dtu-technical-university-of-denmark-4458711406?position=12&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=jpgFSNpWhcVL9zGHYU%2Fxbw%3D%3D</t>
+          <t>https://dk.linkedin.com/jobs/view/product-owner-at-%C3%B8rsted-4457976275?position=30&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=kwPJx%2Freb7nWWcV4YkYqtg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -7520,17 +7520,17 @@
       </c>
       <c r="B112" s="3" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Product Owner</t>
         </is>
       </c>
       <c r="C112" s="3" t="inlineStr">
         <is>
-          <t>Abacus Medicine Group</t>
+          <t>Ørsted</t>
         </is>
       </c>
       <c r="D112" s="3" t="inlineStr">
         <is>
-          <t>Copenhagen, Capital Region of Denmark, Denmark</t>
+          <t>Gentofte, Capital Region of Denmark, Denmark</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
@@ -7538,17 +7538,17 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F112" s="8" t="n">
+      <c r="F112" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="G112" s="9" t="inlineStr">
+      <c r="G112" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H112" s="3" t="inlineStr">
         <is>
-          <t>This is a Data Engineer role focusing on data pipelines, infrastructure, and warehousing, which is entirely unrelated to the candidate's core specialization in Generative AI, LLMs, and agentic workflows. Furthermore, the role is aimed at someone starting their career in data engineering, representing a major seniority mismatch for a Lead Data Scientist with 10 years of experience.</t>
+          <t>This is a Product Owner role focused on commodity and energy trading platforms rather than a hands-on technical Generative AI, LLM, or agentic AI role. There is a severe mismatch in job function and seniority focus, as the candidate is a technical Lead Data Scientist specializing in hands-on GenAI systems.</t>
         </is>
       </c>
       <c r="I112" s="3" t="inlineStr">
@@ -7573,7 +7573,7 @@
       </c>
       <c r="M112" s="6" t="inlineStr">
         <is>
-          <t>https://dk.linkedin.com/jobs/view/data-engineer-at-abacus-medicine-group-4448014908?position=7&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=naNFtA2OuhXjDVLQEaIksw%3D%3D</t>
+          <t>https://dk.linkedin.com/jobs/view/product-owner-at-%C3%B8rsted-4457969343?position=16&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=Srm0W8oPqBLXtVvd0AdJlg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -7583,17 +7583,17 @@
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>Product Owner &amp; Analytics Engineer</t>
+          <t>Dataspecialist - Afd. for Uddannelse og Studerende</t>
         </is>
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>DTU - Technical University of Denmark</t>
         </is>
       </c>
       <c r="D113" s="3" t="inlineStr">
         <is>
-          <t>Viby, Region of Southern Denmark, Denmark</t>
+          <t>Kongens Lyngby, Capital Region of Denmark, Denmark</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
@@ -7601,17 +7601,17 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F113" s="8" t="n">
+      <c r="F113" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="G113" s="9" t="inlineStr">
+      <c r="G113" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H113" s="3" t="inlineStr">
         <is>
-          <t>This role is a Product Owner and Analytics Engineer position focused on data platforms, BI, dbt, and stakeholder management rather than GenAI or LLM development. It is an extremely weak technical fit for a GenAI specialist.</t>
+          <t>This role at DTU focuses on educational data analysis, stakeholder communication, and business intelligence reporting within a university setting, completely lacking any connection to the candidate's core GenAI, LLMs, or agentic AI specialization.</t>
         </is>
       </c>
       <c r="I113" s="3" t="inlineStr">
@@ -7636,7 +7636,7 @@
       </c>
       <c r="M113" s="6" t="inlineStr">
         <is>
-          <t>https://dk.linkedin.com/jobs/view/product-owner-analytics-engineer-at-ok-4457992725?position=11&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=D2ySyPo8bFWVMMg%2FjecIMw%3D%3D</t>
+          <t>https://dk.linkedin.com/jobs/view/dataspecialist-afd-for-uddannelse-og-studerende-at-dtu-technical-university-of-denmark-4458711406?position=12&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=jpgFSNpWhcVL9zGHYU%2Fxbw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -7646,17 +7646,17 @@
       </c>
       <c r="B114" s="3" t="inlineStr">
         <is>
-          <t>Data Scientist - Energy Forecasting</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="C114" s="3" t="inlineStr">
         <is>
-          <t>Danfoss</t>
+          <t>Abacus Medicine Group</t>
         </is>
       </c>
       <c r="D114" s="3" t="inlineStr">
         <is>
-          <t>Kolding, Region of Southern Denmark, Denmark</t>
+          <t>Copenhagen, Capital Region of Denmark, Denmark</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
@@ -7664,22 +7664,22 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F114" s="8" t="n">
+      <c r="F114" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="G114" s="9" t="inlineStr">
+      <c r="G114" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H114" s="3" t="inlineStr">
         <is>
-          <t>This energy forecasting and physical systems role has zero overlap with the candidate's core specialization in Generative AI, LLMs, and agentic workflows, representing a completely different domain.</t>
+          <t>This is a Data Engineer role focusing on data pipelines, infrastructure, and warehousing, which is entirely unrelated to the candidate's core specialization in Generative AI, LLMs, and agentic workflows. Furthermore, the role is aimed at someone starting their career in data engineering, representing a major seniority mismatch for a Lead Data Scientist with 10 years of experience.</t>
         </is>
       </c>
       <c r="I114" s="3" t="inlineStr">
         <is>
-          <t>No - English fluency stated as sufficient</t>
+          <t>Not stated in JD</t>
         </is>
       </c>
       <c r="J114" s="3" t="inlineStr">
@@ -7699,7 +7699,7 @@
       </c>
       <c r="M114" s="6" t="inlineStr">
         <is>
-          <t>https://dk.linkedin.com/jobs/view/data-scientist-energy-forecasting-at-danfoss-4459332327?position=2&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=%2BhOuUASw5VgnQYgphl%2BfiQ%3D%3D</t>
+          <t>https://dk.linkedin.com/jobs/view/data-engineer-at-abacus-medicine-group-4448014908?position=7&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=naNFtA2OuhXjDVLQEaIksw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -7709,17 +7709,17 @@
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>Data Scientist - Energy Forecasting</t>
+          <t>Product Owner &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>Danfoss</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="D115" s="3" t="inlineStr">
         <is>
-          <t>Copenhagen, Capital Region of Denmark, Denmark</t>
+          <t>Viby, Region of Southern Denmark, Denmark</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
@@ -7727,22 +7727,22 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F115" s="8" t="n">
+      <c r="F115" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="G115" s="9" t="inlineStr">
+      <c r="G115" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H115" s="3" t="inlineStr">
         <is>
-          <t>This is a classical machine learning role focused entirely on energy demand forecasting, time-series modeling, and physical systems for district heating, which has no overlap with the candidate's core specialization in Generative AI, LLMs, and agentic workflows.</t>
+          <t>This role is a Product Owner and Analytics Engineer position focused on data platforms, BI, dbt, and stakeholder management rather than GenAI or LLM development. It is an extremely weak technical fit for a GenAI specialist.</t>
         </is>
       </c>
       <c r="I115" s="3" t="inlineStr">
         <is>
-          <t>No - English fluency stated as sufficient</t>
+          <t>Not stated in JD</t>
         </is>
       </c>
       <c r="J115" s="3" t="inlineStr">
@@ -7762,7 +7762,7 @@
       </c>
       <c r="M115" s="6" t="inlineStr">
         <is>
-          <t>https://dk.linkedin.com/jobs/view/data-scientist-energy-forecasting-at-danfoss-4459316434?position=1&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=Jfk6JIiJcse1eCPfqN9rvg%3D%3D</t>
+          <t>https://dk.linkedin.com/jobs/view/product-owner-analytics-engineer-at-ok-4457992725?position=11&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=D2ySyPo8bFWVMMg%2FjecIMw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -7772,40 +7772,40 @@
       </c>
       <c r="B116" s="3" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Engineer (EMIRATI)</t>
+          <t>Data Scientist - Energy Forecasting</t>
         </is>
       </c>
       <c r="C116" s="3" t="inlineStr">
         <is>
-          <t>Salt</t>
+          <t>Danfoss</t>
         </is>
       </c>
       <c r="D116" s="3" t="inlineStr">
         <is>
-          <t>Abu Dhabi Emirate, United Arab Emirates</t>
+          <t>Kolding, Region of Southern Denmark, Denmark</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="F116" s="8" t="n">
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="F116" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="G116" s="9" t="inlineStr">
+      <c r="G116" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H116" s="3" t="inlineStr">
         <is>
-          <t>The role requires an early-career software engineer with 2+ years of experience, representing a significant seniority mismatch for a Lead Data Scientist with 10+ years of experience. Furthermore, the position explicitly specifies that it is for Emirati nationals only.</t>
+          <t>This energy forecasting and physical systems role has zero overlap with the candidate's core specialization in Generative AI, LLMs, and agentic workflows, representing a completely different domain.</t>
         </is>
       </c>
       <c r="I116" s="3" t="inlineStr">
         <is>
-          <t>Not stated in JD</t>
+          <t>No - English fluency stated as sufficient</t>
         </is>
       </c>
       <c r="J116" s="3" t="inlineStr">
@@ -7825,7 +7825,7 @@
       </c>
       <c r="M116" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/artificial-intelligence-engineer-emirati-at-salt-4457723960?position=26&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=OL7voNOllXDyxcDmkFiWQw%3D%3D</t>
+          <t>https://dk.linkedin.com/jobs/view/data-scientist-energy-forecasting-at-danfoss-4459332327?position=2&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=%2BhOuUASw5VgnQYgphl%2BfiQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -7835,17 +7835,17 @@
       </c>
       <c r="B117" s="3" t="inlineStr">
         <is>
-          <t>Junior Research Scientist In the Division of Engineering (Electrical and Computer Engineering) - Dr. Fang Yi</t>
+          <t>Data Scientist - Energy Forecasting</t>
         </is>
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t>New York University Abu Dhabi</t>
+          <t>Danfoss</t>
         </is>
       </c>
       <c r="D117" s="3" t="inlineStr">
         <is>
-          <t>Abu Dhabi, Abu Dhabi Emirate, United Arab Emirates</t>
+          <t>Copenhagen, Capital Region of Denmark, Denmark</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
@@ -7853,27 +7853,27 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F117" s="8" t="n">
+      <c r="F117" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="G117" s="9" t="inlineStr">
+      <c r="G117" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H117" s="3" t="inlineStr">
         <is>
-          <t>This is an academic research scientist role focused on robotics, embodied AI, and assistive technologies, which does not align with the candidate's core specialization in enterprise Generative AI, LLMs, and RAG. Additionally, there is a major seniority mismatch as the role targets junior researchers with under five years of experience, whereas the candidate is a Lead Data Scientist with 10+ years of experience.</t>
+          <t>This is a classical machine learning role focused entirely on energy demand forecasting, time-series modeling, and physical systems for district heating, which has no overlap with the candidate's core specialization in Generative AI, LLMs, and agentic workflows.</t>
         </is>
       </c>
       <c r="I117" s="3" t="inlineStr">
         <is>
-          <t>Not stated in JD</t>
+          <t>No - English fluency stated as sufficient</t>
         </is>
       </c>
       <c r="J117" s="3" t="inlineStr">
         <is>
-          <t>Possible - relocation support mentioned, visa not explicit</t>
+          <t>Not stated in JD</t>
         </is>
       </c>
       <c r="K117" s="2" t="inlineStr">
@@ -7888,7 +7888,7 @@
       </c>
       <c r="M117" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/junior-research-scientist-in-the-division-of-engineering-electrical-and-computer-engineering-dr-fang-yi-at-new-york-university-abu-dhabi-4448981054?position=17&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=Quv11sfD16F354%2FzN0KXRg%3D%3D</t>
+          <t>https://dk.linkedin.com/jobs/view/data-scientist-energy-forecasting-at-danfoss-4459316434?position=1&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=Jfk6JIiJcse1eCPfqN9rvg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -7898,12 +7898,12 @@
       </c>
       <c r="B118" s="3" t="inlineStr">
         <is>
-          <t>Business Intelligence Analytics</t>
+          <t>Artificial Intelligence Engineer (EMIRATI)</t>
         </is>
       </c>
       <c r="C118" s="3" t="inlineStr">
         <is>
-          <t>Confidential</t>
+          <t>Salt</t>
         </is>
       </c>
       <c r="D118" s="3" t="inlineStr">
@@ -7913,20 +7913,20 @@
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="F118" s="8" t="n">
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="F118" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="G118" s="9" t="inlineStr">
+      <c r="G118" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H118" s="3" t="inlineStr">
         <is>
-          <t>This is a Business Intelligence and reporting role focusing on traditional tools like SQL Server, Tableau, PowerBI, and IT service management, completely lacking any Generative AI, LLM, or agentic specialization. The candidate's advanced GenAI and data science background is a severe mismatch for this operational BI position.</t>
+          <t>The role requires an early-career software engineer with 2+ years of experience, representing a significant seniority mismatch for a Lead Data Scientist with 10+ years of experience. Furthermore, the position explicitly specifies that it is for Emirati nationals only.</t>
         </is>
       </c>
       <c r="I118" s="3" t="inlineStr">
@@ -7951,7 +7951,7 @@
       </c>
       <c r="M118" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/business-intelligence-analytics-at-pump-dynamics-4457247369?position=16&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=q3L54POb%2Ba8jMFybGRPVBA%3D%3D&amp;trk=public_jobs_jserp-result_search-card</t>
+          <t>https://ae.linkedin.com/jobs/view/artificial-intelligence-engineer-emirati-at-salt-4457723960?position=26&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=OL7voNOllXDyxcDmkFiWQw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -7961,12 +7961,12 @@
       </c>
       <c r="B119" s="3" t="inlineStr">
         <is>
-          <t>Data Analyst - UAE National, ICQA/LND Analytics Team</t>
+          <t>Junior Research Scientist In the Division of Engineering (Electrical and Computer Engineering) - Dr. Fang Yi</t>
         </is>
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>New York University Abu Dhabi</t>
         </is>
       </c>
       <c r="D119" s="3" t="inlineStr">
@@ -7979,17 +7979,17 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F119" s="8" t="n">
+      <c r="F119" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="G119" s="9" t="inlineStr">
+      <c r="G119" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H119" s="3" t="inlineStr">
         <is>
-          <t>This is a Data Analyst role focusing on standard reporting, SQL, QuickSight, and AWS data warehousing infrastructure, which is entirely unrelated to the candidate's core specialization in Generative AI, LLMs, and agentic workflows. Furthermore, there is a severe seniority and domain mismatch as the role targets data analysis rather than advanced AI leadership.</t>
+          <t>This is an academic research scientist role focused on robotics, embodied AI, and assistive technologies, which does not align with the candidate's core specialization in enterprise Generative AI, LLMs, and RAG. Additionally, there is a major seniority mismatch as the role targets junior researchers with under five years of experience, whereas the candidate is a Lead Data Scientist with 10+ years of experience.</t>
         </is>
       </c>
       <c r="I119" s="3" t="inlineStr">
@@ -7999,7 +7999,7 @@
       </c>
       <c r="J119" s="3" t="inlineStr">
         <is>
-          <t>Not stated in JD</t>
+          <t>Possible - relocation support mentioned, visa not explicit</t>
         </is>
       </c>
       <c r="K119" s="2" t="inlineStr">
@@ -8014,7 +8014,7 @@
       </c>
       <c r="M119" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/data-analyst-uae-national-icqa-lnd-analytics-team-at-amazon-4459175702?position=13&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=2u0HotRhWhUDg980ATy2nw%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/junior-research-scientist-in-the-division-of-engineering-electrical-and-computer-engineering-dr-fang-yi-at-new-york-university-abu-dhabi-4448981054?position=17&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=Quv11sfD16F354%2FzN0KXRg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -8024,35 +8024,35 @@
       </c>
       <c r="B120" s="3" t="inlineStr">
         <is>
-          <t>Mathematician (Remote)</t>
+          <t>Business Intelligence Analytics</t>
         </is>
       </c>
       <c r="C120" s="3" t="inlineStr">
         <is>
-          <t>Hired</t>
+          <t>Confidential</t>
         </is>
       </c>
       <c r="D120" s="3" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>Abu Dhabi Emirate, United Arab Emirates</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="F120" s="8" t="n">
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="F120" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="G120" s="9" t="inlineStr">
+      <c r="G120" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H120" s="3" t="inlineStr">
         <is>
-          <t>This remote contractor role focuses on pure applied mathematics and algorithmic optimization rather than Generative AI, LLMs, or agentic frameworks. While the candidate has a strong data science background, the job is entirely unrelated to his core GenAI and RAG specialization.</t>
+          <t>This is a Business Intelligence and reporting role focusing on traditional tools like SQL Server, Tableau, PowerBI, and IT service management, completely lacking any Generative AI, LLM, or agentic specialization. The candidate's advanced GenAI and data science background is a severe mismatch for this operational BI position.</t>
         </is>
       </c>
       <c r="I120" s="3" t="inlineStr">
@@ -8077,7 +8077,7 @@
       </c>
       <c r="M120" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/mathematician-remote-at-hired-4459651401?position=11&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=L0rt1zlpnHOlSTn4%2BjbBZg%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/business-intelligence-analytics-at-pump-dynamics-4457247369?position=16&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=q3L54POb%2Ba8jMFybGRPVBA%3D%3D&amp;trk=public_jobs_jserp-result_search-card</t>
         </is>
       </c>
     </row>
@@ -8087,35 +8087,35 @@
       </c>
       <c r="B121" s="3" t="inlineStr">
         <is>
-          <t>Statistician (Remote)</t>
+          <t>Data Analyst - UAE National, ICQA/LND Analytics Team</t>
         </is>
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>Hired</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="D121" s="3" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>Abu Dhabi, Abu Dhabi Emirate, United Arab Emirates</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="F121" s="8" t="n">
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="F121" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="G121" s="9" t="inlineStr">
+      <c r="G121" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H121" s="3" t="inlineStr">
         <is>
-          <t>This role focuses heavily on classical statistics, experimental design, and A/B testing, requiring a PhD in Statistics, which does not match the candidate's core GenAI and LLM specialization. Furthermore, it is a contract statistician role rather than an advanced AI engineering or agentic systems role.</t>
+          <t>This is a Data Analyst role focusing on standard reporting, SQL, QuickSight, and AWS data warehousing infrastructure, which is entirely unrelated to the candidate's core specialization in Generative AI, LLMs, and agentic workflows. Furthermore, there is a severe seniority and domain mismatch as the role targets data analysis rather than advanced AI leadership.</t>
         </is>
       </c>
       <c r="I121" s="3" t="inlineStr">
@@ -8140,7 +8140,7 @@
       </c>
       <c r="M121" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/statistician-remote-at-hired-4459636643?position=12&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=%2FKljESl%2B5ntTSKKRsgpGUg%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/data-analyst-uae-national-icqa-lnd-analytics-team-at-amazon-4459175702?position=13&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=2u0HotRhWhUDg980ATy2nw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -8150,17 +8150,17 @@
       </c>
       <c r="B122" s="3" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Mathematician (Remote)</t>
         </is>
       </c>
       <c r="C122" s="3" t="inlineStr">
         <is>
-          <t>TenneT</t>
+          <t>Hired</t>
         </is>
       </c>
       <c r="D122" s="3" t="inlineStr">
         <is>
-          <t>Arnhem, Gelderland, Netherlands</t>
+          <t>United Arab Emirates</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
@@ -8168,17 +8168,17 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="F122" s="8" t="n">
+      <c r="F122" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="G122" s="9" t="inlineStr">
+      <c r="G122" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H122" s="3" t="inlineStr">
         <is>
-          <t>This is a Data Engineer role focused on infrastructure, Java/Python backend development, Kubernetes, and streaming platforms like Apache Kafka, which is completely misaligned with the candidate's specialization in Generative AI, LLMs, and agentic workflows. Additionally, the role explicitly requires professional fluency in Dutch, which the candidate lacks.</t>
+          <t>This remote contractor role focuses on pure applied mathematics and algorithmic optimization rather than Generative AI, LLMs, or agentic frameworks. While the candidate has a strong data science background, the job is entirely unrelated to his core GenAI and RAG specialization.</t>
         </is>
       </c>
       <c r="I122" s="3" t="inlineStr">
@@ -8203,7 +8203,7 @@
       </c>
       <c r="M122" s="6" t="inlineStr">
         <is>
-          <t>https://nl.linkedin.com/jobs/view/data-engineer-at-tennet-4459682650?position=28&amp;pageNum=0&amp;refId=oiBIn1Czflg0JjZjH5z0Lg%3D%3D&amp;trackingId=VjGapIUBNcJsDHWWWnnyCQ%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/mathematician-remote-at-hired-4459651401?position=11&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=L0rt1zlpnHOlSTn4%2BjbBZg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -8213,17 +8213,17 @@
       </c>
       <c r="B123" s="3" t="inlineStr">
         <is>
-          <t>E-commerce Data Analyst</t>
+          <t>Statistician (Remote)</t>
         </is>
       </c>
       <c r="C123" s="3" t="inlineStr">
         <is>
-          <t>My Jewellery</t>
+          <t>Hired</t>
         </is>
       </c>
       <c r="D123" s="3" t="inlineStr">
         <is>
-          <t>’s-Hertogenbosch, North Brabant, Netherlands</t>
+          <t>United Arab Emirates</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
@@ -8231,17 +8231,17 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="F123" s="8" t="n">
+      <c r="F123" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="G123" s="9" t="inlineStr">
+      <c r="G123" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H123" s="3" t="inlineStr">
         <is>
-          <t>This is an e-commerce data analytics role focused on business intelligence, conversion rate optimization, and dashboards rather than Generative AI, LLMs, or agentic systems. Furthermore, the candidate's 10+ years of senior AI/ML and GenAI experience represent a severe overqualification mismatch for a role requiring around 2 years of e-commerce analytics experience.</t>
+          <t>This role focuses heavily on classical statistics, experimental design, and A/B testing, requiring a PhD in Statistics, which does not match the candidate's core GenAI and LLM specialization. Furthermore, it is a contract statistician role rather than an advanced AI engineering or agentic systems role.</t>
         </is>
       </c>
       <c r="I123" s="3" t="inlineStr">
@@ -8266,7 +8266,7 @@
       </c>
       <c r="M123" s="6" t="inlineStr">
         <is>
-          <t>https://nl.linkedin.com/jobs/view/e-commerce-data-analyst-at-my-jewellery-4458352332?position=24&amp;pageNum=0&amp;refId=oiBIn1Czflg0JjZjH5z0Lg%3D%3D&amp;trackingId=l7ZuY53wCY8i%2FsbUtVRI1w%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/statistician-remote-at-hired-4459636643?position=12&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=%2FKljESl%2B5ntTSKKRsgpGUg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -8276,17 +8276,17 @@
       </c>
       <c r="B124" s="3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="C124" s="3" t="inlineStr">
         <is>
-          <t>Kitopi</t>
+          <t>TenneT</t>
         </is>
       </c>
       <c r="D124" s="3" t="inlineStr">
         <is>
-          <t>Dubai, United Arab Emirates</t>
+          <t>Arnhem, Gelderland, Netherlands</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
@@ -8294,17 +8294,17 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="F124" s="8" t="n">
+      <c r="F124" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="G124" s="9" t="inlineStr">
+      <c r="G124" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H124" s="3" t="inlineStr">
         <is>
-          <t>This is a role for a Senior Data Engineer focused on building data pipelines, ELT processes, Snowflake, and dbt, which is completely unrelated to the candidate's core specialization as a Lead Data Scientist specializing in GenAI, LLMs, and agentic workflows.</t>
+          <t>This is a Data Engineer role focused on infrastructure, Java/Python backend development, Kubernetes, and streaming platforms like Apache Kafka, which is completely misaligned with the candidate's specialization in Generative AI, LLMs, and agentic workflows. Additionally, the role explicitly requires professional fluency in Dutch, which the candidate lacks.</t>
         </is>
       </c>
       <c r="I124" s="3" t="inlineStr">
@@ -8317,9 +8317,9 @@
           <t>Not stated in JD</t>
         </is>
       </c>
-      <c r="K124" s="7" t="inlineStr">
-        <is>
-          <t>New this run (2026-08-27 15:40 UTC)</t>
+      <c r="K124" s="2" t="inlineStr">
+        <is>
+          <t>From previous run</t>
         </is>
       </c>
       <c r="L124" s="2" t="inlineStr">
@@ -8329,7 +8329,7 @@
       </c>
       <c r="M124" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/senior-data-engineer-at-kitopi-4457746184?position=4&amp;pageNum=0&amp;refId=50H6yCrEXIuhgr6eqEojNg%3D%3D&amp;trackingId=brdZZnynoUz1kG72mAhlOg%3D%3D</t>
+          <t>https://nl.linkedin.com/jobs/view/data-engineer-at-tennet-4459682650?position=28&amp;pageNum=0&amp;refId=oiBIn1Czflg0JjZjH5z0Lg%3D%3D&amp;trackingId=VjGapIUBNcJsDHWWWnnyCQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -8339,17 +8339,17 @@
       </c>
       <c r="B125" s="3" t="inlineStr">
         <is>
-          <t>Total Rewards Analyst | Corporate Services | Dubai</t>
+          <t>E-commerce Data Analyst</t>
         </is>
       </c>
       <c r="C125" s="3" t="inlineStr">
         <is>
-          <t>Al-Futtaim</t>
+          <t>My Jewellery</t>
         </is>
       </c>
       <c r="D125" s="3" t="inlineStr">
         <is>
-          <t>Dubai, Dubai, United Arab Emirates</t>
+          <t>’s-Hertogenbosch, North Brabant, Netherlands</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
@@ -8357,17 +8357,17 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="F125" s="8" t="n">
+      <c r="F125" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="G125" s="9" t="inlineStr">
+      <c r="G125" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H125" s="3" t="inlineStr">
         <is>
-          <t>This is a Total Rewards (compensation and benefits) HR analyst role focused on HRIS systems, pay equity, and market benchmarking, completely unrelated to the candidate's core specialization in Generative AI, LLMs, and agentic workflows.</t>
+          <t>This is an e-commerce data analytics role focused on business intelligence, conversion rate optimization, and dashboards rather than Generative AI, LLMs, or agentic systems. Furthermore, the candidate's 10+ years of senior AI/ML and GenAI experience represent a severe overqualification mismatch for a role requiring around 2 years of e-commerce analytics experience.</t>
         </is>
       </c>
       <c r="I125" s="3" t="inlineStr">
@@ -8380,9 +8380,9 @@
           <t>Not stated in JD</t>
         </is>
       </c>
-      <c r="K125" s="7" t="inlineStr">
-        <is>
-          <t>New this run (2026-08-27 15:40 UTC)</t>
+      <c r="K125" s="2" t="inlineStr">
+        <is>
+          <t>From previous run</t>
         </is>
       </c>
       <c r="L125" s="2" t="inlineStr">
@@ -8392,7 +8392,7 @@
       </c>
       <c r="M125" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/total-rewards-analyst-corporate-services-dubai-at-al-futtaim-4449646903?position=8&amp;pageNum=0&amp;refId=50H6yCrEXIuhgr6eqEojNg%3D%3D&amp;trackingId=ZNz4Qjdr30DeI436luixFQ%3D%3D</t>
+          <t>https://nl.linkedin.com/jobs/view/e-commerce-data-analyst-at-my-jewellery-4458352332?position=24&amp;pageNum=0&amp;refId=oiBIn1Czflg0JjZjH5z0Lg%3D%3D&amp;trackingId=l7ZuY53wCY8i%2FsbUtVRI1w%3D%3D</t>
         </is>
       </c>
     </row>
@@ -8402,35 +8402,35 @@
       </c>
       <c r="B126" s="3" t="inlineStr">
         <is>
-          <t>Graphene Photonics Data Analyst (f/m/d)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="C126" s="3" t="inlineStr">
         <is>
-          <t>Black Semiconductor</t>
+          <t>Kitopi</t>
         </is>
       </c>
       <c r="D126" s="3" t="inlineStr">
         <is>
-          <t>Aachen, North Rhine-Westphalia, Germany</t>
+          <t>Dubai, United Arab Emirates</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="F126" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="G126" s="9" t="inlineStr">
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="F126" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="G126" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H126" s="3" t="inlineStr">
         <is>
-          <t>This role is entirely focused on semiconductor hardware, graphene photonics, and physical data analysis, with zero relevance to the candidate's core specialization in Generative AI, LLMs, and agentic workflows.</t>
+          <t>This is a role for a Senior Data Engineer focused on building data pipelines, ELT processes, Snowflake, and dbt, which is completely unrelated to the candidate's core specialization as a Lead Data Scientist specializing in GenAI, LLMs, and agentic workflows.</t>
         </is>
       </c>
       <c r="I126" s="3" t="inlineStr">
@@ -8455,7 +8455,7 @@
       </c>
       <c r="M126" s="6" t="inlineStr">
         <is>
-          <t>https://de.linkedin.com/jobs/view/graphene-photonics-data-analyst-f-m-d-at-black-semiconductor-4459334621?position=26&amp;pageNum=0&amp;refId=T%2F0KkBXL%2Fl%2B5Iv5tUGTY7Q%3D%3D&amp;trackingId=KgQ01De6ChDgIN8UxnUvXg%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/senior-data-engineer-at-kitopi-4457746184?position=4&amp;pageNum=0&amp;refId=50H6yCrEXIuhgr6eqEojNg%3D%3D&amp;trackingId=brdZZnynoUz1kG72mAhlOg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -8465,35 +8465,35 @@
       </c>
       <c r="B127" s="3" t="inlineStr">
         <is>
-          <t>Financial Planning and Analysis Manager</t>
+          <t>Total Rewards Analyst | Corporate Services | Dubai</t>
         </is>
       </c>
       <c r="C127" s="3" t="inlineStr">
         <is>
-          <t>Confidential Jobs</t>
+          <t>Al-Futtaim</t>
         </is>
       </c>
       <c r="D127" s="3" t="inlineStr">
         <is>
-          <t>Dubai, United Arab Emirates</t>
+          <t>Dubai, Dubai, United Arab Emirates</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="F127" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="G127" s="9" t="inlineStr">
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="F127" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="G127" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H127" s="3" t="inlineStr">
         <is>
-          <t>This Financial Planning and Analysis Manager role is entirely unrelated to data science, machine learning, or software engineering, focusing instead on corporate finance, budgeting, construction economics, and IFRS 15 accounting. There is a massive domain and seniority mismatch for an AI/GenAI Lead Data Scientist.</t>
+          <t>This is a Total Rewards (compensation and benefits) HR analyst role focused on HRIS systems, pay equity, and market benchmarking, completely unrelated to the candidate's core specialization in Generative AI, LLMs, and agentic workflows.</t>
         </is>
       </c>
       <c r="I127" s="3" t="inlineStr">
@@ -8518,7 +8518,7 @@
       </c>
       <c r="M127" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/financial-planning-and-analysis-manager-at-confidential-jobs-4452594332?position=29&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=KEfZVTEknZKckxH1vstrzQ%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/total-rewards-analyst-corporate-services-dubai-at-al-futtaim-4449646903?position=8&amp;pageNum=0&amp;refId=50H6yCrEXIuhgr6eqEojNg%3D%3D&amp;trackingId=ZNz4Qjdr30DeI436luixFQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -8528,12 +8528,12 @@
       </c>
       <c r="B128" s="3" t="inlineStr">
         <is>
-          <t>Data QA Engineer</t>
+          <t>Senior Technical Software Engineer - AI Computer Vision</t>
         </is>
       </c>
       <c r="C128" s="3" t="inlineStr">
         <is>
-          <t>ClearGrid</t>
+          <t>Emirates</t>
         </is>
       </c>
       <c r="D128" s="3" t="inlineStr">
@@ -8543,20 +8543,20 @@
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="F128" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="G128" s="9" t="inlineStr">
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="F128" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="G128" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H128" s="3" t="inlineStr">
         <is>
-          <t>This role is a Data QA Engineer focused entirely on data quality, dbt testing, and warehouse reconciliation in a fintech/collections environment, lacking any Generative AI, LLM, or agentic specialization. Furthermore, the seniority requirement (2+ years) is well below the candidate's 10+ years as a Lead Data Scientist.</t>
+          <t>This role is focused heavily on Computer Vision, video analytics, GPU-accelerated pipelines, and NVIDIA technologies (DeepStream, TensorRT, CUDA), which falls completely outside the candidate's core specialization in LLMs, RAG, and agentic AI. Although the candidate has foundational Python and ML experience, the domain mismatch results in a very low fit.</t>
         </is>
       </c>
       <c r="I128" s="3" t="inlineStr">
@@ -8569,9 +8569,9 @@
           <t>Not stated in JD</t>
         </is>
       </c>
-      <c r="K128" s="2" t="inlineStr">
-        <is>
-          <t>From previous run</t>
+      <c r="K128" s="9" t="inlineStr">
+        <is>
+          <t>New this run (2026-08-28 08:27 UTC)</t>
         </is>
       </c>
       <c r="L128" s="2" t="inlineStr">
@@ -8581,7 +8581,7 @@
       </c>
       <c r="M128" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/data-qa-engineer-at-cleargrid-4457980735?position=25&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=RbMMQ6DAm%2FMomlqBLUM2IQ%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/senior-technical-software-engineer-ai-computer-vision-at-emirates-4458006917?position=3&amp;pageNum=0&amp;refId=zJBbvwb5H0wsbJ5fs9ZTVw%3D%3D&amp;trackingId=tSUvFCM6ybpvpE988Qbxew%3D%3D</t>
         </is>
       </c>
     </row>
@@ -8591,17 +8591,17 @@
       </c>
       <c r="B129" s="3" t="inlineStr">
         <is>
-          <t>OTR Planning Manager, Hub Delivery UAE , Hub Delivery</t>
+          <t>Graphene Photonics Data Analyst (f/m/d)</t>
         </is>
       </c>
       <c r="C129" s="3" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Black Semiconductor</t>
         </is>
       </c>
       <c r="D129" s="3" t="inlineStr">
         <is>
-          <t>Dubai, Dubai, United Arab Emirates</t>
+          <t>Aachen, North Rhine-Westphalia, Germany</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
@@ -8609,17 +8609,17 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F129" s="8" t="n">
+      <c r="F129" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="G129" s="9" t="inlineStr">
+      <c r="G129" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H129" s="3" t="inlineStr">
         <is>
-          <t>This operations and logistics management role is entirely unrelated to data science, machine learning, and Generative AI, focusing instead on supply chain planning and fleet management. Therefore, it is a very poor match for the candidate's core specialization.</t>
+          <t>This role is entirely focused on semiconductor hardware, graphene photonics, and physical data analysis, with zero relevance to the candidate's core specialization in Generative AI, LLMs, and agentic workflows.</t>
         </is>
       </c>
       <c r="I129" s="3" t="inlineStr">
@@ -8644,7 +8644,7 @@
       </c>
       <c r="M129" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/otr-planning-manager-hub-delivery-uae-hub-delivery-at-amazon-4459184678?position=21&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=bqoXqft%2BGFtLz05C2kL0FA%3D%3D</t>
+          <t>https://de.linkedin.com/jobs/view/graphene-photonics-data-analyst-f-m-d-at-black-semiconductor-4459334621?position=26&amp;pageNum=0&amp;refId=T%2F0KkBXL%2Fl%2B5Iv5tUGTY7Q%3D%3D&amp;trackingId=KgQ01De6ChDgIN8UxnUvXg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -8654,17 +8654,17 @@
       </c>
       <c r="B130" s="3" t="inlineStr">
         <is>
-          <t>Senior Compensation Analyst</t>
+          <t>Financial Planning and Analysis Manager</t>
         </is>
       </c>
       <c r="C130" s="3" t="inlineStr">
         <is>
-          <t>Cartier</t>
+          <t>Confidential Jobs</t>
         </is>
       </c>
       <c r="D130" s="3" t="inlineStr">
         <is>
-          <t>Dubai, Dubai, United Arab Emirates</t>
+          <t>Dubai, United Arab Emirates</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
@@ -8672,17 +8672,17 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F130" s="8" t="n">
+      <c r="F130" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="G130" s="9" t="inlineStr">
+      <c r="G130" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H130" s="3" t="inlineStr">
         <is>
-          <t>This is a non-technical role focused strictly on compensation analysis, financial modeling, and advanced Excel simulation design within HR, which has no overlap with the candidate's core GenAI, LLM, or data science specialization.</t>
+          <t>This Financial Planning and Analysis Manager role is entirely unrelated to data science, machine learning, or software engineering, focusing instead on corporate finance, budgeting, construction economics, and IFRS 15 accounting. There is a massive domain and seniority mismatch for an AI/GenAI Lead Data Scientist.</t>
         </is>
       </c>
       <c r="I130" s="3" t="inlineStr">
@@ -8707,7 +8707,7 @@
       </c>
       <c r="M130" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/senior-compensation-analyst-at-cartier-4448528069?position=20&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=uU%2BxMpwsg7Xv71%2Fjk83xeg%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/financial-planning-and-analysis-manager-at-confidential-jobs-4452594332?position=29&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=KEfZVTEknZKckxH1vstrzQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -8717,12 +8717,12 @@
       </c>
       <c r="B131" s="3" t="inlineStr">
         <is>
-          <t>AI &amp; Data - BrightStar program - Part-Time For Students | UAE Nationals Only - Dubai</t>
+          <t>Data QA Engineer</t>
         </is>
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>ClearGrid</t>
         </is>
       </c>
       <c r="D131" s="3" t="inlineStr">
@@ -8735,17 +8735,17 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F131" s="8" t="n">
+      <c r="F131" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="G131" s="9" t="inlineStr">
+      <c r="G131" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H131" s="3" t="inlineStr">
         <is>
-          <t>This student internship/part-time program is an extreme seniority mismatch for a Lead Data Scientist with 10+ years of experience. Furthermore, the role is strictly restricted to UAE Nationals and unrelated to the candidate's specialized GenAI and agentic AI expertise.</t>
+          <t>This role is a Data QA Engineer focused entirely on data quality, dbt testing, and warehouse reconciliation in a fintech/collections environment, lacking any Generative AI, LLM, or agentic specialization. Furthermore, the seniority requirement (2+ years) is well below the candidate's 10+ years as a Lead Data Scientist.</t>
         </is>
       </c>
       <c r="I131" s="3" t="inlineStr">
@@ -8770,7 +8770,7 @@
       </c>
       <c r="M131" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/ai-data-brightstar-program-part-time-for-students-uae-nationals-only-dubai-at-deloitte-4459165278?position=18&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=rkeXlOzDBapH9BYwLoMUoA%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/data-qa-engineer-at-cleargrid-4457980735?position=25&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=RbMMQ6DAm%2FMomlqBLUM2IQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -8780,12 +8780,12 @@
       </c>
       <c r="B132" s="3" t="inlineStr">
         <is>
-          <t>Junior Market Analyst - UAE National</t>
+          <t>OTR Planning Manager, Hub Delivery UAE , Hub Delivery</t>
         </is>
       </c>
       <c r="C132" s="3" t="inlineStr">
         <is>
-          <t>Richemont</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="D132" s="3" t="inlineStr">
@@ -8798,17 +8798,17 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F132" s="8" t="n">
+      <c r="F132" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="G132" s="9" t="inlineStr">
+      <c r="G132" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H132" s="3" t="inlineStr">
         <is>
-          <t>This role is a junior market research and business development position focused on luxury retail intelligence in the MEIAT region, which is completely unrelated to data science, artificial intelligence, or the candidate's GenAI and LLM specialization.</t>
+          <t>This operations and logistics management role is entirely unrelated to data science, machine learning, and Generative AI, focusing instead on supply chain planning and fleet management. Therefore, it is a very poor match for the candidate's core specialization.</t>
         </is>
       </c>
       <c r="I132" s="3" t="inlineStr">
@@ -8833,7 +8833,7 @@
       </c>
       <c r="M132" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/junior-market-analyst-uae-national-at-richemont-4448527067?position=22&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=fabWFpBqiTWxCuIFUXVosg%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/otr-planning-manager-hub-delivery-uae-hub-delivery-at-amazon-4459184678?position=21&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=bqoXqft%2BGFtLz05C2kL0FA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -8843,12 +8843,12 @@
       </c>
       <c r="B133" s="3" t="inlineStr">
         <is>
-          <t>Data Analyst - (Advanced Excel expertise)</t>
+          <t>Senior Compensation Analyst</t>
         </is>
       </c>
       <c r="C133" s="3" t="inlineStr">
         <is>
-          <t>BigTapp Analytics</t>
+          <t>Cartier</t>
         </is>
       </c>
       <c r="D133" s="3" t="inlineStr">
@@ -8861,17 +8861,17 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F133" s="8" t="n">
+      <c r="F133" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="G133" s="9" t="inlineStr">
+      <c r="G133" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H133" s="3" t="inlineStr">
         <is>
-          <t>This is a Data Analyst role focused entirely on Advanced Excel, corporate tax data quality, and data validation, with no connection to the candidate's GenAI, LLM, or agentic AI specialization.</t>
+          <t>This is a non-technical role focused strictly on compensation analysis, financial modeling, and advanced Excel simulation design within HR, which has no overlap with the candidate's core GenAI, LLM, or data science specialization.</t>
         </is>
       </c>
       <c r="I133" s="3" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="M133" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/data-analyst-advanced-excel-expertise-at-bigtapp-analytics-4459194093?position=16&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=vJ8ubhhJtvsWirwhmdkH%2BA%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/senior-compensation-analyst-at-cartier-4448528069?position=20&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=uU%2BxMpwsg7Xv71%2Fjk83xeg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -8906,17 +8906,17 @@
       </c>
       <c r="B134" s="3" t="inlineStr">
         <is>
-          <t>Junior Data Analyst</t>
+          <t>AI &amp; Data - BrightStar program - Part-Time For Students | UAE Nationals Only - Dubai</t>
         </is>
       </c>
       <c r="C134" s="3" t="inlineStr">
         <is>
-          <t>Arabian Private Holdings</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="D134" s="3" t="inlineStr">
         <is>
-          <t>Sharjah, Sharjah Emirate, United Arab Emirates</t>
+          <t>Dubai, Dubai, United Arab Emirates</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
@@ -8924,17 +8924,17 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F134" s="8" t="n">
+      <c r="F134" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="G134" s="9" t="inlineStr">
+      <c r="G134" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H134" s="3" t="inlineStr">
         <is>
-          <t>This is a junior data analyst role focused on operational data interpretation, basic SQL/Excel database maintenance, and corporate strategy support, completely unrelated to the candidate's GenAI, LLMs, and agentic AI specialization. Additionally, there is a severe seniority mismatch as the role is strictly junior while the candidate is a Lead Data Scientist with 10+ years of experience.</t>
+          <t>This student internship/part-time program is an extreme seniority mismatch for a Lead Data Scientist with 10+ years of experience. Furthermore, the role is strictly restricted to UAE Nationals and unrelated to the candidate's specialized GenAI and agentic AI expertise.</t>
         </is>
       </c>
       <c r="I134" s="3" t="inlineStr">
@@ -8959,7 +8959,7 @@
       </c>
       <c r="M134" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/junior-data-analyst-at-arabian-private-holdings-4457918646?position=11&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=n3OKFNsTAywRSCMqHYFmlg%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/ai-data-brightstar-program-part-time-for-students-uae-nationals-only-dubai-at-deloitte-4459165278?position=18&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=rkeXlOzDBapH9BYwLoMUoA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -8969,17 +8969,17 @@
       </c>
       <c r="B135" s="3" t="inlineStr">
         <is>
-          <t>Data Analyst – Social Support Operations - UAE National</t>
+          <t>Junior Market Analyst - UAE National</t>
         </is>
       </c>
       <c r="C135" s="3" t="inlineStr">
         <is>
-          <t>Ministry of Community Empowerment</t>
+          <t>Richemont</t>
         </is>
       </c>
       <c r="D135" s="3" t="inlineStr">
         <is>
-          <t>Dubai, United Arab Emirates</t>
+          <t>Dubai, Dubai, United Arab Emirates</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
@@ -8987,17 +8987,17 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F135" s="8" t="n">
+      <c r="F135" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="G135" s="9" t="inlineStr">
+      <c r="G135" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H135" s="3" t="inlineStr">
         <is>
-          <t>This role is a data analyst position focused on BI, Power BI dashboards, SQL, and social support operations, which is completely unrelated to the candidate's core GenAI, LLMs, and agentic AI specialization. Additionally, it specifies a nationality requirement.</t>
+          <t>This role is a junior market research and business development position focused on luxury retail intelligence in the MEIAT region, which is completely unrelated to data science, artificial intelligence, or the candidate's GenAI and LLM specialization.</t>
         </is>
       </c>
       <c r="I135" s="3" t="inlineStr">
@@ -9022,7 +9022,7 @@
       </c>
       <c r="M135" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/data-analyst-%E2%80%93-social-support-operations-uae-national-at-ministry-of-community-empowerment-4459118725?position=4&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=q%2FHUZ0XJHF5eY2WSwIWmAg%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/junior-market-analyst-uae-national-at-richemont-4448527067?position=22&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=fabWFpBqiTWxCuIFUXVosg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -9032,12 +9032,12 @@
       </c>
       <c r="B136" s="3" t="inlineStr">
         <is>
-          <t>Graduate - Data Scientist إماراتيين (خلاصة القيد)</t>
+          <t>Data Analyst - (Advanced Excel expertise)</t>
         </is>
       </c>
       <c r="C136" s="3" t="inlineStr">
         <is>
-          <t>AECOM</t>
+          <t>BigTapp Analytics</t>
         </is>
       </c>
       <c r="D136" s="3" t="inlineStr">
@@ -9050,17 +9050,17 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F136" s="8" t="n">
+      <c r="F136" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="G136" s="9" t="inlineStr">
+      <c r="G136" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H136" s="3" t="inlineStr">
         <is>
-          <t>This is a graduate/entry-level program designed specifically for recent graduates (2024-2026) and UAE Nationals, representing a severe seniority and eligibility mismatch for a Lead Data Scientist with 10+ years of experience. Furthermore, the role focuses on construction digital tools, cost management, and general data analytics rather than the candidate's core GenAI, LLMs, and agentic AI specialization.</t>
+          <t>This is a Data Analyst role focused entirely on Advanced Excel, corporate tax data quality, and data validation, with no connection to the candidate's GenAI, LLM, or agentic AI specialization.</t>
         </is>
       </c>
       <c r="I136" s="3" t="inlineStr">
@@ -9085,7 +9085,7 @@
       </c>
       <c r="M136" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/graduate-data-scientist-%D8%A5%D9%85%D8%A7%D8%B1%D8%A7%D8%AA%D9%8A%D9%8A%D9%86-%D8%AE%D9%84%D8%A7%D8%B5%D8%A9-%D8%A7%D9%84%D9%82%D9%8A%D8%AF-at-aecom-4457915285?position=1&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=deUfOEFHstE7TEtandLeTg%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/data-analyst-advanced-excel-expertise-at-bigtapp-analytics-4459194093?position=16&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=vJ8ubhhJtvsWirwhmdkH%2BA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -9095,17 +9095,17 @@
       </c>
       <c r="B137" s="3" t="inlineStr">
         <is>
-          <t>Quantitative Researcher, Quantitative Strategies</t>
+          <t>Junior Data Analyst</t>
         </is>
       </c>
       <c r="C137" s="3" t="inlineStr">
         <is>
-          <t>Millennium</t>
+          <t>Arabian Private Holdings</t>
         </is>
       </c>
       <c r="D137" s="3" t="inlineStr">
         <is>
-          <t>Dubai, Dubai, United Arab Emirates</t>
+          <t>Sharjah, Sharjah Emirate, United Arab Emirates</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
@@ -9113,17 +9113,17 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F137" s="8" t="n">
+      <c r="F137" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="G137" s="9" t="inlineStr">
+      <c r="G137" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H137" s="3" t="inlineStr">
         <is>
-          <t>This role focuses entirely on quantitative finance, statistical modeling, and systematic equity trading in Asian markets, which has no overlap with the candidate's core specialization in Generative AI, LLMs, and agentic systems. Additionally, the domain requires specific desk quant trading experience that is absent from the candidate's profile.</t>
+          <t>This is a junior data analyst role focused on operational data interpretation, basic SQL/Excel database maintenance, and corporate strategy support, completely unrelated to the candidate's GenAI, LLMs, and agentic AI specialization. Additionally, there is a severe seniority mismatch as the role is strictly junior while the candidate is a Lead Data Scientist with 10+ years of experience.</t>
         </is>
       </c>
       <c r="I137" s="3" t="inlineStr">
@@ -9148,7 +9148,7 @@
       </c>
       <c r="M137" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/quantitative-researcher-quantitative-strategies-at-millennium-4439427782?position=2&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=uptfSAbwEngBw3yrsrQehg%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/junior-data-analyst-at-arabian-private-holdings-4457918646?position=11&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=n3OKFNsTAywRSCMqHYFmlg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -9158,17 +9158,17 @@
       </c>
       <c r="B138" s="3" t="inlineStr">
         <is>
-          <t>Analyst I - Advisory</t>
+          <t>Data Analyst – Social Support Operations - UAE National</t>
         </is>
       </c>
       <c r="C138" s="3" t="inlineStr">
         <is>
-          <t>Marsh Risk</t>
+          <t>Ministry of Community Empowerment</t>
         </is>
       </c>
       <c r="D138" s="3" t="inlineStr">
         <is>
-          <t>Dubai, Dubai, United Arab Emirates</t>
+          <t>Dubai, United Arab Emirates</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
@@ -9176,17 +9176,17 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F138" s="8" t="n">
+      <c r="F138" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="G138" s="9" t="inlineStr">
+      <c r="G138" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H138" s="3" t="inlineStr">
         <is>
-          <t>This is a fresh-graduate/entry-level role for recent graduates that focuses heavily on risk engineering and basic internal digitalization using Excel and Microsoft tools, which is far below the candidate's 10+ years of experience as a Lead Data Scientist specializing in advanced GenAI and agentic systems.</t>
+          <t>This role is a data analyst position focused on BI, Power BI dashboards, SQL, and social support operations, which is completely unrelated to the candidate's core GenAI, LLMs, and agentic AI specialization. Additionally, it specifies a nationality requirement.</t>
         </is>
       </c>
       <c r="I138" s="3" t="inlineStr">
@@ -9211,7 +9211,7 @@
       </c>
       <c r="M138" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/analyst-i-advisory-at-marsh-risk-4459165267?position=3&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=NpomdoqDoXrgLAw8%2BZjEQA%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/data-analyst-%E2%80%93-social-support-operations-uae-national-at-ministry-of-community-empowerment-4459118725?position=4&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=q%2FHUZ0XJHF5eY2WSwIWmAg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -9221,17 +9221,17 @@
       </c>
       <c r="B139" s="3" t="inlineStr">
         <is>
-          <t>Demand Planner (f/m/x)</t>
+          <t>Graduate - Data Scientist إماراتيين (خلاصة القيد)</t>
         </is>
       </c>
       <c r="C139" s="3" t="inlineStr">
         <is>
-          <t>HelloFresh</t>
+          <t>AECOM</t>
         </is>
       </c>
       <c r="D139" s="3" t="inlineStr">
         <is>
-          <t>Amsterdam, North Holland, Netherlands</t>
+          <t>Dubai, Dubai, United Arab Emirates</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
@@ -9239,17 +9239,17 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F139" s="8" t="n">
+      <c r="F139" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="G139" s="9" t="inlineStr">
+      <c r="G139" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H139" s="3" t="inlineStr">
         <is>
-          <t>This is a supply chain demand planning role requiring 2-3 years of experience in business forecasting, which is completely unrelated to the candidate's specialization in Generative AI, LLMs, and agentic systems. Furthermore, there is a severe seniority mismatch as the candidate is a Lead Data Scientist with 10+ years of experience.</t>
+          <t>This is a graduate/entry-level program designed specifically for recent graduates (2024-2026) and UAE Nationals, representing a severe seniority and eligibility mismatch for a Lead Data Scientist with 10+ years of experience. Furthermore, the role focuses on construction digital tools, cost management, and general data analytics rather than the candidate's core GenAI, LLMs, and agentic AI specialization.</t>
         </is>
       </c>
       <c r="I139" s="3" t="inlineStr">
@@ -9274,7 +9274,7 @@
       </c>
       <c r="M139" s="6" t="inlineStr">
         <is>
-          <t>https://nl.linkedin.com/jobs/view/demand-planner-f-m-x-at-hellofresh-4459621163?position=29&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=ScTLY%2B93hMGSjD1GtPlxQw%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/graduate-data-scientist-%D8%A5%D9%85%D8%A7%D8%B1%D8%A7%D8%AA%D9%8A%D9%8A%D9%86-%D8%AE%D9%84%D8%A7%D8%B5%D8%A9-%D8%A7%D9%84%D9%82%D9%8A%D8%AF-at-aecom-4457915285?position=1&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=deUfOEFHstE7TEtandLeTg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -9284,17 +9284,17 @@
       </c>
       <c r="B140" s="3" t="inlineStr">
         <is>
-          <t>Traineeship Data Analytics</t>
+          <t>Quantitative Researcher, Quantitative Strategies</t>
         </is>
       </c>
       <c r="C140" s="3" t="inlineStr">
         <is>
-          <t>Breinstein</t>
+          <t>Millennium</t>
         </is>
       </c>
       <c r="D140" s="3" t="inlineStr">
         <is>
-          <t>Groningen, Netherlands</t>
+          <t>Dubai, Dubai, United Arab Emirates</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
@@ -9302,17 +9302,17 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F140" s="8" t="n">
+      <c r="F140" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="G140" s="9" t="inlineStr">
+      <c r="G140" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H140" s="3" t="inlineStr">
         <is>
-          <t>This is a junior/graduate-level traineeship requiring Dutch language proficiency, which represents a severe mismatch with the candidate's 10+ years of senior experience and Generative AI/LLM specialization.</t>
+          <t>This role focuses entirely on quantitative finance, statistical modeling, and systematic equity trading in Asian markets, which has no overlap with the candidate's core specialization in Generative AI, LLMs, and agentic systems. Additionally, the domain requires specific desk quant trading experience that is absent from the candidate's profile.</t>
         </is>
       </c>
       <c r="I140" s="3" t="inlineStr">
@@ -9337,7 +9337,7 @@
       </c>
       <c r="M140" s="6" t="inlineStr">
         <is>
-          <t>https://nl.linkedin.com/jobs/view/traineeship-data-analytics-at-breinstein-4457240429?position=18&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=09Fo%2Bt8pd71ON%2B4bzhNIXw%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/quantitative-researcher-quantitative-strategies-at-millennium-4439427782?position=2&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=uptfSAbwEngBw3yrsrQehg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -9347,17 +9347,17 @@
       </c>
       <c r="B141" s="3" t="inlineStr">
         <is>
-          <t>Økonom til finansielle data om pensionssektoren og investeringsfonde i Nationalbanken</t>
+          <t>Analyst I - Advisory</t>
         </is>
       </c>
       <c r="C141" s="3" t="inlineStr">
         <is>
-          <t>Altandetlige.dk</t>
+          <t>Marsh Risk</t>
         </is>
       </c>
       <c r="D141" s="3" t="inlineStr">
         <is>
-          <t>Copenhagen, Capital Region of Denmark, Denmark</t>
+          <t>Dubai, Dubai, United Arab Emirates</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
@@ -9365,17 +9365,17 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F141" s="8" t="n">
+      <c r="F141" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="G141" s="9" t="inlineStr">
+      <c r="G141" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H141" s="3" t="inlineStr">
         <is>
-          <t>This is a non-technical economics and financial statistics role at Denmark's central bank focusing on pension funds and investment data, which is completely unrelated to the candidate's specialization in Generative AI, LLMs, and agentic systems.</t>
+          <t>This is a fresh-graduate/entry-level role for recent graduates that focuses heavily on risk engineering and basic internal digitalization using Excel and Microsoft tools, which is far below the candidate's 10+ years of experience as a Lead Data Scientist specializing in advanced GenAI and agentic systems.</t>
         </is>
       </c>
       <c r="I141" s="3" t="inlineStr">
@@ -9400,7 +9400,7 @@
       </c>
       <c r="M141" s="6" t="inlineStr">
         <is>
-          <t>https://dk.linkedin.com/jobs/view/%C3%B8konom-til-finansielle-data-om-pensionssektoren-og-investeringsfonde-i-nationalbanken-at-altandetlige-dk-4459168468?position=25&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=%2BEekg%2B%2FvA%2BH0hxU4LsvJ5w%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/analyst-i-advisory-at-marsh-risk-4459165267?position=3&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=NpomdoqDoXrgLAw8%2BZjEQA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -9410,17 +9410,17 @@
       </c>
       <c r="B142" s="3" t="inlineStr">
         <is>
-          <t>Lead Trading Strategist</t>
+          <t>Demand Planner (f/m/x)</t>
         </is>
       </c>
       <c r="C142" s="3" t="inlineStr">
         <is>
-          <t>Ørsted</t>
+          <t>HelloFresh</t>
         </is>
       </c>
       <c r="D142" s="3" t="inlineStr">
         <is>
-          <t>Gentofte, Capital Region of Denmark, Denmark</t>
+          <t>Amsterdam, North Holland, Netherlands</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
@@ -9428,17 +9428,17 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F142" s="8" t="n">
+      <c r="F142" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="G142" s="9" t="inlineStr">
+      <c r="G142" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H142" s="3" t="inlineStr">
         <is>
-          <t>This is a quantitative energy trading and fundamental market analysis role requiring deep domain expertise in European power markets and commodities trading, which is completely unrelated to the candidate's core GenAI, LLM, and data science specialization.</t>
+          <t>This is a supply chain demand planning role requiring 2-3 years of experience in business forecasting, which is completely unrelated to the candidate's specialization in Generative AI, LLMs, and agentic systems. Furthermore, there is a severe seniority mismatch as the candidate is a Lead Data Scientist with 10+ years of experience.</t>
         </is>
       </c>
       <c r="I142" s="3" t="inlineStr">
@@ -9463,7 +9463,7 @@
       </c>
       <c r="M142" s="6" t="inlineStr">
         <is>
-          <t>https://dk.linkedin.com/jobs/view/lead-trading-strategist-at-%C3%B8rsted-4439179684?position=21&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=LxVb1rg9c7QiaOEs5%2BY%2FTw%3D%3D</t>
+          <t>https://nl.linkedin.com/jobs/view/demand-planner-f-m-x-at-hellofresh-4459621163?position=29&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=ScTLY%2B93hMGSjD1GtPlxQw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -9473,17 +9473,17 @@
       </c>
       <c r="B143" s="3" t="inlineStr">
         <is>
-          <t>Analytikere med flair for databehandling til PET's kontraspionageindsats mod Rusland</t>
+          <t>Traineeship Data Analytics</t>
         </is>
       </c>
       <c r="C143" s="3" t="inlineStr">
         <is>
-          <t>Politiets Efterretningstjeneste (PET)</t>
+          <t>Breinstein</t>
         </is>
       </c>
       <c r="D143" s="3" t="inlineStr">
         <is>
-          <t>Copenhagen, Capital Region of Denmark, Denmark</t>
+          <t>Groningen, Netherlands</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
@@ -9491,17 +9491,17 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F143" s="8" t="n">
+      <c r="F143" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="G143" s="9" t="inlineStr">
+      <c r="G143" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H143" s="3" t="inlineStr">
         <is>
-          <t>This is a national security intelligence and counter-espionage analyst role entirely unrelated to data science, artificial intelligence, LLMs, or software engineering. It focuses on intelligence operations and telecommunications data processing rather than the candidate's core Generative AI specialization.</t>
+          <t>This is a junior/graduate-level traineeship requiring Dutch language proficiency, which represents a severe mismatch with the candidate's 10+ years of senior experience and Generative AI/LLM specialization.</t>
         </is>
       </c>
       <c r="I143" s="3" t="inlineStr">
@@ -9526,7 +9526,7 @@
       </c>
       <c r="M143" s="6" t="inlineStr">
         <is>
-          <t>https://dk.linkedin.com/jobs/view/analytikere-med-flair-for-databehandling-til-pet-s-kontraspionageindsats-mod-rusland-at-politiets-efterretningstjeneste-pet-4457295379?position=17&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=jfzRay2PLGqzZJAC5yISBA%3D%3D</t>
+          <t>https://nl.linkedin.com/jobs/view/traineeship-data-analytics-at-breinstein-4457240429?position=18&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=09Fo%2Bt8pd71ON%2B4bzhNIXw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -9536,17 +9536,17 @@
       </c>
       <c r="B144" s="3" t="inlineStr">
         <is>
-          <t>BI Specialist - turn healthcare data into better care decisions</t>
+          <t>Økonom til finansielle data om pensionssektoren og investeringsfonde i Nationalbanken</t>
         </is>
       </c>
       <c r="C144" s="3" t="inlineStr">
         <is>
-          <t>Systematic</t>
+          <t>Altandetlige.dk</t>
         </is>
       </c>
       <c r="D144" s="3" t="inlineStr">
         <is>
-          <t>Aarhus, Central Denmark Region, Denmark</t>
+          <t>Copenhagen, Capital Region of Denmark, Denmark</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
@@ -9554,17 +9554,17 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F144" s="8" t="n">
+      <c r="F144" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="G144" s="9" t="inlineStr">
+      <c r="G144" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H144" s="3" t="inlineStr">
         <is>
-          <t>This role is for a BI Specialist focusing on healthcare data systems, SQL, T-SQL, DAX, and client communication, which is completely unrelated to the candidate's core specialization in Generative AI, LLMs, and agentic AI systems. Additionally, it requires proficiency in Danish.</t>
+          <t>This is a non-technical economics and financial statistics role at Denmark's central bank focusing on pension funds and investment data, which is completely unrelated to the candidate's specialization in Generative AI, LLMs, and agentic systems.</t>
         </is>
       </c>
       <c r="I144" s="3" t="inlineStr">
@@ -9589,7 +9589,7 @@
       </c>
       <c r="M144" s="6" t="inlineStr">
         <is>
-          <t>https://dk.linkedin.com/jobs/view/bi-specialist-turn-healthcare-data-into-better-care-decisions-at-systematic-4449000390?position=13&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=C4YvYCcgfvLE1Lup1m630A%3D%3D</t>
+          <t>https://dk.linkedin.com/jobs/view/%C3%B8konom-til-finansielle-data-om-pensionssektoren-og-investeringsfonde-i-nationalbanken-at-altandetlige-dk-4459168468?position=25&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=%2BEekg%2B%2FvA%2BH0hxU4LsvJ5w%3D%3D</t>
         </is>
       </c>
     </row>
@@ -9599,17 +9599,17 @@
       </c>
       <c r="B145" s="3" t="inlineStr">
         <is>
-          <t>Demand Planner (f/m/x)</t>
+          <t>Lead Trading Strategist</t>
         </is>
       </c>
       <c r="C145" s="3" t="inlineStr">
         <is>
-          <t>HelloFresh</t>
+          <t>Ørsted</t>
         </is>
       </c>
       <c r="D145" s="3" t="inlineStr">
         <is>
-          <t>Copenhagen Municipality, Capital Region of Denmark, Denmark</t>
+          <t>Gentofte, Capital Region of Denmark, Denmark</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
@@ -9617,17 +9617,17 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F145" s="8" t="n">
+      <c r="F145" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="G145" s="9" t="inlineStr">
+      <c r="G145" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H145" s="3" t="inlineStr">
         <is>
-          <t>This is a non-AI supply chain demand planning role focused on SQL, logistics, and forecasting metrics like MAPE, which is completely unrelated to the candidate's core GenAI, LLM, and agentic AI specialization.</t>
+          <t>This is a quantitative energy trading and fundamental market analysis role requiring deep domain expertise in European power markets and commodities trading, which is completely unrelated to the candidate's core GenAI, LLM, and data science specialization.</t>
         </is>
       </c>
       <c r="I145" s="3" t="inlineStr">
@@ -9652,7 +9652,7 @@
       </c>
       <c r="M145" s="6" t="inlineStr">
         <is>
-          <t>https://dk.linkedin.com/jobs/view/demand-planner-f-m-x-at-hellofresh-4459625132?position=6&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=%2FDvrjQmxzWwgXh6GBB3pqA%3D%3D</t>
+          <t>https://dk.linkedin.com/jobs/view/lead-trading-strategist-at-%C3%B8rsted-4439179684?position=21&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=LxVb1rg9c7QiaOEs5%2BY%2FTw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -9662,17 +9662,17 @@
       </c>
       <c r="B146" s="3" t="inlineStr">
         <is>
-          <t>Senior Analyst - Market Intelligence (Trade &amp; Commodities)</t>
+          <t>Analytikere med flair for databehandling til PET's kontraspionageindsats mod Rusland</t>
         </is>
       </c>
       <c r="C146" s="3" t="inlineStr">
         <is>
-          <t>Robert Walters</t>
+          <t>Politiets Efterretningstjeneste (PET)</t>
         </is>
       </c>
       <c r="D146" s="3" t="inlineStr">
         <is>
-          <t>Abu Dhabi, Abu Dhabi Emirate, United Arab Emirates</t>
+          <t>Copenhagen, Capital Region of Denmark, Denmark</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
@@ -9680,17 +9680,17 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F146" s="8" t="n">
+      <c r="F146" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="G146" s="9" t="inlineStr">
+      <c r="G146" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H146" s="3" t="inlineStr">
         <is>
-          <t>This is a non-technical role focusing on market intelligence, trade flows, and supply chain analysis requiring Arabic fluency, which has no overlap with the candidate's core GenAI, LLMs, and agentic AI specialization.</t>
+          <t>This is a national security intelligence and counter-espionage analyst role entirely unrelated to data science, artificial intelligence, LLMs, or software engineering. It focuses on intelligence operations and telecommunications data processing rather than the candidate's core Generative AI specialization.</t>
         </is>
       </c>
       <c r="I146" s="3" t="inlineStr">
@@ -9715,7 +9715,7 @@
       </c>
       <c r="M146" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/senior-analyst-market-intelligence-trade-commodities-at-robert-walters-4457222382?position=30&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=JK2lIzdStMxW3Rb1o%2FxSgQ%3D%3D</t>
+          <t>https://dk.linkedin.com/jobs/view/analytikere-med-flair-for-databehandling-til-pet-s-kontraspionageindsats-mod-rusland-at-politiets-efterretningstjeneste-pet-4457295379?position=17&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=jfzRay2PLGqzZJAC5yISBA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -9725,17 +9725,17 @@
       </c>
       <c r="B147" s="3" t="inlineStr">
         <is>
-          <t>AI &amp; Data - BrightStar program - Part-Time For Students | UAE Nationals Only - Dubai</t>
+          <t>BI Specialist - turn healthcare data into better care decisions</t>
         </is>
       </c>
       <c r="C147" s="3" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Systematic</t>
         </is>
       </c>
       <c r="D147" s="3" t="inlineStr">
         <is>
-          <t>Abu Dhabi, Abu Dhabi Emirate, United Arab Emirates</t>
+          <t>Aarhus, Central Denmark Region, Denmark</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
@@ -9743,17 +9743,17 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F147" s="8" t="n">
+      <c r="F147" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="G147" s="9" t="inlineStr">
+      <c r="G147" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H147" s="3" t="inlineStr">
         <is>
-          <t>This is a student/internship program ('Part-Time For Students') restricted to UAE Nationals only, representing a severe seniority and eligibility mismatch for a Lead Data Scientist with 10 years of experience.</t>
+          <t>This role is for a BI Specialist focusing on healthcare data systems, SQL, T-SQL, DAX, and client communication, which is completely unrelated to the candidate's core specialization in Generative AI, LLMs, and agentic AI systems. Additionally, it requires proficiency in Danish.</t>
         </is>
       </c>
       <c r="I147" s="3" t="inlineStr">
@@ -9778,7 +9778,7 @@
       </c>
       <c r="M147" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/ai-data-brightstar-program-part-time-for-students-uae-nationals-only-dubai-at-deloitte-4459166169?position=29&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=eJo5yKx6Zm7GgBBf0abvaA%3D%3D</t>
+          <t>https://dk.linkedin.com/jobs/view/bi-specialist-turn-healthcare-data-into-better-care-decisions-at-systematic-4449000390?position=13&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=C4YvYCcgfvLE1Lup1m630A%3D%3D</t>
         </is>
       </c>
     </row>
@@ -9788,17 +9788,17 @@
       </c>
       <c r="B148" s="3" t="inlineStr">
         <is>
-          <t>SAS Analyst</t>
+          <t>Demand Planner (f/m/x)</t>
         </is>
       </c>
       <c r="C148" s="3" t="inlineStr">
         <is>
-          <t>One75mb HRM Pvt Ltd.</t>
+          <t>HelloFresh</t>
         </is>
       </c>
       <c r="D148" s="3" t="inlineStr">
         <is>
-          <t>Abu Dhabi Emirate, United Arab Emirates</t>
+          <t>Copenhagen Municipality, Capital Region of Denmark, Denmark</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
@@ -9806,17 +9806,17 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F148" s="8" t="n">
+      <c r="F148" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="G148" s="9" t="inlineStr">
+      <c r="G148" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H148" s="3" t="inlineStr">
         <is>
-          <t>This role is a SAS Anti-Money Laundering (AML) Developer position focused on SAS Viya, SAS programming, and compliance systems. It has no connection to Generative AI, LLMs, RAG, or agentic systems, making it an entirely irrelevant fit for a GenAI specialist.</t>
+          <t>This is a non-AI supply chain demand planning role focused on SQL, logistics, and forecasting metrics like MAPE, which is completely unrelated to the candidate's core GenAI, LLM, and agentic AI specialization.</t>
         </is>
       </c>
       <c r="I148" s="3" t="inlineStr">
@@ -9841,7 +9841,7 @@
       </c>
       <c r="M148" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/sas-analyst-at-one75mb-hrm-pvt-ltd-4459306494?position=19&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=NfyeO5P7KUMAsO5xQjjwEA%3D%3D</t>
+          <t>https://dk.linkedin.com/jobs/view/demand-planner-f-m-x-at-hellofresh-4459625132?position=6&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=%2FDvrjQmxzWwgXh6GBB3pqA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -9851,12 +9851,12 @@
       </c>
       <c r="B149" s="3" t="inlineStr">
         <is>
-          <t>Finance Information Systems Analyst</t>
+          <t>Senior Analyst - Market Intelligence (Trade &amp; Commodities)</t>
         </is>
       </c>
       <c r="C149" s="3" t="inlineStr">
         <is>
-          <t>United Arab Emirates University, Department of Family Medicine</t>
+          <t>Robert Walters</t>
         </is>
       </c>
       <c r="D149" s="3" t="inlineStr">
@@ -9869,17 +9869,17 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F149" s="8" t="n">
+      <c r="F149" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="G149" s="9" t="inlineStr">
+      <c r="G149" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H149" s="3" t="inlineStr">
         <is>
-          <t>This role is for a Finance Information Systems Analyst focusing on Oracle SQL, financial reporting, and system maintenance, which is completely unrelated to the candidate's core expertise in Generative AI, LLMs, and agentic workflows.</t>
+          <t>This is a non-technical role focusing on market intelligence, trade flows, and supply chain analysis requiring Arabic fluency, which has no overlap with the candidate's core GenAI, LLMs, and agentic AI specialization.</t>
         </is>
       </c>
       <c r="I149" s="3" t="inlineStr">
@@ -9904,7 +9904,7 @@
       </c>
       <c r="M149" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/finance-information-systems-analyst-at-united-arab-emirates-university-department-of-family-medicine-4458309884?position=18&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=ZkLRAbbB1OpTP3DQTi%2FB4Q%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/senior-analyst-market-intelligence-trade-commodities-at-robert-walters-4457222382?position=30&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=JK2lIzdStMxW3Rb1o%2FxSgQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -9914,12 +9914,12 @@
       </c>
       <c r="B150" s="3" t="inlineStr">
         <is>
-          <t>Analyst I - Advisory</t>
+          <t>AI &amp; Data - BrightStar program - Part-Time For Students | UAE Nationals Only - Dubai</t>
         </is>
       </c>
       <c r="C150" s="3" t="inlineStr">
         <is>
-          <t>Marsh Risk</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="D150" s="3" t="inlineStr">
@@ -9932,17 +9932,17 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F150" s="8" t="n">
+      <c r="F150" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="G150" s="9" t="inlineStr">
+      <c r="G150" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H150" s="3" t="inlineStr">
         <is>
-          <t>This is a graduate/entry-level risk engineering and data analyst role located in the UAE restricted to UAE Nationals, representing a severe mismatch in both seniority and specialization for a Lead Data Scientist with 10+ years of experience in GenAI.</t>
+          <t>This is a student/internship program ('Part-Time For Students') restricted to UAE Nationals only, representing a severe seniority and eligibility mismatch for a Lead Data Scientist with 10 years of experience.</t>
         </is>
       </c>
       <c r="I150" s="3" t="inlineStr">
@@ -9967,7 +9967,7 @@
       </c>
       <c r="M150" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/analyst-i-advisory-at-marsh-risk-4459170127?position=6&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=hO0QLO%2FIAeXdRsG2PtQkTA%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/ai-data-brightstar-program-part-time-for-students-uae-nationals-only-dubai-at-deloitte-4459166169?position=29&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=eJo5yKx6Zm7GgBBf0abvaA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -9977,17 +9977,17 @@
       </c>
       <c r="B151" s="3" t="inlineStr">
         <is>
-          <t>Senior Economist / Economic Researcher</t>
+          <t>SAS Analyst</t>
         </is>
       </c>
       <c r="C151" s="3" t="inlineStr">
         <is>
-          <t>Robert Walters</t>
+          <t>One75mb HRM Pvt Ltd.</t>
         </is>
       </c>
       <c r="D151" s="3" t="inlineStr">
         <is>
-          <t>Abu Dhabi, Abu Dhabi Emirate, United Arab Emirates</t>
+          <t>Abu Dhabi Emirate, United Arab Emirates</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
@@ -9995,17 +9995,17 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F151" s="8" t="n">
+      <c r="F151" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="G151" s="9" t="inlineStr">
+      <c r="G151" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H151" s="3" t="inlineStr">
         <is>
-          <t>This role is for a Senior Economist focusing on macroeconomic research, policy analysis, and economic forecasting, which is completely unrelated to the candidate's specialization in Generative AI, LLMs, and data science.</t>
+          <t>This role is a SAS Anti-Money Laundering (AML) Developer position focused on SAS Viya, SAS programming, and compliance systems. It has no connection to Generative AI, LLMs, RAG, or agentic systems, making it an entirely irrelevant fit for a GenAI specialist.</t>
         </is>
       </c>
       <c r="I151" s="3" t="inlineStr">
@@ -10030,7 +10030,7 @@
       </c>
       <c r="M151" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/senior-economist-economic-researcher-at-robert-walters-4457234594?position=21&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=hNkG3K%2BgFb1grR8QDMiBxA%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/sas-analyst-at-one75mb-hrm-pvt-ltd-4459306494?position=19&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=NfyeO5P7KUMAsO5xQjjwEA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -10040,35 +10040,35 @@
       </c>
       <c r="B152" s="3" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Finance Information Systems Analyst</t>
         </is>
       </c>
       <c r="C152" s="3" t="inlineStr">
         <is>
-          <t>ChipSoft Nederland</t>
+          <t>United Arab Emirates University, Department of Family Medicine</t>
         </is>
       </c>
       <c r="D152" s="3" t="inlineStr">
         <is>
-          <t>Amsterdam, North Holland, Netherlands</t>
+          <t>Abu Dhabi, Abu Dhabi Emirate, United Arab Emirates</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="F152" s="8" t="n">
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="F152" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="G152" s="9" t="inlineStr">
+      <c r="G152" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H152" s="3" t="inlineStr">
         <is>
-          <t>This is a Data Engineer role focused on ELT, SQL, data warehousing, and clickstream data, which is entirely unrelated to the candidate's core specialization in Generative AI, LLMs, and agentic systems.</t>
+          <t>This role is for a Finance Information Systems Analyst focusing on Oracle SQL, financial reporting, and system maintenance, which is completely unrelated to the candidate's core expertise in Generative AI, LLMs, and agentic workflows.</t>
         </is>
       </c>
       <c r="I152" s="3" t="inlineStr">
@@ -10093,7 +10093,7 @@
       </c>
       <c r="M152" s="6" t="inlineStr">
         <is>
-          <t>https://nl.linkedin.com/jobs/view/data-engineer-at-chipsoft-nederland-4448895866?position=29&amp;pageNum=0&amp;refId=oiBIn1Czflg0JjZjH5z0Lg%3D%3D&amp;trackingId=CakhxR8nCpksAoEXyMZPHQ%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/finance-information-systems-analyst-at-united-arab-emirates-university-department-of-family-medicine-4458309884?position=18&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=ZkLRAbbB1OpTP3DQTi%2FB4Q%3D%3D</t>
         </is>
       </c>
     </row>
@@ -10103,35 +10103,35 @@
       </c>
       <c r="B153" s="3" t="inlineStr">
         <is>
-          <t>Quantitative Developer - Pricing Data</t>
+          <t>Analyst I - Advisory</t>
         </is>
       </c>
       <c r="C153" s="3" t="inlineStr">
         <is>
-          <t>Optiver</t>
+          <t>Marsh Risk</t>
         </is>
       </c>
       <c r="D153" s="3" t="inlineStr">
         <is>
-          <t>Amsterdam, North Holland, Netherlands</t>
+          <t>Abu Dhabi, Abu Dhabi Emirate, United Arab Emirates</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="F153" s="8" t="n">
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="F153" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="G153" s="9" t="inlineStr">
+      <c r="G153" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H153" s="3" t="inlineStr">
         <is>
-          <t>This Quantitative Developer role focuses entirely on financial pricing data systems, market data pipelines, and low-latency/historical trading infrastructure in C++/Python, which is completely unrelated to the candidate's specialization in Generative AI, LLMs, and agentic workflows.</t>
+          <t>This is a graduate/entry-level risk engineering and data analyst role located in the UAE restricted to UAE Nationals, representing a severe mismatch in both seniority and specialization for a Lead Data Scientist with 10+ years of experience in GenAI.</t>
         </is>
       </c>
       <c r="I153" s="3" t="inlineStr">
@@ -10141,7 +10141,7 @@
       </c>
       <c r="J153" s="3" t="inlineStr">
         <is>
-          <t>Yes - explicitly stated in JD</t>
+          <t>Not stated in JD</t>
         </is>
       </c>
       <c r="K153" s="2" t="inlineStr">
@@ -10156,7 +10156,7 @@
       </c>
       <c r="M153" s="6" t="inlineStr">
         <is>
-          <t>https://nl.linkedin.com/jobs/view/quantitative-developer-pricing-data-at-optiver-4437686371?position=21&amp;pageNum=0&amp;refId=oiBIn1Czflg0JjZjH5z0Lg%3D%3D&amp;trackingId=bm7u%2BG7QRNRgNoiTgqdkzg%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/analyst-i-advisory-at-marsh-risk-4459170127?position=6&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=hO0QLO%2FIAeXdRsG2PtQkTA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -10166,35 +10166,35 @@
       </c>
       <c r="B154" s="3" t="inlineStr">
         <is>
-          <t>Data Analyst — Operational Analysis (Python, Power BI, Modelling) for NATO with security clearance</t>
+          <t>Senior Economist / Economic Researcher</t>
         </is>
       </c>
       <c r="C154" s="3" t="inlineStr">
         <is>
-          <t>WLG</t>
+          <t>Robert Walters</t>
         </is>
       </c>
       <c r="D154" s="3" t="inlineStr">
         <is>
-          <t>The Hague, South Holland, Netherlands</t>
+          <t>Abu Dhabi, Abu Dhabi Emirate, United Arab Emirates</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="F154" s="8" t="n">
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="F154" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="G154" s="9" t="inlineStr">
+      <c r="G154" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H154" s="3" t="inlineStr">
         <is>
-          <t>This is an unrelated junior Data Analyst role focused on operational analysis, dashboards, and spreadsheets rather than Generative AI or advanced data science. Given the candidate's 10+ years of experience as a Lead Data Scientist specializing in LLMs and agentic AI, this position represents a severe mismatch in both domain and seniority.</t>
+          <t>This role is for a Senior Economist focusing on macroeconomic research, policy analysis, and economic forecasting, which is completely unrelated to the candidate's specialization in Generative AI, LLMs, and data science.</t>
         </is>
       </c>
       <c r="I154" s="3" t="inlineStr">
@@ -10219,7 +10219,7 @@
       </c>
       <c r="M154" s="6" t="inlineStr">
         <is>
-          <t>https://nl.linkedin.com/jobs/view/data-analyst-%E2%80%94-operational-analysis-python-power-bi-modelling-for-nato-with-security-clearance-at-wlg-4458620413?position=26&amp;pageNum=0&amp;refId=oiBIn1Czflg0JjZjH5z0Lg%3D%3D&amp;trackingId=NK7DxxVQL3iwGI1saGNrZg%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/senior-economist-economic-researcher-at-robert-walters-4457234594?position=21&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=hNkG3K%2BgFb1grR8QDMiBxA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -10229,35 +10229,35 @@
       </c>
       <c r="B155" s="3" t="inlineStr">
         <is>
-          <t>National Assistant Planner</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="C155" s="3" t="inlineStr">
         <is>
-          <t>Al-Futtaim</t>
+          <t>ChipSoft Nederland</t>
         </is>
       </c>
       <c r="D155" s="3" t="inlineStr">
         <is>
-          <t>Dubai, Dubai, United Arab Emirates</t>
+          <t>Amsterdam, North Holland, Netherlands</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="F155" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G155" s="9" t="inlineStr">
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="F155" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="G155" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H155" s="3" t="inlineStr">
         <is>
-          <t>This is a non-technical retail merchandise planning role focused on financial forecasting, inventory management, and sales planning, which is entirely unrelated to the candidate's GenAI, LLM, and data science specialization.</t>
+          <t>This is a Data Engineer role focused on ELT, SQL, data warehousing, and clickstream data, which is entirely unrelated to the candidate's core specialization in Generative AI, LLMs, and agentic systems.</t>
         </is>
       </c>
       <c r="I155" s="3" t="inlineStr">
@@ -10282,7 +10282,7 @@
       </c>
       <c r="M155" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/national-assistant-planner-at-al-futtaim-4459335643?position=23&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=udE1OmanEOJo5NqnDVVmsw%3D%3D</t>
+          <t>https://nl.linkedin.com/jobs/view/data-engineer-at-chipsoft-nederland-4448895866?position=29&amp;pageNum=0&amp;refId=oiBIn1Czflg0JjZjH5z0Lg%3D%3D&amp;trackingId=CakhxR8nCpksAoEXyMZPHQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -10292,17 +10292,17 @@
       </c>
       <c r="B156" s="3" t="inlineStr">
         <is>
-          <t>Forward Deployed AI Integrator (UAE National Only), Field Engineering</t>
+          <t>Quantitative Developer - Pricing Data</t>
         </is>
       </c>
       <c r="C156" s="3" t="inlineStr">
         <is>
-          <t>Amazon Web Services (AWS)</t>
+          <t>Optiver</t>
         </is>
       </c>
       <c r="D156" s="3" t="inlineStr">
         <is>
-          <t>Dubai, Dubai, United Arab Emirates</t>
+          <t>Amsterdam, North Holland, Netherlands</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
@@ -10310,17 +10310,17 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="F156" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G156" s="9" t="inlineStr">
+      <c r="F156" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="G156" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H156" s="3" t="inlineStr">
         <is>
-          <t>Although the role involves AI tooling and Python, it is restricted to UAE Nationals only, making it impossible for the candidate to qualify. Additionally, the position leans heavily toward technical program management rather than hands-on Generative AI and LLM engineering.</t>
+          <t>This Quantitative Developer role focuses entirely on financial pricing data systems, market data pipelines, and low-latency/historical trading infrastructure in C++/Python, which is completely unrelated to the candidate's specialization in Generative AI, LLMs, and agentic workflows.</t>
         </is>
       </c>
       <c r="I156" s="3" t="inlineStr">
@@ -10330,7 +10330,7 @@
       </c>
       <c r="J156" s="3" t="inlineStr">
         <is>
-          <t>Not stated in JD</t>
+          <t>Yes - explicitly stated in JD</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr">
@@ -10345,7 +10345,7 @@
       </c>
       <c r="M156" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/forward-deployed-ai-integrator-uae-national-only-field-engineering-at-amazon-web-services-aws-4459616402?position=14&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=suYy8hgZkG37o3lG7FlDHQ%3D%3D</t>
+          <t>https://nl.linkedin.com/jobs/view/quantitative-developer-pricing-data-at-optiver-4437686371?position=21&amp;pageNum=0&amp;refId=oiBIn1Czflg0JjZjH5z0Lg%3D%3D&amp;trackingId=bm7u%2BG7QRNRgNoiTgqdkzg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -10355,35 +10355,35 @@
       </c>
       <c r="B157" s="3" t="inlineStr">
         <is>
-          <t>GIS Specialist / Developer</t>
+          <t>Data Analyst — Operational Analysis (Python, Power BI, Modelling) for NATO with security clearance</t>
         </is>
       </c>
       <c r="C157" s="3" t="inlineStr">
         <is>
-          <t>AECOM</t>
+          <t>WLG</t>
         </is>
       </c>
       <c r="D157" s="3" t="inlineStr">
         <is>
-          <t>Dubai, Dubai, United Arab Emirates</t>
+          <t>The Hague, South Holland, Netherlands</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="F157" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G157" s="9" t="inlineStr">
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="F157" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="G157" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H157" s="3" t="inlineStr">
         <is>
-          <t>This is a GIS Specialist role focused on ArcGIS Enterprise administration, spatial analysis, and Python/ArcPy automation, which is completely unrelated to the candidate's core specialization in Generative AI, LLMs, and agentic systems.</t>
+          <t>This is an unrelated junior Data Analyst role focused on operational analysis, dashboards, and spreadsheets rather than Generative AI or advanced data science. Given the candidate's 10+ years of experience as a Lead Data Scientist specializing in LLMs and agentic AI, this position represents a severe mismatch in both domain and seniority.</t>
         </is>
       </c>
       <c r="I157" s="3" t="inlineStr">
@@ -10408,7 +10408,7 @@
       </c>
       <c r="M157" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/gis-specialist-developer-at-aecom-4456869023?position=15&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=lGxG6%2FYECt2YwYGWf5hEZA%3D%3D</t>
+          <t>https://nl.linkedin.com/jobs/view/data-analyst-%E2%80%94-operational-analysis-python-power-bi-modelling-for-nato-with-security-clearance-at-wlg-4458620413?position=26&amp;pageNum=0&amp;refId=oiBIn1Czflg0JjZjH5z0Lg%3D%3D&amp;trackingId=NK7DxxVQL3iwGI1saGNrZg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -10418,35 +10418,35 @@
       </c>
       <c r="B158" s="3" t="inlineStr">
         <is>
-          <t>Quant Desk Lead and Portfolio Manager</t>
+          <t>Hadoop / Big Data Engineer</t>
         </is>
       </c>
       <c r="C158" s="3" t="inlineStr">
         <is>
-          <t>EMCD</t>
+          <t>HTC Global Services</t>
         </is>
       </c>
       <c r="D158" s="3" t="inlineStr">
         <is>
-          <t>Dubai, Dubai, United Arab Emirates</t>
+          <t>Dubai, United Arab Emirates</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="F158" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G158" s="9" t="inlineStr">
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="F158" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="G158" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H158" s="3" t="inlineStr">
         <is>
-          <t>This is a finance and quantitative trading role focused on running a systematic trading desk, portfolio management, and P&amp;L ownership, which is entirely unrelated to the candidate's core specialization in Generative AI, LLMs, and agentic systems.</t>
+          <t>This is a classical data engineering and Hadoop role focusing on infrastructure, Spark, Hive, and data pipelines, which is entirely unrelated to the candidate's core specialization in Generative AI, LLMs, and agentic workflows.</t>
         </is>
       </c>
       <c r="I158" s="3" t="inlineStr">
@@ -10459,9 +10459,9 @@
           <t>Not stated in JD</t>
         </is>
       </c>
-      <c r="K158" s="2" t="inlineStr">
-        <is>
-          <t>From previous run</t>
+      <c r="K158" s="9" t="inlineStr">
+        <is>
+          <t>New this run (2026-08-28 08:27 UTC)</t>
         </is>
       </c>
       <c r="L158" s="2" t="inlineStr">
@@ -10471,7 +10471,7 @@
       </c>
       <c r="M158" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/quant-desk-lead-and-portfolio-manager-at-emcd-4457949555?position=13&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=drHtrw6uBtEz5S2i%2BjBT5A%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/hadoop-big-data-engineer-at-htc-global-services-4460123484?position=9&amp;pageNum=0&amp;refId=zJBbvwb5H0wsbJ5fs9ZTVw%3D%3D&amp;trackingId=SQM7VXeym81F4YKdSlXxkg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -10481,17 +10481,17 @@
       </c>
       <c r="B159" s="3" t="inlineStr">
         <is>
-          <t>Join Norlys Energy Trading</t>
+          <t>National Assistant Planner</t>
         </is>
       </c>
       <c r="C159" s="3" t="inlineStr">
         <is>
-          <t>Norlys Energy Trading A/S</t>
+          <t>Al-Futtaim</t>
         </is>
       </c>
       <c r="D159" s="3" t="inlineStr">
         <is>
-          <t>Aalborg, North Denmark Region, Denmark</t>
+          <t>Dubai, Dubai, United Arab Emirates</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
@@ -10499,17 +10499,17 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F159" s="8" t="n">
+      <c r="F159" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="G159" s="9" t="inlineStr">
+      <c r="G159" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H159" s="3" t="inlineStr">
         <is>
-          <t>This is an open, unsolicited job application for a general talent pool in energy trading, rather than a defined Data Science or Generative AI role. It completely lacks technical specifications, making it impossible to evaluate against the candidate's specialized GenAI and LLM expertise.</t>
+          <t>This is a non-technical retail merchandise planning role focused on financial forecasting, inventory management, and sales planning, which is entirely unrelated to the candidate's GenAI, LLM, and data science specialization.</t>
         </is>
       </c>
       <c r="I159" s="3" t="inlineStr">
@@ -10534,7 +10534,7 @@
       </c>
       <c r="M159" s="6" t="inlineStr">
         <is>
-          <t>https://dk.linkedin.com/jobs/view/join-norlys-energy-trading-at-norlys-energy-trading-a-s-4459158084?position=26&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=Z%2BOuDrbPap3omWro18MA2g%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/national-assistant-planner-at-al-futtaim-4459335643?position=23&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=udE1OmanEOJo5NqnDVVmsw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -10544,35 +10544,35 @@
       </c>
       <c r="B160" s="3" t="inlineStr">
         <is>
-          <t>PhD scholarship in Modeling and Control of Parkinson’s Disease - DTU Electro</t>
+          <t>Forward Deployed AI Integrator (UAE National Only), Field Engineering</t>
         </is>
       </c>
       <c r="C160" s="3" t="inlineStr">
         <is>
-          <t>DTU - Technical University of Denmark</t>
+          <t>Amazon Web Services (AWS)</t>
         </is>
       </c>
       <c r="D160" s="3" t="inlineStr">
         <is>
-          <t>Kongens Lyngby, Capital Region of Denmark, Denmark</t>
+          <t>Dubai, Dubai, United Arab Emirates</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="F160" s="8" t="n">
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="F160" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="G160" s="9" t="inlineStr">
+      <c r="G160" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H160" s="3" t="inlineStr">
         <is>
-          <t>This is a PhD scholarship position in neuroengineering, control systems, and healthcare technology at DTU, which is completely unrelated to the candidate's specialization in Generative AI, LLMs, and agentic systems.</t>
+          <t>Although the role involves AI tooling and Python, it is restricted to UAE Nationals only, making it impossible for the candidate to qualify. Additionally, the position leans heavily toward technical program management rather than hands-on Generative AI and LLM engineering.</t>
         </is>
       </c>
       <c r="I160" s="3" t="inlineStr">
@@ -10582,7 +10582,7 @@
       </c>
       <c r="J160" s="3" t="inlineStr">
         <is>
-          <t>Possible - relocation support mentioned, visa not explicit</t>
+          <t>Not stated in JD</t>
         </is>
       </c>
       <c r="K160" s="2" t="inlineStr">
@@ -10597,7 +10597,7 @@
       </c>
       <c r="M160" s="6" t="inlineStr">
         <is>
-          <t>https://dk.linkedin.com/jobs/view/phd-scholarship-in-modeling-and-control-of-parkinson%E2%80%99s-disease-dtu-electro-at-dtu-technical-university-of-denmark-4459145557?position=20&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=mStwcLkWBAvzmreGSwO4Hw%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/forward-deployed-ai-integrator-uae-national-only-field-engineering-at-amazon-web-services-aws-4459616402?position=14&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=suYy8hgZkG37o3lG7FlDHQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -10607,17 +10607,17 @@
       </c>
       <c r="B161" s="3" t="inlineStr">
         <is>
-          <t>Analytikere med flair for databehandling til PET's kontraspionageindsats mod Rusland</t>
+          <t>GIS Specialist / Developer</t>
         </is>
       </c>
       <c r="C161" s="3" t="inlineStr">
         <is>
-          <t>Politi</t>
+          <t>AECOM</t>
         </is>
       </c>
       <c r="D161" s="3" t="inlineStr">
         <is>
-          <t>Copenhagen, Capital Region of Denmark, Denmark</t>
+          <t>Dubai, Dubai, United Arab Emirates</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
@@ -10625,17 +10625,17 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F161" s="8" t="n">
+      <c r="F161" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="G161" s="9" t="inlineStr">
+      <c r="G161" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H161" s="3" t="inlineStr">
         <is>
-          <t>This is a national security intelligence and counter-espionage analyst role at the Danish Security and Intelligence Service (PET), which is completely unrelated to data science, artificial intelligence, or the candidate's Generative AI and LLM specialization.</t>
+          <t>This is a GIS Specialist role focused on ArcGIS Enterprise administration, spatial analysis, and Python/ArcPy automation, which is completely unrelated to the candidate's core specialization in Generative AI, LLMs, and agentic systems.</t>
         </is>
       </c>
       <c r="I161" s="3" t="inlineStr">
@@ -10660,7 +10660,7 @@
       </c>
       <c r="M161" s="6" t="inlineStr">
         <is>
-          <t>https://dk.linkedin.com/jobs/view/analytikere-med-flair-for-databehandling-til-pet-s-kontraspionageindsats-mod-rusland-at-politi-4457943820?position=18&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=%2FGEw4KOC0oARqkQIDTGJ4Q%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/gis-specialist-developer-at-aecom-4456869023?position=15&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=lGxG6%2FYECt2YwYGWf5hEZA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -10670,17 +10670,17 @@
       </c>
       <c r="B162" s="3" t="inlineStr">
         <is>
-          <t>PostDoc - Uncertainty-Aware Optimization in Inverse Problems for Next-Generation 3D Scanning</t>
+          <t>Quant Desk Lead and Portfolio Manager</t>
         </is>
       </c>
       <c r="C162" s="3" t="inlineStr">
         <is>
-          <t>3Shape</t>
+          <t>EMCD</t>
         </is>
       </c>
       <c r="D162" s="3" t="inlineStr">
         <is>
-          <t>Copenhagen, Capital Region of Denmark, Denmark</t>
+          <t>Dubai, Dubai, United Arab Emirates</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
@@ -10688,17 +10688,17 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F162" s="8" t="n">
+      <c r="F162" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="G162" s="9" t="inlineStr">
+      <c r="G162" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H162" s="3" t="inlineStr">
         <is>
-          <t>This is a PostDoc position focused on mathematical optimization, numerical linear algebra, and uncertainty quantification for 3D scanning, which requires a PhD. It has no overlap with the candidate's specialization in GenAI, LLMs, and agentic systems.</t>
+          <t>This is a finance and quantitative trading role focused on running a systematic trading desk, portfolio management, and P&amp;L ownership, which is entirely unrelated to the candidate's core specialization in Generative AI, LLMs, and agentic systems.</t>
         </is>
       </c>
       <c r="I162" s="3" t="inlineStr">
@@ -10723,7 +10723,7 @@
       </c>
       <c r="M162" s="6" t="inlineStr">
         <is>
-          <t>https://dk.linkedin.com/jobs/view/postdoc-uncertainty-aware-optimization-in-inverse-problems-for-next-generation-3d-scanning-at-3shape-4459171806?position=15&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=bO0aSGZ%2FUAxThXN9yvOERg%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/quant-desk-lead-and-portfolio-manager-at-emcd-4457949555?position=13&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=drHtrw6uBtEz5S2i%2BjBT5A%3D%3D</t>
         </is>
       </c>
     </row>
@@ -10733,17 +10733,17 @@
       </c>
       <c r="B163" s="3" t="inlineStr">
         <is>
-          <t>Scientist, Quantitative Clinical Pharmacology (PK/PD Modeling &amp; Simulation)</t>
+          <t>Join Norlys Energy Trading</t>
         </is>
       </c>
       <c r="C163" s="3" t="inlineStr">
         <is>
-          <t>Hemab Therapeutics</t>
+          <t>Norlys Energy Trading A/S</t>
         </is>
       </c>
       <c r="D163" s="3" t="inlineStr">
         <is>
-          <t>Copenhagen Metropolitan Area</t>
+          <t>Aalborg, North Denmark Region, Denmark</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
@@ -10751,17 +10751,17 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F163" s="8" t="n">
+      <c r="F163" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="G163" s="9" t="inlineStr">
+      <c r="G163" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H163" s="3" t="inlineStr">
         <is>
-          <t>This is a highly specialized biomedical role focusing on Pharmacokinetics/Pharmacodynamics (PK/PD) modeling and clinical pharmacology, requiring a Ph.D. and experience with tools like NONMEM or Monolix. It has zero overlap with the candidate's GenAI, LLM, and data science background.</t>
+          <t>This is an open, unsolicited job application for a general talent pool in energy trading, rather than a defined Data Science or Generative AI role. It completely lacks technical specifications, making it impossible to evaluate against the candidate's specialized GenAI and LLM expertise.</t>
         </is>
       </c>
       <c r="I163" s="3" t="inlineStr">
@@ -10786,7 +10786,7 @@
       </c>
       <c r="M163" s="6" t="inlineStr">
         <is>
-          <t>https://dk.linkedin.com/jobs/view/scientist-quantitative-clinical-pharmacology-pk-pd-modeling-simulation-at-hemab-therapeutics-4457218306?position=14&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=jhTyKvDAQ70R9PD5s0x2yA%3D%3D</t>
+          <t>https://dk.linkedin.com/jobs/view/join-norlys-energy-trading-at-norlys-energy-trading-a-s-4459158084?position=26&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=Z%2BOuDrbPap3omWro18MA2g%3D%3D</t>
         </is>
       </c>
     </row>
@@ -10796,17 +10796,17 @@
       </c>
       <c r="B164" s="3" t="inlineStr">
         <is>
-          <t>Senior Payload Data Operator</t>
+          <t>PhD scholarship in Modeling and Control of Parkinson’s Disease - DTU Electro</t>
         </is>
       </c>
       <c r="C164" s="3" t="inlineStr">
         <is>
-          <t>FADA</t>
+          <t>DTU - Technical University of Denmark</t>
         </is>
       </c>
       <c r="D164" s="3" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>Kongens Lyngby, Capital Region of Denmark, Denmark</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
@@ -10814,17 +10814,17 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F164" s="8" t="n">
+      <c r="F164" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="G164" s="9" t="inlineStr">
+      <c r="G164" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H164" s="3" t="inlineStr">
         <is>
-          <t>This is a satellite payload data engineering role focused on aerospace, remote sensing, and image processing (EO/SAR), which is completely unrelated to the candidate's specialization in GenAI, LLMs, and agentic systems.</t>
+          <t>This is a PhD scholarship position in neuroengineering, control systems, and healthcare technology at DTU, which is completely unrelated to the candidate's specialization in Generative AI, LLMs, and agentic systems.</t>
         </is>
       </c>
       <c r="I164" s="3" t="inlineStr">
@@ -10834,7 +10834,7 @@
       </c>
       <c r="J164" s="3" t="inlineStr">
         <is>
-          <t>Not stated in JD</t>
+          <t>Possible - relocation support mentioned, visa not explicit</t>
         </is>
       </c>
       <c r="K164" s="2" t="inlineStr">
@@ -10849,7 +10849,7 @@
       </c>
       <c r="M164" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/senior-payload-data-operator-at-fada-4448986926?position=20&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=xdfP2za0I45WGIW%2FRJb%2BgA%3D%3D</t>
+          <t>https://dk.linkedin.com/jobs/view/phd-scholarship-in-modeling-and-control-of-parkinson%E2%80%99s-disease-dtu-electro-at-dtu-technical-university-of-denmark-4459145557?position=20&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=mStwcLkWBAvzmreGSwO4Hw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -10859,35 +10859,35 @@
       </c>
       <c r="B165" s="3" t="inlineStr">
         <is>
-          <t>Arabic Speech And Natural Language Processing Specialist</t>
+          <t>Analytikere med flair for databehandling til PET's kontraspionageindsats mod Rusland</t>
         </is>
       </c>
       <c r="C165" s="3" t="inlineStr">
         <is>
-          <t>Birbal AI</t>
+          <t>Politi</t>
         </is>
       </c>
       <c r="D165" s="3" t="inlineStr">
         <is>
-          <t>Abu Dhabi Emirate, United Arab Emirates</t>
+          <t>Copenhagen, Capital Region of Denmark, Denmark</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="F165" s="8" t="n">
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="F165" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="G165" s="9" t="inlineStr">
+      <c r="G165" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H165" s="3" t="inlineStr">
         <is>
-          <t>The role requires specialized expertise in Arabic speech technology (ASR, TTS, audio DSP) and native command of Gulf Arabic dialects, which does not match the candidate's core background in GenAI, LLMs, and RAG for English-language banking and HR use cases.</t>
+          <t>This is a national security intelligence and counter-espionage analyst role at the Danish Security and Intelligence Service (PET), which is completely unrelated to data science, artificial intelligence, or the candidate's Generative AI and LLM specialization.</t>
         </is>
       </c>
       <c r="I165" s="3" t="inlineStr">
@@ -10912,7 +10912,7 @@
       </c>
       <c r="M165" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/arabic-speech-and-natural-language-processing-specialist-at-birbal-ai-4457738899?position=14&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=ztG06Ly%2FIZ3fxm%2Fhvl626A%3D%3D</t>
+          <t>https://dk.linkedin.com/jobs/view/analytikere-med-flair-for-databehandling-til-pet-s-kontraspionageindsats-mod-rusland-at-politi-4457943820?position=18&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=%2FGEw4KOC0oARqkQIDTGJ4Q%3D%3D</t>
         </is>
       </c>
     </row>
@@ -10922,35 +10922,35 @@
       </c>
       <c r="B166" s="3" t="inlineStr">
         <is>
-          <t>Member of Technical Staff - Medical Research (Remote)</t>
+          <t>PostDoc - Uncertainty-Aware Optimization in Inverse Problems for Next-Generation 3D Scanning</t>
         </is>
       </c>
       <c r="C166" s="3" t="inlineStr">
         <is>
-          <t>Hire Feed</t>
+          <t>3Shape</t>
         </is>
       </c>
       <c r="D166" s="3" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>Copenhagen, Capital Region of Denmark, Denmark</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="F166" s="8" t="n">
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="F166" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="G166" s="9" t="inlineStr">
+      <c r="G166" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H166" s="3" t="inlineStr">
         <is>
-          <t>This role is completely unrelated to the candidate's specialization in Generative AI, LLMs, and agentic workflows, focusing instead on medical imaging, computational biology, and clinical research requiring a PhD.</t>
+          <t>This is a PostDoc position focused on mathematical optimization, numerical linear algebra, and uncertainty quantification for 3D scanning, which requires a PhD. It has no overlap with the candidate's specialization in GenAI, LLMs, and agentic systems.</t>
         </is>
       </c>
       <c r="I166" s="3" t="inlineStr">
@@ -10975,7 +10975,7 @@
       </c>
       <c r="M166" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/member-of-technical-staff-medical-research-remote-at-hire-feed-4459638503?position=3&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=b91zxKPZNgdFnMmW%2FlYbHA%3D%3D</t>
+          <t>https://dk.linkedin.com/jobs/view/postdoc-uncertainty-aware-optimization-in-inverse-problems-for-next-generation-3d-scanning-at-3shape-4459171806?position=15&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=bO0aSGZ%2FUAxThXN9yvOERg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -10985,60 +10985,438 @@
       </c>
       <c r="B167" s="3" t="inlineStr">
         <is>
+          <t>Scientist, Quantitative Clinical Pharmacology (PK/PD Modeling &amp; Simulation)</t>
+        </is>
+      </c>
+      <c r="C167" s="3" t="inlineStr">
+        <is>
+          <t>Hemab Therapeutics</t>
+        </is>
+      </c>
+      <c r="D167" s="3" t="inlineStr">
+        <is>
+          <t>Copenhagen Metropolitan Area</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="F167" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G167" s="8" t="inlineStr">
+        <is>
+          <t>Below threshold</t>
+        </is>
+      </c>
+      <c r="H167" s="3" t="inlineStr">
+        <is>
+          <t>This is a highly specialized biomedical role focusing on Pharmacokinetics/Pharmacodynamics (PK/PD) modeling and clinical pharmacology, requiring a Ph.D. and experience with tools like NONMEM or Monolix. It has zero overlap with the candidate's GenAI, LLM, and data science background.</t>
+        </is>
+      </c>
+      <c r="I167" s="3" t="inlineStr">
+        <is>
+          <t>Not stated in JD</t>
+        </is>
+      </c>
+      <c r="J167" s="3" t="inlineStr">
+        <is>
+          <t>Not stated in JD</t>
+        </is>
+      </c>
+      <c r="K167" s="2" t="inlineStr">
+        <is>
+          <t>From previous run</t>
+        </is>
+      </c>
+      <c r="L167" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="M167" s="6" t="inlineStr">
+        <is>
+          <t>https://dk.linkedin.com/jobs/view/scientist-quantitative-clinical-pharmacology-pk-pd-modeling-simulation-at-hemab-therapeutics-4457218306?position=14&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=jhTyKvDAQ70R9PD5s0x2yA%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="168" ht="55" customHeight="1">
+      <c r="A168" s="2" t="n">
+        <v>167</v>
+      </c>
+      <c r="B168" s="3" t="inlineStr">
+        <is>
+          <t>Senior Payload Data Operator</t>
+        </is>
+      </c>
+      <c r="C168" s="3" t="inlineStr">
+        <is>
+          <t>FADA</t>
+        </is>
+      </c>
+      <c r="D168" s="3" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="F168" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G168" s="8" t="inlineStr">
+        <is>
+          <t>Below threshold</t>
+        </is>
+      </c>
+      <c r="H168" s="3" t="inlineStr">
+        <is>
+          <t>This is a satellite payload data engineering role focused on aerospace, remote sensing, and image processing (EO/SAR), which is completely unrelated to the candidate's specialization in GenAI, LLMs, and agentic systems.</t>
+        </is>
+      </c>
+      <c r="I168" s="3" t="inlineStr">
+        <is>
+          <t>Not stated in JD</t>
+        </is>
+      </c>
+      <c r="J168" s="3" t="inlineStr">
+        <is>
+          <t>Not stated in JD</t>
+        </is>
+      </c>
+      <c r="K168" s="2" t="inlineStr">
+        <is>
+          <t>From previous run</t>
+        </is>
+      </c>
+      <c r="L168" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="M168" s="6" t="inlineStr">
+        <is>
+          <t>https://ae.linkedin.com/jobs/view/senior-payload-data-operator-at-fada-4448986926?position=20&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=xdfP2za0I45WGIW%2FRJb%2BgA%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="169" ht="55" customHeight="1">
+      <c r="A169" s="2" t="n">
+        <v>168</v>
+      </c>
+      <c r="B169" s="3" t="inlineStr">
+        <is>
+          <t>Arabic Speech And Natural Language Processing Specialist</t>
+        </is>
+      </c>
+      <c r="C169" s="3" t="inlineStr">
+        <is>
+          <t>Birbal AI</t>
+        </is>
+      </c>
+      <c r="D169" s="3" t="inlineStr">
+        <is>
+          <t>Abu Dhabi Emirate, United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="F169" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G169" s="8" t="inlineStr">
+        <is>
+          <t>Below threshold</t>
+        </is>
+      </c>
+      <c r="H169" s="3" t="inlineStr">
+        <is>
+          <t>The role requires specialized expertise in Arabic speech technology (ASR, TTS, audio DSP) and native command of Gulf Arabic dialects, which does not match the candidate's core background in GenAI, LLMs, and RAG for English-language banking and HR use cases.</t>
+        </is>
+      </c>
+      <c r="I169" s="3" t="inlineStr">
+        <is>
+          <t>Not stated in JD</t>
+        </is>
+      </c>
+      <c r="J169" s="3" t="inlineStr">
+        <is>
+          <t>Not stated in JD</t>
+        </is>
+      </c>
+      <c r="K169" s="2" t="inlineStr">
+        <is>
+          <t>From previous run</t>
+        </is>
+      </c>
+      <c r="L169" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="M169" s="6" t="inlineStr">
+        <is>
+          <t>https://ae.linkedin.com/jobs/view/arabic-speech-and-natural-language-processing-specialist-at-birbal-ai-4457738899?position=14&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=ztG06Ly%2FIZ3fxm%2Fhvl626A%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="170" ht="55" customHeight="1">
+      <c r="A170" s="2" t="n">
+        <v>169</v>
+      </c>
+      <c r="B170" s="3" t="inlineStr">
+        <is>
+          <t>Member of Technical Staff - Medical Research (Remote)</t>
+        </is>
+      </c>
+      <c r="C170" s="3" t="inlineStr">
+        <is>
+          <t>Hire Feed</t>
+        </is>
+      </c>
+      <c r="D170" s="3" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="F170" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G170" s="8" t="inlineStr">
+        <is>
+          <t>Below threshold</t>
+        </is>
+      </c>
+      <c r="H170" s="3" t="inlineStr">
+        <is>
+          <t>This role is completely unrelated to the candidate's specialization in Generative AI, LLMs, and agentic workflows, focusing instead on medical imaging, computational biology, and clinical research requiring a PhD.</t>
+        </is>
+      </c>
+      <c r="I170" s="3" t="inlineStr">
+        <is>
+          <t>Not stated in JD</t>
+        </is>
+      </c>
+      <c r="J170" s="3" t="inlineStr">
+        <is>
+          <t>Not stated in JD</t>
+        </is>
+      </c>
+      <c r="K170" s="2" t="inlineStr">
+        <is>
+          <t>From previous run</t>
+        </is>
+      </c>
+      <c r="L170" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="M170" s="6" t="inlineStr">
+        <is>
+          <t>https://ae.linkedin.com/jobs/view/member-of-technical-staff-medical-research-remote-at-hire-feed-4459638503?position=3&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=b91zxKPZNgdFnMmW%2FlYbHA%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="171" ht="55" customHeight="1">
+      <c r="A171" s="2" t="n">
+        <v>170</v>
+      </c>
+      <c r="B171" s="3" t="inlineStr">
+        <is>
           <t>AI Image Specialist</t>
         </is>
       </c>
-      <c r="C167" s="3" t="inlineStr">
+      <c r="C171" s="3" t="inlineStr">
         <is>
           <t>Puffy</t>
         </is>
       </c>
-      <c r="D167" s="3" t="inlineStr">
+      <c r="D171" s="3" t="inlineStr">
         <is>
           <t>Dubai, United Arab Emirates</t>
         </is>
       </c>
-      <c r="E167" s="2" t="inlineStr">
+      <c r="E171" s="2" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="F167" s="8" t="n">
+      <c r="F171" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="G167" s="9" t="inlineStr">
-        <is>
-          <t>Below threshold</t>
-        </is>
-      </c>
-      <c r="H167" s="3" t="inlineStr">
+      <c r="G171" s="8" t="inlineStr">
+        <is>
+          <t>Below threshold</t>
+        </is>
+      </c>
+      <c r="H171" s="3" t="inlineStr">
         <is>
           <t>This is an AI Image Specialist role focused on generative visual design and creative production (Midjourney, DALL-E, image synthesis), which is completely unrelated to the candidate's core specialization in LLMs, RAG, LangChain, and agentic AI pipelines for data science and enterprise applications.</t>
         </is>
       </c>
-      <c r="I167" s="3" t="inlineStr">
-        <is>
-          <t>Not stated in JD</t>
-        </is>
-      </c>
-      <c r="J167" s="3" t="inlineStr">
+      <c r="I171" s="3" t="inlineStr">
+        <is>
+          <t>Not stated in JD</t>
+        </is>
+      </c>
+      <c r="J171" s="3" t="inlineStr">
         <is>
           <t>Yes - explicitly stated in JD</t>
         </is>
       </c>
-      <c r="K167" s="7" t="inlineStr">
-        <is>
-          <t>New this run (2026-08-27 15:40 UTC)</t>
-        </is>
-      </c>
-      <c r="L167" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="M167" s="6" t="inlineStr">
+      <c r="K171" s="2" t="inlineStr">
+        <is>
+          <t>From previous run</t>
+        </is>
+      </c>
+      <c r="L171" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="M171" s="6" t="inlineStr">
         <is>
           <t>https://ae.linkedin.com/jobs/view/ai-image-specialist-at-puffy-4457756193?position=10&amp;pageNum=0&amp;refId=50H6yCrEXIuhgr6eqEojNg%3D%3D&amp;trackingId=9EIvgvUNu%2BE37717JffiJA%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="172" ht="55" customHeight="1">
+      <c r="A172" s="2" t="n">
+        <v>171</v>
+      </c>
+      <c r="B172" s="3" t="inlineStr">
+        <is>
+          <t>Market Operations &amp; Analytics Specialist — Institutional</t>
+        </is>
+      </c>
+      <c r="C172" s="3" t="inlineStr">
+        <is>
+          <t>Confidential</t>
+        </is>
+      </c>
+      <c r="D172" s="3" t="inlineStr">
+        <is>
+          <t>Dubai, United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="F172" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G172" s="8" t="inlineStr">
+        <is>
+          <t>Below threshold</t>
+        </is>
+      </c>
+      <c r="H172" s="3" t="inlineStr">
+        <is>
+          <t>This role is completely unrelated to data science, artificial intelligence, LLMs, or generative AI, focusing entirely on cryptocurrency exchange operations, institutional client management, and trading analytics instead.</t>
+        </is>
+      </c>
+      <c r="I172" s="3" t="inlineStr">
+        <is>
+          <t>Not stated in JD</t>
+        </is>
+      </c>
+      <c r="J172" s="3" t="inlineStr">
+        <is>
+          <t>Not stated in JD</t>
+        </is>
+      </c>
+      <c r="K172" s="9" t="inlineStr">
+        <is>
+          <t>New this run (2026-08-28 08:27 UTC)</t>
+        </is>
+      </c>
+      <c r="L172" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="M172" s="6" t="inlineStr">
+        <is>
+          <t>https://ae.linkedin.com/jobs/view/market-operations-analytics-specialist-%E2%80%94-institutional-at-confidential-4453037100?position=10&amp;pageNum=0&amp;refId=zJBbvwb5H0wsbJ5fs9ZTVw%3D%3D&amp;trackingId=ENnWCvoEQXOg1fXKuxlBug%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="173" ht="55" customHeight="1">
+      <c r="A173" s="2" t="n">
+        <v>172</v>
+      </c>
+      <c r="B173" s="3" t="inlineStr">
+        <is>
+          <t>Quantitative Developer, Systematic Equities</t>
+        </is>
+      </c>
+      <c r="C173" s="3" t="inlineStr">
+        <is>
+          <t>Millennium</t>
+        </is>
+      </c>
+      <c r="D173" s="3" t="inlineStr">
+        <is>
+          <t>Dubai, Dubai, United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="F173" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G173" s="8" t="inlineStr">
+        <is>
+          <t>Below threshold</t>
+        </is>
+      </c>
+      <c r="H173" s="3" t="inlineStr">
+        <is>
+          <t>This role is a quantitative software engineering position focused on low-latency trading infrastructure, C++/C# development, and execution systems for a hedge fund, which is entirely unrelated to the candidate's specialization in GenAI, LLMs, and agentic architectures.</t>
+        </is>
+      </c>
+      <c r="I173" s="3" t="inlineStr">
+        <is>
+          <t>Not stated in JD</t>
+        </is>
+      </c>
+      <c r="J173" s="3" t="inlineStr">
+        <is>
+          <t>Not stated in JD</t>
+        </is>
+      </c>
+      <c r="K173" s="9" t="inlineStr">
+        <is>
+          <t>New this run (2026-08-28 08:27 UTC)</t>
+        </is>
+      </c>
+      <c r="L173" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="M173" s="6" t="inlineStr">
+        <is>
+          <t>https://ae.linkedin.com/jobs/view/quantitative-developer-systematic-equities-at-millennium-4290849018?position=6&amp;pageNum=0&amp;refId=zJBbvwb5H0wsbJ5fs9ZTVw%3D%3D&amp;trackingId=8TTWkyG2j%2F7MELtLSQ5VCA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -11210,6 +11588,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M165" r:id="rId164"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M166" r:id="rId165"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M173" r:id="rId172"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/job_matches.xlsx
+++ b/data/job_matches.xlsx
@@ -68,14 +68,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-        <bgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00FFC7CE"/>
+        <bgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-        <bgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
@@ -131,10 +131,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -517,7 +517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M186"/>
+  <dimension ref="A1:M188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -775,9 +775,9 @@
           <t>Not stated in JD</t>
         </is>
       </c>
-      <c r="K4" s="7" t="inlineStr">
-        <is>
-          <t>New this run (2026-08-28 22:31 UTC)</t>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>From previous run</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -1090,9 +1090,9 @@
           <t>Not stated in JD</t>
         </is>
       </c>
-      <c r="K9" s="7" t="inlineStr">
-        <is>
-          <t>New this run (2026-08-28 22:31 UTC)</t>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>From previous run</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1886,10 +1886,10 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F22" s="8" t="n">
+      <c r="F22" s="7" t="n">
         <v>68</v>
       </c>
-      <c r="G22" s="9" t="inlineStr">
+      <c r="G22" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -1949,10 +1949,10 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F23" s="8" t="n">
+      <c r="F23" s="7" t="n">
         <v>68</v>
       </c>
-      <c r="G23" s="9" t="inlineStr">
+      <c r="G23" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -2012,10 +2012,10 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F24" s="8" t="n">
+      <c r="F24" s="7" t="n">
         <v>68</v>
       </c>
-      <c r="G24" s="9" t="inlineStr">
+      <c r="G24" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -2075,10 +2075,10 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F25" s="8" t="n">
+      <c r="F25" s="7" t="n">
         <v>68</v>
       </c>
-      <c r="G25" s="9" t="inlineStr">
+      <c r="G25" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -2138,10 +2138,10 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="F26" s="8" t="n">
+      <c r="F26" s="7" t="n">
         <v>68</v>
       </c>
-      <c r="G26" s="9" t="inlineStr">
+      <c r="G26" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -2201,10 +2201,10 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="F27" s="8" t="n">
+      <c r="F27" s="7" t="n">
         <v>68</v>
       </c>
-      <c r="G27" s="9" t="inlineStr">
+      <c r="G27" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -2264,10 +2264,10 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="F28" s="8" t="n">
+      <c r="F28" s="7" t="n">
         <v>68</v>
       </c>
-      <c r="G28" s="9" t="inlineStr">
+      <c r="G28" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -2327,10 +2327,10 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="F29" s="8" t="n">
+      <c r="F29" s="7" t="n">
         <v>68</v>
       </c>
-      <c r="G29" s="9" t="inlineStr">
+      <c r="G29" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -2390,10 +2390,10 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="F30" s="8" t="n">
+      <c r="F30" s="7" t="n">
         <v>68</v>
       </c>
-      <c r="G30" s="9" t="inlineStr">
+      <c r="G30" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -2453,10 +2453,10 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F31" s="8" t="n">
+      <c r="F31" s="7" t="n">
         <v>65</v>
       </c>
-      <c r="G31" s="9" t="inlineStr">
+      <c r="G31" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -2516,10 +2516,10 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F32" s="8" t="n">
+      <c r="F32" s="7" t="n">
         <v>65</v>
       </c>
-      <c r="G32" s="9" t="inlineStr">
+      <c r="G32" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -2579,10 +2579,10 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="F33" s="8" t="n">
+      <c r="F33" s="7" t="n">
         <v>65</v>
       </c>
-      <c r="G33" s="9" t="inlineStr">
+      <c r="G33" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -2642,10 +2642,10 @@
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="F34" s="8" t="n">
+      <c r="F34" s="7" t="n">
         <v>65</v>
       </c>
-      <c r="G34" s="9" t="inlineStr">
+      <c r="G34" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -2705,10 +2705,10 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F35" s="8" t="n">
+      <c r="F35" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="G35" s="9" t="inlineStr">
+      <c r="G35" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -2768,10 +2768,10 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F36" s="8" t="n">
+      <c r="F36" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="G36" s="9" t="inlineStr">
+      <c r="G36" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -2831,10 +2831,10 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="F37" s="8" t="n">
+      <c r="F37" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="G37" s="9" t="inlineStr">
+      <c r="G37" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -2894,10 +2894,10 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F38" s="8" t="n">
+      <c r="F38" s="7" t="n">
         <v>45</v>
       </c>
-      <c r="G38" s="9" t="inlineStr">
+      <c r="G38" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -2957,10 +2957,10 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F39" s="8" t="n">
+      <c r="F39" s="7" t="n">
         <v>45</v>
       </c>
-      <c r="G39" s="9" t="inlineStr">
+      <c r="G39" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -3020,10 +3020,10 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="F40" s="8" t="n">
+      <c r="F40" s="7" t="n">
         <v>45</v>
       </c>
-      <c r="G40" s="9" t="inlineStr">
+      <c r="G40" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -3083,10 +3083,10 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F41" s="8" t="n">
+      <c r="F41" s="7" t="n">
         <v>45</v>
       </c>
-      <c r="G41" s="9" t="inlineStr">
+      <c r="G41" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -3146,10 +3146,10 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F42" s="8" t="n">
+      <c r="F42" s="7" t="n">
         <v>45</v>
       </c>
-      <c r="G42" s="9" t="inlineStr">
+      <c r="G42" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -3209,10 +3209,10 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="F43" s="8" t="n">
+      <c r="F43" s="7" t="n">
         <v>45</v>
       </c>
-      <c r="G43" s="9" t="inlineStr">
+      <c r="G43" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -3272,10 +3272,10 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F44" s="8" t="n">
+      <c r="F44" s="7" t="n">
         <v>45</v>
       </c>
-      <c r="G44" s="9" t="inlineStr">
+      <c r="G44" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -3335,10 +3335,10 @@
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="F45" s="8" t="n">
+      <c r="F45" s="7" t="n">
         <v>45</v>
       </c>
-      <c r="G45" s="9" t="inlineStr">
+      <c r="G45" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -3358,9 +3358,9 @@
           <t>Not stated in JD</t>
         </is>
       </c>
-      <c r="K45" s="7" t="inlineStr">
-        <is>
-          <t>New this run (2026-08-28 22:31 UTC)</t>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>From previous run</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
@@ -3398,10 +3398,10 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F46" s="8" t="n">
+      <c r="F46" s="7" t="n">
         <v>42</v>
       </c>
-      <c r="G46" s="9" t="inlineStr">
+      <c r="G46" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -3461,10 +3461,10 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="F47" s="8" t="n">
+      <c r="F47" s="7" t="n">
         <v>40</v>
       </c>
-      <c r="G47" s="9" t="inlineStr">
+      <c r="G47" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -3524,10 +3524,10 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F48" s="8" t="n">
+      <c r="F48" s="7" t="n">
         <v>40</v>
       </c>
-      <c r="G48" s="9" t="inlineStr">
+      <c r="G48" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -3587,10 +3587,10 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F49" s="8" t="n">
+      <c r="F49" s="7" t="n">
         <v>40</v>
       </c>
-      <c r="G49" s="9" t="inlineStr">
+      <c r="G49" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -3650,10 +3650,10 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="F50" s="8" t="n">
+      <c r="F50" s="7" t="n">
         <v>40</v>
       </c>
-      <c r="G50" s="9" t="inlineStr">
+      <c r="G50" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -3713,10 +3713,10 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="F51" s="8" t="n">
+      <c r="F51" s="7" t="n">
         <v>38</v>
       </c>
-      <c r="G51" s="9" t="inlineStr">
+      <c r="G51" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -3776,10 +3776,10 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="F52" s="8" t="n">
+      <c r="F52" s="7" t="n">
         <v>35</v>
       </c>
-      <c r="G52" s="9" t="inlineStr">
+      <c r="G52" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -3839,10 +3839,10 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F53" s="8" t="n">
+      <c r="F53" s="7" t="n">
         <v>35</v>
       </c>
-      <c r="G53" s="9" t="inlineStr">
+      <c r="G53" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -3902,10 +3902,10 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F54" s="8" t="n">
+      <c r="F54" s="7" t="n">
         <v>35</v>
       </c>
-      <c r="G54" s="9" t="inlineStr">
+      <c r="G54" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -3965,10 +3965,10 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F55" s="8" t="n">
+      <c r="F55" s="7" t="n">
         <v>35</v>
       </c>
-      <c r="G55" s="9" t="inlineStr">
+      <c r="G55" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -4028,10 +4028,10 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F56" s="8" t="n">
+      <c r="F56" s="7" t="n">
         <v>35</v>
       </c>
-      <c r="G56" s="9" t="inlineStr">
+      <c r="G56" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -4091,10 +4091,10 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F57" s="8" t="n">
+      <c r="F57" s="7" t="n">
         <v>35</v>
       </c>
-      <c r="G57" s="9" t="inlineStr">
+      <c r="G57" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -4154,10 +4154,10 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F58" s="8" t="n">
+      <c r="F58" s="7" t="n">
         <v>35</v>
       </c>
-      <c r="G58" s="9" t="inlineStr">
+      <c r="G58" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -4217,10 +4217,10 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F59" s="8" t="n">
+      <c r="F59" s="7" t="n">
         <v>35</v>
       </c>
-      <c r="G59" s="9" t="inlineStr">
+      <c r="G59" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -4280,10 +4280,10 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F60" s="8" t="n">
+      <c r="F60" s="7" t="n">
         <v>35</v>
       </c>
-      <c r="G60" s="9" t="inlineStr">
+      <c r="G60" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -4343,10 +4343,10 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F61" s="8" t="n">
+      <c r="F61" s="7" t="n">
         <v>35</v>
       </c>
-      <c r="G61" s="9" t="inlineStr">
+      <c r="G61" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -4406,10 +4406,10 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F62" s="8" t="n">
+      <c r="F62" s="7" t="n">
         <v>35</v>
       </c>
-      <c r="G62" s="9" t="inlineStr">
+      <c r="G62" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -4469,10 +4469,10 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F63" s="8" t="n">
+      <c r="F63" s="7" t="n">
         <v>35</v>
       </c>
-      <c r="G63" s="9" t="inlineStr">
+      <c r="G63" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -4532,10 +4532,10 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F64" s="8" t="n">
+      <c r="F64" s="7" t="n">
         <v>35</v>
       </c>
-      <c r="G64" s="9" t="inlineStr">
+      <c r="G64" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -4595,10 +4595,10 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F65" s="8" t="n">
+      <c r="F65" s="7" t="n">
         <v>35</v>
       </c>
-      <c r="G65" s="9" t="inlineStr">
+      <c r="G65" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -4658,10 +4658,10 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F66" s="8" t="n">
+      <c r="F66" s="7" t="n">
         <v>35</v>
       </c>
-      <c r="G66" s="9" t="inlineStr">
+      <c r="G66" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -4721,10 +4721,10 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F67" s="8" t="n">
+      <c r="F67" s="7" t="n">
         <v>35</v>
       </c>
-      <c r="G67" s="9" t="inlineStr">
+      <c r="G67" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -4784,10 +4784,10 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="F68" s="8" t="n">
+      <c r="F68" s="7" t="n">
         <v>35</v>
       </c>
-      <c r="G68" s="9" t="inlineStr">
+      <c r="G68" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -4847,10 +4847,10 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="F69" s="8" t="n">
+      <c r="F69" s="7" t="n">
         <v>35</v>
       </c>
-      <c r="G69" s="9" t="inlineStr">
+      <c r="G69" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -4910,10 +4910,10 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="F70" s="8" t="n">
+      <c r="F70" s="7" t="n">
         <v>35</v>
       </c>
-      <c r="G70" s="9" t="inlineStr">
+      <c r="G70" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -4973,10 +4973,10 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="F71" s="8" t="n">
+      <c r="F71" s="7" t="n">
         <v>35</v>
       </c>
-      <c r="G71" s="9" t="inlineStr">
+      <c r="G71" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -5036,10 +5036,10 @@
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="F72" s="8" t="n">
+      <c r="F72" s="7" t="n">
         <v>35</v>
       </c>
-      <c r="G72" s="9" t="inlineStr">
+      <c r="G72" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -5059,9 +5059,9 @@
           <t>Not stated in JD</t>
         </is>
       </c>
-      <c r="K72" s="7" t="inlineStr">
-        <is>
-          <t>New this run (2026-08-28 22:31 UTC)</t>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>From previous run</t>
         </is>
       </c>
       <c r="L72" s="2" t="inlineStr">
@@ -5099,10 +5099,10 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F73" s="8" t="n">
+      <c r="F73" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="G73" s="9" t="inlineStr">
+      <c r="G73" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -5162,10 +5162,10 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F74" s="8" t="n">
+      <c r="F74" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="G74" s="9" t="inlineStr">
+      <c r="G74" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -5225,10 +5225,10 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F75" s="8" t="n">
+      <c r="F75" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="G75" s="9" t="inlineStr">
+      <c r="G75" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -5288,10 +5288,10 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F76" s="8" t="n">
+      <c r="F76" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="G76" s="9" t="inlineStr">
+      <c r="G76" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -5351,10 +5351,10 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F77" s="8" t="n">
+      <c r="F77" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="G77" s="9" t="inlineStr">
+      <c r="G77" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -5414,10 +5414,10 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F78" s="8" t="n">
+      <c r="F78" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="G78" s="9" t="inlineStr">
+      <c r="G78" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -5477,10 +5477,10 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F79" s="8" t="n">
+      <c r="F79" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="G79" s="9" t="inlineStr">
+      <c r="G79" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -5540,10 +5540,10 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F80" s="8" t="n">
+      <c r="F80" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="G80" s="9" t="inlineStr">
+      <c r="G80" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -5603,10 +5603,10 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F81" s="8" t="n">
+      <c r="F81" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="G81" s="9" t="inlineStr">
+      <c r="G81" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -5666,10 +5666,10 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F82" s="8" t="n">
+      <c r="F82" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="G82" s="9" t="inlineStr">
+      <c r="G82" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -5729,10 +5729,10 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F83" s="8" t="n">
+      <c r="F83" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="G83" s="9" t="inlineStr">
+      <c r="G83" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -5792,10 +5792,10 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F84" s="8" t="n">
+      <c r="F84" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="G84" s="9" t="inlineStr">
+      <c r="G84" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -5855,10 +5855,10 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F85" s="8" t="n">
+      <c r="F85" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="G85" s="9" t="inlineStr">
+      <c r="G85" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -5918,10 +5918,10 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="F86" s="8" t="n">
+      <c r="F86" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="G86" s="9" t="inlineStr">
+      <c r="G86" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -5981,10 +5981,10 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="F87" s="8" t="n">
+      <c r="F87" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="G87" s="9" t="inlineStr">
+      <c r="G87" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -6044,10 +6044,10 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="F88" s="8" t="n">
+      <c r="F88" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="G88" s="9" t="inlineStr">
+      <c r="G88" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -6107,10 +6107,10 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="F89" s="8" t="n">
+      <c r="F89" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="G89" s="9" t="inlineStr">
+      <c r="G89" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -6170,10 +6170,10 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="F90" s="8" t="n">
+      <c r="F90" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="G90" s="9" t="inlineStr">
+      <c r="G90" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -6233,10 +6233,10 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F91" s="8" t="n">
+      <c r="F91" s="7" t="n">
         <v>25</v>
       </c>
-      <c r="G91" s="9" t="inlineStr">
+      <c r="G91" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -6296,10 +6296,10 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F92" s="8" t="n">
+      <c r="F92" s="7" t="n">
         <v>25</v>
       </c>
-      <c r="G92" s="9" t="inlineStr">
+      <c r="G92" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -6359,10 +6359,10 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F93" s="8" t="n">
+      <c r="F93" s="7" t="n">
         <v>25</v>
       </c>
-      <c r="G93" s="9" t="inlineStr">
+      <c r="G93" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -6422,10 +6422,10 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F94" s="8" t="n">
+      <c r="F94" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="G94" s="9" t="inlineStr">
+      <c r="G94" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -6485,10 +6485,10 @@
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="F95" s="8" t="n">
+      <c r="F95" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="G95" s="9" t="inlineStr">
+      <c r="G95" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -6548,10 +6548,10 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F96" s="8" t="n">
+      <c r="F96" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="G96" s="9" t="inlineStr">
+      <c r="G96" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -6611,10 +6611,10 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F97" s="8" t="n">
+      <c r="F97" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="G97" s="9" t="inlineStr">
+      <c r="G97" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -6674,10 +6674,10 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F98" s="8" t="n">
+      <c r="F98" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="G98" s="9" t="inlineStr">
+      <c r="G98" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -6737,10 +6737,10 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F99" s="8" t="n">
+      <c r="F99" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="G99" s="9" t="inlineStr">
+      <c r="G99" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -6800,10 +6800,10 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F100" s="8" t="n">
+      <c r="F100" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="G100" s="9" t="inlineStr">
+      <c r="G100" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -6863,10 +6863,10 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F101" s="8" t="n">
+      <c r="F101" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="G101" s="9" t="inlineStr">
+      <c r="G101" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -6926,10 +6926,10 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F102" s="8" t="n">
+      <c r="F102" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="G102" s="9" t="inlineStr">
+      <c r="G102" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -6989,10 +6989,10 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F103" s="8" t="n">
+      <c r="F103" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="G103" s="9" t="inlineStr">
+      <c r="G103" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -7052,10 +7052,10 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F104" s="8" t="n">
+      <c r="F104" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="G104" s="9" t="inlineStr">
+      <c r="G104" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -7115,10 +7115,10 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F105" s="8" t="n">
+      <c r="F105" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="G105" s="9" t="inlineStr">
+      <c r="G105" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -7178,10 +7178,10 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F106" s="8" t="n">
+      <c r="F106" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="G106" s="9" t="inlineStr">
+      <c r="G106" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -7241,10 +7241,10 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F107" s="8" t="n">
+      <c r="F107" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="G107" s="9" t="inlineStr">
+      <c r="G107" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -7304,10 +7304,10 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F108" s="8" t="n">
+      <c r="F108" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="G108" s="9" t="inlineStr">
+      <c r="G108" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -7367,10 +7367,10 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F109" s="8" t="n">
+      <c r="F109" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="G109" s="9" t="inlineStr">
+      <c r="G109" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -7430,10 +7430,10 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F110" s="8" t="n">
+      <c r="F110" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="G110" s="9" t="inlineStr">
+      <c r="G110" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -7493,10 +7493,10 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F111" s="8" t="n">
+      <c r="F111" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="G111" s="9" t="inlineStr">
+      <c r="G111" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -7556,10 +7556,10 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F112" s="8" t="n">
+      <c r="F112" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="G112" s="9" t="inlineStr">
+      <c r="G112" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -7619,10 +7619,10 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F113" s="8" t="n">
+      <c r="F113" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="G113" s="9" t="inlineStr">
+      <c r="G113" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -7682,10 +7682,10 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F114" s="8" t="n">
+      <c r="F114" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="G114" s="9" t="inlineStr">
+      <c r="G114" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -7745,10 +7745,10 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F115" s="8" t="n">
+      <c r="F115" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="G115" s="9" t="inlineStr">
+      <c r="G115" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -7808,10 +7808,10 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F116" s="8" t="n">
+      <c r="F116" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="G116" s="9" t="inlineStr">
+      <c r="G116" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -7871,10 +7871,10 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F117" s="8" t="n">
+      <c r="F117" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="G117" s="9" t="inlineStr">
+      <c r="G117" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -7934,10 +7934,10 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F118" s="8" t="n">
+      <c r="F118" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="G118" s="9" t="inlineStr">
+      <c r="G118" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -7997,10 +7997,10 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F119" s="8" t="n">
+      <c r="F119" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="G119" s="9" t="inlineStr">
+      <c r="G119" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -8060,10 +8060,10 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F120" s="8" t="n">
+      <c r="F120" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="G120" s="9" t="inlineStr">
+      <c r="G120" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -8123,10 +8123,10 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="F121" s="8" t="n">
+      <c r="F121" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="G121" s="9" t="inlineStr">
+      <c r="G121" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -8186,10 +8186,10 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F122" s="8" t="n">
+      <c r="F122" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="G122" s="9" t="inlineStr">
+      <c r="G122" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -8249,10 +8249,10 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F123" s="8" t="n">
+      <c r="F123" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="G123" s="9" t="inlineStr">
+      <c r="G123" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -8312,10 +8312,10 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F124" s="8" t="n">
+      <c r="F124" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="G124" s="9" t="inlineStr">
+      <c r="G124" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -8375,10 +8375,10 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="F125" s="8" t="n">
+      <c r="F125" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="G125" s="9" t="inlineStr">
+      <c r="G125" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -8438,10 +8438,10 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="F126" s="8" t="n">
+      <c r="F126" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="G126" s="9" t="inlineStr">
+      <c r="G126" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -8501,10 +8501,10 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="F127" s="8" t="n">
+      <c r="F127" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="G127" s="9" t="inlineStr">
+      <c r="G127" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -8564,10 +8564,10 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="F128" s="8" t="n">
+      <c r="F128" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="G128" s="9" t="inlineStr">
+      <c r="G128" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -8627,10 +8627,10 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="F129" s="8" t="n">
+      <c r="F129" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="G129" s="9" t="inlineStr">
+      <c r="G129" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -8690,10 +8690,10 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="F130" s="8" t="n">
+      <c r="F130" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="G130" s="9" t="inlineStr">
+      <c r="G130" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -8753,10 +8753,10 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="F131" s="8" t="n">
+      <c r="F131" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="G131" s="9" t="inlineStr">
+      <c r="G131" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -8816,10 +8816,10 @@
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="F132" s="8" t="n">
+      <c r="F132" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="G132" s="9" t="inlineStr">
+      <c r="G132" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -8839,9 +8839,9 @@
           <t>Not stated in JD</t>
         </is>
       </c>
-      <c r="K132" s="7" t="inlineStr">
-        <is>
-          <t>New this run (2026-08-28 22:31 UTC)</t>
+      <c r="K132" s="2" t="inlineStr">
+        <is>
+          <t>From previous run</t>
         </is>
       </c>
       <c r="L132" s="2" t="inlineStr">
@@ -8879,10 +8879,10 @@
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="F133" s="8" t="n">
+      <c r="F133" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="G133" s="9" t="inlineStr">
+      <c r="G133" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -8902,9 +8902,9 @@
           <t>Not stated in JD</t>
         </is>
       </c>
-      <c r="K133" s="7" t="inlineStr">
-        <is>
-          <t>New this run (2026-08-28 22:31 UTC)</t>
+      <c r="K133" s="2" t="inlineStr">
+        <is>
+          <t>From previous run</t>
         </is>
       </c>
       <c r="L133" s="2" t="inlineStr">
@@ -8942,10 +8942,10 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F134" s="8" t="n">
+      <c r="F134" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="G134" s="9" t="inlineStr">
+      <c r="G134" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -9005,10 +9005,10 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F135" s="8" t="n">
+      <c r="F135" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="G135" s="9" t="inlineStr">
+      <c r="G135" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -9068,10 +9068,10 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F136" s="8" t="n">
+      <c r="F136" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="G136" s="9" t="inlineStr">
+      <c r="G136" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -9131,10 +9131,10 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F137" s="8" t="n">
+      <c r="F137" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="G137" s="9" t="inlineStr">
+      <c r="G137" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -9194,10 +9194,10 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F138" s="8" t="n">
+      <c r="F138" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="G138" s="9" t="inlineStr">
+      <c r="G138" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -9257,10 +9257,10 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F139" s="8" t="n">
+      <c r="F139" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="G139" s="9" t="inlineStr">
+      <c r="G139" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -9320,10 +9320,10 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F140" s="8" t="n">
+      <c r="F140" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="G140" s="9" t="inlineStr">
+      <c r="G140" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -9383,10 +9383,10 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F141" s="8" t="n">
+      <c r="F141" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="G141" s="9" t="inlineStr">
+      <c r="G141" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -9446,10 +9446,10 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F142" s="8" t="n">
+      <c r="F142" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="G142" s="9" t="inlineStr">
+      <c r="G142" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -9509,10 +9509,10 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F143" s="8" t="n">
+      <c r="F143" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="G143" s="9" t="inlineStr">
+      <c r="G143" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -9572,10 +9572,10 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F144" s="8" t="n">
+      <c r="F144" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="G144" s="9" t="inlineStr">
+      <c r="G144" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -9635,10 +9635,10 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F145" s="8" t="n">
+      <c r="F145" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="G145" s="9" t="inlineStr">
+      <c r="G145" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -9698,10 +9698,10 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F146" s="8" t="n">
+      <c r="F146" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="G146" s="9" t="inlineStr">
+      <c r="G146" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -9761,10 +9761,10 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F147" s="8" t="n">
+      <c r="F147" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="G147" s="9" t="inlineStr">
+      <c r="G147" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -9824,10 +9824,10 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F148" s="8" t="n">
+      <c r="F148" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="G148" s="9" t="inlineStr">
+      <c r="G148" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -9887,10 +9887,10 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F149" s="8" t="n">
+      <c r="F149" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="G149" s="9" t="inlineStr">
+      <c r="G149" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -9950,10 +9950,10 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F150" s="8" t="n">
+      <c r="F150" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="G150" s="9" t="inlineStr">
+      <c r="G150" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -10013,10 +10013,10 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F151" s="8" t="n">
+      <c r="F151" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="G151" s="9" t="inlineStr">
+      <c r="G151" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -10076,10 +10076,10 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F152" s="8" t="n">
+      <c r="F152" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="G152" s="9" t="inlineStr">
+      <c r="G152" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -10139,10 +10139,10 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F153" s="8" t="n">
+      <c r="F153" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="G153" s="9" t="inlineStr">
+      <c r="G153" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -10202,10 +10202,10 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F154" s="8" t="n">
+      <c r="F154" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="G154" s="9" t="inlineStr">
+      <c r="G154" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -10265,10 +10265,10 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F155" s="8" t="n">
+      <c r="F155" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="G155" s="9" t="inlineStr">
+      <c r="G155" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -10328,10 +10328,10 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F156" s="8" t="n">
+      <c r="F156" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="G156" s="9" t="inlineStr">
+      <c r="G156" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -10391,10 +10391,10 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F157" s="8" t="n">
+      <c r="F157" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="G157" s="9" t="inlineStr">
+      <c r="G157" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -10454,10 +10454,10 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F158" s="8" t="n">
+      <c r="F158" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="G158" s="9" t="inlineStr">
+      <c r="G158" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -10517,10 +10517,10 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F159" s="8" t="n">
+      <c r="F159" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="G159" s="9" t="inlineStr">
+      <c r="G159" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -10580,10 +10580,10 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="F160" s="8" t="n">
+      <c r="F160" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="G160" s="9" t="inlineStr">
+      <c r="G160" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -10643,10 +10643,10 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="F161" s="8" t="n">
+      <c r="F161" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="G161" s="9" t="inlineStr">
+      <c r="G161" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -10706,10 +10706,10 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="F162" s="8" t="n">
+      <c r="F162" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="G162" s="9" t="inlineStr">
+      <c r="G162" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -10769,10 +10769,10 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="F163" s="8" t="n">
+      <c r="F163" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="G163" s="9" t="inlineStr">
+      <c r="G163" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -10832,10 +10832,10 @@
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="F164" s="8" t="n">
+      <c r="F164" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="G164" s="9" t="inlineStr">
+      <c r="G164" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -10855,9 +10855,9 @@
           <t>Not stated in JD</t>
         </is>
       </c>
-      <c r="K164" s="7" t="inlineStr">
-        <is>
-          <t>New this run (2026-08-28 22:31 UTC)</t>
+      <c r="K164" s="2" t="inlineStr">
+        <is>
+          <t>From previous run</t>
         </is>
       </c>
       <c r="L164" s="2" t="inlineStr">
@@ -10895,10 +10895,10 @@
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="F165" s="8" t="n">
+      <c r="F165" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="G165" s="9" t="inlineStr">
+      <c r="G165" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -10918,9 +10918,9 @@
           <t>Not stated in JD</t>
         </is>
       </c>
-      <c r="K165" s="7" t="inlineStr">
-        <is>
-          <t>New this run (2026-08-28 22:31 UTC)</t>
+      <c r="K165" s="2" t="inlineStr">
+        <is>
+          <t>From previous run</t>
         </is>
       </c>
       <c r="L165" s="2" t="inlineStr">
@@ -10958,10 +10958,10 @@
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="F166" s="8" t="n">
+      <c r="F166" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="G166" s="9" t="inlineStr">
+      <c r="G166" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -10981,9 +10981,9 @@
           <t>Not stated in JD</t>
         </is>
       </c>
-      <c r="K166" s="7" t="inlineStr">
-        <is>
-          <t>New this run (2026-08-28 22:31 UTC)</t>
+      <c r="K166" s="2" t="inlineStr">
+        <is>
+          <t>From previous run</t>
         </is>
       </c>
       <c r="L166" s="2" t="inlineStr">
@@ -11021,10 +11021,10 @@
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="F167" s="8" t="n">
+      <c r="F167" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="G167" s="9" t="inlineStr">
+      <c r="G167" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
@@ -11044,9 +11044,9 @@
           <t>Not stated in JD</t>
         </is>
       </c>
-      <c r="K167" s="7" t="inlineStr">
-        <is>
-          <t>New this run (2026-08-28 22:31 UTC)</t>
+      <c r="K167" s="2" t="inlineStr">
+        <is>
+          <t>From previous run</t>
         </is>
       </c>
       <c r="L167" s="2" t="inlineStr">
@@ -11066,12 +11066,12 @@
       </c>
       <c r="B168" s="3" t="inlineStr">
         <is>
-          <t>National Assistant Planner</t>
+          <t>BI Engineer</t>
         </is>
       </c>
       <c r="C168" s="3" t="inlineStr">
         <is>
-          <t>Al-Futtaim</t>
+          <t>JD.COM</t>
         </is>
       </c>
       <c r="D168" s="3" t="inlineStr">
@@ -11081,25 +11081,25 @@
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="F168" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G168" s="9" t="inlineStr">
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="F168" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="G168" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H168" s="3" t="inlineStr">
         <is>
-          <t>This is a non-technical retail merchandise planning role focused on financial forecasting, inventory management, and sales planning, which is entirely unrelated to the candidate's GenAI, LLM, and data science specialization.</t>
+          <t>This role is a BI Engineer position focused on supply chain, logistics, and retail operations rather than data science, AI, or Generative AI. It is entirely unrelated to the candidate's core expertise in LLMs, RAG, and agentic systems.</t>
         </is>
       </c>
       <c r="I168" s="3" t="inlineStr">
         <is>
-          <t>Not stated in JD</t>
+          <t>Yes - German required (see JD for exact level)</t>
         </is>
       </c>
       <c r="J168" s="3" t="inlineStr">
@@ -11107,9 +11107,9 @@
           <t>Not stated in JD</t>
         </is>
       </c>
-      <c r="K168" s="2" t="inlineStr">
-        <is>
-          <t>From previous run</t>
+      <c r="K168" s="9" t="inlineStr">
+        <is>
+          <t>New this run (2026-08-29 13:17 UTC)</t>
         </is>
       </c>
       <c r="L168" s="2" t="inlineStr">
@@ -11119,7 +11119,7 @@
       </c>
       <c r="M168" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/national-assistant-planner-at-al-futtaim-4459335643?position=23&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=udE1OmanEOJo5NqnDVVmsw%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/bi-engineer-at-jd-com-4414670937?position=6&amp;pageNum=0&amp;refId=WT017Qp%2F1VFpbzjZb903BA%3D%3D&amp;trackingId=uXRSjK39jDOlXpbtHq2yzQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -11129,35 +11129,35 @@
       </c>
       <c r="B169" s="3" t="inlineStr">
         <is>
-          <t>Forward Deployed AI Integrator (UAE National Only), Field Engineering</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="C169" s="3" t="inlineStr">
         <is>
-          <t>Amazon Web Services (AWS)</t>
+          <t>Danube Group</t>
         </is>
       </c>
       <c r="D169" s="3" t="inlineStr">
         <is>
-          <t>Dubai, Dubai, United Arab Emirates</t>
+          <t>Dubai, United Arab Emirates</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="F169" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G169" s="9" t="inlineStr">
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="F169" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="G169" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H169" s="3" t="inlineStr">
         <is>
-          <t>Although the role involves AI tooling and Python, it is restricted to UAE Nationals only, making it impossible for the candidate to qualify. Additionally, the position leans heavily toward technical program management rather than hands-on Generative AI and LLM engineering.</t>
+          <t>This is a Power BI Developer role focused on dashboards, data visualization, DAX, and SQL, which is completely unrelated to the candidate's core specialization in Generative AI, LLMs, and agentic workflows.</t>
         </is>
       </c>
       <c r="I169" s="3" t="inlineStr">
@@ -11170,9 +11170,9 @@
           <t>Not stated in JD</t>
         </is>
       </c>
-      <c r="K169" s="2" t="inlineStr">
-        <is>
-          <t>From previous run</t>
+      <c r="K169" s="9" t="inlineStr">
+        <is>
+          <t>New this run (2026-08-29 13:17 UTC)</t>
         </is>
       </c>
       <c r="L169" s="2" t="inlineStr">
@@ -11182,7 +11182,7 @@
       </c>
       <c r="M169" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/forward-deployed-ai-integrator-uae-national-only-field-engineering-at-amazon-web-services-aws-4459616402?position=14&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=suYy8hgZkG37o3lG7FlDHQ%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/power-bi-developer-at-danube-group-4459465901?position=5&amp;pageNum=0&amp;refId=WT017Qp%2F1VFpbzjZb903BA%3D%3D&amp;trackingId=2u7KtmoSLaInXvl%2FCAGPzw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -11192,12 +11192,12 @@
       </c>
       <c r="B170" s="3" t="inlineStr">
         <is>
-          <t>GIS Specialist / Developer</t>
+          <t>National Assistant Planner</t>
         </is>
       </c>
       <c r="C170" s="3" t="inlineStr">
         <is>
-          <t>AECOM</t>
+          <t>Al-Futtaim</t>
         </is>
       </c>
       <c r="D170" s="3" t="inlineStr">
@@ -11210,17 +11210,17 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F170" s="8" t="n">
+      <c r="F170" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="G170" s="9" t="inlineStr">
+      <c r="G170" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H170" s="3" t="inlineStr">
         <is>
-          <t>This is a GIS Specialist role focused on ArcGIS Enterprise administration, spatial analysis, and Python/ArcPy automation, which is completely unrelated to the candidate's core specialization in Generative AI, LLMs, and agentic systems.</t>
+          <t>This is a non-technical retail merchandise planning role focused on financial forecasting, inventory management, and sales planning, which is entirely unrelated to the candidate's GenAI, LLM, and data science specialization.</t>
         </is>
       </c>
       <c r="I170" s="3" t="inlineStr">
@@ -11245,7 +11245,7 @@
       </c>
       <c r="M170" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/gis-specialist-developer-at-aecom-4456869023?position=15&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=lGxG6%2FYECt2YwYGWf5hEZA%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/national-assistant-planner-at-al-futtaim-4459335643?position=23&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=udE1OmanEOJo5NqnDVVmsw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -11255,12 +11255,12 @@
       </c>
       <c r="B171" s="3" t="inlineStr">
         <is>
-          <t>Quant Desk Lead and Portfolio Manager</t>
+          <t>Forward Deployed AI Integrator (UAE National Only), Field Engineering</t>
         </is>
       </c>
       <c r="C171" s="3" t="inlineStr">
         <is>
-          <t>EMCD</t>
+          <t>Amazon Web Services (AWS)</t>
         </is>
       </c>
       <c r="D171" s="3" t="inlineStr">
@@ -11270,20 +11270,20 @@
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="F171" s="8" t="n">
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="F171" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="G171" s="9" t="inlineStr">
+      <c r="G171" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H171" s="3" t="inlineStr">
         <is>
-          <t>This is a finance and quantitative trading role focused on running a systematic trading desk, portfolio management, and P&amp;L ownership, which is entirely unrelated to the candidate's core specialization in Generative AI, LLMs, and agentic systems.</t>
+          <t>Although the role involves AI tooling and Python, it is restricted to UAE Nationals only, making it impossible for the candidate to qualify. Additionally, the position leans heavily toward technical program management rather than hands-on Generative AI and LLM engineering.</t>
         </is>
       </c>
       <c r="I171" s="3" t="inlineStr">
@@ -11308,7 +11308,7 @@
       </c>
       <c r="M171" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/quant-desk-lead-and-portfolio-manager-at-emcd-4457949555?position=13&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=drHtrw6uBtEz5S2i%2BjBT5A%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/forward-deployed-ai-integrator-uae-national-only-field-engineering-at-amazon-web-services-aws-4459616402?position=14&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=suYy8hgZkG37o3lG7FlDHQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -11318,17 +11318,17 @@
       </c>
       <c r="B172" s="3" t="inlineStr">
         <is>
-          <t>Join Norlys Energy Trading</t>
+          <t>GIS Specialist / Developer</t>
         </is>
       </c>
       <c r="C172" s="3" t="inlineStr">
         <is>
-          <t>Norlys Energy Trading A/S</t>
+          <t>AECOM</t>
         </is>
       </c>
       <c r="D172" s="3" t="inlineStr">
         <is>
-          <t>Aalborg, North Denmark Region, Denmark</t>
+          <t>Dubai, Dubai, United Arab Emirates</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F172" s="8" t="n">
+      <c r="F172" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="G172" s="9" t="inlineStr">
+      <c r="G172" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H172" s="3" t="inlineStr">
         <is>
-          <t>This is an open, unsolicited job application for a general talent pool in energy trading, rather than a defined Data Science or Generative AI role. It completely lacks technical specifications, making it impossible to evaluate against the candidate's specialized GenAI and LLM expertise.</t>
+          <t>This is a GIS Specialist role focused on ArcGIS Enterprise administration, spatial analysis, and Python/ArcPy automation, which is completely unrelated to the candidate's core specialization in Generative AI, LLMs, and agentic systems.</t>
         </is>
       </c>
       <c r="I172" s="3" t="inlineStr">
@@ -11371,7 +11371,7 @@
       </c>
       <c r="M172" s="6" t="inlineStr">
         <is>
-          <t>https://dk.linkedin.com/jobs/view/join-norlys-energy-trading-at-norlys-energy-trading-a-s-4459158084?position=26&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=Z%2BOuDrbPap3omWro18MA2g%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/gis-specialist-developer-at-aecom-4456869023?position=15&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=lGxG6%2FYECt2YwYGWf5hEZA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -11381,17 +11381,17 @@
       </c>
       <c r="B173" s="3" t="inlineStr">
         <is>
-          <t>PhD scholarship in Modeling and Control of Parkinson’s Disease - DTU Electro</t>
+          <t>Quant Desk Lead and Portfolio Manager</t>
         </is>
       </c>
       <c r="C173" s="3" t="inlineStr">
         <is>
-          <t>DTU - Technical University of Denmark</t>
+          <t>EMCD</t>
         </is>
       </c>
       <c r="D173" s="3" t="inlineStr">
         <is>
-          <t>Kongens Lyngby, Capital Region of Denmark, Denmark</t>
+          <t>Dubai, Dubai, United Arab Emirates</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr">
@@ -11399,17 +11399,17 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F173" s="8" t="n">
+      <c r="F173" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="G173" s="9" t="inlineStr">
+      <c r="G173" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H173" s="3" t="inlineStr">
         <is>
-          <t>This is a PhD scholarship position in neuroengineering, control systems, and healthcare technology at DTU, which is completely unrelated to the candidate's specialization in Generative AI, LLMs, and agentic systems.</t>
+          <t>This is a finance and quantitative trading role focused on running a systematic trading desk, portfolio management, and P&amp;L ownership, which is entirely unrelated to the candidate's core specialization in Generative AI, LLMs, and agentic systems.</t>
         </is>
       </c>
       <c r="I173" s="3" t="inlineStr">
@@ -11419,7 +11419,7 @@
       </c>
       <c r="J173" s="3" t="inlineStr">
         <is>
-          <t>Possible - relocation support mentioned, visa not explicit</t>
+          <t>Not stated in JD</t>
         </is>
       </c>
       <c r="K173" s="2" t="inlineStr">
@@ -11434,7 +11434,7 @@
       </c>
       <c r="M173" s="6" t="inlineStr">
         <is>
-          <t>https://dk.linkedin.com/jobs/view/phd-scholarship-in-modeling-and-control-of-parkinson%E2%80%99s-disease-dtu-electro-at-dtu-technical-university-of-denmark-4459145557?position=20&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=mStwcLkWBAvzmreGSwO4Hw%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/quant-desk-lead-and-portfolio-manager-at-emcd-4457949555?position=13&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=drHtrw6uBtEz5S2i%2BjBT5A%3D%3D</t>
         </is>
       </c>
     </row>
@@ -11444,17 +11444,17 @@
       </c>
       <c r="B174" s="3" t="inlineStr">
         <is>
-          <t>Analytikere med flair for databehandling til PET's kontraspionageindsats mod Rusland</t>
+          <t>Join Norlys Energy Trading</t>
         </is>
       </c>
       <c r="C174" s="3" t="inlineStr">
         <is>
-          <t>Politi</t>
+          <t>Norlys Energy Trading A/S</t>
         </is>
       </c>
       <c r="D174" s="3" t="inlineStr">
         <is>
-          <t>Copenhagen, Capital Region of Denmark, Denmark</t>
+          <t>Aalborg, North Denmark Region, Denmark</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
@@ -11462,17 +11462,17 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F174" s="8" t="n">
+      <c r="F174" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="G174" s="9" t="inlineStr">
+      <c r="G174" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H174" s="3" t="inlineStr">
         <is>
-          <t>This is a national security intelligence and counter-espionage analyst role at the Danish Security and Intelligence Service (PET), which is completely unrelated to data science, artificial intelligence, or the candidate's Generative AI and LLM specialization.</t>
+          <t>This is an open, unsolicited job application for a general talent pool in energy trading, rather than a defined Data Science or Generative AI role. It completely lacks technical specifications, making it impossible to evaluate against the candidate's specialized GenAI and LLM expertise.</t>
         </is>
       </c>
       <c r="I174" s="3" t="inlineStr">
@@ -11497,7 +11497,7 @@
       </c>
       <c r="M174" s="6" t="inlineStr">
         <is>
-          <t>https://dk.linkedin.com/jobs/view/analytikere-med-flair-for-databehandling-til-pet-s-kontraspionageindsats-mod-rusland-at-politi-4457943820?position=18&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=%2FGEw4KOC0oARqkQIDTGJ4Q%3D%3D</t>
+          <t>https://dk.linkedin.com/jobs/view/join-norlys-energy-trading-at-norlys-energy-trading-a-s-4459158084?position=26&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=Z%2BOuDrbPap3omWro18MA2g%3D%3D</t>
         </is>
       </c>
     </row>
@@ -11507,17 +11507,17 @@
       </c>
       <c r="B175" s="3" t="inlineStr">
         <is>
-          <t>PostDoc - Uncertainty-Aware Optimization in Inverse Problems for Next-Generation 3D Scanning</t>
+          <t>PhD scholarship in Modeling and Control of Parkinson’s Disease - DTU Electro</t>
         </is>
       </c>
       <c r="C175" s="3" t="inlineStr">
         <is>
-          <t>3Shape</t>
+          <t>DTU - Technical University of Denmark</t>
         </is>
       </c>
       <c r="D175" s="3" t="inlineStr">
         <is>
-          <t>Copenhagen, Capital Region of Denmark, Denmark</t>
+          <t>Kongens Lyngby, Capital Region of Denmark, Denmark</t>
         </is>
       </c>
       <c r="E175" s="2" t="inlineStr">
@@ -11525,17 +11525,17 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F175" s="8" t="n">
+      <c r="F175" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="G175" s="9" t="inlineStr">
+      <c r="G175" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H175" s="3" t="inlineStr">
         <is>
-          <t>This is a PostDoc position focused on mathematical optimization, numerical linear algebra, and uncertainty quantification for 3D scanning, which requires a PhD. It has no overlap with the candidate's specialization in GenAI, LLMs, and agentic systems.</t>
+          <t>This is a PhD scholarship position in neuroengineering, control systems, and healthcare technology at DTU, which is completely unrelated to the candidate's specialization in Generative AI, LLMs, and agentic systems.</t>
         </is>
       </c>
       <c r="I175" s="3" t="inlineStr">
@@ -11545,7 +11545,7 @@
       </c>
       <c r="J175" s="3" t="inlineStr">
         <is>
-          <t>Not stated in JD</t>
+          <t>Possible - relocation support mentioned, visa not explicit</t>
         </is>
       </c>
       <c r="K175" s="2" t="inlineStr">
@@ -11560,7 +11560,7 @@
       </c>
       <c r="M175" s="6" t="inlineStr">
         <is>
-          <t>https://dk.linkedin.com/jobs/view/postdoc-uncertainty-aware-optimization-in-inverse-problems-for-next-generation-3d-scanning-at-3shape-4459171806?position=15&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=bO0aSGZ%2FUAxThXN9yvOERg%3D%3D</t>
+          <t>https://dk.linkedin.com/jobs/view/phd-scholarship-in-modeling-and-control-of-parkinson%E2%80%99s-disease-dtu-electro-at-dtu-technical-university-of-denmark-4459145557?position=20&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=mStwcLkWBAvzmreGSwO4Hw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -11570,17 +11570,17 @@
       </c>
       <c r="B176" s="3" t="inlineStr">
         <is>
-          <t>Scientist, Quantitative Clinical Pharmacology (PK/PD Modeling &amp; Simulation)</t>
+          <t>Analytikere med flair for databehandling til PET's kontraspionageindsats mod Rusland</t>
         </is>
       </c>
       <c r="C176" s="3" t="inlineStr">
         <is>
-          <t>Hemab Therapeutics</t>
+          <t>Politi</t>
         </is>
       </c>
       <c r="D176" s="3" t="inlineStr">
         <is>
-          <t>Copenhagen Metropolitan Area</t>
+          <t>Copenhagen, Capital Region of Denmark, Denmark</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr">
@@ -11588,17 +11588,17 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F176" s="8" t="n">
+      <c r="F176" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="G176" s="9" t="inlineStr">
+      <c r="G176" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H176" s="3" t="inlineStr">
         <is>
-          <t>This is a highly specialized biomedical role focusing on Pharmacokinetics/Pharmacodynamics (PK/PD) modeling and clinical pharmacology, requiring a Ph.D. and experience with tools like NONMEM or Monolix. It has zero overlap with the candidate's GenAI, LLM, and data science background.</t>
+          <t>This is a national security intelligence and counter-espionage analyst role at the Danish Security and Intelligence Service (PET), which is completely unrelated to data science, artificial intelligence, or the candidate's Generative AI and LLM specialization.</t>
         </is>
       </c>
       <c r="I176" s="3" t="inlineStr">
@@ -11623,7 +11623,7 @@
       </c>
       <c r="M176" s="6" t="inlineStr">
         <is>
-          <t>https://dk.linkedin.com/jobs/view/scientist-quantitative-clinical-pharmacology-pk-pd-modeling-simulation-at-hemab-therapeutics-4457218306?position=14&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=jhTyKvDAQ70R9PD5s0x2yA%3D%3D</t>
+          <t>https://dk.linkedin.com/jobs/view/analytikere-med-flair-for-databehandling-til-pet-s-kontraspionageindsats-mod-rusland-at-politi-4457943820?position=18&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=%2FGEw4KOC0oARqkQIDTGJ4Q%3D%3D</t>
         </is>
       </c>
     </row>
@@ -11633,17 +11633,17 @@
       </c>
       <c r="B177" s="3" t="inlineStr">
         <is>
-          <t>Senior Payload Data Operator</t>
+          <t>PostDoc - Uncertainty-Aware Optimization in Inverse Problems for Next-Generation 3D Scanning</t>
         </is>
       </c>
       <c r="C177" s="3" t="inlineStr">
         <is>
-          <t>FADA</t>
+          <t>3Shape</t>
         </is>
       </c>
       <c r="D177" s="3" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>Copenhagen, Capital Region of Denmark, Denmark</t>
         </is>
       </c>
       <c r="E177" s="2" t="inlineStr">
@@ -11651,17 +11651,17 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F177" s="8" t="n">
+      <c r="F177" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="G177" s="9" t="inlineStr">
+      <c r="G177" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H177" s="3" t="inlineStr">
         <is>
-          <t>This is a satellite payload data engineering role focused on aerospace, remote sensing, and image processing (EO/SAR), which is completely unrelated to the candidate's specialization in GenAI, LLMs, and agentic systems.</t>
+          <t>This is a PostDoc position focused on mathematical optimization, numerical linear algebra, and uncertainty quantification for 3D scanning, which requires a PhD. It has no overlap with the candidate's specialization in GenAI, LLMs, and agentic systems.</t>
         </is>
       </c>
       <c r="I177" s="3" t="inlineStr">
@@ -11686,7 +11686,7 @@
       </c>
       <c r="M177" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/senior-payload-data-operator-at-fada-4448986926?position=20&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=xdfP2za0I45WGIW%2FRJb%2BgA%3D%3D</t>
+          <t>https://dk.linkedin.com/jobs/view/postdoc-uncertainty-aware-optimization-in-inverse-problems-for-next-generation-3d-scanning-at-3shape-4459171806?position=15&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=bO0aSGZ%2FUAxThXN9yvOERg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -11696,35 +11696,35 @@
       </c>
       <c r="B178" s="3" t="inlineStr">
         <is>
-          <t>Arabic Speech And Natural Language Processing Specialist</t>
+          <t>Scientist, Quantitative Clinical Pharmacology (PK/PD Modeling &amp; Simulation)</t>
         </is>
       </c>
       <c r="C178" s="3" t="inlineStr">
         <is>
-          <t>Birbal AI</t>
+          <t>Hemab Therapeutics</t>
         </is>
       </c>
       <c r="D178" s="3" t="inlineStr">
         <is>
-          <t>Abu Dhabi Emirate, United Arab Emirates</t>
+          <t>Copenhagen Metropolitan Area</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="F178" s="8" t="n">
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="F178" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="G178" s="9" t="inlineStr">
+      <c r="G178" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H178" s="3" t="inlineStr">
         <is>
-          <t>The role requires specialized expertise in Arabic speech technology (ASR, TTS, audio DSP) and native command of Gulf Arabic dialects, which does not match the candidate's core background in GenAI, LLMs, and RAG for English-language banking and HR use cases.</t>
+          <t>This is a highly specialized biomedical role focusing on Pharmacokinetics/Pharmacodynamics (PK/PD) modeling and clinical pharmacology, requiring a Ph.D. and experience with tools like NONMEM or Monolix. It has zero overlap with the candidate's GenAI, LLM, and data science background.</t>
         </is>
       </c>
       <c r="I178" s="3" t="inlineStr">
@@ -11749,7 +11749,7 @@
       </c>
       <c r="M178" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/arabic-speech-and-natural-language-processing-specialist-at-birbal-ai-4457738899?position=14&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=ztG06Ly%2FIZ3fxm%2Fhvl626A%3D%3D</t>
+          <t>https://dk.linkedin.com/jobs/view/scientist-quantitative-clinical-pharmacology-pk-pd-modeling-simulation-at-hemab-therapeutics-4457218306?position=14&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=jhTyKvDAQ70R9PD5s0x2yA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -11759,12 +11759,12 @@
       </c>
       <c r="B179" s="3" t="inlineStr">
         <is>
-          <t>Member of Technical Staff - Medical Research (Remote)</t>
+          <t>Senior Payload Data Operator</t>
         </is>
       </c>
       <c r="C179" s="3" t="inlineStr">
         <is>
-          <t>Hire Feed</t>
+          <t>FADA</t>
         </is>
       </c>
       <c r="D179" s="3" t="inlineStr">
@@ -11774,20 +11774,20 @@
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="F179" s="8" t="n">
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="F179" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="G179" s="9" t="inlineStr">
+      <c r="G179" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H179" s="3" t="inlineStr">
         <is>
-          <t>This role is completely unrelated to the candidate's specialization in Generative AI, LLMs, and agentic workflows, focusing instead on medical imaging, computational biology, and clinical research requiring a PhD.</t>
+          <t>This is a satellite payload data engineering role focused on aerospace, remote sensing, and image processing (EO/SAR), which is completely unrelated to the candidate's specialization in GenAI, LLMs, and agentic systems.</t>
         </is>
       </c>
       <c r="I179" s="3" t="inlineStr">
@@ -11812,7 +11812,7 @@
       </c>
       <c r="M179" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/member-of-technical-staff-medical-research-remote-at-hire-feed-4459638503?position=3&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=b91zxKPZNgdFnMmW%2FlYbHA%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/senior-payload-data-operator-at-fada-4448986926?position=20&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=xdfP2za0I45WGIW%2FRJb%2BgA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -11822,17 +11822,17 @@
       </c>
       <c r="B180" s="3" t="inlineStr">
         <is>
-          <t>AI Image Specialist</t>
+          <t>Arabic Speech And Natural Language Processing Specialist</t>
         </is>
       </c>
       <c r="C180" s="3" t="inlineStr">
         <is>
-          <t>Puffy</t>
+          <t>Birbal AI</t>
         </is>
       </c>
       <c r="D180" s="3" t="inlineStr">
         <is>
-          <t>Dubai, United Arab Emirates</t>
+          <t>Abu Dhabi Emirate, United Arab Emirates</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr">
@@ -11840,17 +11840,17 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="F180" s="8" t="n">
+      <c r="F180" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="G180" s="9" t="inlineStr">
+      <c r="G180" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H180" s="3" t="inlineStr">
         <is>
-          <t>This is an AI Image Specialist role focused on generative visual design and creative production (Midjourney, DALL-E, image synthesis), which is completely unrelated to the candidate's core specialization in LLMs, RAG, LangChain, and agentic AI pipelines for data science and enterprise applications.</t>
+          <t>The role requires specialized expertise in Arabic speech technology (ASR, TTS, audio DSP) and native command of Gulf Arabic dialects, which does not match the candidate's core background in GenAI, LLMs, and RAG for English-language banking and HR use cases.</t>
         </is>
       </c>
       <c r="I180" s="3" t="inlineStr">
@@ -11860,7 +11860,7 @@
       </c>
       <c r="J180" s="3" t="inlineStr">
         <is>
-          <t>Yes - explicitly stated in JD</t>
+          <t>Not stated in JD</t>
         </is>
       </c>
       <c r="K180" s="2" t="inlineStr">
@@ -11875,7 +11875,7 @@
       </c>
       <c r="M180" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/ai-image-specialist-at-puffy-4457756193?position=10&amp;pageNum=0&amp;refId=50H6yCrEXIuhgr6eqEojNg%3D%3D&amp;trackingId=9EIvgvUNu%2BE37717JffiJA%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/arabic-speech-and-natural-language-processing-specialist-at-birbal-ai-4457738899?position=14&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=ztG06Ly%2FIZ3fxm%2Fhvl626A%3D%3D</t>
         </is>
       </c>
     </row>
@@ -11885,35 +11885,35 @@
       </c>
       <c r="B181" s="3" t="inlineStr">
         <is>
-          <t>Market Operations &amp; Analytics Specialist — Institutional</t>
+          <t>Member of Technical Staff - Medical Research (Remote)</t>
         </is>
       </c>
       <c r="C181" s="3" t="inlineStr">
         <is>
-          <t>Confidential</t>
+          <t>Hire Feed</t>
         </is>
       </c>
       <c r="D181" s="3" t="inlineStr">
         <is>
-          <t>Dubai, United Arab Emirates</t>
+          <t>United Arab Emirates</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="F181" s="8" t="n">
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="F181" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="G181" s="9" t="inlineStr">
+      <c r="G181" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H181" s="3" t="inlineStr">
         <is>
-          <t>This role is completely unrelated to data science, artificial intelligence, LLMs, or generative AI, focusing entirely on cryptocurrency exchange operations, institutional client management, and trading analytics instead.</t>
+          <t>This role is completely unrelated to the candidate's specialization in Generative AI, LLMs, and agentic workflows, focusing instead on medical imaging, computational biology, and clinical research requiring a PhD.</t>
         </is>
       </c>
       <c r="I181" s="3" t="inlineStr">
@@ -11938,7 +11938,7 @@
       </c>
       <c r="M181" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/market-operations-analytics-specialist-%E2%80%94-institutional-at-confidential-4453037100?position=10&amp;pageNum=0&amp;refId=zJBbvwb5H0wsbJ5fs9ZTVw%3D%3D&amp;trackingId=ENnWCvoEQXOg1fXKuxlBug%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/member-of-technical-staff-medical-research-remote-at-hire-feed-4459638503?position=3&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=b91zxKPZNgdFnMmW%2FlYbHA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -11948,17 +11948,17 @@
       </c>
       <c r="B182" s="3" t="inlineStr">
         <is>
-          <t>Quantitative Developer, Systematic Equities</t>
+          <t>AI Image Specialist</t>
         </is>
       </c>
       <c r="C182" s="3" t="inlineStr">
         <is>
-          <t>Millennium</t>
+          <t>Puffy</t>
         </is>
       </c>
       <c r="D182" s="3" t="inlineStr">
         <is>
-          <t>Dubai, Dubai, United Arab Emirates</t>
+          <t>Dubai, United Arab Emirates</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
@@ -11966,17 +11966,17 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="F182" s="8" t="n">
+      <c r="F182" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="G182" s="9" t="inlineStr">
+      <c r="G182" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H182" s="3" t="inlineStr">
         <is>
-          <t>This role is a quantitative software engineering position focused on low-latency trading infrastructure, C++/C# development, and execution systems for a hedge fund, which is entirely unrelated to the candidate's specialization in GenAI, LLMs, and agentic architectures.</t>
+          <t>This is an AI Image Specialist role focused on generative visual design and creative production (Midjourney, DALL-E, image synthesis), which is completely unrelated to the candidate's core specialization in LLMs, RAG, LangChain, and agentic AI pipelines for data science and enterprise applications.</t>
         </is>
       </c>
       <c r="I182" s="3" t="inlineStr">
@@ -11986,7 +11986,7 @@
       </c>
       <c r="J182" s="3" t="inlineStr">
         <is>
-          <t>Not stated in JD</t>
+          <t>Yes - explicitly stated in JD</t>
         </is>
       </c>
       <c r="K182" s="2" t="inlineStr">
@@ -12001,7 +12001,7 @@
       </c>
       <c r="M182" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/quantitative-developer-systematic-equities-at-millennium-4290849018?position=6&amp;pageNum=0&amp;refId=zJBbvwb5H0wsbJ5fs9ZTVw%3D%3D&amp;trackingId=8TTWkyG2j%2F7MELtLSQ5VCA%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/ai-image-specialist-at-puffy-4457756193?position=10&amp;pageNum=0&amp;refId=50H6yCrEXIuhgr6eqEojNg%3D%3D&amp;trackingId=9EIvgvUNu%2BE37717JffiJA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -12011,17 +12011,17 @@
       </c>
       <c r="B183" s="3" t="inlineStr">
         <is>
-          <t>Senior Specialist - Portfolio Management</t>
+          <t>Market Operations &amp; Analytics Specialist — Institutional</t>
         </is>
       </c>
       <c r="C183" s="3" t="inlineStr">
         <is>
-          <t>MENA Careers</t>
+          <t>Confidential</t>
         </is>
       </c>
       <c r="D183" s="3" t="inlineStr">
         <is>
-          <t>Dubai, Dubai, United Arab Emirates</t>
+          <t>Dubai, United Arab Emirates</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr">
@@ -12029,17 +12029,17 @@
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="F183" s="8" t="n">
+      <c r="F183" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="G183" s="9" t="inlineStr">
+      <c r="G183" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H183" s="3" t="inlineStr">
         <is>
-          <t>This is a non-AI banking role focused on portfolio management, loan optimization, and regulatory capital compliance in Dubai requiring UAE nationality, which completely misaligns with the candidate's GenAI, LLM, and data science specialization.</t>
+          <t>This role is completely unrelated to data science, artificial intelligence, LLMs, or generative AI, focusing entirely on cryptocurrency exchange operations, institutional client management, and trading analytics instead.</t>
         </is>
       </c>
       <c r="I183" s="3" t="inlineStr">
@@ -12052,9 +12052,9 @@
           <t>Not stated in JD</t>
         </is>
       </c>
-      <c r="K183" s="7" t="inlineStr">
-        <is>
-          <t>New this run (2026-08-28 22:31 UTC)</t>
+      <c r="K183" s="2" t="inlineStr">
+        <is>
+          <t>From previous run</t>
         </is>
       </c>
       <c r="L183" s="2" t="inlineStr">
@@ -12064,7 +12064,7 @@
       </c>
       <c r="M183" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/senior-specialist-portfolio-management-at-mena-careers-4458066015?position=12&amp;pageNum=0&amp;refId=umynRMWB8laV9lcrAC5yvg%3D%3D&amp;trackingId=kbnf5IoX2jxOWD9%2Fe1UaKg%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/market-operations-analytics-specialist-%E2%80%94-institutional-at-confidential-4453037100?position=10&amp;pageNum=0&amp;refId=zJBbvwb5H0wsbJ5fs9ZTVw%3D%3D&amp;trackingId=ENnWCvoEQXOg1fXKuxlBug%3D%3D</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="B184" s="3" t="inlineStr">
         <is>
-          <t>Manager Logistics Performance</t>
+          <t>Quantitative Developer, Systematic Equities</t>
         </is>
       </c>
       <c r="C184" s="3" t="inlineStr">
         <is>
-          <t>talabat</t>
+          <t>Millennium</t>
         </is>
       </c>
       <c r="D184" s="3" t="inlineStr">
@@ -12089,25 +12089,25 @@
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="F184" s="8" t="n">
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="F184" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="G184" s="9" t="inlineStr">
+      <c r="G184" s="8" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
       <c r="H184" s="3" t="inlineStr">
         <is>
-          <t>This is a commercial operations, logistics, and P&amp;L management role completely unrelated to data science, artificial intelligence, or Large Language Models. It requires background in marketplace operations, logistics, or quick-commerce rather than GenAI engineering.</t>
+          <t>This role is a quantitative software engineering position focused on low-latency trading infrastructure, C++/C# development, and execution systems for a hedge fund, which is entirely unrelated to the candidate's specialization in GenAI, LLMs, and agentic architectures.</t>
         </is>
       </c>
       <c r="I184" s="3" t="inlineStr">
         <is>
-          <t>Yes - German required (see JD for exact level)</t>
+          <t>Not stated in JD</t>
         </is>
       </c>
       <c r="J184" s="3" t="inlineStr">
@@ -12115,9 +12115,9 @@
           <t>Not stated in JD</t>
         </is>
       </c>
-      <c r="K184" s="7" t="inlineStr">
-        <is>
-          <t>New this run (2026-08-28 22:31 UTC)</t>
+      <c r="K184" s="2" t="inlineStr">
+        <is>
+          <t>From previous run</t>
         </is>
       </c>
       <c r="L184" s="2" t="inlineStr">
@@ -12127,7 +12127,7 @@
       </c>
       <c r="M184" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/manager-logistics-performance-at-talabat-4440740657?position=7&amp;pageNum=0&amp;refId=umynRMWB8laV9lcrAC5yvg%3D%3D&amp;trackingId=lMQWp6LAUNLwXpGhMCpl2Q%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/quantitative-developer-systematic-equities-at-millennium-4290849018?position=6&amp;pageNum=0&amp;refId=zJBbvwb5H0wsbJ5fs9ZTVw%3D%3D&amp;trackingId=8TTWkyG2j%2F7MELtLSQ5VCA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -12137,121 +12137,247 @@
       </c>
       <c r="B185" s="3" t="inlineStr">
         <is>
+          <t>Senior Specialist - Portfolio Management</t>
+        </is>
+      </c>
+      <c r="C185" s="3" t="inlineStr">
+        <is>
+          <t>MENA Careers</t>
+        </is>
+      </c>
+      <c r="D185" s="3" t="inlineStr">
+        <is>
+          <t>Dubai, Dubai, United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="E185" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="F185" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G185" s="8" t="inlineStr">
+        <is>
+          <t>Below threshold</t>
+        </is>
+      </c>
+      <c r="H185" s="3" t="inlineStr">
+        <is>
+          <t>This is a non-AI banking role focused on portfolio management, loan optimization, and regulatory capital compliance in Dubai requiring UAE nationality, which completely misaligns with the candidate's GenAI, LLM, and data science specialization.</t>
+        </is>
+      </c>
+      <c r="I185" s="3" t="inlineStr">
+        <is>
+          <t>Not stated in JD</t>
+        </is>
+      </c>
+      <c r="J185" s="3" t="inlineStr">
+        <is>
+          <t>Not stated in JD</t>
+        </is>
+      </c>
+      <c r="K185" s="2" t="inlineStr">
+        <is>
+          <t>From previous run</t>
+        </is>
+      </c>
+      <c r="L185" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="M185" s="6" t="inlineStr">
+        <is>
+          <t>https://ae.linkedin.com/jobs/view/senior-specialist-portfolio-management-at-mena-careers-4458066015?position=12&amp;pageNum=0&amp;refId=umynRMWB8laV9lcrAC5yvg%3D%3D&amp;trackingId=kbnf5IoX2jxOWD9%2Fe1UaKg%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="186" ht="55" customHeight="1">
+      <c r="A186" s="2" t="n">
+        <v>185</v>
+      </c>
+      <c r="B186" s="3" t="inlineStr">
+        <is>
+          <t>Manager Logistics Performance</t>
+        </is>
+      </c>
+      <c r="C186" s="3" t="inlineStr">
+        <is>
+          <t>talabat</t>
+        </is>
+      </c>
+      <c r="D186" s="3" t="inlineStr">
+        <is>
+          <t>Dubai, Dubai, United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="E186" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="F186" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G186" s="8" t="inlineStr">
+        <is>
+          <t>Below threshold</t>
+        </is>
+      </c>
+      <c r="H186" s="3" t="inlineStr">
+        <is>
+          <t>This is a commercial operations, logistics, and P&amp;L management role completely unrelated to data science, artificial intelligence, or Large Language Models. It requires background in marketplace operations, logistics, or quick-commerce rather than GenAI engineering.</t>
+        </is>
+      </c>
+      <c r="I186" s="3" t="inlineStr">
+        <is>
+          <t>Yes - German required (see JD for exact level)</t>
+        </is>
+      </c>
+      <c r="J186" s="3" t="inlineStr">
+        <is>
+          <t>Not stated in JD</t>
+        </is>
+      </c>
+      <c r="K186" s="2" t="inlineStr">
+        <is>
+          <t>From previous run</t>
+        </is>
+      </c>
+      <c r="L186" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="M186" s="6" t="inlineStr">
+        <is>
+          <t>https://ae.linkedin.com/jobs/view/manager-logistics-performance-at-talabat-4440740657?position=7&amp;pageNum=0&amp;refId=umynRMWB8laV9lcrAC5yvg%3D%3D&amp;trackingId=lMQWp6LAUNLwXpGhMCpl2Q%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="187" ht="55" customHeight="1">
+      <c r="A187" s="2" t="n">
+        <v>186</v>
+      </c>
+      <c r="B187" s="3" t="inlineStr">
+        <is>
           <t>Perception Engineer</t>
         </is>
       </c>
-      <c r="C185" s="3" t="inlineStr">
+      <c r="C187" s="3" t="inlineStr">
         <is>
           <t>Careernet</t>
         </is>
       </c>
-      <c r="D185" s="3" t="inlineStr">
+      <c r="D187" s="3" t="inlineStr">
         <is>
           <t>Ajman, Ajman Emirate, United Arab Emirates</t>
         </is>
       </c>
-      <c r="E185" s="2" t="inlineStr">
+      <c r="E187" s="2" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="F185" s="8" t="n">
+      <c r="F187" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="G185" s="9" t="inlineStr">
-        <is>
-          <t>Below threshold</t>
-        </is>
-      </c>
-      <c r="H185" s="3" t="inlineStr">
+      <c r="G187" s="8" t="inlineStr">
+        <is>
+          <t>Below threshold</t>
+        </is>
+      </c>
+      <c r="H187" s="3" t="inlineStr">
         <is>
           <t>This is a hardware-focused Perception Engineer role centering on 2D/3D computer vision, camera calibration, point clouds, and robotics. It is completely unrelated to the candidate's specialization in GenAI, LLMs, RAG, and agentic AI.</t>
         </is>
       </c>
-      <c r="I185" s="3" t="inlineStr">
-        <is>
-          <t>Not stated in JD</t>
-        </is>
-      </c>
-      <c r="J185" s="3" t="inlineStr">
-        <is>
-          <t>Not stated in JD</t>
-        </is>
-      </c>
-      <c r="K185" s="7" t="inlineStr">
-        <is>
-          <t>New this run (2026-08-28 22:31 UTC)</t>
-        </is>
-      </c>
-      <c r="L185" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="M185" s="6" t="inlineStr">
+      <c r="I187" s="3" t="inlineStr">
+        <is>
+          <t>Not stated in JD</t>
+        </is>
+      </c>
+      <c r="J187" s="3" t="inlineStr">
+        <is>
+          <t>Not stated in JD</t>
+        </is>
+      </c>
+      <c r="K187" s="2" t="inlineStr">
+        <is>
+          <t>From previous run</t>
+        </is>
+      </c>
+      <c r="L187" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="M187" s="6" t="inlineStr">
         <is>
           <t>https://ae.linkedin.com/jobs/view/perception-engineer-at-careernet-4458403150?position=10&amp;pageNum=0&amp;refId=umynRMWB8laV9lcrAC5yvg%3D%3D&amp;trackingId=8I7i%2FeIdinpIC7lB70K7fg%3D%3D</t>
         </is>
       </c>
     </row>
-    <row r="186" ht="55" customHeight="1">
-      <c r="A186" s="10" t="n">
-        <v>185</v>
-      </c>
-      <c r="B186" s="11" t="inlineStr">
+    <row r="188" ht="55" customHeight="1">
+      <c r="A188" s="10" t="n">
+        <v>187</v>
+      </c>
+      <c r="B188" s="11" t="inlineStr">
         <is>
           <t>Data Scientist</t>
         </is>
       </c>
-      <c r="C186" s="11" t="inlineStr">
+      <c r="C188" s="11" t="inlineStr">
         <is>
           <t>Magno IT Recruitment</t>
         </is>
       </c>
-      <c r="D186" s="11" t="inlineStr">
+      <c r="D188" s="11" t="inlineStr">
         <is>
           <t>Amsterdam, North Holland, Netherlands</t>
         </is>
       </c>
-      <c r="E186" s="10" t="inlineStr">
+      <c r="E188" s="10" t="inlineStr">
         <is>
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F186" s="10" t="n">
+      <c r="F188" s="10" t="n">
         <v>92</v>
       </c>
-      <c r="G186" s="12" t="inlineStr">
+      <c r="G188" s="12" t="inlineStr">
         <is>
           <t>APPLY</t>
         </is>
       </c>
-      <c r="H186" s="11" t="inlineStr">
+      <c r="H188" s="11" t="inlineStr">
         <is>
           <t>This Senior AI Engineer role is an exceptional technical match, focusing directly on LLMs, RAG, agentic AI applications, and semantic search which align precisely with the candidate's core specialization. The seniority level (Senior) fits the candidate's 10+ years of experience very well.</t>
         </is>
       </c>
-      <c r="I186" s="11" t="inlineStr">
-        <is>
-          <t>Not stated in JD</t>
-        </is>
-      </c>
-      <c r="J186" s="11" t="inlineStr">
-        <is>
-          <t>Not stated in JD</t>
-        </is>
-      </c>
-      <c r="K186" s="10" t="inlineStr">
-        <is>
-          <t>From previous run</t>
-        </is>
-      </c>
-      <c r="L186" s="10" t="inlineStr">
+      <c r="I188" s="11" t="inlineStr">
+        <is>
+          <t>Not stated in JD</t>
+        </is>
+      </c>
+      <c r="J188" s="11" t="inlineStr">
+        <is>
+          <t>Not stated in JD</t>
+        </is>
+      </c>
+      <c r="K188" s="10" t="inlineStr">
+        <is>
+          <t>From previous run</t>
+        </is>
+      </c>
+      <c r="L188" s="10" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="M186" s="13" t="inlineStr">
+      <c r="M188" s="13" t="inlineStr">
         <is>
           <t>https://nl.linkedin.com/jobs/view/data-scientist-at-magno-it-recruitment-4448992517?position=9&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=26%2BZzuSXNPWrglox%2BL4Wqg%3D%3D</t>
         </is>
@@ -12444,6 +12570,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M184" r:id="rId183"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M185" r:id="rId184"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M188" r:id="rId187"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/job_matches.xlsx
+++ b/data/job_matches.xlsx
@@ -517,7 +517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M188"/>
+  <dimension ref="A1:M190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -8924,26 +8924,26 @@
       </c>
       <c r="B134" s="3" t="inlineStr">
         <is>
-          <t>Graphene Photonics Data Analyst (f/m/d)</t>
+          <t>Postdoctoral Researcher in AI for Testing and Threat Detection : Computer Science and Engineeing (CSE)-College of Engineering</t>
         </is>
       </c>
       <c r="C134" s="3" t="inlineStr">
         <is>
-          <t>Black Semiconductor</t>
+          <t>American University of Sharjah</t>
         </is>
       </c>
       <c r="D134" s="3" t="inlineStr">
         <is>
-          <t>Aachen, North Rhine-Westphalia, Germany</t>
+          <t>Sharjah, Sharjah Emirate, United Arab Emirates</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="F134" s="7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G134" s="8" t="inlineStr">
         <is>
@@ -8952,7 +8952,7 @@
       </c>
       <c r="H134" s="3" t="inlineStr">
         <is>
-          <t>This role is entirely focused on semiconductor hardware, graphene photonics, and physical data analysis, with zero relevance to the candidate's core specialization in Generative AI, LLMs, and agentic workflows.</t>
+          <t>This is a Postdoctoral Researcher role in an academic setting focused on reinforcement learning, formal verification, and threat detection, requiring a recent PhD, which completely mismatches the candidate's industry-focused Lead Data Scientist profile and 10+ years of corporate GenAI/RAG experience.</t>
         </is>
       </c>
       <c r="I134" s="3" t="inlineStr">
@@ -8965,9 +8965,9 @@
           <t>Not stated in JD</t>
         </is>
       </c>
-      <c r="K134" s="2" t="inlineStr">
-        <is>
-          <t>From previous run</t>
+      <c r="K134" s="9" t="inlineStr">
+        <is>
+          <t>New this run (2026-08-29 19:27 UTC)</t>
         </is>
       </c>
       <c r="L134" s="2" t="inlineStr">
@@ -8977,7 +8977,7 @@
       </c>
       <c r="M134" s="6" t="inlineStr">
         <is>
-          <t>https://de.linkedin.com/jobs/view/graphene-photonics-data-analyst-f-m-d-at-black-semiconductor-4459334621?position=26&amp;pageNum=0&amp;refId=T%2F0KkBXL%2Fl%2B5Iv5tUGTY7Q%3D%3D&amp;trackingId=KgQ01De6ChDgIN8UxnUvXg%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/postdoctoral-researcher-in-ai-for-testing-and-threat-detection-computer-science-and-engineeing-cse-college-of-engineering-at-american-university-of-sharjah-4423527619?position=2&amp;pageNum=0&amp;refId=ObYT%2FC%2FLT0LzMJUTwHqKZQ%3D%3D&amp;trackingId=FMQzyAWSKj5TyGLquO63tw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -8987,26 +8987,26 @@
       </c>
       <c r="B135" s="3" t="inlineStr">
         <is>
-          <t>Financial Planning and Analysis Manager</t>
+          <t>Fitch Learning | Data Science Trainer, Associate Director - Dubai, UAE</t>
         </is>
       </c>
       <c r="C135" s="3" t="inlineStr">
         <is>
-          <t>Confidential Jobs</t>
+          <t>Fitch Ratings</t>
         </is>
       </c>
       <c r="D135" s="3" t="inlineStr">
         <is>
-          <t>Dubai, United Arab Emirates</t>
+          <t>Dubai, Dubai, United Arab Emirates</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="F135" s="7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G135" s="8" t="inlineStr">
         <is>
@@ -9015,7 +9015,7 @@
       </c>
       <c r="H135" s="3" t="inlineStr">
         <is>
-          <t>This Financial Planning and Analysis Manager role is entirely unrelated to data science, machine learning, or software engineering, focusing instead on corporate finance, budgeting, construction economics, and IFRS 15 accounting. There is a massive domain and seniority mismatch for an AI/GenAI Lead Data Scientist.</t>
+          <t>This role is for a Data Science Trainer focusing on teaching professional learners, which is a significant mismatch for a hands-on technical Lead Data Scientist specializing in GenAI engineering and agentic workflows.</t>
         </is>
       </c>
       <c r="I135" s="3" t="inlineStr">
@@ -9028,9 +9028,9 @@
           <t>Not stated in JD</t>
         </is>
       </c>
-      <c r="K135" s="2" t="inlineStr">
-        <is>
-          <t>From previous run</t>
+      <c r="K135" s="9" t="inlineStr">
+        <is>
+          <t>New this run (2026-08-29 19:27 UTC)</t>
         </is>
       </c>
       <c r="L135" s="2" t="inlineStr">
@@ -9040,7 +9040,7 @@
       </c>
       <c r="M135" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/financial-planning-and-analysis-manager-at-confidential-jobs-4452594332?position=29&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=KEfZVTEknZKckxH1vstrzQ%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/fitch-learning-data-science-trainer-associate-director-dubai-uae-at-fitch-ratings-4413826649?position=3&amp;pageNum=0&amp;refId=ObYT%2FC%2FLT0LzMJUTwHqKZQ%3D%3D&amp;trackingId=%2B6ZDB6n4%2BzrdaJhgz1Rx5A%3D%3D</t>
         </is>
       </c>
     </row>
@@ -9050,17 +9050,17 @@
       </c>
       <c r="B136" s="3" t="inlineStr">
         <is>
-          <t>Data QA Engineer</t>
+          <t>Graphene Photonics Data Analyst (f/m/d)</t>
         </is>
       </c>
       <c r="C136" s="3" t="inlineStr">
         <is>
-          <t>ClearGrid</t>
+          <t>Black Semiconductor</t>
         </is>
       </c>
       <c r="D136" s="3" t="inlineStr">
         <is>
-          <t>Dubai, Dubai, United Arab Emirates</t>
+          <t>Aachen, North Rhine-Westphalia, Germany</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
@@ -9078,7 +9078,7 @@
       </c>
       <c r="H136" s="3" t="inlineStr">
         <is>
-          <t>This role is a Data QA Engineer focused entirely on data quality, dbt testing, and warehouse reconciliation in a fintech/collections environment, lacking any Generative AI, LLM, or agentic specialization. Furthermore, the seniority requirement (2+ years) is well below the candidate's 10+ years as a Lead Data Scientist.</t>
+          <t>This role is entirely focused on semiconductor hardware, graphene photonics, and physical data analysis, with zero relevance to the candidate's core specialization in Generative AI, LLMs, and agentic workflows.</t>
         </is>
       </c>
       <c r="I136" s="3" t="inlineStr">
@@ -9103,7 +9103,7 @@
       </c>
       <c r="M136" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/data-qa-engineer-at-cleargrid-4457980735?position=25&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=RbMMQ6DAm%2FMomlqBLUM2IQ%3D%3D</t>
+          <t>https://de.linkedin.com/jobs/view/graphene-photonics-data-analyst-f-m-d-at-black-semiconductor-4459334621?position=26&amp;pageNum=0&amp;refId=T%2F0KkBXL%2Fl%2B5Iv5tUGTY7Q%3D%3D&amp;trackingId=KgQ01De6ChDgIN8UxnUvXg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -9113,17 +9113,17 @@
       </c>
       <c r="B137" s="3" t="inlineStr">
         <is>
-          <t>OTR Planning Manager, Hub Delivery UAE , Hub Delivery</t>
+          <t>Financial Planning and Analysis Manager</t>
         </is>
       </c>
       <c r="C137" s="3" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Confidential Jobs</t>
         </is>
       </c>
       <c r="D137" s="3" t="inlineStr">
         <is>
-          <t>Dubai, Dubai, United Arab Emirates</t>
+          <t>Dubai, United Arab Emirates</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
@@ -9141,7 +9141,7 @@
       </c>
       <c r="H137" s="3" t="inlineStr">
         <is>
-          <t>This operations and logistics management role is entirely unrelated to data science, machine learning, and Generative AI, focusing instead on supply chain planning and fleet management. Therefore, it is a very poor match for the candidate's core specialization.</t>
+          <t>This Financial Planning and Analysis Manager role is entirely unrelated to data science, machine learning, or software engineering, focusing instead on corporate finance, budgeting, construction economics, and IFRS 15 accounting. There is a massive domain and seniority mismatch for an AI/GenAI Lead Data Scientist.</t>
         </is>
       </c>
       <c r="I137" s="3" t="inlineStr">
@@ -9166,7 +9166,7 @@
       </c>
       <c r="M137" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/otr-planning-manager-hub-delivery-uae-hub-delivery-at-amazon-4459184678?position=21&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=bqoXqft%2BGFtLz05C2kL0FA%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/financial-planning-and-analysis-manager-at-confidential-jobs-4452594332?position=29&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=KEfZVTEknZKckxH1vstrzQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -9176,12 +9176,12 @@
       </c>
       <c r="B138" s="3" t="inlineStr">
         <is>
-          <t>Senior Compensation Analyst</t>
+          <t>Data QA Engineer</t>
         </is>
       </c>
       <c r="C138" s="3" t="inlineStr">
         <is>
-          <t>Cartier</t>
+          <t>ClearGrid</t>
         </is>
       </c>
       <c r="D138" s="3" t="inlineStr">
@@ -9204,7 +9204,7 @@
       </c>
       <c r="H138" s="3" t="inlineStr">
         <is>
-          <t>This is a non-technical role focused strictly on compensation analysis, financial modeling, and advanced Excel simulation design within HR, which has no overlap with the candidate's core GenAI, LLM, or data science specialization.</t>
+          <t>This role is a Data QA Engineer focused entirely on data quality, dbt testing, and warehouse reconciliation in a fintech/collections environment, lacking any Generative AI, LLM, or agentic specialization. Furthermore, the seniority requirement (2+ years) is well below the candidate's 10+ years as a Lead Data Scientist.</t>
         </is>
       </c>
       <c r="I138" s="3" t="inlineStr">
@@ -9229,7 +9229,7 @@
       </c>
       <c r="M138" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/senior-compensation-analyst-at-cartier-4448528069?position=20&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=uU%2BxMpwsg7Xv71%2Fjk83xeg%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/data-qa-engineer-at-cleargrid-4457980735?position=25&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=RbMMQ6DAm%2FMomlqBLUM2IQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -9239,12 +9239,12 @@
       </c>
       <c r="B139" s="3" t="inlineStr">
         <is>
-          <t>AI &amp; Data - BrightStar program - Part-Time For Students | UAE Nationals Only - Dubai</t>
+          <t>OTR Planning Manager, Hub Delivery UAE , Hub Delivery</t>
         </is>
       </c>
       <c r="C139" s="3" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="D139" s="3" t="inlineStr">
@@ -9267,7 +9267,7 @@
       </c>
       <c r="H139" s="3" t="inlineStr">
         <is>
-          <t>This student internship/part-time program is an extreme seniority mismatch for a Lead Data Scientist with 10+ years of experience. Furthermore, the role is strictly restricted to UAE Nationals and unrelated to the candidate's specialized GenAI and agentic AI expertise.</t>
+          <t>This operations and logistics management role is entirely unrelated to data science, machine learning, and Generative AI, focusing instead on supply chain planning and fleet management. Therefore, it is a very poor match for the candidate's core specialization.</t>
         </is>
       </c>
       <c r="I139" s="3" t="inlineStr">
@@ -9292,7 +9292,7 @@
       </c>
       <c r="M139" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/ai-data-brightstar-program-part-time-for-students-uae-nationals-only-dubai-at-deloitte-4459165278?position=18&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=rkeXlOzDBapH9BYwLoMUoA%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/otr-planning-manager-hub-delivery-uae-hub-delivery-at-amazon-4459184678?position=21&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=bqoXqft%2BGFtLz05C2kL0FA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -9302,12 +9302,12 @@
       </c>
       <c r="B140" s="3" t="inlineStr">
         <is>
-          <t>Junior Market Analyst - UAE National</t>
+          <t>Senior Compensation Analyst</t>
         </is>
       </c>
       <c r="C140" s="3" t="inlineStr">
         <is>
-          <t>Richemont</t>
+          <t>Cartier</t>
         </is>
       </c>
       <c r="D140" s="3" t="inlineStr">
@@ -9330,7 +9330,7 @@
       </c>
       <c r="H140" s="3" t="inlineStr">
         <is>
-          <t>This role is a junior market research and business development position focused on luxury retail intelligence in the MEIAT region, which is completely unrelated to data science, artificial intelligence, or the candidate's GenAI and LLM specialization.</t>
+          <t>This is a non-technical role focused strictly on compensation analysis, financial modeling, and advanced Excel simulation design within HR, which has no overlap with the candidate's core GenAI, LLM, or data science specialization.</t>
         </is>
       </c>
       <c r="I140" s="3" t="inlineStr">
@@ -9355,7 +9355,7 @@
       </c>
       <c r="M140" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/junior-market-analyst-uae-national-at-richemont-4448527067?position=22&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=fabWFpBqiTWxCuIFUXVosg%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/senior-compensation-analyst-at-cartier-4448528069?position=20&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=uU%2BxMpwsg7Xv71%2Fjk83xeg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -9365,12 +9365,12 @@
       </c>
       <c r="B141" s="3" t="inlineStr">
         <is>
-          <t>Data Analyst - (Advanced Excel expertise)</t>
+          <t>AI &amp; Data - BrightStar program - Part-Time For Students | UAE Nationals Only - Dubai</t>
         </is>
       </c>
       <c r="C141" s="3" t="inlineStr">
         <is>
-          <t>BigTapp Analytics</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="D141" s="3" t="inlineStr">
@@ -9393,7 +9393,7 @@
       </c>
       <c r="H141" s="3" t="inlineStr">
         <is>
-          <t>This is a Data Analyst role focused entirely on Advanced Excel, corporate tax data quality, and data validation, with no connection to the candidate's GenAI, LLM, or agentic AI specialization.</t>
+          <t>This student internship/part-time program is an extreme seniority mismatch for a Lead Data Scientist with 10+ years of experience. Furthermore, the role is strictly restricted to UAE Nationals and unrelated to the candidate's specialized GenAI and agentic AI expertise.</t>
         </is>
       </c>
       <c r="I141" s="3" t="inlineStr">
@@ -9418,7 +9418,7 @@
       </c>
       <c r="M141" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/data-analyst-advanced-excel-expertise-at-bigtapp-analytics-4459194093?position=16&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=vJ8ubhhJtvsWirwhmdkH%2BA%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/ai-data-brightstar-program-part-time-for-students-uae-nationals-only-dubai-at-deloitte-4459165278?position=18&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=rkeXlOzDBapH9BYwLoMUoA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -9428,17 +9428,17 @@
       </c>
       <c r="B142" s="3" t="inlineStr">
         <is>
-          <t>Junior Data Analyst</t>
+          <t>Junior Market Analyst - UAE National</t>
         </is>
       </c>
       <c r="C142" s="3" t="inlineStr">
         <is>
-          <t>Arabian Private Holdings</t>
+          <t>Richemont</t>
         </is>
       </c>
       <c r="D142" s="3" t="inlineStr">
         <is>
-          <t>Sharjah, Sharjah Emirate, United Arab Emirates</t>
+          <t>Dubai, Dubai, United Arab Emirates</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
@@ -9456,7 +9456,7 @@
       </c>
       <c r="H142" s="3" t="inlineStr">
         <is>
-          <t>This is a junior data analyst role focused on operational data interpretation, basic SQL/Excel database maintenance, and corporate strategy support, completely unrelated to the candidate's GenAI, LLMs, and agentic AI specialization. Additionally, there is a severe seniority mismatch as the role is strictly junior while the candidate is a Lead Data Scientist with 10+ years of experience.</t>
+          <t>This role is a junior market research and business development position focused on luxury retail intelligence in the MEIAT region, which is completely unrelated to data science, artificial intelligence, or the candidate's GenAI and LLM specialization.</t>
         </is>
       </c>
       <c r="I142" s="3" t="inlineStr">
@@ -9481,7 +9481,7 @@
       </c>
       <c r="M142" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/junior-data-analyst-at-arabian-private-holdings-4457918646?position=11&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=n3OKFNsTAywRSCMqHYFmlg%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/junior-market-analyst-uae-national-at-richemont-4448527067?position=22&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=fabWFpBqiTWxCuIFUXVosg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -9491,17 +9491,17 @@
       </c>
       <c r="B143" s="3" t="inlineStr">
         <is>
-          <t>Data Analyst – Social Support Operations - UAE National</t>
+          <t>Data Analyst - (Advanced Excel expertise)</t>
         </is>
       </c>
       <c r="C143" s="3" t="inlineStr">
         <is>
-          <t>Ministry of Community Empowerment</t>
+          <t>BigTapp Analytics</t>
         </is>
       </c>
       <c r="D143" s="3" t="inlineStr">
         <is>
-          <t>Dubai, United Arab Emirates</t>
+          <t>Dubai, Dubai, United Arab Emirates</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
@@ -9519,7 +9519,7 @@
       </c>
       <c r="H143" s="3" t="inlineStr">
         <is>
-          <t>This role is a data analyst position focused on BI, Power BI dashboards, SQL, and social support operations, which is completely unrelated to the candidate's core GenAI, LLMs, and agentic AI specialization. Additionally, it specifies a nationality requirement.</t>
+          <t>This is a Data Analyst role focused entirely on Advanced Excel, corporate tax data quality, and data validation, with no connection to the candidate's GenAI, LLM, or agentic AI specialization.</t>
         </is>
       </c>
       <c r="I143" s="3" t="inlineStr">
@@ -9544,7 +9544,7 @@
       </c>
       <c r="M143" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/data-analyst-%E2%80%93-social-support-operations-uae-national-at-ministry-of-community-empowerment-4459118725?position=4&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=q%2FHUZ0XJHF5eY2WSwIWmAg%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/data-analyst-advanced-excel-expertise-at-bigtapp-analytics-4459194093?position=16&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=vJ8ubhhJtvsWirwhmdkH%2BA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -9554,17 +9554,17 @@
       </c>
       <c r="B144" s="3" t="inlineStr">
         <is>
-          <t>Graduate - Data Scientist إماراتيين (خلاصة القيد)</t>
+          <t>Junior Data Analyst</t>
         </is>
       </c>
       <c r="C144" s="3" t="inlineStr">
         <is>
-          <t>AECOM</t>
+          <t>Arabian Private Holdings</t>
         </is>
       </c>
       <c r="D144" s="3" t="inlineStr">
         <is>
-          <t>Dubai, Dubai, United Arab Emirates</t>
+          <t>Sharjah, Sharjah Emirate, United Arab Emirates</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
@@ -9582,7 +9582,7 @@
       </c>
       <c r="H144" s="3" t="inlineStr">
         <is>
-          <t>This is a graduate/entry-level program designed specifically for recent graduates (2024-2026) and UAE Nationals, representing a severe seniority and eligibility mismatch for a Lead Data Scientist with 10+ years of experience. Furthermore, the role focuses on construction digital tools, cost management, and general data analytics rather than the candidate's core GenAI, LLMs, and agentic AI specialization.</t>
+          <t>This is a junior data analyst role focused on operational data interpretation, basic SQL/Excel database maintenance, and corporate strategy support, completely unrelated to the candidate's GenAI, LLMs, and agentic AI specialization. Additionally, there is a severe seniority mismatch as the role is strictly junior while the candidate is a Lead Data Scientist with 10+ years of experience.</t>
         </is>
       </c>
       <c r="I144" s="3" t="inlineStr">
@@ -9607,7 +9607,7 @@
       </c>
       <c r="M144" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/graduate-data-scientist-%D8%A5%D9%85%D8%A7%D8%B1%D8%A7%D8%AA%D9%8A%D9%8A%D9%86-%D8%AE%D9%84%D8%A7%D8%B5%D8%A9-%D8%A7%D9%84%D9%82%D9%8A%D8%AF-at-aecom-4457915285?position=1&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=deUfOEFHstE7TEtandLeTg%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/junior-data-analyst-at-arabian-private-holdings-4457918646?position=11&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=n3OKFNsTAywRSCMqHYFmlg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -9617,17 +9617,17 @@
       </c>
       <c r="B145" s="3" t="inlineStr">
         <is>
-          <t>Quantitative Researcher, Quantitative Strategies</t>
+          <t>Data Analyst – Social Support Operations - UAE National</t>
         </is>
       </c>
       <c r="C145" s="3" t="inlineStr">
         <is>
-          <t>Millennium</t>
+          <t>Ministry of Community Empowerment</t>
         </is>
       </c>
       <c r="D145" s="3" t="inlineStr">
         <is>
-          <t>Dubai, Dubai, United Arab Emirates</t>
+          <t>Dubai, United Arab Emirates</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
@@ -9645,7 +9645,7 @@
       </c>
       <c r="H145" s="3" t="inlineStr">
         <is>
-          <t>This role focuses entirely on quantitative finance, statistical modeling, and systematic equity trading in Asian markets, which has no overlap with the candidate's core specialization in Generative AI, LLMs, and agentic systems. Additionally, the domain requires specific desk quant trading experience that is absent from the candidate's profile.</t>
+          <t>This role is a data analyst position focused on BI, Power BI dashboards, SQL, and social support operations, which is completely unrelated to the candidate's core GenAI, LLMs, and agentic AI specialization. Additionally, it specifies a nationality requirement.</t>
         </is>
       </c>
       <c r="I145" s="3" t="inlineStr">
@@ -9670,7 +9670,7 @@
       </c>
       <c r="M145" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/quantitative-researcher-quantitative-strategies-at-millennium-4439427782?position=2&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=uptfSAbwEngBw3yrsrQehg%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/data-analyst-%E2%80%93-social-support-operations-uae-national-at-ministry-of-community-empowerment-4459118725?position=4&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=q%2FHUZ0XJHF5eY2WSwIWmAg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -9680,12 +9680,12 @@
       </c>
       <c r="B146" s="3" t="inlineStr">
         <is>
-          <t>Analyst I - Advisory</t>
+          <t>Graduate - Data Scientist إماراتيين (خلاصة القيد)</t>
         </is>
       </c>
       <c r="C146" s="3" t="inlineStr">
         <is>
-          <t>Marsh Risk</t>
+          <t>AECOM</t>
         </is>
       </c>
       <c r="D146" s="3" t="inlineStr">
@@ -9708,7 +9708,7 @@
       </c>
       <c r="H146" s="3" t="inlineStr">
         <is>
-          <t>This is a fresh-graduate/entry-level role for recent graduates that focuses heavily on risk engineering and basic internal digitalization using Excel and Microsoft tools, which is far below the candidate's 10+ years of experience as a Lead Data Scientist specializing in advanced GenAI and agentic systems.</t>
+          <t>This is a graduate/entry-level program designed specifically for recent graduates (2024-2026) and UAE Nationals, representing a severe seniority and eligibility mismatch for a Lead Data Scientist with 10+ years of experience. Furthermore, the role focuses on construction digital tools, cost management, and general data analytics rather than the candidate's core GenAI, LLMs, and agentic AI specialization.</t>
         </is>
       </c>
       <c r="I146" s="3" t="inlineStr">
@@ -9733,7 +9733,7 @@
       </c>
       <c r="M146" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/analyst-i-advisory-at-marsh-risk-4459165267?position=3&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=NpomdoqDoXrgLAw8%2BZjEQA%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/graduate-data-scientist-%D8%A5%D9%85%D8%A7%D8%B1%D8%A7%D8%AA%D9%8A%D9%8A%D9%86-%D8%AE%D9%84%D8%A7%D8%B5%D8%A9-%D8%A7%D9%84%D9%82%D9%8A%D8%AF-at-aecom-4457915285?position=1&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=deUfOEFHstE7TEtandLeTg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -9743,17 +9743,17 @@
       </c>
       <c r="B147" s="3" t="inlineStr">
         <is>
-          <t>Demand Planner (f/m/x)</t>
+          <t>Quantitative Researcher, Quantitative Strategies</t>
         </is>
       </c>
       <c r="C147" s="3" t="inlineStr">
         <is>
-          <t>HelloFresh</t>
+          <t>Millennium</t>
         </is>
       </c>
       <c r="D147" s="3" t="inlineStr">
         <is>
-          <t>Amsterdam, North Holland, Netherlands</t>
+          <t>Dubai, Dubai, United Arab Emirates</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
@@ -9771,7 +9771,7 @@
       </c>
       <c r="H147" s="3" t="inlineStr">
         <is>
-          <t>This is a supply chain demand planning role requiring 2-3 years of experience in business forecasting, which is completely unrelated to the candidate's specialization in Generative AI, LLMs, and agentic systems. Furthermore, there is a severe seniority mismatch as the candidate is a Lead Data Scientist with 10+ years of experience.</t>
+          <t>This role focuses entirely on quantitative finance, statistical modeling, and systematic equity trading in Asian markets, which has no overlap with the candidate's core specialization in Generative AI, LLMs, and agentic systems. Additionally, the domain requires specific desk quant trading experience that is absent from the candidate's profile.</t>
         </is>
       </c>
       <c r="I147" s="3" t="inlineStr">
@@ -9796,7 +9796,7 @@
       </c>
       <c r="M147" s="6" t="inlineStr">
         <is>
-          <t>https://nl.linkedin.com/jobs/view/demand-planner-f-m-x-at-hellofresh-4459621163?position=29&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=ScTLY%2B93hMGSjD1GtPlxQw%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/quantitative-researcher-quantitative-strategies-at-millennium-4439427782?position=2&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=uptfSAbwEngBw3yrsrQehg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -9806,17 +9806,17 @@
       </c>
       <c r="B148" s="3" t="inlineStr">
         <is>
-          <t>Traineeship Data Analytics</t>
+          <t>Analyst I - Advisory</t>
         </is>
       </c>
       <c r="C148" s="3" t="inlineStr">
         <is>
-          <t>Breinstein</t>
+          <t>Marsh Risk</t>
         </is>
       </c>
       <c r="D148" s="3" t="inlineStr">
         <is>
-          <t>Groningen, Netherlands</t>
+          <t>Dubai, Dubai, United Arab Emirates</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
@@ -9834,7 +9834,7 @@
       </c>
       <c r="H148" s="3" t="inlineStr">
         <is>
-          <t>This is a junior/graduate-level traineeship requiring Dutch language proficiency, which represents a severe mismatch with the candidate's 10+ years of senior experience and Generative AI/LLM specialization.</t>
+          <t>This is a fresh-graduate/entry-level role for recent graduates that focuses heavily on risk engineering and basic internal digitalization using Excel and Microsoft tools, which is far below the candidate's 10+ years of experience as a Lead Data Scientist specializing in advanced GenAI and agentic systems.</t>
         </is>
       </c>
       <c r="I148" s="3" t="inlineStr">
@@ -9859,7 +9859,7 @@
       </c>
       <c r="M148" s="6" t="inlineStr">
         <is>
-          <t>https://nl.linkedin.com/jobs/view/traineeship-data-analytics-at-breinstein-4457240429?position=18&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=09Fo%2Bt8pd71ON%2B4bzhNIXw%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/analyst-i-advisory-at-marsh-risk-4459165267?position=3&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=NpomdoqDoXrgLAw8%2BZjEQA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -9869,17 +9869,17 @@
       </c>
       <c r="B149" s="3" t="inlineStr">
         <is>
-          <t>Økonom til finansielle data om pensionssektoren og investeringsfonde i Nationalbanken</t>
+          <t>Demand Planner (f/m/x)</t>
         </is>
       </c>
       <c r="C149" s="3" t="inlineStr">
         <is>
-          <t>Altandetlige.dk</t>
+          <t>HelloFresh</t>
         </is>
       </c>
       <c r="D149" s="3" t="inlineStr">
         <is>
-          <t>Copenhagen, Capital Region of Denmark, Denmark</t>
+          <t>Amsterdam, North Holland, Netherlands</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
@@ -9897,7 +9897,7 @@
       </c>
       <c r="H149" s="3" t="inlineStr">
         <is>
-          <t>This is a non-technical economics and financial statistics role at Denmark's central bank focusing on pension funds and investment data, which is completely unrelated to the candidate's specialization in Generative AI, LLMs, and agentic systems.</t>
+          <t>This is a supply chain demand planning role requiring 2-3 years of experience in business forecasting, which is completely unrelated to the candidate's specialization in Generative AI, LLMs, and agentic systems. Furthermore, there is a severe seniority mismatch as the candidate is a Lead Data Scientist with 10+ years of experience.</t>
         </is>
       </c>
       <c r="I149" s="3" t="inlineStr">
@@ -9922,7 +9922,7 @@
       </c>
       <c r="M149" s="6" t="inlineStr">
         <is>
-          <t>https://dk.linkedin.com/jobs/view/%C3%B8konom-til-finansielle-data-om-pensionssektoren-og-investeringsfonde-i-nationalbanken-at-altandetlige-dk-4459168468?position=25&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=%2BEekg%2B%2FvA%2BH0hxU4LsvJ5w%3D%3D</t>
+          <t>https://nl.linkedin.com/jobs/view/demand-planner-f-m-x-at-hellofresh-4459621163?position=29&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=ScTLY%2B93hMGSjD1GtPlxQw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -9932,17 +9932,17 @@
       </c>
       <c r="B150" s="3" t="inlineStr">
         <is>
-          <t>Lead Trading Strategist</t>
+          <t>Traineeship Data Analytics</t>
         </is>
       </c>
       <c r="C150" s="3" t="inlineStr">
         <is>
-          <t>Ørsted</t>
+          <t>Breinstein</t>
         </is>
       </c>
       <c r="D150" s="3" t="inlineStr">
         <is>
-          <t>Gentofte, Capital Region of Denmark, Denmark</t>
+          <t>Groningen, Netherlands</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
@@ -9960,7 +9960,7 @@
       </c>
       <c r="H150" s="3" t="inlineStr">
         <is>
-          <t>This is a quantitative energy trading and fundamental market analysis role requiring deep domain expertise in European power markets and commodities trading, which is completely unrelated to the candidate's core GenAI, LLM, and data science specialization.</t>
+          <t>This is a junior/graduate-level traineeship requiring Dutch language proficiency, which represents a severe mismatch with the candidate's 10+ years of senior experience and Generative AI/LLM specialization.</t>
         </is>
       </c>
       <c r="I150" s="3" t="inlineStr">
@@ -9985,7 +9985,7 @@
       </c>
       <c r="M150" s="6" t="inlineStr">
         <is>
-          <t>https://dk.linkedin.com/jobs/view/lead-trading-strategist-at-%C3%B8rsted-4439179684?position=21&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=LxVb1rg9c7QiaOEs5%2BY%2FTw%3D%3D</t>
+          <t>https://nl.linkedin.com/jobs/view/traineeship-data-analytics-at-breinstein-4457240429?position=18&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=09Fo%2Bt8pd71ON%2B4bzhNIXw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -9995,12 +9995,12 @@
       </c>
       <c r="B151" s="3" t="inlineStr">
         <is>
-          <t>Analytikere med flair for databehandling til PET's kontraspionageindsats mod Rusland</t>
+          <t>Økonom til finansielle data om pensionssektoren og investeringsfonde i Nationalbanken</t>
         </is>
       </c>
       <c r="C151" s="3" t="inlineStr">
         <is>
-          <t>Politiets Efterretningstjeneste (PET)</t>
+          <t>Altandetlige.dk</t>
         </is>
       </c>
       <c r="D151" s="3" t="inlineStr">
@@ -10023,7 +10023,7 @@
       </c>
       <c r="H151" s="3" t="inlineStr">
         <is>
-          <t>This is a national security intelligence and counter-espionage analyst role entirely unrelated to data science, artificial intelligence, LLMs, or software engineering. It focuses on intelligence operations and telecommunications data processing rather than the candidate's core Generative AI specialization.</t>
+          <t>This is a non-technical economics and financial statistics role at Denmark's central bank focusing on pension funds and investment data, which is completely unrelated to the candidate's specialization in Generative AI, LLMs, and agentic systems.</t>
         </is>
       </c>
       <c r="I151" s="3" t="inlineStr">
@@ -10048,7 +10048,7 @@
       </c>
       <c r="M151" s="6" t="inlineStr">
         <is>
-          <t>https://dk.linkedin.com/jobs/view/analytikere-med-flair-for-databehandling-til-pet-s-kontraspionageindsats-mod-rusland-at-politiets-efterretningstjeneste-pet-4457295379?position=17&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=jfzRay2PLGqzZJAC5yISBA%3D%3D</t>
+          <t>https://dk.linkedin.com/jobs/view/%C3%B8konom-til-finansielle-data-om-pensionssektoren-og-investeringsfonde-i-nationalbanken-at-altandetlige-dk-4459168468?position=25&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=%2BEekg%2B%2FvA%2BH0hxU4LsvJ5w%3D%3D</t>
         </is>
       </c>
     </row>
@@ -10058,17 +10058,17 @@
       </c>
       <c r="B152" s="3" t="inlineStr">
         <is>
-          <t>BI Specialist - turn healthcare data into better care decisions</t>
+          <t>Lead Trading Strategist</t>
         </is>
       </c>
       <c r="C152" s="3" t="inlineStr">
         <is>
-          <t>Systematic</t>
+          <t>Ørsted</t>
         </is>
       </c>
       <c r="D152" s="3" t="inlineStr">
         <is>
-          <t>Aarhus, Central Denmark Region, Denmark</t>
+          <t>Gentofte, Capital Region of Denmark, Denmark</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
@@ -10086,7 +10086,7 @@
       </c>
       <c r="H152" s="3" t="inlineStr">
         <is>
-          <t>This role is for a BI Specialist focusing on healthcare data systems, SQL, T-SQL, DAX, and client communication, which is completely unrelated to the candidate's core specialization in Generative AI, LLMs, and agentic AI systems. Additionally, it requires proficiency in Danish.</t>
+          <t>This is a quantitative energy trading and fundamental market analysis role requiring deep domain expertise in European power markets and commodities trading, which is completely unrelated to the candidate's core GenAI, LLM, and data science specialization.</t>
         </is>
       </c>
       <c r="I152" s="3" t="inlineStr">
@@ -10111,7 +10111,7 @@
       </c>
       <c r="M152" s="6" t="inlineStr">
         <is>
-          <t>https://dk.linkedin.com/jobs/view/bi-specialist-turn-healthcare-data-into-better-care-decisions-at-systematic-4449000390?position=13&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=C4YvYCcgfvLE1Lup1m630A%3D%3D</t>
+          <t>https://dk.linkedin.com/jobs/view/lead-trading-strategist-at-%C3%B8rsted-4439179684?position=21&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=LxVb1rg9c7QiaOEs5%2BY%2FTw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -10121,17 +10121,17 @@
       </c>
       <c r="B153" s="3" t="inlineStr">
         <is>
-          <t>Demand Planner (f/m/x)</t>
+          <t>Analytikere med flair for databehandling til PET's kontraspionageindsats mod Rusland</t>
         </is>
       </c>
       <c r="C153" s="3" t="inlineStr">
         <is>
-          <t>HelloFresh</t>
+          <t>Politiets Efterretningstjeneste (PET)</t>
         </is>
       </c>
       <c r="D153" s="3" t="inlineStr">
         <is>
-          <t>Copenhagen Municipality, Capital Region of Denmark, Denmark</t>
+          <t>Copenhagen, Capital Region of Denmark, Denmark</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
@@ -10149,7 +10149,7 @@
       </c>
       <c r="H153" s="3" t="inlineStr">
         <is>
-          <t>This is a non-AI supply chain demand planning role focused on SQL, logistics, and forecasting metrics like MAPE, which is completely unrelated to the candidate's core GenAI, LLM, and agentic AI specialization.</t>
+          <t>This is a national security intelligence and counter-espionage analyst role entirely unrelated to data science, artificial intelligence, LLMs, or software engineering. It focuses on intelligence operations and telecommunications data processing rather than the candidate's core Generative AI specialization.</t>
         </is>
       </c>
       <c r="I153" s="3" t="inlineStr">
@@ -10174,7 +10174,7 @@
       </c>
       <c r="M153" s="6" t="inlineStr">
         <is>
-          <t>https://dk.linkedin.com/jobs/view/demand-planner-f-m-x-at-hellofresh-4459625132?position=6&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=%2FDvrjQmxzWwgXh6GBB3pqA%3D%3D</t>
+          <t>https://dk.linkedin.com/jobs/view/analytikere-med-flair-for-databehandling-til-pet-s-kontraspionageindsats-mod-rusland-at-politiets-efterretningstjeneste-pet-4457295379?position=17&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=jfzRay2PLGqzZJAC5yISBA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -10184,17 +10184,17 @@
       </c>
       <c r="B154" s="3" t="inlineStr">
         <is>
-          <t>Senior Analyst - Market Intelligence (Trade &amp; Commodities)</t>
+          <t>BI Specialist - turn healthcare data into better care decisions</t>
         </is>
       </c>
       <c r="C154" s="3" t="inlineStr">
         <is>
-          <t>Robert Walters</t>
+          <t>Systematic</t>
         </is>
       </c>
       <c r="D154" s="3" t="inlineStr">
         <is>
-          <t>Abu Dhabi, Abu Dhabi Emirate, United Arab Emirates</t>
+          <t>Aarhus, Central Denmark Region, Denmark</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
@@ -10212,7 +10212,7 @@
       </c>
       <c r="H154" s="3" t="inlineStr">
         <is>
-          <t>This is a non-technical role focusing on market intelligence, trade flows, and supply chain analysis requiring Arabic fluency, which has no overlap with the candidate's core GenAI, LLMs, and agentic AI specialization.</t>
+          <t>This role is for a BI Specialist focusing on healthcare data systems, SQL, T-SQL, DAX, and client communication, which is completely unrelated to the candidate's core specialization in Generative AI, LLMs, and agentic AI systems. Additionally, it requires proficiency in Danish.</t>
         </is>
       </c>
       <c r="I154" s="3" t="inlineStr">
@@ -10237,7 +10237,7 @@
       </c>
       <c r="M154" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/senior-analyst-market-intelligence-trade-commodities-at-robert-walters-4457222382?position=30&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=JK2lIzdStMxW3Rb1o%2FxSgQ%3D%3D</t>
+          <t>https://dk.linkedin.com/jobs/view/bi-specialist-turn-healthcare-data-into-better-care-decisions-at-systematic-4449000390?position=13&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=C4YvYCcgfvLE1Lup1m630A%3D%3D</t>
         </is>
       </c>
     </row>
@@ -10247,17 +10247,17 @@
       </c>
       <c r="B155" s="3" t="inlineStr">
         <is>
-          <t>AI &amp; Data - BrightStar program - Part-Time For Students | UAE Nationals Only - Dubai</t>
+          <t>Demand Planner (f/m/x)</t>
         </is>
       </c>
       <c r="C155" s="3" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>HelloFresh</t>
         </is>
       </c>
       <c r="D155" s="3" t="inlineStr">
         <is>
-          <t>Abu Dhabi, Abu Dhabi Emirate, United Arab Emirates</t>
+          <t>Copenhagen Municipality, Capital Region of Denmark, Denmark</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
@@ -10275,7 +10275,7 @@
       </c>
       <c r="H155" s="3" t="inlineStr">
         <is>
-          <t>This is a student/internship program ('Part-Time For Students') restricted to UAE Nationals only, representing a severe seniority and eligibility mismatch for a Lead Data Scientist with 10 years of experience.</t>
+          <t>This is a non-AI supply chain demand planning role focused on SQL, logistics, and forecasting metrics like MAPE, which is completely unrelated to the candidate's core GenAI, LLM, and agentic AI specialization.</t>
         </is>
       </c>
       <c r="I155" s="3" t="inlineStr">
@@ -10300,7 +10300,7 @@
       </c>
       <c r="M155" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/ai-data-brightstar-program-part-time-for-students-uae-nationals-only-dubai-at-deloitte-4459166169?position=29&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=eJo5yKx6Zm7GgBBf0abvaA%3D%3D</t>
+          <t>https://dk.linkedin.com/jobs/view/demand-planner-f-m-x-at-hellofresh-4459625132?position=6&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=%2FDvrjQmxzWwgXh6GBB3pqA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -10310,17 +10310,17 @@
       </c>
       <c r="B156" s="3" t="inlineStr">
         <is>
-          <t>SAS Analyst</t>
+          <t>Senior Analyst - Market Intelligence (Trade &amp; Commodities)</t>
         </is>
       </c>
       <c r="C156" s="3" t="inlineStr">
         <is>
-          <t>One75mb HRM Pvt Ltd.</t>
+          <t>Robert Walters</t>
         </is>
       </c>
       <c r="D156" s="3" t="inlineStr">
         <is>
-          <t>Abu Dhabi Emirate, United Arab Emirates</t>
+          <t>Abu Dhabi, Abu Dhabi Emirate, United Arab Emirates</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
@@ -10338,7 +10338,7 @@
       </c>
       <c r="H156" s="3" t="inlineStr">
         <is>
-          <t>This role is a SAS Anti-Money Laundering (AML) Developer position focused on SAS Viya, SAS programming, and compliance systems. It has no connection to Generative AI, LLMs, RAG, or agentic systems, making it an entirely irrelevant fit for a GenAI specialist.</t>
+          <t>This is a non-technical role focusing on market intelligence, trade flows, and supply chain analysis requiring Arabic fluency, which has no overlap with the candidate's core GenAI, LLMs, and agentic AI specialization.</t>
         </is>
       </c>
       <c r="I156" s="3" t="inlineStr">
@@ -10363,7 +10363,7 @@
       </c>
       <c r="M156" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/sas-analyst-at-one75mb-hrm-pvt-ltd-4459306494?position=19&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=NfyeO5P7KUMAsO5xQjjwEA%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/senior-analyst-market-intelligence-trade-commodities-at-robert-walters-4457222382?position=30&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=JK2lIzdStMxW3Rb1o%2FxSgQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -10373,12 +10373,12 @@
       </c>
       <c r="B157" s="3" t="inlineStr">
         <is>
-          <t>Finance Information Systems Analyst</t>
+          <t>AI &amp; Data - BrightStar program - Part-Time For Students | UAE Nationals Only - Dubai</t>
         </is>
       </c>
       <c r="C157" s="3" t="inlineStr">
         <is>
-          <t>United Arab Emirates University, Department of Family Medicine</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="D157" s="3" t="inlineStr">
@@ -10401,7 +10401,7 @@
       </c>
       <c r="H157" s="3" t="inlineStr">
         <is>
-          <t>This role is for a Finance Information Systems Analyst focusing on Oracle SQL, financial reporting, and system maintenance, which is completely unrelated to the candidate's core expertise in Generative AI, LLMs, and agentic workflows.</t>
+          <t>This is a student/internship program ('Part-Time For Students') restricted to UAE Nationals only, representing a severe seniority and eligibility mismatch for a Lead Data Scientist with 10 years of experience.</t>
         </is>
       </c>
       <c r="I157" s="3" t="inlineStr">
@@ -10426,7 +10426,7 @@
       </c>
       <c r="M157" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/finance-information-systems-analyst-at-united-arab-emirates-university-department-of-family-medicine-4458309884?position=18&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=ZkLRAbbB1OpTP3DQTi%2FB4Q%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/ai-data-brightstar-program-part-time-for-students-uae-nationals-only-dubai-at-deloitte-4459166169?position=29&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=eJo5yKx6Zm7GgBBf0abvaA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -10436,17 +10436,17 @@
       </c>
       <c r="B158" s="3" t="inlineStr">
         <is>
-          <t>Analyst I - Advisory</t>
+          <t>SAS Analyst</t>
         </is>
       </c>
       <c r="C158" s="3" t="inlineStr">
         <is>
-          <t>Marsh Risk</t>
+          <t>One75mb HRM Pvt Ltd.</t>
         </is>
       </c>
       <c r="D158" s="3" t="inlineStr">
         <is>
-          <t>Abu Dhabi, Abu Dhabi Emirate, United Arab Emirates</t>
+          <t>Abu Dhabi Emirate, United Arab Emirates</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
@@ -10464,7 +10464,7 @@
       </c>
       <c r="H158" s="3" t="inlineStr">
         <is>
-          <t>This is a graduate/entry-level risk engineering and data analyst role located in the UAE restricted to UAE Nationals, representing a severe mismatch in both seniority and specialization for a Lead Data Scientist with 10+ years of experience in GenAI.</t>
+          <t>This role is a SAS Anti-Money Laundering (AML) Developer position focused on SAS Viya, SAS programming, and compliance systems. It has no connection to Generative AI, LLMs, RAG, or agentic systems, making it an entirely irrelevant fit for a GenAI specialist.</t>
         </is>
       </c>
       <c r="I158" s="3" t="inlineStr">
@@ -10489,7 +10489,7 @@
       </c>
       <c r="M158" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/analyst-i-advisory-at-marsh-risk-4459170127?position=6&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=hO0QLO%2FIAeXdRsG2PtQkTA%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/sas-analyst-at-one75mb-hrm-pvt-ltd-4459306494?position=19&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=NfyeO5P7KUMAsO5xQjjwEA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -10499,12 +10499,12 @@
       </c>
       <c r="B159" s="3" t="inlineStr">
         <is>
-          <t>Senior Economist / Economic Researcher</t>
+          <t>Finance Information Systems Analyst</t>
         </is>
       </c>
       <c r="C159" s="3" t="inlineStr">
         <is>
-          <t>Robert Walters</t>
+          <t>United Arab Emirates University, Department of Family Medicine</t>
         </is>
       </c>
       <c r="D159" s="3" t="inlineStr">
@@ -10527,7 +10527,7 @@
       </c>
       <c r="H159" s="3" t="inlineStr">
         <is>
-          <t>This role is for a Senior Economist focusing on macroeconomic research, policy analysis, and economic forecasting, which is completely unrelated to the candidate's specialization in Generative AI, LLMs, and data science.</t>
+          <t>This role is for a Finance Information Systems Analyst focusing on Oracle SQL, financial reporting, and system maintenance, which is completely unrelated to the candidate's core expertise in Generative AI, LLMs, and agentic workflows.</t>
         </is>
       </c>
       <c r="I159" s="3" t="inlineStr">
@@ -10552,7 +10552,7 @@
       </c>
       <c r="M159" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/senior-economist-economic-researcher-at-robert-walters-4457234594?position=21&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=hNkG3K%2BgFb1grR8QDMiBxA%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/finance-information-systems-analyst-at-united-arab-emirates-university-department-of-family-medicine-4458309884?position=18&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=ZkLRAbbB1OpTP3DQTi%2FB4Q%3D%3D</t>
         </is>
       </c>
     </row>
@@ -10562,22 +10562,22 @@
       </c>
       <c r="B160" s="3" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Analyst I - Advisory</t>
         </is>
       </c>
       <c r="C160" s="3" t="inlineStr">
         <is>
-          <t>ChipSoft Nederland</t>
+          <t>Marsh Risk</t>
         </is>
       </c>
       <c r="D160" s="3" t="inlineStr">
         <is>
-          <t>Amsterdam, North Holland, Netherlands</t>
+          <t>Abu Dhabi, Abu Dhabi Emirate, United Arab Emirates</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F160" s="7" t="n">
@@ -10590,7 +10590,7 @@
       </c>
       <c r="H160" s="3" t="inlineStr">
         <is>
-          <t>This is a Data Engineer role focused on ELT, SQL, data warehousing, and clickstream data, which is entirely unrelated to the candidate's core specialization in Generative AI, LLMs, and agentic systems.</t>
+          <t>This is a graduate/entry-level risk engineering and data analyst role located in the UAE restricted to UAE Nationals, representing a severe mismatch in both seniority and specialization for a Lead Data Scientist with 10+ years of experience in GenAI.</t>
         </is>
       </c>
       <c r="I160" s="3" t="inlineStr">
@@ -10615,7 +10615,7 @@
       </c>
       <c r="M160" s="6" t="inlineStr">
         <is>
-          <t>https://nl.linkedin.com/jobs/view/data-engineer-at-chipsoft-nederland-4448895866?position=29&amp;pageNum=0&amp;refId=oiBIn1Czflg0JjZjH5z0Lg%3D%3D&amp;trackingId=CakhxR8nCpksAoEXyMZPHQ%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/analyst-i-advisory-at-marsh-risk-4459170127?position=6&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=hO0QLO%2FIAeXdRsG2PtQkTA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -10625,22 +10625,22 @@
       </c>
       <c r="B161" s="3" t="inlineStr">
         <is>
-          <t>Quantitative Developer - Pricing Data</t>
+          <t>Senior Economist / Economic Researcher</t>
         </is>
       </c>
       <c r="C161" s="3" t="inlineStr">
         <is>
-          <t>Optiver</t>
+          <t>Robert Walters</t>
         </is>
       </c>
       <c r="D161" s="3" t="inlineStr">
         <is>
-          <t>Amsterdam, North Holland, Netherlands</t>
+          <t>Abu Dhabi, Abu Dhabi Emirate, United Arab Emirates</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F161" s="7" t="n">
@@ -10653,7 +10653,7 @@
       </c>
       <c r="H161" s="3" t="inlineStr">
         <is>
-          <t>This Quantitative Developer role focuses entirely on financial pricing data systems, market data pipelines, and low-latency/historical trading infrastructure in C++/Python, which is completely unrelated to the candidate's specialization in Generative AI, LLMs, and agentic workflows.</t>
+          <t>This role is for a Senior Economist focusing on macroeconomic research, policy analysis, and economic forecasting, which is completely unrelated to the candidate's specialization in Generative AI, LLMs, and data science.</t>
         </is>
       </c>
       <c r="I161" s="3" t="inlineStr">
@@ -10663,7 +10663,7 @@
       </c>
       <c r="J161" s="3" t="inlineStr">
         <is>
-          <t>Yes - explicitly stated in JD</t>
+          <t>Not stated in JD</t>
         </is>
       </c>
       <c r="K161" s="2" t="inlineStr">
@@ -10678,7 +10678,7 @@
       </c>
       <c r="M161" s="6" t="inlineStr">
         <is>
-          <t>https://nl.linkedin.com/jobs/view/quantitative-developer-pricing-data-at-optiver-4437686371?position=21&amp;pageNum=0&amp;refId=oiBIn1Czflg0JjZjH5z0Lg%3D%3D&amp;trackingId=bm7u%2BG7QRNRgNoiTgqdkzg%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/senior-economist-economic-researcher-at-robert-walters-4457234594?position=21&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=hNkG3K%2BgFb1grR8QDMiBxA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -10688,17 +10688,17 @@
       </c>
       <c r="B162" s="3" t="inlineStr">
         <is>
-          <t>Data Analyst — Operational Analysis (Python, Power BI, Modelling) for NATO with security clearance</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="C162" s="3" t="inlineStr">
         <is>
-          <t>WLG</t>
+          <t>ChipSoft Nederland</t>
         </is>
       </c>
       <c r="D162" s="3" t="inlineStr">
         <is>
-          <t>The Hague, South Holland, Netherlands</t>
+          <t>Amsterdam, North Holland, Netherlands</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
@@ -10716,7 +10716,7 @@
       </c>
       <c r="H162" s="3" t="inlineStr">
         <is>
-          <t>This is an unrelated junior Data Analyst role focused on operational analysis, dashboards, and spreadsheets rather than Generative AI or advanced data science. Given the candidate's 10+ years of experience as a Lead Data Scientist specializing in LLMs and agentic AI, this position represents a severe mismatch in both domain and seniority.</t>
+          <t>This is a Data Engineer role focused on ELT, SQL, data warehousing, and clickstream data, which is entirely unrelated to the candidate's core specialization in Generative AI, LLMs, and agentic systems.</t>
         </is>
       </c>
       <c r="I162" s="3" t="inlineStr">
@@ -10741,7 +10741,7 @@
       </c>
       <c r="M162" s="6" t="inlineStr">
         <is>
-          <t>https://nl.linkedin.com/jobs/view/data-analyst-%E2%80%94-operational-analysis-python-power-bi-modelling-for-nato-with-security-clearance-at-wlg-4458620413?position=26&amp;pageNum=0&amp;refId=oiBIn1Czflg0JjZjH5z0Lg%3D%3D&amp;trackingId=NK7DxxVQL3iwGI1saGNrZg%3D%3D</t>
+          <t>https://nl.linkedin.com/jobs/view/data-engineer-at-chipsoft-nederland-4448895866?position=29&amp;pageNum=0&amp;refId=oiBIn1Czflg0JjZjH5z0Lg%3D%3D&amp;trackingId=CakhxR8nCpksAoEXyMZPHQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -10751,17 +10751,17 @@
       </c>
       <c r="B163" s="3" t="inlineStr">
         <is>
-          <t>Hadoop / Big Data Engineer</t>
+          <t>Quantitative Developer - Pricing Data</t>
         </is>
       </c>
       <c r="C163" s="3" t="inlineStr">
         <is>
-          <t>HTC Global Services</t>
+          <t>Optiver</t>
         </is>
       </c>
       <c r="D163" s="3" t="inlineStr">
         <is>
-          <t>Dubai, United Arab Emirates</t>
+          <t>Amsterdam, North Holland, Netherlands</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
@@ -10779,7 +10779,7 @@
       </c>
       <c r="H163" s="3" t="inlineStr">
         <is>
-          <t>This is a classical data engineering and Hadoop role focusing on infrastructure, Spark, Hive, and data pipelines, which is entirely unrelated to the candidate's core specialization in Generative AI, LLMs, and agentic workflows.</t>
+          <t>This Quantitative Developer role focuses entirely on financial pricing data systems, market data pipelines, and low-latency/historical trading infrastructure in C++/Python, which is completely unrelated to the candidate's specialization in Generative AI, LLMs, and agentic workflows.</t>
         </is>
       </c>
       <c r="I163" s="3" t="inlineStr">
@@ -10789,7 +10789,7 @@
       </c>
       <c r="J163" s="3" t="inlineStr">
         <is>
-          <t>Not stated in JD</t>
+          <t>Yes - explicitly stated in JD</t>
         </is>
       </c>
       <c r="K163" s="2" t="inlineStr">
@@ -10804,7 +10804,7 @@
       </c>
       <c r="M163" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/hadoop-big-data-engineer-at-htc-global-services-4460123484?position=9&amp;pageNum=0&amp;refId=zJBbvwb5H0wsbJ5fs9ZTVw%3D%3D&amp;trackingId=SQM7VXeym81F4YKdSlXxkg%3D%3D</t>
+          <t>https://nl.linkedin.com/jobs/view/quantitative-developer-pricing-data-at-optiver-4437686371?position=21&amp;pageNum=0&amp;refId=oiBIn1Czflg0JjZjH5z0Lg%3D%3D&amp;trackingId=bm7u%2BG7QRNRgNoiTgqdkzg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -10814,22 +10814,22 @@
       </c>
       <c r="B164" s="3" t="inlineStr">
         <is>
-          <t>Business Analyst - Dubai (UAE Nationals only)</t>
+          <t>Data Analyst — Operational Analysis (Python, Power BI, Modelling) for NATO with security clearance</t>
         </is>
       </c>
       <c r="C164" s="3" t="inlineStr">
         <is>
-          <t>Efficio</t>
+          <t>WLG</t>
         </is>
       </c>
       <c r="D164" s="3" t="inlineStr">
         <is>
-          <t>Dubai, Dubai, United Arab Emirates</t>
+          <t>The Hague, South Holland, Netherlands</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F164" s="7" t="n">
@@ -10842,7 +10842,7 @@
       </c>
       <c r="H164" s="3" t="inlineStr">
         <is>
-          <t>This role is a Business Analyst position focused on procurement and supply chain consulting, completely unrelated to data science, artificial intelligence, or the candidate's core GenAI/LLM specialization. Furthermore, the role explicitly requires being a UAE National.</t>
+          <t>This is an unrelated junior Data Analyst role focused on operational analysis, dashboards, and spreadsheets rather than Generative AI or advanced data science. Given the candidate's 10+ years of experience as a Lead Data Scientist specializing in LLMs and agentic AI, this position represents a severe mismatch in both domain and seniority.</t>
         </is>
       </c>
       <c r="I164" s="3" t="inlineStr">
@@ -10867,7 +10867,7 @@
       </c>
       <c r="M164" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/business-analyst-dubai-uae-nationals-only-at-efficio-4291615037?position=11&amp;pageNum=0&amp;refId=umynRMWB8laV9lcrAC5yvg%3D%3D&amp;trackingId=97gwiNAcH3ASkR2fVgtg7A%3D%3D</t>
+          <t>https://nl.linkedin.com/jobs/view/data-analyst-%E2%80%94-operational-analysis-python-power-bi-modelling-for-nato-with-security-clearance-at-wlg-4458620413?position=26&amp;pageNum=0&amp;refId=oiBIn1Czflg0JjZjH5z0Lg%3D%3D&amp;trackingId=NK7DxxVQL3iwGI1saGNrZg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -10877,22 +10877,22 @@
       </c>
       <c r="B165" s="3" t="inlineStr">
         <is>
-          <t>Oliver Wyman - Government and Public Institutions (GPI) and Financial Services (FS) Researcher - Dubai</t>
+          <t>Hadoop / Big Data Engineer</t>
         </is>
       </c>
       <c r="C165" s="3" t="inlineStr">
         <is>
-          <t>Oliver Wyman</t>
+          <t>HTC Global Services</t>
         </is>
       </c>
       <c r="D165" s="3" t="inlineStr">
         <is>
-          <t>Dubai, Dubai, United Arab Emirates</t>
+          <t>Dubai, United Arab Emirates</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F165" s="7" t="n">
@@ -10905,7 +10905,7 @@
       </c>
       <c r="H165" s="3" t="inlineStr">
         <is>
-          <t>This is a non-technical management consulting research role focusing on market data, databases like Factiva, and slide preparation in Excel/PowerPoint. It has no connection to the candidate's core specialization in Generative AI, LLMs, LangChain, or data science modeling.</t>
+          <t>This is a classical data engineering and Hadoop role focusing on infrastructure, Spark, Hive, and data pipelines, which is entirely unrelated to the candidate's core specialization in Generative AI, LLMs, and agentic workflows.</t>
         </is>
       </c>
       <c r="I165" s="3" t="inlineStr">
@@ -10930,7 +10930,7 @@
       </c>
       <c r="M165" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/oliver-wyman-government-and-public-institutions-gpi-and-financial-services-fs-researcher-dubai-at-oliver-wyman-4460354191?position=14&amp;pageNum=0&amp;refId=umynRMWB8laV9lcrAC5yvg%3D%3D&amp;trackingId=ELxpmziWW%2B8sDM8xGhxmOA%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/hadoop-big-data-engineer-at-htc-global-services-4460123484?position=9&amp;pageNum=0&amp;refId=zJBbvwb5H0wsbJ5fs9ZTVw%3D%3D&amp;trackingId=SQM7VXeym81F4YKdSlXxkg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -10940,12 +10940,12 @@
       </c>
       <c r="B166" s="3" t="inlineStr">
         <is>
-          <t>Oliver Wyman - Associate - Health and Life Sciences - Dubai</t>
+          <t>Business Analyst - Dubai (UAE Nationals only)</t>
         </is>
       </c>
       <c r="C166" s="3" t="inlineStr">
         <is>
-          <t>Oliver Wyman</t>
+          <t>Efficio</t>
         </is>
       </c>
       <c r="D166" s="3" t="inlineStr">
@@ -10968,7 +10968,7 @@
       </c>
       <c r="H166" s="3" t="inlineStr">
         <is>
-          <t>This is a management consulting role focused on Health and Life Sciences strategy at Oliver Wyman, requiring deep industry expertise in pharmaceuticals or MedTech and top-tier strategy consulting experience. It has zero alignment with the candidate's core GenAI, LLM, or Data Science specialization.</t>
+          <t>This role is a Business Analyst position focused on procurement and supply chain consulting, completely unrelated to data science, artificial intelligence, or the candidate's core GenAI/LLM specialization. Furthermore, the role explicitly requires being a UAE National.</t>
         </is>
       </c>
       <c r="I166" s="3" t="inlineStr">
@@ -10993,7 +10993,7 @@
       </c>
       <c r="M166" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/oliver-wyman-associate-health-and-life-sciences-dubai-at-oliver-wyman-4460351294?position=8&amp;pageNum=0&amp;refId=umynRMWB8laV9lcrAC5yvg%3D%3D&amp;trackingId=GWJpOuiL92AZx2SkHg%2FfPg%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/business-analyst-dubai-uae-nationals-only-at-efficio-4291615037?position=11&amp;pageNum=0&amp;refId=umynRMWB8laV9lcrAC5yvg%3D%3D&amp;trackingId=97gwiNAcH3ASkR2fVgtg7A%3D%3D</t>
         </is>
       </c>
     </row>
@@ -11003,12 +11003,12 @@
       </c>
       <c r="B167" s="3" t="inlineStr">
         <is>
-          <t>F&amp;S Associate - UAE National</t>
+          <t>Oliver Wyman - Government and Public Institutions (GPI) and Financial Services (FS) Researcher - Dubai</t>
         </is>
       </c>
       <c r="C167" s="3" t="inlineStr">
         <is>
-          <t>Deliveroo</t>
+          <t>Oliver Wyman</t>
         </is>
       </c>
       <c r="D167" s="3" t="inlineStr">
@@ -11031,7 +11031,7 @@
       </c>
       <c r="H167" s="3" t="inlineStr">
         <is>
-          <t>This is a finance and strategy role focused on spreadsheets, variance analysis, and business reporting with no relation to Generative AI, machine learning, or data science. It is completely unrelated to the candidate's core technical specialization and profile.</t>
+          <t>This is a non-technical management consulting research role focusing on market data, databases like Factiva, and slide preparation in Excel/PowerPoint. It has no connection to the candidate's core specialization in Generative AI, LLMs, LangChain, or data science modeling.</t>
         </is>
       </c>
       <c r="I167" s="3" t="inlineStr">
@@ -11056,7 +11056,7 @@
       </c>
       <c r="M167" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/f-s-associate-uae-national-at-deliveroo-4449749711?position=6&amp;pageNum=0&amp;refId=umynRMWB8laV9lcrAC5yvg%3D%3D&amp;trackingId=xir3IHLZTYXuoIlF3oUkeg%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/oliver-wyman-government-and-public-institutions-gpi-and-financial-services-fs-researcher-dubai-at-oliver-wyman-4460354191?position=14&amp;pageNum=0&amp;refId=umynRMWB8laV9lcrAC5yvg%3D%3D&amp;trackingId=ELxpmziWW%2B8sDM8xGhxmOA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -11066,12 +11066,12 @@
       </c>
       <c r="B168" s="3" t="inlineStr">
         <is>
-          <t>BI Engineer</t>
+          <t>Oliver Wyman - Associate - Health and Life Sciences - Dubai</t>
         </is>
       </c>
       <c r="C168" s="3" t="inlineStr">
         <is>
-          <t>JD.COM</t>
+          <t>Oliver Wyman</t>
         </is>
       </c>
       <c r="D168" s="3" t="inlineStr">
@@ -11081,7 +11081,7 @@
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="F168" s="7" t="n">
@@ -11094,12 +11094,12 @@
       </c>
       <c r="H168" s="3" t="inlineStr">
         <is>
-          <t>This role is a BI Engineer position focused on supply chain, logistics, and retail operations rather than data science, AI, or Generative AI. It is entirely unrelated to the candidate's core expertise in LLMs, RAG, and agentic systems.</t>
+          <t>This is a management consulting role focused on Health and Life Sciences strategy at Oliver Wyman, requiring deep industry expertise in pharmaceuticals or MedTech and top-tier strategy consulting experience. It has zero alignment with the candidate's core GenAI, LLM, or Data Science specialization.</t>
         </is>
       </c>
       <c r="I168" s="3" t="inlineStr">
         <is>
-          <t>Yes - German required (see JD for exact level)</t>
+          <t>Not stated in JD</t>
         </is>
       </c>
       <c r="J168" s="3" t="inlineStr">
@@ -11107,9 +11107,9 @@
           <t>Not stated in JD</t>
         </is>
       </c>
-      <c r="K168" s="9" t="inlineStr">
-        <is>
-          <t>New this run (2026-08-29 13:17 UTC)</t>
+      <c r="K168" s="2" t="inlineStr">
+        <is>
+          <t>From previous run</t>
         </is>
       </c>
       <c r="L168" s="2" t="inlineStr">
@@ -11119,7 +11119,7 @@
       </c>
       <c r="M168" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/bi-engineer-at-jd-com-4414670937?position=6&amp;pageNum=0&amp;refId=WT017Qp%2F1VFpbzjZb903BA%3D%3D&amp;trackingId=uXRSjK39jDOlXpbtHq2yzQ%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/oliver-wyman-associate-health-and-life-sciences-dubai-at-oliver-wyman-4460351294?position=8&amp;pageNum=0&amp;refId=umynRMWB8laV9lcrAC5yvg%3D%3D&amp;trackingId=GWJpOuiL92AZx2SkHg%2FfPg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -11129,22 +11129,22 @@
       </c>
       <c r="B169" s="3" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>F&amp;S Associate - UAE National</t>
         </is>
       </c>
       <c r="C169" s="3" t="inlineStr">
         <is>
-          <t>Danube Group</t>
+          <t>Deliveroo</t>
         </is>
       </c>
       <c r="D169" s="3" t="inlineStr">
         <is>
-          <t>Dubai, United Arab Emirates</t>
+          <t>Dubai, Dubai, United Arab Emirates</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="F169" s="7" t="n">
@@ -11157,7 +11157,7 @@
       </c>
       <c r="H169" s="3" t="inlineStr">
         <is>
-          <t>This is a Power BI Developer role focused on dashboards, data visualization, DAX, and SQL, which is completely unrelated to the candidate's core specialization in Generative AI, LLMs, and agentic workflows.</t>
+          <t>This is a finance and strategy role focused on spreadsheets, variance analysis, and business reporting with no relation to Generative AI, machine learning, or data science. It is completely unrelated to the candidate's core technical specialization and profile.</t>
         </is>
       </c>
       <c r="I169" s="3" t="inlineStr">
@@ -11170,9 +11170,9 @@
           <t>Not stated in JD</t>
         </is>
       </c>
-      <c r="K169" s="9" t="inlineStr">
-        <is>
-          <t>New this run (2026-08-29 13:17 UTC)</t>
+      <c r="K169" s="2" t="inlineStr">
+        <is>
+          <t>From previous run</t>
         </is>
       </c>
       <c r="L169" s="2" t="inlineStr">
@@ -11182,7 +11182,7 @@
       </c>
       <c r="M169" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/power-bi-developer-at-danube-group-4459465901?position=5&amp;pageNum=0&amp;refId=WT017Qp%2F1VFpbzjZb903BA%3D%3D&amp;trackingId=2u7KtmoSLaInXvl%2FCAGPzw%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/f-s-associate-uae-national-at-deliveroo-4449749711?position=6&amp;pageNum=0&amp;refId=umynRMWB8laV9lcrAC5yvg%3D%3D&amp;trackingId=xir3IHLZTYXuoIlF3oUkeg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -11192,12 +11192,12 @@
       </c>
       <c r="B170" s="3" t="inlineStr">
         <is>
-          <t>National Assistant Planner</t>
+          <t>BI Engineer</t>
         </is>
       </c>
       <c r="C170" s="3" t="inlineStr">
         <is>
-          <t>Al-Futtaim</t>
+          <t>JD.COM</t>
         </is>
       </c>
       <c r="D170" s="3" t="inlineStr">
@@ -11207,11 +11207,11 @@
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="F170" s="7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G170" s="8" t="inlineStr">
         <is>
@@ -11220,12 +11220,12 @@
       </c>
       <c r="H170" s="3" t="inlineStr">
         <is>
-          <t>This is a non-technical retail merchandise planning role focused on financial forecasting, inventory management, and sales planning, which is entirely unrelated to the candidate's GenAI, LLM, and data science specialization.</t>
+          <t>This role is a BI Engineer position focused on supply chain, logistics, and retail operations rather than data science, AI, or Generative AI. It is entirely unrelated to the candidate's core expertise in LLMs, RAG, and agentic systems.</t>
         </is>
       </c>
       <c r="I170" s="3" t="inlineStr">
         <is>
-          <t>Not stated in JD</t>
+          <t>Yes - German required (see JD for exact level)</t>
         </is>
       </c>
       <c r="J170" s="3" t="inlineStr">
@@ -11245,7 +11245,7 @@
       </c>
       <c r="M170" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/national-assistant-planner-at-al-futtaim-4459335643?position=23&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=udE1OmanEOJo5NqnDVVmsw%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/bi-engineer-at-jd-com-4414670937?position=6&amp;pageNum=0&amp;refId=WT017Qp%2F1VFpbzjZb903BA%3D%3D&amp;trackingId=uXRSjK39jDOlXpbtHq2yzQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -11255,26 +11255,26 @@
       </c>
       <c r="B171" s="3" t="inlineStr">
         <is>
-          <t>Forward Deployed AI Integrator (UAE National Only), Field Engineering</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="C171" s="3" t="inlineStr">
         <is>
-          <t>Amazon Web Services (AWS)</t>
+          <t>Danube Group</t>
         </is>
       </c>
       <c r="D171" s="3" t="inlineStr">
         <is>
-          <t>Dubai, Dubai, United Arab Emirates</t>
+          <t>Dubai, United Arab Emirates</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="F171" s="7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G171" s="8" t="inlineStr">
         <is>
@@ -11283,7 +11283,7 @@
       </c>
       <c r="H171" s="3" t="inlineStr">
         <is>
-          <t>Although the role involves AI tooling and Python, it is restricted to UAE Nationals only, making it impossible for the candidate to qualify. Additionally, the position leans heavily toward technical program management rather than hands-on Generative AI and LLM engineering.</t>
+          <t>This is a Power BI Developer role focused on dashboards, data visualization, DAX, and SQL, which is completely unrelated to the candidate's core specialization in Generative AI, LLMs, and agentic workflows.</t>
         </is>
       </c>
       <c r="I171" s="3" t="inlineStr">
@@ -11308,7 +11308,7 @@
       </c>
       <c r="M171" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/forward-deployed-ai-integrator-uae-national-only-field-engineering-at-amazon-web-services-aws-4459616402?position=14&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=suYy8hgZkG37o3lG7FlDHQ%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/power-bi-developer-at-danube-group-4459465901?position=5&amp;pageNum=0&amp;refId=WT017Qp%2F1VFpbzjZb903BA%3D%3D&amp;trackingId=2u7KtmoSLaInXvl%2FCAGPzw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -11318,12 +11318,12 @@
       </c>
       <c r="B172" s="3" t="inlineStr">
         <is>
-          <t>GIS Specialist / Developer</t>
+          <t>National Assistant Planner</t>
         </is>
       </c>
       <c r="C172" s="3" t="inlineStr">
         <is>
-          <t>AECOM</t>
+          <t>Al-Futtaim</t>
         </is>
       </c>
       <c r="D172" s="3" t="inlineStr">
@@ -11346,7 +11346,7 @@
       </c>
       <c r="H172" s="3" t="inlineStr">
         <is>
-          <t>This is a GIS Specialist role focused on ArcGIS Enterprise administration, spatial analysis, and Python/ArcPy automation, which is completely unrelated to the candidate's core specialization in Generative AI, LLMs, and agentic systems.</t>
+          <t>This is a non-technical retail merchandise planning role focused on financial forecasting, inventory management, and sales planning, which is entirely unrelated to the candidate's GenAI, LLM, and data science specialization.</t>
         </is>
       </c>
       <c r="I172" s="3" t="inlineStr">
@@ -11371,7 +11371,7 @@
       </c>
       <c r="M172" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/gis-specialist-developer-at-aecom-4456869023?position=15&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=lGxG6%2FYECt2YwYGWf5hEZA%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/national-assistant-planner-at-al-futtaim-4459335643?position=23&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=udE1OmanEOJo5NqnDVVmsw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -11381,12 +11381,12 @@
       </c>
       <c r="B173" s="3" t="inlineStr">
         <is>
-          <t>Quant Desk Lead and Portfolio Manager</t>
+          <t>Forward Deployed AI Integrator (UAE National Only), Field Engineering</t>
         </is>
       </c>
       <c r="C173" s="3" t="inlineStr">
         <is>
-          <t>EMCD</t>
+          <t>Amazon Web Services (AWS)</t>
         </is>
       </c>
       <c r="D173" s="3" t="inlineStr">
@@ -11396,7 +11396,7 @@
       </c>
       <c r="E173" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F173" s="7" t="n">
@@ -11409,7 +11409,7 @@
       </c>
       <c r="H173" s="3" t="inlineStr">
         <is>
-          <t>This is a finance and quantitative trading role focused on running a systematic trading desk, portfolio management, and P&amp;L ownership, which is entirely unrelated to the candidate's core specialization in Generative AI, LLMs, and agentic systems.</t>
+          <t>Although the role involves AI tooling and Python, it is restricted to UAE Nationals only, making it impossible for the candidate to qualify. Additionally, the position leans heavily toward technical program management rather than hands-on Generative AI and LLM engineering.</t>
         </is>
       </c>
       <c r="I173" s="3" t="inlineStr">
@@ -11434,7 +11434,7 @@
       </c>
       <c r="M173" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/quant-desk-lead-and-portfolio-manager-at-emcd-4457949555?position=13&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=drHtrw6uBtEz5S2i%2BjBT5A%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/forward-deployed-ai-integrator-uae-national-only-field-engineering-at-amazon-web-services-aws-4459616402?position=14&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=suYy8hgZkG37o3lG7FlDHQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -11444,17 +11444,17 @@
       </c>
       <c r="B174" s="3" t="inlineStr">
         <is>
-          <t>Join Norlys Energy Trading</t>
+          <t>GIS Specialist / Developer</t>
         </is>
       </c>
       <c r="C174" s="3" t="inlineStr">
         <is>
-          <t>Norlys Energy Trading A/S</t>
+          <t>AECOM</t>
         </is>
       </c>
       <c r="D174" s="3" t="inlineStr">
         <is>
-          <t>Aalborg, North Denmark Region, Denmark</t>
+          <t>Dubai, Dubai, United Arab Emirates</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
@@ -11472,7 +11472,7 @@
       </c>
       <c r="H174" s="3" t="inlineStr">
         <is>
-          <t>This is an open, unsolicited job application for a general talent pool in energy trading, rather than a defined Data Science or Generative AI role. It completely lacks technical specifications, making it impossible to evaluate against the candidate's specialized GenAI and LLM expertise.</t>
+          <t>This is a GIS Specialist role focused on ArcGIS Enterprise administration, spatial analysis, and Python/ArcPy automation, which is completely unrelated to the candidate's core specialization in Generative AI, LLMs, and agentic systems.</t>
         </is>
       </c>
       <c r="I174" s="3" t="inlineStr">
@@ -11497,7 +11497,7 @@
       </c>
       <c r="M174" s="6" t="inlineStr">
         <is>
-          <t>https://dk.linkedin.com/jobs/view/join-norlys-energy-trading-at-norlys-energy-trading-a-s-4459158084?position=26&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=Z%2BOuDrbPap3omWro18MA2g%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/gis-specialist-developer-at-aecom-4456869023?position=15&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=lGxG6%2FYECt2YwYGWf5hEZA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -11507,17 +11507,17 @@
       </c>
       <c r="B175" s="3" t="inlineStr">
         <is>
-          <t>PhD scholarship in Modeling and Control of Parkinson’s Disease - DTU Electro</t>
+          <t>Quant Desk Lead and Portfolio Manager</t>
         </is>
       </c>
       <c r="C175" s="3" t="inlineStr">
         <is>
-          <t>DTU - Technical University of Denmark</t>
+          <t>EMCD</t>
         </is>
       </c>
       <c r="D175" s="3" t="inlineStr">
         <is>
-          <t>Kongens Lyngby, Capital Region of Denmark, Denmark</t>
+          <t>Dubai, Dubai, United Arab Emirates</t>
         </is>
       </c>
       <c r="E175" s="2" t="inlineStr">
@@ -11535,7 +11535,7 @@
       </c>
       <c r="H175" s="3" t="inlineStr">
         <is>
-          <t>This is a PhD scholarship position in neuroengineering, control systems, and healthcare technology at DTU, which is completely unrelated to the candidate's specialization in Generative AI, LLMs, and agentic systems.</t>
+          <t>This is a finance and quantitative trading role focused on running a systematic trading desk, portfolio management, and P&amp;L ownership, which is entirely unrelated to the candidate's core specialization in Generative AI, LLMs, and agentic systems.</t>
         </is>
       </c>
       <c r="I175" s="3" t="inlineStr">
@@ -11545,7 +11545,7 @@
       </c>
       <c r="J175" s="3" t="inlineStr">
         <is>
-          <t>Possible - relocation support mentioned, visa not explicit</t>
+          <t>Not stated in JD</t>
         </is>
       </c>
       <c r="K175" s="2" t="inlineStr">
@@ -11560,7 +11560,7 @@
       </c>
       <c r="M175" s="6" t="inlineStr">
         <is>
-          <t>https://dk.linkedin.com/jobs/view/phd-scholarship-in-modeling-and-control-of-parkinson%E2%80%99s-disease-dtu-electro-at-dtu-technical-university-of-denmark-4459145557?position=20&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=mStwcLkWBAvzmreGSwO4Hw%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/quant-desk-lead-and-portfolio-manager-at-emcd-4457949555?position=13&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=drHtrw6uBtEz5S2i%2BjBT5A%3D%3D</t>
         </is>
       </c>
     </row>
@@ -11570,17 +11570,17 @@
       </c>
       <c r="B176" s="3" t="inlineStr">
         <is>
-          <t>Analytikere med flair for databehandling til PET's kontraspionageindsats mod Rusland</t>
+          <t>Join Norlys Energy Trading</t>
         </is>
       </c>
       <c r="C176" s="3" t="inlineStr">
         <is>
-          <t>Politi</t>
+          <t>Norlys Energy Trading A/S</t>
         </is>
       </c>
       <c r="D176" s="3" t="inlineStr">
         <is>
-          <t>Copenhagen, Capital Region of Denmark, Denmark</t>
+          <t>Aalborg, North Denmark Region, Denmark</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr">
@@ -11598,7 +11598,7 @@
       </c>
       <c r="H176" s="3" t="inlineStr">
         <is>
-          <t>This is a national security intelligence and counter-espionage analyst role at the Danish Security and Intelligence Service (PET), which is completely unrelated to data science, artificial intelligence, or the candidate's Generative AI and LLM specialization.</t>
+          <t>This is an open, unsolicited job application for a general talent pool in energy trading, rather than a defined Data Science or Generative AI role. It completely lacks technical specifications, making it impossible to evaluate against the candidate's specialized GenAI and LLM expertise.</t>
         </is>
       </c>
       <c r="I176" s="3" t="inlineStr">
@@ -11623,7 +11623,7 @@
       </c>
       <c r="M176" s="6" t="inlineStr">
         <is>
-          <t>https://dk.linkedin.com/jobs/view/analytikere-med-flair-for-databehandling-til-pet-s-kontraspionageindsats-mod-rusland-at-politi-4457943820?position=18&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=%2FGEw4KOC0oARqkQIDTGJ4Q%3D%3D</t>
+          <t>https://dk.linkedin.com/jobs/view/join-norlys-energy-trading-at-norlys-energy-trading-a-s-4459158084?position=26&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=Z%2BOuDrbPap3omWro18MA2g%3D%3D</t>
         </is>
       </c>
     </row>
@@ -11633,17 +11633,17 @@
       </c>
       <c r="B177" s="3" t="inlineStr">
         <is>
-          <t>PostDoc - Uncertainty-Aware Optimization in Inverse Problems for Next-Generation 3D Scanning</t>
+          <t>PhD scholarship in Modeling and Control of Parkinson’s Disease - DTU Electro</t>
         </is>
       </c>
       <c r="C177" s="3" t="inlineStr">
         <is>
-          <t>3Shape</t>
+          <t>DTU - Technical University of Denmark</t>
         </is>
       </c>
       <c r="D177" s="3" t="inlineStr">
         <is>
-          <t>Copenhagen, Capital Region of Denmark, Denmark</t>
+          <t>Kongens Lyngby, Capital Region of Denmark, Denmark</t>
         </is>
       </c>
       <c r="E177" s="2" t="inlineStr">
@@ -11661,7 +11661,7 @@
       </c>
       <c r="H177" s="3" t="inlineStr">
         <is>
-          <t>This is a PostDoc position focused on mathematical optimization, numerical linear algebra, and uncertainty quantification for 3D scanning, which requires a PhD. It has no overlap with the candidate's specialization in GenAI, LLMs, and agentic systems.</t>
+          <t>This is a PhD scholarship position in neuroengineering, control systems, and healthcare technology at DTU, which is completely unrelated to the candidate's specialization in Generative AI, LLMs, and agentic systems.</t>
         </is>
       </c>
       <c r="I177" s="3" t="inlineStr">
@@ -11671,7 +11671,7 @@
       </c>
       <c r="J177" s="3" t="inlineStr">
         <is>
-          <t>Not stated in JD</t>
+          <t>Possible - relocation support mentioned, visa not explicit</t>
         </is>
       </c>
       <c r="K177" s="2" t="inlineStr">
@@ -11686,7 +11686,7 @@
       </c>
       <c r="M177" s="6" t="inlineStr">
         <is>
-          <t>https://dk.linkedin.com/jobs/view/postdoc-uncertainty-aware-optimization-in-inverse-problems-for-next-generation-3d-scanning-at-3shape-4459171806?position=15&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=bO0aSGZ%2FUAxThXN9yvOERg%3D%3D</t>
+          <t>https://dk.linkedin.com/jobs/view/phd-scholarship-in-modeling-and-control-of-parkinson%E2%80%99s-disease-dtu-electro-at-dtu-technical-university-of-denmark-4459145557?position=20&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=mStwcLkWBAvzmreGSwO4Hw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -11696,17 +11696,17 @@
       </c>
       <c r="B178" s="3" t="inlineStr">
         <is>
-          <t>Scientist, Quantitative Clinical Pharmacology (PK/PD Modeling &amp; Simulation)</t>
+          <t>Analytikere med flair for databehandling til PET's kontraspionageindsats mod Rusland</t>
         </is>
       </c>
       <c r="C178" s="3" t="inlineStr">
         <is>
-          <t>Hemab Therapeutics</t>
+          <t>Politi</t>
         </is>
       </c>
       <c r="D178" s="3" t="inlineStr">
         <is>
-          <t>Copenhagen Metropolitan Area</t>
+          <t>Copenhagen, Capital Region of Denmark, Denmark</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr">
@@ -11724,7 +11724,7 @@
       </c>
       <c r="H178" s="3" t="inlineStr">
         <is>
-          <t>This is a highly specialized biomedical role focusing on Pharmacokinetics/Pharmacodynamics (PK/PD) modeling and clinical pharmacology, requiring a Ph.D. and experience with tools like NONMEM or Monolix. It has zero overlap with the candidate's GenAI, LLM, and data science background.</t>
+          <t>This is a national security intelligence and counter-espionage analyst role at the Danish Security and Intelligence Service (PET), which is completely unrelated to data science, artificial intelligence, or the candidate's Generative AI and LLM specialization.</t>
         </is>
       </c>
       <c r="I178" s="3" t="inlineStr">
@@ -11749,7 +11749,7 @@
       </c>
       <c r="M178" s="6" t="inlineStr">
         <is>
-          <t>https://dk.linkedin.com/jobs/view/scientist-quantitative-clinical-pharmacology-pk-pd-modeling-simulation-at-hemab-therapeutics-4457218306?position=14&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=jhTyKvDAQ70R9PD5s0x2yA%3D%3D</t>
+          <t>https://dk.linkedin.com/jobs/view/analytikere-med-flair-for-databehandling-til-pet-s-kontraspionageindsats-mod-rusland-at-politi-4457943820?position=18&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=%2FGEw4KOC0oARqkQIDTGJ4Q%3D%3D</t>
         </is>
       </c>
     </row>
@@ -11759,17 +11759,17 @@
       </c>
       <c r="B179" s="3" t="inlineStr">
         <is>
-          <t>Senior Payload Data Operator</t>
+          <t>PostDoc - Uncertainty-Aware Optimization in Inverse Problems for Next-Generation 3D Scanning</t>
         </is>
       </c>
       <c r="C179" s="3" t="inlineStr">
         <is>
-          <t>FADA</t>
+          <t>3Shape</t>
         </is>
       </c>
       <c r="D179" s="3" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>Copenhagen, Capital Region of Denmark, Denmark</t>
         </is>
       </c>
       <c r="E179" s="2" t="inlineStr">
@@ -11787,7 +11787,7 @@
       </c>
       <c r="H179" s="3" t="inlineStr">
         <is>
-          <t>This is a satellite payload data engineering role focused on aerospace, remote sensing, and image processing (EO/SAR), which is completely unrelated to the candidate's specialization in GenAI, LLMs, and agentic systems.</t>
+          <t>This is a PostDoc position focused on mathematical optimization, numerical linear algebra, and uncertainty quantification for 3D scanning, which requires a PhD. It has no overlap with the candidate's specialization in GenAI, LLMs, and agentic systems.</t>
         </is>
       </c>
       <c r="I179" s="3" t="inlineStr">
@@ -11812,7 +11812,7 @@
       </c>
       <c r="M179" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/senior-payload-data-operator-at-fada-4448986926?position=20&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=xdfP2za0I45WGIW%2FRJb%2BgA%3D%3D</t>
+          <t>https://dk.linkedin.com/jobs/view/postdoc-uncertainty-aware-optimization-in-inverse-problems-for-next-generation-3d-scanning-at-3shape-4459171806?position=15&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=bO0aSGZ%2FUAxThXN9yvOERg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -11822,22 +11822,22 @@
       </c>
       <c r="B180" s="3" t="inlineStr">
         <is>
-          <t>Arabic Speech And Natural Language Processing Specialist</t>
+          <t>Scientist, Quantitative Clinical Pharmacology (PK/PD Modeling &amp; Simulation)</t>
         </is>
       </c>
       <c r="C180" s="3" t="inlineStr">
         <is>
-          <t>Birbal AI</t>
+          <t>Hemab Therapeutics</t>
         </is>
       </c>
       <c r="D180" s="3" t="inlineStr">
         <is>
-          <t>Abu Dhabi Emirate, United Arab Emirates</t>
+          <t>Copenhagen Metropolitan Area</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F180" s="7" t="n">
@@ -11850,7 +11850,7 @@
       </c>
       <c r="H180" s="3" t="inlineStr">
         <is>
-          <t>The role requires specialized expertise in Arabic speech technology (ASR, TTS, audio DSP) and native command of Gulf Arabic dialects, which does not match the candidate's core background in GenAI, LLMs, and RAG for English-language banking and HR use cases.</t>
+          <t>This is a highly specialized biomedical role focusing on Pharmacokinetics/Pharmacodynamics (PK/PD) modeling and clinical pharmacology, requiring a Ph.D. and experience with tools like NONMEM or Monolix. It has zero overlap with the candidate's GenAI, LLM, and data science background.</t>
         </is>
       </c>
       <c r="I180" s="3" t="inlineStr">
@@ -11875,7 +11875,7 @@
       </c>
       <c r="M180" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/arabic-speech-and-natural-language-processing-specialist-at-birbal-ai-4457738899?position=14&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=ztG06Ly%2FIZ3fxm%2Fhvl626A%3D%3D</t>
+          <t>https://dk.linkedin.com/jobs/view/scientist-quantitative-clinical-pharmacology-pk-pd-modeling-simulation-at-hemab-therapeutics-4457218306?position=14&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=jhTyKvDAQ70R9PD5s0x2yA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -11885,12 +11885,12 @@
       </c>
       <c r="B181" s="3" t="inlineStr">
         <is>
-          <t>Member of Technical Staff - Medical Research (Remote)</t>
+          <t>Senior Payload Data Operator</t>
         </is>
       </c>
       <c r="C181" s="3" t="inlineStr">
         <is>
-          <t>Hire Feed</t>
+          <t>FADA</t>
         </is>
       </c>
       <c r="D181" s="3" t="inlineStr">
@@ -11900,7 +11900,7 @@
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F181" s="7" t="n">
@@ -11913,7 +11913,7 @@
       </c>
       <c r="H181" s="3" t="inlineStr">
         <is>
-          <t>This role is completely unrelated to the candidate's specialization in Generative AI, LLMs, and agentic workflows, focusing instead on medical imaging, computational biology, and clinical research requiring a PhD.</t>
+          <t>This is a satellite payload data engineering role focused on aerospace, remote sensing, and image processing (EO/SAR), which is completely unrelated to the candidate's specialization in GenAI, LLMs, and agentic systems.</t>
         </is>
       </c>
       <c r="I181" s="3" t="inlineStr">
@@ -11938,7 +11938,7 @@
       </c>
       <c r="M181" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/member-of-technical-staff-medical-research-remote-at-hire-feed-4459638503?position=3&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=b91zxKPZNgdFnMmW%2FlYbHA%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/senior-payload-data-operator-at-fada-4448986926?position=20&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=xdfP2za0I45WGIW%2FRJb%2BgA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -11948,17 +11948,17 @@
       </c>
       <c r="B182" s="3" t="inlineStr">
         <is>
-          <t>AI Image Specialist</t>
+          <t>Arabic Speech And Natural Language Processing Specialist</t>
         </is>
       </c>
       <c r="C182" s="3" t="inlineStr">
         <is>
-          <t>Puffy</t>
+          <t>Birbal AI</t>
         </is>
       </c>
       <c r="D182" s="3" t="inlineStr">
         <is>
-          <t>Dubai, United Arab Emirates</t>
+          <t>Abu Dhabi Emirate, United Arab Emirates</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
@@ -11976,7 +11976,7 @@
       </c>
       <c r="H182" s="3" t="inlineStr">
         <is>
-          <t>This is an AI Image Specialist role focused on generative visual design and creative production (Midjourney, DALL-E, image synthesis), which is completely unrelated to the candidate's core specialization in LLMs, RAG, LangChain, and agentic AI pipelines for data science and enterprise applications.</t>
+          <t>The role requires specialized expertise in Arabic speech technology (ASR, TTS, audio DSP) and native command of Gulf Arabic dialects, which does not match the candidate's core background in GenAI, LLMs, and RAG for English-language banking and HR use cases.</t>
         </is>
       </c>
       <c r="I182" s="3" t="inlineStr">
@@ -11986,7 +11986,7 @@
       </c>
       <c r="J182" s="3" t="inlineStr">
         <is>
-          <t>Yes - explicitly stated in JD</t>
+          <t>Not stated in JD</t>
         </is>
       </c>
       <c r="K182" s="2" t="inlineStr">
@@ -12001,7 +12001,7 @@
       </c>
       <c r="M182" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/ai-image-specialist-at-puffy-4457756193?position=10&amp;pageNum=0&amp;refId=50H6yCrEXIuhgr6eqEojNg%3D%3D&amp;trackingId=9EIvgvUNu%2BE37717JffiJA%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/arabic-speech-and-natural-language-processing-specialist-at-birbal-ai-4457738899?position=14&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=ztG06Ly%2FIZ3fxm%2Fhvl626A%3D%3D</t>
         </is>
       </c>
     </row>
@@ -12011,22 +12011,22 @@
       </c>
       <c r="B183" s="3" t="inlineStr">
         <is>
-          <t>Market Operations &amp; Analytics Specialist — Institutional</t>
+          <t>Member of Technical Staff - Medical Research (Remote)</t>
         </is>
       </c>
       <c r="C183" s="3" t="inlineStr">
         <is>
-          <t>Confidential</t>
+          <t>Hire Feed</t>
         </is>
       </c>
       <c r="D183" s="3" t="inlineStr">
         <is>
-          <t>Dubai, United Arab Emirates</t>
+          <t>United Arab Emirates</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F183" s="7" t="n">
@@ -12039,7 +12039,7 @@
       </c>
       <c r="H183" s="3" t="inlineStr">
         <is>
-          <t>This role is completely unrelated to data science, artificial intelligence, LLMs, or generative AI, focusing entirely on cryptocurrency exchange operations, institutional client management, and trading analytics instead.</t>
+          <t>This role is completely unrelated to the candidate's specialization in Generative AI, LLMs, and agentic workflows, focusing instead on medical imaging, computational biology, and clinical research requiring a PhD.</t>
         </is>
       </c>
       <c r="I183" s="3" t="inlineStr">
@@ -12064,7 +12064,7 @@
       </c>
       <c r="M183" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/market-operations-analytics-specialist-%E2%80%94-institutional-at-confidential-4453037100?position=10&amp;pageNum=0&amp;refId=zJBbvwb5H0wsbJ5fs9ZTVw%3D%3D&amp;trackingId=ENnWCvoEQXOg1fXKuxlBug%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/member-of-technical-staff-medical-research-remote-at-hire-feed-4459638503?position=3&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=b91zxKPZNgdFnMmW%2FlYbHA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -12074,17 +12074,17 @@
       </c>
       <c r="B184" s="3" t="inlineStr">
         <is>
-          <t>Quantitative Developer, Systematic Equities</t>
+          <t>AI Image Specialist</t>
         </is>
       </c>
       <c r="C184" s="3" t="inlineStr">
         <is>
-          <t>Millennium</t>
+          <t>Puffy</t>
         </is>
       </c>
       <c r="D184" s="3" t="inlineStr">
         <is>
-          <t>Dubai, Dubai, United Arab Emirates</t>
+          <t>Dubai, United Arab Emirates</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
@@ -12102,7 +12102,7 @@
       </c>
       <c r="H184" s="3" t="inlineStr">
         <is>
-          <t>This role is a quantitative software engineering position focused on low-latency trading infrastructure, C++/C# development, and execution systems for a hedge fund, which is entirely unrelated to the candidate's specialization in GenAI, LLMs, and agentic architectures.</t>
+          <t>This is an AI Image Specialist role focused on generative visual design and creative production (Midjourney, DALL-E, image synthesis), which is completely unrelated to the candidate's core specialization in LLMs, RAG, LangChain, and agentic AI pipelines for data science and enterprise applications.</t>
         </is>
       </c>
       <c r="I184" s="3" t="inlineStr">
@@ -12112,7 +12112,7 @@
       </c>
       <c r="J184" s="3" t="inlineStr">
         <is>
-          <t>Not stated in JD</t>
+          <t>Yes - explicitly stated in JD</t>
         </is>
       </c>
       <c r="K184" s="2" t="inlineStr">
@@ -12127,7 +12127,7 @@
       </c>
       <c r="M184" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/quantitative-developer-systematic-equities-at-millennium-4290849018?position=6&amp;pageNum=0&amp;refId=zJBbvwb5H0wsbJ5fs9ZTVw%3D%3D&amp;trackingId=8TTWkyG2j%2F7MELtLSQ5VCA%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/ai-image-specialist-at-puffy-4457756193?position=10&amp;pageNum=0&amp;refId=50H6yCrEXIuhgr6eqEojNg%3D%3D&amp;trackingId=9EIvgvUNu%2BE37717JffiJA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -12137,17 +12137,17 @@
       </c>
       <c r="B185" s="3" t="inlineStr">
         <is>
-          <t>Senior Specialist - Portfolio Management</t>
+          <t>Market Operations &amp; Analytics Specialist — Institutional</t>
         </is>
       </c>
       <c r="C185" s="3" t="inlineStr">
         <is>
-          <t>MENA Careers</t>
+          <t>Confidential</t>
         </is>
       </c>
       <c r="D185" s="3" t="inlineStr">
         <is>
-          <t>Dubai, Dubai, United Arab Emirates</t>
+          <t>Dubai, United Arab Emirates</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr">
@@ -12165,7 +12165,7 @@
       </c>
       <c r="H185" s="3" t="inlineStr">
         <is>
-          <t>This is a non-AI banking role focused on portfolio management, loan optimization, and regulatory capital compliance in Dubai requiring UAE nationality, which completely misaligns with the candidate's GenAI, LLM, and data science specialization.</t>
+          <t>This role is completely unrelated to data science, artificial intelligence, LLMs, or generative AI, focusing entirely on cryptocurrency exchange operations, institutional client management, and trading analytics instead.</t>
         </is>
       </c>
       <c r="I185" s="3" t="inlineStr">
@@ -12190,7 +12190,7 @@
       </c>
       <c r="M185" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/senior-specialist-portfolio-management-at-mena-careers-4458066015?position=12&amp;pageNum=0&amp;refId=umynRMWB8laV9lcrAC5yvg%3D%3D&amp;trackingId=kbnf5IoX2jxOWD9%2Fe1UaKg%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/market-operations-analytics-specialist-%E2%80%94-institutional-at-confidential-4453037100?position=10&amp;pageNum=0&amp;refId=zJBbvwb5H0wsbJ5fs9ZTVw%3D%3D&amp;trackingId=ENnWCvoEQXOg1fXKuxlBug%3D%3D</t>
         </is>
       </c>
     </row>
@@ -12200,12 +12200,12 @@
       </c>
       <c r="B186" s="3" t="inlineStr">
         <is>
-          <t>Manager Logistics Performance</t>
+          <t>Quantitative Developer, Systematic Equities</t>
         </is>
       </c>
       <c r="C186" s="3" t="inlineStr">
         <is>
-          <t>talabat</t>
+          <t>Millennium</t>
         </is>
       </c>
       <c r="D186" s="3" t="inlineStr">
@@ -12215,7 +12215,7 @@
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F186" s="7" t="n">
@@ -12228,12 +12228,12 @@
       </c>
       <c r="H186" s="3" t="inlineStr">
         <is>
-          <t>This is a commercial operations, logistics, and P&amp;L management role completely unrelated to data science, artificial intelligence, or Large Language Models. It requires background in marketplace operations, logistics, or quick-commerce rather than GenAI engineering.</t>
+          <t>This role is a quantitative software engineering position focused on low-latency trading infrastructure, C++/C# development, and execution systems for a hedge fund, which is entirely unrelated to the candidate's specialization in GenAI, LLMs, and agentic architectures.</t>
         </is>
       </c>
       <c r="I186" s="3" t="inlineStr">
         <is>
-          <t>Yes - German required (see JD for exact level)</t>
+          <t>Not stated in JD</t>
         </is>
       </c>
       <c r="J186" s="3" t="inlineStr">
@@ -12253,7 +12253,7 @@
       </c>
       <c r="M186" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/manager-logistics-performance-at-talabat-4440740657?position=7&amp;pageNum=0&amp;refId=umynRMWB8laV9lcrAC5yvg%3D%3D&amp;trackingId=lMQWp6LAUNLwXpGhMCpl2Q%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/quantitative-developer-systematic-equities-at-millennium-4290849018?position=6&amp;pageNum=0&amp;refId=zJBbvwb5H0wsbJ5fs9ZTVw%3D%3D&amp;trackingId=8TTWkyG2j%2F7MELtLSQ5VCA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -12263,17 +12263,17 @@
       </c>
       <c r="B187" s="3" t="inlineStr">
         <is>
-          <t>Perception Engineer</t>
+          <t>Senior Specialist - Portfolio Management</t>
         </is>
       </c>
       <c r="C187" s="3" t="inlineStr">
         <is>
-          <t>Careernet</t>
+          <t>MENA Careers</t>
         </is>
       </c>
       <c r="D187" s="3" t="inlineStr">
         <is>
-          <t>Ajman, Ajman Emirate, United Arab Emirates</t>
+          <t>Dubai, Dubai, United Arab Emirates</t>
         </is>
       </c>
       <c r="E187" s="2" t="inlineStr">
@@ -12291,93 +12291,219 @@
       </c>
       <c r="H187" s="3" t="inlineStr">
         <is>
+          <t>This is a non-AI banking role focused on portfolio management, loan optimization, and regulatory capital compliance in Dubai requiring UAE nationality, which completely misaligns with the candidate's GenAI, LLM, and data science specialization.</t>
+        </is>
+      </c>
+      <c r="I187" s="3" t="inlineStr">
+        <is>
+          <t>Not stated in JD</t>
+        </is>
+      </c>
+      <c r="J187" s="3" t="inlineStr">
+        <is>
+          <t>Not stated in JD</t>
+        </is>
+      </c>
+      <c r="K187" s="2" t="inlineStr">
+        <is>
+          <t>From previous run</t>
+        </is>
+      </c>
+      <c r="L187" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="M187" s="6" t="inlineStr">
+        <is>
+          <t>https://ae.linkedin.com/jobs/view/senior-specialist-portfolio-management-at-mena-careers-4458066015?position=12&amp;pageNum=0&amp;refId=umynRMWB8laV9lcrAC5yvg%3D%3D&amp;trackingId=kbnf5IoX2jxOWD9%2Fe1UaKg%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="188" ht="55" customHeight="1">
+      <c r="A188" s="2" t="n">
+        <v>187</v>
+      </c>
+      <c r="B188" s="3" t="inlineStr">
+        <is>
+          <t>Manager Logistics Performance</t>
+        </is>
+      </c>
+      <c r="C188" s="3" t="inlineStr">
+        <is>
+          <t>talabat</t>
+        </is>
+      </c>
+      <c r="D188" s="3" t="inlineStr">
+        <is>
+          <t>Dubai, Dubai, United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="E188" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="F188" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G188" s="8" t="inlineStr">
+        <is>
+          <t>Below threshold</t>
+        </is>
+      </c>
+      <c r="H188" s="3" t="inlineStr">
+        <is>
+          <t>This is a commercial operations, logistics, and P&amp;L management role completely unrelated to data science, artificial intelligence, or Large Language Models. It requires background in marketplace operations, logistics, or quick-commerce rather than GenAI engineering.</t>
+        </is>
+      </c>
+      <c r="I188" s="3" t="inlineStr">
+        <is>
+          <t>Yes - German required (see JD for exact level)</t>
+        </is>
+      </c>
+      <c r="J188" s="3" t="inlineStr">
+        <is>
+          <t>Not stated in JD</t>
+        </is>
+      </c>
+      <c r="K188" s="2" t="inlineStr">
+        <is>
+          <t>From previous run</t>
+        </is>
+      </c>
+      <c r="L188" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="M188" s="6" t="inlineStr">
+        <is>
+          <t>https://ae.linkedin.com/jobs/view/manager-logistics-performance-at-talabat-4440740657?position=7&amp;pageNum=0&amp;refId=umynRMWB8laV9lcrAC5yvg%3D%3D&amp;trackingId=lMQWp6LAUNLwXpGhMCpl2Q%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="189" ht="55" customHeight="1">
+      <c r="A189" s="2" t="n">
+        <v>188</v>
+      </c>
+      <c r="B189" s="3" t="inlineStr">
+        <is>
+          <t>Perception Engineer</t>
+        </is>
+      </c>
+      <c r="C189" s="3" t="inlineStr">
+        <is>
+          <t>Careernet</t>
+        </is>
+      </c>
+      <c r="D189" s="3" t="inlineStr">
+        <is>
+          <t>Ajman, Ajman Emirate, United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="E189" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="F189" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G189" s="8" t="inlineStr">
+        <is>
+          <t>Below threshold</t>
+        </is>
+      </c>
+      <c r="H189" s="3" t="inlineStr">
+        <is>
           <t>This is a hardware-focused Perception Engineer role centering on 2D/3D computer vision, camera calibration, point clouds, and robotics. It is completely unrelated to the candidate's specialization in GenAI, LLMs, RAG, and agentic AI.</t>
         </is>
       </c>
-      <c r="I187" s="3" t="inlineStr">
-        <is>
-          <t>Not stated in JD</t>
-        </is>
-      </c>
-      <c r="J187" s="3" t="inlineStr">
-        <is>
-          <t>Not stated in JD</t>
-        </is>
-      </c>
-      <c r="K187" s="2" t="inlineStr">
-        <is>
-          <t>From previous run</t>
-        </is>
-      </c>
-      <c r="L187" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="M187" s="6" t="inlineStr">
+      <c r="I189" s="3" t="inlineStr">
+        <is>
+          <t>Not stated in JD</t>
+        </is>
+      </c>
+      <c r="J189" s="3" t="inlineStr">
+        <is>
+          <t>Not stated in JD</t>
+        </is>
+      </c>
+      <c r="K189" s="2" t="inlineStr">
+        <is>
+          <t>From previous run</t>
+        </is>
+      </c>
+      <c r="L189" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="M189" s="6" t="inlineStr">
         <is>
           <t>https://ae.linkedin.com/jobs/view/perception-engineer-at-careernet-4458403150?position=10&amp;pageNum=0&amp;refId=umynRMWB8laV9lcrAC5yvg%3D%3D&amp;trackingId=8I7i%2FeIdinpIC7lB70K7fg%3D%3D</t>
         </is>
       </c>
     </row>
-    <row r="188" ht="55" customHeight="1">
-      <c r="A188" s="10" t="n">
-        <v>187</v>
-      </c>
-      <c r="B188" s="11" t="inlineStr">
+    <row r="190" ht="55" customHeight="1">
+      <c r="A190" s="10" t="n">
+        <v>189</v>
+      </c>
+      <c r="B190" s="11" t="inlineStr">
         <is>
           <t>Data Scientist</t>
         </is>
       </c>
-      <c r="C188" s="11" t="inlineStr">
+      <c r="C190" s="11" t="inlineStr">
         <is>
           <t>Magno IT Recruitment</t>
         </is>
       </c>
-      <c r="D188" s="11" t="inlineStr">
+      <c r="D190" s="11" t="inlineStr">
         <is>
           <t>Amsterdam, North Holland, Netherlands</t>
         </is>
       </c>
-      <c r="E188" s="10" t="inlineStr">
+      <c r="E190" s="10" t="inlineStr">
         <is>
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F188" s="10" t="n">
+      <c r="F190" s="10" t="n">
         <v>92</v>
       </c>
-      <c r="G188" s="12" t="inlineStr">
+      <c r="G190" s="12" t="inlineStr">
         <is>
           <t>APPLY</t>
         </is>
       </c>
-      <c r="H188" s="11" t="inlineStr">
+      <c r="H190" s="11" t="inlineStr">
         <is>
           <t>This Senior AI Engineer role is an exceptional technical match, focusing directly on LLMs, RAG, agentic AI applications, and semantic search which align precisely with the candidate's core specialization. The seniority level (Senior) fits the candidate's 10+ years of experience very well.</t>
         </is>
       </c>
-      <c r="I188" s="11" t="inlineStr">
-        <is>
-          <t>Not stated in JD</t>
-        </is>
-      </c>
-      <c r="J188" s="11" t="inlineStr">
-        <is>
-          <t>Not stated in JD</t>
-        </is>
-      </c>
-      <c r="K188" s="10" t="inlineStr">
-        <is>
-          <t>From previous run</t>
-        </is>
-      </c>
-      <c r="L188" s="10" t="inlineStr">
+      <c r="I190" s="11" t="inlineStr">
+        <is>
+          <t>Not stated in JD</t>
+        </is>
+      </c>
+      <c r="J190" s="11" t="inlineStr">
+        <is>
+          <t>Not stated in JD</t>
+        </is>
+      </c>
+      <c r="K190" s="10" t="inlineStr">
+        <is>
+          <t>From previous run</t>
+        </is>
+      </c>
+      <c r="L190" s="10" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="M188" s="13" t="inlineStr">
+      <c r="M190" s="13" t="inlineStr">
         <is>
           <t>https://nl.linkedin.com/jobs/view/data-scientist-at-magno-it-recruitment-4448992517?position=9&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=26%2BZzuSXNPWrglox%2BL4Wqg%3D%3D</t>
         </is>
@@ -12572,6 +12698,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M186" r:id="rId185"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M187" r:id="rId186"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M190" r:id="rId189"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/job_matches.xlsx
+++ b/data/job_matches.xlsx
@@ -517,7 +517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M190"/>
+  <dimension ref="A1:M191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3758,26 +3758,26 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>Machine Learning (AI) Engineer (Hybrid)</t>
+          <t>Data Intelligence Machine Learning Engineer</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>Quik Hire Staffing</t>
+          <t>Dyson</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Dubai, Dubai, United Arab Emirates</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="F52" s="7" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G52" s="8" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t>The role focuses heavily on traditional deep learning frameworks (TensorFlow, PyTorch), MLOps, and model training rather than the candidate's core specialization in Generative AI, LLMs, and agentic workflows. However, it is still a technical AI/ML engineering position that aligns reasonably well in terms of experience level.</t>
+          <t>The role is focused on data-centric AI, active learning, weak supervision, and synthetic data generation for computer vision/NLP pipelines rather than the candidate's core specialization in GenAI, LLMs, and agentic systems. While the candidate has strong overall machine learning experience, the specific mismatch in technical focus (data labelling infrastructure vs. generative AI applications) results in a mediocre fit.</t>
         </is>
       </c>
       <c r="I52" s="3" t="inlineStr">
@@ -3799,9 +3799,9 @@
           <t>Not stated in JD</t>
         </is>
       </c>
-      <c r="K52" s="2" t="inlineStr">
-        <is>
-          <t>From previous run</t>
+      <c r="K52" s="9" t="inlineStr">
+        <is>
+          <t>New this run (2026-08-30 13:07 UTC)</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="M52" s="6" t="inlineStr">
         <is>
-          <t>https://de.linkedin.com/jobs/view/machine-learning-ai-engineer-hybrid-at-quik-hire-staffing-4459653741?position=27&amp;pageNum=0&amp;refId=T%2F0KkBXL%2Fl%2B5Iv5tUGTY7Q%3D%3D&amp;trackingId=xAvCgryMmzYLEKjSJh9cEw%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/data-intelligence-machine-learning-engineer-at-dyson-4384578924?position=1&amp;pageNum=0&amp;refId=AwhpSuwCXzdYoCWJZXzMEg%3D%3D&amp;trackingId=PqWeXprZoF9vaGEviBCjLg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -3821,22 +3821,22 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>Senior Applied Scientist (All genders)</t>
+          <t>Machine Learning (AI) Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>Zalando</t>
+          <t>Quik Hire Staffing</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>Berlin, Berlin, Germany</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F53" s="7" t="n">
@@ -3849,7 +3849,7 @@
       </c>
       <c r="H53" s="3" t="inlineStr">
         <is>
-          <t>This is a classical ML and causal inference role focused on marketing mix modeling, experimentation, and econometrics rather than the candidate's core specialization in Generative AI, LLMs, and agentic systems. However, the seniority level (Senior Applied Scientist with 5+ years experience) aligns reasonably well with the candidate's 10+ years of experience.</t>
+          <t>The role focuses heavily on traditional deep learning frameworks (TensorFlow, PyTorch), MLOps, and model training rather than the candidate's core specialization in Generative AI, LLMs, and agentic workflows. However, it is still a technical AI/ML engineering position that aligns reasonably well in terms of experience level.</t>
         </is>
       </c>
       <c r="I53" s="3" t="inlineStr">
@@ -3859,7 +3859,7 @@
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t>Possible - relocation support mentioned, visa not explicit</t>
+          <t>Not stated in JD</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="M53" s="6" t="inlineStr">
         <is>
-          <t>https://de.linkedin.com/jobs/view/senior-applied-scientist-all-genders-at-zalando-4457268030?position=29&amp;pageNum=0&amp;refId=T%2F0KkBXL%2Fl%2B5Iv5tUGTY7Q%3D%3D&amp;trackingId=uPBCURAa%2BhpqUjOtZt20sg%3D%3D</t>
+          <t>https://de.linkedin.com/jobs/view/machine-learning-ai-engineer-hybrid-at-quik-hire-staffing-4459653741?position=27&amp;pageNum=0&amp;refId=T%2F0KkBXL%2Fl%2B5Iv5tUGTY7Q%3D%3D&amp;trackingId=xAvCgryMmzYLEKjSJh9cEw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -3884,17 +3884,17 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>Consultant Business &amp; AI Insights (m/w/d) in München</t>
+          <t>Senior Applied Scientist (All genders)</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Zalando</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>Munich, Bavaria, Germany</t>
+          <t>Berlin, Berlin, Germany</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -3912,17 +3912,17 @@
       </c>
       <c r="H54" s="3" t="inlineStr">
         <is>
-          <t>The candidate has strong GenAI and MLOps specialization, but this Deloitte role is at the junior/consultant level requiring early-career experience, making it a severe seniority mismatch for a Lead Data Scientist with 10+ years of experience. Furthermore, the role focuses heavily on general BI, analytics engineering, and basic consulting rather than advanced agentic AI development.</t>
+          <t>This is a classical ML and causal inference role focused on marketing mix modeling, experimentation, and econometrics rather than the candidate's core specialization in Generative AI, LLMs, and agentic systems. However, the seniority level (Senior Applied Scientist with 5+ years experience) aligns reasonably well with the candidate's 10+ years of experience.</t>
         </is>
       </c>
       <c r="I54" s="3" t="inlineStr">
         <is>
-          <t>Yes - fluent/C1+ German explicitly required</t>
+          <t>Not stated in JD</t>
         </is>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>Not stated in JD</t>
+          <t>Possible - relocation support mentioned, visa not explicit</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="M54" s="6" t="inlineStr">
         <is>
-          <t>https://de.linkedin.com/jobs/view/consultant-business-ai-insights-m-w-d-in-m%C3%BCnchen-at-deloitte-4440568216?position=21&amp;pageNum=0&amp;refId=T%2F0KkBXL%2Fl%2B5Iv5tUGTY7Q%3D%3D&amp;trackingId=%2BjmC%2BHZAc9MdN%2BCr7d%2BCiw%3D%3D</t>
+          <t>https://de.linkedin.com/jobs/view/senior-applied-scientist-all-genders-at-zalando-4457268030?position=29&amp;pageNum=0&amp;refId=T%2F0KkBXL%2Fl%2B5Iv5tUGTY7Q%3D%3D&amp;trackingId=uPBCURAa%2BhpqUjOtZt20sg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -3947,17 +3947,17 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>Senior Manager - Artificial Intelligence</t>
+          <t>Consultant Business &amp; AI Insights (m/w/d) in München</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>Hays</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>Dubai, United Arab Emirates</t>
+          <t>Munich, Bavaria, Germany</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -3975,12 +3975,12 @@
       </c>
       <c r="H55" s="3" t="inlineStr">
         <is>
-          <t>The role focuses heavily on AI governance, assurance, model evaluation, and risk management rather than hands-on GenAI application development or agentic workflows, which are the candidate's core strengths. Additionally, the Senior Manager title leans toward a managerial and compliance track compared to the candidate's hands-on Lead Data Scientist background.</t>
+          <t>The candidate has strong GenAI and MLOps specialization, but this Deloitte role is at the junior/consultant level requiring early-career experience, making it a severe seniority mismatch for a Lead Data Scientist with 10+ years of experience. Furthermore, the role focuses heavily on general BI, analytics engineering, and basic consulting rather than advanced agentic AI development.</t>
         </is>
       </c>
       <c r="I55" s="3" t="inlineStr">
         <is>
-          <t>Not stated in JD</t>
+          <t>Yes - fluent/C1+ German explicitly required</t>
         </is>
       </c>
       <c r="J55" s="3" t="inlineStr">
@@ -4000,7 +4000,7 @@
       </c>
       <c r="M55" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/senior-manager-artificial-intelligence-at-hays-4457227403?position=27&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=m8EGYWiqeCT0F9aowu0X7g%3D%3D</t>
+          <t>https://de.linkedin.com/jobs/view/consultant-business-ai-insights-m-w-d-in-m%C3%BCnchen-at-deloitte-4440568216?position=21&amp;pageNum=0&amp;refId=T%2F0KkBXL%2Fl%2B5Iv5tUGTY7Q%3D%3D&amp;trackingId=%2BjmC%2BHZAc9MdN%2BCr7d%2BCiw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -4010,17 +4010,17 @@
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>AI GTM Consulting - Banking</t>
+          <t>Senior Manager - Artificial Intelligence</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>NTT DATA, Inc.</t>
+          <t>Hays</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>Dubai, Dubai, United Arab Emirates</t>
+          <t>Dubai, United Arab Emirates</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -4038,7 +4038,7 @@
       </c>
       <c r="H56" s="3" t="inlineStr">
         <is>
-          <t>The candidate has strong technical GenAI and LLM expertise, but this role is primarily a client-facing AI GTM consulting and pre-sales position focused on the Middle East banking sector rather than hands-on technical model development. Additionally, the candidate lacks the required regional Gulf consulting experience and heavy banking industry operating model background.</t>
+          <t>The role focuses heavily on AI governance, assurance, model evaluation, and risk management rather than hands-on GenAI application development or agentic workflows, which are the candidate's core strengths. Additionally, the Senior Manager title leans toward a managerial and compliance track compared to the candidate's hands-on Lead Data Scientist background.</t>
         </is>
       </c>
       <c r="I56" s="3" t="inlineStr">
@@ -4063,7 +4063,7 @@
       </c>
       <c r="M56" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/ai-gtm-consulting-banking-at-ntt-data-inc-4446632891?position=28&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=KvV4cGbrQRe2y%2FdaiwjIeA%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/senior-manager-artificial-intelligence-at-hays-4457227403?position=27&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=m8EGYWiqeCT0F9aowu0X7g%3D%3D</t>
         </is>
       </c>
     </row>
@@ -4073,17 +4073,17 @@
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>Senior Consultant - Financial Crime Prevention</t>
+          <t>AI GTM Consulting - Banking</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>Zanders</t>
+          <t>NTT DATA, Inc.</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>Utrecht, Utrecht, Netherlands</t>
+          <t>Dubai, Dubai, United Arab Emirates</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="H57" s="3" t="inlineStr">
         <is>
-          <t>The role is primarily a traditional quantitative financial crime and risk consulting position where GenAI and LLMs are only mentioned as a minor plus, making it a weak match for the candidate's core GenAI and agentic AI specialization despite matching his overall years of experience.</t>
+          <t>The candidate has strong technical GenAI and LLM expertise, but this role is primarily a client-facing AI GTM consulting and pre-sales position focused on the Middle East banking sector rather than hands-on technical model development. Additionally, the candidate lacks the required regional Gulf consulting experience and heavy banking industry operating model background.</t>
         </is>
       </c>
       <c r="I57" s="3" t="inlineStr">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="M57" s="6" t="inlineStr">
         <is>
-          <t>https://nl.linkedin.com/jobs/view/senior-consultant-financial-crime-prevention-at-zanders-4457921059?position=27&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=Xn8L7cLgbmU3MmPJfLc4Jg%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/ai-gtm-consulting-banking-at-ntt-data-inc-4446632891?position=28&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=KvV4cGbrQRe2y%2FdaiwjIeA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>Amsterdam, North Holland, Netherlands</t>
+          <t>Utrecht, Utrecht, Netherlands</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -4164,7 +4164,7 @@
       </c>
       <c r="H58" s="3" t="inlineStr">
         <is>
-          <t>The role is primarily focused on quantitative risk advisory and financial crime prevention consulting with classical modeling and model validation, where NLP and LLM pipeline experience is only a minor plus rather than the core focus. Seniority-wise, the Senior Consultant position requires 2+ years of track record, which aligns with the candidate's experience, but the domain mismatch results in a lower score.</t>
+          <t>The role is primarily a traditional quantitative financial crime and risk consulting position where GenAI and LLMs are only mentioned as a minor plus, making it a weak match for the candidate's core GenAI and agentic AI specialization despite matching his overall years of experience.</t>
         </is>
       </c>
       <c r="I58" s="3" t="inlineStr">
@@ -4189,7 +4189,7 @@
       </c>
       <c r="M58" s="6" t="inlineStr">
         <is>
-          <t>https://nl.linkedin.com/jobs/view/senior-consultant-financial-crime-prevention-at-zanders-4457902287?position=25&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=JPzSeOLZttSxrJAgb7RtbQ%3D%3D</t>
+          <t>https://nl.linkedin.com/jobs/view/senior-consultant-financial-crime-prevention-at-zanders-4457921059?position=27&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=Xn8L7cLgbmU3MmPJfLc4Jg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -4199,17 +4199,17 @@
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>Lead Data Scientist</t>
+          <t>Senior Consultant - Financial Crime Prevention</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>AS Watson Benelux</t>
+          <t>Zanders</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>Renswoude, Utrecht, Netherlands</t>
+          <t>Amsterdam, North Holland, Netherlands</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -4227,7 +4227,7 @@
       </c>
       <c r="H59" s="3" t="inlineStr">
         <is>
-          <t>This Lead Data Scientist role focuses heavily on classical machine learning, forecasting, optimization, and traditional data science applications for retail (such as sales forecasting and promotional personalization), with no mention of Generative AI, LLMs, or agentic workflows. However, the candidate's 10+ years of experience and leadership background align well with the seniority requirements of the role.</t>
+          <t>The role is primarily focused on quantitative risk advisory and financial crime prevention consulting with classical modeling and model validation, where NLP and LLM pipeline experience is only a minor plus rather than the core focus. Seniority-wise, the Senior Consultant position requires 2+ years of track record, which aligns with the candidate's experience, but the domain mismatch results in a lower score.</t>
         </is>
       </c>
       <c r="I59" s="3" t="inlineStr">
@@ -4252,7 +4252,7 @@
       </c>
       <c r="M59" s="6" t="inlineStr">
         <is>
-          <t>https://nl.linkedin.com/jobs/view/lead-data-scientist-at-as-watson-benelux-4377637626?position=11&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=D%2Bd%2FEPbAvDXvjR5ZJgWEIQ%3D%3D</t>
+          <t>https://nl.linkedin.com/jobs/view/senior-consultant-financial-crime-prevention-at-zanders-4457902287?position=25&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=JPzSeOLZttSxrJAgb7RtbQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -4262,17 +4262,17 @@
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>Applied Data Scientist - Intelligent Document Processing</t>
+          <t>Lead Data Scientist</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>ABN AMRO Bank N.V.</t>
+          <t>AS Watson Benelux</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>Amersfoort, Utrecht, Netherlands</t>
+          <t>Renswoude, Utrecht, Netherlands</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -4290,7 +4290,7 @@
       </c>
       <c r="H60" s="3" t="inlineStr">
         <is>
-          <t>The role focuses on Intelligent Document Processing (IDP) and document classification using existing components rather than cutting-edge GenAI/LLM orchestration or agentic systems. Additionally, the position asks for 3-6 years of experience (whereas the candidate has 10+) and explicitly requires Dutch language proficiency, making it a weaker fit.</t>
+          <t>This Lead Data Scientist role focuses heavily on classical machine learning, forecasting, optimization, and traditional data science applications for retail (such as sales forecasting and promotional personalization), with no mention of Generative AI, LLMs, or agentic workflows. However, the candidate's 10+ years of experience and leadership background align well with the seniority requirements of the role.</t>
         </is>
       </c>
       <c r="I60" s="3" t="inlineStr">
@@ -4315,7 +4315,7 @@
       </c>
       <c r="M60" s="6" t="inlineStr">
         <is>
-          <t>https://nl.linkedin.com/jobs/view/applied-data-scientist-intelligent-document-processing-at-abn-amro-bank-n-v-4440507839?position=4&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=yeF1JJiNzo5kSVTx1eGVfw%3D%3D</t>
+          <t>https://nl.linkedin.com/jobs/view/lead-data-scientist-at-as-watson-benelux-4377637626?position=11&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=D%2Bd%2FEPbAvDXvjR5ZJgWEIQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -4325,17 +4325,17 @@
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Applied Data Scientist - Intelligent Document Processing</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>CIMSOLUTIONS</t>
+          <t>ABN AMRO Bank N.V.</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>North Brabant, Netherlands</t>
+          <t>Amersfoort, Utrecht, Netherlands</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -4353,7 +4353,7 @@
       </c>
       <c r="H61" s="3" t="inlineStr">
         <is>
-          <t>This role focuses on traditional data science, predictive analysis, and business intelligence without any mention of Generative AI, LLMs, or agentic frameworks. Additionally, the job explicitly requires excellent communication skills in both Dutch and English, which creates a mismatch as the candidate lacks Dutch fluency.</t>
+          <t>The role focuses on Intelligent Document Processing (IDP) and document classification using existing components rather than cutting-edge GenAI/LLM orchestration or agentic systems. Additionally, the position asks for 3-6 years of experience (whereas the candidate has 10+) and explicitly requires Dutch language proficiency, making it a weaker fit.</t>
         </is>
       </c>
       <c r="I61" s="3" t="inlineStr">
@@ -4378,7 +4378,7 @@
       </c>
       <c r="M61" s="6" t="inlineStr">
         <is>
-          <t>https://nl.linkedin.com/jobs/view/data-scientist-at-cimsolutions-4457901406?position=2&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=b3VmH8PYtChkdpJv0VgUxA%3D%3D</t>
+          <t>https://nl.linkedin.com/jobs/view/applied-data-scientist-intelligent-document-processing-at-abn-amro-bank-n-v-4440507839?position=4&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=yeF1JJiNzo5kSVTx1eGVfw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -4388,17 +4388,17 @@
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>Data Scientist Kruidvat</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>AS Watson Benelux</t>
+          <t>CIMSOLUTIONS</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>Renswoude, Utrecht, Netherlands</t>
+          <t>North Brabant, Netherlands</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="H62" s="3" t="inlineStr">
         <is>
-          <t>This role focuses on classical data science applications like time-series forecasting, supply chain optimization, and predictive modeling for retail, lacking any mention of Generative AI, LLMs, or agentic systems which are the candidate's core specialization. Although the tech stack includes Databricks and Azure, the domain mismatch makes it a weak fit.</t>
+          <t>This role focuses on traditional data science, predictive analysis, and business intelligence without any mention of Generative AI, LLMs, or agentic frameworks. Additionally, the job explicitly requires excellent communication skills in both Dutch and English, which creates a mismatch as the candidate lacks Dutch fluency.</t>
         </is>
       </c>
       <c r="I62" s="3" t="inlineStr">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="M62" s="6" t="inlineStr">
         <is>
-          <t>https://nl.linkedin.com/jobs/view/data-scientist-kruidvat-at-as-watson-benelux-4439964615?position=3&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=tWylwGWz364M%2B%2FotR1FLZg%3D%3D</t>
+          <t>https://nl.linkedin.com/jobs/view/data-scientist-at-cimsolutions-4457901406?position=2&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=b3VmH8PYtChkdpJv0VgUxA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -4451,17 +4451,17 @@
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Data Scientist Kruidvat</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>CIMSOLUTIONS</t>
+          <t>AS Watson Benelux</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>South Holland, Netherlands</t>
+          <t>Renswoude, Utrecht, Netherlands</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -4479,7 +4479,7 @@
       </c>
       <c r="H63" s="3" t="inlineStr">
         <is>
-          <t>This role focuses on traditional data science, predictive modeling, and business intelligence with standard ML libraries (TensorFlow, scikit-learn), lacking any focus on the candidate's core Generative AI, LLM, and agentic AI specialization. Additionally, the job explicitly requires excellent communication skills in both Dutch and English, which creates a significant language mismatch for the candidate.</t>
+          <t>This role focuses on classical data science applications like time-series forecasting, supply chain optimization, and predictive modeling for retail, lacking any mention of Generative AI, LLMs, or agentic systems which are the candidate's core specialization. Although the tech stack includes Databricks and Azure, the domain mismatch makes it a weak fit.</t>
         </is>
       </c>
       <c r="I63" s="3" t="inlineStr">
@@ -4504,7 +4504,7 @@
       </c>
       <c r="M63" s="6" t="inlineStr">
         <is>
-          <t>https://nl.linkedin.com/jobs/view/data-scientist-at-cimsolutions-4457917043?position=1&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=1JSHNn3m2jBGxvl6iC8lcw%3D%3D</t>
+          <t>https://nl.linkedin.com/jobs/view/data-scientist-kruidvat-at-as-watson-benelux-4439964615?position=3&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=tWylwGWz364M%2B%2FotR1FLZg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -4514,17 +4514,17 @@
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>AI Product Owner</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>Novo Nordisk</t>
+          <t>CIMSOLUTIONS</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>Ballerup Municipality, Capital Region of Denmark, Denmark</t>
+          <t>South Holland, Netherlands</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -4542,7 +4542,7 @@
       </c>
       <c r="H64" s="3" t="inlineStr">
         <is>
-          <t>This is an AI Product Owner role focused on manufacturing and supply chain systems, which requires product management and stakeholder alignment rather than hands-on GenAI/LLM development. The candidate is a technical Lead Data Scientist specializing in hands-on LangChain/LangGraph and agentic workflows, presenting a significant mismatch in role function and domain expertise.</t>
+          <t>This role focuses on traditional data science, predictive modeling, and business intelligence with standard ML libraries (TensorFlow, scikit-learn), lacking any focus on the candidate's core Generative AI, LLM, and agentic AI specialization. Additionally, the job explicitly requires excellent communication skills in both Dutch and English, which creates a significant language mismatch for the candidate.</t>
         </is>
       </c>
       <c r="I64" s="3" t="inlineStr">
@@ -4567,7 +4567,7 @@
       </c>
       <c r="M64" s="6" t="inlineStr">
         <is>
-          <t>https://dk.linkedin.com/jobs/view/ai-product-owner-at-novo-nordisk-4457258669?position=24&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=s56Z90FxaVSj7XKQs6qQuA%3D%3D</t>
+          <t>https://nl.linkedin.com/jobs/view/data-scientist-at-cimsolutions-4457917043?position=1&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=1JSHNn3m2jBGxvl6iC8lcw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -4577,17 +4577,17 @@
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>Forretningskonsulent</t>
+          <t>AI Product Owner</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>Bankdata</t>
+          <t>Novo Nordisk</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>Silkeborg, Central Denmark Region, Denmark</t>
+          <t>Ballerup Municipality, Capital Region of Denmark, Denmark</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -4605,7 +4605,7 @@
       </c>
       <c r="H65" s="3" t="inlineStr">
         <is>
-          <t>This is a business/risk consultant role focusing on regulatory compliance, credit risk models, and SAS/SQL data analysis rather than a hands-on Generative AI or LLM specialization. While the candidate brings strong banking domain experience and Python skills, the core responsibilities do not align with his advanced GenAI and agentic AI expertise.</t>
+          <t>This is an AI Product Owner role focused on manufacturing and supply chain systems, which requires product management and stakeholder alignment rather than hands-on GenAI/LLM development. The candidate is a technical Lead Data Scientist specializing in hands-on LangChain/LangGraph and agentic workflows, presenting a significant mismatch in role function and domain expertise.</t>
         </is>
       </c>
       <c r="I65" s="3" t="inlineStr">
@@ -4630,7 +4630,7 @@
       </c>
       <c r="M65" s="6" t="inlineStr">
         <is>
-          <t>https://dk.linkedin.com/jobs/view/forretningskonsulent-at-bankdata-4448894922?position=22&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=o%2BWOTBX123ODc%2FiV7%2B9GIw%3D%3D</t>
+          <t>https://dk.linkedin.com/jobs/view/ai-product-owner-at-novo-nordisk-4457258669?position=24&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=s56Z90FxaVSj7XKQs6qQuA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -4640,17 +4640,17 @@
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>Developer</t>
+          <t>Forretningskonsulent</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>MAP</t>
+          <t>Bankdata</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>Copenhagen, Capital Region of Denmark, Denmark</t>
+          <t>Silkeborg, Central Denmark Region, Denmark</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -4668,7 +4668,7 @@
       </c>
       <c r="H66" s="3" t="inlineStr">
         <is>
-          <t>The role is primarily a backend/full-stack software engineering position requiring .NET/C# and Vue/TypeScript, which does not align with the candidate's core Data Science and GenAI specialization. While there are passing mentions of Python and agentic AI as nice-to-haves, the job is fundamentally a software development role rather than an advanced GenAI/LLM specialist position.</t>
+          <t>This is a business/risk consultant role focusing on regulatory compliance, credit risk models, and SAS/SQL data analysis rather than a hands-on Generative AI or LLM specialization. While the candidate brings strong banking domain experience and Python skills, the core responsibilities do not align with his advanced GenAI and agentic AI expertise.</t>
         </is>
       </c>
       <c r="I66" s="3" t="inlineStr">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="M66" s="6" t="inlineStr">
         <is>
-          <t>https://dk.linkedin.com/jobs/view/developer-at-map-4459176960?position=23&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=YgE2RztI4uaVgk5SXXlkQw%3D%3D</t>
+          <t>https://dk.linkedin.com/jobs/view/forretningskonsulent-at-bankdata-4448894922?position=22&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=o%2BWOTBX123ODc%2FiV7%2B9GIw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -4703,17 +4703,17 @@
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>AI Innovation Specialist - Renewable Energy Solutions</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>Vestas</t>
+          <t>MAP</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>Aarhus Municipality, Central Denmark Region, Denmark</t>
+          <t>Copenhagen, Capital Region of Denmark, Denmark</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="H67" s="3" t="inlineStr">
         <is>
-          <t>The candidate has strong technical skills in Python and machine learning, but this role focuses heavily on industrial AI, computer vision, sensor data, and predictive maintenance in the renewable energy sector rather than the candidate's core specialization in LLMs, RAG, and agentic workflows. Furthermore, the seniority alignment is slightly mismatched as the role asks for 4+ years while the candidate is a senior/lead with 10 years of experience.</t>
+          <t>The role is primarily a backend/full-stack software engineering position requiring .NET/C# and Vue/TypeScript, which does not align with the candidate's core Data Science and GenAI specialization. While there are passing mentions of Python and agentic AI as nice-to-haves, the job is fundamentally a software development role rather than an advanced GenAI/LLM specialist position.</t>
         </is>
       </c>
       <c r="I67" s="3" t="inlineStr">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="M67" s="6" t="inlineStr">
         <is>
-          <t>https://dk.linkedin.com/jobs/view/ai-innovation-specialist-renewable-energy-solutions-at-vestas-4459358646?position=4&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=x6uemge6vMfQH6CFPei6kw%3D%3D</t>
+          <t>https://dk.linkedin.com/jobs/view/developer-at-map-4459176960?position=23&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=YgE2RztI4uaVgk5SXXlkQw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -4766,22 +4766,22 @@
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>Data Scientist (Remote)</t>
+          <t>AI Innovation Specialist - Renewable Energy Solutions</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>Hire Feed</t>
+          <t>Vestas</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>Aarhus Municipality, Central Denmark Region, Denmark</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F68" s="7" t="n">
@@ -4794,7 +4794,7 @@
       </c>
       <c r="H68" s="3" t="inlineStr">
         <is>
-          <t>This role is a generic classical machine learning position focused on predictive modeling, Python, and scikit-learn, with no mention of Generative AI, LLMs, RAG, or agentic systems that form the core of the candidate's expertise. While the candidate has the necessary background to perform the work, it underutilizes his specialized GenAI skillset and matches the scoring guidance for a weaker classical ML/statistics fit.</t>
+          <t>The candidate has strong technical skills in Python and machine learning, but this role focuses heavily on industrial AI, computer vision, sensor data, and predictive maintenance in the renewable energy sector rather than the candidate's core specialization in LLMs, RAG, and agentic workflows. Furthermore, the seniority alignment is slightly mismatched as the role asks for 4+ years while the candidate is a senior/lead with 10 years of experience.</t>
         </is>
       </c>
       <c r="I68" s="3" t="inlineStr">
@@ -4819,7 +4819,7 @@
       </c>
       <c r="M68" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/data-scientist-remote-at-hire-feed-4459652348?position=8&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=eN2UeQevFS%2FiNl5F%2FHqH8A%3D%3D</t>
+          <t>https://dk.linkedin.com/jobs/view/ai-innovation-specialist-renewable-energy-solutions-at-vestas-4459358646?position=4&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=x6uemge6vMfQH6CFPei6kw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -4829,12 +4829,12 @@
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>Machine Learning (AI) Engineer (Hybrid)</t>
+          <t>Data Scientist (Remote)</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>Quik Hire Staffing</t>
+          <t>Hire Feed</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="H69" s="3" t="inlineStr">
         <is>
-          <t>The role is focused heavily on classical Machine Learning, MLOps, deep learning frameworks (TensorFlow, PyTorch), and model training rather than the candidate's core specialization in Generative AI, LLMs, RAG, and agentic systems. Seniority aligns well, but the technical domain mismatch makes this a weaker fit.</t>
+          <t>This role is a generic classical machine learning position focused on predictive modeling, Python, and scikit-learn, with no mention of Generative AI, LLMs, RAG, or agentic systems that form the core of the candidate's expertise. While the candidate has the necessary background to perform the work, it underutilizes his specialized GenAI skillset and matches the scoring guidance for a weaker classical ML/statistics fit.</t>
         </is>
       </c>
       <c r="I69" s="3" t="inlineStr">
@@ -4882,7 +4882,7 @@
       </c>
       <c r="M69" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/machine-learning-ai-engineer-hybrid-at-quik-hire-staffing-4459649596?position=5&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=sbTD%2BYZZjPOfeagKS2Yixw%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/data-scientist-remote-at-hire-feed-4459652348?position=8&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=eN2UeQevFS%2FiNl5F%2FHqH8A%3D%3D</t>
         </is>
       </c>
     </row>
@@ -4892,17 +4892,17 @@
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>Consultant Data &amp; AI</t>
+          <t>Machine Learning (AI) Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>ITDS</t>
+          <t>Quik Hire Staffing</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>Amsterdam, North Holland, Netherlands</t>
+          <t>United Arab Emirates</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -4920,7 +4920,7 @@
       </c>
       <c r="H70" s="3" t="inlineStr">
         <is>
-          <t>The role is a generalist data and AI consulting position focusing heavily on data management, business analysis, and governance within the financial sector, rather than a specialized GenAI/LLM engineering role. Additionally, it requires Dutch language proficiency and a consultant/analyst profile that is a mismatch for the candidate's senior GenAI technical expertise.</t>
+          <t>The role is focused heavily on classical Machine Learning, MLOps, deep learning frameworks (TensorFlow, PyTorch), and model training rather than the candidate's core specialization in Generative AI, LLMs, RAG, and agentic systems. Seniority aligns well, but the technical domain mismatch makes this a weaker fit.</t>
         </is>
       </c>
       <c r="I70" s="3" t="inlineStr">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="M70" s="6" t="inlineStr">
         <is>
-          <t>https://nl.linkedin.com/jobs/view/consultant-data-ai-at-itds-4458351898?position=19&amp;pageNum=0&amp;refId=oiBIn1Czflg0JjZjH5z0Lg%3D%3D&amp;trackingId=1Zr9TFJHo0JFjEQpwgyXZg%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/machine-learning-ai-engineer-hybrid-at-quik-hire-staffing-4459649596?position=5&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=sbTD%2BYZZjPOfeagKS2Yixw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -4955,17 +4955,17 @@
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Consultant Data &amp; AI</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>Rubicon Cloud Advisor</t>
+          <t>ITDS</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>The Randstad, Netherlands</t>
+          <t>Amsterdam, North Holland, Netherlands</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -4983,7 +4983,7 @@
       </c>
       <c r="H71" s="3" t="inlineStr">
         <is>
-          <t>The role is for an MLOps Engineer focusing on ML infrastructure, pipelines, and deployment using Databricks and MLflow, which touches some of the candidate's supporting tech stack but misses his core Generative AI, LLM, and agentic specialization. Additionally, the job posting requires Dutch language proficiency, though language fit was not factored into the penalty per instructions.</t>
+          <t>The role is a generalist data and AI consulting position focusing heavily on data management, business analysis, and governance within the financial sector, rather than a specialized GenAI/LLM engineering role. Additionally, it requires Dutch language proficiency and a consultant/analyst profile that is a mismatch for the candidate's senior GenAI technical expertise.</t>
         </is>
       </c>
       <c r="I71" s="3" t="inlineStr">
@@ -5008,7 +5008,7 @@
       </c>
       <c r="M71" s="6" t="inlineStr">
         <is>
-          <t>https://nl.linkedin.com/jobs/view/mlops-engineer-at-rubicon-cloud-advisor-4450093837?position=15&amp;pageNum=0&amp;refId=oiBIn1Czflg0JjZjH5z0Lg%3D%3D&amp;trackingId=bnH0HGZbT4T4t%2FkIxlYWZQ%3D%3D</t>
+          <t>https://nl.linkedin.com/jobs/view/consultant-data-ai-at-itds-4458351898?position=19&amp;pageNum=0&amp;refId=oiBIn1Czflg0JjZjH5z0Lg%3D%3D&amp;trackingId=1Zr9TFJHo0JFjEQpwgyXZg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -5018,22 +5018,22 @@
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>Data migration Lead</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Rubicon Cloud Advisor</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>Dubai, Dubai, United Arab Emirates</t>
+          <t>The Randstad, Netherlands</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F72" s="7" t="n">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="H72" s="3" t="inlineStr">
         <is>
-          <t>The role is titled Data Migration Lead and is structured as a Sr Architect position focused on data engineering, Databricks pipelines, Delta Lake, and enterprise analytics architectures rather than hands-on GenAI, LLMs, or agentic applications. While it mentions Databricks and AI components (like Mosaic AI), it is primarily a data architecture and engineering role rather than a GenAI specialist position, creating a significant domain and seniority mismatch.</t>
+          <t>The role is for an MLOps Engineer focusing on ML infrastructure, pipelines, and deployment using Databricks and MLflow, which touches some of the candidate's supporting tech stack but misses his core Generative AI, LLM, and agentic specialization. Additionally, the job posting requires Dutch language proficiency, though language fit was not factored into the penalty per instructions.</t>
         </is>
       </c>
       <c r="I72" s="3" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="M72" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/data-migration-lead-at-cognizant-4459410800?position=5&amp;pageNum=0&amp;refId=umynRMWB8laV9lcrAC5yvg%3D%3D&amp;trackingId=zF3RnOXbiFVhroKlN1ve%2FQ%3D%3D</t>
+          <t>https://nl.linkedin.com/jobs/view/mlops-engineer-at-rubicon-cloud-advisor-4450093837?position=15&amp;pageNum=0&amp;refId=oiBIn1Czflg0JjZjH5z0Lg%3D%3D&amp;trackingId=bnH0HGZbT4T4t%2FkIxlYWZQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -5081,26 +5081,26 @@
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>Decision Scientist, Marketing Modelling Intelligence, Marketing DSA</t>
+          <t>Data migration Lead</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>Vinted</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>Berlin, Berlin, Germany</t>
+          <t>Dubai, Dubai, United Arab Emirates</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="F73" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G73" s="8" t="inlineStr">
         <is>
@@ -5109,12 +5109,12 @@
       </c>
       <c r="H73" s="3" t="inlineStr">
         <is>
-          <t>This is a classical marketing analytics and econometrics role focused on Bayesian Media Mix Modeling and ROI measurement with no mention of Generative AI, LLMs, or agentic systems. Furthermore, the candidate is a Lead Data Scientist with 10+ years of experience, making the 2-4 year experience requirement a significant seniority mismatch.</t>
+          <t>The role is titled Data Migration Lead and is structured as a Sr Architect position focused on data engineering, Databricks pipelines, Delta Lake, and enterprise analytics architectures rather than hands-on GenAI, LLMs, or agentic applications. While it mentions Databricks and AI components (like Mosaic AI), it is primarily a data architecture and engineering role rather than a GenAI specialist position, creating a significant domain and seniority mismatch.</t>
         </is>
       </c>
       <c r="I73" s="3" t="inlineStr">
         <is>
-          <t>Yes - German required (see JD for exact level)</t>
+          <t>Not stated in JD</t>
         </is>
       </c>
       <c r="J73" s="3" t="inlineStr">
@@ -5134,7 +5134,7 @@
       </c>
       <c r="M73" s="6" t="inlineStr">
         <is>
-          <t>https://de.linkedin.com/jobs/view/decision-scientist-marketing-modelling-intelligence-marketing-dsa-at-vinted-4431734157?position=23&amp;pageNum=0&amp;refId=T%2F0KkBXL%2Fl%2B5Iv5tUGTY7Q%3D%3D&amp;trackingId=ym8Uxiee8AvGv52T5S0EVQ%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/data-migration-lead-at-cognizant-4459410800?position=5&amp;pageNum=0&amp;refId=umynRMWB8laV9lcrAC5yvg%3D%3D&amp;trackingId=zF3RnOXbiFVhroKlN1ve%2FQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -5144,17 +5144,17 @@
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>Data Analyst / Data Science Specialist (m/w/d)</t>
+          <t>Decision Scientist, Marketing Modelling Intelligence, Marketing DSA</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>Molkerei Gropper GmbH &amp; Co. KG</t>
+          <t>Vinted</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>Bissingen, Bavaria, Germany</t>
+          <t>Berlin, Berlin, Germany</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -5172,7 +5172,7 @@
       </c>
       <c r="H74" s="3" t="inlineStr">
         <is>
-          <t>This role is focused primarily on traditional Data Warehousing, BI, ETL, and reporting with SAP systems, where AI is merely a passing mention of interest rather than a core focus. It is a significant mismatch for the candidate's advanced Generative AI, LLM, and agentic specialization.</t>
+          <t>This is a classical marketing analytics and econometrics role focused on Bayesian Media Mix Modeling and ROI measurement with no mention of Generative AI, LLMs, or agentic systems. Furthermore, the candidate is a Lead Data Scientist with 10+ years of experience, making the 2-4 year experience requirement a significant seniority mismatch.</t>
         </is>
       </c>
       <c r="I74" s="3" t="inlineStr">
@@ -5197,7 +5197,7 @@
       </c>
       <c r="M74" s="6" t="inlineStr">
         <is>
-          <t>https://de.linkedin.com/jobs/view/data-analyst-data-science-specialist-m-w-d-at-molkerei-gropper-gmbh-co-kg-4459396175?position=16&amp;pageNum=0&amp;refId=T%2F0KkBXL%2Fl%2B5Iv5tUGTY7Q%3D%3D&amp;trackingId=hDs2N%2Ft3sDgczR%2Fh%2Biow4g%3D%3D</t>
+          <t>https://de.linkedin.com/jobs/view/decision-scientist-marketing-modelling-intelligence-marketing-dsa-at-vinted-4431734157?position=23&amp;pageNum=0&amp;refId=T%2F0KkBXL%2Fl%2B5Iv5tUGTY7Q%3D%3D&amp;trackingId=ym8Uxiee8AvGv52T5S0EVQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -5207,17 +5207,17 @@
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>Specialist Data Science</t>
+          <t>Data Analyst / Data Science Specialist (m/w/d)</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>HDI Group</t>
+          <t>Molkerei Gropper GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>Hannover, Lower Saxony, Germany</t>
+          <t>Bissingen, Bavaria, Germany</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
@@ -5235,12 +5235,12 @@
       </c>
       <c r="H75" s="3" t="inlineStr">
         <is>
-          <t>This role focuses heavily on data engineering, analytics, and R-based pricing tools within the insurance domain, offering only passing alignment with classical data science rather than the candidate's core GenAI, LLMs, and agentic AI specialization.</t>
+          <t>This role is focused primarily on traditional Data Warehousing, BI, ETL, and reporting with SAP systems, where AI is merely a passing mention of interest rather than a core focus. It is a significant mismatch for the candidate's advanced Generative AI, LLM, and agentic specialization.</t>
         </is>
       </c>
       <c r="I75" s="3" t="inlineStr">
         <is>
-          <t>Not stated in JD</t>
+          <t>Yes - German required (see JD for exact level)</t>
         </is>
       </c>
       <c r="J75" s="3" t="inlineStr">
@@ -5260,7 +5260,7 @@
       </c>
       <c r="M75" s="6" t="inlineStr">
         <is>
-          <t>https://de.linkedin.com/jobs/view/specialist-data-science-at-hdi-group-4449488553?position=9&amp;pageNum=0&amp;refId=T%2F0KkBXL%2Fl%2B5Iv5tUGTY7Q%3D%3D&amp;trackingId=4kEwk2%2BQdqX%2FDjmyxZ2xyA%3D%3D</t>
+          <t>https://de.linkedin.com/jobs/view/data-analyst-data-science-specialist-m-w-d-at-molkerei-gropper-gmbh-co-kg-4459396175?position=16&amp;pageNum=0&amp;refId=T%2F0KkBXL%2Fl%2B5Iv5tUGTY7Q%3D%3D&amp;trackingId=hDs2N%2Ft3sDgczR%2Fh%2Biow4g%3D%3D</t>
         </is>
       </c>
     </row>
@@ -5270,17 +5270,17 @@
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>Data Scientist (m/w/d) für analytisches CRM und datengestützte Potenziale</t>
+          <t>Specialist Data Science</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>R+V Versicherung</t>
+          <t>HDI Group</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>Wiesbaden, Hesse, Germany</t>
+          <t>Hannover, Lower Saxony, Germany</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -5298,12 +5298,12 @@
       </c>
       <c r="H76" s="3" t="inlineStr">
         <is>
-          <t>This role focuses on analytical CRM, customer segmentation, and rule-based next-best-offer systems using SQL and traditional data methods, offering only passing mention of AI approaches. It lacks the core Generative AI, LLM, and agentic specialization that defines the candidate's profile.</t>
+          <t>This role focuses heavily on data engineering, analytics, and R-based pricing tools within the insurance domain, offering only passing alignment with classical data science rather than the candidate's core GenAI, LLMs, and agentic AI specialization.</t>
         </is>
       </c>
       <c r="I76" s="3" t="inlineStr">
         <is>
-          <t>Yes - fluent/C1+ German explicitly required</t>
+          <t>Not stated in JD</t>
         </is>
       </c>
       <c r="J76" s="3" t="inlineStr">
@@ -5323,7 +5323,7 @@
       </c>
       <c r="M76" s="6" t="inlineStr">
         <is>
-          <t>https://de.linkedin.com/jobs/view/data-scientist-m-w-d-f%C3%BCr-analytisches-crm-und-datengest%C3%BCtzte-potenziale-at-r%2Bv-versicherung-4446660524?position=7&amp;pageNum=0&amp;refId=T%2F0KkBXL%2Fl%2B5Iv5tUGTY7Q%3D%3D&amp;trackingId=na3WACzOriMr43dXtkckXw%3D%3D</t>
+          <t>https://de.linkedin.com/jobs/view/specialist-data-science-at-hdi-group-4449488553?position=9&amp;pageNum=0&amp;refId=T%2F0KkBXL%2Fl%2B5Iv5tUGTY7Q%3D%3D&amp;trackingId=4kEwk2%2BQdqX%2FDjmyxZ2xyA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -5333,17 +5333,17 @@
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>Senior Data Scientist (m/f/d)</t>
+          <t>Data Scientist (m/w/d) für analytisches CRM und datengestützte Potenziale</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>AutoScout24</t>
+          <t>R+V Versicherung</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>Munich, Bavaria, Germany</t>
+          <t>Wiesbaden, Hesse, Germany</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -5361,12 +5361,12 @@
       </c>
       <c r="H77" s="3" t="inlineStr">
         <is>
-          <t>[FALLBACK SCORER - Gemini call failed] Matched 2 core GenAI term(s) via keyword search. Verify manually; this is a degraded-mode score.</t>
+          <t>This role focuses on analytical CRM, customer segmentation, and rule-based next-best-offer systems using SQL and traditional data methods, offering only passing mention of AI approaches. It lacks the core Generative AI, LLM, and agentic specialization that defines the candidate's profile.</t>
         </is>
       </c>
       <c r="I77" s="3" t="inlineStr">
         <is>
-          <t>Not stated in JD</t>
+          <t>Yes - fluent/C1+ German explicitly required</t>
         </is>
       </c>
       <c r="J77" s="3" t="inlineStr">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="M77" s="6" t="inlineStr">
         <is>
-          <t>https://de.linkedin.com/jobs/view/senior-data-scientist-m-f-d-at-autoscout24-4432214339?position=11&amp;pageNum=0&amp;refId=T%2F0KkBXL%2Fl%2B5Iv5tUGTY7Q%3D%3D&amp;trackingId=7SGOVxV%2FwAFkUhW1fBv2EA%3D%3D</t>
+          <t>https://de.linkedin.com/jobs/view/data-scientist-m-w-d-f%C3%BCr-analytisches-crm-und-datengest%C3%BCtzte-potenziale-at-r%2Bv-versicherung-4446660524?position=7&amp;pageNum=0&amp;refId=T%2F0KkBXL%2Fl%2B5Iv5tUGTY7Q%3D%3D&amp;trackingId=na3WACzOriMr43dXtkckXw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -5396,17 +5396,17 @@
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>Data Analyst / Scientist (m/w/d)</t>
+          <t>Senior Data Scientist (m/f/d)</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>Dr. Wolff Group</t>
+          <t>AutoScout24</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>Bielefeld, North Rhine-Westphalia, Germany</t>
+          <t>Munich, Bavaria, Germany</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -5429,7 +5429,7 @@
       </c>
       <c r="I78" s="3" t="inlineStr">
         <is>
-          <t>Yes - German required (see JD for exact level)</t>
+          <t>Not stated in JD</t>
         </is>
       </c>
       <c r="J78" s="3" t="inlineStr">
@@ -5449,7 +5449,7 @@
       </c>
       <c r="M78" s="6" t="inlineStr">
         <is>
-          <t>https://de.linkedin.com/jobs/view/data-analyst-scientist-m-w-d-at-dr-wolff-group-4459323885?position=2&amp;pageNum=0&amp;refId=T%2F0KkBXL%2Fl%2B5Iv5tUGTY7Q%3D%3D&amp;trackingId=fnXlAvETsQ4TzuiWcW6AWA%3D%3D</t>
+          <t>https://de.linkedin.com/jobs/view/senior-data-scientist-m-f-d-at-autoscout24-4432214339?position=11&amp;pageNum=0&amp;refId=T%2F0KkBXL%2Fl%2B5Iv5tUGTY7Q%3D%3D&amp;trackingId=7SGOVxV%2FwAFkUhW1fBv2EA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -5459,17 +5459,17 @@
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>Data Scientist - AI Search &amp; Ranking</t>
+          <t>Data Analyst / Scientist (m/w/d)</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>trivago</t>
+          <t>Dr. Wolff Group</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>Düsseldorf, North Rhine-Westphalia, Germany</t>
+          <t>Bielefeld, North Rhine-Westphalia, Germany</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
@@ -5492,7 +5492,7 @@
       </c>
       <c r="I79" s="3" t="inlineStr">
         <is>
-          <t>Not stated in JD</t>
+          <t>Yes - German required (see JD for exact level)</t>
         </is>
       </c>
       <c r="J79" s="3" t="inlineStr">
@@ -5512,7 +5512,7 @@
       </c>
       <c r="M79" s="6" t="inlineStr">
         <is>
-          <t>https://de.linkedin.com/jobs/view/data-scientist-ai-search-ranking-at-trivago-4451695166?position=3&amp;pageNum=0&amp;refId=T%2F0KkBXL%2Fl%2B5Iv5tUGTY7Q%3D%3D&amp;trackingId=653eapm3ns02Vx9zaTVbNw%3D%3D</t>
+          <t>https://de.linkedin.com/jobs/view/data-analyst-scientist-m-w-d-at-dr-wolff-group-4459323885?position=2&amp;pageNum=0&amp;refId=T%2F0KkBXL%2Fl%2B5Iv5tUGTY7Q%3D%3D&amp;trackingId=fnXlAvETsQ4TzuiWcW6AWA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -5522,17 +5522,17 @@
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>Senior Manager, Digital Forensics &amp; eDiscovery</t>
+          <t>Data Scientist - AI Search &amp; Ranking</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>Robert Walters</t>
+          <t>trivago</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>Dubai, Dubai, United Arab Emirates</t>
+          <t>Düsseldorf, North Rhine-Westphalia, Germany</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -5550,7 +5550,7 @@
       </c>
       <c r="H80" s="3" t="inlineStr">
         <is>
-          <t>The role is focused heavily on digital forensics, eDiscovery, and regulatory investigations, which does not align with the candidate's core specialization in Generative AI, LangGraph, and agentic LLM pipelines. While it mentions emerging AI technologies and LLMs as a secondary component, the candidate's strong GenAI background is largely mismatched with the core forensic and eDiscovery tech stack.</t>
+          <t>[FALLBACK SCORER - Gemini call failed] Matched 2 core GenAI term(s) via keyword search. Verify manually; this is a degraded-mode score.</t>
         </is>
       </c>
       <c r="I80" s="3" t="inlineStr">
@@ -5575,7 +5575,7 @@
       </c>
       <c r="M80" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/senior-manager-digital-forensics-ediscovery-at-robert-walters-4457258106?position=26&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=nugpWYWcIAXvX9xB18JHdw%3D%3D</t>
+          <t>https://de.linkedin.com/jobs/view/data-scientist-ai-search-ranking-at-trivago-4451695166?position=3&amp;pageNum=0&amp;refId=T%2F0KkBXL%2Fl%2B5Iv5tUGTY7Q%3D%3D&amp;trackingId=653eapm3ns02Vx9zaTVbNw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -5585,12 +5585,12 @@
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>Business Analyst - instashop</t>
+          <t>Senior Manager, Digital Forensics &amp; eDiscovery</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>talabat</t>
+          <t>Robert Walters</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
@@ -5613,7 +5613,7 @@
       </c>
       <c r="H81" s="3" t="inlineStr">
         <is>
-          <t>This is a Business Analyst role focused on traditional commercial analytics, SQL, and BI reporting, with only passing mentions of using generative AI tools as productivity boosters. It represents a significant mismatch in domain and seniority compared to the candidate's core specialization as a Lead GenAI/LLM/Agentic AI specialist with 10+ years of experience.</t>
+          <t>The role is focused heavily on digital forensics, eDiscovery, and regulatory investigations, which does not align with the candidate's core specialization in Generative AI, LangGraph, and agentic LLM pipelines. While it mentions emerging AI technologies and LLMs as a secondary component, the candidate's strong GenAI background is largely mismatched with the core forensic and eDiscovery tech stack.</t>
         </is>
       </c>
       <c r="I81" s="3" t="inlineStr">
@@ -5638,7 +5638,7 @@
       </c>
       <c r="M81" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/business-analyst-instashop-at-talabat-4447352935?position=6&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=gGEviUFke%2FcNigxE2hYK8w%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/senior-manager-digital-forensics-ediscovery-at-robert-walters-4457258106?position=26&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=nugpWYWcIAXvX9xB18JHdw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -5648,17 +5648,17 @@
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>Senior MLOps/Data Engineer</t>
+          <t>Business Analyst - instashop</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>TomTom</t>
+          <t>talabat</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>Amsterdam, North Holland, Netherlands</t>
+          <t>Dubai, Dubai, United Arab Emirates</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="H82" s="3" t="inlineStr">
         <is>
-          <t>This is a Senior MLOps/Data Engineer role focusing on PySpark, Databricks, and pipeline orchestration rather than Generative AI or LLMs. While the candidate has Azure and Python experience, the core technical requirements do not align with his GenAI and agentic specialization.</t>
+          <t>This is a Business Analyst role focused on traditional commercial analytics, SQL, and BI reporting, with only passing mentions of using generative AI tools as productivity boosters. It represents a significant mismatch in domain and seniority compared to the candidate's core specialization as a Lead GenAI/LLM/Agentic AI specialist with 10+ years of experience.</t>
         </is>
       </c>
       <c r="I82" s="3" t="inlineStr">
@@ -5701,7 +5701,7 @@
       </c>
       <c r="M82" s="6" t="inlineStr">
         <is>
-          <t>https://nl.linkedin.com/jobs/view/senior-mlops-data-engineer-at-tomtom-4448554856?position=23&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=SHR8gYATTGX6qegw6hmLAw%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/business-analyst-instashop-at-talabat-4447352935?position=6&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=gGEviUFke%2FcNigxE2hYK8w%3D%3D</t>
         </is>
       </c>
     </row>
@@ -5711,12 +5711,12 @@
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>Decision Scientist, Marketing Modelling Intelligence, Marketing DSA</t>
+          <t>Senior MLOps/Data Engineer</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>Vinted</t>
+          <t>TomTom</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr">
@@ -5739,7 +5739,7 @@
       </c>
       <c r="H83" s="3" t="inlineStr">
         <is>
-          <t>This is a marketing analytics and econometric modeling role focused on Bayesian Media Mix Models, which only touches classical statistics and regression without any GenAI, LLMs, or agentic systems. Furthermore, the seniority expectation (2-4 years) is a major mismatch for a candidate with 10+ years of experience.</t>
+          <t>This is a Senior MLOps/Data Engineer role focusing on PySpark, Databricks, and pipeline orchestration rather than Generative AI or LLMs. While the candidate has Azure and Python experience, the core technical requirements do not align with his GenAI and agentic specialization.</t>
         </is>
       </c>
       <c r="I83" s="3" t="inlineStr">
@@ -5764,7 +5764,7 @@
       </c>
       <c r="M83" s="6" t="inlineStr">
         <is>
-          <t>https://nl.linkedin.com/jobs/view/decision-scientist-marketing-modelling-intelligence-marketing-dsa-at-vinted-4431724987?position=12&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=CGELWLumu99gkHZTfq3gCQ%3D%3D</t>
+          <t>https://nl.linkedin.com/jobs/view/senior-mlops-data-engineer-at-tomtom-4448554856?position=23&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=SHR8gYATTGX6qegw6hmLAw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -5774,17 +5774,17 @@
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>Lead Data Science</t>
+          <t>Decision Scientist, Marketing Modelling Intelligence, Marketing DSA</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>Zonneplan</t>
+          <t>Vinted</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>Zwolle, Overijssel, Netherlands</t>
+          <t>Amsterdam, North Holland, Netherlands</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -5802,7 +5802,7 @@
       </c>
       <c r="H84" s="3" t="inlineStr">
         <is>
-          <t>The role is focused heavily on classical time-series forecasting, energy optimization, and MLOps for trading systems rather than Generative AI, LLMs, or agentic workflows. While the candidate's seniority as a Lead matches well, the lack of core GenAI focus makes this a weak technical fit.</t>
+          <t>This is a marketing analytics and econometric modeling role focused on Bayesian Media Mix Models, which only touches classical statistics and regression without any GenAI, LLMs, or agentic systems. Furthermore, the seniority expectation (2-4 years) is a major mismatch for a candidate with 10+ years of experience.</t>
         </is>
       </c>
       <c r="I84" s="3" t="inlineStr">
@@ -5827,7 +5827,7 @@
       </c>
       <c r="M84" s="6" t="inlineStr">
         <is>
-          <t>https://nl.linkedin.com/jobs/view/lead-data-science-at-zonneplan-4414158731?position=8&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=1yTKWUbJDbOf0JWJnBF0EQ%3D%3D</t>
+          <t>https://nl.linkedin.com/jobs/view/decision-scientist-marketing-modelling-intelligence-marketing-dsa-at-vinted-4431724987?position=12&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=CGELWLumu99gkHZTfq3gCQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -5837,17 +5837,17 @@
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Lead Data Science</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>Confidential</t>
+          <t>Zonneplan</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>Abu Dhabi Emirate, United Arab Emirates</t>
+          <t>Zwolle, Overijssel, Netherlands</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
@@ -5865,7 +5865,7 @@
       </c>
       <c r="H85" s="3" t="inlineStr">
         <is>
-          <t>This is a Data Engineering role focusing on cloud pipelines, lakehouses, streaming, and data warehousing rather than a GenAI or LLM specialization role. While it mentions building datasets and vector pipelines for AI, the core function is infrastructure and data engineering rather than the candidate's core expertise as a Lead Data Scientist in GenAI and agentic workflows.</t>
+          <t>The role is focused heavily on classical time-series forecasting, energy optimization, and MLOps for trading systems rather than Generative AI, LLMs, or agentic workflows. While the candidate's seniority as a Lead matches well, the lack of core GenAI focus makes this a weak technical fit.</t>
         </is>
       </c>
       <c r="I85" s="3" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="M85" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/data-engineer-at-confidential-4457913992?position=27&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=0E%2Bet6hk0hz6AFQRQUNpjg%3D%3D</t>
+          <t>https://nl.linkedin.com/jobs/view/lead-data-science-at-zonneplan-4414158731?position=8&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=1yTKWUbJDbOf0JWJnBF0EQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -5900,22 +5900,22 @@
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>Head of Data Science</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>Jex Recruitment | Connecting top talent with leading companies</t>
+          <t>Confidential</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>Abu Dhabi, Abu Dhabi Emirate, United Arab Emirates</t>
+          <t>Abu Dhabi Emirate, United Arab Emirates</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F86" s="7" t="n">
@@ -5928,7 +5928,7 @@
       </c>
       <c r="H86" s="3" t="inlineStr">
         <is>
-          <t>The role requires executive leadership (Head of Data Science) focused on managing teams, strategy, and classical banking use cases rather than hands-on technical GenAI or agentic AI work. This is a significant seniority and role-type mismatch for a Lead Data Scientist specializing in LLMs and RAG.</t>
+          <t>This is a Data Engineering role focusing on cloud pipelines, lakehouses, streaming, and data warehousing rather than a GenAI or LLM specialization role. While it mentions building datasets and vector pipelines for AI, the core function is infrastructure and data engineering rather than the candidate's core expertise as a Lead Data Scientist in GenAI and agentic workflows.</t>
         </is>
       </c>
       <c r="I86" s="3" t="inlineStr">
@@ -5938,7 +5938,7 @@
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
-          <t>Possible - relocation support mentioned, visa not explicit</t>
+          <t>Not stated in JD</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
@@ -5953,7 +5953,7 @@
       </c>
       <c r="M86" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/head-of-data-science-at-jex-recruitment-connecting-top-talent-with-leading-companies-4458343957?position=23&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=SiTMdQz8r7KHa1LqknvQjg%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/data-engineer-at-confidential-4457913992?position=27&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=0E%2Bet6hk0hz6AFQRQUNpjg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -5963,17 +5963,17 @@
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>Data Scientist Delivery Domain</t>
+          <t>Head of Data Science</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>Coolblue</t>
+          <t>Jex Recruitment | Connecting top talent with leading companies</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>Rotterdam, South Holland, Netherlands</t>
+          <t>Abu Dhabi, Abu Dhabi Emirate, United Arab Emirates</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
@@ -5991,7 +5991,7 @@
       </c>
       <c r="H87" s="3" t="inlineStr">
         <is>
-          <t>This is a classical forecasting and operations research role focusing on delivery and installation planning using Python and SQL, with no mention of Generative AI, LLMs, or agentic systems which are the candidate's core specialization. Although the candidate has background in traditional machine learning that overlaps slightly, it represents a weak fit for his current profile.</t>
+          <t>The role requires executive leadership (Head of Data Science) focused on managing teams, strategy, and classical banking use cases rather than hands-on technical GenAI or agentic AI work. This is a significant seniority and role-type mismatch for a Lead Data Scientist specializing in LLMs and RAG.</t>
         </is>
       </c>
       <c r="I87" s="3" t="inlineStr">
@@ -6001,7 +6001,7 @@
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
-          <t>Not stated in JD</t>
+          <t>Possible - relocation support mentioned, visa not explicit</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
@@ -6016,7 +6016,7 @@
       </c>
       <c r="M87" s="6" t="inlineStr">
         <is>
-          <t>https://nl.linkedin.com/jobs/view/data-scientist-delivery-domain-at-coolblue-4459662808?position=3&amp;pageNum=0&amp;refId=oiBIn1Czflg0JjZjH5z0Lg%3D%3D&amp;trackingId=V2dKcwpv0YpijBJw41fQVg%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/head-of-data-science-at-jex-recruitment-connecting-top-talent-with-leading-companies-4458343957?position=23&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=SiTMdQz8r7KHa1LqknvQjg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -6026,17 +6026,17 @@
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>Lead Data Scientist, Revenue - Ads, Revenue</t>
+          <t>Data Scientist Delivery Domain</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>Vinted</t>
+          <t>Coolblue</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>Amsterdam, North Holland, Netherlands</t>
+          <t>Rotterdam, South Holland, Netherlands</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -6054,7 +6054,7 @@
       </c>
       <c r="H88" s="3" t="inlineStr">
         <is>
-          <t>This role focuses heavily on Ad Tech systems, auction mechanics, ads ranking, and real-time optimization, which falls outside the candidate's core specialization in Generative AI, LLMs, and agentic pipelines. While the seniority level (Lead Data Scientist) aligns, the domain mismatch makes it a weak technical fit.</t>
+          <t>This is a classical forecasting and operations research role focusing on delivery and installation planning using Python and SQL, with no mention of Generative AI, LLMs, or agentic systems which are the candidate's core specialization. Although the candidate has background in traditional machine learning that overlaps slightly, it represents a weak fit for his current profile.</t>
         </is>
       </c>
       <c r="I88" s="3" t="inlineStr">
@@ -6079,7 +6079,7 @@
       </c>
       <c r="M88" s="6" t="inlineStr">
         <is>
-          <t>https://nl.linkedin.com/jobs/view/lead-data-scientist-revenue-ads-revenue-at-vinted-4431741084?position=8&amp;pageNum=0&amp;refId=oiBIn1Czflg0JjZjH5z0Lg%3D%3D&amp;trackingId=ZcYNzhXf9h2M3%2FWEms9aMw%3D%3D</t>
+          <t>https://nl.linkedin.com/jobs/view/data-scientist-delivery-domain-at-coolblue-4459662808?position=3&amp;pageNum=0&amp;refId=oiBIn1Czflg0JjZjH5z0Lg%3D%3D&amp;trackingId=V2dKcwpv0YpijBJw41fQVg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -6089,17 +6089,17 @@
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>AI Product Manager</t>
+          <t>Lead Data Scientist, Revenue - Ads, Revenue</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>Auxo Talent</t>
+          <t>Vinted</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>Dubai, United Arab Emirates</t>
+          <t>Amsterdam, North Holland, Netherlands</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
@@ -6117,7 +6117,7 @@
       </c>
       <c r="H89" s="3" t="inlineStr">
         <is>
-          <t>This role is for an AI Product Manager rather than a hands-on technical Data Scientist or Generative AI engineer. While the candidate has deep technical expertise in GenAI and relevant fintech domain knowledge, he lacks the required professional product management background and roadmap-owning experience demanded by the position.</t>
+          <t>This role focuses heavily on Ad Tech systems, auction mechanics, ads ranking, and real-time optimization, which falls outside the candidate's core specialization in Generative AI, LLMs, and agentic pipelines. While the seniority level (Lead Data Scientist) aligns, the domain mismatch makes it a weak technical fit.</t>
         </is>
       </c>
       <c r="I89" s="3" t="inlineStr">
@@ -6142,7 +6142,7 @@
       </c>
       <c r="M89" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/ai-product-manager-at-auxo-talent-4458373508?position=12&amp;pageNum=0&amp;refId=50H6yCrEXIuhgr6eqEojNg%3D%3D&amp;trackingId=y5Nqep1ywbJPUkaTD9Vo3g%3D%3D</t>
+          <t>https://nl.linkedin.com/jobs/view/lead-data-scientist-revenue-ads-revenue-at-vinted-4431741084?position=8&amp;pageNum=0&amp;refId=oiBIn1Czflg0JjZjH5z0Lg%3D%3D&amp;trackingId=ZcYNzhXf9h2M3%2FWEms9aMw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -6152,12 +6152,12 @@
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>AI and Data Architect</t>
+          <t>AI Product Manager</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>Fundamentl</t>
+          <t>Auxo Talent</t>
         </is>
       </c>
       <c r="D90" s="3" t="inlineStr">
@@ -6180,17 +6180,17 @@
       </c>
       <c r="H90" s="3" t="inlineStr">
         <is>
-          <t>The role aligns well technically with the candidate's specialization in GenAI, Agentic AI, RAG, LangChain, LangGraph, and Azure tools. However, there is a severe seniority mismatch requiring 18+ years of experience for an AI and Data Architect role, whereas the candidate has 10 years of experience, making it a weak fit.</t>
+          <t>This role is for an AI Product Manager rather than a hands-on technical Data Scientist or Generative AI engineer. While the candidate has deep technical expertise in GenAI and relevant fintech domain knowledge, he lacks the required professional product management background and roadmap-owning experience demanded by the position.</t>
         </is>
       </c>
       <c r="I90" s="3" t="inlineStr">
         <is>
-          <t>No - English fluency stated as sufficient</t>
+          <t>Not stated in JD</t>
         </is>
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
-          <t>Yes - explicitly stated in JD</t>
+          <t>Not stated in JD</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
@@ -6205,7 +6205,7 @@
       </c>
       <c r="M90" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/ai-and-data-architect-at-fundamentl-4459845026?position=11&amp;pageNum=0&amp;refId=50H6yCrEXIuhgr6eqEojNg%3D%3D&amp;trackingId=Bd15IH4kHpjPXnejnC%2BLzw%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/ai-product-manager-at-auxo-talent-4458373508?position=12&amp;pageNum=0&amp;refId=50H6yCrEXIuhgr6eqEojNg%3D%3D&amp;trackingId=y5Nqep1ywbJPUkaTD9Vo3g%3D%3D</t>
         </is>
       </c>
     </row>
@@ -6215,26 +6215,26 @@
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI and Data Architect</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>Mammoet</t>
+          <t>Fundamentl</t>
         </is>
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>Schiedam, South Holland, Netherlands</t>
+          <t>Dubai, United Arab Emirates</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F91" s="7" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="G91" s="8" t="inlineStr">
         <is>
@@ -6243,17 +6243,17 @@
       </c>
       <c r="H91" s="3" t="inlineStr">
         <is>
-          <t>This is a Data Engineer role focused on cloud data platforms, ETL pipelines, and Data Vault modeling, which does not leverage the candidate's core specialization in Generative AI, LLMs, and agentic workflows. Additionally, the required 0-5 years of experience represents a seniority mismatch for a Lead Data Scientist with over 10 years of experience.</t>
+          <t>The role aligns well technically with the candidate's specialization in GenAI, Agentic AI, RAG, LangChain, LangGraph, and Azure tools. However, there is a severe seniority mismatch requiring 18+ years of experience for an AI and Data Architect role, whereas the candidate has 10 years of experience, making it a weak fit.</t>
         </is>
       </c>
       <c r="I91" s="3" t="inlineStr">
         <is>
-          <t>Not stated in JD</t>
+          <t>No - English fluency stated as sufficient</t>
         </is>
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
-          <t>Not stated in JD</t>
+          <t>Yes - explicitly stated in JD</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
@@ -6268,7 +6268,7 @@
       </c>
       <c r="M91" s="6" t="inlineStr">
         <is>
-          <t>https://nl.linkedin.com/jobs/view/data-engineer-at-mammoet-4459379074?position=24&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=vEO3k7c4HScCtKkTbNh8Xg%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/ai-and-data-architect-at-fundamentl-4459845026?position=11&amp;pageNum=0&amp;refId=50H6yCrEXIuhgr6eqEojNg%3D%3D&amp;trackingId=Bd15IH4kHpjPXnejnC%2BLzw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -6278,17 +6278,17 @@
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>Medior data-analist</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>Finance Ideas</t>
+          <t>Mammoet</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>Utrecht, Utrecht, Netherlands</t>
+          <t>Schiedam, South Holland, Netherlands</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="H92" s="3" t="inlineStr">
         <is>
-          <t>This is a medior data analyst role focused on financial and strategic healthcare dashboards and predictive modeling using SQL and Excel, with only a passing mention of AI. It does not utilize the candidate's core GenAI, LLM, and agentic specialization, and represents a significant mismatch in both focus and seniority.</t>
+          <t>This is a Data Engineer role focused on cloud data platforms, ETL pipelines, and Data Vault modeling, which does not leverage the candidate's core specialization in Generative AI, LLMs, and agentic workflows. Additionally, the required 0-5 years of experience represents a seniority mismatch for a Lead Data Scientist with over 10 years of experience.</t>
         </is>
       </c>
       <c r="I92" s="3" t="inlineStr">
@@ -6331,7 +6331,7 @@
       </c>
       <c r="M92" s="6" t="inlineStr">
         <is>
-          <t>https://nl.linkedin.com/jobs/view/medior-data-analist-at-finance-ideas-4459185767?position=16&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=Aag%2FWZa%2Bp4QUCt1avtmqXw%3D%3D</t>
+          <t>https://nl.linkedin.com/jobs/view/data-engineer-at-mammoet-4459379074?position=24&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=vEO3k7c4HScCtKkTbNh8Xg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -6341,17 +6341,17 @@
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>Junior Data Scientist – Personalization</t>
+          <t>Medior data-analist</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>Future Impact</t>
+          <t>Finance Ideas</t>
         </is>
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>Amsterdam, North Holland, Netherlands</t>
+          <t>Utrecht, Utrecht, Netherlands</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
@@ -6369,7 +6369,7 @@
       </c>
       <c r="H93" s="3" t="inlineStr">
         <is>
-          <t>This role is a severe seniority and domain mismatch, requiring a junior-level data scientist (1+ years experience) focused on classical machine learning, personalization, and tabular/text mining rather than the candidate's advanced GenAI, LLMs, and agentic orchestration specialization.</t>
+          <t>This is a medior data analyst role focused on financial and strategic healthcare dashboards and predictive modeling using SQL and Excel, with only a passing mention of AI. It does not utilize the candidate's core GenAI, LLM, and agentic specialization, and represents a significant mismatch in both focus and seniority.</t>
         </is>
       </c>
       <c r="I93" s="3" t="inlineStr">
@@ -6379,7 +6379,7 @@
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
-          <t>Possible - relocation support mentioned, visa not explicit</t>
+          <t>Not stated in JD</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="M93" s="6" t="inlineStr">
         <is>
-          <t>https://nl.linkedin.com/jobs/view/junior-data-scientist-%E2%80%93-personalization-at-future-impact-4459176208?position=6&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=%2F2X0%2FMpduifeqyUanMFmiQ%3D%3D</t>
+          <t>https://nl.linkedin.com/jobs/view/medior-data-analist-at-finance-ideas-4459185767?position=16&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=Aag%2FWZa%2Bp4QUCt1avtmqXw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -6404,17 +6404,17 @@
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>Senior Software Developer</t>
+          <t>Junior Data Scientist – Personalization</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>Bankdata</t>
+          <t>Future Impact</t>
         </is>
       </c>
       <c r="D94" s="3" t="inlineStr">
         <is>
-          <t>Silkeborg, Central Denmark Region, Denmark</t>
+          <t>Amsterdam, North Holland, Netherlands</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -6423,7 +6423,7 @@
         </is>
       </c>
       <c r="F94" s="7" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G94" s="8" t="inlineStr">
         <is>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="H94" s="3" t="inlineStr">
         <is>
-          <t>This is a Senior Software Developer role focused on core data engineering, Java/Spring Boot, Angular, and legacy systems rather than Generative AI or LLMs. Although Databricks, Python, and financial domain experience overlap with the candidate's background, the lack of software engineering specialization in Java/frontend and absence of GenAI/agentic requirements make it a weak technical fit.</t>
+          <t>This role is a severe seniority and domain mismatch, requiring a junior-level data scientist (1+ years experience) focused on classical machine learning, personalization, and tabular/text mining rather than the candidate's advanced GenAI, LLMs, and agentic orchestration specialization.</t>
         </is>
       </c>
       <c r="I94" s="3" t="inlineStr">
@@ -6442,7 +6442,7 @@
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
-          <t>Not stated in JD</t>
+          <t>Possible - relocation support mentioned, visa not explicit</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
@@ -6457,7 +6457,7 @@
       </c>
       <c r="M94" s="6" t="inlineStr">
         <is>
-          <t>https://dk.linkedin.com/jobs/view/senior-software-developer-at-bankdata-4449002669?position=27&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=HL%2Flu1131ad6ecWWSqhgeg%3D%3D</t>
+          <t>https://nl.linkedin.com/jobs/view/junior-data-scientist-%E2%80%93-personalization-at-future-impact-4459176208?position=6&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=%2F2X0%2FMpduifeqyUanMFmiQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -6467,22 +6467,22 @@
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Developer</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>Wilshire Lane Capital</t>
+          <t>Bankdata</t>
         </is>
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t>Dubai, Dubai, United Arab Emirates</t>
+          <t>Silkeborg, Central Denmark Region, Denmark</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F95" s="7" t="n">
@@ -6495,7 +6495,7 @@
       </c>
       <c r="H95" s="3" t="inlineStr">
         <is>
-          <t>This is a Senior Data Engineer role focused on Snowflake, ELT pipelines, dbt, and Airflow rather than GenAI, LLMs, or agentic systems. While the candidate has Python and SQL skills, the core domain is infrastructure engineering rather than the candidate's specialization in Generative AI and data science.</t>
+          <t>This is a Senior Software Developer role focused on core data engineering, Java/Spring Boot, Angular, and legacy systems rather than Generative AI or LLMs. Although Databricks, Python, and financial domain experience overlap with the candidate's background, the lack of software engineering specialization in Java/frontend and absence of GenAI/agentic requirements make it a weak technical fit.</t>
         </is>
       </c>
       <c r="I95" s="3" t="inlineStr">
@@ -6520,7 +6520,7 @@
       </c>
       <c r="M95" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/senior-data-engineer-at-wilshire-lane-capital-4460178348?position=5&amp;pageNum=0&amp;refId=zJBbvwb5H0wsbJ5fs9ZTVw%3D%3D&amp;trackingId=TNqC9%2FHt9lY4eoN2myLPYg%3D%3D</t>
+          <t>https://dk.linkedin.com/jobs/view/senior-software-developer-at-bankdata-4449002669?position=27&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=HL%2Flu1131ad6ecWWSqhgeg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -6530,26 +6530,26 @@
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>Data Scientist (m/w/d)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>Alliance Healthcare Deutschland GmbH</t>
+          <t>Wilshire Lane Capital</t>
         </is>
       </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
-          <t>Frankfurt, Hesse, Germany</t>
+          <t>Dubai, Dubai, United Arab Emirates</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="F96" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G96" s="8" t="inlineStr">
         <is>
@@ -6558,12 +6558,12 @@
       </c>
       <c r="H96" s="3" t="inlineStr">
         <is>
-          <t>[FALLBACK SCORER - Gemini call failed] Matched 1 core GenAI term(s) via keyword search. Verify manually; this is a degraded-mode score.</t>
+          <t>This is a Senior Data Engineer role focused on Snowflake, ELT pipelines, dbt, and Airflow rather than GenAI, LLMs, or agentic systems. While the candidate has Python and SQL skills, the core domain is infrastructure engineering rather than the candidate's specialization in Generative AI and data science.</t>
         </is>
       </c>
       <c r="I96" s="3" t="inlineStr">
         <is>
-          <t>Yes - fluent/C1+ German explicitly required</t>
+          <t>Not stated in JD</t>
         </is>
       </c>
       <c r="J96" s="3" t="inlineStr">
@@ -6583,7 +6583,7 @@
       </c>
       <c r="M96" s="6" t="inlineStr">
         <is>
-          <t>https://de.linkedin.com/jobs/view/data-scientist-m-w-d-at-alliance-healthcare-deutschland-gmbh-4459307202?position=1&amp;pageNum=0&amp;refId=T%2F0KkBXL%2Fl%2B5Iv5tUGTY7Q%3D%3D&amp;trackingId=a%2BRgoPI8HwvjxaQsctZHFQ%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/senior-data-engineer-at-wilshire-lane-capital-4460178348?position=5&amp;pageNum=0&amp;refId=zJBbvwb5H0wsbJ5fs9ZTVw%3D%3D&amp;trackingId=TNqC9%2FHt9lY4eoN2myLPYg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -6593,17 +6593,17 @@
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>Data Analytics Manager</t>
+          <t>Data Scientist (m/w/d)</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>Salt</t>
+          <t>Alliance Healthcare Deutschland GmbH</t>
         </is>
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t>Dubai, United Arab Emirates</t>
+          <t>Frankfurt, Hesse, Germany</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="H97" s="3" t="inlineStr">
         <is>
-          <t>This is a traditional Business Intelligence and Analytics Manager role focused on SQL, BI platforms, and dashboard governance, which is entirely misaligned with the candidate's core specialization in Generative AI, LLMs, and agentic systems. Although the seniority and years of experience generally align, the technical scope is classical data analytics rather than advanced AI.</t>
+          <t>[FALLBACK SCORER - Gemini call failed] Matched 1 core GenAI term(s) via keyword search. Verify manually; this is a degraded-mode score.</t>
         </is>
       </c>
       <c r="I97" s="3" t="inlineStr">
         <is>
-          <t>Not stated in JD</t>
+          <t>Yes - fluent/C1+ German explicitly required</t>
         </is>
       </c>
       <c r="J97" s="3" t="inlineStr">
@@ -6646,7 +6646,7 @@
       </c>
       <c r="M97" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/data-analytics-manager-at-salt-4444546523?position=19&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=nocZsmIJ8Yx5LNeo0Qbyfg%3D%3D</t>
+          <t>https://de.linkedin.com/jobs/view/data-scientist-m-w-d-at-alliance-healthcare-deutschland-gmbh-4459307202?position=1&amp;pageNum=0&amp;refId=T%2F0KkBXL%2Fl%2B5Iv5tUGTY7Q%3D%3D&amp;trackingId=a%2BRgoPI8HwvjxaQsctZHFQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -6656,17 +6656,17 @@
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>Junior Data Scientist Hypotheken DataLab (Amersfoort)</t>
+          <t>Data Analytics Manager</t>
         </is>
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>Future Impact</t>
+          <t>Salt</t>
         </is>
       </c>
       <c r="D98" s="3" t="inlineStr">
         <is>
-          <t>Amsterdam, North Holland, Netherlands</t>
+          <t>Dubai, United Arab Emirates</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
@@ -6684,7 +6684,7 @@
       </c>
       <c r="H98" s="3" t="inlineStr">
         <is>
-          <t>This is a junior data scientist role focused on traditional mortgage analytics and classical machine learning, representing a severe seniority and domain mismatch for a 10+ year GenAI lead specialist. Additionally, the role explicitly requires fluent Dutch language skills which the candidate lacks.</t>
+          <t>This is a traditional Business Intelligence and Analytics Manager role focused on SQL, BI platforms, and dashboard governance, which is entirely misaligned with the candidate's core specialization in Generative AI, LLMs, and agentic systems. Although the seniority and years of experience generally align, the technical scope is classical data analytics rather than advanced AI.</t>
         </is>
       </c>
       <c r="I98" s="3" t="inlineStr">
@@ -6709,7 +6709,7 @@
       </c>
       <c r="M98" s="6" t="inlineStr">
         <is>
-          <t>https://nl.linkedin.com/jobs/view/junior-data-scientist-hypotheken-datalab-amersfoort-at-future-impact-4459169232?position=10&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=PCmMM9pEfOFRNmRrvy5XFw%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/data-analytics-manager-at-salt-4444546523?position=19&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=nocZsmIJ8Yx5LNeo0Qbyfg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -6719,17 +6719,17 @@
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>Manager – Data Engineering, Architecture &amp; Reporting Platform - Dubai / Abu Dhabi</t>
+          <t>Junior Data Scientist Hypotheken DataLab (Amersfoort)</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>Agthia Group PJSC</t>
+          <t>Future Impact</t>
         </is>
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
-          <t>Dubai, Dubai, United Arab Emirates</t>
+          <t>Amsterdam, North Holland, Netherlands</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -6738,7 +6738,7 @@
         </is>
       </c>
       <c r="F99" s="7" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G99" s="8" t="inlineStr">
         <is>
@@ -6747,7 +6747,7 @@
       </c>
       <c r="H99" s="3" t="inlineStr">
         <is>
-          <t>This is a data engineering and platform architecture role focused on cloud lakehouse setup, ETL pipelines, and semantic layers, completely lacking any Generative AI, LLMs, or agentic workflows which form the candidate's core specialization. Additionally, while the candidate has 10+ years of experience, the heavy infrastructure and data engineering focus makes it a weak technical fit.</t>
+          <t>This is a junior data scientist role focused on traditional mortgage analytics and classical machine learning, representing a severe seniority and domain mismatch for a 10+ year GenAI lead specialist. Additionally, the role explicitly requires fluent Dutch language skills which the candidate lacks.</t>
         </is>
       </c>
       <c r="I99" s="3" t="inlineStr">
@@ -6772,7 +6772,7 @@
       </c>
       <c r="M99" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/manager-%E2%80%93-data-engineering-architecture-reporting-platform-dubai-abu-dhabi-at-agthia-group-pjsc-4457225736?position=30&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=uCZRYkPcw%2FLl2O0EJmhVdQ%3D%3D</t>
+          <t>https://nl.linkedin.com/jobs/view/junior-data-scientist-hypotheken-datalab-amersfoort-at-future-impact-4459169232?position=10&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=PCmMM9pEfOFRNmRrvy5XFw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -6782,17 +6782,17 @@
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>Research Informatics Data Engineer</t>
+          <t>Manager – Data Engineering, Architecture &amp; Reporting Platform - Dubai / Abu Dhabi</t>
         </is>
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>Lundbeck</t>
+          <t>Agthia Group PJSC</t>
         </is>
       </c>
       <c r="D100" s="3" t="inlineStr">
         <is>
-          <t>Copenhagen, Capital Region of Denmark, Denmark</t>
+          <t>Dubai, Dubai, United Arab Emirates</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -6810,7 +6810,7 @@
       </c>
       <c r="H100" s="3" t="inlineStr">
         <is>
-          <t>This is a Research Informatics Data Engineer role focusing on life sciences data management, laboratory informatics, and scientific platform integration rather than Generative AI or advanced LLM application development. While LLMs are briefly mentioned as an optional tool for coding assistance, the candidate's core specialization in multi-agent orchestration, RAG architectures, and production GenAI systems does not align with this software/data engineering workflow role.</t>
+          <t>This is a data engineering and platform architecture role focused on cloud lakehouse setup, ETL pipelines, and semantic layers, completely lacking any Generative AI, LLMs, or agentic workflows which form the candidate's core specialization. Additionally, while the candidate has 10+ years of experience, the heavy infrastructure and data engineering focus makes it a weak technical fit.</t>
         </is>
       </c>
       <c r="I100" s="3" t="inlineStr">
@@ -6835,7 +6835,7 @@
       </c>
       <c r="M100" s="6" t="inlineStr">
         <is>
-          <t>https://dk.linkedin.com/jobs/view/research-informatics-data-engineer-at-lundbeck-4448898202?position=5&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=5fkJnjfpF2QdhMDLztM5Vw%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/manager-%E2%80%93-data-engineering-architecture-reporting-platform-dubai-abu-dhabi-at-agthia-group-pjsc-4457225736?position=30&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=uCZRYkPcw%2FLl2O0EJmhVdQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -6845,17 +6845,17 @@
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>Head of Data Analytics</t>
+          <t>Research Informatics Data Engineer</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>Right Calibre Consulting</t>
+          <t>Lundbeck</t>
         </is>
       </c>
       <c r="D101" s="3" t="inlineStr">
         <is>
-          <t>Dubai, United Arab Emirates</t>
+          <t>Copenhagen, Capital Region of Denmark, Denmark</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
@@ -6864,7 +6864,7 @@
         </is>
       </c>
       <c r="F101" s="7" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G101" s="8" t="inlineStr">
         <is>
@@ -6873,7 +6873,7 @@
       </c>
       <c r="H101" s="3" t="inlineStr">
         <is>
-          <t>This is a Head of Data Analytics role focused on traditional BI, commercial insights, data governance, and leading analytics teams in the media and technology sector. It completely lacks any GenAI, LLM, or agentic AI focus, and the Head/Director-level leadership scope exceeds the candidate's current Lead Data Scientist level.</t>
+          <t>This is a Research Informatics Data Engineer role focusing on life sciences data management, laboratory informatics, and scientific platform integration rather than Generative AI or advanced LLM application development. While LLMs are briefly mentioned as an optional tool for coding assistance, the candidate's core specialization in multi-agent orchestration, RAG architectures, and production GenAI systems does not align with this software/data engineering workflow role.</t>
         </is>
       </c>
       <c r="I101" s="3" t="inlineStr">
@@ -6898,7 +6898,7 @@
       </c>
       <c r="M101" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/head-of-data-analytics-at-right-calibre-consulting-4459174081?position=24&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=dZTHuLROd%2FTUDsdWxlHCPg%3D%3D</t>
+          <t>https://dk.linkedin.com/jobs/view/research-informatics-data-engineer-at-lundbeck-4448898202?position=5&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=5fkJnjfpF2QdhMDLztM5Vw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -6908,17 +6908,17 @@
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t>Customer Intelligence Manager</t>
+          <t>Head of Data Analytics</t>
         </is>
       </c>
       <c r="C102" s="3" t="inlineStr">
         <is>
-          <t>Al Tayer Insignia</t>
+          <t>Right Calibre Consulting</t>
         </is>
       </c>
       <c r="D102" s="3" t="inlineStr">
         <is>
-          <t>Dubai, Dubai, United Arab Emirates</t>
+          <t>Dubai, United Arab Emirates</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -6936,7 +6936,7 @@
       </c>
       <c r="H102" s="3" t="inlineStr">
         <is>
-          <t>This Customer Intelligence Manager role focuses on market research, consumer insights, and retail analytics rather than Generative AI, LLMs, or agentic systems. It represents a fundamental domain mismatch for the candidate's specialized technical profile.</t>
+          <t>This is a Head of Data Analytics role focused on traditional BI, commercial insights, data governance, and leading analytics teams in the media and technology sector. It completely lacks any GenAI, LLM, or agentic AI focus, and the Head/Director-level leadership scope exceeds the candidate's current Lead Data Scientist level.</t>
         </is>
       </c>
       <c r="I102" s="3" t="inlineStr">
@@ -6961,7 +6961,7 @@
       </c>
       <c r="M102" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/customer-intelligence-manager-at-al-tayer-insignia-4457235794?position=9&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=PiyoN3pPhVcxMx9vtAIf5g%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/head-of-data-analytics-at-right-calibre-consulting-4459174081?position=24&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=dZTHuLROd%2FTUDsdWxlHCPg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -6971,17 +6971,17 @@
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>Service Review Insights Lead</t>
+          <t>Customer Intelligence Manager</t>
         </is>
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>Discovered MENA</t>
+          <t>Al Tayer Insignia</t>
         </is>
       </c>
       <c r="D103" s="3" t="inlineStr">
         <is>
-          <t>Dubai, United Arab Emirates</t>
+          <t>Dubai, Dubai, United Arab Emirates</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
@@ -6999,7 +6999,7 @@
       </c>
       <c r="H103" s="3" t="inlineStr">
         <is>
-          <t>This role focuses heavily on operational analytics, call center metrics, and executive board presentations with no connection to Generative AI, LLMs, or data science. It is completely outside the candidate's core technical specialization and domain.</t>
+          <t>This Customer Intelligence Manager role focuses on market research, consumer insights, and retail analytics rather than Generative AI, LLMs, or agentic systems. It represents a fundamental domain mismatch for the candidate's specialized technical profile.</t>
         </is>
       </c>
       <c r="I103" s="3" t="inlineStr">
@@ -7024,7 +7024,7 @@
       </c>
       <c r="M103" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/service-review-insights-lead-at-discovered-mena-4456958136?position=10&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=oMos4kbDfkh42RiAd%2Bimnw%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/customer-intelligence-manager-at-al-tayer-insignia-4457235794?position=9&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=PiyoN3pPhVcxMx9vtAIf5g%3D%3D</t>
         </is>
       </c>
     </row>
@@ -7034,17 +7034,17 @@
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>QEHS Digital Analyst - UAE National</t>
+          <t>Service Review Insights Lead</t>
         </is>
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t>Siemens Energy</t>
+          <t>Discovered MENA</t>
         </is>
       </c>
       <c r="D104" s="3" t="inlineStr">
         <is>
-          <t>Dubai, Dubai, United Arab Emirates</t>
+          <t>Dubai, United Arab Emirates</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
@@ -7062,7 +7062,7 @@
       </c>
       <c r="H104" s="3" t="inlineStr">
         <is>
-          <t>This role is focused on Quality, Environment, Health, and Safety (QEHS) digital transformation, enterprise systems like SAP and Salesforce, and quality management standards rather than Generative AI or LLM specialization. It represents a significant domain and technical mismatch for a Lead Data Scientist specializing in agentic AI and RAG architectures.</t>
+          <t>This role focuses heavily on operational analytics, call center metrics, and executive board presentations with no connection to Generative AI, LLMs, or data science. It is completely outside the candidate's core technical specialization and domain.</t>
         </is>
       </c>
       <c r="I104" s="3" t="inlineStr">
@@ -7087,7 +7087,7 @@
       </c>
       <c r="M104" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/qehs-digital-analyst-uae-national-at-siemens-energy-4439835820?position=8&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=jLKXnOBvB%2BaDszNV2BAbbA%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/service-review-insights-lead-at-discovered-mena-4456958136?position=10&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=oMos4kbDfkh42RiAd%2Bimnw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -7097,12 +7097,12 @@
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>Data Analyst - UAE National, ICQA/LND Analytics Team</t>
+          <t>QEHS Digital Analyst - UAE National</t>
         </is>
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Siemens Energy</t>
         </is>
       </c>
       <c r="D105" s="3" t="inlineStr">
@@ -7125,7 +7125,7 @@
       </c>
       <c r="H105" s="3" t="inlineStr">
         <is>
-          <t>This Data Analyst role at Amazon focuses on SQL reporting, dashboards, and operational data management, lacking any connection to the candidate's core GenAI, LLMs, and agentic AI specialization. Furthermore, the role is restricted to UAE Nationals and represents a significant mismatch in domain and function.</t>
+          <t>This role is focused on Quality, Environment, Health, and Safety (QEHS) digital transformation, enterprise systems like SAP and Salesforce, and quality management standards rather than Generative AI or LLM specialization. It represents a significant domain and technical mismatch for a Lead Data Scientist specializing in agentic AI and RAG architectures.</t>
         </is>
       </c>
       <c r="I105" s="3" t="inlineStr">
@@ -7150,7 +7150,7 @@
       </c>
       <c r="M105" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/data-analyst-uae-national-icqa-lnd-analytics-team-at-amazon-4459169756?position=7&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=dtuARx3ylMmIho9xSQNgYg%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/qehs-digital-analyst-uae-national-at-siemens-energy-4439835820?position=8&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=jLKXnOBvB%2BaDszNV2BAbbA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -7160,12 +7160,12 @@
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t>Senior Data Analyst - Strategy</t>
+          <t>Data Analyst - UAE National, ICQA/LND Analytics Team</t>
         </is>
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t>dubizzle</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="D106" s="3" t="inlineStr">
@@ -7188,7 +7188,7 @@
       </c>
       <c r="H106" s="3" t="inlineStr">
         <is>
-          <t>This is a Senior Data Analyst - Strategy role focused on business analytics, executive dashboards, and commercial growth rather than AI, lacking any GenAI, LLM, or agentic specialization. Additionally, it represents a domain and functional mismatch for an AI/ML Lead Data Scientist.</t>
+          <t>This Data Analyst role at Amazon focuses on SQL reporting, dashboards, and operational data management, lacking any connection to the candidate's core GenAI, LLMs, and agentic AI specialization. Furthermore, the role is restricted to UAE Nationals and represents a significant mismatch in domain and function.</t>
         </is>
       </c>
       <c r="I106" s="3" t="inlineStr">
@@ -7213,7 +7213,7 @@
       </c>
       <c r="M106" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/senior-data-analyst-strategy-at-dubizzle-4446647656?position=5&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=oDSAohEFPlpSK2IK3vFpNg%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/data-analyst-uae-national-icqa-lnd-analytics-team-at-amazon-4459169756?position=7&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=dtuARx3ylMmIho9xSQNgYg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -7223,17 +7223,17 @@
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Senior Data Analyst - Strategy</t>
         </is>
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>Insify</t>
+          <t>dubizzle</t>
         </is>
       </c>
       <c r="D107" s="3" t="inlineStr">
         <is>
-          <t>Amsterdam, North Holland, Netherlands</t>
+          <t>Dubai, Dubai, United Arab Emirates</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
@@ -7251,12 +7251,12 @@
       </c>
       <c r="H107" s="3" t="inlineStr">
         <is>
-          <t>This is a classical Data Analyst role focused on SQL, A/B testing, and business metrics, which is completely unrelated to the candidate's core specialization in Generative AI, LLMs, and agentic workflows.</t>
+          <t>This is a Senior Data Analyst - Strategy role focused on business analytics, executive dashboards, and commercial growth rather than AI, lacking any GenAI, LLM, or agentic specialization. Additionally, it represents a domain and functional mismatch for an AI/ML Lead Data Scientist.</t>
         </is>
       </c>
       <c r="I107" s="3" t="inlineStr">
         <is>
-          <t>Yes - German required (see JD for exact level)</t>
+          <t>Not stated in JD</t>
         </is>
       </c>
       <c r="J107" s="3" t="inlineStr">
@@ -7276,7 +7276,7 @@
       </c>
       <c r="M107" s="6" t="inlineStr">
         <is>
-          <t>https://nl.linkedin.com/jobs/view/data-analyst-at-insify-4457952341?position=26&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=kZIox38P2PV0MRG6Tih7Dw%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/senior-data-analyst-strategy-at-dubizzle-4446647656?position=5&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=oDSAohEFPlpSK2IK3vFpNg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -7286,17 +7286,17 @@
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t>Research Analyst - NL</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t>OPEN Health</t>
+          <t>Insify</t>
         </is>
       </c>
       <c r="D108" s="3" t="inlineStr">
         <is>
-          <t>Rotterdam, South Holland, Netherlands</t>
+          <t>Amsterdam, North Holland, Netherlands</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
@@ -7314,12 +7314,12 @@
       </c>
       <c r="H108" s="3" t="inlineStr">
         <is>
-          <t>This role focuses on health economics, meta-analysis, and HEOR modeling (cost-effectiveness, budget impact) using R and statistical software, which is completely unrelated to the candidate's GenAI, LLMs, and agentic AI specialization.</t>
+          <t>This is a classical Data Analyst role focused on SQL, A/B testing, and business metrics, which is completely unrelated to the candidate's core specialization in Generative AI, LLMs, and agentic workflows.</t>
         </is>
       </c>
       <c r="I108" s="3" t="inlineStr">
         <is>
-          <t>Not stated in JD</t>
+          <t>Yes - German required (see JD for exact level)</t>
         </is>
       </c>
       <c r="J108" s="3" t="inlineStr">
@@ -7339,7 +7339,7 @@
       </c>
       <c r="M108" s="6" t="inlineStr">
         <is>
-          <t>https://nl.linkedin.com/jobs/view/research-analyst-nl-at-open-health-4457247414?position=28&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=lxrHLFZXxcKuwp8%2F8mz0KA%3D%3D</t>
+          <t>https://nl.linkedin.com/jobs/view/data-analyst-at-insify-4457952341?position=26&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=kZIox38P2PV0MRG6Tih7Dw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -7349,17 +7349,17 @@
       </c>
       <c r="B109" s="3" t="inlineStr">
         <is>
-          <t>Data Analyst / Data Scientist</t>
+          <t>Research Analyst - NL</t>
         </is>
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>Trinamics</t>
+          <t>OPEN Health</t>
         </is>
       </c>
       <c r="D109" s="3" t="inlineStr">
         <is>
-          <t>North Brabant, Netherlands</t>
+          <t>Rotterdam, South Holland, Netherlands</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
@@ -7377,7 +7377,7 @@
       </c>
       <c r="H109" s="3" t="inlineStr">
         <is>
-          <t>This is a financial reporting, data analysis, and dashboard-building role focusing on SAP, Spotfire, and Power BI with no connection to Generative AI, LLMs, or agentic systems. It is entirely unrelated to the candidate's core specialization and represents a major mismatch in domain and technical stack.</t>
+          <t>This role focuses on health economics, meta-analysis, and HEOR modeling (cost-effectiveness, budget impact) using R and statistical software, which is completely unrelated to the candidate's GenAI, LLMs, and agentic AI specialization.</t>
         </is>
       </c>
       <c r="I109" s="3" t="inlineStr">
@@ -7402,7 +7402,7 @@
       </c>
       <c r="M109" s="6" t="inlineStr">
         <is>
-          <t>https://nl.linkedin.com/jobs/view/data-analyst-data-scientist-at-trinamics-4459172477?position=15&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=wKQaRNJqc3u7QhTWjoCU%2FQ%3D%3D</t>
+          <t>https://nl.linkedin.com/jobs/view/research-analyst-nl-at-open-health-4457247414?position=28&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=lxrHLFZXxcKuwp8%2F8mz0KA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -7412,17 +7412,17 @@
       </c>
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t>De Rijksoverheid zoekt: Data scientist AI driven weather model</t>
+          <t>Data Analyst / Data Scientist</t>
         </is>
       </c>
       <c r="C110" s="3" t="inlineStr">
         <is>
-          <t>KNMI - Royal Netherlands Meteorological Institute</t>
+          <t>Trinamics</t>
         </is>
       </c>
       <c r="D110" s="3" t="inlineStr">
         <is>
-          <t>De Bilt, Utrecht, Netherlands</t>
+          <t>North Brabant, Netherlands</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
@@ -7440,7 +7440,7 @@
       </c>
       <c r="H110" s="3" t="inlineStr">
         <is>
-          <t>This role focuses on specialized deep learning for meteorological modeling, graph neural networks, and diffusion models applied to weather forecasting, which has virtually no overlap with the candidate's core GenAI, LLMs, and agentic AI specialization.</t>
+          <t>This is a financial reporting, data analysis, and dashboard-building role focusing on SAP, Spotfire, and Power BI with no connection to Generative AI, LLMs, or agentic systems. It is entirely unrelated to the candidate's core specialization and represents a major mismatch in domain and technical stack.</t>
         </is>
       </c>
       <c r="I110" s="3" t="inlineStr">
@@ -7465,7 +7465,7 @@
       </c>
       <c r="M110" s="6" t="inlineStr">
         <is>
-          <t>https://nl.linkedin.com/jobs/view/de-rijksoverheid-zoekt-data-scientist-ai-driven-weather-model-at-knmi-royal-netherlands-meteorological-institute-4459321694?position=7&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=uEDe9phb4vscnrkupOYRog%3D%3D</t>
+          <t>https://nl.linkedin.com/jobs/view/data-analyst-data-scientist-at-trinamics-4459172477?position=15&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=wKQaRNJqc3u7QhTWjoCU%2FQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -7475,17 +7475,17 @@
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>Decision Scientist, Trust &amp; Safety</t>
+          <t>De Rijksoverheid zoekt: Data scientist AI driven weather model</t>
         </is>
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>Vinted</t>
+          <t>KNMI - Royal Netherlands Meteorological Institute</t>
         </is>
       </c>
       <c r="D111" s="3" t="inlineStr">
         <is>
-          <t>Amsterdam, North Holland, Netherlands</t>
+          <t>De Bilt, Utrecht, Netherlands</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H111" s="3" t="inlineStr">
         <is>
-          <t>This is a Decision Scientist role focused on product experimentation, SQL/BI dashboards, and Trust &amp; Safety analytics, which is completely unrelated to the candidate's core specialization in Generative AI, LLMs, and agentic workflows.</t>
+          <t>This role focuses on specialized deep learning for meteorological modeling, graph neural networks, and diffusion models applied to weather forecasting, which has virtually no overlap with the candidate's core GenAI, LLMs, and agentic AI specialization.</t>
         </is>
       </c>
       <c r="I111" s="3" t="inlineStr">
         <is>
-          <t>No - English fluency stated as sufficient</t>
+          <t>Not stated in JD</t>
         </is>
       </c>
       <c r="J111" s="3" t="inlineStr">
@@ -7528,7 +7528,7 @@
       </c>
       <c r="M111" s="6" t="inlineStr">
         <is>
-          <t>https://nl.linkedin.com/jobs/view/decision-scientist-trust-safety-at-vinted-4431734156?position=13&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=5DKFgkv450iADwhSNzZiDw%3D%3D</t>
+          <t>https://nl.linkedin.com/jobs/view/de-rijksoverheid-zoekt-data-scientist-ai-driven-weather-model-at-knmi-royal-netherlands-meteorological-institute-4459321694?position=7&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=uEDe9phb4vscnrkupOYRog%3D%3D</t>
         </is>
       </c>
     </row>
@@ -7538,17 +7538,17 @@
       </c>
       <c r="B112" s="3" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - System Optimization</t>
+          <t>Decision Scientist, Trust &amp; Safety</t>
         </is>
       </c>
       <c r="C112" s="3" t="inlineStr">
         <is>
-          <t>Danfoss</t>
+          <t>Vinted</t>
         </is>
       </c>
       <c r="D112" s="3" t="inlineStr">
         <is>
-          <t>Copenhagen, Capital Region of Denmark, Denmark</t>
+          <t>Amsterdam, North Holland, Netherlands</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
@@ -7566,7 +7566,7 @@
       </c>
       <c r="H112" s="3" t="inlineStr">
         <is>
-          <t>This is a Senior Data Scientist role focused on physical modelling, thermo-hydraulic simulation, and Mixed-Integer Linear Programming (MILP) for energy networks, which has zero overlap with the candidate's core specialization in Generative AI, LLMs, and agentic systems.</t>
+          <t>This is a Decision Scientist role focused on product experimentation, SQL/BI dashboards, and Trust &amp; Safety analytics, which is completely unrelated to the candidate's core specialization in Generative AI, LLMs, and agentic workflows.</t>
         </is>
       </c>
       <c r="I112" s="3" t="inlineStr">
@@ -7591,7 +7591,7 @@
       </c>
       <c r="M112" s="6" t="inlineStr">
         <is>
-          <t>https://dk.linkedin.com/jobs/view/senior-data-scientist-system-optimization-at-danfoss-4459328391?position=28&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=pWSiaSPEvTB%2Fj17raCtBPA%3D%3D</t>
+          <t>https://nl.linkedin.com/jobs/view/decision-scientist-trust-safety-at-vinted-4431734156?position=13&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=5DKFgkv450iADwhSNzZiDw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -7611,7 +7611,7 @@
       </c>
       <c r="D113" s="3" t="inlineStr">
         <is>
-          <t>Kolding, Region of Southern Denmark, Denmark</t>
+          <t>Copenhagen, Capital Region of Denmark, Denmark</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
@@ -7629,7 +7629,7 @@
       </c>
       <c r="H113" s="3" t="inlineStr">
         <is>
-          <t>This is a Senior Data Scientist role focused on physical modelling, thermo-hydraulic simulation of energy networks, and Mixed-Integer Linear Programming (MILP), which is entirely unrelated to the candidate's core specialization in Generative AI, LLMs, and agentic systems.</t>
+          <t>This is a Senior Data Scientist role focused on physical modelling, thermo-hydraulic simulation, and Mixed-Integer Linear Programming (MILP) for energy networks, which has zero overlap with the candidate's core specialization in Generative AI, LLMs, and agentic systems.</t>
         </is>
       </c>
       <c r="I113" s="3" t="inlineStr">
@@ -7654,7 +7654,7 @@
       </c>
       <c r="M113" s="6" t="inlineStr">
         <is>
-          <t>https://dk.linkedin.com/jobs/view/senior-data-scientist-system-optimization-at-danfoss-4459334294?position=29&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=6IO8CqSe4TjOJrnH%2BoTbig%3D%3D</t>
+          <t>https://dk.linkedin.com/jobs/view/senior-data-scientist-system-optimization-at-danfoss-4459328391?position=28&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=pWSiaSPEvTB%2Fj17raCtBPA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -7664,17 +7664,17 @@
       </c>
       <c r="B114" s="3" t="inlineStr">
         <is>
-          <t>Product Owner</t>
+          <t>Senior Data Scientist - System Optimization</t>
         </is>
       </c>
       <c r="C114" s="3" t="inlineStr">
         <is>
-          <t>Ørsted</t>
+          <t>Danfoss</t>
         </is>
       </c>
       <c r="D114" s="3" t="inlineStr">
         <is>
-          <t>Gentofte, Capital Region of Denmark, Denmark</t>
+          <t>Kolding, Region of Southern Denmark, Denmark</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
@@ -7692,12 +7692,12 @@
       </c>
       <c r="H114" s="3" t="inlineStr">
         <is>
-          <t>This is a Product Owner role focused on quantitative analytics, portfolio models, and trading infrastructure rather than a hands-on Generative AI or data science engineering position. It is completely outside the candidate's core specialization in LLMs, RAG, and agentic systems, and involves product management responsibilities rather than technical AI development.</t>
+          <t>This is a Senior Data Scientist role focused on physical modelling, thermo-hydraulic simulation of energy networks, and Mixed-Integer Linear Programming (MILP), which is entirely unrelated to the candidate's core specialization in Generative AI, LLMs, and agentic systems.</t>
         </is>
       </c>
       <c r="I114" s="3" t="inlineStr">
         <is>
-          <t>Not stated in JD</t>
+          <t>No - English fluency stated as sufficient</t>
         </is>
       </c>
       <c r="J114" s="3" t="inlineStr">
@@ -7717,7 +7717,7 @@
       </c>
       <c r="M114" s="6" t="inlineStr">
         <is>
-          <t>https://dk.linkedin.com/jobs/view/product-owner-at-%C3%B8rsted-4457976275?position=30&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=kwPJx%2Freb7nWWcV4YkYqtg%3D%3D</t>
+          <t>https://dk.linkedin.com/jobs/view/senior-data-scientist-system-optimization-at-danfoss-4459334294?position=29&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=6IO8CqSe4TjOJrnH%2BoTbig%3D%3D</t>
         </is>
       </c>
     </row>
@@ -7755,7 +7755,7 @@
       </c>
       <c r="H115" s="3" t="inlineStr">
         <is>
-          <t>This is a Product Owner role focused on commodity and energy trading platforms rather than a hands-on technical Generative AI, LLM, or agentic AI role. There is a severe mismatch in job function and seniority focus, as the candidate is a technical Lead Data Scientist specializing in hands-on GenAI systems.</t>
+          <t>This is a Product Owner role focused on quantitative analytics, portfolio models, and trading infrastructure rather than a hands-on Generative AI or data science engineering position. It is completely outside the candidate's core specialization in LLMs, RAG, and agentic systems, and involves product management responsibilities rather than technical AI development.</t>
         </is>
       </c>
       <c r="I115" s="3" t="inlineStr">
@@ -7780,7 +7780,7 @@
       </c>
       <c r="M115" s="6" t="inlineStr">
         <is>
-          <t>https://dk.linkedin.com/jobs/view/product-owner-at-%C3%B8rsted-4457969343?position=16&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=Srm0W8oPqBLXtVvd0AdJlg%3D%3D</t>
+          <t>https://dk.linkedin.com/jobs/view/product-owner-at-%C3%B8rsted-4457976275?position=30&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=kwPJx%2Freb7nWWcV4YkYqtg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -7790,17 +7790,17 @@
       </c>
       <c r="B116" s="3" t="inlineStr">
         <is>
-          <t>Dataspecialist - Afd. for Uddannelse og Studerende</t>
+          <t>Product Owner</t>
         </is>
       </c>
       <c r="C116" s="3" t="inlineStr">
         <is>
-          <t>DTU - Technical University of Denmark</t>
+          <t>Ørsted</t>
         </is>
       </c>
       <c r="D116" s="3" t="inlineStr">
         <is>
-          <t>Kongens Lyngby, Capital Region of Denmark, Denmark</t>
+          <t>Gentofte, Capital Region of Denmark, Denmark</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
@@ -7818,7 +7818,7 @@
       </c>
       <c r="H116" s="3" t="inlineStr">
         <is>
-          <t>This role at DTU focuses on educational data analysis, stakeholder communication, and business intelligence reporting within a university setting, completely lacking any connection to the candidate's core GenAI, LLMs, or agentic AI specialization.</t>
+          <t>This is a Product Owner role focused on commodity and energy trading platforms rather than a hands-on technical Generative AI, LLM, or agentic AI role. There is a severe mismatch in job function and seniority focus, as the candidate is a technical Lead Data Scientist specializing in hands-on GenAI systems.</t>
         </is>
       </c>
       <c r="I116" s="3" t="inlineStr">
@@ -7843,7 +7843,7 @@
       </c>
       <c r="M116" s="6" t="inlineStr">
         <is>
-          <t>https://dk.linkedin.com/jobs/view/dataspecialist-afd-for-uddannelse-og-studerende-at-dtu-technical-university-of-denmark-4458711406?position=12&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=jpgFSNpWhcVL9zGHYU%2Fxbw%3D%3D</t>
+          <t>https://dk.linkedin.com/jobs/view/product-owner-at-%C3%B8rsted-4457969343?position=16&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=Srm0W8oPqBLXtVvd0AdJlg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -7853,17 +7853,17 @@
       </c>
       <c r="B117" s="3" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Dataspecialist - Afd. for Uddannelse og Studerende</t>
         </is>
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t>Abacus Medicine Group</t>
+          <t>DTU - Technical University of Denmark</t>
         </is>
       </c>
       <c r="D117" s="3" t="inlineStr">
         <is>
-          <t>Copenhagen, Capital Region of Denmark, Denmark</t>
+          <t>Kongens Lyngby, Capital Region of Denmark, Denmark</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
@@ -7881,7 +7881,7 @@
       </c>
       <c r="H117" s="3" t="inlineStr">
         <is>
-          <t>This is a Data Engineer role focusing on data pipelines, infrastructure, and warehousing, which is entirely unrelated to the candidate's core specialization in Generative AI, LLMs, and agentic workflows. Furthermore, the role is aimed at someone starting their career in data engineering, representing a major seniority mismatch for a Lead Data Scientist with 10 years of experience.</t>
+          <t>This role at DTU focuses on educational data analysis, stakeholder communication, and business intelligence reporting within a university setting, completely lacking any connection to the candidate's core GenAI, LLMs, or agentic AI specialization.</t>
         </is>
       </c>
       <c r="I117" s="3" t="inlineStr">
@@ -7906,7 +7906,7 @@
       </c>
       <c r="M117" s="6" t="inlineStr">
         <is>
-          <t>https://dk.linkedin.com/jobs/view/data-engineer-at-abacus-medicine-group-4448014908?position=7&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=naNFtA2OuhXjDVLQEaIksw%3D%3D</t>
+          <t>https://dk.linkedin.com/jobs/view/dataspecialist-afd-for-uddannelse-og-studerende-at-dtu-technical-university-of-denmark-4458711406?position=12&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=jpgFSNpWhcVL9zGHYU%2Fxbw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -7916,17 +7916,17 @@
       </c>
       <c r="B118" s="3" t="inlineStr">
         <is>
-          <t>Product Owner &amp; Analytics Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="C118" s="3" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>Abacus Medicine Group</t>
         </is>
       </c>
       <c r="D118" s="3" t="inlineStr">
         <is>
-          <t>Viby, Region of Southern Denmark, Denmark</t>
+          <t>Copenhagen, Capital Region of Denmark, Denmark</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
@@ -7944,7 +7944,7 @@
       </c>
       <c r="H118" s="3" t="inlineStr">
         <is>
-          <t>This role is a Product Owner and Analytics Engineer position focused on data platforms, BI, dbt, and stakeholder management rather than GenAI or LLM development. It is an extremely weak technical fit for a GenAI specialist.</t>
+          <t>This is a Data Engineer role focusing on data pipelines, infrastructure, and warehousing, which is entirely unrelated to the candidate's core specialization in Generative AI, LLMs, and agentic workflows. Furthermore, the role is aimed at someone starting their career in data engineering, representing a major seniority mismatch for a Lead Data Scientist with 10 years of experience.</t>
         </is>
       </c>
       <c r="I118" s="3" t="inlineStr">
@@ -7969,7 +7969,7 @@
       </c>
       <c r="M118" s="6" t="inlineStr">
         <is>
-          <t>https://dk.linkedin.com/jobs/view/product-owner-analytics-engineer-at-ok-4457992725?position=11&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=D2ySyPo8bFWVMMg%2FjecIMw%3D%3D</t>
+          <t>https://dk.linkedin.com/jobs/view/data-engineer-at-abacus-medicine-group-4448014908?position=7&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=naNFtA2OuhXjDVLQEaIksw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -7979,17 +7979,17 @@
       </c>
       <c r="B119" s="3" t="inlineStr">
         <is>
-          <t>Data Scientist - Energy Forecasting</t>
+          <t>Product Owner &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>Danfoss</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="D119" s="3" t="inlineStr">
         <is>
-          <t>Kolding, Region of Southern Denmark, Denmark</t>
+          <t>Viby, Region of Southern Denmark, Denmark</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="H119" s="3" t="inlineStr">
         <is>
-          <t>This energy forecasting and physical systems role has zero overlap with the candidate's core specialization in Generative AI, LLMs, and agentic workflows, representing a completely different domain.</t>
+          <t>This role is a Product Owner and Analytics Engineer position focused on data platforms, BI, dbt, and stakeholder management rather than GenAI or LLM development. It is an extremely weak technical fit for a GenAI specialist.</t>
         </is>
       </c>
       <c r="I119" s="3" t="inlineStr">
         <is>
-          <t>No - English fluency stated as sufficient</t>
+          <t>Not stated in JD</t>
         </is>
       </c>
       <c r="J119" s="3" t="inlineStr">
@@ -8032,7 +8032,7 @@
       </c>
       <c r="M119" s="6" t="inlineStr">
         <is>
-          <t>https://dk.linkedin.com/jobs/view/data-scientist-energy-forecasting-at-danfoss-4459332327?position=2&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=%2BhOuUASw5VgnQYgphl%2BfiQ%3D%3D</t>
+          <t>https://dk.linkedin.com/jobs/view/product-owner-analytics-engineer-at-ok-4457992725?position=11&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=D2ySyPo8bFWVMMg%2FjecIMw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -8052,7 +8052,7 @@
       </c>
       <c r="D120" s="3" t="inlineStr">
         <is>
-          <t>Copenhagen, Capital Region of Denmark, Denmark</t>
+          <t>Kolding, Region of Southern Denmark, Denmark</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="H120" s="3" t="inlineStr">
         <is>
-          <t>This is a classical machine learning role focused entirely on energy demand forecasting, time-series modeling, and physical systems for district heating, which has no overlap with the candidate's core specialization in Generative AI, LLMs, and agentic workflows.</t>
+          <t>This energy forecasting and physical systems role has zero overlap with the candidate's core specialization in Generative AI, LLMs, and agentic workflows, representing a completely different domain.</t>
         </is>
       </c>
       <c r="I120" s="3" t="inlineStr">
@@ -8095,7 +8095,7 @@
       </c>
       <c r="M120" s="6" t="inlineStr">
         <is>
-          <t>https://dk.linkedin.com/jobs/view/data-scientist-energy-forecasting-at-danfoss-4459316434?position=1&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=Jfk6JIiJcse1eCPfqN9rvg%3D%3D</t>
+          <t>https://dk.linkedin.com/jobs/view/data-scientist-energy-forecasting-at-danfoss-4459332327?position=2&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=%2BhOuUASw5VgnQYgphl%2BfiQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -8105,22 +8105,22 @@
       </c>
       <c r="B121" s="3" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Engineer (EMIRATI)</t>
+          <t>Data Scientist - Energy Forecasting</t>
         </is>
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>Salt</t>
+          <t>Danfoss</t>
         </is>
       </c>
       <c r="D121" s="3" t="inlineStr">
         <is>
-          <t>Abu Dhabi Emirate, United Arab Emirates</t>
+          <t>Copenhagen, Capital Region of Denmark, Denmark</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F121" s="7" t="n">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="H121" s="3" t="inlineStr">
         <is>
-          <t>The role requires an early-career software engineer with 2+ years of experience, representing a significant seniority mismatch for a Lead Data Scientist with 10+ years of experience. Furthermore, the position explicitly specifies that it is for Emirati nationals only.</t>
+          <t>This is a classical machine learning role focused entirely on energy demand forecasting, time-series modeling, and physical systems for district heating, which has no overlap with the candidate's core specialization in Generative AI, LLMs, and agentic workflows.</t>
         </is>
       </c>
       <c r="I121" s="3" t="inlineStr">
         <is>
-          <t>Not stated in JD</t>
+          <t>No - English fluency stated as sufficient</t>
         </is>
       </c>
       <c r="J121" s="3" t="inlineStr">
@@ -8158,7 +8158,7 @@
       </c>
       <c r="M121" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/artificial-intelligence-engineer-emirati-at-salt-4457723960?position=26&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=OL7voNOllXDyxcDmkFiWQw%3D%3D</t>
+          <t>https://dk.linkedin.com/jobs/view/data-scientist-energy-forecasting-at-danfoss-4459316434?position=1&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=Jfk6JIiJcse1eCPfqN9rvg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -8168,22 +8168,22 @@
       </c>
       <c r="B122" s="3" t="inlineStr">
         <is>
-          <t>Junior Research Scientist In the Division of Engineering (Electrical and Computer Engineering) - Dr. Fang Yi</t>
+          <t>Artificial Intelligence Engineer (EMIRATI)</t>
         </is>
       </c>
       <c r="C122" s="3" t="inlineStr">
         <is>
-          <t>New York University Abu Dhabi</t>
+          <t>Salt</t>
         </is>
       </c>
       <c r="D122" s="3" t="inlineStr">
         <is>
-          <t>Abu Dhabi, Abu Dhabi Emirate, United Arab Emirates</t>
+          <t>Abu Dhabi Emirate, United Arab Emirates</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F122" s="7" t="n">
@@ -8196,7 +8196,7 @@
       </c>
       <c r="H122" s="3" t="inlineStr">
         <is>
-          <t>This is an academic research scientist role focused on robotics, embodied AI, and assistive technologies, which does not align with the candidate's core specialization in enterprise Generative AI, LLMs, and RAG. Additionally, there is a major seniority mismatch as the role targets junior researchers with under five years of experience, whereas the candidate is a Lead Data Scientist with 10+ years of experience.</t>
+          <t>The role requires an early-career software engineer with 2+ years of experience, representing a significant seniority mismatch for a Lead Data Scientist with 10+ years of experience. Furthermore, the position explicitly specifies that it is for Emirati nationals only.</t>
         </is>
       </c>
       <c r="I122" s="3" t="inlineStr">
@@ -8206,7 +8206,7 @@
       </c>
       <c r="J122" s="3" t="inlineStr">
         <is>
-          <t>Possible - relocation support mentioned, visa not explicit</t>
+          <t>Not stated in JD</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
@@ -8221,7 +8221,7 @@
       </c>
       <c r="M122" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/junior-research-scientist-in-the-division-of-engineering-electrical-and-computer-engineering-dr-fang-yi-at-new-york-university-abu-dhabi-4448981054?position=17&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=Quv11sfD16F354%2FzN0KXRg%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/artificial-intelligence-engineer-emirati-at-salt-4457723960?position=26&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=OL7voNOllXDyxcDmkFiWQw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -8231,17 +8231,17 @@
       </c>
       <c r="B123" s="3" t="inlineStr">
         <is>
-          <t>Business Intelligence Analytics</t>
+          <t>Junior Research Scientist In the Division of Engineering (Electrical and Computer Engineering) - Dr. Fang Yi</t>
         </is>
       </c>
       <c r="C123" s="3" t="inlineStr">
         <is>
-          <t>Confidential</t>
+          <t>New York University Abu Dhabi</t>
         </is>
       </c>
       <c r="D123" s="3" t="inlineStr">
         <is>
-          <t>Abu Dhabi Emirate, United Arab Emirates</t>
+          <t>Abu Dhabi, Abu Dhabi Emirate, United Arab Emirates</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
@@ -8259,7 +8259,7 @@
       </c>
       <c r="H123" s="3" t="inlineStr">
         <is>
-          <t>This is a Business Intelligence and reporting role focusing on traditional tools like SQL Server, Tableau, PowerBI, and IT service management, completely lacking any Generative AI, LLM, or agentic specialization. The candidate's advanced GenAI and data science background is a severe mismatch for this operational BI position.</t>
+          <t>This is an academic research scientist role focused on robotics, embodied AI, and assistive technologies, which does not align with the candidate's core specialization in enterprise Generative AI, LLMs, and RAG. Additionally, there is a major seniority mismatch as the role targets junior researchers with under five years of experience, whereas the candidate is a Lead Data Scientist with 10+ years of experience.</t>
         </is>
       </c>
       <c r="I123" s="3" t="inlineStr">
@@ -8269,7 +8269,7 @@
       </c>
       <c r="J123" s="3" t="inlineStr">
         <is>
-          <t>Not stated in JD</t>
+          <t>Possible - relocation support mentioned, visa not explicit</t>
         </is>
       </c>
       <c r="K123" s="2" t="inlineStr">
@@ -8284,7 +8284,7 @@
       </c>
       <c r="M123" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/business-intelligence-analytics-at-pump-dynamics-4457247369?position=16&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=q3L54POb%2Ba8jMFybGRPVBA%3D%3D&amp;trk=public_jobs_jserp-result_search-card</t>
+          <t>https://ae.linkedin.com/jobs/view/junior-research-scientist-in-the-division-of-engineering-electrical-and-computer-engineering-dr-fang-yi-at-new-york-university-abu-dhabi-4448981054?position=17&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=Quv11sfD16F354%2FzN0KXRg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -8294,17 +8294,17 @@
       </c>
       <c r="B124" s="3" t="inlineStr">
         <is>
-          <t>Data Analyst - UAE National, ICQA/LND Analytics Team</t>
+          <t>Business Intelligence Analytics</t>
         </is>
       </c>
       <c r="C124" s="3" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Confidential</t>
         </is>
       </c>
       <c r="D124" s="3" t="inlineStr">
         <is>
-          <t>Abu Dhabi, Abu Dhabi Emirate, United Arab Emirates</t>
+          <t>Abu Dhabi Emirate, United Arab Emirates</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
@@ -8322,7 +8322,7 @@
       </c>
       <c r="H124" s="3" t="inlineStr">
         <is>
-          <t>This is a Data Analyst role focusing on standard reporting, SQL, QuickSight, and AWS data warehousing infrastructure, which is entirely unrelated to the candidate's core specialization in Generative AI, LLMs, and agentic workflows. Furthermore, there is a severe seniority and domain mismatch as the role targets data analysis rather than advanced AI leadership.</t>
+          <t>This is a Business Intelligence and reporting role focusing on traditional tools like SQL Server, Tableau, PowerBI, and IT service management, completely lacking any Generative AI, LLM, or agentic specialization. The candidate's advanced GenAI and data science background is a severe mismatch for this operational BI position.</t>
         </is>
       </c>
       <c r="I124" s="3" t="inlineStr">
@@ -8347,7 +8347,7 @@
       </c>
       <c r="M124" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/data-analyst-uae-national-icqa-lnd-analytics-team-at-amazon-4459175702?position=13&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=2u0HotRhWhUDg980ATy2nw%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/business-intelligence-analytics-at-pump-dynamics-4457247369?position=16&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=q3L54POb%2Ba8jMFybGRPVBA%3D%3D&amp;trk=public_jobs_jserp-result_search-card</t>
         </is>
       </c>
     </row>
@@ -8357,22 +8357,22 @@
       </c>
       <c r="B125" s="3" t="inlineStr">
         <is>
-          <t>Mathematician (Remote)</t>
+          <t>Data Analyst - UAE National, ICQA/LND Analytics Team</t>
         </is>
       </c>
       <c r="C125" s="3" t="inlineStr">
         <is>
-          <t>Hired</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="D125" s="3" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>Abu Dhabi, Abu Dhabi Emirate, United Arab Emirates</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F125" s="7" t="n">
@@ -8385,7 +8385,7 @@
       </c>
       <c r="H125" s="3" t="inlineStr">
         <is>
-          <t>This remote contractor role focuses on pure applied mathematics and algorithmic optimization rather than Generative AI, LLMs, or agentic frameworks. While the candidate has a strong data science background, the job is entirely unrelated to his core GenAI and RAG specialization.</t>
+          <t>This is a Data Analyst role focusing on standard reporting, SQL, QuickSight, and AWS data warehousing infrastructure, which is entirely unrelated to the candidate's core specialization in Generative AI, LLMs, and agentic workflows. Furthermore, there is a severe seniority and domain mismatch as the role targets data analysis rather than advanced AI leadership.</t>
         </is>
       </c>
       <c r="I125" s="3" t="inlineStr">
@@ -8410,7 +8410,7 @@
       </c>
       <c r="M125" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/mathematician-remote-at-hired-4459651401?position=11&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=L0rt1zlpnHOlSTn4%2BjbBZg%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/data-analyst-uae-national-icqa-lnd-analytics-team-at-amazon-4459175702?position=13&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=2u0HotRhWhUDg980ATy2nw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -8420,7 +8420,7 @@
       </c>
       <c r="B126" s="3" t="inlineStr">
         <is>
-          <t>Statistician (Remote)</t>
+          <t>Mathematician (Remote)</t>
         </is>
       </c>
       <c r="C126" s="3" t="inlineStr">
@@ -8448,7 +8448,7 @@
       </c>
       <c r="H126" s="3" t="inlineStr">
         <is>
-          <t>This role focuses heavily on classical statistics, experimental design, and A/B testing, requiring a PhD in Statistics, which does not match the candidate's core GenAI and LLM specialization. Furthermore, it is a contract statistician role rather than an advanced AI engineering or agentic systems role.</t>
+          <t>This remote contractor role focuses on pure applied mathematics and algorithmic optimization rather than Generative AI, LLMs, or agentic frameworks. While the candidate has a strong data science background, the job is entirely unrelated to his core GenAI and RAG specialization.</t>
         </is>
       </c>
       <c r="I126" s="3" t="inlineStr">
@@ -8473,7 +8473,7 @@
       </c>
       <c r="M126" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/statistician-remote-at-hired-4459636643?position=12&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=%2FKljESl%2B5ntTSKKRsgpGUg%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/mathematician-remote-at-hired-4459651401?position=11&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=L0rt1zlpnHOlSTn4%2BjbBZg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -8483,17 +8483,17 @@
       </c>
       <c r="B127" s="3" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Statistician (Remote)</t>
         </is>
       </c>
       <c r="C127" s="3" t="inlineStr">
         <is>
-          <t>TenneT</t>
+          <t>Hired</t>
         </is>
       </c>
       <c r="D127" s="3" t="inlineStr">
         <is>
-          <t>Arnhem, Gelderland, Netherlands</t>
+          <t>United Arab Emirates</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
@@ -8511,7 +8511,7 @@
       </c>
       <c r="H127" s="3" t="inlineStr">
         <is>
-          <t>This is a Data Engineer role focused on infrastructure, Java/Python backend development, Kubernetes, and streaming platforms like Apache Kafka, which is completely misaligned with the candidate's specialization in Generative AI, LLMs, and agentic workflows. Additionally, the role explicitly requires professional fluency in Dutch, which the candidate lacks.</t>
+          <t>This role focuses heavily on classical statistics, experimental design, and A/B testing, requiring a PhD in Statistics, which does not match the candidate's core GenAI and LLM specialization. Furthermore, it is a contract statistician role rather than an advanced AI engineering or agentic systems role.</t>
         </is>
       </c>
       <c r="I127" s="3" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="M127" s="6" t="inlineStr">
         <is>
-          <t>https://nl.linkedin.com/jobs/view/data-engineer-at-tennet-4459682650?position=28&amp;pageNum=0&amp;refId=oiBIn1Czflg0JjZjH5z0Lg%3D%3D&amp;trackingId=VjGapIUBNcJsDHWWWnnyCQ%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/statistician-remote-at-hired-4459636643?position=12&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=%2FKljESl%2B5ntTSKKRsgpGUg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -8546,17 +8546,17 @@
       </c>
       <c r="B128" s="3" t="inlineStr">
         <is>
-          <t>E-commerce Data Analyst</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="C128" s="3" t="inlineStr">
         <is>
-          <t>My Jewellery</t>
+          <t>TenneT</t>
         </is>
       </c>
       <c r="D128" s="3" t="inlineStr">
         <is>
-          <t>’s-Hertogenbosch, North Brabant, Netherlands</t>
+          <t>Arnhem, Gelderland, Netherlands</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
@@ -8574,7 +8574,7 @@
       </c>
       <c r="H128" s="3" t="inlineStr">
         <is>
-          <t>This is an e-commerce data analytics role focused on business intelligence, conversion rate optimization, and dashboards rather than Generative AI, LLMs, or agentic systems. Furthermore, the candidate's 10+ years of senior AI/ML and GenAI experience represent a severe overqualification mismatch for a role requiring around 2 years of e-commerce analytics experience.</t>
+          <t>This is a Data Engineer role focused on infrastructure, Java/Python backend development, Kubernetes, and streaming platforms like Apache Kafka, which is completely misaligned with the candidate's specialization in Generative AI, LLMs, and agentic workflows. Additionally, the role explicitly requires professional fluency in Dutch, which the candidate lacks.</t>
         </is>
       </c>
       <c r="I128" s="3" t="inlineStr">
@@ -8599,7 +8599,7 @@
       </c>
       <c r="M128" s="6" t="inlineStr">
         <is>
-          <t>https://nl.linkedin.com/jobs/view/e-commerce-data-analyst-at-my-jewellery-4458352332?position=24&amp;pageNum=0&amp;refId=oiBIn1Czflg0JjZjH5z0Lg%3D%3D&amp;trackingId=l7ZuY53wCY8i%2FsbUtVRI1w%3D%3D</t>
+          <t>https://nl.linkedin.com/jobs/view/data-engineer-at-tennet-4459682650?position=28&amp;pageNum=0&amp;refId=oiBIn1Czflg0JjZjH5z0Lg%3D%3D&amp;trackingId=VjGapIUBNcJsDHWWWnnyCQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -8609,17 +8609,17 @@
       </c>
       <c r="B129" s="3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>E-commerce Data Analyst</t>
         </is>
       </c>
       <c r="C129" s="3" t="inlineStr">
         <is>
-          <t>Kitopi</t>
+          <t>My Jewellery</t>
         </is>
       </c>
       <c r="D129" s="3" t="inlineStr">
         <is>
-          <t>Dubai, United Arab Emirates</t>
+          <t>’s-Hertogenbosch, North Brabant, Netherlands</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
@@ -8637,7 +8637,7 @@
       </c>
       <c r="H129" s="3" t="inlineStr">
         <is>
-          <t>This is a role for a Senior Data Engineer focused on building data pipelines, ELT processes, Snowflake, and dbt, which is completely unrelated to the candidate's core specialization as a Lead Data Scientist specializing in GenAI, LLMs, and agentic workflows.</t>
+          <t>This is an e-commerce data analytics role focused on business intelligence, conversion rate optimization, and dashboards rather than Generative AI, LLMs, or agentic systems. Furthermore, the candidate's 10+ years of senior AI/ML and GenAI experience represent a severe overqualification mismatch for a role requiring around 2 years of e-commerce analytics experience.</t>
         </is>
       </c>
       <c r="I129" s="3" t="inlineStr">
@@ -8662,7 +8662,7 @@
       </c>
       <c r="M129" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/senior-data-engineer-at-kitopi-4457746184?position=4&amp;pageNum=0&amp;refId=50H6yCrEXIuhgr6eqEojNg%3D%3D&amp;trackingId=brdZZnynoUz1kG72mAhlOg%3D%3D</t>
+          <t>https://nl.linkedin.com/jobs/view/e-commerce-data-analyst-at-my-jewellery-4458352332?position=24&amp;pageNum=0&amp;refId=oiBIn1Czflg0JjZjH5z0Lg%3D%3D&amp;trackingId=l7ZuY53wCY8i%2FsbUtVRI1w%3D%3D</t>
         </is>
       </c>
     </row>
@@ -8672,17 +8672,17 @@
       </c>
       <c r="B130" s="3" t="inlineStr">
         <is>
-          <t>Total Rewards Analyst | Corporate Services | Dubai</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="C130" s="3" t="inlineStr">
         <is>
-          <t>Al-Futtaim</t>
+          <t>Kitopi</t>
         </is>
       </c>
       <c r="D130" s="3" t="inlineStr">
         <is>
-          <t>Dubai, Dubai, United Arab Emirates</t>
+          <t>Dubai, United Arab Emirates</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
@@ -8700,7 +8700,7 @@
       </c>
       <c r="H130" s="3" t="inlineStr">
         <is>
-          <t>This is a Total Rewards (compensation and benefits) HR analyst role focused on HRIS systems, pay equity, and market benchmarking, completely unrelated to the candidate's core specialization in Generative AI, LLMs, and agentic workflows.</t>
+          <t>This is a role for a Senior Data Engineer focused on building data pipelines, ELT processes, Snowflake, and dbt, which is completely unrelated to the candidate's core specialization as a Lead Data Scientist specializing in GenAI, LLMs, and agentic workflows.</t>
         </is>
       </c>
       <c r="I130" s="3" t="inlineStr">
@@ -8725,7 +8725,7 @@
       </c>
       <c r="M130" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/total-rewards-analyst-corporate-services-dubai-at-al-futtaim-4449646903?position=8&amp;pageNum=0&amp;refId=50H6yCrEXIuhgr6eqEojNg%3D%3D&amp;trackingId=ZNz4Qjdr30DeI436luixFQ%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/senior-data-engineer-at-kitopi-4457746184?position=4&amp;pageNum=0&amp;refId=50H6yCrEXIuhgr6eqEojNg%3D%3D&amp;trackingId=brdZZnynoUz1kG72mAhlOg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -8735,12 +8735,12 @@
       </c>
       <c r="B131" s="3" t="inlineStr">
         <is>
-          <t>Senior Technical Software Engineer - AI Computer Vision</t>
+          <t>Total Rewards Analyst | Corporate Services | Dubai</t>
         </is>
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t>Emirates</t>
+          <t>Al-Futtaim</t>
         </is>
       </c>
       <c r="D131" s="3" t="inlineStr">
@@ -8763,7 +8763,7 @@
       </c>
       <c r="H131" s="3" t="inlineStr">
         <is>
-          <t>This role is focused heavily on Computer Vision, video analytics, GPU-accelerated pipelines, and NVIDIA technologies (DeepStream, TensorRT, CUDA), which falls completely outside the candidate's core specialization in LLMs, RAG, and agentic AI. Although the candidate has foundational Python and ML experience, the domain mismatch results in a very low fit.</t>
+          <t>This is a Total Rewards (compensation and benefits) HR analyst role focused on HRIS systems, pay equity, and market benchmarking, completely unrelated to the candidate's core specialization in Generative AI, LLMs, and agentic workflows.</t>
         </is>
       </c>
       <c r="I131" s="3" t="inlineStr">
@@ -8788,7 +8788,7 @@
       </c>
       <c r="M131" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/senior-technical-software-engineer-ai-computer-vision-at-emirates-4458006917?position=3&amp;pageNum=0&amp;refId=zJBbvwb5H0wsbJ5fs9ZTVw%3D%3D&amp;trackingId=tSUvFCM6ybpvpE988Qbxew%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/total-rewards-analyst-corporate-services-dubai-at-al-futtaim-4449646903?position=8&amp;pageNum=0&amp;refId=50H6yCrEXIuhgr6eqEojNg%3D%3D&amp;trackingId=ZNz4Qjdr30DeI436luixFQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -8798,12 +8798,12 @@
       </c>
       <c r="B132" s="3" t="inlineStr">
         <is>
-          <t>OLIVER WYMAN - CORE CONSULTING GROUP - CONSULTANT MIDDLE EAST</t>
+          <t>Senior Technical Software Engineer - AI Computer Vision</t>
         </is>
       </c>
       <c r="C132" s="3" t="inlineStr">
         <is>
-          <t>Oliver Wyman</t>
+          <t>Emirates</t>
         </is>
       </c>
       <c r="D132" s="3" t="inlineStr">
@@ -8813,7 +8813,7 @@
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F132" s="7" t="n">
@@ -8826,7 +8826,7 @@
       </c>
       <c r="H132" s="3" t="inlineStr">
         <is>
-          <t>This is a general management consulting role at Oliver Wyman rather than a technical data science or GenAI position, representing a significant domain and career path mismatch for the candidate's deep technical specialization.</t>
+          <t>This role is focused heavily on Computer Vision, video analytics, GPU-accelerated pipelines, and NVIDIA technologies (DeepStream, TensorRT, CUDA), which falls completely outside the candidate's core specialization in LLMs, RAG, and agentic AI. Although the candidate has foundational Python and ML experience, the domain mismatch results in a very low fit.</t>
         </is>
       </c>
       <c r="I132" s="3" t="inlineStr">
@@ -8851,7 +8851,7 @@
       </c>
       <c r="M132" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/oliver-wyman-core-consulting-group-consultant-middle-east-at-oliver-wyman-4460347959?position=9&amp;pageNum=0&amp;refId=umynRMWB8laV9lcrAC5yvg%3D%3D&amp;trackingId=aruth9erwHbRMnXOXEO4Sg%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/senior-technical-software-engineer-ai-computer-vision-at-emirates-4458006917?position=3&amp;pageNum=0&amp;refId=zJBbvwb5H0wsbJ5fs9ZTVw%3D%3D&amp;trackingId=tSUvFCM6ybpvpE988Qbxew%3D%3D</t>
         </is>
       </c>
     </row>
@@ -8861,12 +8861,12 @@
       </c>
       <c r="B133" s="3" t="inlineStr">
         <is>
-          <t>Manager - Analytics</t>
+          <t>OLIVER WYMAN - CORE CONSULTING GROUP - CONSULTANT MIDDLE EAST</t>
         </is>
       </c>
       <c r="C133" s="3" t="inlineStr">
         <is>
-          <t>Publicis Groupe Middle East</t>
+          <t>Oliver Wyman</t>
         </is>
       </c>
       <c r="D133" s="3" t="inlineStr">
@@ -8889,12 +8889,12 @@
       </c>
       <c r="H133" s="3" t="inlineStr">
         <is>
-          <t>This role focuses entirely on marketing mix modeling and econometrics rather than Generative AI or LLMs. While the candidate has classical statistical and Python experience, the domain mismatch makes this a poor fit.</t>
+          <t>This is a general management consulting role at Oliver Wyman rather than a technical data science or GenAI position, representing a significant domain and career path mismatch for the candidate's deep technical specialization.</t>
         </is>
       </c>
       <c r="I133" s="3" t="inlineStr">
         <is>
-          <t>No - English fluency stated as sufficient</t>
+          <t>Not stated in JD</t>
         </is>
       </c>
       <c r="J133" s="3" t="inlineStr">
@@ -8914,7 +8914,7 @@
       </c>
       <c r="M133" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/manager-analytics-at-publicis-groupe-middle-east-4256186272?position=2&amp;pageNum=0&amp;refId=umynRMWB8laV9lcrAC5yvg%3D%3D&amp;trackingId=k7%2Bky5b7RnFYcRCK%2Bsft9Q%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/oliver-wyman-core-consulting-group-consultant-middle-east-at-oliver-wyman-4460347959?position=9&amp;pageNum=0&amp;refId=umynRMWB8laV9lcrAC5yvg%3D%3D&amp;trackingId=aruth9erwHbRMnXOXEO4Sg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -8924,22 +8924,22 @@
       </c>
       <c r="B134" s="3" t="inlineStr">
         <is>
-          <t>Postdoctoral Researcher in AI for Testing and Threat Detection : Computer Science and Engineeing (CSE)-College of Engineering</t>
+          <t>Manager - Analytics</t>
         </is>
       </c>
       <c r="C134" s="3" t="inlineStr">
         <is>
-          <t>American University of Sharjah</t>
+          <t>Publicis Groupe Middle East</t>
         </is>
       </c>
       <c r="D134" s="3" t="inlineStr">
         <is>
-          <t>Sharjah, Sharjah Emirate, United Arab Emirates</t>
+          <t>Dubai, Dubai, United Arab Emirates</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="F134" s="7" t="n">
@@ -8952,12 +8952,12 @@
       </c>
       <c r="H134" s="3" t="inlineStr">
         <is>
-          <t>This is a Postdoctoral Researcher role in an academic setting focused on reinforcement learning, formal verification, and threat detection, requiring a recent PhD, which completely mismatches the candidate's industry-focused Lead Data Scientist profile and 10+ years of corporate GenAI/RAG experience.</t>
+          <t>This role focuses entirely on marketing mix modeling and econometrics rather than Generative AI or LLMs. While the candidate has classical statistical and Python experience, the domain mismatch makes this a poor fit.</t>
         </is>
       </c>
       <c r="I134" s="3" t="inlineStr">
         <is>
-          <t>Not stated in JD</t>
+          <t>No - English fluency stated as sufficient</t>
         </is>
       </c>
       <c r="J134" s="3" t="inlineStr">
@@ -8965,9 +8965,9 @@
           <t>Not stated in JD</t>
         </is>
       </c>
-      <c r="K134" s="9" t="inlineStr">
-        <is>
-          <t>New this run (2026-08-29 19:27 UTC)</t>
+      <c r="K134" s="2" t="inlineStr">
+        <is>
+          <t>From previous run</t>
         </is>
       </c>
       <c r="L134" s="2" t="inlineStr">
@@ -8977,7 +8977,7 @@
       </c>
       <c r="M134" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/postdoctoral-researcher-in-ai-for-testing-and-threat-detection-computer-science-and-engineeing-cse-college-of-engineering-at-american-university-of-sharjah-4423527619?position=2&amp;pageNum=0&amp;refId=ObYT%2FC%2FLT0LzMJUTwHqKZQ%3D%3D&amp;trackingId=FMQzyAWSKj5TyGLquO63tw%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/manager-analytics-at-publicis-groupe-middle-east-4256186272?position=2&amp;pageNum=0&amp;refId=umynRMWB8laV9lcrAC5yvg%3D%3D&amp;trackingId=k7%2Bky5b7RnFYcRCK%2Bsft9Q%3D%3D</t>
         </is>
       </c>
     </row>
@@ -8987,17 +8987,17 @@
       </c>
       <c r="B135" s="3" t="inlineStr">
         <is>
-          <t>Fitch Learning | Data Science Trainer, Associate Director - Dubai, UAE</t>
+          <t>Postdoctoral Researcher in AI for Testing and Threat Detection : Computer Science and Engineeing (CSE)-College of Engineering</t>
         </is>
       </c>
       <c r="C135" s="3" t="inlineStr">
         <is>
-          <t>Fitch Ratings</t>
+          <t>American University of Sharjah</t>
         </is>
       </c>
       <c r="D135" s="3" t="inlineStr">
         <is>
-          <t>Dubai, Dubai, United Arab Emirates</t>
+          <t>Sharjah, Sharjah Emirate, United Arab Emirates</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
@@ -9015,7 +9015,7 @@
       </c>
       <c r="H135" s="3" t="inlineStr">
         <is>
-          <t>This role is for a Data Science Trainer focusing on teaching professional learners, which is a significant mismatch for a hands-on technical Lead Data Scientist specializing in GenAI engineering and agentic workflows.</t>
+          <t>This is a Postdoctoral Researcher role in an academic setting focused on reinforcement learning, formal verification, and threat detection, requiring a recent PhD, which completely mismatches the candidate's industry-focused Lead Data Scientist profile and 10+ years of corporate GenAI/RAG experience.</t>
         </is>
       </c>
       <c r="I135" s="3" t="inlineStr">
@@ -9028,9 +9028,9 @@
           <t>Not stated in JD</t>
         </is>
       </c>
-      <c r="K135" s="9" t="inlineStr">
-        <is>
-          <t>New this run (2026-08-29 19:27 UTC)</t>
+      <c r="K135" s="2" t="inlineStr">
+        <is>
+          <t>From previous run</t>
         </is>
       </c>
       <c r="L135" s="2" t="inlineStr">
@@ -9040,7 +9040,7 @@
       </c>
       <c r="M135" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/fitch-learning-data-science-trainer-associate-director-dubai-uae-at-fitch-ratings-4413826649?position=3&amp;pageNum=0&amp;refId=ObYT%2FC%2FLT0LzMJUTwHqKZQ%3D%3D&amp;trackingId=%2B6ZDB6n4%2BzrdaJhgz1Rx5A%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/postdoctoral-researcher-in-ai-for-testing-and-threat-detection-computer-science-and-engineeing-cse-college-of-engineering-at-american-university-of-sharjah-4423527619?position=2&amp;pageNum=0&amp;refId=ObYT%2FC%2FLT0LzMJUTwHqKZQ%3D%3D&amp;trackingId=FMQzyAWSKj5TyGLquO63tw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -9050,26 +9050,26 @@
       </c>
       <c r="B136" s="3" t="inlineStr">
         <is>
-          <t>Graphene Photonics Data Analyst (f/m/d)</t>
+          <t>Fitch Learning | Data Science Trainer, Associate Director - Dubai, UAE</t>
         </is>
       </c>
       <c r="C136" s="3" t="inlineStr">
         <is>
-          <t>Black Semiconductor</t>
+          <t>Fitch Ratings</t>
         </is>
       </c>
       <c r="D136" s="3" t="inlineStr">
         <is>
-          <t>Aachen, North Rhine-Westphalia, Germany</t>
+          <t>Dubai, Dubai, United Arab Emirates</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="F136" s="7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G136" s="8" t="inlineStr">
         <is>
@@ -9078,7 +9078,7 @@
       </c>
       <c r="H136" s="3" t="inlineStr">
         <is>
-          <t>This role is entirely focused on semiconductor hardware, graphene photonics, and physical data analysis, with zero relevance to the candidate's core specialization in Generative AI, LLMs, and agentic workflows.</t>
+          <t>This role is for a Data Science Trainer focusing on teaching professional learners, which is a significant mismatch for a hands-on technical Lead Data Scientist specializing in GenAI engineering and agentic workflows.</t>
         </is>
       </c>
       <c r="I136" s="3" t="inlineStr">
@@ -9103,7 +9103,7 @@
       </c>
       <c r="M136" s="6" t="inlineStr">
         <is>
-          <t>https://de.linkedin.com/jobs/view/graphene-photonics-data-analyst-f-m-d-at-black-semiconductor-4459334621?position=26&amp;pageNum=0&amp;refId=T%2F0KkBXL%2Fl%2B5Iv5tUGTY7Q%3D%3D&amp;trackingId=KgQ01De6ChDgIN8UxnUvXg%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/fitch-learning-data-science-trainer-associate-director-dubai-uae-at-fitch-ratings-4413826649?position=3&amp;pageNum=0&amp;refId=ObYT%2FC%2FLT0LzMJUTwHqKZQ%3D%3D&amp;trackingId=%2B6ZDB6n4%2BzrdaJhgz1Rx5A%3D%3D</t>
         </is>
       </c>
     </row>
@@ -9113,17 +9113,17 @@
       </c>
       <c r="B137" s="3" t="inlineStr">
         <is>
-          <t>Financial Planning and Analysis Manager</t>
+          <t>Graphene Photonics Data Analyst (f/m/d)</t>
         </is>
       </c>
       <c r="C137" s="3" t="inlineStr">
         <is>
-          <t>Confidential Jobs</t>
+          <t>Black Semiconductor</t>
         </is>
       </c>
       <c r="D137" s="3" t="inlineStr">
         <is>
-          <t>Dubai, United Arab Emirates</t>
+          <t>Aachen, North Rhine-Westphalia, Germany</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
@@ -9141,7 +9141,7 @@
       </c>
       <c r="H137" s="3" t="inlineStr">
         <is>
-          <t>This Financial Planning and Analysis Manager role is entirely unrelated to data science, machine learning, or software engineering, focusing instead on corporate finance, budgeting, construction economics, and IFRS 15 accounting. There is a massive domain and seniority mismatch for an AI/GenAI Lead Data Scientist.</t>
+          <t>This role is entirely focused on semiconductor hardware, graphene photonics, and physical data analysis, with zero relevance to the candidate's core specialization in Generative AI, LLMs, and agentic workflows.</t>
         </is>
       </c>
       <c r="I137" s="3" t="inlineStr">
@@ -9166,7 +9166,7 @@
       </c>
       <c r="M137" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/financial-planning-and-analysis-manager-at-confidential-jobs-4452594332?position=29&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=KEfZVTEknZKckxH1vstrzQ%3D%3D</t>
+          <t>https://de.linkedin.com/jobs/view/graphene-photonics-data-analyst-f-m-d-at-black-semiconductor-4459334621?position=26&amp;pageNum=0&amp;refId=T%2F0KkBXL%2Fl%2B5Iv5tUGTY7Q%3D%3D&amp;trackingId=KgQ01De6ChDgIN8UxnUvXg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -9176,17 +9176,17 @@
       </c>
       <c r="B138" s="3" t="inlineStr">
         <is>
-          <t>Data QA Engineer</t>
+          <t>Financial Planning and Analysis Manager</t>
         </is>
       </c>
       <c r="C138" s="3" t="inlineStr">
         <is>
-          <t>ClearGrid</t>
+          <t>Confidential Jobs</t>
         </is>
       </c>
       <c r="D138" s="3" t="inlineStr">
         <is>
-          <t>Dubai, Dubai, United Arab Emirates</t>
+          <t>Dubai, United Arab Emirates</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
@@ -9204,7 +9204,7 @@
       </c>
       <c r="H138" s="3" t="inlineStr">
         <is>
-          <t>This role is a Data QA Engineer focused entirely on data quality, dbt testing, and warehouse reconciliation in a fintech/collections environment, lacking any Generative AI, LLM, or agentic specialization. Furthermore, the seniority requirement (2+ years) is well below the candidate's 10+ years as a Lead Data Scientist.</t>
+          <t>This Financial Planning and Analysis Manager role is entirely unrelated to data science, machine learning, or software engineering, focusing instead on corporate finance, budgeting, construction economics, and IFRS 15 accounting. There is a massive domain and seniority mismatch for an AI/GenAI Lead Data Scientist.</t>
         </is>
       </c>
       <c r="I138" s="3" t="inlineStr">
@@ -9229,7 +9229,7 @@
       </c>
       <c r="M138" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/data-qa-engineer-at-cleargrid-4457980735?position=25&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=RbMMQ6DAm%2FMomlqBLUM2IQ%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/financial-planning-and-analysis-manager-at-confidential-jobs-4452594332?position=29&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=KEfZVTEknZKckxH1vstrzQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -9239,12 +9239,12 @@
       </c>
       <c r="B139" s="3" t="inlineStr">
         <is>
-          <t>OTR Planning Manager, Hub Delivery UAE , Hub Delivery</t>
+          <t>Data QA Engineer</t>
         </is>
       </c>
       <c r="C139" s="3" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>ClearGrid</t>
         </is>
       </c>
       <c r="D139" s="3" t="inlineStr">
@@ -9267,7 +9267,7 @@
       </c>
       <c r="H139" s="3" t="inlineStr">
         <is>
-          <t>This operations and logistics management role is entirely unrelated to data science, machine learning, and Generative AI, focusing instead on supply chain planning and fleet management. Therefore, it is a very poor match for the candidate's core specialization.</t>
+          <t>This role is a Data QA Engineer focused entirely on data quality, dbt testing, and warehouse reconciliation in a fintech/collections environment, lacking any Generative AI, LLM, or agentic specialization. Furthermore, the seniority requirement (2+ years) is well below the candidate's 10+ years as a Lead Data Scientist.</t>
         </is>
       </c>
       <c r="I139" s="3" t="inlineStr">
@@ -9292,7 +9292,7 @@
       </c>
       <c r="M139" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/otr-planning-manager-hub-delivery-uae-hub-delivery-at-amazon-4459184678?position=21&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=bqoXqft%2BGFtLz05C2kL0FA%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/data-qa-engineer-at-cleargrid-4457980735?position=25&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=RbMMQ6DAm%2FMomlqBLUM2IQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -9302,12 +9302,12 @@
       </c>
       <c r="B140" s="3" t="inlineStr">
         <is>
-          <t>Senior Compensation Analyst</t>
+          <t>OTR Planning Manager, Hub Delivery UAE , Hub Delivery</t>
         </is>
       </c>
       <c r="C140" s="3" t="inlineStr">
         <is>
-          <t>Cartier</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="D140" s="3" t="inlineStr">
@@ -9330,7 +9330,7 @@
       </c>
       <c r="H140" s="3" t="inlineStr">
         <is>
-          <t>This is a non-technical role focused strictly on compensation analysis, financial modeling, and advanced Excel simulation design within HR, which has no overlap with the candidate's core GenAI, LLM, or data science specialization.</t>
+          <t>This operations and logistics management role is entirely unrelated to data science, machine learning, and Generative AI, focusing instead on supply chain planning and fleet management. Therefore, it is a very poor match for the candidate's core specialization.</t>
         </is>
       </c>
       <c r="I140" s="3" t="inlineStr">
@@ -9355,7 +9355,7 @@
       </c>
       <c r="M140" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/senior-compensation-analyst-at-cartier-4448528069?position=20&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=uU%2BxMpwsg7Xv71%2Fjk83xeg%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/otr-planning-manager-hub-delivery-uae-hub-delivery-at-amazon-4459184678?position=21&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=bqoXqft%2BGFtLz05C2kL0FA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -9365,12 +9365,12 @@
       </c>
       <c r="B141" s="3" t="inlineStr">
         <is>
-          <t>AI &amp; Data - BrightStar program - Part-Time For Students | UAE Nationals Only - Dubai</t>
+          <t>Senior Compensation Analyst</t>
         </is>
       </c>
       <c r="C141" s="3" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Cartier</t>
         </is>
       </c>
       <c r="D141" s="3" t="inlineStr">
@@ -9393,7 +9393,7 @@
       </c>
       <c r="H141" s="3" t="inlineStr">
         <is>
-          <t>This student internship/part-time program is an extreme seniority mismatch for a Lead Data Scientist with 10+ years of experience. Furthermore, the role is strictly restricted to UAE Nationals and unrelated to the candidate's specialized GenAI and agentic AI expertise.</t>
+          <t>This is a non-technical role focused strictly on compensation analysis, financial modeling, and advanced Excel simulation design within HR, which has no overlap with the candidate's core GenAI, LLM, or data science specialization.</t>
         </is>
       </c>
       <c r="I141" s="3" t="inlineStr">
@@ -9418,7 +9418,7 @@
       </c>
       <c r="M141" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/ai-data-brightstar-program-part-time-for-students-uae-nationals-only-dubai-at-deloitte-4459165278?position=18&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=rkeXlOzDBapH9BYwLoMUoA%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/senior-compensation-analyst-at-cartier-4448528069?position=20&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=uU%2BxMpwsg7Xv71%2Fjk83xeg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -9428,12 +9428,12 @@
       </c>
       <c r="B142" s="3" t="inlineStr">
         <is>
-          <t>Junior Market Analyst - UAE National</t>
+          <t>AI &amp; Data - BrightStar program - Part-Time For Students | UAE Nationals Only - Dubai</t>
         </is>
       </c>
       <c r="C142" s="3" t="inlineStr">
         <is>
-          <t>Richemont</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="D142" s="3" t="inlineStr">
@@ -9456,7 +9456,7 @@
       </c>
       <c r="H142" s="3" t="inlineStr">
         <is>
-          <t>This role is a junior market research and business development position focused on luxury retail intelligence in the MEIAT region, which is completely unrelated to data science, artificial intelligence, or the candidate's GenAI and LLM specialization.</t>
+          <t>This student internship/part-time program is an extreme seniority mismatch for a Lead Data Scientist with 10+ years of experience. Furthermore, the role is strictly restricted to UAE Nationals and unrelated to the candidate's specialized GenAI and agentic AI expertise.</t>
         </is>
       </c>
       <c r="I142" s="3" t="inlineStr">
@@ -9481,7 +9481,7 @@
       </c>
       <c r="M142" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/junior-market-analyst-uae-national-at-richemont-4448527067?position=22&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=fabWFpBqiTWxCuIFUXVosg%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/ai-data-brightstar-program-part-time-for-students-uae-nationals-only-dubai-at-deloitte-4459165278?position=18&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=rkeXlOzDBapH9BYwLoMUoA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -9491,12 +9491,12 @@
       </c>
       <c r="B143" s="3" t="inlineStr">
         <is>
-          <t>Data Analyst - (Advanced Excel expertise)</t>
+          <t>Junior Market Analyst - UAE National</t>
         </is>
       </c>
       <c r="C143" s="3" t="inlineStr">
         <is>
-          <t>BigTapp Analytics</t>
+          <t>Richemont</t>
         </is>
       </c>
       <c r="D143" s="3" t="inlineStr">
@@ -9519,7 +9519,7 @@
       </c>
       <c r="H143" s="3" t="inlineStr">
         <is>
-          <t>This is a Data Analyst role focused entirely on Advanced Excel, corporate tax data quality, and data validation, with no connection to the candidate's GenAI, LLM, or agentic AI specialization.</t>
+          <t>This role is a junior market research and business development position focused on luxury retail intelligence in the MEIAT region, which is completely unrelated to data science, artificial intelligence, or the candidate's GenAI and LLM specialization.</t>
         </is>
       </c>
       <c r="I143" s="3" t="inlineStr">
@@ -9544,7 +9544,7 @@
       </c>
       <c r="M143" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/data-analyst-advanced-excel-expertise-at-bigtapp-analytics-4459194093?position=16&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=vJ8ubhhJtvsWirwhmdkH%2BA%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/junior-market-analyst-uae-national-at-richemont-4448527067?position=22&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=fabWFpBqiTWxCuIFUXVosg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -9554,17 +9554,17 @@
       </c>
       <c r="B144" s="3" t="inlineStr">
         <is>
-          <t>Junior Data Analyst</t>
+          <t>Data Analyst - (Advanced Excel expertise)</t>
         </is>
       </c>
       <c r="C144" s="3" t="inlineStr">
         <is>
-          <t>Arabian Private Holdings</t>
+          <t>BigTapp Analytics</t>
         </is>
       </c>
       <c r="D144" s="3" t="inlineStr">
         <is>
-          <t>Sharjah, Sharjah Emirate, United Arab Emirates</t>
+          <t>Dubai, Dubai, United Arab Emirates</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
@@ -9582,7 +9582,7 @@
       </c>
       <c r="H144" s="3" t="inlineStr">
         <is>
-          <t>This is a junior data analyst role focused on operational data interpretation, basic SQL/Excel database maintenance, and corporate strategy support, completely unrelated to the candidate's GenAI, LLMs, and agentic AI specialization. Additionally, there is a severe seniority mismatch as the role is strictly junior while the candidate is a Lead Data Scientist with 10+ years of experience.</t>
+          <t>This is a Data Analyst role focused entirely on Advanced Excel, corporate tax data quality, and data validation, with no connection to the candidate's GenAI, LLM, or agentic AI specialization.</t>
         </is>
       </c>
       <c r="I144" s="3" t="inlineStr">
@@ -9607,7 +9607,7 @@
       </c>
       <c r="M144" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/junior-data-analyst-at-arabian-private-holdings-4457918646?position=11&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=n3OKFNsTAywRSCMqHYFmlg%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/data-analyst-advanced-excel-expertise-at-bigtapp-analytics-4459194093?position=16&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=vJ8ubhhJtvsWirwhmdkH%2BA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -9617,17 +9617,17 @@
       </c>
       <c r="B145" s="3" t="inlineStr">
         <is>
-          <t>Data Analyst – Social Support Operations - UAE National</t>
+          <t>Junior Data Analyst</t>
         </is>
       </c>
       <c r="C145" s="3" t="inlineStr">
         <is>
-          <t>Ministry of Community Empowerment</t>
+          <t>Arabian Private Holdings</t>
         </is>
       </c>
       <c r="D145" s="3" t="inlineStr">
         <is>
-          <t>Dubai, United Arab Emirates</t>
+          <t>Sharjah, Sharjah Emirate, United Arab Emirates</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
@@ -9645,7 +9645,7 @@
       </c>
       <c r="H145" s="3" t="inlineStr">
         <is>
-          <t>This role is a data analyst position focused on BI, Power BI dashboards, SQL, and social support operations, which is completely unrelated to the candidate's core GenAI, LLMs, and agentic AI specialization. Additionally, it specifies a nationality requirement.</t>
+          <t>This is a junior data analyst role focused on operational data interpretation, basic SQL/Excel database maintenance, and corporate strategy support, completely unrelated to the candidate's GenAI, LLMs, and agentic AI specialization. Additionally, there is a severe seniority mismatch as the role is strictly junior while the candidate is a Lead Data Scientist with 10+ years of experience.</t>
         </is>
       </c>
       <c r="I145" s="3" t="inlineStr">
@@ -9670,7 +9670,7 @@
       </c>
       <c r="M145" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/data-analyst-%E2%80%93-social-support-operations-uae-national-at-ministry-of-community-empowerment-4459118725?position=4&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=q%2FHUZ0XJHF5eY2WSwIWmAg%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/junior-data-analyst-at-arabian-private-holdings-4457918646?position=11&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=n3OKFNsTAywRSCMqHYFmlg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -9680,17 +9680,17 @@
       </c>
       <c r="B146" s="3" t="inlineStr">
         <is>
-          <t>Graduate - Data Scientist إماراتيين (خلاصة القيد)</t>
+          <t>Data Analyst – Social Support Operations - UAE National</t>
         </is>
       </c>
       <c r="C146" s="3" t="inlineStr">
         <is>
-          <t>AECOM</t>
+          <t>Ministry of Community Empowerment</t>
         </is>
       </c>
       <c r="D146" s="3" t="inlineStr">
         <is>
-          <t>Dubai, Dubai, United Arab Emirates</t>
+          <t>Dubai, United Arab Emirates</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
@@ -9708,7 +9708,7 @@
       </c>
       <c r="H146" s="3" t="inlineStr">
         <is>
-          <t>This is a graduate/entry-level program designed specifically for recent graduates (2024-2026) and UAE Nationals, representing a severe seniority and eligibility mismatch for a Lead Data Scientist with 10+ years of experience. Furthermore, the role focuses on construction digital tools, cost management, and general data analytics rather than the candidate's core GenAI, LLMs, and agentic AI specialization.</t>
+          <t>This role is a data analyst position focused on BI, Power BI dashboards, SQL, and social support operations, which is completely unrelated to the candidate's core GenAI, LLMs, and agentic AI specialization. Additionally, it specifies a nationality requirement.</t>
         </is>
       </c>
       <c r="I146" s="3" t="inlineStr">
@@ -9733,7 +9733,7 @@
       </c>
       <c r="M146" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/graduate-data-scientist-%D8%A5%D9%85%D8%A7%D8%B1%D8%A7%D8%AA%D9%8A%D9%8A%D9%86-%D8%AE%D9%84%D8%A7%D8%B5%D8%A9-%D8%A7%D9%84%D9%82%D9%8A%D8%AF-at-aecom-4457915285?position=1&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=deUfOEFHstE7TEtandLeTg%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/data-analyst-%E2%80%93-social-support-operations-uae-national-at-ministry-of-community-empowerment-4459118725?position=4&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=q%2FHUZ0XJHF5eY2WSwIWmAg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -9743,12 +9743,12 @@
       </c>
       <c r="B147" s="3" t="inlineStr">
         <is>
-          <t>Quantitative Researcher, Quantitative Strategies</t>
+          <t>Graduate - Data Scientist إماراتيين (خلاصة القيد)</t>
         </is>
       </c>
       <c r="C147" s="3" t="inlineStr">
         <is>
-          <t>Millennium</t>
+          <t>AECOM</t>
         </is>
       </c>
       <c r="D147" s="3" t="inlineStr">
@@ -9771,7 +9771,7 @@
       </c>
       <c r="H147" s="3" t="inlineStr">
         <is>
-          <t>This role focuses entirely on quantitative finance, statistical modeling, and systematic equity trading in Asian markets, which has no overlap with the candidate's core specialization in Generative AI, LLMs, and agentic systems. Additionally, the domain requires specific desk quant trading experience that is absent from the candidate's profile.</t>
+          <t>This is a graduate/entry-level program designed specifically for recent graduates (2024-2026) and UAE Nationals, representing a severe seniority and eligibility mismatch for a Lead Data Scientist with 10+ years of experience. Furthermore, the role focuses on construction digital tools, cost management, and general data analytics rather than the candidate's core GenAI, LLMs, and agentic AI specialization.</t>
         </is>
       </c>
       <c r="I147" s="3" t="inlineStr">
@@ -9796,7 +9796,7 @@
       </c>
       <c r="M147" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/quantitative-researcher-quantitative-strategies-at-millennium-4439427782?position=2&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=uptfSAbwEngBw3yrsrQehg%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/graduate-data-scientist-%D8%A5%D9%85%D8%A7%D8%B1%D8%A7%D8%AA%D9%8A%D9%8A%D9%86-%D8%AE%D9%84%D8%A7%D8%B5%D8%A9-%D8%A7%D9%84%D9%82%D9%8A%D8%AF-at-aecom-4457915285?position=1&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=deUfOEFHstE7TEtandLeTg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -9806,12 +9806,12 @@
       </c>
       <c r="B148" s="3" t="inlineStr">
         <is>
-          <t>Analyst I - Advisory</t>
+          <t>Quantitative Researcher, Quantitative Strategies</t>
         </is>
       </c>
       <c r="C148" s="3" t="inlineStr">
         <is>
-          <t>Marsh Risk</t>
+          <t>Millennium</t>
         </is>
       </c>
       <c r="D148" s="3" t="inlineStr">
@@ -9834,7 +9834,7 @@
       </c>
       <c r="H148" s="3" t="inlineStr">
         <is>
-          <t>This is a fresh-graduate/entry-level role for recent graduates that focuses heavily on risk engineering and basic internal digitalization using Excel and Microsoft tools, which is far below the candidate's 10+ years of experience as a Lead Data Scientist specializing in advanced GenAI and agentic systems.</t>
+          <t>This role focuses entirely on quantitative finance, statistical modeling, and systematic equity trading in Asian markets, which has no overlap with the candidate's core specialization in Generative AI, LLMs, and agentic systems. Additionally, the domain requires specific desk quant trading experience that is absent from the candidate's profile.</t>
         </is>
       </c>
       <c r="I148" s="3" t="inlineStr">
@@ -9859,7 +9859,7 @@
       </c>
       <c r="M148" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/analyst-i-advisory-at-marsh-risk-4459165267?position=3&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=NpomdoqDoXrgLAw8%2BZjEQA%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/quantitative-researcher-quantitative-strategies-at-millennium-4439427782?position=2&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=uptfSAbwEngBw3yrsrQehg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -9869,17 +9869,17 @@
       </c>
       <c r="B149" s="3" t="inlineStr">
         <is>
-          <t>Demand Planner (f/m/x)</t>
+          <t>Analyst I - Advisory</t>
         </is>
       </c>
       <c r="C149" s="3" t="inlineStr">
         <is>
-          <t>HelloFresh</t>
+          <t>Marsh Risk</t>
         </is>
       </c>
       <c r="D149" s="3" t="inlineStr">
         <is>
-          <t>Amsterdam, North Holland, Netherlands</t>
+          <t>Dubai, Dubai, United Arab Emirates</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
@@ -9897,7 +9897,7 @@
       </c>
       <c r="H149" s="3" t="inlineStr">
         <is>
-          <t>This is a supply chain demand planning role requiring 2-3 years of experience in business forecasting, which is completely unrelated to the candidate's specialization in Generative AI, LLMs, and agentic systems. Furthermore, there is a severe seniority mismatch as the candidate is a Lead Data Scientist with 10+ years of experience.</t>
+          <t>This is a fresh-graduate/entry-level role for recent graduates that focuses heavily on risk engineering and basic internal digitalization using Excel and Microsoft tools, which is far below the candidate's 10+ years of experience as a Lead Data Scientist specializing in advanced GenAI and agentic systems.</t>
         </is>
       </c>
       <c r="I149" s="3" t="inlineStr">
@@ -9922,7 +9922,7 @@
       </c>
       <c r="M149" s="6" t="inlineStr">
         <is>
-          <t>https://nl.linkedin.com/jobs/view/demand-planner-f-m-x-at-hellofresh-4459621163?position=29&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=ScTLY%2B93hMGSjD1GtPlxQw%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/analyst-i-advisory-at-marsh-risk-4459165267?position=3&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=NpomdoqDoXrgLAw8%2BZjEQA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -9932,17 +9932,17 @@
       </c>
       <c r="B150" s="3" t="inlineStr">
         <is>
-          <t>Traineeship Data Analytics</t>
+          <t>Demand Planner (f/m/x)</t>
         </is>
       </c>
       <c r="C150" s="3" t="inlineStr">
         <is>
-          <t>Breinstein</t>
+          <t>HelloFresh</t>
         </is>
       </c>
       <c r="D150" s="3" t="inlineStr">
         <is>
-          <t>Groningen, Netherlands</t>
+          <t>Amsterdam, North Holland, Netherlands</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
@@ -9960,7 +9960,7 @@
       </c>
       <c r="H150" s="3" t="inlineStr">
         <is>
-          <t>This is a junior/graduate-level traineeship requiring Dutch language proficiency, which represents a severe mismatch with the candidate's 10+ years of senior experience and Generative AI/LLM specialization.</t>
+          <t>This is a supply chain demand planning role requiring 2-3 years of experience in business forecasting, which is completely unrelated to the candidate's specialization in Generative AI, LLMs, and agentic systems. Furthermore, there is a severe seniority mismatch as the candidate is a Lead Data Scientist with 10+ years of experience.</t>
         </is>
       </c>
       <c r="I150" s="3" t="inlineStr">
@@ -9985,7 +9985,7 @@
       </c>
       <c r="M150" s="6" t="inlineStr">
         <is>
-          <t>https://nl.linkedin.com/jobs/view/traineeship-data-analytics-at-breinstein-4457240429?position=18&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=09Fo%2Bt8pd71ON%2B4bzhNIXw%3D%3D</t>
+          <t>https://nl.linkedin.com/jobs/view/demand-planner-f-m-x-at-hellofresh-4459621163?position=29&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=ScTLY%2B93hMGSjD1GtPlxQw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -9995,17 +9995,17 @@
       </c>
       <c r="B151" s="3" t="inlineStr">
         <is>
-          <t>Økonom til finansielle data om pensionssektoren og investeringsfonde i Nationalbanken</t>
+          <t>Traineeship Data Analytics</t>
         </is>
       </c>
       <c r="C151" s="3" t="inlineStr">
         <is>
-          <t>Altandetlige.dk</t>
+          <t>Breinstein</t>
         </is>
       </c>
       <c r="D151" s="3" t="inlineStr">
         <is>
-          <t>Copenhagen, Capital Region of Denmark, Denmark</t>
+          <t>Groningen, Netherlands</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
@@ -10023,7 +10023,7 @@
       </c>
       <c r="H151" s="3" t="inlineStr">
         <is>
-          <t>This is a non-technical economics and financial statistics role at Denmark's central bank focusing on pension funds and investment data, which is completely unrelated to the candidate's specialization in Generative AI, LLMs, and agentic systems.</t>
+          <t>This is a junior/graduate-level traineeship requiring Dutch language proficiency, which represents a severe mismatch with the candidate's 10+ years of senior experience and Generative AI/LLM specialization.</t>
         </is>
       </c>
       <c r="I151" s="3" t="inlineStr">
@@ -10048,7 +10048,7 @@
       </c>
       <c r="M151" s="6" t="inlineStr">
         <is>
-          <t>https://dk.linkedin.com/jobs/view/%C3%B8konom-til-finansielle-data-om-pensionssektoren-og-investeringsfonde-i-nationalbanken-at-altandetlige-dk-4459168468?position=25&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=%2BEekg%2B%2FvA%2BH0hxU4LsvJ5w%3D%3D</t>
+          <t>https://nl.linkedin.com/jobs/view/traineeship-data-analytics-at-breinstein-4457240429?position=18&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=09Fo%2Bt8pd71ON%2B4bzhNIXw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -10058,17 +10058,17 @@
       </c>
       <c r="B152" s="3" t="inlineStr">
         <is>
-          <t>Lead Trading Strategist</t>
+          <t>Økonom til finansielle data om pensionssektoren og investeringsfonde i Nationalbanken</t>
         </is>
       </c>
       <c r="C152" s="3" t="inlineStr">
         <is>
-          <t>Ørsted</t>
+          <t>Altandetlige.dk</t>
         </is>
       </c>
       <c r="D152" s="3" t="inlineStr">
         <is>
-          <t>Gentofte, Capital Region of Denmark, Denmark</t>
+          <t>Copenhagen, Capital Region of Denmark, Denmark</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
@@ -10086,7 +10086,7 @@
       </c>
       <c r="H152" s="3" t="inlineStr">
         <is>
-          <t>This is a quantitative energy trading and fundamental market analysis role requiring deep domain expertise in European power markets and commodities trading, which is completely unrelated to the candidate's core GenAI, LLM, and data science specialization.</t>
+          <t>This is a non-technical economics and financial statistics role at Denmark's central bank focusing on pension funds and investment data, which is completely unrelated to the candidate's specialization in Generative AI, LLMs, and agentic systems.</t>
         </is>
       </c>
       <c r="I152" s="3" t="inlineStr">
@@ -10111,7 +10111,7 @@
       </c>
       <c r="M152" s="6" t="inlineStr">
         <is>
-          <t>https://dk.linkedin.com/jobs/view/lead-trading-strategist-at-%C3%B8rsted-4439179684?position=21&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=LxVb1rg9c7QiaOEs5%2BY%2FTw%3D%3D</t>
+          <t>https://dk.linkedin.com/jobs/view/%C3%B8konom-til-finansielle-data-om-pensionssektoren-og-investeringsfonde-i-nationalbanken-at-altandetlige-dk-4459168468?position=25&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=%2BEekg%2B%2FvA%2BH0hxU4LsvJ5w%3D%3D</t>
         </is>
       </c>
     </row>
@@ -10121,17 +10121,17 @@
       </c>
       <c r="B153" s="3" t="inlineStr">
         <is>
-          <t>Analytikere med flair for databehandling til PET's kontraspionageindsats mod Rusland</t>
+          <t>Lead Trading Strategist</t>
         </is>
       </c>
       <c r="C153" s="3" t="inlineStr">
         <is>
-          <t>Politiets Efterretningstjeneste (PET)</t>
+          <t>Ørsted</t>
         </is>
       </c>
       <c r="D153" s="3" t="inlineStr">
         <is>
-          <t>Copenhagen, Capital Region of Denmark, Denmark</t>
+          <t>Gentofte, Capital Region of Denmark, Denmark</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
@@ -10149,7 +10149,7 @@
       </c>
       <c r="H153" s="3" t="inlineStr">
         <is>
-          <t>This is a national security intelligence and counter-espionage analyst role entirely unrelated to data science, artificial intelligence, LLMs, or software engineering. It focuses on intelligence operations and telecommunications data processing rather than the candidate's core Generative AI specialization.</t>
+          <t>This is a quantitative energy trading and fundamental market analysis role requiring deep domain expertise in European power markets and commodities trading, which is completely unrelated to the candidate's core GenAI, LLM, and data science specialization.</t>
         </is>
       </c>
       <c r="I153" s="3" t="inlineStr">
@@ -10174,7 +10174,7 @@
       </c>
       <c r="M153" s="6" t="inlineStr">
         <is>
-          <t>https://dk.linkedin.com/jobs/view/analytikere-med-flair-for-databehandling-til-pet-s-kontraspionageindsats-mod-rusland-at-politiets-efterretningstjeneste-pet-4457295379?position=17&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=jfzRay2PLGqzZJAC5yISBA%3D%3D</t>
+          <t>https://dk.linkedin.com/jobs/view/lead-trading-strategist-at-%C3%B8rsted-4439179684?position=21&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=LxVb1rg9c7QiaOEs5%2BY%2FTw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -10184,17 +10184,17 @@
       </c>
       <c r="B154" s="3" t="inlineStr">
         <is>
-          <t>BI Specialist - turn healthcare data into better care decisions</t>
+          <t>Analytikere med flair for databehandling til PET's kontraspionageindsats mod Rusland</t>
         </is>
       </c>
       <c r="C154" s="3" t="inlineStr">
         <is>
-          <t>Systematic</t>
+          <t>Politiets Efterretningstjeneste (PET)</t>
         </is>
       </c>
       <c r="D154" s="3" t="inlineStr">
         <is>
-          <t>Aarhus, Central Denmark Region, Denmark</t>
+          <t>Copenhagen, Capital Region of Denmark, Denmark</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
@@ -10212,7 +10212,7 @@
       </c>
       <c r="H154" s="3" t="inlineStr">
         <is>
-          <t>This role is for a BI Specialist focusing on healthcare data systems, SQL, T-SQL, DAX, and client communication, which is completely unrelated to the candidate's core specialization in Generative AI, LLMs, and agentic AI systems. Additionally, it requires proficiency in Danish.</t>
+          <t>This is a national security intelligence and counter-espionage analyst role entirely unrelated to data science, artificial intelligence, LLMs, or software engineering. It focuses on intelligence operations and telecommunications data processing rather than the candidate's core Generative AI specialization.</t>
         </is>
       </c>
       <c r="I154" s="3" t="inlineStr">
@@ -10237,7 +10237,7 @@
       </c>
       <c r="M154" s="6" t="inlineStr">
         <is>
-          <t>https://dk.linkedin.com/jobs/view/bi-specialist-turn-healthcare-data-into-better-care-decisions-at-systematic-4449000390?position=13&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=C4YvYCcgfvLE1Lup1m630A%3D%3D</t>
+          <t>https://dk.linkedin.com/jobs/view/analytikere-med-flair-for-databehandling-til-pet-s-kontraspionageindsats-mod-rusland-at-politiets-efterretningstjeneste-pet-4457295379?position=17&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=jfzRay2PLGqzZJAC5yISBA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -10247,17 +10247,17 @@
       </c>
       <c r="B155" s="3" t="inlineStr">
         <is>
-          <t>Demand Planner (f/m/x)</t>
+          <t>BI Specialist - turn healthcare data into better care decisions</t>
         </is>
       </c>
       <c r="C155" s="3" t="inlineStr">
         <is>
-          <t>HelloFresh</t>
+          <t>Systematic</t>
         </is>
       </c>
       <c r="D155" s="3" t="inlineStr">
         <is>
-          <t>Copenhagen Municipality, Capital Region of Denmark, Denmark</t>
+          <t>Aarhus, Central Denmark Region, Denmark</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
@@ -10275,7 +10275,7 @@
       </c>
       <c r="H155" s="3" t="inlineStr">
         <is>
-          <t>This is a non-AI supply chain demand planning role focused on SQL, logistics, and forecasting metrics like MAPE, which is completely unrelated to the candidate's core GenAI, LLM, and agentic AI specialization.</t>
+          <t>This role is for a BI Specialist focusing on healthcare data systems, SQL, T-SQL, DAX, and client communication, which is completely unrelated to the candidate's core specialization in Generative AI, LLMs, and agentic AI systems. Additionally, it requires proficiency in Danish.</t>
         </is>
       </c>
       <c r="I155" s="3" t="inlineStr">
@@ -10300,7 +10300,7 @@
       </c>
       <c r="M155" s="6" t="inlineStr">
         <is>
-          <t>https://dk.linkedin.com/jobs/view/demand-planner-f-m-x-at-hellofresh-4459625132?position=6&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=%2FDvrjQmxzWwgXh6GBB3pqA%3D%3D</t>
+          <t>https://dk.linkedin.com/jobs/view/bi-specialist-turn-healthcare-data-into-better-care-decisions-at-systematic-4449000390?position=13&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=C4YvYCcgfvLE1Lup1m630A%3D%3D</t>
         </is>
       </c>
     </row>
@@ -10310,17 +10310,17 @@
       </c>
       <c r="B156" s="3" t="inlineStr">
         <is>
-          <t>Senior Analyst - Market Intelligence (Trade &amp; Commodities)</t>
+          <t>Demand Planner (f/m/x)</t>
         </is>
       </c>
       <c r="C156" s="3" t="inlineStr">
         <is>
-          <t>Robert Walters</t>
+          <t>HelloFresh</t>
         </is>
       </c>
       <c r="D156" s="3" t="inlineStr">
         <is>
-          <t>Abu Dhabi, Abu Dhabi Emirate, United Arab Emirates</t>
+          <t>Copenhagen Municipality, Capital Region of Denmark, Denmark</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
@@ -10338,7 +10338,7 @@
       </c>
       <c r="H156" s="3" t="inlineStr">
         <is>
-          <t>This is a non-technical role focusing on market intelligence, trade flows, and supply chain analysis requiring Arabic fluency, which has no overlap with the candidate's core GenAI, LLMs, and agentic AI specialization.</t>
+          <t>This is a non-AI supply chain demand planning role focused on SQL, logistics, and forecasting metrics like MAPE, which is completely unrelated to the candidate's core GenAI, LLM, and agentic AI specialization.</t>
         </is>
       </c>
       <c r="I156" s="3" t="inlineStr">
@@ -10363,7 +10363,7 @@
       </c>
       <c r="M156" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/senior-analyst-market-intelligence-trade-commodities-at-robert-walters-4457222382?position=30&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=JK2lIzdStMxW3Rb1o%2FxSgQ%3D%3D</t>
+          <t>https://dk.linkedin.com/jobs/view/demand-planner-f-m-x-at-hellofresh-4459625132?position=6&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=%2FDvrjQmxzWwgXh6GBB3pqA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -10373,12 +10373,12 @@
       </c>
       <c r="B157" s="3" t="inlineStr">
         <is>
-          <t>AI &amp; Data - BrightStar program - Part-Time For Students | UAE Nationals Only - Dubai</t>
+          <t>Senior Analyst - Market Intelligence (Trade &amp; Commodities)</t>
         </is>
       </c>
       <c r="C157" s="3" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Robert Walters</t>
         </is>
       </c>
       <c r="D157" s="3" t="inlineStr">
@@ -10401,7 +10401,7 @@
       </c>
       <c r="H157" s="3" t="inlineStr">
         <is>
-          <t>This is a student/internship program ('Part-Time For Students') restricted to UAE Nationals only, representing a severe seniority and eligibility mismatch for a Lead Data Scientist with 10 years of experience.</t>
+          <t>This is a non-technical role focusing on market intelligence, trade flows, and supply chain analysis requiring Arabic fluency, which has no overlap with the candidate's core GenAI, LLMs, and agentic AI specialization.</t>
         </is>
       </c>
       <c r="I157" s="3" t="inlineStr">
@@ -10426,7 +10426,7 @@
       </c>
       <c r="M157" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/ai-data-brightstar-program-part-time-for-students-uae-nationals-only-dubai-at-deloitte-4459166169?position=29&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=eJo5yKx6Zm7GgBBf0abvaA%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/senior-analyst-market-intelligence-trade-commodities-at-robert-walters-4457222382?position=30&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=JK2lIzdStMxW3Rb1o%2FxSgQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -10436,17 +10436,17 @@
       </c>
       <c r="B158" s="3" t="inlineStr">
         <is>
-          <t>SAS Analyst</t>
+          <t>AI &amp; Data - BrightStar program - Part-Time For Students | UAE Nationals Only - Dubai</t>
         </is>
       </c>
       <c r="C158" s="3" t="inlineStr">
         <is>
-          <t>One75mb HRM Pvt Ltd.</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="D158" s="3" t="inlineStr">
         <is>
-          <t>Abu Dhabi Emirate, United Arab Emirates</t>
+          <t>Abu Dhabi, Abu Dhabi Emirate, United Arab Emirates</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
@@ -10464,7 +10464,7 @@
       </c>
       <c r="H158" s="3" t="inlineStr">
         <is>
-          <t>This role is a SAS Anti-Money Laundering (AML) Developer position focused on SAS Viya, SAS programming, and compliance systems. It has no connection to Generative AI, LLMs, RAG, or agentic systems, making it an entirely irrelevant fit for a GenAI specialist.</t>
+          <t>This is a student/internship program ('Part-Time For Students') restricted to UAE Nationals only, representing a severe seniority and eligibility mismatch for a Lead Data Scientist with 10 years of experience.</t>
         </is>
       </c>
       <c r="I158" s="3" t="inlineStr">
@@ -10489,7 +10489,7 @@
       </c>
       <c r="M158" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/sas-analyst-at-one75mb-hrm-pvt-ltd-4459306494?position=19&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=NfyeO5P7KUMAsO5xQjjwEA%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/ai-data-brightstar-program-part-time-for-students-uae-nationals-only-dubai-at-deloitte-4459166169?position=29&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=eJo5yKx6Zm7GgBBf0abvaA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -10499,17 +10499,17 @@
       </c>
       <c r="B159" s="3" t="inlineStr">
         <is>
-          <t>Finance Information Systems Analyst</t>
+          <t>SAS Analyst</t>
         </is>
       </c>
       <c r="C159" s="3" t="inlineStr">
         <is>
-          <t>United Arab Emirates University, Department of Family Medicine</t>
+          <t>One75mb HRM Pvt Ltd.</t>
         </is>
       </c>
       <c r="D159" s="3" t="inlineStr">
         <is>
-          <t>Abu Dhabi, Abu Dhabi Emirate, United Arab Emirates</t>
+          <t>Abu Dhabi Emirate, United Arab Emirates</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
@@ -10527,7 +10527,7 @@
       </c>
       <c r="H159" s="3" t="inlineStr">
         <is>
-          <t>This role is for a Finance Information Systems Analyst focusing on Oracle SQL, financial reporting, and system maintenance, which is completely unrelated to the candidate's core expertise in Generative AI, LLMs, and agentic workflows.</t>
+          <t>This role is a SAS Anti-Money Laundering (AML) Developer position focused on SAS Viya, SAS programming, and compliance systems. It has no connection to Generative AI, LLMs, RAG, or agentic systems, making it an entirely irrelevant fit for a GenAI specialist.</t>
         </is>
       </c>
       <c r="I159" s="3" t="inlineStr">
@@ -10552,7 +10552,7 @@
       </c>
       <c r="M159" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/finance-information-systems-analyst-at-united-arab-emirates-university-department-of-family-medicine-4458309884?position=18&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=ZkLRAbbB1OpTP3DQTi%2FB4Q%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/sas-analyst-at-one75mb-hrm-pvt-ltd-4459306494?position=19&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=NfyeO5P7KUMAsO5xQjjwEA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -10562,12 +10562,12 @@
       </c>
       <c r="B160" s="3" t="inlineStr">
         <is>
-          <t>Analyst I - Advisory</t>
+          <t>Finance Information Systems Analyst</t>
         </is>
       </c>
       <c r="C160" s="3" t="inlineStr">
         <is>
-          <t>Marsh Risk</t>
+          <t>United Arab Emirates University, Department of Family Medicine</t>
         </is>
       </c>
       <c r="D160" s="3" t="inlineStr">
@@ -10590,7 +10590,7 @@
       </c>
       <c r="H160" s="3" t="inlineStr">
         <is>
-          <t>This is a graduate/entry-level risk engineering and data analyst role located in the UAE restricted to UAE Nationals, representing a severe mismatch in both seniority and specialization for a Lead Data Scientist with 10+ years of experience in GenAI.</t>
+          <t>This role is for a Finance Information Systems Analyst focusing on Oracle SQL, financial reporting, and system maintenance, which is completely unrelated to the candidate's core expertise in Generative AI, LLMs, and agentic workflows.</t>
         </is>
       </c>
       <c r="I160" s="3" t="inlineStr">
@@ -10615,7 +10615,7 @@
       </c>
       <c r="M160" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/analyst-i-advisory-at-marsh-risk-4459170127?position=6&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=hO0QLO%2FIAeXdRsG2PtQkTA%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/finance-information-systems-analyst-at-united-arab-emirates-university-department-of-family-medicine-4458309884?position=18&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=ZkLRAbbB1OpTP3DQTi%2FB4Q%3D%3D</t>
         </is>
       </c>
     </row>
@@ -10625,12 +10625,12 @@
       </c>
       <c r="B161" s="3" t="inlineStr">
         <is>
-          <t>Senior Economist / Economic Researcher</t>
+          <t>Analyst I - Advisory</t>
         </is>
       </c>
       <c r="C161" s="3" t="inlineStr">
         <is>
-          <t>Robert Walters</t>
+          <t>Marsh Risk</t>
         </is>
       </c>
       <c r="D161" s="3" t="inlineStr">
@@ -10653,7 +10653,7 @@
       </c>
       <c r="H161" s="3" t="inlineStr">
         <is>
-          <t>This role is for a Senior Economist focusing on macroeconomic research, policy analysis, and economic forecasting, which is completely unrelated to the candidate's specialization in Generative AI, LLMs, and data science.</t>
+          <t>This is a graduate/entry-level risk engineering and data analyst role located in the UAE restricted to UAE Nationals, representing a severe mismatch in both seniority and specialization for a Lead Data Scientist with 10+ years of experience in GenAI.</t>
         </is>
       </c>
       <c r="I161" s="3" t="inlineStr">
@@ -10678,7 +10678,7 @@
       </c>
       <c r="M161" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/senior-economist-economic-researcher-at-robert-walters-4457234594?position=21&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=hNkG3K%2BgFb1grR8QDMiBxA%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/analyst-i-advisory-at-marsh-risk-4459170127?position=6&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=hO0QLO%2FIAeXdRsG2PtQkTA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -10688,22 +10688,22 @@
       </c>
       <c r="B162" s="3" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Economist / Economic Researcher</t>
         </is>
       </c>
       <c r="C162" s="3" t="inlineStr">
         <is>
-          <t>ChipSoft Nederland</t>
+          <t>Robert Walters</t>
         </is>
       </c>
       <c r="D162" s="3" t="inlineStr">
         <is>
-          <t>Amsterdam, North Holland, Netherlands</t>
+          <t>Abu Dhabi, Abu Dhabi Emirate, United Arab Emirates</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F162" s="7" t="n">
@@ -10716,7 +10716,7 @@
       </c>
       <c r="H162" s="3" t="inlineStr">
         <is>
-          <t>This is a Data Engineer role focused on ELT, SQL, data warehousing, and clickstream data, which is entirely unrelated to the candidate's core specialization in Generative AI, LLMs, and agentic systems.</t>
+          <t>This role is for a Senior Economist focusing on macroeconomic research, policy analysis, and economic forecasting, which is completely unrelated to the candidate's specialization in Generative AI, LLMs, and data science.</t>
         </is>
       </c>
       <c r="I162" s="3" t="inlineStr">
@@ -10741,7 +10741,7 @@
       </c>
       <c r="M162" s="6" t="inlineStr">
         <is>
-          <t>https://nl.linkedin.com/jobs/view/data-engineer-at-chipsoft-nederland-4448895866?position=29&amp;pageNum=0&amp;refId=oiBIn1Czflg0JjZjH5z0Lg%3D%3D&amp;trackingId=CakhxR8nCpksAoEXyMZPHQ%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/senior-economist-economic-researcher-at-robert-walters-4457234594?position=21&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=hNkG3K%2BgFb1grR8QDMiBxA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -10751,12 +10751,12 @@
       </c>
       <c r="B163" s="3" t="inlineStr">
         <is>
-          <t>Quantitative Developer - Pricing Data</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="C163" s="3" t="inlineStr">
         <is>
-          <t>Optiver</t>
+          <t>ChipSoft Nederland</t>
         </is>
       </c>
       <c r="D163" s="3" t="inlineStr">
@@ -10779,7 +10779,7 @@
       </c>
       <c r="H163" s="3" t="inlineStr">
         <is>
-          <t>This Quantitative Developer role focuses entirely on financial pricing data systems, market data pipelines, and low-latency/historical trading infrastructure in C++/Python, which is completely unrelated to the candidate's specialization in Generative AI, LLMs, and agentic workflows.</t>
+          <t>This is a Data Engineer role focused on ELT, SQL, data warehousing, and clickstream data, which is entirely unrelated to the candidate's core specialization in Generative AI, LLMs, and agentic systems.</t>
         </is>
       </c>
       <c r="I163" s="3" t="inlineStr">
@@ -10789,7 +10789,7 @@
       </c>
       <c r="J163" s="3" t="inlineStr">
         <is>
-          <t>Yes - explicitly stated in JD</t>
+          <t>Not stated in JD</t>
         </is>
       </c>
       <c r="K163" s="2" t="inlineStr">
@@ -10804,7 +10804,7 @@
       </c>
       <c r="M163" s="6" t="inlineStr">
         <is>
-          <t>https://nl.linkedin.com/jobs/view/quantitative-developer-pricing-data-at-optiver-4437686371?position=21&amp;pageNum=0&amp;refId=oiBIn1Czflg0JjZjH5z0Lg%3D%3D&amp;trackingId=bm7u%2BG7QRNRgNoiTgqdkzg%3D%3D</t>
+          <t>https://nl.linkedin.com/jobs/view/data-engineer-at-chipsoft-nederland-4448895866?position=29&amp;pageNum=0&amp;refId=oiBIn1Czflg0JjZjH5z0Lg%3D%3D&amp;trackingId=CakhxR8nCpksAoEXyMZPHQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -10814,17 +10814,17 @@
       </c>
       <c r="B164" s="3" t="inlineStr">
         <is>
-          <t>Data Analyst — Operational Analysis (Python, Power BI, Modelling) for NATO with security clearance</t>
+          <t>Quantitative Developer - Pricing Data</t>
         </is>
       </c>
       <c r="C164" s="3" t="inlineStr">
         <is>
-          <t>WLG</t>
+          <t>Optiver</t>
         </is>
       </c>
       <c r="D164" s="3" t="inlineStr">
         <is>
-          <t>The Hague, South Holland, Netherlands</t>
+          <t>Amsterdam, North Holland, Netherlands</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
@@ -10842,7 +10842,7 @@
       </c>
       <c r="H164" s="3" t="inlineStr">
         <is>
-          <t>This is an unrelated junior Data Analyst role focused on operational analysis, dashboards, and spreadsheets rather than Generative AI or advanced data science. Given the candidate's 10+ years of experience as a Lead Data Scientist specializing in LLMs and agentic AI, this position represents a severe mismatch in both domain and seniority.</t>
+          <t>This Quantitative Developer role focuses entirely on financial pricing data systems, market data pipelines, and low-latency/historical trading infrastructure in C++/Python, which is completely unrelated to the candidate's specialization in Generative AI, LLMs, and agentic workflows.</t>
         </is>
       </c>
       <c r="I164" s="3" t="inlineStr">
@@ -10852,7 +10852,7 @@
       </c>
       <c r="J164" s="3" t="inlineStr">
         <is>
-          <t>Not stated in JD</t>
+          <t>Yes - explicitly stated in JD</t>
         </is>
       </c>
       <c r="K164" s="2" t="inlineStr">
@@ -10867,7 +10867,7 @@
       </c>
       <c r="M164" s="6" t="inlineStr">
         <is>
-          <t>https://nl.linkedin.com/jobs/view/data-analyst-%E2%80%94-operational-analysis-python-power-bi-modelling-for-nato-with-security-clearance-at-wlg-4458620413?position=26&amp;pageNum=0&amp;refId=oiBIn1Czflg0JjZjH5z0Lg%3D%3D&amp;trackingId=NK7DxxVQL3iwGI1saGNrZg%3D%3D</t>
+          <t>https://nl.linkedin.com/jobs/view/quantitative-developer-pricing-data-at-optiver-4437686371?position=21&amp;pageNum=0&amp;refId=oiBIn1Czflg0JjZjH5z0Lg%3D%3D&amp;trackingId=bm7u%2BG7QRNRgNoiTgqdkzg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -10877,17 +10877,17 @@
       </c>
       <c r="B165" s="3" t="inlineStr">
         <is>
-          <t>Hadoop / Big Data Engineer</t>
+          <t>Data Analyst — Operational Analysis (Python, Power BI, Modelling) for NATO with security clearance</t>
         </is>
       </c>
       <c r="C165" s="3" t="inlineStr">
         <is>
-          <t>HTC Global Services</t>
+          <t>WLG</t>
         </is>
       </c>
       <c r="D165" s="3" t="inlineStr">
         <is>
-          <t>Dubai, United Arab Emirates</t>
+          <t>The Hague, South Holland, Netherlands</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr">
@@ -10905,7 +10905,7 @@
       </c>
       <c r="H165" s="3" t="inlineStr">
         <is>
-          <t>This is a classical data engineering and Hadoop role focusing on infrastructure, Spark, Hive, and data pipelines, which is entirely unrelated to the candidate's core specialization in Generative AI, LLMs, and agentic workflows.</t>
+          <t>This is an unrelated junior Data Analyst role focused on operational analysis, dashboards, and spreadsheets rather than Generative AI or advanced data science. Given the candidate's 10+ years of experience as a Lead Data Scientist specializing in LLMs and agentic AI, this position represents a severe mismatch in both domain and seniority.</t>
         </is>
       </c>
       <c r="I165" s="3" t="inlineStr">
@@ -10930,7 +10930,7 @@
       </c>
       <c r="M165" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/hadoop-big-data-engineer-at-htc-global-services-4460123484?position=9&amp;pageNum=0&amp;refId=zJBbvwb5H0wsbJ5fs9ZTVw%3D%3D&amp;trackingId=SQM7VXeym81F4YKdSlXxkg%3D%3D</t>
+          <t>https://nl.linkedin.com/jobs/view/data-analyst-%E2%80%94-operational-analysis-python-power-bi-modelling-for-nato-with-security-clearance-at-wlg-4458620413?position=26&amp;pageNum=0&amp;refId=oiBIn1Czflg0JjZjH5z0Lg%3D%3D&amp;trackingId=NK7DxxVQL3iwGI1saGNrZg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -10940,22 +10940,22 @@
       </c>
       <c r="B166" s="3" t="inlineStr">
         <is>
-          <t>Business Analyst - Dubai (UAE Nationals only)</t>
+          <t>Hadoop / Big Data Engineer</t>
         </is>
       </c>
       <c r="C166" s="3" t="inlineStr">
         <is>
-          <t>Efficio</t>
+          <t>HTC Global Services</t>
         </is>
       </c>
       <c r="D166" s="3" t="inlineStr">
         <is>
-          <t>Dubai, Dubai, United Arab Emirates</t>
+          <t>Dubai, United Arab Emirates</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F166" s="7" t="n">
@@ -10968,7 +10968,7 @@
       </c>
       <c r="H166" s="3" t="inlineStr">
         <is>
-          <t>This role is a Business Analyst position focused on procurement and supply chain consulting, completely unrelated to data science, artificial intelligence, or the candidate's core GenAI/LLM specialization. Furthermore, the role explicitly requires being a UAE National.</t>
+          <t>This is a classical data engineering and Hadoop role focusing on infrastructure, Spark, Hive, and data pipelines, which is entirely unrelated to the candidate's core specialization in Generative AI, LLMs, and agentic workflows.</t>
         </is>
       </c>
       <c r="I166" s="3" t="inlineStr">
@@ -10993,7 +10993,7 @@
       </c>
       <c r="M166" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/business-analyst-dubai-uae-nationals-only-at-efficio-4291615037?position=11&amp;pageNum=0&amp;refId=umynRMWB8laV9lcrAC5yvg%3D%3D&amp;trackingId=97gwiNAcH3ASkR2fVgtg7A%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/hadoop-big-data-engineer-at-htc-global-services-4460123484?position=9&amp;pageNum=0&amp;refId=zJBbvwb5H0wsbJ5fs9ZTVw%3D%3D&amp;trackingId=SQM7VXeym81F4YKdSlXxkg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -11003,12 +11003,12 @@
       </c>
       <c r="B167" s="3" t="inlineStr">
         <is>
-          <t>Oliver Wyman - Government and Public Institutions (GPI) and Financial Services (FS) Researcher - Dubai</t>
+          <t>Business Analyst - Dubai (UAE Nationals only)</t>
         </is>
       </c>
       <c r="C167" s="3" t="inlineStr">
         <is>
-          <t>Oliver Wyman</t>
+          <t>Efficio</t>
         </is>
       </c>
       <c r="D167" s="3" t="inlineStr">
@@ -11031,7 +11031,7 @@
       </c>
       <c r="H167" s="3" t="inlineStr">
         <is>
-          <t>This is a non-technical management consulting research role focusing on market data, databases like Factiva, and slide preparation in Excel/PowerPoint. It has no connection to the candidate's core specialization in Generative AI, LLMs, LangChain, or data science modeling.</t>
+          <t>This role is a Business Analyst position focused on procurement and supply chain consulting, completely unrelated to data science, artificial intelligence, or the candidate's core GenAI/LLM specialization. Furthermore, the role explicitly requires being a UAE National.</t>
         </is>
       </c>
       <c r="I167" s="3" t="inlineStr">
@@ -11056,7 +11056,7 @@
       </c>
       <c r="M167" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/oliver-wyman-government-and-public-institutions-gpi-and-financial-services-fs-researcher-dubai-at-oliver-wyman-4460354191?position=14&amp;pageNum=0&amp;refId=umynRMWB8laV9lcrAC5yvg%3D%3D&amp;trackingId=ELxpmziWW%2B8sDM8xGhxmOA%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/business-analyst-dubai-uae-nationals-only-at-efficio-4291615037?position=11&amp;pageNum=0&amp;refId=umynRMWB8laV9lcrAC5yvg%3D%3D&amp;trackingId=97gwiNAcH3ASkR2fVgtg7A%3D%3D</t>
         </is>
       </c>
     </row>
@@ -11066,7 +11066,7 @@
       </c>
       <c r="B168" s="3" t="inlineStr">
         <is>
-          <t>Oliver Wyman - Associate - Health and Life Sciences - Dubai</t>
+          <t>Oliver Wyman - Government and Public Institutions (GPI) and Financial Services (FS) Researcher - Dubai</t>
         </is>
       </c>
       <c r="C168" s="3" t="inlineStr">
@@ -11094,7 +11094,7 @@
       </c>
       <c r="H168" s="3" t="inlineStr">
         <is>
-          <t>This is a management consulting role focused on Health and Life Sciences strategy at Oliver Wyman, requiring deep industry expertise in pharmaceuticals or MedTech and top-tier strategy consulting experience. It has zero alignment with the candidate's core GenAI, LLM, or Data Science specialization.</t>
+          <t>This is a non-technical management consulting research role focusing on market data, databases like Factiva, and slide preparation in Excel/PowerPoint. It has no connection to the candidate's core specialization in Generative AI, LLMs, LangChain, or data science modeling.</t>
         </is>
       </c>
       <c r="I168" s="3" t="inlineStr">
@@ -11119,7 +11119,7 @@
       </c>
       <c r="M168" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/oliver-wyman-associate-health-and-life-sciences-dubai-at-oliver-wyman-4460351294?position=8&amp;pageNum=0&amp;refId=umynRMWB8laV9lcrAC5yvg%3D%3D&amp;trackingId=GWJpOuiL92AZx2SkHg%2FfPg%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/oliver-wyman-government-and-public-institutions-gpi-and-financial-services-fs-researcher-dubai-at-oliver-wyman-4460354191?position=14&amp;pageNum=0&amp;refId=umynRMWB8laV9lcrAC5yvg%3D%3D&amp;trackingId=ELxpmziWW%2B8sDM8xGhxmOA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -11129,12 +11129,12 @@
       </c>
       <c r="B169" s="3" t="inlineStr">
         <is>
-          <t>F&amp;S Associate - UAE National</t>
+          <t>Oliver Wyman - Associate - Health and Life Sciences - Dubai</t>
         </is>
       </c>
       <c r="C169" s="3" t="inlineStr">
         <is>
-          <t>Deliveroo</t>
+          <t>Oliver Wyman</t>
         </is>
       </c>
       <c r="D169" s="3" t="inlineStr">
@@ -11157,7 +11157,7 @@
       </c>
       <c r="H169" s="3" t="inlineStr">
         <is>
-          <t>This is a finance and strategy role focused on spreadsheets, variance analysis, and business reporting with no relation to Generative AI, machine learning, or data science. It is completely unrelated to the candidate's core technical specialization and profile.</t>
+          <t>This is a management consulting role focused on Health and Life Sciences strategy at Oliver Wyman, requiring deep industry expertise in pharmaceuticals or MedTech and top-tier strategy consulting experience. It has zero alignment with the candidate's core GenAI, LLM, or Data Science specialization.</t>
         </is>
       </c>
       <c r="I169" s="3" t="inlineStr">
@@ -11182,7 +11182,7 @@
       </c>
       <c r="M169" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/f-s-associate-uae-national-at-deliveroo-4449749711?position=6&amp;pageNum=0&amp;refId=umynRMWB8laV9lcrAC5yvg%3D%3D&amp;trackingId=xir3IHLZTYXuoIlF3oUkeg%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/oliver-wyman-associate-health-and-life-sciences-dubai-at-oliver-wyman-4460351294?position=8&amp;pageNum=0&amp;refId=umynRMWB8laV9lcrAC5yvg%3D%3D&amp;trackingId=GWJpOuiL92AZx2SkHg%2FfPg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -11192,12 +11192,12 @@
       </c>
       <c r="B170" s="3" t="inlineStr">
         <is>
-          <t>BI Engineer</t>
+          <t>F&amp;S Associate - UAE National</t>
         </is>
       </c>
       <c r="C170" s="3" t="inlineStr">
         <is>
-          <t>JD.COM</t>
+          <t>Deliveroo</t>
         </is>
       </c>
       <c r="D170" s="3" t="inlineStr">
@@ -11207,7 +11207,7 @@
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="F170" s="7" t="n">
@@ -11220,12 +11220,12 @@
       </c>
       <c r="H170" s="3" t="inlineStr">
         <is>
-          <t>This role is a BI Engineer position focused on supply chain, logistics, and retail operations rather than data science, AI, or Generative AI. It is entirely unrelated to the candidate's core expertise in LLMs, RAG, and agentic systems.</t>
+          <t>This is a finance and strategy role focused on spreadsheets, variance analysis, and business reporting with no relation to Generative AI, machine learning, or data science. It is completely unrelated to the candidate's core technical specialization and profile.</t>
         </is>
       </c>
       <c r="I170" s="3" t="inlineStr">
         <is>
-          <t>Yes - German required (see JD for exact level)</t>
+          <t>Not stated in JD</t>
         </is>
       </c>
       <c r="J170" s="3" t="inlineStr">
@@ -11245,7 +11245,7 @@
       </c>
       <c r="M170" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/bi-engineer-at-jd-com-4414670937?position=6&amp;pageNum=0&amp;refId=WT017Qp%2F1VFpbzjZb903BA%3D%3D&amp;trackingId=uXRSjK39jDOlXpbtHq2yzQ%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/f-s-associate-uae-national-at-deliveroo-4449749711?position=6&amp;pageNum=0&amp;refId=umynRMWB8laV9lcrAC5yvg%3D%3D&amp;trackingId=xir3IHLZTYXuoIlF3oUkeg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -11255,17 +11255,17 @@
       </c>
       <c r="B171" s="3" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>BI Engineer</t>
         </is>
       </c>
       <c r="C171" s="3" t="inlineStr">
         <is>
-          <t>Danube Group</t>
+          <t>JD.COM</t>
         </is>
       </c>
       <c r="D171" s="3" t="inlineStr">
         <is>
-          <t>Dubai, United Arab Emirates</t>
+          <t>Dubai, Dubai, United Arab Emirates</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr">
@@ -11283,12 +11283,12 @@
       </c>
       <c r="H171" s="3" t="inlineStr">
         <is>
-          <t>This is a Power BI Developer role focused on dashboards, data visualization, DAX, and SQL, which is completely unrelated to the candidate's core specialization in Generative AI, LLMs, and agentic workflows.</t>
+          <t>This role is a BI Engineer position focused on supply chain, logistics, and retail operations rather than data science, AI, or Generative AI. It is entirely unrelated to the candidate's core expertise in LLMs, RAG, and agentic systems.</t>
         </is>
       </c>
       <c r="I171" s="3" t="inlineStr">
         <is>
-          <t>Not stated in JD</t>
+          <t>Yes - German required (see JD for exact level)</t>
         </is>
       </c>
       <c r="J171" s="3" t="inlineStr">
@@ -11308,7 +11308,7 @@
       </c>
       <c r="M171" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/power-bi-developer-at-danube-group-4459465901?position=5&amp;pageNum=0&amp;refId=WT017Qp%2F1VFpbzjZb903BA%3D%3D&amp;trackingId=2u7KtmoSLaInXvl%2FCAGPzw%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/bi-engineer-at-jd-com-4414670937?position=6&amp;pageNum=0&amp;refId=WT017Qp%2F1VFpbzjZb903BA%3D%3D&amp;trackingId=uXRSjK39jDOlXpbtHq2yzQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -11318,26 +11318,26 @@
       </c>
       <c r="B172" s="3" t="inlineStr">
         <is>
-          <t>National Assistant Planner</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="C172" s="3" t="inlineStr">
         <is>
-          <t>Al-Futtaim</t>
+          <t>Danube Group</t>
         </is>
       </c>
       <c r="D172" s="3" t="inlineStr">
         <is>
-          <t>Dubai, Dubai, United Arab Emirates</t>
+          <t>Dubai, United Arab Emirates</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="F172" s="7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G172" s="8" t="inlineStr">
         <is>
@@ -11346,7 +11346,7 @@
       </c>
       <c r="H172" s="3" t="inlineStr">
         <is>
-          <t>This is a non-technical retail merchandise planning role focused on financial forecasting, inventory management, and sales planning, which is entirely unrelated to the candidate's GenAI, LLM, and data science specialization.</t>
+          <t>This is a Power BI Developer role focused on dashboards, data visualization, DAX, and SQL, which is completely unrelated to the candidate's core specialization in Generative AI, LLMs, and agentic workflows.</t>
         </is>
       </c>
       <c r="I172" s="3" t="inlineStr">
@@ -11371,7 +11371,7 @@
       </c>
       <c r="M172" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/national-assistant-planner-at-al-futtaim-4459335643?position=23&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=udE1OmanEOJo5NqnDVVmsw%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/power-bi-developer-at-danube-group-4459465901?position=5&amp;pageNum=0&amp;refId=WT017Qp%2F1VFpbzjZb903BA%3D%3D&amp;trackingId=2u7KtmoSLaInXvl%2FCAGPzw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -11381,12 +11381,12 @@
       </c>
       <c r="B173" s="3" t="inlineStr">
         <is>
-          <t>Forward Deployed AI Integrator (UAE National Only), Field Engineering</t>
+          <t>National Assistant Planner</t>
         </is>
       </c>
       <c r="C173" s="3" t="inlineStr">
         <is>
-          <t>Amazon Web Services (AWS)</t>
+          <t>Al-Futtaim</t>
         </is>
       </c>
       <c r="D173" s="3" t="inlineStr">
@@ -11396,7 +11396,7 @@
       </c>
       <c r="E173" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F173" s="7" t="n">
@@ -11409,7 +11409,7 @@
       </c>
       <c r="H173" s="3" t="inlineStr">
         <is>
-          <t>Although the role involves AI tooling and Python, it is restricted to UAE Nationals only, making it impossible for the candidate to qualify. Additionally, the position leans heavily toward technical program management rather than hands-on Generative AI and LLM engineering.</t>
+          <t>This is a non-technical retail merchandise planning role focused on financial forecasting, inventory management, and sales planning, which is entirely unrelated to the candidate's GenAI, LLM, and data science specialization.</t>
         </is>
       </c>
       <c r="I173" s="3" t="inlineStr">
@@ -11434,7 +11434,7 @@
       </c>
       <c r="M173" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/forward-deployed-ai-integrator-uae-national-only-field-engineering-at-amazon-web-services-aws-4459616402?position=14&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=suYy8hgZkG37o3lG7FlDHQ%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/national-assistant-planner-at-al-futtaim-4459335643?position=23&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=udE1OmanEOJo5NqnDVVmsw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -11444,12 +11444,12 @@
       </c>
       <c r="B174" s="3" t="inlineStr">
         <is>
-          <t>GIS Specialist / Developer</t>
+          <t>Forward Deployed AI Integrator (UAE National Only), Field Engineering</t>
         </is>
       </c>
       <c r="C174" s="3" t="inlineStr">
         <is>
-          <t>AECOM</t>
+          <t>Amazon Web Services (AWS)</t>
         </is>
       </c>
       <c r="D174" s="3" t="inlineStr">
@@ -11459,7 +11459,7 @@
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F174" s="7" t="n">
@@ -11472,7 +11472,7 @@
       </c>
       <c r="H174" s="3" t="inlineStr">
         <is>
-          <t>This is a GIS Specialist role focused on ArcGIS Enterprise administration, spatial analysis, and Python/ArcPy automation, which is completely unrelated to the candidate's core specialization in Generative AI, LLMs, and agentic systems.</t>
+          <t>Although the role involves AI tooling and Python, it is restricted to UAE Nationals only, making it impossible for the candidate to qualify. Additionally, the position leans heavily toward technical program management rather than hands-on Generative AI and LLM engineering.</t>
         </is>
       </c>
       <c r="I174" s="3" t="inlineStr">
@@ -11497,7 +11497,7 @@
       </c>
       <c r="M174" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/gis-specialist-developer-at-aecom-4456869023?position=15&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=lGxG6%2FYECt2YwYGWf5hEZA%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/forward-deployed-ai-integrator-uae-national-only-field-engineering-at-amazon-web-services-aws-4459616402?position=14&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=suYy8hgZkG37o3lG7FlDHQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -11507,12 +11507,12 @@
       </c>
       <c r="B175" s="3" t="inlineStr">
         <is>
-          <t>Quant Desk Lead and Portfolio Manager</t>
+          <t>GIS Specialist / Developer</t>
         </is>
       </c>
       <c r="C175" s="3" t="inlineStr">
         <is>
-          <t>EMCD</t>
+          <t>AECOM</t>
         </is>
       </c>
       <c r="D175" s="3" t="inlineStr">
@@ -11535,7 +11535,7 @@
       </c>
       <c r="H175" s="3" t="inlineStr">
         <is>
-          <t>This is a finance and quantitative trading role focused on running a systematic trading desk, portfolio management, and P&amp;L ownership, which is entirely unrelated to the candidate's core specialization in Generative AI, LLMs, and agentic systems.</t>
+          <t>This is a GIS Specialist role focused on ArcGIS Enterprise administration, spatial analysis, and Python/ArcPy automation, which is completely unrelated to the candidate's core specialization in Generative AI, LLMs, and agentic systems.</t>
         </is>
       </c>
       <c r="I175" s="3" t="inlineStr">
@@ -11560,7 +11560,7 @@
       </c>
       <c r="M175" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/quant-desk-lead-and-portfolio-manager-at-emcd-4457949555?position=13&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=drHtrw6uBtEz5S2i%2BjBT5A%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/gis-specialist-developer-at-aecom-4456869023?position=15&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=lGxG6%2FYECt2YwYGWf5hEZA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -11570,17 +11570,17 @@
       </c>
       <c r="B176" s="3" t="inlineStr">
         <is>
-          <t>Join Norlys Energy Trading</t>
+          <t>Quant Desk Lead and Portfolio Manager</t>
         </is>
       </c>
       <c r="C176" s="3" t="inlineStr">
         <is>
-          <t>Norlys Energy Trading A/S</t>
+          <t>EMCD</t>
         </is>
       </c>
       <c r="D176" s="3" t="inlineStr">
         <is>
-          <t>Aalborg, North Denmark Region, Denmark</t>
+          <t>Dubai, Dubai, United Arab Emirates</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr">
@@ -11598,7 +11598,7 @@
       </c>
       <c r="H176" s="3" t="inlineStr">
         <is>
-          <t>This is an open, unsolicited job application for a general talent pool in energy trading, rather than a defined Data Science or Generative AI role. It completely lacks technical specifications, making it impossible to evaluate against the candidate's specialized GenAI and LLM expertise.</t>
+          <t>This is a finance and quantitative trading role focused on running a systematic trading desk, portfolio management, and P&amp;L ownership, which is entirely unrelated to the candidate's core specialization in Generative AI, LLMs, and agentic systems.</t>
         </is>
       </c>
       <c r="I176" s="3" t="inlineStr">
@@ -11623,7 +11623,7 @@
       </c>
       <c r="M176" s="6" t="inlineStr">
         <is>
-          <t>https://dk.linkedin.com/jobs/view/join-norlys-energy-trading-at-norlys-energy-trading-a-s-4459158084?position=26&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=Z%2BOuDrbPap3omWro18MA2g%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/quant-desk-lead-and-portfolio-manager-at-emcd-4457949555?position=13&amp;pageNum=0&amp;refId=JBPPMgbgbAFzpV%2BDL5h2AA%3D%3D&amp;trackingId=drHtrw6uBtEz5S2i%2BjBT5A%3D%3D</t>
         </is>
       </c>
     </row>
@@ -11633,17 +11633,17 @@
       </c>
       <c r="B177" s="3" t="inlineStr">
         <is>
-          <t>PhD scholarship in Modeling and Control of Parkinson’s Disease - DTU Electro</t>
+          <t>Join Norlys Energy Trading</t>
         </is>
       </c>
       <c r="C177" s="3" t="inlineStr">
         <is>
-          <t>DTU - Technical University of Denmark</t>
+          <t>Norlys Energy Trading A/S</t>
         </is>
       </c>
       <c r="D177" s="3" t="inlineStr">
         <is>
-          <t>Kongens Lyngby, Capital Region of Denmark, Denmark</t>
+          <t>Aalborg, North Denmark Region, Denmark</t>
         </is>
       </c>
       <c r="E177" s="2" t="inlineStr">
@@ -11661,7 +11661,7 @@
       </c>
       <c r="H177" s="3" t="inlineStr">
         <is>
-          <t>This is a PhD scholarship position in neuroengineering, control systems, and healthcare technology at DTU, which is completely unrelated to the candidate's specialization in Generative AI, LLMs, and agentic systems.</t>
+          <t>This is an open, unsolicited job application for a general talent pool in energy trading, rather than a defined Data Science or Generative AI role. It completely lacks technical specifications, making it impossible to evaluate against the candidate's specialized GenAI and LLM expertise.</t>
         </is>
       </c>
       <c r="I177" s="3" t="inlineStr">
@@ -11671,7 +11671,7 @@
       </c>
       <c r="J177" s="3" t="inlineStr">
         <is>
-          <t>Possible - relocation support mentioned, visa not explicit</t>
+          <t>Not stated in JD</t>
         </is>
       </c>
       <c r="K177" s="2" t="inlineStr">
@@ -11686,7 +11686,7 @@
       </c>
       <c r="M177" s="6" t="inlineStr">
         <is>
-          <t>https://dk.linkedin.com/jobs/view/phd-scholarship-in-modeling-and-control-of-parkinson%E2%80%99s-disease-dtu-electro-at-dtu-technical-university-of-denmark-4459145557?position=20&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=mStwcLkWBAvzmreGSwO4Hw%3D%3D</t>
+          <t>https://dk.linkedin.com/jobs/view/join-norlys-energy-trading-at-norlys-energy-trading-a-s-4459158084?position=26&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=Z%2BOuDrbPap3omWro18MA2g%3D%3D</t>
         </is>
       </c>
     </row>
@@ -11696,17 +11696,17 @@
       </c>
       <c r="B178" s="3" t="inlineStr">
         <is>
-          <t>Analytikere med flair for databehandling til PET's kontraspionageindsats mod Rusland</t>
+          <t>PhD scholarship in Modeling and Control of Parkinson’s Disease - DTU Electro</t>
         </is>
       </c>
       <c r="C178" s="3" t="inlineStr">
         <is>
-          <t>Politi</t>
+          <t>DTU - Technical University of Denmark</t>
         </is>
       </c>
       <c r="D178" s="3" t="inlineStr">
         <is>
-          <t>Copenhagen, Capital Region of Denmark, Denmark</t>
+          <t>Kongens Lyngby, Capital Region of Denmark, Denmark</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr">
@@ -11724,7 +11724,7 @@
       </c>
       <c r="H178" s="3" t="inlineStr">
         <is>
-          <t>This is a national security intelligence and counter-espionage analyst role at the Danish Security and Intelligence Service (PET), which is completely unrelated to data science, artificial intelligence, or the candidate's Generative AI and LLM specialization.</t>
+          <t>This is a PhD scholarship position in neuroengineering, control systems, and healthcare technology at DTU, which is completely unrelated to the candidate's specialization in Generative AI, LLMs, and agentic systems.</t>
         </is>
       </c>
       <c r="I178" s="3" t="inlineStr">
@@ -11734,7 +11734,7 @@
       </c>
       <c r="J178" s="3" t="inlineStr">
         <is>
-          <t>Not stated in JD</t>
+          <t>Possible - relocation support mentioned, visa not explicit</t>
         </is>
       </c>
       <c r="K178" s="2" t="inlineStr">
@@ -11749,7 +11749,7 @@
       </c>
       <c r="M178" s="6" t="inlineStr">
         <is>
-          <t>https://dk.linkedin.com/jobs/view/analytikere-med-flair-for-databehandling-til-pet-s-kontraspionageindsats-mod-rusland-at-politi-4457943820?position=18&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=%2FGEw4KOC0oARqkQIDTGJ4Q%3D%3D</t>
+          <t>https://dk.linkedin.com/jobs/view/phd-scholarship-in-modeling-and-control-of-parkinson%E2%80%99s-disease-dtu-electro-at-dtu-technical-university-of-denmark-4459145557?position=20&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=mStwcLkWBAvzmreGSwO4Hw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -11759,12 +11759,12 @@
       </c>
       <c r="B179" s="3" t="inlineStr">
         <is>
-          <t>PostDoc - Uncertainty-Aware Optimization in Inverse Problems for Next-Generation 3D Scanning</t>
+          <t>Analytikere med flair for databehandling til PET's kontraspionageindsats mod Rusland</t>
         </is>
       </c>
       <c r="C179" s="3" t="inlineStr">
         <is>
-          <t>3Shape</t>
+          <t>Politi</t>
         </is>
       </c>
       <c r="D179" s="3" t="inlineStr">
@@ -11787,7 +11787,7 @@
       </c>
       <c r="H179" s="3" t="inlineStr">
         <is>
-          <t>This is a PostDoc position focused on mathematical optimization, numerical linear algebra, and uncertainty quantification for 3D scanning, which requires a PhD. It has no overlap with the candidate's specialization in GenAI, LLMs, and agentic systems.</t>
+          <t>This is a national security intelligence and counter-espionage analyst role at the Danish Security and Intelligence Service (PET), which is completely unrelated to data science, artificial intelligence, or the candidate's Generative AI and LLM specialization.</t>
         </is>
       </c>
       <c r="I179" s="3" t="inlineStr">
@@ -11812,7 +11812,7 @@
       </c>
       <c r="M179" s="6" t="inlineStr">
         <is>
-          <t>https://dk.linkedin.com/jobs/view/postdoc-uncertainty-aware-optimization-in-inverse-problems-for-next-generation-3d-scanning-at-3shape-4459171806?position=15&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=bO0aSGZ%2FUAxThXN9yvOERg%3D%3D</t>
+          <t>https://dk.linkedin.com/jobs/view/analytikere-med-flair-for-databehandling-til-pet-s-kontraspionageindsats-mod-rusland-at-politi-4457943820?position=18&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=%2FGEw4KOC0oARqkQIDTGJ4Q%3D%3D</t>
         </is>
       </c>
     </row>
@@ -11822,17 +11822,17 @@
       </c>
       <c r="B180" s="3" t="inlineStr">
         <is>
-          <t>Scientist, Quantitative Clinical Pharmacology (PK/PD Modeling &amp; Simulation)</t>
+          <t>PostDoc - Uncertainty-Aware Optimization in Inverse Problems for Next-Generation 3D Scanning</t>
         </is>
       </c>
       <c r="C180" s="3" t="inlineStr">
         <is>
-          <t>Hemab Therapeutics</t>
+          <t>3Shape</t>
         </is>
       </c>
       <c r="D180" s="3" t="inlineStr">
         <is>
-          <t>Copenhagen Metropolitan Area</t>
+          <t>Copenhagen, Capital Region of Denmark, Denmark</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr">
@@ -11850,7 +11850,7 @@
       </c>
       <c r="H180" s="3" t="inlineStr">
         <is>
-          <t>This is a highly specialized biomedical role focusing on Pharmacokinetics/Pharmacodynamics (PK/PD) modeling and clinical pharmacology, requiring a Ph.D. and experience with tools like NONMEM or Monolix. It has zero overlap with the candidate's GenAI, LLM, and data science background.</t>
+          <t>This is a PostDoc position focused on mathematical optimization, numerical linear algebra, and uncertainty quantification for 3D scanning, which requires a PhD. It has no overlap with the candidate's specialization in GenAI, LLMs, and agentic systems.</t>
         </is>
       </c>
       <c r="I180" s="3" t="inlineStr">
@@ -11875,7 +11875,7 @@
       </c>
       <c r="M180" s="6" t="inlineStr">
         <is>
-          <t>https://dk.linkedin.com/jobs/view/scientist-quantitative-clinical-pharmacology-pk-pd-modeling-simulation-at-hemab-therapeutics-4457218306?position=14&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=jhTyKvDAQ70R9PD5s0x2yA%3D%3D</t>
+          <t>https://dk.linkedin.com/jobs/view/postdoc-uncertainty-aware-optimization-in-inverse-problems-for-next-generation-3d-scanning-at-3shape-4459171806?position=15&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=bO0aSGZ%2FUAxThXN9yvOERg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -11885,17 +11885,17 @@
       </c>
       <c r="B181" s="3" t="inlineStr">
         <is>
-          <t>Senior Payload Data Operator</t>
+          <t>Scientist, Quantitative Clinical Pharmacology (PK/PD Modeling &amp; Simulation)</t>
         </is>
       </c>
       <c r="C181" s="3" t="inlineStr">
         <is>
-          <t>FADA</t>
+          <t>Hemab Therapeutics</t>
         </is>
       </c>
       <c r="D181" s="3" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>Copenhagen Metropolitan Area</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr">
@@ -11913,7 +11913,7 @@
       </c>
       <c r="H181" s="3" t="inlineStr">
         <is>
-          <t>This is a satellite payload data engineering role focused on aerospace, remote sensing, and image processing (EO/SAR), which is completely unrelated to the candidate's specialization in GenAI, LLMs, and agentic systems.</t>
+          <t>This is a highly specialized biomedical role focusing on Pharmacokinetics/Pharmacodynamics (PK/PD) modeling and clinical pharmacology, requiring a Ph.D. and experience with tools like NONMEM or Monolix. It has zero overlap with the candidate's GenAI, LLM, and data science background.</t>
         </is>
       </c>
       <c r="I181" s="3" t="inlineStr">
@@ -11938,7 +11938,7 @@
       </c>
       <c r="M181" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/senior-payload-data-operator-at-fada-4448986926?position=20&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=xdfP2za0I45WGIW%2FRJb%2BgA%3D%3D</t>
+          <t>https://dk.linkedin.com/jobs/view/scientist-quantitative-clinical-pharmacology-pk-pd-modeling-simulation-at-hemab-therapeutics-4457218306?position=14&amp;pageNum=0&amp;refId=Pb2EWWHgR9a7i9BrLIIg7g%3D%3D&amp;trackingId=jhTyKvDAQ70R9PD5s0x2yA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -11948,22 +11948,22 @@
       </c>
       <c r="B182" s="3" t="inlineStr">
         <is>
-          <t>Arabic Speech And Natural Language Processing Specialist</t>
+          <t>Senior Payload Data Operator</t>
         </is>
       </c>
       <c r="C182" s="3" t="inlineStr">
         <is>
-          <t>Birbal AI</t>
+          <t>FADA</t>
         </is>
       </c>
       <c r="D182" s="3" t="inlineStr">
         <is>
-          <t>Abu Dhabi Emirate, United Arab Emirates</t>
+          <t>United Arab Emirates</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F182" s="7" t="n">
@@ -11976,7 +11976,7 @@
       </c>
       <c r="H182" s="3" t="inlineStr">
         <is>
-          <t>The role requires specialized expertise in Arabic speech technology (ASR, TTS, audio DSP) and native command of Gulf Arabic dialects, which does not match the candidate's core background in GenAI, LLMs, and RAG for English-language banking and HR use cases.</t>
+          <t>This is a satellite payload data engineering role focused on aerospace, remote sensing, and image processing (EO/SAR), which is completely unrelated to the candidate's specialization in GenAI, LLMs, and agentic systems.</t>
         </is>
       </c>
       <c r="I182" s="3" t="inlineStr">
@@ -12001,7 +12001,7 @@
       </c>
       <c r="M182" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/arabic-speech-and-natural-language-processing-specialist-at-birbal-ai-4457738899?position=14&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=ztG06Ly%2FIZ3fxm%2Fhvl626A%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/senior-payload-data-operator-at-fada-4448986926?position=20&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=xdfP2za0I45WGIW%2FRJb%2BgA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -12011,17 +12011,17 @@
       </c>
       <c r="B183" s="3" t="inlineStr">
         <is>
-          <t>Member of Technical Staff - Medical Research (Remote)</t>
+          <t>Arabic Speech And Natural Language Processing Specialist</t>
         </is>
       </c>
       <c r="C183" s="3" t="inlineStr">
         <is>
-          <t>Hire Feed</t>
+          <t>Birbal AI</t>
         </is>
       </c>
       <c r="D183" s="3" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>Abu Dhabi Emirate, United Arab Emirates</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr">
@@ -12039,7 +12039,7 @@
       </c>
       <c r="H183" s="3" t="inlineStr">
         <is>
-          <t>This role is completely unrelated to the candidate's specialization in Generative AI, LLMs, and agentic workflows, focusing instead on medical imaging, computational biology, and clinical research requiring a PhD.</t>
+          <t>The role requires specialized expertise in Arabic speech technology (ASR, TTS, audio DSP) and native command of Gulf Arabic dialects, which does not match the candidate's core background in GenAI, LLMs, and RAG for English-language banking and HR use cases.</t>
         </is>
       </c>
       <c r="I183" s="3" t="inlineStr">
@@ -12064,7 +12064,7 @@
       </c>
       <c r="M183" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/member-of-technical-staff-medical-research-remote-at-hire-feed-4459638503?position=3&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=b91zxKPZNgdFnMmW%2FlYbHA%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/arabic-speech-and-natural-language-processing-specialist-at-birbal-ai-4457738899?position=14&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=ztG06Ly%2FIZ3fxm%2Fhvl626A%3D%3D</t>
         </is>
       </c>
     </row>
@@ -12074,17 +12074,17 @@
       </c>
       <c r="B184" s="3" t="inlineStr">
         <is>
-          <t>AI Image Specialist</t>
+          <t>Member of Technical Staff - Medical Research (Remote)</t>
         </is>
       </c>
       <c r="C184" s="3" t="inlineStr">
         <is>
-          <t>Puffy</t>
+          <t>Hire Feed</t>
         </is>
       </c>
       <c r="D184" s="3" t="inlineStr">
         <is>
-          <t>Dubai, United Arab Emirates</t>
+          <t>United Arab Emirates</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
@@ -12102,7 +12102,7 @@
       </c>
       <c r="H184" s="3" t="inlineStr">
         <is>
-          <t>This is an AI Image Specialist role focused on generative visual design and creative production (Midjourney, DALL-E, image synthesis), which is completely unrelated to the candidate's core specialization in LLMs, RAG, LangChain, and agentic AI pipelines for data science and enterprise applications.</t>
+          <t>This role is completely unrelated to the candidate's specialization in Generative AI, LLMs, and agentic workflows, focusing instead on medical imaging, computational biology, and clinical research requiring a PhD.</t>
         </is>
       </c>
       <c r="I184" s="3" t="inlineStr">
@@ -12112,7 +12112,7 @@
       </c>
       <c r="J184" s="3" t="inlineStr">
         <is>
-          <t>Yes - explicitly stated in JD</t>
+          <t>Not stated in JD</t>
         </is>
       </c>
       <c r="K184" s="2" t="inlineStr">
@@ -12127,7 +12127,7 @@
       </c>
       <c r="M184" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/ai-image-specialist-at-puffy-4457756193?position=10&amp;pageNum=0&amp;refId=50H6yCrEXIuhgr6eqEojNg%3D%3D&amp;trackingId=9EIvgvUNu%2BE37717JffiJA%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/member-of-technical-staff-medical-research-remote-at-hire-feed-4459638503?position=3&amp;pageNum=0&amp;refId=W92GFmCMxOQHlXfyvp17MQ%3D%3D&amp;trackingId=b91zxKPZNgdFnMmW%2FlYbHA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -12137,12 +12137,12 @@
       </c>
       <c r="B185" s="3" t="inlineStr">
         <is>
-          <t>Market Operations &amp; Analytics Specialist — Institutional</t>
+          <t>AI Image Specialist</t>
         </is>
       </c>
       <c r="C185" s="3" t="inlineStr">
         <is>
-          <t>Confidential</t>
+          <t>Puffy</t>
         </is>
       </c>
       <c r="D185" s="3" t="inlineStr">
@@ -12152,7 +12152,7 @@
       </c>
       <c r="E185" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F185" s="7" t="n">
@@ -12165,7 +12165,7 @@
       </c>
       <c r="H185" s="3" t="inlineStr">
         <is>
-          <t>This role is completely unrelated to data science, artificial intelligence, LLMs, or generative AI, focusing entirely on cryptocurrency exchange operations, institutional client management, and trading analytics instead.</t>
+          <t>This is an AI Image Specialist role focused on generative visual design and creative production (Midjourney, DALL-E, image synthesis), which is completely unrelated to the candidate's core specialization in LLMs, RAG, LangChain, and agentic AI pipelines for data science and enterprise applications.</t>
         </is>
       </c>
       <c r="I185" s="3" t="inlineStr">
@@ -12175,7 +12175,7 @@
       </c>
       <c r="J185" s="3" t="inlineStr">
         <is>
-          <t>Not stated in JD</t>
+          <t>Yes - explicitly stated in JD</t>
         </is>
       </c>
       <c r="K185" s="2" t="inlineStr">
@@ -12190,7 +12190,7 @@
       </c>
       <c r="M185" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/market-operations-analytics-specialist-%E2%80%94-institutional-at-confidential-4453037100?position=10&amp;pageNum=0&amp;refId=zJBbvwb5H0wsbJ5fs9ZTVw%3D%3D&amp;trackingId=ENnWCvoEQXOg1fXKuxlBug%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/ai-image-specialist-at-puffy-4457756193?position=10&amp;pageNum=0&amp;refId=50H6yCrEXIuhgr6eqEojNg%3D%3D&amp;trackingId=9EIvgvUNu%2BE37717JffiJA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -12200,22 +12200,22 @@
       </c>
       <c r="B186" s="3" t="inlineStr">
         <is>
-          <t>Quantitative Developer, Systematic Equities</t>
+          <t>Market Operations &amp; Analytics Specialist — Institutional</t>
         </is>
       </c>
       <c r="C186" s="3" t="inlineStr">
         <is>
-          <t>Millennium</t>
+          <t>Confidential</t>
         </is>
       </c>
       <c r="D186" s="3" t="inlineStr">
         <is>
-          <t>Dubai, Dubai, United Arab Emirates</t>
+          <t>Dubai, United Arab Emirates</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="F186" s="7" t="n">
@@ -12228,7 +12228,7 @@
       </c>
       <c r="H186" s="3" t="inlineStr">
         <is>
-          <t>This role is a quantitative software engineering position focused on low-latency trading infrastructure, C++/C# development, and execution systems for a hedge fund, which is entirely unrelated to the candidate's specialization in GenAI, LLMs, and agentic architectures.</t>
+          <t>This role is completely unrelated to data science, artificial intelligence, LLMs, or generative AI, focusing entirely on cryptocurrency exchange operations, institutional client management, and trading analytics instead.</t>
         </is>
       </c>
       <c r="I186" s="3" t="inlineStr">
@@ -12253,7 +12253,7 @@
       </c>
       <c r="M186" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/quantitative-developer-systematic-equities-at-millennium-4290849018?position=6&amp;pageNum=0&amp;refId=zJBbvwb5H0wsbJ5fs9ZTVw%3D%3D&amp;trackingId=8TTWkyG2j%2F7MELtLSQ5VCA%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/market-operations-analytics-specialist-%E2%80%94-institutional-at-confidential-4453037100?position=10&amp;pageNum=0&amp;refId=zJBbvwb5H0wsbJ5fs9ZTVw%3D%3D&amp;trackingId=ENnWCvoEQXOg1fXKuxlBug%3D%3D</t>
         </is>
       </c>
     </row>
@@ -12263,12 +12263,12 @@
       </c>
       <c r="B187" s="3" t="inlineStr">
         <is>
-          <t>Senior Specialist - Portfolio Management</t>
+          <t>Quantitative Developer, Systematic Equities</t>
         </is>
       </c>
       <c r="C187" s="3" t="inlineStr">
         <is>
-          <t>MENA Careers</t>
+          <t>Millennium</t>
         </is>
       </c>
       <c r="D187" s="3" t="inlineStr">
@@ -12278,7 +12278,7 @@
       </c>
       <c r="E187" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F187" s="7" t="n">
@@ -12291,7 +12291,7 @@
       </c>
       <c r="H187" s="3" t="inlineStr">
         <is>
-          <t>This is a non-AI banking role focused on portfolio management, loan optimization, and regulatory capital compliance in Dubai requiring UAE nationality, which completely misaligns with the candidate's GenAI, LLM, and data science specialization.</t>
+          <t>This role is a quantitative software engineering position focused on low-latency trading infrastructure, C++/C# development, and execution systems for a hedge fund, which is entirely unrelated to the candidate's specialization in GenAI, LLMs, and agentic architectures.</t>
         </is>
       </c>
       <c r="I187" s="3" t="inlineStr">
@@ -12316,7 +12316,7 @@
       </c>
       <c r="M187" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/senior-specialist-portfolio-management-at-mena-careers-4458066015?position=12&amp;pageNum=0&amp;refId=umynRMWB8laV9lcrAC5yvg%3D%3D&amp;trackingId=kbnf5IoX2jxOWD9%2Fe1UaKg%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/quantitative-developer-systematic-equities-at-millennium-4290849018?position=6&amp;pageNum=0&amp;refId=zJBbvwb5H0wsbJ5fs9ZTVw%3D%3D&amp;trackingId=8TTWkyG2j%2F7MELtLSQ5VCA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -12326,12 +12326,12 @@
       </c>
       <c r="B188" s="3" t="inlineStr">
         <is>
-          <t>Manager Logistics Performance</t>
+          <t>Senior Specialist - Portfolio Management</t>
         </is>
       </c>
       <c r="C188" s="3" t="inlineStr">
         <is>
-          <t>talabat</t>
+          <t>MENA Careers</t>
         </is>
       </c>
       <c r="D188" s="3" t="inlineStr">
@@ -12354,12 +12354,12 @@
       </c>
       <c r="H188" s="3" t="inlineStr">
         <is>
-          <t>This is a commercial operations, logistics, and P&amp;L management role completely unrelated to data science, artificial intelligence, or Large Language Models. It requires background in marketplace operations, logistics, or quick-commerce rather than GenAI engineering.</t>
+          <t>This is a non-AI banking role focused on portfolio management, loan optimization, and regulatory capital compliance in Dubai requiring UAE nationality, which completely misaligns with the candidate's GenAI, LLM, and data science specialization.</t>
         </is>
       </c>
       <c r="I188" s="3" t="inlineStr">
         <is>
-          <t>Yes - German required (see JD for exact level)</t>
+          <t>Not stated in JD</t>
         </is>
       </c>
       <c r="J188" s="3" t="inlineStr">
@@ -12379,7 +12379,7 @@
       </c>
       <c r="M188" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/jobs/view/manager-logistics-performance-at-talabat-4440740657?position=7&amp;pageNum=0&amp;refId=umynRMWB8laV9lcrAC5yvg%3D%3D&amp;trackingId=lMQWp6LAUNLwXpGhMCpl2Q%3D%3D</t>
+          <t>https://ae.linkedin.com/jobs/view/senior-specialist-portfolio-management-at-mena-careers-4458066015?position=12&amp;pageNum=0&amp;refId=umynRMWB8laV9lcrAC5yvg%3D%3D&amp;trackingId=kbnf5IoX2jxOWD9%2Fe1UaKg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -12389,17 +12389,17 @@
       </c>
       <c r="B189" s="3" t="inlineStr">
         <is>
-          <t>Perception Engineer</t>
+          <t>Manager Logistics Performance</t>
         </is>
       </c>
       <c r="C189" s="3" t="inlineStr">
         <is>
-          <t>Careernet</t>
+          <t>talabat</t>
         </is>
       </c>
       <c r="D189" s="3" t="inlineStr">
         <is>
-          <t>Ajman, Ajman Emirate, United Arab Emirates</t>
+          <t>Dubai, Dubai, United Arab Emirates</t>
         </is>
       </c>
       <c r="E189" s="2" t="inlineStr">
@@ -12417,93 +12417,156 @@
       </c>
       <c r="H189" s="3" t="inlineStr">
         <is>
+          <t>This is a commercial operations, logistics, and P&amp;L management role completely unrelated to data science, artificial intelligence, or Large Language Models. It requires background in marketplace operations, logistics, or quick-commerce rather than GenAI engineering.</t>
+        </is>
+      </c>
+      <c r="I189" s="3" t="inlineStr">
+        <is>
+          <t>Yes - German required (see JD for exact level)</t>
+        </is>
+      </c>
+      <c r="J189" s="3" t="inlineStr">
+        <is>
+          <t>Not stated in JD</t>
+        </is>
+      </c>
+      <c r="K189" s="2" t="inlineStr">
+        <is>
+          <t>From previous run</t>
+        </is>
+      </c>
+      <c r="L189" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="M189" s="6" t="inlineStr">
+        <is>
+          <t>https://ae.linkedin.com/jobs/view/manager-logistics-performance-at-talabat-4440740657?position=7&amp;pageNum=0&amp;refId=umynRMWB8laV9lcrAC5yvg%3D%3D&amp;trackingId=lMQWp6LAUNLwXpGhMCpl2Q%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="190" ht="55" customHeight="1">
+      <c r="A190" s="2" t="n">
+        <v>189</v>
+      </c>
+      <c r="B190" s="3" t="inlineStr">
+        <is>
+          <t>Perception Engineer</t>
+        </is>
+      </c>
+      <c r="C190" s="3" t="inlineStr">
+        <is>
+          <t>Careernet</t>
+        </is>
+      </c>
+      <c r="D190" s="3" t="inlineStr">
+        <is>
+          <t>Ajman, Ajman Emirate, United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="E190" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="F190" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G190" s="8" t="inlineStr">
+        <is>
+          <t>Below threshold</t>
+        </is>
+      </c>
+      <c r="H190" s="3" t="inlineStr">
+        <is>
           <t>This is a hardware-focused Perception Engineer role centering on 2D/3D computer vision, camera calibration, point clouds, and robotics. It is completely unrelated to the candidate's specialization in GenAI, LLMs, RAG, and agentic AI.</t>
         </is>
       </c>
-      <c r="I189" s="3" t="inlineStr">
-        <is>
-          <t>Not stated in JD</t>
-        </is>
-      </c>
-      <c r="J189" s="3" t="inlineStr">
-        <is>
-          <t>Not stated in JD</t>
-        </is>
-      </c>
-      <c r="K189" s="2" t="inlineStr">
-        <is>
-          <t>From previous run</t>
-        </is>
-      </c>
-      <c r="L189" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="M189" s="6" t="inlineStr">
+      <c r="I190" s="3" t="inlineStr">
+        <is>
+          <t>Not stated in JD</t>
+        </is>
+      </c>
+      <c r="J190" s="3" t="inlineStr">
+        <is>
+          <t>Not stated in JD</t>
+        </is>
+      </c>
+      <c r="K190" s="2" t="inlineStr">
+        <is>
+          <t>From previous run</t>
+        </is>
+      </c>
+      <c r="L190" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="M190" s="6" t="inlineStr">
         <is>
           <t>https://ae.linkedin.com/jobs/view/perception-engineer-at-careernet-4458403150?position=10&amp;pageNum=0&amp;refId=umynRMWB8laV9lcrAC5yvg%3D%3D&amp;trackingId=8I7i%2FeIdinpIC7lB70K7fg%3D%3D</t>
         </is>
       </c>
     </row>
-    <row r="190" ht="55" customHeight="1">
-      <c r="A190" s="10" t="n">
-        <v>189</v>
-      </c>
-      <c r="B190" s="11" t="inlineStr">
+    <row r="191" ht="55" customHeight="1">
+      <c r="A191" s="10" t="n">
+        <v>190</v>
+      </c>
+      <c r="B191" s="11" t="inlineStr">
         <is>
           <t>Data Scientist</t>
         </is>
       </c>
-      <c r="C190" s="11" t="inlineStr">
+      <c r="C191" s="11" t="inlineStr">
         <is>
           <t>Magno IT Recruitment</t>
         </is>
       </c>
-      <c r="D190" s="11" t="inlineStr">
+      <c r="D191" s="11" t="inlineStr">
         <is>
           <t>Amsterdam, North Holland, Netherlands</t>
         </is>
       </c>
-      <c r="E190" s="10" t="inlineStr">
+      <c r="E191" s="10" t="inlineStr">
         <is>
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F190" s="10" t="n">
+      <c r="F191" s="10" t="n">
         <v>92</v>
       </c>
-      <c r="G190" s="12" t="inlineStr">
+      <c r="G191" s="12" t="inlineStr">
         <is>
           <t>APPLY</t>
         </is>
       </c>
-      <c r="H190" s="11" t="inlineStr">
+      <c r="H191" s="11" t="inlineStr">
         <is>
           <t>This Senior AI Engineer role is an exceptional technical match, focusing directly on LLMs, RAG, agentic AI applications, and semantic search which align precisely with the candidate's core specialization. The seniority level (Senior) fits the candidate's 10+ years of experience very well.</t>
         </is>
       </c>
-      <c r="I190" s="11" t="inlineStr">
-        <is>
-          <t>Not stated in JD</t>
-        </is>
-      </c>
-      <c r="J190" s="11" t="inlineStr">
-        <is>
-          <t>Not stated in JD</t>
-        </is>
-      </c>
-      <c r="K190" s="10" t="inlineStr">
-        <is>
-          <t>From previous run</t>
-        </is>
-      </c>
-      <c r="L190" s="10" t="inlineStr">
+      <c r="I191" s="11" t="inlineStr">
+        <is>
+          <t>Not stated in JD</t>
+        </is>
+      </c>
+      <c r="J191" s="11" t="inlineStr">
+        <is>
+          <t>Not stated in JD</t>
+        </is>
+      </c>
+      <c r="K191" s="10" t="inlineStr">
+        <is>
+          <t>From previous run</t>
+        </is>
+      </c>
+      <c r="L191" s="10" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="M190" s="13" t="inlineStr">
+      <c r="M191" s="13" t="inlineStr">
         <is>
           <t>https://nl.linkedin.com/jobs/view/data-scientist-at-magno-it-recruitment-4448992517?position=9&amp;pageNum=0&amp;refId=AM27LUOGtvYOeETm648UMw%3D%3D&amp;trackingId=26%2BZzuSXNPWrglox%2BL4Wqg%3D%3D</t>
         </is>
@@ -12700,6 +12763,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M188" r:id="rId187"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M189" r:id="rId188"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M191" r:id="rId190"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
